--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="1958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1960">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954605102539</t>
+    <t xml:space="preserve">42.4954566955566</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0423049926758</t>
+    <t xml:space="preserve">43.2980880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.042308807373</t>
   </si>
   <si>
     <t xml:space="preserve">42.9276466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8218040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1514701843262</t>
+    <t xml:space="preserve">42.8218002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1514739990234</t>
   </si>
   <si>
     <t xml:space="preserve">42.4689979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7281036376953</t>
+    <t xml:space="preserve">41.7281112670898</t>
   </si>
   <si>
     <t xml:space="preserve">41.2870979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9993591308594</t>
+    <t xml:space="preserve">39.9993476867676</t>
   </si>
   <si>
     <t xml:space="preserve">39.2761039733887</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0765571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443824768066</t>
+    <t xml:space="preserve">38.0765609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443748474121</t>
   </si>
   <si>
     <t xml:space="preserve">38.9585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2551422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606353759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3664817810059</t>
+    <t xml:space="preserve">40.2551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2606315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3664741516113</t>
   </si>
   <si>
     <t xml:space="preserve">42.777702331543</t>
@@ -104,130 +104,130 @@
     <t xml:space="preserve">43.0687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2341766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4172248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7590370178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0148277282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6057739257812</t>
+    <t xml:space="preserve">42.9982109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780479431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2341728210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4172286987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7590484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.014820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6057777404785</t>
   </si>
   <si>
     <t xml:space="preserve">38.4029159545898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1228446960449</t>
+    <t xml:space="preserve">40.1228408813477</t>
   </si>
   <si>
     <t xml:space="preserve">40.3962631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4932861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4017639160156</t>
+    <t xml:space="preserve">40.4932899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4017562866211</t>
   </si>
   <si>
     <t xml:space="preserve">42.5483818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9397926330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5924758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.209888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2275314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5571975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.807487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7071342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7600631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7578926086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3521575927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0081787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1636161804199</t>
+    <t xml:space="preserve">41.9397850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2098922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9011878967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2275276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.557201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8074913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6454010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7071380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.760066986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7578887939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3521614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0081825256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1636199951172</t>
   </si>
   <si>
     <t xml:space="preserve">40.5726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1581230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6200904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1140174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2904205322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8405876159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1316604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4668235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1007270812988</t>
+    <t xml:space="preserve">40.1581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6200828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1140098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2904167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8405952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1316566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4668273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1007194519043</t>
   </si>
   <si>
     <t xml:space="preserve">44.7622375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2914390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8647575378418</t>
+    <t xml:space="preserve">45.2914428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8647537231445</t>
   </si>
   <si>
     <t xml:space="preserve">45.3796424865723</t>
   </si>
   <si>
-    <t xml:space="preserve">45.688346862793</t>
+    <t xml:space="preserve">45.6883544921875</t>
   </si>
   <si>
     <t xml:space="preserve">46.8349685668945</t>
@@ -236,346 +236,346 @@
     <t xml:space="preserve">45.9088516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4237480163574</t>
+    <t xml:space="preserve">45.4237518310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.203239440918</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8945426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9386367797852</t>
+    <t xml:space="preserve">44.89453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9386405944824</t>
   </si>
   <si>
     <t xml:space="preserve">45.3355484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7181358337402</t>
+    <t xml:space="preserve">44.8063278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7181282043457</t>
   </si>
   <si>
     <t xml:space="preserve">45.2473449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9827346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8504371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7765502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8206520080566</t>
+    <t xml:space="preserve">44.9827423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8504409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.776554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8206558227539</t>
   </si>
   <si>
     <t xml:space="preserve">46.3057556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1734504699707</t>
+    <t xml:space="preserve">46.173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.261661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6144638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.085262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.422664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5119781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1100807189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5836715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2358779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0748710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1641807556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9855575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7352485656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6188926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9314727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0924758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.011344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.038387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8962554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7446823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.414493560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.137134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9409065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8339881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0302124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2629165649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.861026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7987670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9949913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7717208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2805328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.191219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6201591491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5849304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0937385559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1654357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3440551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3711013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1207809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6648025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6824111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6377639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2453155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7541160583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.441535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.352222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8880805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.084300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4591407775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4767608642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2981376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9773864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5132369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6918563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346176147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2899627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7094688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736106872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270698547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1465682983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.905689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0126037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6459350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8245506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3239250183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7258110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3956260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6635513305664</t>
   </si>
   <si>
     <t xml:space="preserve">46.2616653442383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6144638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0852546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.422664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5119781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1100883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5836791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5660629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2358741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0748710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9679489135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1641807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7000312805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9855613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7352485656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.618896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.092472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0113487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0383911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8962478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7446823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.414493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1371307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9409065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.030216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2182655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2629203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.575496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.798770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9949951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7717247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2805290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6201553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5849342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1654396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.37109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1207847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0666885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6648025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6824150085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6377601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2453079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7541122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4415321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3522300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8880805969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0843048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4591407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4767608642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2981338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9773864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5132369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6918563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346176147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2899627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7094650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1465682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.905689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0126037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.645938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8245468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3239250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7258148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.547191619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.395622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6635437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2616577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7704620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1277008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5742378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4402809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9937362670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4578895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.68115234375</t>
+    <t xml:space="preserve">45.7704658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1276969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4402770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9937400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4578819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811561584473</t>
   </si>
   <si>
     <t xml:space="preserve">46.5295829772949</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">47.2440528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4673194885254</t>
+    <t xml:space="preserve">47.4673233032227</t>
   </si>
   <si>
     <t xml:space="preserve">49.2088279724121</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3698387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.156005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5037994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8515968322754</t>
+    <t xml:space="preserve">50.3698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1560096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5038032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8516006469727</t>
   </si>
   <si>
     <t xml:space="preserve">49.6107177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8163833618164</t>
+    <t xml:space="preserve">50.8163795471191</t>
   </si>
   <si>
     <t xml:space="preserve">51.1289558410645</t>
@@ -623,106 +623,106 @@
     <t xml:space="preserve">53.3616638183594</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4063148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4509773254395</t>
+    <t xml:space="preserve">53.406322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4509696960449</t>
   </si>
   <si>
     <t xml:space="preserve">53.6742362976074</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9151229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2723579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8528633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7905883789062</t>
+    <t xml:space="preserve">52.9151191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2723617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7905921936035</t>
   </si>
   <si>
     <t xml:space="preserve">55.5943717956543</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3264427185059</t>
+    <t xml:space="preserve">55.3264465332031</t>
   </si>
   <si>
     <t xml:space="preserve">55.5050582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2641792297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1302146911621</t>
+    <t xml:space="preserve">56.2641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1302185058594</t>
   </si>
   <si>
     <t xml:space="preserve">55.6390190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8000297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5321044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9786415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
+    <t xml:space="preserve">56.8000259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5321006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.978645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251937866211</t>
   </si>
   <si>
     <t xml:space="preserve">57.3358764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0503387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8987731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0327415466309</t>
+    <t xml:space="preserve">58.0503425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8987770080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0327339172363</t>
   </si>
   <si>
     <t xml:space="preserve">58.7648124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0950050354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1572608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3805351257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5861930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0151214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9434242248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.300666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440689086914</t>
+    <t xml:space="preserve">58.0950012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3805313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5862007141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9434280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3006629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440650939941</t>
   </si>
   <si>
     <t xml:space="preserve">63.4088363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1585235595703</t>
+    <t xml:space="preserve">62.158519744873</t>
   </si>
   <si>
     <t xml:space="preserve">61.6226692199707</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">61.8906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8283424377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3818016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7390213012695</t>
+    <t xml:space="preserve">62.8283348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7390098571777</t>
   </si>
   <si>
     <t xml:space="preserve">62.5157585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8635520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937370300293</t>
+    <t xml:space="preserve">60.8635597229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937408447266</t>
   </si>
   <si>
     <t xml:space="preserve">60.9528694152832</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">61.6758079528809</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9469184875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824432373047</t>
+    <t xml:space="preserve">61.9468955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0824508666992</t>
   </si>
   <si>
     <t xml:space="preserve">62.3083763122559</t>
   </si>
   <si>
-    <t xml:space="preserve">62.534294128418</t>
+    <t xml:space="preserve">62.5342826843262</t>
   </si>
   <si>
     <t xml:space="preserve">61.4950714111328</t>
@@ -776,109 +776,109 @@
     <t xml:space="preserve">63.4379692077637</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4831466674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5675582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0705490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5164260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668586730957</t>
+    <t xml:space="preserve">63.7542533874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4831390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5675735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0705261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8386611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5164337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1668663024902</t>
   </si>
   <si>
     <t xml:space="preserve">63.031307220459</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5223846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8898086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4320068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2964630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1609039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6971588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6425323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721328735352</t>
+    <t xml:space="preserve">64.5223770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8898124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4320297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2964553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1609115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.697151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0884132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6425361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721214294434</t>
   </si>
   <si>
     <t xml:space="preserve">60.1847381591797</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8173217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5462188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6877288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.449893951416</t>
+    <t xml:space="preserve">60.8173141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5462074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6877174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.449878692627</t>
   </si>
   <si>
     <t xml:space="preserve">62.398738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2120513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735282897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2393569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7815628051758</t>
+    <t xml:space="preserve">63.212043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2393646240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7815704345703</t>
   </si>
   <si>
     <t xml:space="preserve">66.0134429931641</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5104675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3297271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.96826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778991699219</t>
+    <t xml:space="preserve">66.5104446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3297348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9682388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778915405273</t>
   </si>
   <si>
     <t xml:space="preserve">65.6067810058594</t>
@@ -887,31 +887,31 @@
     <t xml:space="preserve">65.019401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2001419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7483062744141</t>
+    <t xml:space="preserve">65.2001266479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7482986450195</t>
   </si>
   <si>
     <t xml:space="preserve">64.7934722900391</t>
   </si>
   <si>
-    <t xml:space="preserve">64.6579360961914</t>
+    <t xml:space="preserve">64.6579284667969</t>
   </si>
   <si>
     <t xml:space="preserve">64.4771881103516</t>
   </si>
   <si>
-    <t xml:space="preserve">63.980167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3024253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4260559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4712295532227</t>
+    <t xml:space="preserve">63.9801826477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3024139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4260406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
     <t xml:space="preserve">66.284538269043</t>
@@ -920,31 +920,31 @@
     <t xml:space="preserve">66.600830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4652938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8719253540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0586090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3749084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6912002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141387939453</t>
+    <t xml:space="preserve">66.4652709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8719329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0586242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3749160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6911926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141311645508</t>
   </si>
   <si>
     <t xml:space="preserve">68.5437316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1370697021484</t>
+    <t xml:space="preserve">68.1370620727539</t>
   </si>
   <si>
     <t xml:space="preserve">67.865966796875</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">67.9563446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1822509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1311111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3059005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3903045654297</t>
+    <t xml:space="preserve">68.182258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1311264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776840209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3903121948242</t>
   </si>
   <si>
     <t xml:space="preserve">71.5258636474609</t>
@@ -977,43 +977,43 @@
     <t xml:space="preserve">70.8481140136719</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1643981933594</t>
+    <t xml:space="preserve">71.1643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">72.7910079956055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8932800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2607192993164</t>
+    <t xml:space="preserve">70.8932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2607040405273</t>
   </si>
   <si>
     <t xml:space="preserve">70.3510818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5318298339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866333007812</t>
+    <t xml:space="preserve">70.5318069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866256713867</t>
   </si>
   <si>
     <t xml:space="preserve">70.5770034790039</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3451232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4414443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5710296630859</t>
+    <t xml:space="preserve">71.3451156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4414367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5710372924805</t>
   </si>
   <si>
     <t xml:space="preserve">70.9836578369141</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">65.5616073608398</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4593200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8207778930664</t>
+    <t xml:space="preserve">67.4593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">69.2666625976562</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0347900390625</t>
+    <t xml:space="preserve">70.034782409668</t>
   </si>
   <si>
     <t xml:space="preserve">69.7636871337891</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3237762451172</t>
+    <t xml:space="preserve">67.3237686157227</t>
   </si>
   <si>
     <t xml:space="preserve">68.3629989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">69.040771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1763153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9444198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1703414916992</t>
+    <t xml:space="preserve">69.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1763000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9444274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1703491210938</t>
   </si>
   <si>
     <t xml:space="preserve">71.887336730957</t>
@@ -1073,46 +1073,46 @@
     <t xml:space="preserve">69.8992385864258</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4985580444336</t>
+    <t xml:space="preserve">68.4985656738281</t>
   </si>
   <si>
     <t xml:space="preserve">68.4081726074219</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2785873413086</t>
+    <t xml:space="preserve">67.2785797119141</t>
   </si>
   <si>
     <t xml:space="preserve">67.6400604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">69.402229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6162338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9325180053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0228729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7065811157227</t>
+    <t xml:space="preserve">69.4022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9325103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0228881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7065963745117</t>
   </si>
   <si>
     <t xml:space="preserve">71.4806747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4354858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6614227294922</t>
+    <t xml:space="preserve">71.4354934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614074707031</t>
   </si>
   <si>
     <t xml:space="preserve">71.254753112793</t>
@@ -1121,61 +1121,61 @@
     <t xml:space="preserve">69.8088684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7517852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0918960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9623107910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572364807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6187133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0765075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9409561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602119445801</t>
+    <t xml:space="preserve">71.7517776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6187057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0764961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9409484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602043151855</t>
   </si>
   <si>
     <t xml:space="preserve">61.9017181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9528579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7329063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113632202148</t>
+    <t xml:space="preserve">60.9528656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0040054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7329025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.811351776123</t>
   </si>
   <si>
     <t xml:space="preserve">63.7994384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">67.549690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7363815307617</t>
+    <t xml:space="preserve">67.549674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7363891601562</t>
   </si>
   <si>
     <t xml:space="preserve">65.2453079223633</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">65.6519775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2904968261719</t>
+    <t xml:space="preserve">65.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">66.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2726364135742</t>
+    <t xml:space="preserve">68.2726287841797</t>
   </si>
   <si>
     <t xml:space="preserve">70.1251678466797</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">68.8600082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8540725708008</t>
+    <t xml:space="preserve">69.8540573120117</t>
   </si>
   <si>
     <t xml:space="preserve">70.622184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1192092895508</t>
+    <t xml:space="preserve">71.1192016601562</t>
   </si>
   <si>
     <t xml:space="preserve">71.0740203857422</t>
@@ -1223,31 +1223,31 @@
     <t xml:space="preserve">72.474723815918</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4687652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1976547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3783950805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6887283325195</t>
+    <t xml:space="preserve">73.46875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1976699829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3783874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6887130737305</t>
   </si>
   <si>
     <t xml:space="preserve">73.5591278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">74.198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919692993164</t>
+    <t xml:space="preserve">74.1983642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919464111328</t>
   </si>
   <si>
     <t xml:space="preserve">73.6961059570312</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9289398193359</t>
+    <t xml:space="preserve">74.9289474487305</t>
   </si>
   <si>
     <t xml:space="preserve">76.8466796875</t>
@@ -1259,28 +1259,28 @@
     <t xml:space="preserve">74.152717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">77.2576293945312</t>
+    <t xml:space="preserve">77.2576370239258</t>
   </si>
   <si>
     <t xml:space="preserve">75.4312057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0795288085938</t>
+    <t xml:space="preserve">78.0795135498047</t>
   </si>
   <si>
     <t xml:space="preserve">79.9059371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">80.5908432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.362548828125</t>
+    <t xml:space="preserve">80.5908508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3625335693359</t>
   </si>
   <si>
     <t xml:space="preserve">80.7278289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">80.2712249755859</t>
+    <t xml:space="preserve">80.2712326049805</t>
   </si>
   <si>
     <t xml:space="preserve">81.230094909668</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">83.102180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">84.3806686401367</t>
+    <t xml:space="preserve">84.3806838989258</t>
   </si>
   <si>
     <t xml:space="preserve">85.2482223510742</t>
@@ -1301,43 +1301,43 @@
     <t xml:space="preserve">84.2893600463867</t>
   </si>
   <si>
-    <t xml:space="preserve">83.056510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8006744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3942565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8554000854492</t>
+    <t xml:space="preserve">83.0565185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.412727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8006820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3942718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8553924560547</t>
   </si>
   <si>
     <t xml:space="preserve">87.9878540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2206954956055</t>
+    <t xml:space="preserve">89.2206878662109</t>
   </si>
   <si>
     <t xml:space="preserve">87.9421920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">89.0380401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572784423828</t>
+    <t xml:space="preserve">89.0380477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2572860717773</t>
   </si>
   <si>
     <t xml:space="preserve">87.485595703125</t>
@@ -1346,52 +1346,52 @@
     <t xml:space="preserve">87.5769195556641</t>
   </si>
   <si>
-    <t xml:space="preserve">87.8052215576172</t>
+    <t xml:space="preserve">87.8052139282227</t>
   </si>
   <si>
     <t xml:space="preserve">89.6772918701172</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1750335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4033355712891</t>
+    <t xml:space="preserve">89.1750259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4033203125</t>
   </si>
   <si>
     <t xml:space="preserve">88.1248321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6225662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3531494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2984161376953</t>
+    <t xml:space="preserve">87.6225738525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3531341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2984085083008</t>
   </si>
   <si>
     <t xml:space="preserve">85.8418045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">86.1614227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4719848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8327484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7689514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474395751953</t>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4719924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6685791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474472045898</t>
   </si>
   <si>
     <t xml:space="preserve">80.2255630493164</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">80.453857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">79.358024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4995346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123474121094</t>
+    <t xml:space="preserve">79.3580169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4995269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123550415039</t>
   </si>
   <si>
     <t xml:space="preserve">85.1112365722656</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">83.5587844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8783950805664</t>
+    <t xml:space="preserve">83.87841796875</t>
   </si>
   <si>
     <t xml:space="preserve">83.6501007080078</t>
@@ -1430,142 +1430,142 @@
     <t xml:space="preserve">83.2391586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">83.7414321899414</t>
+    <t xml:space="preserve">83.7414245605469</t>
   </si>
   <si>
     <t xml:space="preserve">84.8372802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6591567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6410522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9149932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0018005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2757568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.53125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2436981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.882942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7368850708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3761367797852</t>
+    <t xml:space="preserve">85.6591644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3349990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9150009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0017852783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.275749206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8282089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5312423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.882926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7368774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">81.4583969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2666931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1572494506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4266738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8376235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6002502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9198684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5179977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4357452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8285522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9700698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.06591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5270614624023</t>
+    <t xml:space="preserve">79.2667007446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.1572418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4266815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.330810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8376083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6002578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5179901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4357376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8285675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8330841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.2806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9700622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0659103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.5270690917969</t>
   </si>
   <si>
     <t xml:space="preserve">79.9515991210938</t>
   </si>
   <si>
-    <t xml:space="preserve">75.3398895263672</t>
+    <t xml:space="preserve">75.3398818969727</t>
   </si>
   <si>
     <t xml:space="preserve">76.1161193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0568695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5455322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6825103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0934600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9609985351562</t>
+    <t xml:space="preserve">73.0568542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5455169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6824951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0934448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9610061645508</t>
   </si>
   <si>
     <t xml:space="preserve">73.1025238037109</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3262786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0478057861328</t>
+    <t xml:space="preserve">72.3262939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477905273438</t>
   </si>
   <si>
     <t xml:space="preserve">70.8651504516602</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">68.5821304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4908142089844</t>
+    <t xml:space="preserve">68.4908065795898</t>
   </si>
   <si>
     <t xml:space="preserve">68.8560943603516</t>
@@ -1583,37 +1583,37 @@
     <t xml:space="preserve">71.3217620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8013687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3949508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9383544921875</t>
+    <t xml:space="preserve">66.8013610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3949432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.938346862793</t>
   </si>
   <si>
     <t xml:space="preserve">66.6187210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5775909423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8470306396484</t>
+    <t xml:space="preserve">67.5776062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">65.5228805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0160675048828</t>
+    <t xml:space="preserve">64.0160751342773</t>
   </si>
   <si>
     <t xml:space="preserve">64.4270172119141</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2900543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7922973632812</t>
+    <t xml:space="preserve">64.2900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7922897338867</t>
   </si>
   <si>
     <t xml:space="preserve">66.1621170043945</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">66.2089462280273</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6771774291992</t>
+    <t xml:space="preserve">66.6771697998047</t>
   </si>
   <si>
     <t xml:space="preserve">66.3025894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0016784667969</t>
+    <t xml:space="preserve">70.0016632080078</t>
   </si>
   <si>
     <t xml:space="preserve">69.4866027832031</t>
   </si>
   <si>
-    <t xml:space="preserve">69.205680847168</t>
+    <t xml:space="preserve">69.2056655883789</t>
   </si>
   <si>
     <t xml:space="preserve">69.627082824707</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675628662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8913345336914</t>
+    <t xml:space="preserve">69.7675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8913192749023</t>
   </si>
   <si>
     <t xml:space="preserve">72.5769958496094</t>
@@ -1661,61 +1661,61 @@
     <t xml:space="preserve">73.0452194213867</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1054763793945</t>
+    <t xml:space="preserve">75.2459411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.10546875</t>
   </si>
   <si>
     <t xml:space="preserve">74.9650039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">74.5904235839844</t>
+    <t xml:space="preserve">74.5904159545898</t>
   </si>
   <si>
     <t xml:space="preserve">75.0586547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2927780151367</t>
+    <t xml:space="preserve">75.2927703857422</t>
   </si>
   <si>
     <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5570220947266</t>
+    <t xml:space="preserve">76.5570068359375</t>
   </si>
   <si>
     <t xml:space="preserve">76.1355972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8713531494141</t>
+    <t xml:space="preserve">74.8713455200195</t>
   </si>
   <si>
     <t xml:space="preserve">76.8847808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">76.9784240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7109222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.694221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2728042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.6005706787109</t>
+    <t xml:space="preserve">76.9784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7109146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6172637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6942138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2727966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6005630493164</t>
   </si>
   <si>
     <t xml:space="preserve">79.2259826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4132766723633</t>
+    <t xml:space="preserve">79.4132690429688</t>
   </si>
   <si>
     <t xml:space="preserve">79.7878570556641</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">80.0219802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">79.038688659668</t>
+    <t xml:space="preserve">79.0386810302734</t>
   </si>
   <si>
     <t xml:space="preserve">79.8815155029297</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">80.6775207519531</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3029251098633</t>
+    <t xml:space="preserve">80.3029174804688</t>
   </si>
   <si>
     <t xml:space="preserve">80.7711639404297</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">82.0354156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">81.707649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3330459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2394104003906</t>
+    <t xml:space="preserve">81.7076416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3330535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2394027709961</t>
   </si>
   <si>
     <t xml:space="preserve">82.2227096557617</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">81.145751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3497543334961</t>
+    <t xml:space="preserve">80.3497467041016</t>
   </si>
   <si>
     <t xml:space="preserve">79.9751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">82.26953125</t>
+    <t xml:space="preserve">82.2695236206055</t>
   </si>
   <si>
     <t xml:space="preserve">82.5036392211914</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">82.9718780517578</t>
   </si>
   <si>
-    <t xml:space="preserve">84.0488433837891</t>
+    <t xml:space="preserve">84.048828125</t>
   </si>
   <si>
     <t xml:space="preserve">84.0019989013672</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">84.7980117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7813186645508</t>
+    <t xml:space="preserve">85.7813110351562</t>
   </si>
   <si>
     <t xml:space="preserve">86.8582611083984</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">86.1558990478516</t>
   </si>
   <si>
-    <t xml:space="preserve">85.8281326293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6876678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2194366455078</t>
+    <t xml:space="preserve">85.8281402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6876754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2194290161133</t>
   </si>
   <si>
     <t xml:space="preserve">85.1257781982422</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">82.0822372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7410354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5671768188477</t>
+    <t xml:space="preserve">79.7410278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2560882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5671691894531</t>
   </si>
   <si>
     <t xml:space="preserve">81.8481063842773</t>
@@ -1838,73 +1838,73 @@
     <t xml:space="preserve">83.8147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">84.1893005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2829437255859</t>
+    <t xml:space="preserve">84.1892929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.282958984375</t>
   </si>
   <si>
     <t xml:space="preserve">85.3130798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1693267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4803924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2597045898438</t>
+    <t xml:space="preserve">88.1693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4804077148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2596969604492</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6854858398438</t>
+    <t xml:space="preserve">91.6855010986328</t>
   </si>
   <si>
     <t xml:space="preserve">91.1656188964844</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1580963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.543701171875</t>
+    <t xml:space="preserve">92.158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">90.8348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">90.598503112793</t>
+    <t xml:space="preserve">90.5984878540039</t>
   </si>
   <si>
     <t xml:space="preserve">89.1806793212891</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3299789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8025894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5341033935547</t>
+    <t xml:space="preserve">88.3299865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8025970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5340957641602</t>
   </si>
   <si>
     <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3546600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9690551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1033172607422</t>
+    <t xml:space="preserve">91.3546676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9690475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">95.5608520507812</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4115447998047</t>
+    <t xml:space="preserve">96.4115524291992</t>
   </si>
   <si>
     <t xml:space="preserve">93.8122100830078</t>
@@ -1913,49 +1913,49 @@
     <t xml:space="preserve">97.0731887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">97.8293685913086</t>
+    <t xml:space="preserve">97.8293609619141</t>
   </si>
   <si>
     <t xml:space="preserve">99.3417053222656</t>
   </si>
   <si>
-    <t xml:space="preserve">101.326644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2471771240234</t>
+    <t xml:space="preserve">101.326637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.247184753418</t>
   </si>
   <si>
     <t xml:space="preserve">96.884147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6403350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9389495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3170394897461</t>
+    <t xml:space="preserve">97.6403274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9389419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.317024230957</t>
   </si>
   <si>
     <t xml:space="preserve">96.5060653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2622375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9786834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5307540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3019714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.3567504882812</t>
+    <t xml:space="preserve">97.2622451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9786682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3019790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3567657470703</t>
   </si>
   <si>
     <t xml:space="preserve">98.2074432373047</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">97.167724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">97.5457916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2225036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7498931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8444137573242</t>
+    <t xml:space="preserve">97.5457992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2225189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7499008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8444213867188</t>
   </si>
   <si>
     <t xml:space="preserve">95.4663391113281</t>
@@ -1982,10 +1982,10 @@
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475959777832</t>
+    <t xml:space="preserve">102.082809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475967407227</t>
   </si>
   <si>
     <t xml:space="preserve">99.1526641845703</t>
@@ -1997,22 +1997,22 @@
     <t xml:space="preserve">100.665000915527</t>
   </si>
   <si>
-    <t xml:space="preserve">100.097869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.908821105957</t>
+    <t xml:space="preserve">100.097877502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9088287353516</t>
   </si>
   <si>
     <t xml:space="preserve">98.396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">100.192398071289</t>
+    <t xml:space="preserve">100.192390441895</t>
   </si>
   <si>
     <t xml:space="preserve">102.366386413574</t>
   </si>
   <si>
-    <t xml:space="preserve">102.17733001709</t>
+    <t xml:space="preserve">102.177337646484</t>
   </si>
   <si>
     <t xml:space="preserve">103.784194946289</t>
@@ -2021,49 +2021,49 @@
     <t xml:space="preserve">103.028030395508</t>
   </si>
   <si>
-    <t xml:space="preserve">100.003356933594</t>
+    <t xml:space="preserve">100.003349304199</t>
   </si>
   <si>
     <t xml:space="preserve">101.137603759766</t>
   </si>
   <si>
-    <t xml:space="preserve">101.704734802246</t>
+    <t xml:space="preserve">101.704727172852</t>
   </si>
   <si>
     <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">103.500625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.933502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.38143157959</t>
+    <t xml:space="preserve">103.500633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.93350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.381423950195</t>
   </si>
   <si>
     <t xml:space="preserve">98.5855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">96.6951065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.112922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.948554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.286903381348</t>
+    <t xml:space="preserve">96.6951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0581436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.94856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.286918640137</t>
   </si>
   <si>
     <t xml:space="preserve">99.7197875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">100.854042053223</t>
+    <t xml:space="preserve">100.854049682617</t>
   </si>
   <si>
     <t xml:space="preserve">99.6252593994141</t>
@@ -2075,25 +2075,25 @@
     <t xml:space="preserve">94.7101669311523</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8594741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0957870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2848281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6156539916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5211181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6382293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3471374511719</t>
+    <t xml:space="preserve">93.8594818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0957794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2848129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6156463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.521125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6382369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">91.3074035644531</t>
@@ -2102,61 +2102,61 @@
     <t xml:space="preserve">92.2998809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7327575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0163040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1505661010742</t>
+    <t xml:space="preserve">91.7327499389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0163192749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1505737304688</t>
   </si>
   <si>
     <t xml:space="preserve">95.3718185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8690948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9238815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.75951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.122550964355</t>
+    <t xml:space="preserve">94.8046951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8690872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9238891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.759506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.122543334961</t>
   </si>
   <si>
     <t xml:space="preserve">104.634880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">105.95817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.659553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.07738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.574653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.803436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519859313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.654136657715</t>
+    <t xml:space="preserve">105.958183288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.226676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.659561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.077369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.574661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.803421020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.654121398926</t>
   </si>
   <si>
     <t xml:space="preserve">111.818489074707</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977416992188</t>
+    <t xml:space="preserve">115.977424621582</t>
   </si>
   <si>
     <t xml:space="preserve">117.206192016602</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">117.017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">115.315780639648</t>
+    <t xml:space="preserve">115.315765380859</t>
   </si>
   <si>
     <t xml:space="preserve">114.370559692383</t>
@@ -2183,46 +2183,46 @@
     <t xml:space="preserve">113.425346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">109.644493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.251358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.589714050293</t>
+    <t xml:space="preserve">109.644508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.251350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.589721679688</t>
   </si>
   <si>
     <t xml:space="preserve">110.306144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">111.156837463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.723960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.117111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.833541870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.51025390625</t>
+    <t xml:space="preserve">111.156852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.723968505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.062324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.11710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.510261535645</t>
   </si>
   <si>
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291107177734</t>
+    <t xml:space="preserve">112.29109954834</t>
   </si>
   <si>
     <t xml:space="preserve">112.952751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">110.87328338623</t>
+    <t xml:space="preserve">110.873275756836</t>
   </si>
   <si>
     <t xml:space="preserve">109.455467224121</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">106.997909545898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.918441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.769134521484</t>
+    <t xml:space="preserve">104.91845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.769142150879</t>
   </si>
   <si>
     <t xml:space="preserve">107.754081726074</t>
@@ -2267,49 +2267,49 @@
     <t xml:space="preserve">108.415725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">108.321197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.211631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.276039123535</t>
+    <t xml:space="preserve">108.321212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.211639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.27604675293</t>
   </si>
   <si>
     <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
-    <t xml:space="preserve">109.928077697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.540367126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7745742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.808868408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.595146179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.893768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8143081665039</t>
+    <t xml:space="preserve">109.928070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.54035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7745666503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.808876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.595153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.893775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8143005371094</t>
   </si>
   <si>
     <t xml:space="preserve">108.132164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">105.485572814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.400672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.888336181641</t>
+    <t xml:space="preserve">105.485580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.400680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.888320922852</t>
   </si>
   <si>
     <t xml:space="preserve">106.52530670166</t>
@@ -2321,43 +2321,43 @@
     <t xml:space="preserve">102.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">114.086990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.629455566406</t>
+    <t xml:space="preserve">114.08699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.629440307617</t>
   </si>
   <si>
     <t xml:space="preserve">118.056884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">122.310333251953</t>
+    <t xml:space="preserve">122.310317993164</t>
   </si>
   <si>
     <t xml:space="preserve">126.091171264648</t>
   </si>
   <si>
-    <t xml:space="preserve">132.32958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.5830078125</t>
+    <t xml:space="preserve">132.329574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.583023071289</t>
   </si>
   <si>
     <t xml:space="preserve">145.089935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">144.239242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.959854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.383102416992</t>
+    <t xml:space="preserve">144.2392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.959838867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.38313293457</t>
   </si>
   <si>
     <t xml:space="preserve">153.691345214844</t>
@@ -2369,61 +2369,61 @@
     <t xml:space="preserve">157.944808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">153.313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791320800781</t>
+    <t xml:space="preserve">153.313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.791305541992</t>
   </si>
   <si>
     <t xml:space="preserve">146.885818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">146.507751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.522811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.318695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.641983032227</t>
+    <t xml:space="preserve">146.507766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.52278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.318710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.641998291016</t>
   </si>
   <si>
     <t xml:space="preserve">153.596832275391</t>
   </si>
   <si>
-    <t xml:space="preserve">151.706390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.048934936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.302398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.10791015625</t>
+    <t xml:space="preserve">151.706420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.048950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.107925415039</t>
   </si>
   <si>
     <t xml:space="preserve">174.675018310547</t>
   </si>
   <si>
-    <t xml:space="preserve">169.381866455078</t>
+    <t xml:space="preserve">169.381851196289</t>
   </si>
   <si>
     <t xml:space="preserve">178.833969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">180.440841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.688827514648</t>
+    <t xml:space="preserve">180.440811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.688842773438</t>
   </si>
   <si>
     <t xml:space="preserve">197.927215576172</t>
   </si>
   <si>
-    <t xml:space="preserve">186.206634521484</t>
+    <t xml:space="preserve">186.206604003906</t>
   </si>
   <si>
     <t xml:space="preserve">163.521545410156</t>
@@ -2438,28 +2438,28 @@
     <t xml:space="preserve">171.55583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">169.098281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.994155883789</t>
+    <t xml:space="preserve">169.098297119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.994140625</t>
   </si>
   <si>
     <t xml:space="preserve">164.655807495117</t>
   </si>
   <si>
-    <t xml:space="preserve">156.905075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.855712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.651626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.014633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.606460571289</t>
+    <t xml:space="preserve">156.905059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.855697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.651611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.0146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.606430053711</t>
   </si>
   <si>
     <t xml:space="preserve">157.850280761719</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">162.36572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">161.890426635742</t>
+    <t xml:space="preserve">161.890411376953</t>
   </si>
   <si>
     <t xml:space="preserve">161.129913330078</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">159.133605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">162.270629882812</t>
+    <t xml:space="preserve">162.270645141602</t>
   </si>
   <si>
     <t xml:space="preserve">167.118804931641</t>
@@ -2489,37 +2489,37 @@
     <t xml:space="preserve">164.457077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">162.936080932617</t>
+    <t xml:space="preserve">162.936065673828</t>
   </si>
   <si>
     <t xml:space="preserve">161.320022583008</t>
   </si>
   <si>
-    <t xml:space="preserve">161.985458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.55583190918</t>
+    <t xml:space="preserve">161.985473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.555847167969</t>
   </si>
   <si>
     <t xml:space="preserve">162.841033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">162.650909423828</t>
+    <t xml:space="preserve">162.650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.350891113281</t>
+    <t xml:space="preserve">169.685485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.35090637207</t>
   </si>
   <si>
     <t xml:space="preserve">163.031143188477</t>
   </si>
   <si>
-    <t xml:space="preserve">164.361999511719</t>
+    <t xml:space="preserve">164.362014770508</t>
   </si>
   <si>
     <t xml:space="preserve">165.122497558594</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">169.305252075195</t>
   </si>
   <si>
-    <t xml:space="preserve">169.400283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.966949462891</t>
+    <t xml:space="preserve">169.400299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.96696472168</t>
   </si>
   <si>
     <t xml:space="preserve">169.495361328125</t>
@@ -2543,49 +2543,49 @@
     <t xml:space="preserve">166.358306884766</t>
   </si>
   <si>
-    <t xml:space="preserve">160.939804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.66569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.175598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.742279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.228652954102</t>
+    <t xml:space="preserve">160.939788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.665710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.17561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.742263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.22868347168</t>
   </si>
   <si>
     <t xml:space="preserve">157.802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">152.669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.817565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.775543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.768173217773</t>
+    <t xml:space="preserve">152.669403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.81755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.775573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.768188476562</t>
   </si>
   <si>
     <t xml:space="preserve">145.254577636719</t>
   </si>
   <si>
-    <t xml:space="preserve">149.722473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.289154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.62370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.391647338867</t>
+    <t xml:space="preserve">149.72248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.289138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.623733520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.391616821289</t>
   </si>
   <si>
     <t xml:space="preserve">154.760757446289</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">151.24348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">154.190383911133</t>
+    <t xml:space="preserve">154.190368652344</t>
   </si>
   <si>
     <t xml:space="preserve">154.855819702148</t>
@@ -2603,37 +2603,37 @@
     <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">155.426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.806442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.41877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.634811401367</t>
+    <t xml:space="preserve">155.426193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.806427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.418792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.634826660156</t>
   </si>
   <si>
     <t xml:space="preserve">138.600250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">144.018753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.589157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.543441772461</t>
+    <t xml:space="preserve">144.018768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.589126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.54345703125</t>
   </si>
   <si>
     <t xml:space="preserve">135.558288574219</t>
   </si>
   <si>
-    <t xml:space="preserve">134.797760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.364440917969</t>
+    <t xml:space="preserve">134.797775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.36442565918</t>
   </si>
   <si>
     <t xml:space="preserve">137.17431640625</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">143.258270263672</t>
   </si>
   <si>
-    <t xml:space="preserve">147.060745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.726165771484</t>
+    <t xml:space="preserve">147.060760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.726181030273</t>
   </si>
   <si>
     <t xml:space="preserve">149.247177124023</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">150.387908935547</t>
   </si>
   <si>
-    <t xml:space="preserve">161.034851074219</t>
+    <t xml:space="preserve">161.03483581543</t>
   </si>
   <si>
     <t xml:space="preserve">160.654602050781</t>
@@ -2669,16 +2669,16 @@
     <t xml:space="preserve">162.080535888672</t>
   </si>
   <si>
-    <t xml:space="preserve">161.795333862305</t>
+    <t xml:space="preserve">161.795349121094</t>
   </si>
   <si>
     <t xml:space="preserve">163.411376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913864135742</t>
+    <t xml:space="preserve">168.069412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.913879394531</t>
   </si>
   <si>
     <t xml:space="preserve">175.294128417969</t>
@@ -2687,19 +2687,19 @@
     <t xml:space="preserve">177.670669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">173.487945556641</t>
+    <t xml:space="preserve">173.487976074219</t>
   </si>
   <si>
     <t xml:space="preserve">178.716354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">180.712677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.24104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.853408813477</t>
+    <t xml:space="preserve">180.712661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.241058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.853393554688</t>
   </si>
   <si>
     <t xml:space="preserve">179.666976928711</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">184.990447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">184.039840698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.663299560547</t>
+    <t xml:space="preserve">184.039825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.663284301758</t>
   </si>
   <si>
     <t xml:space="preserve">185.275619506836</t>
   </si>
   <si>
-    <t xml:space="preserve">183.089218139648</t>
+    <t xml:space="preserve">183.089202880859</t>
   </si>
   <si>
     <t xml:space="preserve">181.568222045898</t>
@@ -2726,31 +2726,31 @@
     <t xml:space="preserve">179.286758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">178.050933837891</t>
+    <t xml:space="preserve">178.050918579102</t>
   </si>
   <si>
     <t xml:space="preserve">179.191665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">176.529937744141</t>
+    <t xml:space="preserve">176.529922485352</t>
   </si>
   <si>
     <t xml:space="preserve">177.860809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">184.610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.838577270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.264526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.703979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.886703491211</t>
+    <t xml:space="preserve">184.61018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.838607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.264541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.703994750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.88671875</t>
   </si>
   <si>
     <t xml:space="preserve">165.217575073242</t>
@@ -2759,34 +2759,34 @@
     <t xml:space="preserve">164.932388305664</t>
   </si>
   <si>
-    <t xml:space="preserve">164.076858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.947204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.8447265625</t>
+    <t xml:space="preserve">164.076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.947189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.844741821289</t>
   </si>
   <si>
     <t xml:space="preserve">164.266967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">167.879333496094</t>
+    <t xml:space="preserve">167.879318237305</t>
   </si>
   <si>
     <t xml:space="preserve">163.696578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">161.605209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.084228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.745956420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.179306030273</t>
+    <t xml:space="preserve">161.605224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.084243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.745971679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.179290771484</t>
   </si>
   <si>
     <t xml:space="preserve">159.323745727539</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">158.468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">158.848434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.221252441406</t>
+    <t xml:space="preserve">158.848419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.221267700195</t>
   </si>
   <si>
     <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">159.608901977539</t>
+    <t xml:space="preserve">159.608917236328</t>
   </si>
   <si>
     <t xml:space="preserve">161.700302124023</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">161.224975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">153.810150146484</t>
+    <t xml:space="preserve">153.810134887695</t>
   </si>
   <si>
     <t xml:space="preserve">152.859527587891</t>
   </si>
   <si>
-    <t xml:space="preserve">151.52864074707</t>
+    <t xml:space="preserve">151.528656005859</t>
   </si>
   <si>
     <t xml:space="preserve">155.616302490234</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">157.992858886719</t>
   </si>
   <si>
-    <t xml:space="preserve">170.826217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.970687866211</t>
+    <t xml:space="preserve">170.826202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">179.001556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">168.924987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.68180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.111389160156</t>
+    <t xml:space="preserve">168.92497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.681793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.111404418945</t>
   </si>
   <si>
     <t xml:space="preserve">170.541015625</t>
@@ -2861,49 +2861,49 @@
     <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.868194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.202758789062</t>
+    <t xml:space="preserve">170.255844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.868209838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">175.389190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">176.43489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.149703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.195358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.438568115234</t>
+    <t xml:space="preserve">176.434875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.195373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.438583374023</t>
   </si>
   <si>
     <t xml:space="preserve">156.186706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">151.813827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.996597290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.380493164062</t>
+    <t xml:space="preserve">151.813842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.996566772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.380508422852</t>
   </si>
   <si>
     <t xml:space="preserve">155.901504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">157.137313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.000259399414</t>
+    <t xml:space="preserve">157.137298583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.000274658203</t>
   </si>
   <si>
     <t xml:space="preserve">150.197799682617</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">149.057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">147.155807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.706405639648</t>
+    <t xml:space="preserve">147.155822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.706420898438</t>
   </si>
   <si>
     <t xml:space="preserve">135.082962036133</t>
@@ -2924,31 +2924,31 @@
     <t xml:space="preserve">138.695281982422</t>
   </si>
   <si>
-    <t xml:space="preserve">134.987884521484</t>
+    <t xml:space="preserve">134.987899780273</t>
   </si>
   <si>
     <t xml:space="preserve">133.181716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">136.033584594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.276779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.037261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.086654663086</t>
+    <t xml:space="preserve">136.033569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.276763916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.03727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.086669921875</t>
   </si>
   <si>
     <t xml:space="preserve">135.273071289062</t>
   </si>
   <si>
-    <t xml:space="preserve">132.136016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.519989013672</t>
+    <t xml:space="preserve">132.136047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.519973754883</t>
   </si>
   <si>
     <t xml:space="preserve">130.90022277832</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">130.044677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">132.848983764648</t>
+    <t xml:space="preserve">132.848999023438</t>
   </si>
   <si>
     <t xml:space="preserve">135.463195800781</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">133.229232788086</t>
   </si>
   <si>
-    <t xml:space="preserve">145.492218017578</t>
+    <t xml:space="preserve">145.492233276367</t>
   </si>
   <si>
     <t xml:space="preserve">143.59098815918</t>
   </si>
   <si>
-    <t xml:space="preserve">141.784790039062</t>
+    <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
     <t xml:space="preserve">148.20149230957</t>
   </si>
   <si>
-    <t xml:space="preserve">148.058898925781</t>
+    <t xml:space="preserve">148.05891418457</t>
   </si>
   <si>
     <t xml:space="preserve">146.300247192383</t>
@@ -2990,34 +2990,34 @@
     <t xml:space="preserve">144.874313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">136.98420715332</t>
+    <t xml:space="preserve">136.984191894531</t>
   </si>
   <si>
     <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">133.324310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.274917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.894683837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.227386474609</t>
+    <t xml:space="preserve">133.324295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.274932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.89469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.227401733398</t>
   </si>
   <si>
     <t xml:space="preserve">131.660720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">133.847152709961</t>
+    <t xml:space="preserve">133.84716796875</t>
   </si>
   <si>
     <t xml:space="preserve">135.60578918457</t>
   </si>
   <si>
-    <t xml:space="preserve">131.423080444336</t>
+    <t xml:space="preserve">131.423065185547</t>
   </si>
   <si>
     <t xml:space="preserve">128.333557128906</t>
@@ -3029,22 +3029,22 @@
     <t xml:space="preserve">131.185409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">134.655181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889129638672</t>
+    <t xml:space="preserve">134.655166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889144897461</t>
   </si>
   <si>
     <t xml:space="preserve">137.031707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">136.983871459961</t>
+    <t xml:space="preserve">136.983856201172</t>
   </si>
   <si>
     <t xml:space="preserve">136.744552612305</t>
   </si>
   <si>
-    <t xml:space="preserve">137.84538269043</t>
+    <t xml:space="preserve">137.845397949219</t>
   </si>
   <si>
     <t xml:space="preserve">137.797515869141</t>
@@ -3053,22 +3053,22 @@
     <t xml:space="preserve">138.084701538086</t>
   </si>
   <si>
-    <t xml:space="preserve">138.467590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.978744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.05908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.963348388672</t>
+    <t xml:space="preserve">138.46760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.978729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.059097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.963363647461</t>
   </si>
   <si>
     <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">136.218048095703</t>
+    <t xml:space="preserve">136.218032836914</t>
   </si>
   <si>
     <t xml:space="preserve">137.510345458984</t>
@@ -3077,19 +3077,19 @@
     <t xml:space="preserve">138.659072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">139.185531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.206069946289</t>
+    <t xml:space="preserve">139.185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.206039428711</t>
   </si>
   <si>
     <t xml:space="preserve">144.306900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">144.01969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.269287109375</t>
+    <t xml:space="preserve">144.019714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.269271850586</t>
   </si>
   <si>
     <t xml:space="preserve">145.790649414062</t>
@@ -3098,28 +3098,28 @@
     <t xml:space="preserve">147.322250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">146.843612670898</t>
+    <t xml:space="preserve">146.843627929688</t>
   </si>
   <si>
     <t xml:space="preserve">147.226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">143.397506713867</t>
+    <t xml:space="preserve">143.397491455078</t>
   </si>
   <si>
     <t xml:space="preserve">147.99235534668</t>
   </si>
   <si>
-    <t xml:space="preserve">149.428253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.289749145508</t>
+    <t xml:space="preserve">149.42822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.289764404297</t>
   </si>
   <si>
     <t xml:space="preserve">153.065811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">152.682907104492</t>
+    <t xml:space="preserve">152.682922363281</t>
   </si>
   <si>
     <t xml:space="preserve">150.76838684082</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906875610352</t>
+    <t xml:space="preserve">149.906890869141</t>
   </si>
   <si>
     <t xml:space="preserve">153.879486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">156.320510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.395736694336</t>
+    <t xml:space="preserve">156.320495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.395721435547</t>
   </si>
   <si>
     <t xml:space="preserve">153.783767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">155.123931884766</t>
+    <t xml:space="preserve">155.123916625977</t>
   </si>
   <si>
     <t xml:space="preserve">155.458953857422</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">155.650436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.081192016602</t>
+    <t xml:space="preserve">155.650421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.081207275391</t>
   </si>
   <si>
     <t xml:space="preserve">158.905090332031</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">160.149536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">162.207656860352</t>
+    <t xml:space="preserve">162.207641601562</t>
   </si>
   <si>
     <t xml:space="preserve">163.643539428711</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">164.983703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">161.729019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.91535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.351257324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.07942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.834976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.908447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.600784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.142639160156</t>
+    <t xml:space="preserve">161.72900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.915344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.35124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.079437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.834991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.908462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.600799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.142654418945</t>
   </si>
   <si>
     <t xml:space="preserve">168.860595703125</t>
@@ -3203,25 +3203,25 @@
     <t xml:space="preserve">166.036682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">168.669143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.334121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.05207824707</t>
+    <t xml:space="preserve">168.669158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.334106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">170.248641967773</t>
+    <t xml:space="preserve">170.248626708984</t>
   </si>
   <si>
     <t xml:space="preserve">171.349472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">176.040023803711</t>
+    <t xml:space="preserve">176.040054321289</t>
   </si>
   <si>
     <t xml:space="preserve">176.949447631836</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">177.140899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">180.108383178711</t>
+    <t xml:space="preserve">180.1083984375</t>
   </si>
   <si>
     <t xml:space="preserve">179.534057617188</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">177.810989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">181.352844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.740859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.016052246094</t>
+    <t xml:space="preserve">181.352828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.740844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.016036987305</t>
   </si>
   <si>
     <t xml:space="preserve">192.4091796875</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">196.908309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">196.812606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.386932373047</t>
+    <t xml:space="preserve">196.812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.386947631836</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">190.351089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">192.026306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.940795898438</t>
+    <t xml:space="preserve">192.026290893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.940811157227</t>
   </si>
   <si>
     <t xml:space="preserve">195.855331420898</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">174.987060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">174.077682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.599029541016</t>
+    <t xml:space="preserve">174.077667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.599044799805</t>
   </si>
   <si>
     <t xml:space="preserve">167.664016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">164.505081176758</t>
+    <t xml:space="preserve">164.505065917969</t>
   </si>
   <si>
     <t xml:space="preserve">165.462341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">162.782012939453</t>
+    <t xml:space="preserve">162.781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">163.404205322266</t>
@@ -3332,31 +3332,31 @@
     <t xml:space="preserve">164.744400024414</t>
   </si>
   <si>
-    <t xml:space="preserve">162.111938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.515319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.870849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.253723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.402465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684539794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.742630004883</t>
+    <t xml:space="preserve">162.111923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.515289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.253753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.402481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.742614746094</t>
   </si>
   <si>
     <t xml:space="preserve">177.715240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">181.448577880859</t>
+    <t xml:space="preserve">181.44856262207</t>
   </si>
   <si>
     <t xml:space="preserve">180.82633972168</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">182.884460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">182.836578369141</t>
+    <t xml:space="preserve">182.83659362793</t>
   </si>
   <si>
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.000686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.723724365234</t>
+    <t xml:space="preserve">187.096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.000671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.723739624023</t>
   </si>
   <si>
     <t xml:space="preserve">189.202362060547</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.699890136719</t>
+    <t xml:space="preserve">174.699905395508</t>
   </si>
   <si>
     <t xml:space="preserve">176.231506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">175.561401367188</t>
+    <t xml:space="preserve">175.561416625977</t>
   </si>
   <si>
     <t xml:space="preserve">177.093048095703</t>
@@ -3407,28 +3407,28 @@
     <t xml:space="preserve">180.874206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">183.50666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.896469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.614410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.800720214844</t>
+    <t xml:space="preserve">183.506652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.896453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.614395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.800704956055</t>
   </si>
   <si>
     <t xml:space="preserve">171.636657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">169.865707397461</t>
+    <t xml:space="preserve">169.86572265625</t>
   </si>
   <si>
     <t xml:space="preserve">179.294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">177.188781738281</t>
+    <t xml:space="preserve">177.188766479492</t>
   </si>
   <si>
     <t xml:space="preserve">180.682754516602</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">175.082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">170.296478271484</t>
+    <t xml:space="preserve">170.296463012695</t>
   </si>
   <si>
     <t xml:space="preserve">169.14778137207</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">164.935836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">167.472564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.392227172852</t>
+    <t xml:space="preserve">167.472579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">172.306747436523</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">172.785369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">170.535781860352</t>
+    <t xml:space="preserve">170.53581237793</t>
   </si>
   <si>
     <t xml:space="preserve">152.060699462891</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">153.688049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">153.400863647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932495117188</t>
+    <t xml:space="preserve">153.400848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932479858398</t>
   </si>
   <si>
     <t xml:space="preserve">154.741012573242</t>
@@ -3485,28 +3485,28 @@
     <t xml:space="preserve">159.240158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">157.947845458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.293121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.22477722168</t>
+    <t xml:space="preserve">157.947830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.293106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.224761962891</t>
   </si>
   <si>
     <t xml:space="preserve">152.15641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">153.640167236328</t>
+    <t xml:space="preserve">153.640182495117</t>
   </si>
   <si>
     <t xml:space="preserve">148.183807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">141.770172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.780395507812</t>
+    <t xml:space="preserve">141.770156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.780380249023</t>
   </si>
   <si>
     <t xml:space="preserve">147.609436035156</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">141.387252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">139.855651855469</t>
+    <t xml:space="preserve">139.85563659668</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
@@ -3533,19 +3533,19 @@
     <t xml:space="preserve">128.94287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">126.884765625</t>
+    <t xml:space="preserve">126.884750366211</t>
   </si>
   <si>
     <t xml:space="preserve">128.990737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">129.325775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.144561767578</t>
+    <t xml:space="preserve">129.325790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.048843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.144577026367</t>
   </si>
   <si>
     <t xml:space="preserve">132.006103515625</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">127.698425292969</t>
   </si>
   <si>
-    <t xml:space="preserve">125.975372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.418144226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.289916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.662582397461</t>
+    <t xml:space="preserve">125.975379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.41813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.289924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.662574768066</t>
   </si>
   <si>
     <t xml:space="preserve">117.934379577637</t>
@@ -3575,34 +3575,34 @@
     <t xml:space="preserve">114.631843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">117.072860717773</t>
+    <t xml:space="preserve">117.072853088379</t>
   </si>
   <si>
     <t xml:space="preserve">116.546363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">115.589096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.286567687988</t>
+    <t xml:space="preserve">115.58910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.286560058594</t>
   </si>
   <si>
     <t xml:space="preserve">112.430137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">116.211326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.136085510254</t>
+    <t xml:space="preserve">116.211318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.136093139648</t>
   </si>
   <si>
     <t xml:space="preserve">123.10359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">122.864280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.93775177002</t>
+    <t xml:space="preserve">122.864288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937744140625</t>
   </si>
   <si>
     <t xml:space="preserve">127.124099731445</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">120.08821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.242042541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.503623962402</t>
+    <t xml:space="preserve">120.088218688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.242057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.503616333008</t>
   </si>
   <si>
     <t xml:space="preserve">120.806159973145</t>
@@ -3632,31 +3632,31 @@
     <t xml:space="preserve">117.599349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">121.859161376953</t>
+    <t xml:space="preserve">121.859153747559</t>
   </si>
   <si>
     <t xml:space="preserve">131.718933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">132.293258666992</t>
+    <t xml:space="preserve">132.293273925781</t>
   </si>
   <si>
     <t xml:space="preserve">126.693321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">126.59757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.448883056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.824920654297</t>
+    <t xml:space="preserve">126.597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.824890136719</t>
   </si>
   <si>
     <t xml:space="preserve">135.73942565918</t>
@@ -3665,52 +3665,52 @@
     <t xml:space="preserve">135.83512878418</t>
   </si>
   <si>
-    <t xml:space="preserve">139.329147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.616333007812</t>
+    <t xml:space="preserve">139.329132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">142.105194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">139.041961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.170196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.260803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.628341674805</t>
+    <t xml:space="preserve">139.041976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.170166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.260787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.628326416016</t>
   </si>
   <si>
     <t xml:space="preserve">129.038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">129.086486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.559967041016</t>
+    <t xml:space="preserve">129.086471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.559982299805</t>
   </si>
   <si>
     <t xml:space="preserve">128.416366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">126.454010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.539489746094</t>
+    <t xml:space="preserve">126.453994750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.539482116699</t>
   </si>
   <si>
     <t xml:space="preserve">120.997619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">118.700202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.254066467285</t>
+    <t xml:space="preserve">118.700187683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.254051208496</t>
   </si>
   <si>
     <t xml:space="preserve">118.652328491211</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">119.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">118.173698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.64720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392532348633</t>
+    <t xml:space="preserve">118.173713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392524719238</t>
   </si>
   <si>
     <t xml:space="preserve">114.823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">115.493377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.271194458008</t>
+    <t xml:space="preserve">115.493385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.271186828613</t>
   </si>
   <si>
     <t xml:space="preserve">106.590858459473</t>
@@ -3743,31 +3743,31 @@
     <t xml:space="preserve">109.654098510742</t>
   </si>
   <si>
-    <t xml:space="preserve">107.16520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.009613037109</t>
+    <t xml:space="preserve">107.165214538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.009620666504</t>
   </si>
   <si>
     <t xml:space="preserve">114.871154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">113.435264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.563491821289</t>
+    <t xml:space="preserve">113.435272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.563484191895</t>
   </si>
   <si>
     <t xml:space="preserve">113.052360534668</t>
   </si>
   <si>
-    <t xml:space="preserve">114.057487487793</t>
+    <t xml:space="preserve">114.057479858398</t>
   </si>
   <si>
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884498596191</t>
+    <t xml:space="preserve">111.884506225586</t>
   </si>
   <si>
     <t xml:space="preserve">111.932792663574</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">117.292816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">118.403450012207</t>
+    <t xml:space="preserve">118.403457641602</t>
   </si>
   <si>
     <t xml:space="preserve">118.30687713623</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">116.761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">119.803833007812</t>
+    <t xml:space="preserve">119.803825378418</t>
   </si>
   <si>
     <t xml:space="preserve">116.278762817383</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">111.787925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">110.918724060059</t>
+    <t xml:space="preserve">110.918731689453</t>
   </si>
   <si>
     <t xml:space="preserve">107.683403015137</t>
@@ -3818,25 +3818,25 @@
     <t xml:space="preserve">112.657119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">109.904685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.685241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.80199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.912620544434</t>
+    <t xml:space="preserve">109.904678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.685234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.801986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.912612915039</t>
   </si>
   <si>
     <t xml:space="preserve">113.526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">120.190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.377166748047</t>
+    <t xml:space="preserve">120.190132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.377174377441</t>
   </si>
   <si>
     <t xml:space="preserve">122.797714233398</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">120.866172790527</t>
   </si>
   <si>
-    <t xml:space="preserve">120.914451599121</t>
+    <t xml:space="preserve">120.914459228516</t>
   </si>
   <si>
     <t xml:space="preserve">122.025093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">126.56421661377</t>
+    <t xml:space="preserve">126.564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">127.578285217285</t>
@@ -3863,31 +3863,31 @@
     <t xml:space="preserve">129.799545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">130.668746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.151626586914</t>
+    <t xml:space="preserve">130.668731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.151641845703</t>
   </si>
   <si>
     <t xml:space="preserve">131.537933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">125.598457336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.964584350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.970680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.916282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.433410644531</t>
+    <t xml:space="preserve">125.598449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.964576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.970687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.674850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.433403015137</t>
   </si>
   <si>
     <t xml:space="preserve">129.413238525391</t>
@@ -3896,28 +3896,28 @@
     <t xml:space="preserve">135.497589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">136.077041625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.841720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.785507202148</t>
+    <t xml:space="preserve">136.077056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.841735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.785491943359</t>
   </si>
   <si>
     <t xml:space="preserve">125.936454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">130.234161376953</t>
+    <t xml:space="preserve">130.234146118164</t>
   </si>
   <si>
     <t xml:space="preserve">130.958480834961</t>
   </si>
   <si>
-    <t xml:space="preserve">130.861892700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.640609741211</t>
+    <t xml:space="preserve">130.861907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.640625</t>
   </si>
   <si>
     <t xml:space="preserve">130.137557983398</t>
@@ -3926,19 +3926,19 @@
     <t xml:space="preserve">135.787338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">132.213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.910202026367</t>
+    <t xml:space="preserve">132.213973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.910171508789</t>
   </si>
   <si>
     <t xml:space="preserve">131.924240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">135.111267089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890029907227</t>
+    <t xml:space="preserve">135.111282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890014648438</t>
   </si>
   <si>
     <t xml:space="preserve">131.779373168945</t>
@@ -3950,28 +3950,28 @@
     <t xml:space="preserve">132.020812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">131.489624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.86799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.88818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.171798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.061172485352</t>
+    <t xml:space="preserve">131.489639282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.310562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.515922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.868003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.467643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.888191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.171813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.061157226562</t>
   </si>
   <si>
     <t xml:space="preserve">128.93034362793</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">129.123504638672</t>
   </si>
   <si>
-    <t xml:space="preserve">129.992721557617</t>
+    <t xml:space="preserve">129.992706298828</t>
   </si>
   <si>
     <t xml:space="preserve">131.972518920898</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">123.473747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">121.397338867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.721298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.135734558105</t>
+    <t xml:space="preserve">121.397331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.721305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.135726928711</t>
   </si>
   <si>
     <t xml:space="preserve">111.449913024902</t>
@@ -4019,43 +4019,43 @@
     <t xml:space="preserve">107.779975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">110.870452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.09782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.816040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.305038452148</t>
+    <t xml:space="preserve">110.870445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.097831726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.816047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.305046081543</t>
   </si>
   <si>
     <t xml:space="preserve">108.504302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">109.132064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.974975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.763481140137</t>
+    <t xml:space="preserve">109.132057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.974967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.763473510742</t>
   </si>
   <si>
     <t xml:space="preserve">121.687072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">124.58438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.646743774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.586212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.344787597656</t>
+    <t xml:space="preserve">124.584381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.646728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.586227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.344772338867</t>
   </si>
   <si>
     <t xml:space="preserve">121.300765991211</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">124.680969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">127.771430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.660774230957</t>
+    <t xml:space="preserve">127.771423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.660789489746</t>
   </si>
   <si>
     <t xml:space="preserve">124.922409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">122.314834594727</t>
+    <t xml:space="preserve">122.314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">124.777534484863</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">125.018974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">128.592315673828</t>
+    <t xml:space="preserve">128.592330932617</t>
   </si>
   <si>
     <t xml:space="preserve">132.069107055664</t>
@@ -4097,19 +4097,19 @@
     <t xml:space="preserve">128.302612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">126.612518310547</t>
+    <t xml:space="preserve">126.612503051758</t>
   </si>
   <si>
     <t xml:space="preserve">128.206024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">127.04711151123</t>
+    <t xml:space="preserve">127.047096252441</t>
   </si>
   <si>
     <t xml:space="preserve">124.487808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">127.240257263184</t>
+    <t xml:space="preserve">127.240249633789</t>
   </si>
   <si>
     <t xml:space="preserve">129.316650390625</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">125.26042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">129.509826660156</t>
+    <t xml:space="preserve">129.509811401367</t>
   </si>
   <si>
     <t xml:space="preserve">131.682815551758</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">129.84782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">125.067268371582</t>
+    <t xml:space="preserve">125.067276000977</t>
   </si>
   <si>
     <t xml:space="preserve">120.286712646484</t>
@@ -4142,34 +4142,34 @@
     <t xml:space="preserve">123.425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">121.783645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.522041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.039161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.652847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.874122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.405303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.845993041992</t>
+    <t xml:space="preserve">121.783653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.522033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.039154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.652854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.62654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.874114990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.405296325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.846000671387</t>
   </si>
   <si>
     <t xml:space="preserve">122.169960021973</t>
   </si>
   <si>
-    <t xml:space="preserve">123.232299804688</t>
+    <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
     <t xml:space="preserve">121.880218505859</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">122.218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">120.141845703125</t>
+    <t xml:space="preserve">120.14183807373</t>
   </si>
   <si>
     <t xml:space="preserve">125.550155639648</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">121.011039733887</t>
   </si>
   <si>
-    <t xml:space="preserve">120.479866027832</t>
+    <t xml:space="preserve">120.479858398438</t>
   </si>
   <si>
     <t xml:space="preserve">119.465797424316</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">115.168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.188293457031</t>
+    <t xml:space="preserve">113.188285827637</t>
   </si>
   <si>
     <t xml:space="preserve">115.651008605957</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">117.196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">117.775695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.906517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.250648498535</t>
+    <t xml:space="preserve">117.775703430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.250640869141</t>
   </si>
   <si>
     <t xml:space="preserve">112.415679931641</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">112.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.077667236328</t>
+    <t xml:space="preserve">112.077659606934</t>
   </si>
   <si>
     <t xml:space="preserve">109.42179107666</t>
@@ -4250,16 +4250,16 @@
     <t xml:space="preserve">107.20051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.186447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.649169921875</t>
+    <t xml:space="preserve">106.186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.64917755127</t>
   </si>
   <si>
     <t xml:space="preserve">108.842323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">108.11799621582</t>
+    <t xml:space="preserve">108.118003845215</t>
   </si>
   <si>
     <t xml:space="preserve">107.73169708252</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">105.993301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">104.303207397461</t>
+    <t xml:space="preserve">104.303199768066</t>
   </si>
   <si>
     <t xml:space="preserve">104.013473510742</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">103.675453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">102.081924438477</t>
+    <t xml:space="preserve">102.081932067871</t>
   </si>
   <si>
     <t xml:space="preserve">97.7359619140625</t>
@@ -4289,28 +4289,28 @@
     <t xml:space="preserve">98.9431762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">97.5911102294922</t>
+    <t xml:space="preserve">97.5911026000977</t>
   </si>
   <si>
     <t xml:space="preserve">95.1283874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">98.556884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6455001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.5770416259766</t>
+    <t xml:space="preserve">98.5568771362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5770492553711</t>
   </si>
   <si>
     <t xml:space="preserve">94.6648178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0704345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.737678527832</t>
+    <t xml:space="preserve">95.070442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7376708984375</t>
   </si>
   <si>
     <t xml:space="preserve">93.6797332763672</t>
@@ -4328,34 +4328,34 @@
     <t xml:space="preserve">93.9887771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5251998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9694671630859</t>
+    <t xml:space="preserve">93.5252075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9694595336914</t>
   </si>
   <si>
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5340118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9589462280273</t>
+    <t xml:space="preserve">93.8342666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5340042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9589538574219</t>
   </si>
   <si>
     <t xml:space="preserve">94.1819305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1582183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1090774536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3750839233398</t>
+    <t xml:space="preserve">93.1582107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1090698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3750915527344</t>
   </si>
   <si>
     <t xml:space="preserve">94.6068725585938</t>
@@ -4367,22 +4367,22 @@
     <t xml:space="preserve">100.874717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">98.7017288208008</t>
+    <t xml:space="preserve">98.7017364501953</t>
   </si>
   <si>
     <t xml:space="preserve">101.164451599121</t>
   </si>
   <si>
-    <t xml:space="preserve">101.9853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.454193115234</t>
+    <t xml:space="preserve">101.985359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.45418548584</t>
   </si>
   <si>
     <t xml:space="preserve">98.0739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1222686767578</t>
+    <t xml:space="preserve">98.1222763061523</t>
   </si>
   <si>
     <t xml:space="preserve">98.8948974609375</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">100.408088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2853927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299819946289</t>
+    <t xml:space="preserve">99.2853851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299743652344</t>
   </si>
   <si>
     <t xml:space="preserve">96.8642730712891</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">95.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6384124755859</t>
+    <t xml:space="preserve">94.6384048461914</t>
   </si>
   <si>
     <t xml:space="preserve">94.4236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0679550170898</t>
+    <t xml:space="preserve">95.0679626464844</t>
   </si>
   <si>
     <t xml:space="preserve">95.1265411376953</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">95.4389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3579559326172</t>
+    <t xml:space="preserve">98.3579483032227</t>
   </si>
   <si>
     <t xml:space="preserve">96.6104431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4779968261719</t>
+    <t xml:space="preserve">95.4779891967773</t>
   </si>
   <si>
     <t xml:space="preserve">94.7946090698242</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">90.8700561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4404983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0848388671875</t>
+    <t xml:space="preserve">90.4405059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.084831237793</t>
   </si>
   <si>
     <t xml:space="preserve">91.5534362792969</t>
@@ -4499,13 +4499,13 @@
     <t xml:space="preserve">90.1280975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7054214477539</t>
+    <t xml:space="preserve">92.7054138183594</t>
   </si>
   <si>
     <t xml:space="preserve">92.1196670532227</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5729598999023</t>
+    <t xml:space="preserve">91.5729675292969</t>
   </si>
   <si>
     <t xml:space="preserve">90.0109405517578</t>
@@ -4526,954 +4526,957 @@
     <t xml:space="preserve">91.7877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2716522216797</t>
+    <t xml:space="preserve">93.2716445922852</t>
   </si>
   <si>
     <t xml:space="preserve">93.6816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3091278076172</t>
+    <t xml:space="preserve">98.3091354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6270904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9397201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8030395507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7682113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5492172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6273193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.11279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1365280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1016998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6679382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3164825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7375946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9676818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8114700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8225708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4626846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0721740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1238784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2800827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6790161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6357498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5032958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.303825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9328536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8003921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3681793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1755828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4853286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.9581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2314987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5090713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8563079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3053817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6373138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7824249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4378433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5175094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3961410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2008895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.673713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2678985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6193466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6932373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2985153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8146057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4436264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.131217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8800506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3206939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0974807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5006408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7892990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1185684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8394393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2969512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3096008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6526184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3792724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8520889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4183120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.98876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5201644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1380996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1143569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8758392333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.5243835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2942962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2663345336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8589553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6093521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9064483642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3402252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9703369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7180709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.980339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1518402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4600296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2996063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9481582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9872055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0262603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8436584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6135787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2774276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4294128417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7808685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2341613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.121223449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9106674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1296539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9037933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3138198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4742431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.6304397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3877105712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3486557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8605270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4547119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9428405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1966705322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.9344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.055778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6958923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7001113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7196350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2578964233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1170120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2647705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7138519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9286270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3302230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.388801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3149108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2843017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8310012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4753341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4125518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5017395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5645217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.369270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5423431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4515838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6399765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9259719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0863952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3750534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1338806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9275360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3222579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7238464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6721420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2858581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4098815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.4531555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0151672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6858978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5840530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7402496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4362869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6468505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9550247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8352203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7724304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6510543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1043548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2004241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9437026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.749778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7484588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1389617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6002044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1460113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0993728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0598907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5733261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.375846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4789733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.380241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6918106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.244743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2321319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4296035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.268890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9287796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1827545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7439270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9342727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1388702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5788116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0922470092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3868179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7494049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.675895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0834655761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3006973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1032104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2628479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0796356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1657562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8624038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6523132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0275192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3308639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8739318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.219512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.466361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.515731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.342391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.046173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.490501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.082931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1191253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7258224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6764526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9359130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8865432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2249984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3632354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8371734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5607070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1855087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.120780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.700592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.910682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.305633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.971580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.317161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.687973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8245620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.94743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.651222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.762580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.293022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.10816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.194282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.404373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.008323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.576622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.786712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.625984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.93482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.749961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.589241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.996810913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.095542907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.24365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.428512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.503120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.713203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.23104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7384414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4027328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2815017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.170143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.748863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.575523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.118591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.105972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.526161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.699501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.033561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.094451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.045082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.403282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.218421936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.465270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.527252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.836082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.391754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.638603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.565093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.367622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9726715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9852828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1262588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.663833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.144912719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.267791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.05770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.477882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.860214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.441131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.280403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.55248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.861312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0840225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.632568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3237380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7186965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6594467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.009422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0346527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.4745864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1964721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2035980224609</t>
   </si>
   <si>
     <t xml:space="preserve">99.627082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9397201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8030395507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7682113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5492248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6273193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1127853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1365280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1016998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6679306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3164825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7375946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9676818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8225708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4626846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0721817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1238784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2800827026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6790161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6357498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.503288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.303825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9328460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8003921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3681793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1755828857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2077560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4853286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.9581527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2314987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5090713500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8563079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3053894042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6373138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7824249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4378433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4700164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5175094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3961410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.673713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2678985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6193466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6932373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2985153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8145980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4436264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.1312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8800506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3206939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0974807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7391586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5006408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.789306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1185684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8394393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2969436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3096008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6526184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3792724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8520889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6916732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4183197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.98876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5201644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1380996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1143569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8758392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.5243835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2942962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2663345336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6985397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8589630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6093521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9064407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3402252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9703369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7180709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.980339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1518402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4600296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2996063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9481582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9871978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8436584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6135711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2774276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7808609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2341613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5117340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.121223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9106674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9037933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3138198852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4742431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6304397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3877029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3486557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8605270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0014114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.454719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9428405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1966705322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9344100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0557708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8953552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6958923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7001037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7196350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2579040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1170120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2647705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7138519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9286270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3302230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.388801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3149108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.284309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7096405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8310089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4753341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4125442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5017395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5645217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.369270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5423431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2605667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6399765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9259796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0863952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6177825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3750534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1338806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9275283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3222579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7238464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6721496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2858581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4098892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4531555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0151672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6858978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5840454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7402496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4362869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.646842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9550247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8352203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7724304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6510620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1043548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2004241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9437026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.749778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7484588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1389617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6002044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1460113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0598907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5733261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.375846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4789733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.380241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6918106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.244743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2321319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4296035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.268890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9287796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1827545166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7439270019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9342727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1388702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5788116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0922470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3868179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7494049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.675895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0834655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3006973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1032104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2628479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0796356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1657562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.8624038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6523132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0275192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3308639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8739318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0077743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.219512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.466361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.515731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.342391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.046173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.490501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.082931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1191253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7258224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9359130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8865432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2249984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3632354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8371734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5607070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1855087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.120780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.700592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.910682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.971580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.317161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.687973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8245620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.94743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.651222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.762580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.293022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.10816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.194282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.404373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.008323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.576622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.786712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.625984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.93482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.749961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.095542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.24365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.428512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.503120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.23104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4027328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2815017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.170143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.748863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.575523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.118591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.105972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.526161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.699501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.033561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.094451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.045082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.403282165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.218421936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.465270996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.527252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.836082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.391754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.638603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.565093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.367622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9726715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9852828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1262588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.663833618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.144912719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.267791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.05770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.477882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.860214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.441131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.280403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.55248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.861312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0840225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.632568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3237380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7186965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6594467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.009422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0346527099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5283508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.4745864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1964721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2035980224609</t>
-  </si>
-  <si>
     <t xml:space="preserve">97.6128234863281</t>
   </si>
   <si>
@@ -5886,6 +5889,9 @@
   </si>
   <si>
     <t xml:space="preserve">74.8000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1999969482422</t>
   </si>
 </sst>
 </file>
@@ -66978,7 +66984,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1507</v>
+        <v>1820</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67030,7 +67036,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67056,7 +67062,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67082,7 +67088,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67108,7 +67114,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67134,7 +67140,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67160,7 +67166,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67186,7 +67192,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67212,7 +67218,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67238,7 +67244,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67264,7 +67270,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67290,7 +67296,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67316,7 +67322,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67342,7 +67348,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67368,7 +67374,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67394,7 +67400,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67420,7 +67426,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67446,7 +67452,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67498,7 +67504,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67524,7 +67530,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67550,7 +67556,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67576,7 +67582,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67602,7 +67608,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67628,7 +67634,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67680,7 +67686,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67706,7 +67712,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67732,7 +67738,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67758,7 +67764,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67810,7 +67816,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67862,7 +67868,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67914,7 +67920,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67966,7 +67972,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67992,7 +67998,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68044,7 +68050,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68070,7 +68076,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68096,7 +68102,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68122,7 +68128,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68148,7 +68154,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68174,7 +68180,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68200,7 +68206,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68226,7 +68232,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68252,7 +68258,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68278,7 +68284,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68304,7 +68310,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68330,7 +68336,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68356,7 +68362,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68382,7 +68388,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68408,7 +68414,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68434,7 +68440,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68460,7 +68466,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68486,7 +68492,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68512,7 +68518,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68538,7 +68544,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68564,7 +68570,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68590,7 +68596,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68616,7 +68622,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68642,7 +68648,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68668,7 +68674,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68694,7 +68700,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68720,7 +68726,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68746,7 +68752,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68772,7 +68778,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68798,7 +68804,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68824,7 +68830,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68850,7 +68856,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68876,7 +68882,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68902,7 +68908,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68928,7 +68934,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68954,7 +68960,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68980,7 +68986,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69006,7 +69012,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69032,7 +69038,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69058,7 +69064,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69084,7 +69090,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69110,7 +69116,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69136,7 +69142,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69162,7 +69168,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69188,7 +69194,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69214,7 +69220,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69240,7 +69246,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69266,7 +69272,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69292,7 +69298,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69318,7 +69324,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69344,7 +69350,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69370,7 +69376,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69396,7 +69402,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69422,7 +69428,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69448,7 +69454,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69474,7 +69480,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69500,7 +69506,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69526,7 +69532,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69552,7 +69558,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69578,7 +69584,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69604,7 +69610,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69630,7 +69636,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69656,7 +69662,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69682,7 +69688,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69708,7 +69714,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69734,7 +69740,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69760,7 +69766,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69786,7 +69792,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69812,7 +69818,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69838,7 +69844,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69864,7 +69870,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69890,7 +69896,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69916,7 +69922,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69942,7 +69948,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69968,7 +69974,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69994,7 +70000,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70020,7 +70026,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70046,7 +70052,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70072,7 +70078,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70098,7 +70104,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70124,7 +70130,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70150,7 +70156,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70176,7 +70182,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70202,7 +70208,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70228,7 +70234,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70254,7 +70260,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70280,7 +70286,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70306,7 +70312,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70332,7 +70338,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70358,7 +70364,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70384,7 +70390,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70410,7 +70416,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70436,7 +70442,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70462,7 +70468,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70488,7 +70494,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70514,7 +70520,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70540,7 +70546,7 @@
         <v>77.8600006103516</v>
       </c>
       <c r="G2474" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70566,7 +70572,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2475" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70592,7 +70598,7 @@
         <v>74.1800003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70618,7 +70624,7 @@
         <v>74.1399993896484</v>
       </c>
       <c r="G2477" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70644,7 +70650,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2478" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70670,7 +70676,7 @@
         <v>75.5199966430664</v>
       </c>
       <c r="G2479" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70696,7 +70702,7 @@
         <v>77.6600036621094</v>
       </c>
       <c r="G2480" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70722,7 +70728,7 @@
         <v>77.8399963378906</v>
       </c>
       <c r="G2481" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70748,7 +70754,7 @@
         <v>78.879997253418</v>
       </c>
       <c r="G2482" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70774,7 +70780,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2483" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70800,7 +70806,7 @@
         <v>79.0400009155273</v>
       </c>
       <c r="G2484" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70826,7 +70832,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G2485" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70852,7 +70858,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G2486" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70878,7 +70884,7 @@
         <v>75.6399993896484</v>
       </c>
       <c r="G2487" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70886,7 +70892,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493518519</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>343083</v>
@@ -70904,9 +70910,35 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2488" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493634259</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>160880</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>74.8399963378906</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>74.0199966430664</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>74.0199966430664</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>74.1999969482422</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="1959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1960">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954566955566</t>
+    <t xml:space="preserve">42.4954528808594</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980880737305</t>
+    <t xml:space="preserve">43.2980918884277</t>
   </si>
   <si>
     <t xml:space="preserve">43.0423049926758</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">42.9276466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8218002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1514739990234</t>
+    <t xml:space="preserve">42.8218040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1514701843262</t>
   </si>
   <si>
     <t xml:space="preserve">42.468994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7281036376953</t>
+    <t xml:space="preserve">41.7281074523926</t>
   </si>
   <si>
     <t xml:space="preserve">41.2870979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9993553161621</t>
+    <t xml:space="preserve">39.9993591308594</t>
   </si>
   <si>
     <t xml:space="preserve">39.2761039733887</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">38.0765647888184</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8384246826172</t>
+    <t xml:space="preserve">37.8384208679199</t>
   </si>
   <si>
     <t xml:space="preserve">37.6443748474121</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9585838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2551422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606391906738</t>
+    <t xml:space="preserve">38.9585800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2606430053711</t>
   </si>
   <si>
     <t xml:space="preserve">42.0544509887695</t>
@@ -98,64 +98,64 @@
     <t xml:space="preserve">41.3664817810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.777702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0687675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9982070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.878044128418</t>
+    <t xml:space="preserve">42.7777061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.068775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780479431152</t>
   </si>
   <si>
     <t xml:space="preserve">41.2341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4172248840332</t>
+    <t xml:space="preserve">39.4172286987305</t>
   </si>
   <si>
     <t xml:space="preserve">37.7590408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0148239135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881271362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.605770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4029083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1228370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3962593078613</t>
+    <t xml:space="preserve">38.014820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.588134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6057739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4029121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1228408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3962631225586</t>
   </si>
   <si>
     <t xml:space="preserve">40.4932861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4017562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5483779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9397850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5924758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.209888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.901180267334</t>
+    <t xml:space="preserve">41.4017601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5483818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9397926330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5924835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2098922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9011840820312</t>
   </si>
   <si>
     <t xml:space="preserve">43.2275276184082</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">41.8074913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6454048156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7071418762207</t>
+    <t xml:space="preserve">42.645393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7071380615234</t>
   </si>
   <si>
     <t xml:space="preserve">42.7600593566895</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">40.352165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0081787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1636161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5726623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1581153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6200904846191</t>
+    <t xml:space="preserve">40.0081748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1636123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5726661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1581230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6200828552246</t>
   </si>
   <si>
     <t xml:space="preserve">40.114013671875</t>
@@ -215,58 +215,58 @@
     <t xml:space="preserve">44.1007232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7622337341309</t>
+    <t xml:space="preserve">44.7622375488281</t>
   </si>
   <si>
     <t xml:space="preserve">45.2914390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8647499084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3796463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6883506774902</t>
+    <t xml:space="preserve">45.8647537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3796424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6883430480957</t>
   </si>
   <si>
     <t xml:space="preserve">46.8349723815918</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9088554382324</t>
+    <t xml:space="preserve">45.9088592529297</t>
   </si>
   <si>
     <t xml:space="preserve">45.4237442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8945426940918</t>
+    <t xml:space="preserve">45.203239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8945388793945</t>
   </si>
   <si>
     <t xml:space="preserve">44.9386367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3355445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.806339263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7181282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9827423095703</t>
+    <t xml:space="preserve">45.3355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8063278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7181358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.982738494873</t>
   </si>
   <si>
     <t xml:space="preserve">44.8504409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7765502929688</t>
+    <t xml:space="preserve">45.776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">45.6442489624023</t>
@@ -281,43 +281,43 @@
     <t xml:space="preserve">46.1734580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2616653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6144676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0852546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970550537109</t>
+    <t xml:space="preserve">46.2616577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6144599914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0852584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970512390137</t>
   </si>
   <si>
     <t xml:space="preserve">47.4226684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5119743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1100845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5836791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553726196289</t>
+    <t xml:space="preserve">47.5119781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1100883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5836715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5660591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553649902344</t>
   </si>
   <si>
     <t xml:space="preserve">50.2358779907227</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">49.7000312805176</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9855613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566368103027</t>
+    <t xml:space="preserve">48.9855575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566253662109</t>
   </si>
   <si>
     <t xml:space="preserve">47.7352447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6188850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9314651489258</t>
+    <t xml:space="preserve">46.618896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.931468963623</t>
   </si>
   <si>
     <t xml:space="preserve">48.0924758911133</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">49.3427925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1723480224609</t>
+    <t xml:space="preserve">46.1723556518555</t>
   </si>
   <si>
     <t xml:space="preserve">45.0113487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0383949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8962554931641</t>
+    <t xml:space="preserve">46.0383911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8962516784668</t>
   </si>
   <si>
     <t xml:space="preserve">49.7446823120117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.414493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1371307373047</t>
+    <t xml:space="preserve">50.4144973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.137134552002</t>
   </si>
   <si>
     <t xml:space="preserve">48.9409027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">49.833984375</t>
+    <t xml:space="preserve">49.8339920043945</t>
   </si>
   <si>
     <t xml:space="preserve">49.030216217041</t>
@@ -389,34 +389,34 @@
     <t xml:space="preserve">50.5931053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">51.21826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2629280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503402709961</t>
+    <t xml:space="preserve">51.2182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2629165649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503440856934</t>
   </si>
   <si>
     <t xml:space="preserve">50.8610343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5755043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7987670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9949913024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7717247009277</t>
+    <t xml:space="preserve">51.575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7987632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9949951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">50.2805290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0572547912598</t>
+    <t xml:space="preserve">50.057258605957</t>
   </si>
   <si>
     <t xml:space="preserve">49.8786392211914</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">51.6201553344727</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5849418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0937423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1654357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.344051361084</t>
+    <t xml:space="preserve">53.5849380493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0937461853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1654396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3440475463867</t>
   </si>
   <si>
     <t xml:space="preserve">55.3711013793945</t>
@@ -446,19 +446,19 @@
     <t xml:space="preserve">54.1207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0666923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6648063659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6824111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6377639770508</t>
+    <t xml:space="preserve">52.0666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6648025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6824150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6377601623535</t>
   </si>
   <si>
     <t xml:space="preserve">52.2453079223633</t>
@@ -467,31 +467,31 @@
     <t xml:space="preserve">51.7541198730469</t>
   </si>
   <si>
-    <t xml:space="preserve">51.441535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3522300720215</t>
+    <t xml:space="preserve">51.4415397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3522338867188</t>
   </si>
   <si>
     <t xml:space="preserve">51.8880767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0843048095703</t>
+    <t xml:space="preserve">51.084300994873</t>
   </si>
   <si>
     <t xml:space="preserve">50.4591445922852</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4767532348633</t>
+    <t xml:space="preserve">49.476749420166</t>
   </si>
   <si>
     <t xml:space="preserve">49.2981414794922</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9773941040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5132331848145</t>
+    <t xml:space="preserve">51.9773864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5132369995117</t>
   </si>
   <si>
     <t xml:space="preserve">52.6918525695801</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">51.5308418273926</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3346138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.289966583252</t>
+    <t xml:space="preserve">52.3346176147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2899627685547</t>
   </si>
   <si>
     <t xml:space="preserve">53.1830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7094650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736068725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1465721130371</t>
+    <t xml:space="preserve">51.7094612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736106872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270774841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1465682983398</t>
   </si>
   <si>
     <t xml:space="preserve">50.9056854248047</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">50.0126075744629</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7176322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6459312438965</t>
+    <t xml:space="preserve">48.7176399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.645938873291</t>
   </si>
   <si>
     <t xml:space="preserve">47.8245544433594</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">45.3239250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7258148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5471992492676</t>
+    <t xml:space="preserve">45.7258110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5471954345703</t>
   </si>
   <si>
     <t xml:space="preserve">46.3956184387207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6635437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.261661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7704658508301</t>
+    <t xml:space="preserve">46.6635475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2616539001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7704620361328</t>
   </si>
   <si>
     <t xml:space="preserve">46.1277008056641</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5742378234863</t>
+    <t xml:space="preserve">46.5742340087891</t>
   </si>
   <si>
     <t xml:space="preserve">46.4402770996094</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">45.9937324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4578895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6811599731445</t>
+    <t xml:space="preserve">45.4578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811561584473</t>
   </si>
   <si>
     <t xml:space="preserve">46.5295829772949</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3063087463379</t>
+    <t xml:space="preserve">46.3063163757324</t>
   </si>
   <si>
     <t xml:space="preserve">47.2440490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4673271179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2088317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3698348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1560096740723</t>
+    <t xml:space="preserve">47.4673233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2088279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1560020446777</t>
   </si>
   <si>
     <t xml:space="preserve">50.5037956237793</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">48.8516006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6107215881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8163757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1289596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2006568908691</t>
+    <t xml:space="preserve">49.6107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8163833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1289558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2006530761719</t>
   </si>
   <si>
     <t xml:space="preserve">52.4685821533203</t>
@@ -626,145 +626,145 @@
     <t xml:space="preserve">53.4063186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4509696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6742401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9151191711426</t>
+    <t xml:space="preserve">53.4509658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6742362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9151306152344</t>
   </si>
   <si>
     <t xml:space="preserve">53.2723579406738</t>
   </si>
   <si>
-    <t xml:space="preserve">53.852855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5943717956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264465332031</t>
+    <t xml:space="preserve">53.8528518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7905883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.594367980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264427185059</t>
   </si>
   <si>
     <t xml:space="preserve">55.5050621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2641792297363</t>
+    <t xml:space="preserve">56.2641830444336</t>
   </si>
   <si>
     <t xml:space="preserve">56.1302146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6390342712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8000259399414</t>
+    <t xml:space="preserve">55.6390266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8000297546387</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9786415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
+    <t xml:space="preserve">56.9786491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251861572266</t>
   </si>
   <si>
     <t xml:space="preserve">57.3358764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0503387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8987770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0327415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7648124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0950088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1572608947754</t>
+    <t xml:space="preserve">58.0503463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8987731933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0327377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7648162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0950050354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1572685241699</t>
   </si>
   <si>
     <t xml:space="preserve">57.3805351257324</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5861968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0151176452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.943431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3006629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4088401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1585121154785</t>
+    <t xml:space="preserve">58.5862007141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0151214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9434242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4088325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585159301758</t>
   </si>
   <si>
     <t xml:space="preserve">61.622673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8906059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7390403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.515754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8635559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6758041381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.946891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083686828613</t>
+    <t xml:space="preserve">61.8905982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7390289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5157508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8635520935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6757926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.082447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083724975586</t>
   </si>
   <si>
     <t xml:space="preserve">62.5342903137207</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">63.4379615783691</t>
   </si>
   <si>
-    <t xml:space="preserve">63.754264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.483154296875</t>
+    <t xml:space="preserve">63.7542572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4831619262695</t>
   </si>
   <si>
     <t xml:space="preserve">64.5675659179688</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">64.0705413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8386764526367</t>
+    <t xml:space="preserve">64.8386688232422</t>
   </si>
   <si>
     <t xml:space="preserve">65.5164184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1668548583984</t>
+    <t xml:space="preserve">63.1668663024902</t>
   </si>
   <si>
     <t xml:space="preserve">63.0313148498535</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">64.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8898010253906</t>
+    <t xml:space="preserve">63.8898086547852</t>
   </si>
   <si>
     <t xml:space="preserve">64.432014465332</t>
@@ -818,28 +818,28 @@
     <t xml:space="preserve">65.6971435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6425399780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1847305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8173179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5462074279785</t>
+    <t xml:space="preserve">61.0884094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6425323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1847229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8173027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5462036132812</t>
   </si>
   <si>
     <t xml:space="preserve">59.6877212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">60.6365699768066</t>
+    <t xml:space="preserve">60.6365776062012</t>
   </si>
   <si>
     <t xml:space="preserve">61.4498825073242</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">62.3987426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2120361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735282897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2393569946289</t>
+    <t xml:space="preserve">63.2120513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2393646240234</t>
   </si>
   <si>
     <t xml:space="preserve">66.7815628051758</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">66.3297271728516</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9682464599609</t>
+    <t xml:space="preserve">65.9682540893555</t>
   </si>
   <si>
     <t xml:space="preserve">65.8778991699219</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">65.6067886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">65.019401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2001419067383</t>
+    <t xml:space="preserve">65.0193939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2001342773438</t>
   </si>
   <si>
     <t xml:space="preserve">64.7482986450195</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">64.6579284667969</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4771957397461</t>
+    <t xml:space="preserve">64.477180480957</t>
   </si>
   <si>
     <t xml:space="preserve">63.9801826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">63.302417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4260559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4712448120117</t>
+    <t xml:space="preserve">63.3024101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4260482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
     <t xml:space="preserve">66.284538269043</t>
   </si>
   <si>
-    <t xml:space="preserve">66.600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4652786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.871940612793</t>
+    <t xml:space="preserve">66.6008224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4652709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8719253540039</t>
   </si>
   <si>
     <t xml:space="preserve">66.0586242675781</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">66.3749008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">67.0978393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6911926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5437240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1370697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8659820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563522338867</t>
+    <t xml:space="preserve">67.0978546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6912078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5437316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.137077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8659744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">68.1822662353516</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">69.1311111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3059005737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776992797852</t>
+    <t xml:space="preserve">70.3058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776840209961</t>
   </si>
   <si>
     <t xml:space="preserve">71.3903045654297</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">71.5258636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8480987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1643753051758</t>
+    <t xml:space="preserve">70.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">72.7910079956055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8932647705078</t>
+    <t xml:space="preserve">70.8932723999023</t>
   </si>
   <si>
     <t xml:space="preserve">70.2607192993164</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3510818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5318222045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029022216797</t>
+    <t xml:space="preserve">70.35107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5318298339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029098510742</t>
   </si>
   <si>
     <t xml:space="preserve">70.4866256713867</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">71.3451232910156</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4414367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.983642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1097793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5616073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4593200683594</t>
+    <t xml:space="preserve">70.4414520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5710296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.9836654663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1097640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4593124389648</t>
   </si>
   <si>
     <t xml:space="preserve">67.8207931518555</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">69.2666702270508</t>
   </si>
   <si>
-    <t xml:space="preserve">70.034797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7636795043945</t>
+    <t xml:space="preserve">70.034782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.763671875</t>
   </si>
   <si>
     <t xml:space="preserve">68.9955673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3237762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3629989624023</t>
+    <t xml:space="preserve">67.3237686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3630065917969</t>
   </si>
   <si>
     <t xml:space="preserve">69.0407562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">69.1763153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9444198608398</t>
+    <t xml:space="preserve">69.1763076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9444274902344</t>
   </si>
   <si>
     <t xml:space="preserve">70.1703414916992</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">72.6102676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8992462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4081726074219</t>
+    <t xml:space="preserve">69.8992309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4081573486328</t>
   </si>
   <si>
     <t xml:space="preserve">67.2785797119141</t>
@@ -1085,88 +1085,88 @@
     <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.402214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391647338867</t>
+    <t xml:space="preserve">69.4022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391799926758</t>
   </si>
   <si>
     <t xml:space="preserve">71.7969665527344</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6162261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9325180053711</t>
+    <t xml:space="preserve">71.6162338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9325103759766</t>
   </si>
   <si>
     <t xml:space="preserve">72.0228805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7065963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4806747436523</t>
+    <t xml:space="preserve">71.7065887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4806671142578</t>
   </si>
   <si>
     <t xml:space="preserve">71.4354858398438</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6614151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2547454833984</t>
+    <t xml:space="preserve">71.6614227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2547607421875</t>
   </si>
   <si>
     <t xml:space="preserve">69.8088760375977</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7517852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0918884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.962287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572288513184</t>
+    <t xml:space="preserve">71.7517776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9623031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8505783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572364807129</t>
   </si>
   <si>
     <t xml:space="preserve">63.6186981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0764999389648</t>
+    <t xml:space="preserve">63.0765151977539</t>
   </si>
   <si>
     <t xml:space="preserve">62.9409484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">62.7602043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.901725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7329025268555</t>
+    <t xml:space="preserve">62.7602195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0040016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7328987121582</t>
   </si>
   <si>
     <t xml:space="preserve">60.862491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">61.811351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.799430847168</t>
+    <t xml:space="preserve">61.8113479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.799446105957</t>
   </si>
   <si>
     <t xml:space="preserve">67.5496978759766</t>
@@ -1178,25 +1178,25 @@
     <t xml:space="preserve">65.2453155517578</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8838424682617</t>
+    <t xml:space="preserve">64.8838500976562</t>
   </si>
   <si>
     <t xml:space="preserve">65.651969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2904968261719</t>
+    <t xml:space="preserve">65.2904891967773</t>
   </si>
   <si>
     <t xml:space="preserve">66.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2726364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1251525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8600006103516</t>
+    <t xml:space="preserve">68.2726287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1251602172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8600158691406</t>
   </si>
   <si>
     <t xml:space="preserve">69.8540573120117</t>
@@ -1205,67 +1205,67 @@
     <t xml:space="preserve">70.6221771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1192016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0740280151367</t>
+    <t xml:space="preserve">71.1191940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0740203857422</t>
   </si>
   <si>
     <t xml:space="preserve">72.6554565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6946868896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4747161865234</t>
+    <t xml:space="preserve">73.694694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.474723815918</t>
   </si>
   <si>
     <t xml:space="preserve">73.4687652587891</t>
   </si>
   <si>
-    <t xml:space="preserve">73.197639465332</t>
+    <t xml:space="preserve">73.1976623535156</t>
   </si>
   <si>
     <t xml:space="preserve">73.3783950805664</t>
   </si>
   <si>
-    <t xml:space="preserve">74.688720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5591201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.198371887207</t>
+    <t xml:space="preserve">74.6887130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5591278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1983642578125</t>
   </si>
   <si>
     <t xml:space="preserve">74.7919616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6961059570312</t>
+    <t xml:space="preserve">73.6960983276367</t>
   </si>
   <si>
     <t xml:space="preserve">74.9289398193359</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8466873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.7964935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1527099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.2576065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.4312133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9059448242188</t>
+    <t xml:space="preserve">76.8466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.7964859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.152702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.2576141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.4312057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0795288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9059371948242</t>
   </si>
   <si>
     <t xml:space="preserve">80.5908508300781</t>
@@ -1274,16 +1274,16 @@
     <t xml:space="preserve">80.3625411987305</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7278366088867</t>
+    <t xml:space="preserve">80.7278289794922</t>
   </si>
   <si>
     <t xml:space="preserve">80.2712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2300872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.102180480957</t>
+    <t xml:space="preserve">81.230094909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1021728515625</t>
   </si>
   <si>
     <t xml:space="preserve">84.3806686401367</t>
@@ -1292,55 +1292,55 @@
     <t xml:space="preserve">85.2482147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">84.928596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893447875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0565185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682281494141</t>
+    <t xml:space="preserve">84.9285888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893600463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.056526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682357788086</t>
   </si>
   <si>
     <t xml:space="preserve">86.8006820678711</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3942565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8554077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9878616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2206802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9421920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0380554199219</t>
+    <t xml:space="preserve">87.3942642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8554153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9878463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9421997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0380401611328</t>
   </si>
   <si>
     <t xml:space="preserve">88.0335235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2572860717773</t>
+    <t xml:space="preserve">87.2572937011719</t>
   </si>
   <si>
     <t xml:space="preserve">87.4855880737305</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5769119262695</t>
+    <t xml:space="preserve">87.5769195556641</t>
   </si>
   <si>
     <t xml:space="preserve">87.8052139282227</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">89.6772842407227</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1750183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4033279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1248397827148</t>
+    <t xml:space="preserve">89.1750335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4033355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1248321533203</t>
   </si>
   <si>
     <t xml:space="preserve">87.62255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3531341552734</t>
+    <t xml:space="preserve">88.353141784668</t>
   </si>
   <si>
     <t xml:space="preserve">86.2984237670898</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">85.8418045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">86.1614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263381958008</t>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263229370117</t>
   </si>
   <si>
     <t xml:space="preserve">84.4719924926758</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">83.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">77.668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7689514160156</t>
+    <t xml:space="preserve">77.6685791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7689590454102</t>
   </si>
   <si>
     <t xml:space="preserve">81.0474472045898</t>
@@ -1397,43 +1397,43 @@
     <t xml:space="preserve">80.4538650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">79.3580093383789</t>
+    <t xml:space="preserve">79.3580169677734</t>
   </si>
   <si>
     <t xml:space="preserve">80.4995346069336</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0383911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112365722656</t>
+    <t xml:space="preserve">79.0383834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112442016602</t>
   </si>
   <si>
     <t xml:space="preserve">85.6135101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">83.5587768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8783874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6501083374023</t>
+    <t xml:space="preserve">83.5587921142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6501007080078</t>
   </si>
   <si>
     <t xml:space="preserve">83.2391586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">83.7414321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.837272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591720581055</t>
+    <t xml:space="preserve">83.7414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.837287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591644287109</t>
   </si>
   <si>
     <t xml:space="preserve">84.3350143432617</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">81.2757568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">82.8282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5312423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640762329102</t>
+    <t xml:space="preserve">82.8282089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.53125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640838623047</t>
   </si>
   <si>
     <t xml:space="preserve">84.2436904907227</t>
   </si>
   <si>
-    <t xml:space="preserve">85.0199279785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.882926940918</t>
+    <t xml:space="preserve">85.0199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8829193115234</t>
   </si>
   <si>
     <t xml:space="preserve">82.7368927001953</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">81.4583892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2666931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1572570800781</t>
+    <t xml:space="preserve">79.2667007446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.1572494506836</t>
   </si>
   <si>
     <t xml:space="preserve">74.4266738891602</t>
@@ -1493,76 +1493,76 @@
     <t xml:space="preserve">72.7828979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8376159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6002655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9198760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5179977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485656738281</t>
+    <t xml:space="preserve">74.8376083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6002502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9198608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5179824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485733032227</t>
   </si>
   <si>
     <t xml:space="preserve">76.4357299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8285598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8330841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.2806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9700698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0659103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5270614624023</t>
+    <t xml:space="preserve">72.8285522460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9700775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.06591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.5270690917969</t>
   </si>
   <si>
     <t xml:space="preserve">79.9515991210938</t>
   </si>
   <si>
-    <t xml:space="preserve">75.3398818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1161193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0568542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.545524597168</t>
+    <t xml:space="preserve">75.3398742675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1161041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0568618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.545539855957</t>
   </si>
   <si>
     <t xml:space="preserve">70.6825103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0934677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9610061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1025314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.326286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0477981567383</t>
+    <t xml:space="preserve">71.0934524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9610137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3262786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0478057861328</t>
   </si>
   <si>
     <t xml:space="preserve">70.8651504516602</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">68.4908065795898</t>
   </si>
   <si>
-    <t xml:space="preserve">68.856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3217697143555</t>
+    <t xml:space="preserve">68.8560943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">66.8013763427734</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">67.3949508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">66.938346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187286376953</t>
+    <t xml:space="preserve">66.938362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187210083008</t>
   </si>
   <si>
     <t xml:space="preserve">67.5775985717773</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">66.8470230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5228652954102</t>
+    <t xml:space="preserve">65.5228805541992</t>
   </si>
   <si>
     <t xml:space="preserve">64.0160675048828</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">64.2900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7923049926758</t>
+    <t xml:space="preserve">64.7922973632812</t>
   </si>
   <si>
     <t xml:space="preserve">66.1621170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">64.9446868896484</t>
+    <t xml:space="preserve">64.944694519043</t>
   </si>
   <si>
     <t xml:space="preserve">66.2089309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6771850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3025894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0016708374023</t>
+    <t xml:space="preserve">66.6771697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0016784667969</t>
   </si>
   <si>
     <t xml:space="preserve">69.4866104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">69.205680847168</t>
+    <t xml:space="preserve">69.2056732177734</t>
   </si>
   <si>
     <t xml:space="preserve">69.627082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7508544921875</t>
+    <t xml:space="preserve">70.750862121582</t>
   </si>
   <si>
     <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675628662109</t>
+    <t xml:space="preserve">69.7675552368164</t>
   </si>
   <si>
     <t xml:space="preserve">70.8913269042969</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">73.0452194213867</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459487915039</t>
+    <t xml:space="preserve">75.2459411621094</t>
   </si>
   <si>
     <t xml:space="preserve">75.10546875</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">74.9650115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">74.5904159545898</t>
+    <t xml:space="preserve">74.5904235839844</t>
   </si>
   <si>
     <t xml:space="preserve">75.0586547851562</t>
@@ -1679,22 +1679,22 @@
     <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5570068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1355972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8713531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8847808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9784317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7109222412109</t>
+    <t xml:space="preserve">76.5570220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1356048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8713455200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8847732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9784164428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7109146118164</t>
   </si>
   <si>
     <t xml:space="preserve">78.6172561645508</t>
@@ -1703,31 +1703,31 @@
     <t xml:space="preserve">79.694221496582</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2727966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.6005630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2259674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4132843017578</t>
+    <t xml:space="preserve">79.2728118896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6005554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4132766723633</t>
   </si>
   <si>
     <t xml:space="preserve">79.7878646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">80.0219802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0386734008789</t>
+    <t xml:space="preserve">80.0219650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0386810302734</t>
   </si>
   <si>
     <t xml:space="preserve">79.8815078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6775131225586</t>
+    <t xml:space="preserve">80.6775207519531</t>
   </si>
   <si>
     <t xml:space="preserve">80.3029251098633</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">80.7711563110352</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0354156494141</t>
+    <t xml:space="preserve">82.0354080200195</t>
   </si>
   <si>
     <t xml:space="preserve">81.7076416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">81.3798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3330535888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2394027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2227096557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.145751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497467041016</t>
+    <t xml:space="preserve">81.3798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3330383300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2394104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2227020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497543334961</t>
   </si>
   <si>
     <t xml:space="preserve">79.9751586914062</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">82.2695236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5036468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0187149047852</t>
+    <t xml:space="preserve">82.5036392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0187072753906</t>
   </si>
   <si>
     <t xml:space="preserve">83.2528305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6742248535156</t>
+    <t xml:space="preserve">82.9250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6742401123047</t>
   </si>
   <si>
     <t xml:space="preserve">82.9718780517578</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">84.0019989013672</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7980194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.7813186645508</t>
+    <t xml:space="preserve">84.7980270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7813110351562</t>
   </si>
   <si>
     <t xml:space="preserve">86.8582611083984</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">85.8281402587891</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6876602172852</t>
+    <t xml:space="preserve">85.6876678466797</t>
   </si>
   <si>
     <t xml:space="preserve">85.2194290161133</t>
@@ -1814,58 +1814,58 @@
     <t xml:space="preserve">85.1257781982422</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6408538818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7410354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.256103515625</t>
+    <t xml:space="preserve">85.6408386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7410430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2560958862305</t>
   </si>
   <si>
     <t xml:space="preserve">81.5671615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8481140136719</t>
+    <t xml:space="preserve">81.8480987548828</t>
   </si>
   <si>
     <t xml:space="preserve">83.8147125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">84.1893005371094</t>
+    <t xml:space="preserve">84.1893081665039</t>
   </si>
   <si>
     <t xml:space="preserve">84.2829513549805</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3130722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1693267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4804000854492</t>
+    <t xml:space="preserve">85.3130798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4804077148438</t>
   </si>
   <si>
     <t xml:space="preserve">91.2596969604492</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2128829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6854858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656265258789</t>
+    <t xml:space="preserve">91.212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6854934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656188964844</t>
   </si>
   <si>
     <t xml:space="preserve">92.1580963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">91.543701171875</t>
+    <t xml:space="preserve">91.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">90.8348007202148</t>
@@ -1874,31 +1874,31 @@
     <t xml:space="preserve">90.5984954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1806716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3299865722656</t>
+    <t xml:space="preserve">89.1806793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3299789428711</t>
   </si>
   <si>
     <t xml:space="preserve">88.8025894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">86.5340881347656</t>
+    <t xml:space="preserve">86.5340957641602</t>
   </si>
   <si>
     <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3546752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9690551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1033172607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5608444213867</t>
+    <t xml:space="preserve">91.3546600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9690628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1033096313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5608520507812</t>
   </si>
   <si>
     <t xml:space="preserve">96.4115371704102</t>
@@ -1907,40 +1907,40 @@
     <t xml:space="preserve">93.8122100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0731964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8293533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3416900634766</t>
+    <t xml:space="preserve">97.0731811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3416976928711</t>
   </si>
   <si>
     <t xml:space="preserve">101.326637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6800537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.247184753418</t>
+    <t xml:space="preserve">98.680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2471771240234</t>
   </si>
   <si>
     <t xml:space="preserve">96.884147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6403274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9389419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.317024230957</t>
+    <t xml:space="preserve">97.6403350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9389495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3170394897461</t>
   </si>
   <si>
     <t xml:space="preserve">96.5060653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2622451782227</t>
+    <t xml:space="preserve">97.2622375488281</t>
   </si>
   <si>
     <t xml:space="preserve">96.9786758422852</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">99.5307540893555</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3019638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.3567581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2074432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1677169799805</t>
+    <t xml:space="preserve">98.3019714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3567504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2074508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">97.5457916259766</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">96.2225112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7499008178711</t>
+    <t xml:space="preserve">95.7498931884766</t>
   </si>
   <si>
     <t xml:space="preserve">95.8444213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4663314819336</t>
+    <t xml:space="preserve">95.4663391113281</t>
   </si>
   <si>
     <t xml:space="preserve">96.7896347045898</t>
@@ -1985,25 +1985,25 @@
     <t xml:space="preserve">100.475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">99.1526565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.664993286133</t>
+    <t xml:space="preserve">99.1526641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.799247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.665000915527</t>
   </si>
   <si>
     <t xml:space="preserve">100.097869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9088287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.192390441895</t>
+    <t xml:space="preserve">99.908821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3964767456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.192398071289</t>
   </si>
   <si>
     <t xml:space="preserve">102.36637878418</t>
@@ -2012,37 +2012,37 @@
     <t xml:space="preserve">102.17733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">103.784194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.028030395508</t>
+    <t xml:space="preserve">103.784202575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.028022766113</t>
   </si>
   <si>
     <t xml:space="preserve">100.003356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">101.13761138916</t>
+    <t xml:space="preserve">101.137603759766</t>
   </si>
   <si>
     <t xml:space="preserve">101.704719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">103.689674377441</t>
+    <t xml:space="preserve">103.689659118652</t>
   </si>
   <si>
     <t xml:space="preserve">103.500625610352</t>
   </si>
   <si>
-    <t xml:space="preserve">102.933502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.38143157959</t>
+    <t xml:space="preserve">102.933517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.381423950195</t>
   </si>
   <si>
     <t xml:space="preserve">98.5855407714844</t>
   </si>
   <si>
-    <t xml:space="preserve">96.6950988769531</t>
+    <t xml:space="preserve">96.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">98.1129302978516</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">100.286911010742</t>
   </si>
   <si>
-    <t xml:space="preserve">99.7197875976562</t>
+    <t xml:space="preserve">99.7197799682617</t>
   </si>
   <si>
     <t xml:space="preserve">100.854034423828</t>
@@ -2066,10 +2066,10 @@
     <t xml:space="preserve">99.6252670288086</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4266052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7101745605469</t>
+    <t xml:space="preserve">94.4265975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7101669311523</t>
   </si>
   <si>
     <t xml:space="preserve">93.8594818115234</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">94.0957870483398</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2848281860352</t>
+    <t xml:space="preserve">94.2848205566406</t>
   </si>
   <si>
     <t xml:space="preserve">94.6156463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">94.521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6382293701172</t>
+    <t xml:space="preserve">94.5211181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6382217407227</t>
   </si>
   <si>
     <t xml:space="preserve">92.3471374511719</t>
@@ -2096,25 +2096,25 @@
     <t xml:space="preserve">91.3074035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">92.2998733520508</t>
+    <t xml:space="preserve">92.2998809814453</t>
   </si>
   <si>
     <t xml:space="preserve">91.7327575683594</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0163116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1505661010742</t>
+    <t xml:space="preserve">92.0163040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1505737304688</t>
   </si>
   <si>
     <t xml:space="preserve">95.3718185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8046798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8691024780273</t>
+    <t xml:space="preserve">94.8046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8690948486328</t>
   </si>
   <si>
     <t xml:space="preserve">97.9238815307617</t>
@@ -2129,67 +2129,67 @@
     <t xml:space="preserve">104.634887695312</t>
   </si>
   <si>
-    <t xml:space="preserve">105.958183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.226684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.659561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.077377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.574661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.803428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519866943359</t>
+    <t xml:space="preserve">105.95817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.226692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.659553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.07738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.574653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.803436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519859313965</t>
   </si>
   <si>
     <t xml:space="preserve">114.65412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">111.818504333496</t>
+    <t xml:space="preserve">111.818496704102</t>
   </si>
   <si>
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977424621582</t>
+    <t xml:space="preserve">115.977416992188</t>
   </si>
   <si>
     <t xml:space="preserve">117.206199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">117.017158508301</t>
+    <t xml:space="preserve">117.017150878906</t>
   </si>
   <si>
     <t xml:space="preserve">115.315773010254</t>
   </si>
   <si>
-    <t xml:space="preserve">114.370559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.425346374512</t>
+    <t xml:space="preserve">114.370552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.425354003906</t>
   </si>
   <si>
     <t xml:space="preserve">109.644500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">111.251365661621</t>
+    <t xml:space="preserve">111.251358032227</t>
   </si>
   <si>
     <t xml:space="preserve">110.589714050293</t>
   </si>
   <si>
-    <t xml:space="preserve">110.30615234375</t>
+    <t xml:space="preserve">110.306137084961</t>
   </si>
   <si>
     <t xml:space="preserve">111.156837463379</t>
@@ -2198,52 +2198,52 @@
     <t xml:space="preserve">111.723968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.117118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.833549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.510246276855</t>
+    <t xml:space="preserve">111.062324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.117111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.833541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.510261535645</t>
   </si>
   <si>
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291091918945</t>
+    <t xml:space="preserve">112.29109954834</t>
   </si>
   <si>
     <t xml:space="preserve">112.952743530273</t>
   </si>
   <si>
-    <t xml:space="preserve">110.873275756836</t>
+    <t xml:space="preserve">110.873291015625</t>
   </si>
   <si>
     <t xml:space="preserve">109.455467224121</t>
   </si>
   <si>
-    <t xml:space="preserve">107.470520019531</t>
+    <t xml:space="preserve">107.470512390137</t>
   </si>
   <si>
     <t xml:space="preserve">110.49520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">108.037651062012</t>
+    <t xml:space="preserve">108.037643432617</t>
   </si>
   <si>
     <t xml:space="preserve">107.848602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">108.793815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.430786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.171905517578</t>
+    <t xml:space="preserve">108.793807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.430778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.171897888184</t>
   </si>
   <si>
     <t xml:space="preserve">109.266418457031</t>
@@ -2252,19 +2252,19 @@
     <t xml:space="preserve">106.997909545898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.918449401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.769134521484</t>
+    <t xml:space="preserve">104.91845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.769142150879</t>
   </si>
   <si>
     <t xml:space="preserve">107.754081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">108.415725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.32120513916</t>
+    <t xml:space="preserve">108.415718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.321197509766</t>
   </si>
   <si>
     <t xml:space="preserve">110.211631774902</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
-    <t xml:space="preserve">109.928062438965</t>
+    <t xml:space="preserve">109.928070068359</t>
   </si>
   <si>
     <t xml:space="preserve">104.54035949707</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">98.7745742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">106.808876037598</t>
+    <t xml:space="preserve">106.808868408203</t>
   </si>
   <si>
     <t xml:space="preserve">103.595153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">101.893768310547</t>
+    <t xml:space="preserve">101.893775939941</t>
   </si>
   <si>
     <t xml:space="preserve">99.8143081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">108.132164001465</t>
+    <t xml:space="preserve">108.132171630859</t>
   </si>
   <si>
     <t xml:space="preserve">105.485572814941</t>
   </si>
   <si>
-    <t xml:space="preserve">110.400672912598</t>
+    <t xml:space="preserve">110.400680541992</t>
   </si>
   <si>
     <t xml:space="preserve">108.888336181641</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">111.629447937012</t>
   </si>
   <si>
-    <t xml:space="preserve">118.056884765625</t>
+    <t xml:space="preserve">118.05689239502</t>
   </si>
   <si>
     <t xml:space="preserve">122.310325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">126.091156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.329574584961</t>
+    <t xml:space="preserve">126.091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.329559326172</t>
   </si>
   <si>
     <t xml:space="preserve">141.592651367188</t>
@@ -2342,16 +2342,16 @@
     <t xml:space="preserve">141.876220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">136.583038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.089904785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.239227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.959854125977</t>
+    <t xml:space="preserve">136.583023071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.089920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.2392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.959823608398</t>
   </si>
   <si>
     <t xml:space="preserve">150.383102416992</t>
@@ -2360,58 +2360,58 @@
     <t xml:space="preserve">153.691360473633</t>
   </si>
   <si>
-    <t xml:space="preserve">157.755767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.944793701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791305541992</t>
+    <t xml:space="preserve">157.755752563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.944808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.791320800781</t>
   </si>
   <si>
     <t xml:space="preserve">146.885818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">146.507720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.52278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.318710327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.641998291016</t>
+    <t xml:space="preserve">146.507736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.522796630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.318695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.641983032227</t>
   </si>
   <si>
     <t xml:space="preserve">153.596817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">151.706420898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.048934936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.302383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.10791015625</t>
+    <t xml:space="preserve">151.706390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.048919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.302398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.107894897461</t>
   </si>
   <si>
     <t xml:space="preserve">174.675033569336</t>
   </si>
   <si>
-    <t xml:space="preserve">169.381866455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.440841674805</t>
+    <t xml:space="preserve">169.381851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.440826416016</t>
   </si>
   <si>
     <t xml:space="preserve">191.688842773438</t>
@@ -2420,22 +2420,22 @@
     <t xml:space="preserve">197.927215576172</t>
   </si>
   <si>
-    <t xml:space="preserve">186.206634521484</t>
+    <t xml:space="preserve">186.206619262695</t>
   </si>
   <si>
     <t xml:space="preserve">163.521545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.172332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.555816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.098297119141</t>
+    <t xml:space="preserve">171.839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.172317504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.55583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.098266601562</t>
   </si>
   <si>
     <t xml:space="preserve">163.994155883789</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">155.0146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">158.606430053711</t>
+    <t xml:space="preserve">158.6064453125</t>
   </si>
   <si>
     <t xml:space="preserve">157.850280761719</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">162.36572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">161.890411376953</t>
+    <t xml:space="preserve">161.890426635742</t>
   </si>
   <si>
     <t xml:space="preserve">161.129913330078</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">159.133605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">162.270660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.11882019043</t>
+    <t xml:space="preserve">162.270629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.118804931641</t>
   </si>
   <si>
     <t xml:space="preserve">164.457077026367</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">162.936080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">161.320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.985473632812</t>
+    <t xml:space="preserve">161.320022583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.985458374023</t>
   </si>
   <si>
     <t xml:space="preserve">162.55583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">162.841033935547</t>
+    <t xml:space="preserve">162.841049194336</t>
   </si>
   <si>
     <t xml:space="preserve">162.650909423828</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.685455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.350921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.031143188477</t>
+    <t xml:space="preserve">169.685485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.35090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.031158447266</t>
   </si>
   <si>
     <t xml:space="preserve">164.361999511719</t>
@@ -2525,49 +2525,49 @@
     <t xml:space="preserve">164.647201538086</t>
   </si>
   <si>
-    <t xml:space="preserve">169.305221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.400299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.96696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.495361328125</t>
+    <t xml:space="preserve">169.305252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.400283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.966949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.495376586914</t>
   </si>
   <si>
     <t xml:space="preserve">166.358306884766</t>
   </si>
   <si>
-    <t xml:space="preserve">160.939788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.665710449219</t>
+    <t xml:space="preserve">160.939804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.66569519043</t>
   </si>
   <si>
     <t xml:space="preserve">162.175598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">164.742263793945</t>
+    <t xml:space="preserve">164.742279052734</t>
   </si>
   <si>
     <t xml:space="preserve">159.228652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">157.802749633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.669403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.81755065918</t>
+    <t xml:space="preserve">157.802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.669418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.817565917969</t>
   </si>
   <si>
     <t xml:space="preserve">146.77555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768188476562</t>
+    <t xml:space="preserve">150.768173217773</t>
   </si>
   <si>
     <t xml:space="preserve">145.254577636719</t>
@@ -2582,19 +2582,19 @@
     <t xml:space="preserve">151.623718261719</t>
   </si>
   <si>
-    <t xml:space="preserve">148.391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.7607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.243469238281</t>
+    <t xml:space="preserve">148.391647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.760757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.243499755859</t>
   </si>
   <si>
     <t xml:space="preserve">154.190383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">154.855834960938</t>
+    <t xml:space="preserve">154.855819702148</t>
   </si>
   <si>
     <t xml:space="preserve">154.950881958008</t>
@@ -2603,61 +2603,61 @@
     <t xml:space="preserve">155.426193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">155.806457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.418792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.634826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.600234985352</t>
+    <t xml:space="preserve">155.806427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.41877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.634811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.600250244141</t>
   </si>
   <si>
     <t xml:space="preserve">144.018768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">144.589157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.543472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.55827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.797775268555</t>
+    <t xml:space="preserve">144.589141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.54345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.558288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.797760009766</t>
   </si>
   <si>
     <t xml:space="preserve">137.364440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">137.174301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.779251098633</t>
+    <t xml:space="preserve">137.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.779266357422</t>
   </si>
   <si>
     <t xml:space="preserve">143.258270263672</t>
   </si>
   <si>
-    <t xml:space="preserve">147.060760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.726181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.247161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.95458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.034851074219</t>
+    <t xml:space="preserve">147.060745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.726165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.247177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.954574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.387924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.03483581543</t>
   </si>
   <si>
     <t xml:space="preserve">160.654586791992</t>
@@ -2666,19 +2666,19 @@
     <t xml:space="preserve">162.080520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">161.795333862305</t>
+    <t xml:space="preserve">161.795349121094</t>
   </si>
   <si>
     <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.294128417969</t>
+    <t xml:space="preserve">168.069442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.913864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.29411315918</t>
   </si>
   <si>
     <t xml:space="preserve">177.670669555664</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">173.487945556641</t>
   </si>
   <si>
-    <t xml:space="preserve">178.716339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.712692260742</t>
+    <t xml:space="preserve">178.716354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.712677001953</t>
   </si>
   <si>
     <t xml:space="preserve">178.24104309082</t>
@@ -2699,16 +2699,16 @@
     <t xml:space="preserve">181.853408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">179.666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990463256836</t>
+    <t xml:space="preserve">179.666976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990447998047</t>
   </si>
   <si>
     <t xml:space="preserve">184.039840698242</t>
   </si>
   <si>
-    <t xml:space="preserve">181.663284301758</t>
+    <t xml:space="preserve">181.663299560547</t>
   </si>
   <si>
     <t xml:space="preserve">185.275619506836</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">179.191665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">176.529937744141</t>
+    <t xml:space="preserve">176.529922485352</t>
   </si>
   <si>
     <t xml:space="preserve">177.860809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">184.610214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.838592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.264526367188</t>
+    <t xml:space="preserve">184.61018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.838577270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.264511108398</t>
   </si>
   <si>
     <t xml:space="preserve">159.703979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">163.88671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.217590332031</t>
+    <t xml:space="preserve">163.886688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.217575073242</t>
   </si>
   <si>
     <t xml:space="preserve">164.932388305664</t>
@@ -2759,34 +2759,34 @@
     <t xml:space="preserve">164.076843261719</t>
   </si>
   <si>
-    <t xml:space="preserve">156.947189331055</t>
+    <t xml:space="preserve">156.947219848633</t>
   </si>
   <si>
     <t xml:space="preserve">160.844711303711</t>
   </si>
   <si>
-    <t xml:space="preserve">164.266967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.879318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.696578979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.605209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.084213256836</t>
+    <t xml:space="preserve">164.266952514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.879333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.696563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.605224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.084228515625</t>
   </si>
   <si>
     <t xml:space="preserve">162.745956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">160.179290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.32373046875</t>
+    <t xml:space="preserve">160.179306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.323745727539</t>
   </si>
   <si>
     <t xml:space="preserve">158.468170166016</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">158.848434448242</t>
   </si>
   <si>
-    <t xml:space="preserve">163.221252441406</t>
+    <t xml:space="preserve">163.221267700195</t>
   </si>
   <si>
     <t xml:space="preserve">159.038558959961</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">161.224975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">153.810134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.859497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.528656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.616317749023</t>
+    <t xml:space="preserve">153.810150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.859527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.52864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.616302490234</t>
   </si>
   <si>
     <t xml:space="preserve">154.475570678711</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">179.001556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">168.92497253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.68180847168</t>
+    <t xml:space="preserve">168.924987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.681793212891</t>
   </si>
   <si>
     <t xml:space="preserve">171.111404418945</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">170.541030883789</t>
   </si>
   <si>
-    <t xml:space="preserve">167.784255981445</t>
+    <t xml:space="preserve">167.784240722656</t>
   </si>
   <si>
     <t xml:space="preserve">167.499053955078</t>
@@ -2870,28 +2870,28 @@
     <t xml:space="preserve">175.389190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">176.434875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.149688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.195373535156</t>
+    <t xml:space="preserve">176.43489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.149703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.195358276367</t>
   </si>
   <si>
     <t xml:space="preserve">174.438568115234</t>
   </si>
   <si>
-    <t xml:space="preserve">156.186676025391</t>
+    <t xml:space="preserve">156.18669128418</t>
   </si>
   <si>
     <t xml:space="preserve">151.813842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">155.996566772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.380508422852</t>
+    <t xml:space="preserve">155.99658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.380493164062</t>
   </si>
   <si>
     <t xml:space="preserve">155.901504516602</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">154.000259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">150.197784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.057052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.155807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.706405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.082977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.6953125</t>
+    <t xml:space="preserve">150.197799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.057037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.155822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.706420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.082962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.695297241211</t>
   </si>
   <si>
     <t xml:space="preserve">134.987884521484</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">133.181716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">136.033569335938</t>
+    <t xml:space="preserve">136.033599853516</t>
   </si>
   <si>
     <t xml:space="preserve">133.276763916016</t>
@@ -2936,73 +2936,73 @@
     <t xml:space="preserve">134.037261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">133.086654663086</t>
+    <t xml:space="preserve">133.086639404297</t>
   </si>
   <si>
     <t xml:space="preserve">135.273071289062</t>
   </si>
   <si>
-    <t xml:space="preserve">132.136016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.519958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.044677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.848999023438</t>
+    <t xml:space="preserve">132.136032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.519989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.90022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.044662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.848983764648</t>
   </si>
   <si>
     <t xml:space="preserve">135.463195800781</t>
   </si>
   <si>
-    <t xml:space="preserve">133.229248046875</t>
+    <t xml:space="preserve">133.229232788086</t>
   </si>
   <si>
     <t xml:space="preserve">145.492218017578</t>
   </si>
   <si>
-    <t xml:space="preserve">143.59098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.784805297852</t>
+    <t xml:space="preserve">143.590972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.784790039062</t>
   </si>
   <si>
     <t xml:space="preserve">148.20149230957</t>
   </si>
   <si>
-    <t xml:space="preserve">148.058883666992</t>
+    <t xml:space="preserve">148.058898925781</t>
   </si>
   <si>
     <t xml:space="preserve">146.300247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.01692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.984191894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.794067382812</t>
+    <t xml:space="preserve">145.016906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874313354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.98420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">133.324310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">134.274932861328</t>
+    <t xml:space="preserve">134.274917602539</t>
   </si>
   <si>
     <t xml:space="preserve">133.894683837891</t>
   </si>
   <si>
-    <t xml:space="preserve">134.227386474609</t>
+    <t xml:space="preserve">134.227401733398</t>
   </si>
   <si>
     <t xml:space="preserve">131.660720825195</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">131.470596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">131.185409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.655181884766</t>
+    <t xml:space="preserve">131.185424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.655166625977</t>
   </si>
   <si>
     <t xml:space="preserve">136.889114379883</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">136.983871459961</t>
   </si>
   <si>
-    <t xml:space="preserve">136.744537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.845397949219</t>
+    <t xml:space="preserve">136.744552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.84538269043</t>
   </si>
   <si>
     <t xml:space="preserve">137.797515869141</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">138.084701538086</t>
   </si>
   <si>
-    <t xml:space="preserve">138.46760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.978729248047</t>
+    <t xml:space="preserve">138.467590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.978744506836</t>
   </si>
   <si>
     <t xml:space="preserve">133.05908203125</t>
@@ -3071,19 +3071,19 @@
     <t xml:space="preserve">137.510345458984</t>
   </si>
   <si>
-    <t xml:space="preserve">138.659057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.2060546875</t>
+    <t xml:space="preserve">138.659072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.185531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.206069946289</t>
   </si>
   <si>
     <t xml:space="preserve">144.306900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">144.019714355469</t>
+    <t xml:space="preserve">144.01969909668</t>
   </si>
   <si>
     <t xml:space="preserve">146.269287109375</t>
@@ -3095,31 +3095,31 @@
     <t xml:space="preserve">147.322250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">146.843627929688</t>
+    <t xml:space="preserve">146.843612670898</t>
   </si>
   <si>
     <t xml:space="preserve">147.226531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">143.397491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.428237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.289764404297</t>
+    <t xml:space="preserve">143.397506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.99235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.428253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.289749145508</t>
   </si>
   <si>
     <t xml:space="preserve">153.065811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">152.682922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.768402099609</t>
+    <t xml:space="preserve">152.682907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.76838684082</t>
   </si>
   <si>
     <t xml:space="preserve">151.534210205078</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">149.906875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">153.879470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.320495605469</t>
+    <t xml:space="preserve">153.879486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.320510864258</t>
   </si>
   <si>
     <t xml:space="preserve">152.395736694336</t>
   </si>
   <si>
-    <t xml:space="preserve">153.783752441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.123916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.458969116211</t>
+    <t xml:space="preserve">153.783767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">155.028198242188</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">160.149536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">162.207641601562</t>
+    <t xml:space="preserve">162.207656860352</t>
   </si>
   <si>
     <t xml:space="preserve">163.643539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">164.983688354492</t>
+    <t xml:space="preserve">164.983703613281</t>
   </si>
   <si>
     <t xml:space="preserve">161.729019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">160.915344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.351226806641</t>
+    <t xml:space="preserve">160.91535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.351257324219</t>
   </si>
   <si>
     <t xml:space="preserve">165.07942199707</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">163.834976196289</t>
   </si>
   <si>
-    <t xml:space="preserve">168.908462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.600799560547</t>
+    <t xml:space="preserve">168.908447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.600784301758</t>
   </si>
   <si>
     <t xml:space="preserve">168.142639160156</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">168.334121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">169.052062988281</t>
+    <t xml:space="preserve">169.05207824707</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">171.349472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">176.0400390625</t>
+    <t xml:space="preserve">176.040023803711</t>
   </si>
   <si>
     <t xml:space="preserve">176.949447631836</t>
@@ -3227,46 +3227,46 @@
     <t xml:space="preserve">177.140899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">180.1083984375</t>
+    <t xml:space="preserve">180.108383178711</t>
   </si>
   <si>
     <t xml:space="preserve">179.534057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">178.050308227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.475921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.810974121094</t>
+    <t xml:space="preserve">178.05029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.475936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.810989379883</t>
   </si>
   <si>
     <t xml:space="preserve">181.352844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">182.740875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.016036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.409194946289</t>
+    <t xml:space="preserve">182.740859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.016052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.4091796875</t>
   </si>
   <si>
     <t xml:space="preserve">193.270721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">195.568161010742</t>
+    <t xml:space="preserve">195.568145751953</t>
   </si>
   <si>
     <t xml:space="preserve">191.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">196.908325195312</t>
+    <t xml:space="preserve">196.908309936523</t>
   </si>
   <si>
     <t xml:space="preserve">196.812606811523</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">188.29296875</t>
   </si>
   <si>
-    <t xml:space="preserve">193.175018310547</t>
+    <t xml:space="preserve">193.175003051758</t>
   </si>
   <si>
     <t xml:space="preserve">190.351089477539</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">192.026306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">193.940811157227</t>
+    <t xml:space="preserve">193.940795898438</t>
   </si>
   <si>
     <t xml:space="preserve">195.855331420898</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">187.479309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">180.539169311523</t>
+    <t xml:space="preserve">180.539184570312</t>
   </si>
   <si>
     <t xml:space="preserve">174.987060546875</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">174.077682495117</t>
   </si>
   <si>
-    <t xml:space="preserve">173.599044799805</t>
+    <t xml:space="preserve">173.599029541016</t>
   </si>
   <si>
     <t xml:space="preserve">167.664016723633</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">162.782012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">163.404220581055</t>
+    <t xml:space="preserve">163.404205322266</t>
   </si>
   <si>
     <t xml:space="preserve">164.744400024414</t>
   </si>
   <si>
-    <t xml:space="preserve">162.111923217773</t>
+    <t xml:space="preserve">162.111938476562</t>
   </si>
   <si>
     <t xml:space="preserve">166.515319824219</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">170.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">171.25373840332</t>
+    <t xml:space="preserve">171.253723144531</t>
   </si>
   <si>
     <t xml:space="preserve">172.402465820312</t>
@@ -3347,34 +3347,34 @@
     <t xml:space="preserve">171.684539794922</t>
   </si>
   <si>
-    <t xml:space="preserve">173.742614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.715255737305</t>
+    <t xml:space="preserve">173.742630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.715240478516</t>
   </si>
   <si>
     <t xml:space="preserve">181.448577880859</t>
   </si>
   <si>
-    <t xml:space="preserve">180.826354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.88444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.83659362793</t>
+    <t xml:space="preserve">180.82633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.884460449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.836578369141</t>
   </si>
   <si>
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096420288086</t>
+    <t xml:space="preserve">187.096389770508</t>
   </si>
   <si>
     <t xml:space="preserve">187.000686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">188.723739624023</t>
+    <t xml:space="preserve">188.723724365234</t>
   </si>
   <si>
     <t xml:space="preserve">189.202362060547</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.69987487793</t>
+    <t xml:space="preserve">174.699890136719</t>
   </si>
   <si>
     <t xml:space="preserve">176.231506347656</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">175.561401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">177.093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.964828491211</t>
+    <t xml:space="preserve">177.093048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.964813232422</t>
   </si>
   <si>
     <t xml:space="preserve">180.874206542969</t>
@@ -3410,22 +3410,22 @@
     <t xml:space="preserve">175.896469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">176.614395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.800735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.636672973633</t>
+    <t xml:space="preserve">176.614410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.800720214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.636657714844</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">179.294738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.188766479492</t>
+    <t xml:space="preserve">179.294723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.188781738281</t>
   </si>
   <si>
     <t xml:space="preserve">180.682754516602</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">175.082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">170.296493530273</t>
+    <t xml:space="preserve">170.296478271484</t>
   </si>
   <si>
     <t xml:space="preserve">169.14778137207</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">172.306747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">172.928970336914</t>
+    <t xml:space="preserve">172.928955078125</t>
   </si>
   <si>
     <t xml:space="preserve">168.764877319336</t>
@@ -3461,19 +3461,19 @@
     <t xml:space="preserve">172.785369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">170.535797119141</t>
+    <t xml:space="preserve">170.535781860352</t>
   </si>
   <si>
     <t xml:space="preserve">152.060699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">153.688034057617</t>
+    <t xml:space="preserve">153.688049316406</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">154.932479858398</t>
+    <t xml:space="preserve">154.932495117188</t>
   </si>
   <si>
     <t xml:space="preserve">154.741012573242</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">152.15641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">153.640182495117</t>
+    <t xml:space="preserve">153.640167236328</t>
   </si>
   <si>
     <t xml:space="preserve">148.183807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">141.770156860352</t>
+    <t xml:space="preserve">141.770172119141</t>
   </si>
   <si>
     <t xml:space="preserve">143.780395507812</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">138.946228027344</t>
   </si>
   <si>
-    <t xml:space="preserve">140.717178344727</t>
+    <t xml:space="preserve">140.717163085938</t>
   </si>
   <si>
     <t xml:space="preserve">128.94287109375</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">126.884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">128.990753173828</t>
+    <t xml:space="preserve">128.990737915039</t>
   </si>
   <si>
     <t xml:space="preserve">129.325775146484</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">132.006103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">127.698440551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975364685059</t>
+    <t xml:space="preserve">127.698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975372314453</t>
   </si>
   <si>
     <t xml:space="preserve">120.518989562988</t>
@@ -3566,25 +3566,25 @@
     <t xml:space="preserve">120.662582397461</t>
   </si>
   <si>
-    <t xml:space="preserve">117.934387207031</t>
+    <t xml:space="preserve">117.934379577637</t>
   </si>
   <si>
     <t xml:space="preserve">114.631843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">117.072853088379</t>
+    <t xml:space="preserve">117.072860717773</t>
   </si>
   <si>
     <t xml:space="preserve">116.546363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">115.58910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.286560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.430145263672</t>
+    <t xml:space="preserve">115.589096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.286567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.430137634277</t>
   </si>
   <si>
     <t xml:space="preserve">116.211326599121</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">123.10359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">122.864273071289</t>
+    <t xml:space="preserve">122.864280700684</t>
   </si>
   <si>
     <t xml:space="preserve">127.93775177002</t>
   </si>
   <si>
-    <t xml:space="preserve">127.124084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.773666381836</t>
+    <t xml:space="preserve">127.124099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.77367401123</t>
   </si>
   <si>
     <t xml:space="preserve">123.15145111084</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">120.08821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">122.242050170898</t>
+    <t xml:space="preserve">122.242042541504</t>
   </si>
   <si>
     <t xml:space="preserve">117.503623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">120.806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541229248047</t>
+    <t xml:space="preserve">120.806159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541236877441</t>
   </si>
   <si>
     <t xml:space="preserve">117.599349975586</t>
@@ -3632,49 +3632,49 @@
     <t xml:space="preserve">121.859161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">131.71891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.293273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.693305969238</t>
+    <t xml:space="preserve">131.718933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.293258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.693321228027</t>
   </si>
   <si>
     <t xml:space="preserve">126.59757232666</t>
   </si>
   <si>
-    <t xml:space="preserve">125.257438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204444885254</t>
+    <t xml:space="preserve">125.257446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204437255859</t>
   </si>
   <si>
     <t xml:space="preserve">125.448883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.824890136719</t>
+    <t xml:space="preserve">133.824920654297</t>
   </si>
   <si>
     <t xml:space="preserve">135.73942565918</t>
   </si>
   <si>
-    <t xml:space="preserve">135.835159301758</t>
+    <t xml:space="preserve">135.83512878418</t>
   </si>
   <si>
     <t xml:space="preserve">139.329147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">139.616317749023</t>
+    <t xml:space="preserve">139.616333007812</t>
   </si>
   <si>
     <t xml:space="preserve">142.105194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">139.041946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.170181274414</t>
+    <t xml:space="preserve">139.041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.170196533203</t>
   </si>
   <si>
     <t xml:space="preserve">135.260803222656</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">128.559967041016</t>
   </si>
   <si>
-    <t xml:space="preserve">128.416381835938</t>
+    <t xml:space="preserve">128.416366577148</t>
   </si>
   <si>
     <t xml:space="preserve">126.454010009766</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">124.539489746094</t>
   </si>
   <si>
-    <t xml:space="preserve">120.997611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.7001953125</t>
+    <t xml:space="preserve">120.997619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.700202941895</t>
   </si>
   <si>
     <t xml:space="preserve">115.254066467285</t>
@@ -3716,40 +3716,40 @@
     <t xml:space="preserve">119.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">118.173706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.647216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.823295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.493370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.271186828613</t>
+    <t xml:space="preserve">118.173698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.64720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392532348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.823287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.493377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.271194458008</t>
   </si>
   <si>
     <t xml:space="preserve">106.590858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">109.654090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.165214538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.009620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.871147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.435272216797</t>
+    <t xml:space="preserve">109.654098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.16520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.009613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.871154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.435264587402</t>
   </si>
   <si>
     <t xml:space="preserve">110.563491821289</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">111.932792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">113.381454467773</t>
+    <t xml:space="preserve">113.381446838379</t>
   </si>
   <si>
     <t xml:space="preserve">117.292816162109</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">118.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">118.306884765625</t>
+    <t xml:space="preserve">118.30687713623</t>
   </si>
   <si>
     <t xml:space="preserve">116.761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">119.803825378418</t>
+    <t xml:space="preserve">119.803833007812</t>
   </si>
   <si>
     <t xml:space="preserve">116.278762817383</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">115.071548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">111.787933349609</t>
+    <t xml:space="preserve">111.787925720215</t>
   </si>
   <si>
     <t xml:space="preserve">110.918724060059</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">112.657119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">109.904678344727</t>
+    <t xml:space="preserve">109.904685974121</t>
   </si>
   <si>
     <t xml:space="preserve">114.685241699219</t>
@@ -3830,22 +3830,22 @@
     <t xml:space="preserve">113.526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">120.190132141113</t>
+    <t xml:space="preserve">120.190124511719</t>
   </si>
   <si>
     <t xml:space="preserve">123.377166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">122.797706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.866180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.914459228516</t>
+    <t xml:space="preserve">122.797714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.866172790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.914451599121</t>
   </si>
   <si>
     <t xml:space="preserve">122.025093078613</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">131.537933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">125.598449707031</t>
+    <t xml:space="preserve">125.598457336426</t>
   </si>
   <si>
     <t xml:space="preserve">127.964584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">124.970687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.916297912598</t>
+    <t xml:space="preserve">124.970680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.916282653809</t>
   </si>
   <si>
     <t xml:space="preserve">127.674842834473</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">128.785507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">125.936462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.234146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.958465576172</t>
+    <t xml:space="preserve">125.936454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.234161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.958480834961</t>
   </si>
   <si>
     <t xml:space="preserve">130.861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">128.640625</t>
+    <t xml:space="preserve">128.640609741211</t>
   </si>
   <si>
     <t xml:space="preserve">130.137557983398</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">132.213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">130.910186767578</t>
+    <t xml:space="preserve">130.910202026367</t>
   </si>
   <si>
     <t xml:space="preserve">131.924240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">135.111282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890014648438</t>
+    <t xml:space="preserve">135.111267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">131.779373168945</t>
@@ -3944,28 +3944,28 @@
     <t xml:space="preserve">130.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">132.02082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.489639282227</t>
+    <t xml:space="preserve">132.020812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.489624023438</t>
   </si>
   <si>
     <t xml:space="preserve">132.310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">126.515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.868011474609</t>
+    <t xml:space="preserve">126.515930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.86799621582</t>
   </si>
   <si>
     <t xml:space="preserve">126.467628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">125.888168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.171783447266</t>
+    <t xml:space="preserve">125.88818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.171798706055</t>
   </si>
   <si>
     <t xml:space="preserve">128.061172485352</t>
@@ -3980,16 +3980,16 @@
     <t xml:space="preserve">129.123504638672</t>
   </si>
   <si>
-    <t xml:space="preserve">129.992706298828</t>
+    <t xml:space="preserve">129.992721557617</t>
   </si>
   <si>
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.11555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473754882812</t>
+    <t xml:space="preserve">125.115562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473747253418</t>
   </si>
   <si>
     <t xml:space="preserve">121.397338867188</t>
@@ -4007,19 +4007,19 @@
     <t xml:space="preserve">112.463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">111.643051147461</t>
+    <t xml:space="preserve">111.643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.870445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.097831726074</t>
+    <t xml:space="preserve">107.779975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.870452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.09782409668</t>
   </si>
   <si>
     <t xml:space="preserve">113.816040039062</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">111.305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">108.50431060791</t>
+    <t xml:space="preserve">108.504302978516</t>
   </si>
   <si>
     <t xml:space="preserve">109.132064819336</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">114.974975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">123.763473510742</t>
+    <t xml:space="preserve">123.763481140137</t>
   </si>
   <si>
     <t xml:space="preserve">121.687072753906</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">124.58438873291</t>
   </si>
   <si>
-    <t xml:space="preserve">125.64673614502</t>
+    <t xml:space="preserve">125.646743774414</t>
   </si>
   <si>
     <t xml:space="preserve">131.586212158203</t>
@@ -4061,16 +4061,16 @@
     <t xml:space="preserve">124.680969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">127.771423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.660789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.922416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.314826965332</t>
+    <t xml:space="preserve">127.771430969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.660774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.922409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.314834594727</t>
   </si>
   <si>
     <t xml:space="preserve">124.777534484863</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">125.018974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">128.592330932617</t>
+    <t xml:space="preserve">128.592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">132.069107055664</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.765319824219</t>
+    <t xml:space="preserve">130.76530456543</t>
   </si>
   <si>
     <t xml:space="preserve">128.302612304688</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">128.206024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">127.047096252441</t>
+    <t xml:space="preserve">127.04711151123</t>
   </si>
   <si>
     <t xml:space="preserve">124.487808227539</t>
@@ -4109,25 +4109,25 @@
     <t xml:space="preserve">127.240257263184</t>
   </si>
   <si>
-    <t xml:space="preserve">129.316665649414</t>
+    <t xml:space="preserve">129.316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">128.157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">125.260429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.682800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.847839355469</t>
+    <t xml:space="preserve">125.26042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.509826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.682815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.84782409668</t>
   </si>
   <si>
     <t xml:space="preserve">125.067268371582</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.42546081543</t>
+    <t xml:space="preserve">123.425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">121.783645629883</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">123.522041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">123.039154052734</t>
+    <t xml:space="preserve">123.039161682129</t>
   </si>
   <si>
     <t xml:space="preserve">122.652847290039</t>
@@ -4157,19 +4157,19 @@
     <t xml:space="preserve">124.874122619629</t>
   </si>
   <si>
-    <t xml:space="preserve">125.405296325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.846000671387</t>
+    <t xml:space="preserve">125.405303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.845993041992</t>
   </si>
   <si>
     <t xml:space="preserve">122.169960021973</t>
   </si>
   <si>
-    <t xml:space="preserve">123.232307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.880226135254</t>
+    <t xml:space="preserve">123.232299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.880218505859</t>
   </si>
   <si>
     <t xml:space="preserve">122.218254089355</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">121.011039733887</t>
   </si>
   <si>
-    <t xml:space="preserve">120.479858398438</t>
+    <t xml:space="preserve">120.479866027832</t>
   </si>
   <si>
     <t xml:space="preserve">119.465797424316</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">117.775695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">116.906509399414</t>
+    <t xml:space="preserve">116.906517028809</t>
   </si>
   <si>
     <t xml:space="preserve">114.250648498535</t>
@@ -4223,10 +4223,10 @@
     <t xml:space="preserve">112.415679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">113.23657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.31909942627</t>
+    <t xml:space="preserve">113.236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.319107055664</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">109.42179107666</t>
   </si>
   <si>
-    <t xml:space="preserve">111.063606262207</t>
+    <t xml:space="preserve">111.063598632812</t>
   </si>
   <si>
     <t xml:space="preserve">110.242698669434</t>
@@ -4247,16 +4247,16 @@
     <t xml:space="preserve">107.20051574707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.186454772949</t>
+    <t xml:space="preserve">106.186447143555</t>
   </si>
   <si>
     <t xml:space="preserve">108.649169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">108.842330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.118003845215</t>
+    <t xml:space="preserve">108.842323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.11799621582</t>
   </si>
   <si>
     <t xml:space="preserve">107.73169708252</t>
@@ -4277,22 +4277,22 @@
     <t xml:space="preserve">103.675453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">102.081932067871</t>
+    <t xml:space="preserve">102.081924438477</t>
   </si>
   <si>
     <t xml:space="preserve">97.7359619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9431838989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5911026000977</t>
+    <t xml:space="preserve">98.9431762695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5911102294922</t>
   </si>
   <si>
     <t xml:space="preserve">95.1283874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5568771362305</t>
+    <t xml:space="preserve">98.556884765625</t>
   </si>
   <si>
     <t xml:space="preserve">94.6455001831055</t>
@@ -4304,46 +4304,46 @@
     <t xml:space="preserve">94.6648178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">95.070442199707</t>
+    <t xml:space="preserve">95.0704345703125</t>
   </si>
   <si>
     <t xml:space="preserve">93.737678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6797256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2100601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7851028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7078552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9887847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5252075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9694595336914</t>
+    <t xml:space="preserve">93.6797332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2100524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7078475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9887771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5251998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9694671630859</t>
   </si>
   <si>
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342514038086</t>
+    <t xml:space="preserve">93.8342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">95.5340118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9589538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1819229125977</t>
+    <t xml:space="preserve">95.9589462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1819305419922</t>
   </si>
   <si>
     <t xml:space="preserve">93.1582183837891</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">95.1090774536133</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3750915527344</t>
+    <t xml:space="preserve">94.3750839233398</t>
   </si>
   <si>
     <t xml:space="preserve">94.6068725585938</t>
@@ -4364,16 +4364,16 @@
     <t xml:space="preserve">100.874717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">98.7017364501953</t>
+    <t xml:space="preserve">98.7017288208008</t>
   </si>
   <si>
     <t xml:space="preserve">101.164451599121</t>
   </si>
   <si>
-    <t xml:space="preserve">101.985359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.45418548584</t>
+    <t xml:space="preserve">101.9853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.454193115234</t>
   </si>
   <si>
     <t xml:space="preserve">98.0739898681641</t>
@@ -5889,6 +5889,9 @@
   </si>
   <si>
     <t xml:space="preserve">74.2399978637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9400024414062</t>
   </si>
 </sst>
 </file>
@@ -70941,7 +70944,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6499074074</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>191990</v>
@@ -70962,6 +70965,32 @@
         <v>1958</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6501273148</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>175028</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>75.0800018310547</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>74.1399993896484</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>74.4800033569336</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>74.9400024414062</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="1965">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.298095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0423126220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9276428222656</t>
+    <t xml:space="preserve">43.2980918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.042308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9276466369629</t>
   </si>
   <si>
     <t xml:space="preserve">42.8218040466309</t>
@@ -59,82 +59,82 @@
     <t xml:space="preserve">42.1514701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4690055847168</t>
+    <t xml:space="preserve">42.4690017700195</t>
   </si>
   <si>
     <t xml:space="preserve">41.7281036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2870903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9993553161621</t>
+    <t xml:space="preserve">41.2870979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9993629455566</t>
   </si>
   <si>
     <t xml:space="preserve">39.2761001586914</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0765609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384246826172</t>
+    <t xml:space="preserve">38.0765647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384208679199</t>
   </si>
   <si>
     <t xml:space="preserve">37.6443786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9585723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2551460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7776985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.068775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2341766357422</t>
+    <t xml:space="preserve">38.9585838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2551422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.260627746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3664855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7777061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0687713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9982070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780479431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2341804504395</t>
   </si>
   <si>
     <t xml:space="preserve">39.4172248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7590408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0148239135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881309509277</t>
+    <t xml:space="preserve">37.7590370178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0148277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881271362305</t>
   </si>
   <si>
     <t xml:space="preserve">38.6057739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">38.402904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1228332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3962669372559</t>
+    <t xml:space="preserve">38.4029159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1228370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3962631225586</t>
   </si>
   <si>
     <t xml:space="preserve">40.4932861328125</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">41.4017562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5483779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9397888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5924758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2098960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011840820312</t>
+    <t xml:space="preserve">42.5483818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9397850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.209888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.901180267334</t>
   </si>
   <si>
     <t xml:space="preserve">43.2275238037109</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">42.5571975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8074798583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6454010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7071342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7600593566895</t>
+    <t xml:space="preserve">41.8074913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6454048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.707145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7600631713867</t>
   </si>
   <si>
     <t xml:space="preserve">40.7578887939453</t>
   </si>
   <si>
-    <t xml:space="preserve">40.352165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0081748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1636238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5726623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1581153869629</t>
+    <t xml:space="preserve">40.3521614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.008171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1636123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5726661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1581230163574</t>
   </si>
   <si>
     <t xml:space="preserve">39.6200904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1140174865723</t>
+    <t xml:space="preserve">40.1140213012695</t>
   </si>
   <si>
     <t xml:space="preserve">40.2904243469238</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">40.4668235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1007232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7622375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2914428710938</t>
+    <t xml:space="preserve">44.1007194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7622299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2914390563965</t>
   </si>
   <si>
     <t xml:space="preserve">45.8647499084473</t>
@@ -236,88 +236,88 @@
     <t xml:space="preserve">45.9088516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4237480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.203239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8945426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9386367797852</t>
+    <t xml:space="preserve">45.4237442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2032470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8945350646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9386405944824</t>
   </si>
   <si>
     <t xml:space="preserve">45.3355445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.982738494873</t>
+    <t xml:space="preserve">44.8063316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7181358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9827346801758</t>
   </si>
   <si>
     <t xml:space="preserve">44.8504371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">45.776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8206596374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3057518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1734580993652</t>
+    <t xml:space="preserve">45.7765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8206520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3057594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.173454284668</t>
   </si>
   <si>
     <t xml:space="preserve">46.2616577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6144676208496</t>
+    <t xml:space="preserve">46.6144599914551</t>
   </si>
   <si>
     <t xml:space="preserve">46.0852546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4226608276367</t>
+    <t xml:space="preserve">45.9970550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4226684570312</t>
   </si>
   <si>
     <t xml:space="preserve">47.5119743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1100807189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195220947266</t>
+    <t xml:space="preserve">47.1100921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195259094238</t>
   </si>
   <si>
     <t xml:space="preserve">48.5836753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553726196289</t>
+    <t xml:space="preserve">49.5660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553688049316</t>
   </si>
   <si>
     <t xml:space="preserve">50.2358741760254</t>
@@ -329,31 +329,31 @@
     <t xml:space="preserve">49.9679489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1641807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7000274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9855575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7352485656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6188926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9314765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0924758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427848815918</t>
+    <t xml:space="preserve">49.1641731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000312805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9855537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7352447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6188850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9314651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427925109863</t>
   </si>
   <si>
     <t xml:space="preserve">46.1723518371582</t>
@@ -371,49 +371,49 @@
     <t xml:space="preserve">49.7446746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">50.414493560791</t>
+    <t xml:space="preserve">50.4144859313965</t>
   </si>
   <si>
     <t xml:space="preserve">48.1371307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9409103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8339881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.030216217041</t>
+    <t xml:space="preserve">48.9409065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8339920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0302200317383</t>
   </si>
   <si>
     <t xml:space="preserve">50.5931091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">51.21826171875</t>
+    <t xml:space="preserve">51.2182655334473</t>
   </si>
   <si>
     <t xml:space="preserve">51.2629241943359</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9503402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5755004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.798770904541</t>
+    <t xml:space="preserve">50.9503364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8610343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5755043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7987670898438</t>
   </si>
   <si>
     <t xml:space="preserve">50.9949913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7717208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2805328369141</t>
+    <t xml:space="preserve">50.7717247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2805252075195</t>
   </si>
   <si>
     <t xml:space="preserve">50.057258605957</t>
@@ -422,49 +422,49 @@
     <t xml:space="preserve">49.8786392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6201553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5849304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1654434204102</t>
+    <t xml:space="preserve">50.1912155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6201477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5849342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0937423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1654396057129</t>
   </si>
   <si>
     <t xml:space="preserve">54.344051361084</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3710899353027</t>
+    <t xml:space="preserve">55.3710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">54.1207809448242</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0666961669922</t>
+    <t xml:space="preserve">52.0666885375977</t>
   </si>
   <si>
     <t xml:space="preserve">51.6648063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6824111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6377601623535</t>
+    <t xml:space="preserve">50.6824188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6377639770508</t>
   </si>
   <si>
     <t xml:space="preserve">52.2453117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7541160583496</t>
+    <t xml:space="preserve">51.7541122436523</t>
   </si>
   <si>
     <t xml:space="preserve">51.4415321350098</t>
@@ -473,49 +473,49 @@
     <t xml:space="preserve">51.3522300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8880767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.084300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4591407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4767570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2981414794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9773864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5132331848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6918487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346176147461</t>
+    <t xml:space="preserve">51.8880805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0843086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4591445922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4767532348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2981452941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9773902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5132369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6918525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346138000488</t>
   </si>
   <si>
     <t xml:space="preserve">52.6025428771973</t>
   </si>
   <si>
-    <t xml:space="preserve">52.289966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1830520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7094650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736106872559</t>
+    <t xml:space="preserve">52.2899589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.183048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7094612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736068725586</t>
   </si>
   <si>
     <t xml:space="preserve">50.7270736694336</t>
@@ -527,46 +527,46 @@
     <t xml:space="preserve">50.905689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0126075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176361083984</t>
+    <t xml:space="preserve">50.0126037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176322937012</t>
   </si>
   <si>
     <t xml:space="preserve">47.6459350585938</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8245506286621</t>
+    <t xml:space="preserve">47.8245468139648</t>
   </si>
   <si>
     <t xml:space="preserve">45.3239250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7258071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.395622253418</t>
+    <t xml:space="preserve">45.7258148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.547191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3956184387207</t>
   </si>
   <si>
     <t xml:space="preserve">46.6635437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7704620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1276931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5742416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4402809143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9937362670898</t>
+    <t xml:space="preserve">45.7704658508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1277008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5742378234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4402770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9937400817871</t>
   </si>
   <si>
     <t xml:space="preserve">45.4578895568848</t>
@@ -575,16 +575,16 @@
     <t xml:space="preserve">45.6811637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5295867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3063125610352</t>
+    <t xml:space="preserve">46.5295829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3063163757324</t>
   </si>
   <si>
     <t xml:space="preserve">47.2440528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4673194885254</t>
+    <t xml:space="preserve">47.4673233032227</t>
   </si>
   <si>
     <t xml:space="preserve">49.2088279724121</t>
@@ -593,40 +593,40 @@
     <t xml:space="preserve">50.3698387145996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1560020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5038032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8516006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6107177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8163795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1289596557617</t>
+    <t xml:space="preserve">52.156005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5037956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8516044616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.610725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8163833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">52.2006568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">52.468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3616638183594</t>
+    <t xml:space="preserve">52.4685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">53.4063186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4509658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6742401123047</t>
+    <t xml:space="preserve">53.4509696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.674243927002</t>
   </si>
   <si>
     <t xml:space="preserve">52.9151229858398</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">55.3264427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5050659179688</t>
+    <t xml:space="preserve">55.5050582885742</t>
   </si>
   <si>
     <t xml:space="preserve">56.2641792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1302146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6390228271484</t>
+    <t xml:space="preserve">56.1302185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6390266418457</t>
   </si>
   <si>
     <t xml:space="preserve">56.8000297546387</t>
@@ -665,223 +665,223 @@
     <t xml:space="preserve">56.5321006774902</t>
   </si>
   <si>
-    <t xml:space="preserve">56.978645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3358764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0503387451172</t>
+    <t xml:space="preserve">56.9786491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251861572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3358726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0503425598145</t>
   </si>
   <si>
     <t xml:space="preserve">58.8987693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0327339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7648124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0950050354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1572647094727</t>
+    <t xml:space="preserve">59.0327377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7648086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0950088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1572608947754</t>
   </si>
   <si>
     <t xml:space="preserve">57.3805313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5861930847168</t>
+    <t xml:space="preserve">58.5861968994141</t>
   </si>
   <si>
     <t xml:space="preserve">60.0151214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9434280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3006553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4088401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.158519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.622673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8906097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817939758301</t>
+    <t xml:space="preserve">58.9434242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3006629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440612792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4088325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6226768493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8906059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817977905273</t>
   </si>
   <si>
     <t xml:space="preserve">62.7390289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">62.5157508850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8635559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528694152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.946907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5342826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4379730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7542533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4831504821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5675735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0705490112305</t>
+    <t xml:space="preserve">62.515754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6758041381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9469032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0824508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5342864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4950675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7542572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.483154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5675659179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0705413818359</t>
   </si>
   <si>
     <t xml:space="preserve">64.8386688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5164260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668701171875</t>
+    <t xml:space="preserve">65.5164184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1668663024902</t>
   </si>
   <si>
     <t xml:space="preserve">63.0313148498535</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5223846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8897933959961</t>
+    <t xml:space="preserve">64.5223922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8898086547852</t>
   </si>
   <si>
     <t xml:space="preserve">64.432014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2964630126953</t>
+    <t xml:space="preserve">64.2964553833008</t>
   </si>
   <si>
     <t xml:space="preserve">64.1609115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">65.697151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0884094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6425323486328</t>
+    <t xml:space="preserve">65.6971435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0884208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6425285339355</t>
   </si>
   <si>
     <t xml:space="preserve">60.7721290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1847381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5462074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6877250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365776062012</t>
+    <t xml:space="preserve">60.184741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8173179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6877174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365737915039</t>
   </si>
   <si>
     <t xml:space="preserve">61.4498863220215</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3987503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735282897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927879333496</t>
+    <t xml:space="preserve">62.3987464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2120513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927803039551</t>
   </si>
   <si>
     <t xml:space="preserve">63.1216888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2393646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7815704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0134429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5104675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3297348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9682388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6067886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.019401550293</t>
+    <t xml:space="preserve">66.2393569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7815551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0134353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5104598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.329719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9682464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6067810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0193939208984</t>
   </si>
   <si>
     <t xml:space="preserve">65.2001419067383</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">64.7482986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7934722900391</t>
+    <t xml:space="preserve">64.7934951782227</t>
   </si>
   <si>
     <t xml:space="preserve">64.6579360961914</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4771881103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9801635742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.302433013916</t>
+    <t xml:space="preserve">64.4771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9801750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.302417755127</t>
   </si>
   <si>
     <t xml:space="preserve">65.4260482788086</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2845458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6008224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4652862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8719253540039</t>
+    <t xml:space="preserve">66.284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.600830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4652786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8719329833984</t>
   </si>
   <si>
     <t xml:space="preserve">66.0586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3749084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978469848633</t>
+    <t xml:space="preserve">66.3749008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978546142578</t>
   </si>
   <si>
     <t xml:space="preserve">66.6911926269531</t>
@@ -938,31 +938,31 @@
     <t xml:space="preserve">67.4141311645508</t>
   </si>
   <si>
-    <t xml:space="preserve">68.5437316894531</t>
+    <t xml:space="preserve">68.5437240600586</t>
   </si>
   <si>
     <t xml:space="preserve">68.137077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1822662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1311187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3058929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776992797852</t>
+    <t xml:space="preserve">67.865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.182258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.131103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.305908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776916503906</t>
   </si>
   <si>
     <t xml:space="preserve">71.3903045654297</t>
@@ -971,10 +971,10 @@
     <t xml:space="preserve">71.5258636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8480987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1643981933594</t>
+    <t xml:space="preserve">70.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1643905639648</t>
   </si>
   <si>
     <t xml:space="preserve">72.7910003662109</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">70.3510818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5318222045898</t>
+    <t xml:space="preserve">70.5318298339844</t>
   </si>
   <si>
     <t xml:space="preserve">70.7577285766602</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5769805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3451309204102</t>
+    <t xml:space="preserve">70.8029251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3451156616211</t>
   </si>
   <si>
     <t xml:space="preserve">70.4414520263672</t>
@@ -1013,43 +1013,43 @@
     <t xml:space="preserve">71.5710372924805</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9836502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1097717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5616073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4593353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2666778564453</t>
+    <t xml:space="preserve">70.983642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1097640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4593200683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.82080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2666625976562</t>
   </si>
   <si>
     <t xml:space="preserve">70.0347900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7636795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9955673217773</t>
+    <t xml:space="preserve">69.7636871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
     <t xml:space="preserve">67.3237762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3629913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0407485961914</t>
+    <t xml:space="preserve">68.3629989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0407562255859</t>
   </si>
   <si>
     <t xml:space="preserve">69.1763076782227</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">69.9444274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1703567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6102676391602</t>
+    <t xml:space="preserve">70.1703491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.887321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6102600097656</t>
   </si>
   <si>
     <t xml:space="preserve">69.8992385864258</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">68.4985504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4081726074219</t>
+    <t xml:space="preserve">68.4081802368164</t>
   </si>
   <si>
     <t xml:space="preserve">67.2785873413086</t>
   </si>
   <si>
-    <t xml:space="preserve">67.6400604248047</t>
+    <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
     <t xml:space="preserve">69.4022216796875</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">71.7969589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6162261962891</t>
+    <t xml:space="preserve">71.6162185668945</t>
   </si>
   <si>
     <t xml:space="preserve">71.9325103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0228652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7065887451172</t>
+    <t xml:space="preserve">72.0228729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7065734863281</t>
   </si>
   <si>
     <t xml:space="preserve">71.4806747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4354934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6614151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2547607421875</t>
+    <t xml:space="preserve">71.4354782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.254753112793</t>
   </si>
   <si>
     <t xml:space="preserve">69.8088760375977</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7517700195312</t>
+    <t xml:space="preserve">71.7517776489258</t>
   </si>
   <si>
     <t xml:space="preserve">68.0919036865234</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">66.9622955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8505783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572402954102</t>
+    <t xml:space="preserve">62.8505744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572364807129</t>
   </si>
   <si>
     <t xml:space="preserve">63.6187057495117</t>
@@ -1142,70 +1142,70 @@
     <t xml:space="preserve">63.0765037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9409446716309</t>
+    <t xml:space="preserve">62.9409523010254</t>
   </si>
   <si>
     <t xml:space="preserve">62.7602043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9017219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7329025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113594055176</t>
+    <t xml:space="preserve">61.901725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0040054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7328948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8113555908203</t>
   </si>
   <si>
     <t xml:space="preserve">63.799430847168</t>
   </si>
   <si>
-    <t xml:space="preserve">67.549690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7363891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838424682617</t>
+    <t xml:space="preserve">67.5496978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7363815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838500976562</t>
   </si>
   <si>
     <t xml:space="preserve">65.6519775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2905044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4200897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2726364135742</t>
+    <t xml:space="preserve">65.2904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4200820922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2726287841797</t>
   </si>
   <si>
     <t xml:space="preserve">70.1251602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8600082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6221771240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1192092895508</t>
+    <t xml:space="preserve">68.8600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540573120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1192016601562</t>
   </si>
   <si>
     <t xml:space="preserve">71.0740203857422</t>
@@ -1214,328 +1214,328 @@
     <t xml:space="preserve">72.6554489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6946868896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.474723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4687652587891</t>
+    <t xml:space="preserve">73.6946792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4747161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4687576293945</t>
   </si>
   <si>
     <t xml:space="preserve">73.1976547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3783874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.688720703125</t>
+    <t xml:space="preserve">73.3783950805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6887283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5591201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1983642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6960906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.928955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8466873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.7964935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1527099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.2576217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.4312133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0795135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9059371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5908508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.362548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7278366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2712326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2300872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.102180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3806762695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2482223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.928596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893447875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.056526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8006820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3942642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8554000854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9878540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9421920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2572784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.4855804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5769119262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6772918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1750259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4033279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1248321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6225738525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.353141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2984161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4719848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8327484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.668571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7689437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2255630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.453857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3580169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4995269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123397827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6135177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8783950805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6501083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.837272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3350219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6410369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9149932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0017929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2757568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8282165527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.53125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8829193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3761444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.458381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2666931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4266738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3308258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8376159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6002655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5179977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4357299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">73.5591278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1983795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9289474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.7964935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.152717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.2576217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.4312057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9059295654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5908508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3625564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7278213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2712249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.230094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.102180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3806762695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2482147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9286041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.056510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8006820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3942642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8554077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9878540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2206878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9421920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0380477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4855880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.576904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6772918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1750335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4033355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1248397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6225662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3531494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2984161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8418121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4719924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8327560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7689514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2255706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4538650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.358024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4995269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6501083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2391662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7414169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.837272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6410446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9149932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0018005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.275764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5312423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2436904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8829345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7368927001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3761444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4583969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2666931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1572494506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4266738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8376007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6002426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9198760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5180053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4357376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8285522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5591201782227</t>
-  </si>
-  <si>
     <t xml:space="preserve">73.8330841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">72.280632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9700698852539</t>
+    <t xml:space="preserve">72.2806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9700622558594</t>
   </si>
   <si>
     <t xml:space="preserve">75.06591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5270614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9515991210938</t>
+    <t xml:space="preserve">76.5270538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9516067504883</t>
   </si>
   <si>
     <t xml:space="preserve">75.3398895263672</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">76.1161193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0568695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.545524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6825180053711</t>
+    <t xml:space="preserve">73.0568618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5455322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6825103759766</t>
   </si>
   <si>
     <t xml:space="preserve">71.0934600830078</t>
@@ -1565,40 +1565,40 @@
     <t xml:space="preserve">72.326286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0477981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8651580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5821228027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4908142089844</t>
+    <t xml:space="preserve">71.0478057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8651504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5821304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4907989501953</t>
   </si>
   <si>
     <t xml:space="preserve">68.8560943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3217468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8013763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3949508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9383544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5775909423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8470230102539</t>
+    <t xml:space="preserve">71.3217620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8013687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3949584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.938346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5775985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">65.5228729248047</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">64.0160751342773</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4270172119141</t>
+    <t xml:space="preserve">64.4270095825195</t>
   </si>
   <si>
     <t xml:space="preserve">64.2900390625</t>
@@ -1619,22 +1619,22 @@
     <t xml:space="preserve">66.1621170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">64.944694519043</t>
+    <t xml:space="preserve">64.9446868896484</t>
   </si>
   <si>
     <t xml:space="preserve">66.2089385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6771697998047</t>
+    <t xml:space="preserve">66.6771774291992</t>
   </si>
   <si>
     <t xml:space="preserve">66.3025970458984</t>
   </si>
   <si>
-    <t xml:space="preserve">70.0016784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4866104125977</t>
+    <t xml:space="preserve">70.0016708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4866027832031</t>
   </si>
   <si>
     <t xml:space="preserve">69.2056732177734</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675704956055</t>
+    <t xml:space="preserve">69.7675552368164</t>
   </si>
   <si>
     <t xml:space="preserve">70.8913345336914</t>
@@ -1661,19 +1661,19 @@
     <t xml:space="preserve">73.0452270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1054763793945</t>
+    <t xml:space="preserve">75.2459335327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.10546875</t>
   </si>
   <si>
     <t xml:space="preserve">74.9650039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">74.5904235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0586547851562</t>
+    <t xml:space="preserve">74.5904159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0586624145508</t>
   </si>
   <si>
     <t xml:space="preserve">75.2927703857422</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5570220947266</t>
+    <t xml:space="preserve">76.557014465332</t>
   </si>
   <si>
     <t xml:space="preserve">76.1356048583984</t>
@@ -1694,46 +1694,46 @@
     <t xml:space="preserve">76.8847808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">76.9784240722656</t>
+    <t xml:space="preserve">76.9784317016602</t>
   </si>
   <si>
     <t xml:space="preserve">78.7109146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6172561645508</t>
+    <t xml:space="preserve">78.6172637939453</t>
   </si>
   <si>
     <t xml:space="preserve">79.6942138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2728042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.6005706787109</t>
+    <t xml:space="preserve">79.2727966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6005554199219</t>
   </si>
   <si>
     <t xml:space="preserve">79.2259750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4132766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7878494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0219879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.038688659668</t>
+    <t xml:space="preserve">79.4132690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7878646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.02197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0386734008789</t>
   </si>
   <si>
     <t xml:space="preserve">79.8815155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6775054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3029251098633</t>
+    <t xml:space="preserve">80.6775131225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3029174804688</t>
   </si>
   <si>
     <t xml:space="preserve">80.7711639404297</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">82.0354080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">81.707633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798751831055</t>
+    <t xml:space="preserve">81.707649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798828125</t>
   </si>
   <si>
     <t xml:space="preserve">81.3330459594727</t>
@@ -1757,31 +1757,31 @@
     <t xml:space="preserve">82.2227020263672</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1457595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497543334961</t>
+    <t xml:space="preserve">81.145751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.349739074707</t>
   </si>
   <si>
     <t xml:space="preserve">79.9751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2695236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5036392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0187149047852</t>
+    <t xml:space="preserve">82.2695159912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5036468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0187072753906</t>
   </si>
   <si>
     <t xml:space="preserve">83.2528305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6742401123047</t>
+    <t xml:space="preserve">82.9250564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6742324829102</t>
   </si>
   <si>
     <t xml:space="preserve">82.9718780517578</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">84.0019989013672</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7980194091797</t>
+    <t xml:space="preserve">84.7980117797852</t>
   </si>
   <si>
     <t xml:space="preserve">85.7813186645508</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">86.8582611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">86.155891418457</t>
+    <t xml:space="preserve">86.1559143066406</t>
   </si>
   <si>
     <t xml:space="preserve">85.8281402587891</t>
@@ -1811,70 +1811,70 @@
     <t xml:space="preserve">85.6876678466797</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2194290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1257781982422</t>
+    <t xml:space="preserve">85.2194366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1257705688477</t>
   </si>
   <si>
     <t xml:space="preserve">85.6408462524414</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0822372436523</t>
+    <t xml:space="preserve">82.0822296142578</t>
   </si>
   <si>
     <t xml:space="preserve">79.7410430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">80.256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5671615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8481216430664</t>
+    <t xml:space="preserve">80.2560958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5671691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8481063842773</t>
   </si>
   <si>
     <t xml:space="preserve">83.8147125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">84.1893081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2829437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3130722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1693267822266</t>
+    <t xml:space="preserve">84.1892929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2829513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3130798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1693344116211</t>
   </si>
   <si>
     <t xml:space="preserve">89.4804000854492</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2597045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656112670898</t>
+    <t xml:space="preserve">91.2597122192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6854858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656265258789</t>
   </si>
   <si>
     <t xml:space="preserve">92.1580963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5437088012695</t>
+    <t xml:space="preserve">91.543701171875</t>
   </si>
   <si>
     <t xml:space="preserve">90.8348083496094</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5984954833984</t>
+    <t xml:space="preserve">90.5984878540039</t>
   </si>
   <si>
     <t xml:space="preserve">89.1806793212891</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">88.8025894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">86.5340957641602</t>
+    <t xml:space="preserve">86.5340881347656</t>
   </si>
   <si>
     <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3546676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9690551757812</t>
+    <t xml:space="preserve">91.3546600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9690628051758</t>
   </si>
   <si>
     <t xml:space="preserve">93.1033096313477</t>
@@ -1904,25 +1904,25 @@
     <t xml:space="preserve">95.5608520507812</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4115447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8122177124023</t>
+    <t xml:space="preserve">96.4115371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8122100830078</t>
   </si>
   <si>
     <t xml:space="preserve">97.0731887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">97.8293762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3417053222656</t>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3416976928711</t>
   </si>
   <si>
     <t xml:space="preserve">101.326644897461</t>
   </si>
   <si>
-    <t xml:space="preserve">98.680061340332</t>
+    <t xml:space="preserve">98.6800537109375</t>
   </si>
   <si>
     <t xml:space="preserve">99.2471771240234</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">96.8841552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6403274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9389495849609</t>
+    <t xml:space="preserve">97.6403350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">96.3170318603516</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">96.5060653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2622375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9786682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5307540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3019714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.3567581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2074432373047</t>
+    <t xml:space="preserve">97.2622451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9786758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3019638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3567504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">97.167724609375</t>
@@ -1967,133 +1967,133 @@
     <t xml:space="preserve">97.5457916259766</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2225112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7499008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8444137573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4663391113281</t>
+    <t xml:space="preserve">96.2225036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7498931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4663314819336</t>
   </si>
   <si>
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082809448242</t>
+    <t xml:space="preserve">102.082817077637</t>
   </si>
   <si>
     <t xml:space="preserve">100.475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">99.1526641845703</t>
+    <t xml:space="preserve">99.1526565551758</t>
   </si>
   <si>
     <t xml:space="preserve">101.799247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">100.664993286133</t>
+    <t xml:space="preserve">100.665008544922</t>
   </si>
   <si>
     <t xml:space="preserve">100.097869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">99.908821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3964920043945</t>
+    <t xml:space="preserve">99.9088287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.396484375</t>
   </si>
   <si>
     <t xml:space="preserve">100.192390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">102.366394042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.17733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.784202575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.028022766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.003356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.137603759766</t>
+    <t xml:space="preserve">102.366371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.177322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.784194946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.028030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.003349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.13761138916</t>
   </si>
   <si>
     <t xml:space="preserve">101.704727172852</t>
   </si>
   <si>
-    <t xml:space="preserve">103.689666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.500633239746</t>
+    <t xml:space="preserve">103.689674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">102.93350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">100.381423950195</t>
+    <t xml:space="preserve">100.38143157959</t>
   </si>
   <si>
     <t xml:space="preserve">98.5855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">96.6951065063477</t>
+    <t xml:space="preserve">96.6951141357422</t>
   </si>
   <si>
     <t xml:space="preserve">98.1129379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0581436157227</t>
+    <t xml:space="preserve">99.0581359863281</t>
   </si>
   <si>
     <t xml:space="preserve">100.94856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">100.286903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7197799682617</t>
+    <t xml:space="preserve">100.286911010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7197875976562</t>
   </si>
   <si>
     <t xml:space="preserve">100.854042053223</t>
   </si>
   <si>
-    <t xml:space="preserve">99.6252670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4266128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7101593017578</t>
+    <t xml:space="preserve">99.6252593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4265975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7101745605469</t>
   </si>
   <si>
     <t xml:space="preserve">93.8594818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0957794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2848281860352</t>
+    <t xml:space="preserve">94.0957870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2848205566406</t>
   </si>
   <si>
     <t xml:space="preserve">94.6156463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5211181640625</t>
+    <t xml:space="preserve">94.521125793457</t>
   </si>
   <si>
     <t xml:space="preserve">91.6382217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3471298217773</t>
+    <t xml:space="preserve">92.3471374511719</t>
   </si>
   <si>
     <t xml:space="preserve">91.3074035644531</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">92.2998809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7327575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0163192749023</t>
+    <t xml:space="preserve">91.7327499389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0163116455078</t>
   </si>
   <si>
     <t xml:space="preserve">93.1505661010742</t>
@@ -2114,25 +2114,25 @@
     <t xml:space="preserve">95.3718185424805</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8046951293945</t>
+    <t xml:space="preserve">94.8046875</t>
   </si>
   <si>
     <t xml:space="preserve">98.8690948486328</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9238815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.75951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.122535705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.634880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.95817565918</t>
+    <t xml:space="preserve">97.9238891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.759521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.122543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.634895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.958183288574</t>
   </si>
   <si>
     <t xml:space="preserve">108.226684570312</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">109.077377319336</t>
   </si>
   <si>
-    <t xml:space="preserve">112.574653625488</t>
+    <t xml:space="preserve">112.574661254883</t>
   </si>
   <si>
     <t xml:space="preserve">113.803436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">113.236305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519866943359</t>
+    <t xml:space="preserve">113.236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519874572754</t>
   </si>
   <si>
     <t xml:space="preserve">114.654121398926</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.206192016602</t>
+    <t xml:space="preserve">115.977409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.206199645996</t>
   </si>
   <si>
     <t xml:space="preserve">117.017158508301</t>
@@ -2177,19 +2177,19 @@
     <t xml:space="preserve">115.315773010254</t>
   </si>
   <si>
-    <t xml:space="preserve">114.370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.425346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.644500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.251365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.589714050293</t>
+    <t xml:space="preserve">114.370567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.425354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.644508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.589721679688</t>
   </si>
   <si>
     <t xml:space="preserve">110.30615234375</t>
@@ -2204,82 +2204,82 @@
     <t xml:space="preserve">111.062316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">110.11710357666</t>
+    <t xml:space="preserve">110.117111206055</t>
   </si>
   <si>
     <t xml:space="preserve">109.833541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">108.510246276855</t>
+    <t xml:space="preserve">108.51025390625</t>
   </si>
   <si>
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.873275756836</t>
+    <t xml:space="preserve">112.29109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952735900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.87328338623</t>
   </si>
   <si>
     <t xml:space="preserve">109.455467224121</t>
   </si>
   <si>
-    <t xml:space="preserve">107.470512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.495193481445</t>
+    <t xml:space="preserve">107.470520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.49520111084</t>
   </si>
   <si>
     <t xml:space="preserve">108.037651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">107.848602294922</t>
+    <t xml:space="preserve">107.848609924316</t>
   </si>
   <si>
     <t xml:space="preserve">108.793807983398</t>
   </si>
   <si>
-    <t xml:space="preserve">106.430786132812</t>
+    <t xml:space="preserve">106.430793762207</t>
   </si>
   <si>
     <t xml:space="preserve">109.171897888184</t>
   </si>
   <si>
-    <t xml:space="preserve">109.266418457031</t>
+    <t xml:space="preserve">109.266410827637</t>
   </si>
   <si>
     <t xml:space="preserve">106.997909545898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.918441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.76912689209</t>
+    <t xml:space="preserve">104.918449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.769134521484</t>
   </si>
   <si>
     <t xml:space="preserve">107.754089355469</t>
   </si>
   <si>
-    <t xml:space="preserve">108.415733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.32120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.211631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.27604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.46508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.928070068359</t>
+    <t xml:space="preserve">108.415725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.321197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.276039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.465087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.928062438965</t>
   </si>
   <si>
     <t xml:space="preserve">104.540367126465</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">106.808868408203</t>
   </si>
   <si>
-    <t xml:space="preserve">103.595146179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.893775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8143005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.132164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.485565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.400665283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.888336181641</t>
+    <t xml:space="preserve">103.595153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.893760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8143157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.132171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.485572814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.400680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.888328552246</t>
   </si>
   <si>
     <t xml:space="preserve">106.52530670166</t>
@@ -2321,31 +2321,31 @@
     <t xml:space="preserve">102.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">114.08699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.629447937012</t>
+    <t xml:space="preserve">114.086990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.629440307617</t>
   </si>
   <si>
     <t xml:space="preserve">118.056884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">122.310333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.091171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.32958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.583038330078</t>
+    <t xml:space="preserve">122.310325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.091163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.329574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.5830078125</t>
   </si>
   <si>
     <t xml:space="preserve">145.089935302734</t>
@@ -2354,73 +2354,73 @@
     <t xml:space="preserve">144.239242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">155.959869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.383117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.755752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.94482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.313247680664</t>
+    <t xml:space="preserve">155.959854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.383102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.691345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.755737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.944793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.313278198242</t>
   </si>
   <si>
     <t xml:space="preserve">146.791320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">146.885833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.507736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.522811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.318710327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.641983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.596832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.706390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.048950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.302398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.107925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.675048828125</t>
+    <t xml:space="preserve">146.885818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.507720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.52278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.318695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.641998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.596817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.706405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.048934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.10791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.675033569336</t>
   </si>
   <si>
     <t xml:space="preserve">169.381866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">178.833969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.440826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.688827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.927230834961</t>
+    <t xml:space="preserve">178.833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.440841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.688842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.927215576172</t>
   </si>
   <si>
     <t xml:space="preserve">186.206619262695</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">163.521545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.172332763672</t>
+    <t xml:space="preserve">171.839385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.172317504883</t>
   </si>
   <si>
     <t xml:space="preserve">171.55583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">169.098297119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.994155883789</t>
+    <t xml:space="preserve">169.098281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.994140625</t>
   </si>
   <si>
     <t xml:space="preserve">164.655792236328</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">150.855728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">152.651596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.014633178711</t>
+    <t xml:space="preserve">152.651626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.0146484375</t>
   </si>
   <si>
     <t xml:space="preserve">158.6064453125</t>
@@ -2465,25 +2465,25 @@
     <t xml:space="preserve">157.850280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">161.510147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.365707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.890396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.129928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.133590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.270645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.11882019043</t>
+    <t xml:space="preserve">161.510162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.36572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.890411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.129898071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.133605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.270660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.118835449219</t>
   </si>
   <si>
     <t xml:space="preserve">164.457061767578</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">162.936080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">161.320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.985458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.55583190918</t>
+    <t xml:space="preserve">161.320053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.985473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.555816650391</t>
   </si>
   <si>
     <t xml:space="preserve">162.841018676758</t>
@@ -2510,28 +2510,28 @@
     <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.685485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.35090637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.031143188477</t>
+    <t xml:space="preserve">169.685470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.350921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.031127929688</t>
   </si>
   <si>
     <t xml:space="preserve">164.361999511719</t>
   </si>
   <si>
-    <t xml:space="preserve">165.122482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.305252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.400283813477</t>
+    <t xml:space="preserve">165.122497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.400299072266</t>
   </si>
   <si>
     <t xml:space="preserve">171.96696472168</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">169.495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.358306884766</t>
+    <t xml:space="preserve">166.358291625977</t>
   </si>
   <si>
     <t xml:space="preserve">160.939788818359</t>
   </si>
   <si>
-    <t xml:space="preserve">154.665679931641</t>
+    <t xml:space="preserve">154.66569519043</t>
   </si>
   <si>
     <t xml:space="preserve">162.175598144531</t>
@@ -2561,43 +2561,43 @@
     <t xml:space="preserve">157.802749633789</t>
   </si>
   <si>
-    <t xml:space="preserve">152.669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.81755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.775543212891</t>
+    <t xml:space="preserve">152.669403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.817565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.77555847168</t>
   </si>
   <si>
     <t xml:space="preserve">150.768173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">145.25456237793</t>
+    <t xml:space="preserve">145.254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">149.72248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">152.289154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.623718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.391616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.760772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.24348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.190383911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.855819702148</t>
+    <t xml:space="preserve">152.289169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.623733520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.7607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.243469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.190399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.855834960938</t>
   </si>
   <si>
     <t xml:space="preserve">154.950881958008</t>
@@ -2606,40 +2606,40 @@
     <t xml:space="preserve">155.426193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">155.806427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.418792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.634796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.600250244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.018783569336</t>
+    <t xml:space="preserve">155.806457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.418807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.634826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.600234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.018768310547</t>
   </si>
   <si>
     <t xml:space="preserve">144.589157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">143.543472290039</t>
+    <t xml:space="preserve">143.54345703125</t>
   </si>
   <si>
     <t xml:space="preserve">135.55827331543</t>
   </si>
   <si>
-    <t xml:space="preserve">134.797775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.364440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.17431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.779266357422</t>
+    <t xml:space="preserve">134.797760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.36442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.779251098633</t>
   </si>
   <si>
     <t xml:space="preserve">143.258270263672</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">147.060745239258</t>
   </si>
   <si>
-    <t xml:space="preserve">147.726165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.247177124023</t>
+    <t xml:space="preserve">147.726181030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.247161865234</t>
   </si>
   <si>
     <t xml:space="preserve">152.95458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">150.387908935547</t>
+    <t xml:space="preserve">150.387924194336</t>
   </si>
   <si>
     <t xml:space="preserve">161.03483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">160.65461730957</t>
+    <t xml:space="preserve">160.654602050781</t>
   </si>
   <si>
     <t xml:space="preserve">162.080535888672</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913879394531</t>
+    <t xml:space="preserve">168.069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.91389465332</t>
   </si>
   <si>
     <t xml:space="preserve">175.294128417969</t>
@@ -2687,43 +2687,43 @@
     <t xml:space="preserve">177.670669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">173.48796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.716354370117</t>
+    <t xml:space="preserve">173.487945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.716339111328</t>
   </si>
   <si>
     <t xml:space="preserve">180.712677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">178.241058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.853424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.666976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.039825439453</t>
+    <t xml:space="preserve">178.24104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.853393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.039840698242</t>
   </si>
   <si>
     <t xml:space="preserve">181.663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">185.275619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.089202880859</t>
+    <t xml:space="preserve">185.275634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.089218139648</t>
   </si>
   <si>
     <t xml:space="preserve">181.568222045898</t>
   </si>
   <si>
-    <t xml:space="preserve">179.286743164062</t>
+    <t xml:space="preserve">179.286727905273</t>
   </si>
   <si>
     <t xml:space="preserve">178.050933837891</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">179.191665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">176.52995300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.860824584961</t>
+    <t xml:space="preserve">176.529922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.860809326172</t>
   </si>
   <si>
     <t xml:space="preserve">184.610198974609</t>
@@ -2750,52 +2750,52 @@
     <t xml:space="preserve">159.703979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">163.886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.217575073242</t>
+    <t xml:space="preserve">163.88671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.21760559082</t>
   </si>
   <si>
     <t xml:space="preserve">164.932373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">164.07682800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.947204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.8447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.266952514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.879333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.696563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.605224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.084213256836</t>
+    <t xml:space="preserve">164.076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.947189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.844711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.266967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.879318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.696578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.605209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.084228515625</t>
   </si>
   <si>
     <t xml:space="preserve">162.745956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">160.179306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.323745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.468185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.848449707031</t>
+    <t xml:space="preserve">160.179290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.32373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.468170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.848434448242</t>
   </si>
   <si>
     <t xml:space="preserve">163.221267700195</t>
@@ -2804,25 +2804,25 @@
     <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">159.608901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.700286865234</t>
+    <t xml:space="preserve">159.608917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.700302124023</t>
   </si>
   <si>
     <t xml:space="preserve">161.224975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">153.810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.859527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.52864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.616302490234</t>
+    <t xml:space="preserve">153.810134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.859497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.528656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.616333007812</t>
   </si>
   <si>
     <t xml:space="preserve">154.475570678711</t>
@@ -2831,37 +2831,37 @@
     <t xml:space="preserve">154.570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">157.992874145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.826217651367</t>
+    <t xml:space="preserve">157.992858886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.826202392578</t>
   </si>
   <si>
     <t xml:space="preserve">169.970672607422</t>
   </si>
   <si>
-    <t xml:space="preserve">179.001541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.92497253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.681793212891</t>
+    <t xml:space="preserve">179.001556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.924957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.68180847168</t>
   </si>
   <si>
     <t xml:space="preserve">171.111419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">170.541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.784240722656</t>
+    <t xml:space="preserve">170.541030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.784255981445</t>
   </si>
   <si>
     <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255859375</t>
+    <t xml:space="preserve">170.255844116211</t>
   </si>
   <si>
     <t xml:space="preserve">173.868194580078</t>
@@ -2870,40 +2870,40 @@
     <t xml:space="preserve">173.202758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">175.389190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.434906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.149703979492</t>
+    <t xml:space="preserve">175.389175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.434875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.149688720703</t>
   </si>
   <si>
     <t xml:space="preserve">177.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">174.438583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.186706542969</t>
+    <t xml:space="preserve">174.438568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.18669128418</t>
   </si>
   <si>
     <t xml:space="preserve">151.813842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">155.99658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.380523681641</t>
+    <t xml:space="preserve">155.996566772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.380508422852</t>
   </si>
   <si>
     <t xml:space="preserve">155.901504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">157.137329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.000274658203</t>
+    <t xml:space="preserve">157.137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.000259399414</t>
   </si>
   <si>
     <t xml:space="preserve">150.197784423828</t>
@@ -2912,43 +2912,43 @@
     <t xml:space="preserve">149.057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">147.155822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.706420898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.082962036133</t>
+    <t xml:space="preserve">147.155807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.706405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.082977294922</t>
   </si>
   <si>
     <t xml:space="preserve">138.695297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">134.987899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.033569335938</t>
+    <t xml:space="preserve">134.987884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.033584594727</t>
   </si>
   <si>
     <t xml:space="preserve">133.276763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">134.03727722168</t>
+    <t xml:space="preserve">134.037261962891</t>
   </si>
   <si>
     <t xml:space="preserve">133.086654663086</t>
   </si>
   <si>
-    <t xml:space="preserve">135.273086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.136016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.519989013672</t>
+    <t xml:space="preserve">135.273071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.136032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.519973754883</t>
   </si>
   <si>
     <t xml:space="preserve">130.90022277832</t>
@@ -2960,34 +2960,34 @@
     <t xml:space="preserve">132.848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">135.46321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.229232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.492233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.591003417969</t>
+    <t xml:space="preserve">135.463195800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.229248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.492218017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.59098815918</t>
   </si>
   <si>
     <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">148.201477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.05891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.300231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.016937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874313354492</t>
+    <t xml:space="preserve">148.20149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.058883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.300247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.01692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874328613281</t>
   </si>
   <si>
     <t xml:space="preserve">136.984191894531</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">134.227386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">131.660705566406</t>
+    <t xml:space="preserve">131.660720825195</t>
   </si>
   <si>
     <t xml:space="preserve">133.847152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">135.60578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.423065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.333541870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.470596313477</t>
+    <t xml:space="preserve">135.605804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.423080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.333557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.470581054688</t>
   </si>
   <si>
     <t xml:space="preserve">131.185409545898</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">136.889129638672</t>
   </si>
   <si>
-    <t xml:space="preserve">137.031692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.983856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.744552612305</t>
+    <t xml:space="preserve">137.031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.983871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.744537353516</t>
   </si>
   <si>
     <t xml:space="preserve">137.845397949219</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">137.797515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">138.084716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.467590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.978744506836</t>
+    <t xml:space="preserve">138.084701538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.46760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.978729248047</t>
   </si>
   <si>
     <t xml:space="preserve">133.05908203125</t>
@@ -3071,19 +3071,19 @@
     <t xml:space="preserve">136.218048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">137.510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.659072875977</t>
+    <t xml:space="preserve">137.510345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.659057617188</t>
   </si>
   <si>
     <t xml:space="preserve">139.185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">143.206069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.306884765625</t>
+    <t xml:space="preserve">143.2060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.306900024414</t>
   </si>
   <si>
     <t xml:space="preserve">144.019714355469</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">146.843627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">147.226547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.397506713867</t>
+    <t xml:space="preserve">147.226531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.397491455078</t>
   </si>
   <si>
     <t xml:space="preserve">147.992340087891</t>
@@ -3113,46 +3113,46 @@
     <t xml:space="preserve">149.428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">150.289749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.065795898438</t>
+    <t xml:space="preserve">150.289764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.065811157227</t>
   </si>
   <si>
     <t xml:space="preserve">152.682922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">150.76838684082</t>
+    <t xml:space="preserve">150.768402099609</t>
   </si>
   <si>
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.879486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.320510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.395721435547</t>
+    <t xml:space="preserve">149.906875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.879470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.320495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.395736694336</t>
   </si>
   <si>
     <t xml:space="preserve">153.783752441406</t>
   </si>
   <si>
-    <t xml:space="preserve">155.123931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.458953857422</t>
+    <t xml:space="preserve">155.123916625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.458969116211</t>
   </si>
   <si>
     <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">155.650421142578</t>
+    <t xml:space="preserve">155.650436401367</t>
   </si>
   <si>
     <t xml:space="preserve">156.081192016602</t>
@@ -3161,25 +3161,25 @@
     <t xml:space="preserve">158.905090332031</t>
   </si>
   <si>
-    <t xml:space="preserve">160.149551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.207656860352</t>
+    <t xml:space="preserve">160.149536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.207641601562</t>
   </si>
   <si>
     <t xml:space="preserve">163.643539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">164.98371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.72900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.91535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.35124206543</t>
+    <t xml:space="preserve">164.983688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.729019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.915344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.351226806641</t>
   </si>
   <si>
     <t xml:space="preserve">165.07942199707</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">163.834976196289</t>
   </si>
   <si>
-    <t xml:space="preserve">168.908447265625</t>
+    <t xml:space="preserve">168.908462524414</t>
   </si>
   <si>
     <t xml:space="preserve">164.600799560547</t>
@@ -3197,10 +3197,10 @@
     <t xml:space="preserve">168.142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">168.860580444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.036666870117</t>
+    <t xml:space="preserve">168.860595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.036682128906</t>
   </si>
   <si>
     <t xml:space="preserve">168.669143676758</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">171.158020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">170.248626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.349487304688</t>
+    <t xml:space="preserve">170.248641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.349472045898</t>
   </si>
   <si>
     <t xml:space="preserve">176.0400390625</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">179.534057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">178.05029296875</t>
+    <t xml:space="preserve">178.050308227539</t>
   </si>
   <si>
     <t xml:space="preserve">177.475921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">177.810989379883</t>
+    <t xml:space="preserve">177.810974121094</t>
   </si>
   <si>
     <t xml:space="preserve">181.352844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">182.740859985352</t>
+    <t xml:space="preserve">182.740875244141</t>
   </si>
   <si>
     <t xml:space="preserve">184.990432739258</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">192.409194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">193.270706176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.568145751953</t>
+    <t xml:space="preserve">193.270721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.568161010742</t>
   </si>
   <si>
     <t xml:space="preserve">191.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">196.908309936523</t>
+    <t xml:space="preserve">196.908325195312</t>
   </si>
   <si>
     <t xml:space="preserve">196.812606811523</t>
   </si>
   <si>
-    <t xml:space="preserve">197.386947631836</t>
+    <t xml:space="preserve">197.386932373047</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
@@ -3296,22 +3296,22 @@
     <t xml:space="preserve">195.855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">194.515167236328</t>
+    <t xml:space="preserve">194.515151977539</t>
   </si>
   <si>
     <t xml:space="preserve">187.479309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">180.539184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.987075805664</t>
+    <t xml:space="preserve">180.539169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.987060546875</t>
   </si>
   <si>
     <t xml:space="preserve">174.077682495117</t>
   </si>
   <si>
-    <t xml:space="preserve">173.599060058594</t>
+    <t xml:space="preserve">173.599044799805</t>
   </si>
   <si>
     <t xml:space="preserve">167.664016723633</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">165.462341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">162.781997680664</t>
+    <t xml:space="preserve">162.782012939453</t>
   </si>
   <si>
     <t xml:space="preserve">163.404220581055</t>
@@ -3335,34 +3335,34 @@
     <t xml:space="preserve">162.111923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">166.51530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.870864868164</t>
+    <t xml:space="preserve">166.515319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.870849609375</t>
   </si>
   <si>
     <t xml:space="preserve">171.25373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">172.402481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.742630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.715240478516</t>
+    <t xml:space="preserve">172.402465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.742614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.715255737305</t>
   </si>
   <si>
     <t xml:space="preserve">181.448577880859</t>
   </si>
   <si>
-    <t xml:space="preserve">180.826324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.884460449219</t>
+    <t xml:space="preserve">180.826354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.88444519043</t>
   </si>
   <si>
     <t xml:space="preserve">182.83659362793</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096389770508</t>
+    <t xml:space="preserve">187.096420288086</t>
   </si>
   <si>
     <t xml:space="preserve">187.000686645508</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.699890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.231521606445</t>
+    <t xml:space="preserve">174.69987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.231506347656</t>
   </si>
   <si>
     <t xml:space="preserve">175.561401367188</t>
@@ -3404,28 +3404,28 @@
     <t xml:space="preserve">179.964828491211</t>
   </si>
   <si>
-    <t xml:space="preserve">180.874221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.506652832031</t>
+    <t xml:space="preserve">180.874206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.50666809082</t>
   </si>
   <si>
     <t xml:space="preserve">175.896469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">176.614410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.800704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.636657714844</t>
+    <t xml:space="preserve">176.614395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.800735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.636672973633</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">179.294723510742</t>
+    <t xml:space="preserve">179.294738769531</t>
   </si>
   <si>
     <t xml:space="preserve">177.188766479492</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">180.682754516602</t>
   </si>
   <si>
-    <t xml:space="preserve">175.082794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.296478271484</t>
+    <t xml:space="preserve">175.082778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.296493530273</t>
   </si>
   <si>
     <t xml:space="preserve">169.14778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">164.935852050781</t>
+    <t xml:space="preserve">164.935836791992</t>
   </si>
   <si>
     <t xml:space="preserve">167.472564697266</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">170.392227172852</t>
   </si>
   <si>
-    <t xml:space="preserve">172.306732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.928939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.764892578125</t>
+    <t xml:space="preserve">172.306747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.928970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.764877319336</t>
   </si>
   <si>
     <t xml:space="preserve">172.785369873047</t>
@@ -3467,16 +3467,16 @@
     <t xml:space="preserve">170.535797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">152.06071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.688049316406</t>
+    <t xml:space="preserve">152.060699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.688034057617</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">154.932495117188</t>
+    <t xml:space="preserve">154.932479858398</t>
   </si>
   <si>
     <t xml:space="preserve">154.741012573242</t>
@@ -3485,25 +3485,25 @@
     <t xml:space="preserve">159.240158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">157.947830200195</t>
+    <t xml:space="preserve">157.947845458984</t>
   </si>
   <si>
     <t xml:space="preserve">160.293121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">156.224761962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.156402587891</t>
+    <t xml:space="preserve">156.22477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.15641784668</t>
   </si>
   <si>
     <t xml:space="preserve">153.640182495117</t>
   </si>
   <si>
-    <t xml:space="preserve">148.183792114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.770172119141</t>
+    <t xml:space="preserve">148.183807373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.770156860352</t>
   </si>
   <si>
     <t xml:space="preserve">143.780395507812</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">141.387252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">139.85563659668</t>
+    <t xml:space="preserve">139.855651855469</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">137.223175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.946212768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.717163085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.884773254395</t>
+    <t xml:space="preserve">138.946228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.717178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.94287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.884765625</t>
   </si>
   <si>
     <t xml:space="preserve">128.990753173828</t>
@@ -3545,37 +3545,37 @@
     <t xml:space="preserve">131.048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">131.144577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.006088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518997192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.41813659668</t>
+    <t xml:space="preserve">131.144561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.006103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.418144226074</t>
   </si>
   <si>
     <t xml:space="preserve">122.289916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">120.662574768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.934379577637</t>
+    <t xml:space="preserve">120.662582397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.934387207031</t>
   </si>
   <si>
     <t xml:space="preserve">114.631843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">117.072860717773</t>
+    <t xml:space="preserve">117.072853088379</t>
   </si>
   <si>
     <t xml:space="preserve">116.546363830566</t>
@@ -3584,10 +3584,10 @@
     <t xml:space="preserve">115.58910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">112.286567687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.430137634277</t>
+    <t xml:space="preserve">112.286560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.430145263672</t>
   </si>
   <si>
     <t xml:space="preserve">116.211326599121</t>
@@ -3596,22 +3596,22 @@
     <t xml:space="preserve">120.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.103591918945</t>
+    <t xml:space="preserve">123.10359954834</t>
   </si>
   <si>
     <t xml:space="preserve">122.864273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">127.937728881836</t>
+    <t xml:space="preserve">127.93775177002</t>
   </si>
   <si>
     <t xml:space="preserve">127.124084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">123.773681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.151443481445</t>
+    <t xml:space="preserve">123.773666381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
     <t xml:space="preserve">120.08821105957</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">122.242050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">117.503631591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.806159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541236877441</t>
+    <t xml:space="preserve">117.503623962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.806167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541229248047</t>
   </si>
   <si>
     <t xml:space="preserve">117.599349975586</t>
@@ -3635,76 +3635,76 @@
     <t xml:space="preserve">121.859161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">131.718948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.29328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.693321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.597579956055</t>
+    <t xml:space="preserve">131.71891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.293273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.693305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.59757232666</t>
   </si>
   <si>
     <t xml:space="preserve">125.257438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">124.204437255859</t>
+    <t xml:space="preserve">124.204444885254</t>
   </si>
   <si>
     <t xml:space="preserve">125.448883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.824905395508</t>
+    <t xml:space="preserve">133.824890136719</t>
   </si>
   <si>
     <t xml:space="preserve">135.73942565918</t>
   </si>
   <si>
-    <t xml:space="preserve">135.83512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.329132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.616333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.041976928711</t>
+    <t xml:space="preserve">135.835159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.329147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.105194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.041946411133</t>
   </si>
   <si>
     <t xml:space="preserve">136.170181274414</t>
   </si>
   <si>
-    <t xml:space="preserve">135.260787963867</t>
+    <t xml:space="preserve">135.260803222656</t>
   </si>
   <si>
     <t xml:space="preserve">132.628341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">129.038619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.559982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.45401763916</t>
+    <t xml:space="preserve">129.038604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.086486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.559967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.416381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.454010009766</t>
   </si>
   <si>
     <t xml:space="preserve">124.539489746094</t>
   </si>
   <si>
-    <t xml:space="preserve">120.997627258301</t>
+    <t xml:space="preserve">120.997611999512</t>
   </si>
   <si>
     <t xml:space="preserve">118.7001953125</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">118.173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">117.64720916748</t>
+    <t xml:space="preserve">117.647216796875</t>
   </si>
   <si>
     <t xml:space="preserve">114.392524719238</t>
@@ -3731,16 +3731,16 @@
     <t xml:space="preserve">114.823295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">115.493385314941</t>
+    <t xml:space="preserve">115.493370056152</t>
   </si>
   <si>
     <t xml:space="preserve">109.271186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">106.590866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.654098510742</t>
+    <t xml:space="preserve">106.590858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.654090881348</t>
   </si>
   <si>
     <t xml:space="preserve">107.165214538574</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">114.009620666504</t>
   </si>
   <si>
-    <t xml:space="preserve">114.871154785156</t>
+    <t xml:space="preserve">114.871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">113.435272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">110.563484191895</t>
+    <t xml:space="preserve">110.563491821289</t>
   </si>
   <si>
     <t xml:space="preserve">113.052360534668</t>
@@ -3767,25 +3767,25 @@
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.932800292969</t>
+    <t xml:space="preserve">111.884498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.932792663574</t>
   </si>
   <si>
     <t xml:space="preserve">113.381454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">117.292808532715</t>
+    <t xml:space="preserve">117.292816162109</t>
   </si>
   <si>
     <t xml:space="preserve">118.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">118.30687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.761650085449</t>
+    <t xml:space="preserve">118.306884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.761642456055</t>
   </si>
   <si>
     <t xml:space="preserve">119.803825378418</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">117.727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">118.74146270752</t>
+    <t xml:space="preserve">118.741470336914</t>
   </si>
   <si>
     <t xml:space="preserve">115.071548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">111.787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.918731689453</t>
+    <t xml:space="preserve">111.787933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.918724060059</t>
   </si>
   <si>
     <t xml:space="preserve">107.683403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">112.657127380371</t>
+    <t xml:space="preserve">112.657119750977</t>
   </si>
   <si>
     <t xml:space="preserve">109.904678344727</t>
@@ -3824,49 +3824,49 @@
     <t xml:space="preserve">114.685241699219</t>
   </si>
   <si>
-    <t xml:space="preserve">112.801986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.912612915039</t>
+    <t xml:space="preserve">112.80199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.912620544434</t>
   </si>
   <si>
     <t xml:space="preserve">113.526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">120.190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.377174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.797714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.866172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.914451599121</t>
+    <t xml:space="preserve">120.190132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.377166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.797706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.866180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.914459228516</t>
   </si>
   <si>
     <t xml:space="preserve">122.025093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">126.564224243164</t>
+    <t xml:space="preserve">126.56421661377</t>
   </si>
   <si>
     <t xml:space="preserve">127.578285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">129.799530029297</t>
+    <t xml:space="preserve">129.799545288086</t>
   </si>
   <si>
     <t xml:space="preserve">130.668746948242</t>
   </si>
   <si>
-    <t xml:space="preserve">131.151641845703</t>
+    <t xml:space="preserve">131.151626586914</t>
   </si>
   <si>
     <t xml:space="preserve">131.537933349609</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">124.970687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">127.916290283203</t>
+    <t xml:space="preserve">127.916297912598</t>
   </si>
   <si>
     <t xml:space="preserve">127.674842834473</t>
@@ -3905,22 +3905,22 @@
     <t xml:space="preserve">128.785507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">125.936454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.234161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.958480834961</t>
+    <t xml:space="preserve">125.936462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.234146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.958465576172</t>
   </si>
   <si>
     <t xml:space="preserve">130.861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">128.640609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.137573242188</t>
+    <t xml:space="preserve">128.640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.137557983398</t>
   </si>
   <si>
     <t xml:space="preserve">135.787338256836</t>
@@ -3935,10 +3935,10 @@
     <t xml:space="preserve">131.924240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">135.111267089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890029907227</t>
+    <t xml:space="preserve">135.111282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890014648438</t>
   </si>
   <si>
     <t xml:space="preserve">131.779373168945</t>
@@ -3947,25 +3947,25 @@
     <t xml:space="preserve">130.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">132.020812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.489624023438</t>
+    <t xml:space="preserve">132.02082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.489639282227</t>
   </si>
   <si>
     <t xml:space="preserve">132.310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">126.515922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.86799621582</t>
+    <t xml:space="preserve">126.515914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.868011474609</t>
   </si>
   <si>
     <t xml:space="preserve">126.467628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">125.888191223145</t>
+    <t xml:space="preserve">125.888168334961</t>
   </si>
   <si>
     <t xml:space="preserve">129.171783447266</t>
@@ -3974,13 +3974,13 @@
     <t xml:space="preserve">128.061172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">128.930358886719</t>
+    <t xml:space="preserve">128.93034362793</t>
   </si>
   <si>
     <t xml:space="preserve">126.226188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">129.123489379883</t>
+    <t xml:space="preserve">129.123504638672</t>
   </si>
   <si>
     <t xml:space="preserve">129.992706298828</t>
@@ -3989,16 +3989,16 @@
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.115562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473747253418</t>
+    <t xml:space="preserve">125.11555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473754882812</t>
   </si>
   <si>
     <t xml:space="preserve">121.397338867188</t>
   </si>
   <si>
-    <t xml:space="preserve">120.721305847168</t>
+    <t xml:space="preserve">120.721298217773</t>
   </si>
   <si>
     <t xml:space="preserve">123.135734558105</t>
@@ -4007,19 +4007,19 @@
     <t xml:space="preserve">111.449913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">112.463958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.643058776855</t>
+    <t xml:space="preserve">112.463966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.643051147461</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.870452880859</t>
+    <t xml:space="preserve">107.779983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.870445251465</t>
   </si>
   <si>
     <t xml:space="preserve">110.097831726074</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">111.305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">108.504302978516</t>
+    <t xml:space="preserve">108.50431060791</t>
   </si>
   <si>
     <t xml:space="preserve">109.132064819336</t>
@@ -4049,28 +4049,28 @@
     <t xml:space="preserve">124.58438873291</t>
   </si>
   <si>
-    <t xml:space="preserve">125.646743774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.586227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.344772338867</t>
+    <t xml:space="preserve">125.64673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.586212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.344787597656</t>
   </si>
   <si>
     <t xml:space="preserve">121.300765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">124.680961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.771430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.660781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.922409057617</t>
+    <t xml:space="preserve">124.680969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.771423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.660789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.922416687012</t>
   </si>
   <si>
     <t xml:space="preserve">122.314826965332</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">125.018974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">128.592315673828</t>
+    <t xml:space="preserve">128.592330932617</t>
   </si>
   <si>
     <t xml:space="preserve">132.069107055664</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.76530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.302627563477</t>
+    <t xml:space="preserve">130.765319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.302612304688</t>
   </si>
   <si>
     <t xml:space="preserve">126.612518310547</t>
@@ -4103,34 +4103,34 @@
     <t xml:space="preserve">128.206024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">127.04711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.487800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.240249633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.316650390625</t>
+    <t xml:space="preserve">127.047096252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.487808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.240257263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.316665649414</t>
   </si>
   <si>
     <t xml:space="preserve">128.157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">125.26042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.509826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.682815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.84782409668</t>
+    <t xml:space="preserve">125.260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.682800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.847839355469</t>
   </si>
   <si>
     <t xml:space="preserve">125.067268371582</t>
@@ -4139,10 +4139,10 @@
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.783653259277</t>
+    <t xml:space="preserve">123.42546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.783645629883</t>
   </si>
   <si>
     <t xml:space="preserve">123.522041320801</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">123.039154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">122.652839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.62654876709</t>
+    <t xml:space="preserve">122.652847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.626556396484</t>
   </si>
   <si>
     <t xml:space="preserve">124.874122619629</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">125.405296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">122.845993041992</t>
+    <t xml:space="preserve">122.846000671387</t>
   </si>
   <si>
     <t xml:space="preserve">122.169960021973</t>
@@ -4172,13 +4172,13 @@
     <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">121.880218505859</t>
+    <t xml:space="preserve">121.880226135254</t>
   </si>
   <si>
     <t xml:space="preserve">122.218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">120.14183807373</t>
+    <t xml:space="preserve">120.141845703125</t>
   </si>
   <si>
     <t xml:space="preserve">125.550155639648</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">115.168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.188285827637</t>
+    <t xml:space="preserve">113.188293457031</t>
   </si>
   <si>
     <t xml:space="preserve">115.651008605957</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">117.775695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">116.906517028809</t>
+    <t xml:space="preserve">116.906509399414</t>
   </si>
   <si>
     <t xml:space="preserve">114.250648498535</t>
@@ -4229,22 +4229,22 @@
     <t xml:space="preserve">113.23657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">112.319107055664</t>
+    <t xml:space="preserve">112.31909942627</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.077659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.421798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.063598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.242691040039</t>
+    <t xml:space="preserve">112.077667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.42179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.063606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.242698669434</t>
   </si>
   <si>
     <t xml:space="preserve">107.20051574707</t>
@@ -4256,22 +4256,22 @@
     <t xml:space="preserve">108.649169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">108.842315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.11799621582</t>
+    <t xml:space="preserve">108.842330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.118003845215</t>
   </si>
   <si>
     <t xml:space="preserve">107.73169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">105.993309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.303199768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.013465881348</t>
+    <t xml:space="preserve">105.993301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.303207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.013473510742</t>
   </si>
   <si>
     <t xml:space="preserve">101.937072753906</t>
@@ -4286,13 +4286,13 @@
     <t xml:space="preserve">97.7359619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9431762695312</t>
+    <t xml:space="preserve">98.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">97.5911026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1283798217773</t>
+    <t xml:space="preserve">95.1283874511719</t>
   </si>
   <si>
     <t xml:space="preserve">98.5568771362305</t>
@@ -4313,31 +4313,31 @@
     <t xml:space="preserve">93.737678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6797332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2100524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7851104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7078475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9887771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5251998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9694671630859</t>
+    <t xml:space="preserve">93.6797256469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2100601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7851028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7078552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9887847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5252075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9694595336914</t>
   </si>
   <si>
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342590332031</t>
+    <t xml:space="preserve">93.8342514038086</t>
   </si>
   <si>
     <t xml:space="preserve">95.5340118408203</t>
@@ -4346,34 +4346,34 @@
     <t xml:space="preserve">95.9589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1819305419922</t>
+    <t xml:space="preserve">94.1819229125977</t>
   </si>
   <si>
     <t xml:space="preserve">93.1582183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1090698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3750839233398</t>
+    <t xml:space="preserve">95.1090774536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3750915527344</t>
   </si>
   <si>
     <t xml:space="preserve">94.6068725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3645782470703</t>
+    <t xml:space="preserve">96.3645706176758</t>
   </si>
   <si>
     <t xml:space="preserve">100.874717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">98.7017288208008</t>
+    <t xml:space="preserve">98.7017364501953</t>
   </si>
   <si>
     <t xml:space="preserve">101.164451599121</t>
   </si>
   <si>
-    <t xml:space="preserve">101.9853515625</t>
+    <t xml:space="preserve">101.985359191895</t>
   </si>
   <si>
     <t xml:space="preserve">101.45418548584</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">98.0739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1222763061523</t>
+    <t xml:space="preserve">98.1222686767578</t>
   </si>
   <si>
     <t xml:space="preserve">98.8948974609375</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">100.408088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2853851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299743652344</t>
+    <t xml:space="preserve">99.2853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299819946289</t>
   </si>
   <si>
     <t xml:space="preserve">96.8642730712891</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">95.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6384048461914</t>
+    <t xml:space="preserve">94.6384124755859</t>
   </si>
   <si>
     <t xml:space="preserve">94.4236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0679626464844</t>
+    <t xml:space="preserve">95.0679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">95.1265411376953</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">95.4389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3579483032227</t>
+    <t xml:space="preserve">98.3579559326172</t>
   </si>
   <si>
     <t xml:space="preserve">96.6104431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4779891967773</t>
+    <t xml:space="preserve">95.4779968261719</t>
   </si>
   <si>
     <t xml:space="preserve">94.7946090698242</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">90.8700561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4405059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.084831237793</t>
+    <t xml:space="preserve">90.4404983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0848388671875</t>
   </si>
   <si>
     <t xml:space="preserve">91.5534362792969</t>
@@ -4499,13 +4499,13 @@
     <t xml:space="preserve">90.1280975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7054138183594</t>
+    <t xml:space="preserve">92.7054214477539</t>
   </si>
   <si>
     <t xml:space="preserve">92.1196670532227</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5729675292969</t>
+    <t xml:space="preserve">91.5729598999023</t>
   </si>
   <si>
     <t xml:space="preserve">90.0109405517578</t>
@@ -4526,19 +4526,19 @@
     <t xml:space="preserve">91.7877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2716445922852</t>
+    <t xml:space="preserve">93.2716522216797</t>
   </si>
   <si>
     <t xml:space="preserve">93.6816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3091354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6270904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3413162231445</t>
+    <t xml:space="preserve">98.3091278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.627082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413238525391</t>
   </si>
   <si>
     <t xml:space="preserve">92.9397201538086</t>
@@ -4550,13 +4550,13 @@
     <t xml:space="preserve">91.7682113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5492172241211</t>
+    <t xml:space="preserve">92.5492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">92.6273193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">89.11279296875</t>
+    <t xml:space="preserve">89.1127853393555</t>
   </si>
   <si>
     <t xml:space="preserve">88.1365280151367</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">87.1016998291016</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6679382324219</t>
+    <t xml:space="preserve">87.6679306030273</t>
   </si>
   <si>
     <t xml:space="preserve">87.3164825439453</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">90.9676818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8114700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906387329102</t>
+    <t xml:space="preserve">90.8114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906463623047</t>
   </si>
   <si>
     <t xml:space="preserve">92.8225708007812</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">94.4626846313477</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0721740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444686889648</t>
+    <t xml:space="preserve">94.0721817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444763183594</t>
   </si>
   <si>
     <t xml:space="preserve">91.1238784790039</t>
@@ -4610,13 +4610,13 @@
     <t xml:space="preserve">90.6357498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5032958984375</t>
+    <t xml:space="preserve">89.503288269043</t>
   </si>
   <si>
     <t xml:space="preserve">90.303825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9328536987305</t>
+    <t xml:space="preserve">89.9328460693359</t>
   </si>
   <si>
     <t xml:space="preserve">88.8003921508789</t>
@@ -4628,22 +4628,22 @@
     <t xml:space="preserve">88.1755828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">85.207763671875</t>
+    <t xml:space="preserve">85.2077560424805</t>
   </si>
   <si>
     <t xml:space="preserve">84.4853286743164</t>
   </si>
   <si>
-    <t xml:space="preserve">83.9581451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132904052734</t>
+    <t xml:space="preserve">83.9581527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132827758789</t>
   </si>
   <si>
     <t xml:space="preserve">84.2314987182617</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">84.8563079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3053817749023</t>
+    <t xml:space="preserve">85.3053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">85.6373138427734</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">86.4378433227539</t>
   </si>
   <si>
-    <t xml:space="preserve">83.4700241088867</t>
+    <t xml:space="preserve">83.4700164794922</t>
   </si>
   <si>
     <t xml:space="preserve">81.5175094604492</t>
@@ -4694,16 +4694,16 @@
     <t xml:space="preserve">82.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8146057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531234741211</t>
+    <t xml:space="preserve">80.8145980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531158447266</t>
   </si>
   <si>
     <t xml:space="preserve">80.4436264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">80.131217956543</t>
+    <t xml:space="preserve">80.1312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">82.493766784668</t>
@@ -4724,10 +4724,10 @@
     <t xml:space="preserve">85.5006408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7892990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816390991211</t>
+    <t xml:space="preserve">86.789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816467285156</t>
   </si>
   <si>
     <t xml:space="preserve">83.1185684204102</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">88.8394393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2969512939453</t>
+    <t xml:space="preserve">87.2969436645508</t>
   </si>
   <si>
     <t xml:space="preserve">84.3096008300781</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">86.6916732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4183120727539</t>
+    <t xml:space="preserve">86.4183197021484</t>
   </si>
   <si>
     <t xml:space="preserve">85.98876953125</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">89.6985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8589553833008</t>
+    <t xml:space="preserve">88.8589630126953</t>
   </si>
   <si>
     <t xml:space="preserve">87.6093521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9064483642578</t>
+    <t xml:space="preserve">86.9064407348633</t>
   </si>
   <si>
     <t xml:space="preserve">86.3402252197266</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">90.9481582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9872055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0262603759766</t>
+    <t xml:space="preserve">90.9871978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">87.8436584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6135787963867</t>
+    <t xml:space="preserve">86.6135711669922</t>
   </si>
   <si>
     <t xml:space="preserve">87.2774276733398</t>
@@ -4835,13 +4835,13 @@
     <t xml:space="preserve">88.4294128417969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.7808685302734</t>
+    <t xml:space="preserve">88.7808609008789</t>
   </si>
   <si>
     <t xml:space="preserve">88.2341613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5117263793945</t>
+    <t xml:space="preserve">87.5117340087891</t>
   </si>
   <si>
     <t xml:space="preserve">87.121223449707</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">85.9106674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1296539306641</t>
+    <t xml:space="preserve">85.1296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">84.0167236328125</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">82.6304397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">84.3877105712891</t>
+    <t xml:space="preserve">84.3877029418945</t>
   </si>
   <si>
     <t xml:space="preserve">84.3486557006836</t>
@@ -4877,10 +4877,10 @@
     <t xml:space="preserve">83.8605270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4547119140625</t>
+    <t xml:space="preserve">83.0014114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.454719543457</t>
   </si>
   <si>
     <t xml:space="preserve">82.9428405761719</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">84.9344100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">84.055778503418</t>
+    <t xml:space="preserve">84.0557708740234</t>
   </si>
   <si>
     <t xml:space="preserve">84.8953552246094</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">85.6958923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7001113891602</t>
+    <t xml:space="preserve">84.7001037597656</t>
   </si>
   <si>
     <t xml:space="preserve">84.7196350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2578964233398</t>
+    <t xml:space="preserve">87.2579040527344</t>
   </si>
   <si>
     <t xml:space="preserve">88.1170120239258</t>
@@ -4931,19 +4931,19 @@
     <t xml:space="preserve">92.3149108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2843017578125</t>
+    <t xml:space="preserve">90.284309387207</t>
   </si>
   <si>
     <t xml:space="preserve">91.7096405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8310012817383</t>
+    <t xml:space="preserve">90.8310089111328</t>
   </si>
   <si>
     <t xml:space="preserve">91.4753341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4125518798828</t>
+    <t xml:space="preserve">92.4125442504883</t>
   </si>
   <si>
     <t xml:space="preserve">94.5017395019531</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">91.2605667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4515838623047</t>
+    <t xml:space="preserve">92.4515914916992</t>
   </si>
   <si>
     <t xml:space="preserve">89.6399765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9259719848633</t>
+    <t xml:space="preserve">86.9259796142578</t>
   </si>
   <si>
     <t xml:space="preserve">86.0863952636719</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">84.1338806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9275360107422</t>
+    <t xml:space="preserve">81.9275283813477</t>
   </si>
   <si>
     <t xml:space="preserve">81.3222579956055</t>
@@ -4991,22 +4991,22 @@
     <t xml:space="preserve">83.7238464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6721420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615936279297</t>
+    <t xml:space="preserve">86.6721496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615859985352</t>
   </si>
   <si>
     <t xml:space="preserve">85.2858581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4098815917969</t>
+    <t xml:space="preserve">88.4098892211914</t>
   </si>
   <si>
     <t xml:space="preserve">87.4531555175781</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">92.6858978271484</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5840530395508</t>
+    <t xml:space="preserve">93.5840454101562</t>
   </si>
   <si>
     <t xml:space="preserve">93.7402496337891</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">91.4362869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6468505859375</t>
+    <t xml:space="preserve">92.646842956543</t>
   </si>
   <si>
     <t xml:space="preserve">93.9550247192383</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">90.7724304199219</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6510543823242</t>
+    <t xml:space="preserve">91.6510620117188</t>
   </si>
   <si>
     <t xml:space="preserve">91.1043548583984</t>
@@ -5472,9 +5472,6 @@
   </si>
   <si>
     <t xml:space="preserve">95.2035980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.627082824707</t>
   </si>
   <si>
     <t xml:space="preserve">97.6128234863281</t>
@@ -67002,7 +66999,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1820</v>
+        <v>1507</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67054,7 +67051,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67080,7 +67077,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67106,7 +67103,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67132,7 +67129,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67158,7 +67155,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67184,7 +67181,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67210,7 +67207,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67236,7 +67233,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67262,7 +67259,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67288,7 +67285,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67314,7 +67311,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67340,7 +67337,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67366,7 +67363,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67392,7 +67389,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67418,7 +67415,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67444,7 +67441,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67470,7 +67467,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67522,7 +67519,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67548,7 +67545,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67574,7 +67571,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67600,7 +67597,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67626,7 +67623,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67652,7 +67649,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67704,7 +67701,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67730,7 +67727,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67756,7 +67753,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67782,7 +67779,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67834,7 +67831,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67886,7 +67883,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67938,7 +67935,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67990,7 +67987,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68016,7 +68013,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68068,7 +68065,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68094,7 +68091,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68120,7 +68117,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68146,7 +68143,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68172,7 +68169,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68198,7 +68195,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68224,7 +68221,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68250,7 +68247,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68276,7 +68273,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68302,7 +68299,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68328,7 +68325,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68354,7 +68351,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68380,7 +68377,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68406,7 +68403,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68432,7 +68429,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68458,7 +68455,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68484,7 +68481,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68510,7 +68507,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68536,7 +68533,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68562,7 +68559,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68588,7 +68585,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68614,7 +68611,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68640,7 +68637,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68666,7 +68663,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68692,7 +68689,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68718,7 +68715,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68744,7 +68741,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68770,7 +68767,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68796,7 +68793,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68822,7 +68819,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68848,7 +68845,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68874,7 +68871,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68900,7 +68897,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68926,7 +68923,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68952,7 +68949,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68978,7 +68975,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69004,7 +69001,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69030,7 +69027,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69056,7 +69053,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69082,7 +69079,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69108,7 +69105,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69134,7 +69131,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69160,7 +69157,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69186,7 +69183,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69212,7 +69209,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69238,7 +69235,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69264,7 +69261,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69290,7 +69287,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69316,7 +69313,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69342,7 +69339,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69368,7 +69365,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69394,7 +69391,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69420,7 +69417,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69446,7 +69443,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69472,7 +69469,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69498,7 +69495,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69524,7 +69521,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69550,7 +69547,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69576,7 +69573,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69602,7 +69599,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69628,7 +69625,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69654,7 +69651,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69680,7 +69677,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69706,7 +69703,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69732,7 +69729,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69758,7 +69755,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69784,7 +69781,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69810,7 +69807,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69836,7 +69833,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69862,7 +69859,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69888,7 +69885,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69914,7 +69911,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69940,7 +69937,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69966,7 +69963,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69992,7 +69989,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70018,7 +70015,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70044,7 +70041,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70070,7 +70067,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70096,7 +70093,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70122,7 +70119,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70148,7 +70145,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70174,7 +70171,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70200,7 +70197,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70226,7 +70223,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70252,7 +70249,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70278,7 +70275,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70304,7 +70301,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70330,7 +70327,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70356,7 +70353,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70382,7 +70379,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70408,7 +70405,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70434,7 +70431,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70460,7 +70457,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70486,7 +70483,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70512,7 +70509,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70538,7 +70535,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70564,7 +70561,7 @@
         <v>77.8600006103516</v>
       </c>
       <c r="G2474" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70590,7 +70587,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2475" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70616,7 +70613,7 @@
         <v>74.1800003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70642,7 +70639,7 @@
         <v>74.1399993896484</v>
       </c>
       <c r="G2477" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70668,7 +70665,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2478" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70694,7 +70691,7 @@
         <v>75.5199966430664</v>
       </c>
       <c r="G2479" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70720,7 +70717,7 @@
         <v>77.6600036621094</v>
       </c>
       <c r="G2480" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70746,7 +70743,7 @@
         <v>77.8399963378906</v>
       </c>
       <c r="G2481" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70772,7 +70769,7 @@
         <v>78.879997253418</v>
       </c>
       <c r="G2482" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70798,7 +70795,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2483" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70824,7 +70821,7 @@
         <v>79.0400009155273</v>
       </c>
       <c r="G2484" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70850,7 +70847,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G2485" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70876,7 +70873,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G2486" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70902,7 +70899,7 @@
         <v>75.6399993896484</v>
       </c>
       <c r="G2487" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70928,7 +70925,7 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2488" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70954,7 +70951,7 @@
         <v>74.1999969482422</v>
       </c>
       <c r="G2489" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70980,7 +70977,7 @@
         <v>74.2399978637695</v>
       </c>
       <c r="G2490" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -71006,7 +71003,7 @@
         <v>74.9400024414062</v>
       </c>
       <c r="G2491" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -71032,7 +71029,7 @@
         <v>75.2600021362305</v>
       </c>
       <c r="G2492" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71058,7 +71055,7 @@
         <v>75.9400024414062</v>
       </c>
       <c r="G2493" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71084,7 +71081,7 @@
         <v>75.9599990844727</v>
       </c>
       <c r="G2494" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71092,7 +71089,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6493055556</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>298255</v>
@@ -71110,9 +71107,35 @@
         <v>77.9400024414062</v>
       </c>
       <c r="G2495" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6493402778</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>177452</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>78.3000030517578</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>77.4199981689453</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>78.3000030517578</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="1967">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954605102539</t>
+    <t xml:space="preserve">42.4954643249512</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.042308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9276466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8218078613281</t>
+    <t xml:space="preserve">43.2980918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0423049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9276351928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8218040466309</t>
   </si>
   <si>
     <t xml:space="preserve">42.1514701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4689979553223</t>
+    <t xml:space="preserve">42.4689903259277</t>
   </si>
   <si>
     <t xml:space="preserve">41.7281036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2870979309082</t>
+    <t xml:space="preserve">41.2871017456055</t>
   </si>
   <si>
     <t xml:space="preserve">39.9993515014648</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2761116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0765647888184</t>
+    <t xml:space="preserve">39.2761039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0765609741211</t>
   </si>
   <si>
     <t xml:space="preserve">37.8384208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6443824768066</t>
+    <t xml:space="preserve">37.6443786621094</t>
   </si>
   <si>
     <t xml:space="preserve">38.9585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2551422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606353759766</t>
+    <t xml:space="preserve">40.2551345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2606315612793</t>
   </si>
   <si>
     <t xml:space="preserve">42.0544509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3664855957031</t>
+    <t xml:space="preserve">41.3664817810059</t>
   </si>
   <si>
     <t xml:space="preserve">42.7776985168457</t>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">42.9982070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8780479431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2341804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4172248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7590408325195</t>
+    <t xml:space="preserve">41.878044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2341728210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4172210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7590446472168</t>
   </si>
   <si>
     <t xml:space="preserve">38.014820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">38.588134765625</t>
+    <t xml:space="preserve">38.5881385803223</t>
   </si>
   <si>
     <t xml:space="preserve">38.6057777404785</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4029159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1228408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3962669372559</t>
+    <t xml:space="preserve">38.4029121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1228370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3962631225586</t>
   </si>
   <si>
     <t xml:space="preserve">40.4932823181152</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">41.4017601013184</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5483779907227</t>
+    <t xml:space="preserve">42.5483894348145</t>
   </si>
   <si>
     <t xml:space="preserve">41.9397888183594</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">42.5924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2098960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2275314331055</t>
+    <t xml:space="preserve">43.209888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.901180267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2275276184082</t>
   </si>
   <si>
     <t xml:space="preserve">42.557201385498</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8074798583984</t>
+    <t xml:space="preserve">41.807487487793</t>
   </si>
   <si>
     <t xml:space="preserve">42.6453971862793</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">42.7071418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7600593566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7578887939453</t>
+    <t xml:space="preserve">42.7600555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.757884979248</t>
   </si>
   <si>
     <t xml:space="preserve">40.3521614074707</t>
@@ -185,148 +185,148 @@
     <t xml:space="preserve">40.0081787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1636161804199</t>
+    <t xml:space="preserve">41.1636085510254</t>
   </si>
   <si>
     <t xml:space="preserve">40.5726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1581115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6200942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1140213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2904205322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8405952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.131649017334</t>
+    <t xml:space="preserve">40.1581153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6200904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1140251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2904243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8405990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1316566467285</t>
   </si>
   <si>
     <t xml:space="preserve">40.4668197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1007270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7622261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.291446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.86474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3796424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.688346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8349647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9088554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4237518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2032470703125</t>
+    <t xml:space="preserve">44.1007232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7622375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2914428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8647613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3796463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6883506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9088516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4237480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2032432556152</t>
   </si>
   <si>
     <t xml:space="preserve">44.8945388793945</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9386444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3355407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8063316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7181396484375</t>
+    <t xml:space="preserve">44.9386405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3355445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8063354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7181358337402</t>
   </si>
   <si>
     <t xml:space="preserve">45.2473411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">44.982738494873</t>
+    <t xml:space="preserve">44.9827423095703</t>
   </si>
   <si>
     <t xml:space="preserve">44.8504333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">45.776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442527770996</t>
+    <t xml:space="preserve">45.7765579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442489624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.8206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3057594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.173454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2616691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6144676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0852584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4226608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5119743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1100883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5836715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5660591125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553764343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2358818054199</t>
+    <t xml:space="preserve">46.3057518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1734619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.261661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6144599914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0852546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4226570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5119781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1100845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5836753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2358741760254</t>
   </si>
   <si>
     <t xml:space="preserve">49.0748672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">49.967945098877</t>
+    <t xml:space="preserve">49.9679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">49.164176940918</t>
@@ -335,76 +335,76 @@
     <t xml:space="preserve">49.700023651123</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9855575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566291809082</t>
+    <t xml:space="preserve">48.9855690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566253662109</t>
   </si>
   <si>
     <t xml:space="preserve">47.7352447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6188926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.931468963623</t>
+    <t xml:space="preserve">46.6188850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9314727783203</t>
   </si>
   <si>
     <t xml:space="preserve">48.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723556518555</t>
+    <t xml:space="preserve">49.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723594665527</t>
   </si>
   <si>
     <t xml:space="preserve">45.011344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0383834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8962554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7446823120117</t>
+    <t xml:space="preserve">46.0383796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8962516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.744686126709</t>
   </si>
   <si>
     <t xml:space="preserve">50.414493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1371307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9409065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8339805603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.030216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2182693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2629241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.575496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7987632751465</t>
+    <t xml:space="preserve">48.137134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9408988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8339881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0302124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2629203796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.861026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5755004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.798770904541</t>
   </si>
   <si>
     <t xml:space="preserve">50.9949913024902</t>
@@ -416,31 +416,31 @@
     <t xml:space="preserve">50.2805290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1912231445312</t>
+    <t xml:space="preserve">50.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.191219329834</t>
   </si>
   <si>
     <t xml:space="preserve">51.6201553344727</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5849380493164</t>
+    <t xml:space="preserve">53.5849342346191</t>
   </si>
   <si>
     <t xml:space="preserve">53.0937385559082</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1654396057129</t>
+    <t xml:space="preserve">54.1654434204102</t>
   </si>
   <si>
     <t xml:space="preserve">54.344051361084</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3711013793945</t>
+    <t xml:space="preserve">55.3710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">54.1207809448242</t>
@@ -449,37 +449,37 @@
     <t xml:space="preserve">52.0666923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6648063659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6824111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968772888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.637767791748</t>
+    <t xml:space="preserve">51.6648025512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6824150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6377639770508</t>
   </si>
   <si>
     <t xml:space="preserve">52.2453117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7541160583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4415397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3522338867188</t>
+    <t xml:space="preserve">51.7541122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4415321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3522300720215</t>
   </si>
   <si>
     <t xml:space="preserve">51.8880767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">51.084300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4591445922852</t>
+    <t xml:space="preserve">51.0843086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4591407775879</t>
   </si>
   <si>
     <t xml:space="preserve">49.476749420166</t>
@@ -488,52 +488,52 @@
     <t xml:space="preserve">49.2981414794922</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9773864746094</t>
+    <t xml:space="preserve">51.9773902893066</t>
   </si>
   <si>
     <t xml:space="preserve">52.5132331848145</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6918525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.289966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.183048248291</t>
+    <t xml:space="preserve">52.6918487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2899589538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1830444335938</t>
   </si>
   <si>
     <t xml:space="preserve">51.7094612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1736030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1465721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9056930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0126075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6459350585938</t>
+    <t xml:space="preserve">51.1736106872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270736694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1465606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9056854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0126113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6459312438965</t>
   </si>
   <si>
     <t xml:space="preserve">47.8245544433594</t>
@@ -551,52 +551,49 @@
     <t xml:space="preserve">46.395622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6635475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2616653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7704658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1277008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5742378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4402732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9937324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4578857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6811485290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5295867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3063125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2440528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4673194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2088317871094</t>
+    <t xml:space="preserve">46.6635437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7704696655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1276969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4402809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9937362670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4578895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5295829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3063087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2440490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4673271179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2088279724121</t>
   </si>
   <si>
     <t xml:space="preserve">50.3698387145996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1560020446777</t>
+    <t xml:space="preserve">52.156005859375</t>
   </si>
   <si>
     <t xml:space="preserve">50.5037994384766</t>
@@ -605,22 +602,22 @@
     <t xml:space="preserve">48.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6107139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8163719177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1289596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2006530761719</t>
+    <t xml:space="preserve">49.6107215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8163833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1289558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2006568908691</t>
   </si>
   <si>
     <t xml:space="preserve">52.4685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3616638183594</t>
+    <t xml:space="preserve">53.3616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">53.4063186645508</t>
@@ -632,28 +629,28 @@
     <t xml:space="preserve">53.674243927002</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9151229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2723617553711</t>
+    <t xml:space="preserve">52.9151191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2723579406738</t>
   </si>
   <si>
     <t xml:space="preserve">53.852855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7905960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.594367980957</t>
+    <t xml:space="preserve">54.7905921936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5943641662598</t>
   </si>
   <si>
     <t xml:space="preserve">55.3264427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5050582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2641830444336</t>
+    <t xml:space="preserve">55.5050659179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2641792297363</t>
   </si>
   <si>
     <t xml:space="preserve">56.1302185058594</t>
@@ -662,46 +659,46 @@
     <t xml:space="preserve">55.6390228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8000297546387</t>
+    <t xml:space="preserve">56.8000259399414</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9786415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.335880279541</t>
+    <t xml:space="preserve">56.978645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3358764648438</t>
   </si>
   <si>
     <t xml:space="preserve">58.0503463745117</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8987770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0327339172363</t>
+    <t xml:space="preserve">58.8987731933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0327262878418</t>
   </si>
   <si>
     <t xml:space="preserve">58.7648086547852</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0950012207031</t>
+    <t xml:space="preserve">58.0949974060059</t>
   </si>
   <si>
     <t xml:space="preserve">57.1572685241699</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3805389404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5861968994141</t>
+    <t xml:space="preserve">57.3805274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5861892700195</t>
   </si>
   <si>
     <t xml:space="preserve">60.0151214599609</t>
@@ -710,580 +707,583 @@
     <t xml:space="preserve">58.9434280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">59.3006629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830619812012</t>
+    <t xml:space="preserve">59.3006706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830505371094</t>
   </si>
   <si>
     <t xml:space="preserve">61.4440612792969</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4088363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.158519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6226768493652</t>
+    <t xml:space="preserve">63.4088478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6226692199707</t>
   </si>
   <si>
     <t xml:space="preserve">61.8906021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8283386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817939758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7390327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8635520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937370300293</t>
+    <t xml:space="preserve">62.8283348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7390289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5157661437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8635444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528617858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6758041381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.946907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0824508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5342979431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4950675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4379730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7542457580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4831504821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5675582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0705413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8386611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5164260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1668663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5223846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8898086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4320068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2964706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1609115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6971435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0884132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6425361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721176147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.817310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5462074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6877174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4498825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3987464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2120399475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927726745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2393569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7815628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0134582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5104446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3297348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9682464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6067733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0193939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2001419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7482986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7934646606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6579360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9801788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.302417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4260406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4712371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.600830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4652862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8719253540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0586166381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3749160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6911926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5437316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1370697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8659744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1822662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1311187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3902893066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5258560180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8480987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7910003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2607116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.35107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5318222045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5769882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3451232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4414520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5710372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.9836578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7125473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1097717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5616073608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4593200683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.82080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2666625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.034797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7636871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9955749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3237609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3629989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1763076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9444198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1703491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.887336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6102676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8992385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4985427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4081802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2785949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6400527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6162185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0228652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7065963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4806747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4354934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8088836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7517700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9623031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8505783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6186981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0765037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9409446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017219543457</t>
   </si>
   <si>
     <t xml:space="preserve">60.9528503417969</t>
   </si>
   <si>
-    <t xml:space="preserve">61.6757965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9468955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.082447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4379653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7542572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4831504821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5675582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0705337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8386611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5164108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0313110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5223846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8897933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4320220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2964630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1609115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.697151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6425361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.817310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.546215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6877174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4498748779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3987464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216735839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2393646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7815551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0134353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5104598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3297271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.96826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6067886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.0193939208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2001342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7483062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7934722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6579360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9801712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3024101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4260482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4712295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4652862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8719329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0586318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3749084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6912002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5437316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.137077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8659820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.182258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1311111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.305908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3903121948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5258560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8480987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1643829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7910003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8932800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2607269287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3510818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5318069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5770034790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3451232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4414443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5710372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.9836654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7125396728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1097564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5615997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4593200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.82080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2666702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0347900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7636871337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9955673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3237762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3629989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0407485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1762924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9444274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1703414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6102523803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8992462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4985504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4081802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2785873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6400604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.402229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6162261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.932502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0228805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7065963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4806747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4354934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6614074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8088836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7517852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0918807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8505783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6186904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0765075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9409523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9017219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7328987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7994346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.549690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7363739013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838577270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.651969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2904891967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4200973510742</t>
+    <t xml:space="preserve">60.0040130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7328910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.811351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.799446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5496826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7363815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6519775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2905120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4200897216797</t>
   </si>
   <si>
     <t xml:space="preserve">68.2726287841797</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1251602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8600082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540649414062</t>
+    <t xml:space="preserve">70.1251449584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540725708008</t>
   </si>
   <si>
     <t xml:space="preserve">70.622184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1191787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0740127563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6554565429688</t>
+    <t xml:space="preserve">71.1192016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0740203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6554489135742</t>
   </si>
   <si>
     <t xml:space="preserve">73.6946792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4747085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4687652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1976470947266</t>
+    <t xml:space="preserve">72.4747161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.46875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1976547241211</t>
   </si>
   <si>
     <t xml:space="preserve">73.3783798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.6887130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5591278076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1983642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6960983276367</t>
+    <t xml:space="preserve">74.688720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5591354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6961059570312</t>
   </si>
   <si>
     <t xml:space="preserve">74.9289398193359</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8466720581055</t>
+    <t xml:space="preserve">76.8466796875</t>
   </si>
   <si>
     <t xml:space="preserve">75.7964935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">74.152717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.2576293945312</t>
+    <t xml:space="preserve">74.1527099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.2576370239258</t>
   </si>
   <si>
     <t xml:space="preserve">75.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0795059204102</t>
+    <t xml:space="preserve">78.0795135498047</t>
   </si>
   <si>
     <t xml:space="preserve">79.9059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">80.5908432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.362548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7278366088867</t>
+    <t xml:space="preserve">80.5908584594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3625411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7278213500977</t>
   </si>
   <si>
     <t xml:space="preserve">80.2712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2300796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1021881103516</t>
+    <t xml:space="preserve">81.2300872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1021728515625</t>
   </si>
   <si>
     <t xml:space="preserve">84.3806686401367</t>
@@ -1292,25 +1292,25 @@
     <t xml:space="preserve">85.2482223510742</t>
   </si>
   <si>
-    <t xml:space="preserve">84.9285888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893524169922</t>
+    <t xml:space="preserve">84.928596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893600463867</t>
   </si>
   <si>
     <t xml:space="preserve">83.0565185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8006896972656</t>
+    <t xml:space="preserve">81.7323760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8006744384766</t>
   </si>
   <si>
     <t xml:space="preserve">87.3942718505859</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">89.2206878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9422073364258</t>
+    <t xml:space="preserve">87.9421844482422</t>
   </si>
   <si>
     <t xml:space="preserve">89.0380477905273</t>
   </si>
   <si>
-    <t xml:space="preserve">88.0335083007812</t>
+    <t xml:space="preserve">88.0335159301758</t>
   </si>
   <si>
     <t xml:space="preserve">87.2572860717773</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">87.4855880737305</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5769119262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052139282227</t>
+    <t xml:space="preserve">87.576904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052215576172</t>
   </si>
   <si>
     <t xml:space="preserve">89.6772918701172</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">89.4033355712891</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1248245239258</t>
+    <t xml:space="preserve">88.1248321533203</t>
   </si>
   <si>
     <t xml:space="preserve">87.6225662231445</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3531494140625</t>
+    <t xml:space="preserve">88.353141784668</t>
   </si>
   <si>
     <t xml:space="preserve">86.2984085083008</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">85.8418121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">86.1614227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4719848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8327560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.6685791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7689666748047</t>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4720001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.832763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.668571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7689590454102</t>
   </si>
   <si>
     <t xml:space="preserve">81.0474548339844</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">80.2255630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">80.4538650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.358024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4995422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.312370300293</t>
+    <t xml:space="preserve">80.453857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3580169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4995269775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123550415039</t>
   </si>
   <si>
     <t xml:space="preserve">85.1112442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6135025024414</t>
+    <t xml:space="preserve">85.6135177612305</t>
   </si>
   <si>
     <t xml:space="preserve">83.5587768554688</t>
@@ -1421,115 +1421,115 @@
     <t xml:space="preserve">83.8784103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6501083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2391510009766</t>
+    <t xml:space="preserve">83.6501007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2391662597656</t>
   </si>
   <si>
     <t xml:space="preserve">83.7414169311523</t>
   </si>
   <si>
-    <t xml:space="preserve">84.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6410369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9150009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0017929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.275764465332</t>
+    <t xml:space="preserve">84.837272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3350143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9150085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0017852783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.275749206543</t>
   </si>
   <si>
     <t xml:space="preserve">82.8282089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5312423706055</t>
+    <t xml:space="preserve">87.5312576293945</t>
   </si>
   <si>
     <t xml:space="preserve">88.7640762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2437057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199279785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.882926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3761444091797</t>
+    <t xml:space="preserve">84.2436904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.882942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7368927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3761367797852</t>
   </si>
   <si>
     <t xml:space="preserve">81.4583969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2666854858398</t>
+    <t xml:space="preserve">79.2667007446289</t>
   </si>
   <si>
     <t xml:space="preserve">75.1572418212891</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4266815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3308181762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8376235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6002502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9198837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5179901123047</t>
+    <t xml:space="preserve">74.4266586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.330810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8376159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6002578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5180053710938</t>
   </si>
   <si>
     <t xml:space="preserve">74.8832855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2485656738281</t>
+    <t xml:space="preserve">75.2485733032227</t>
   </si>
   <si>
     <t xml:space="preserve">76.4357376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8285522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8330917358398</t>
+    <t xml:space="preserve">72.8285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8330841064453</t>
   </si>
   <si>
     <t xml:space="preserve">72.2806243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9700775146484</t>
+    <t xml:space="preserve">73.9700622558594</t>
   </si>
   <si>
     <t xml:space="preserve">75.0659103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5270690917969</t>
+    <t xml:space="preserve">76.5270614624023</t>
   </si>
   <si>
     <t xml:space="preserve">79.9515991210938</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">75.3398895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">76.1161041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0568542480469</t>
+    <t xml:space="preserve">76.1161193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0568618774414</t>
   </si>
   <si>
     <t xml:space="preserve">70.5455322265625</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">71.9610137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">73.1025161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.326286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0477828979492</t>
+    <t xml:space="preserve">73.1025238037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3262786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477981567383</t>
   </si>
   <si>
     <t xml:space="preserve">70.8651504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">68.5821151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4907989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8560943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3217468261719</t>
+    <t xml:space="preserve">68.5821228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4908142089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8560791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">66.8013610839844</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">66.938346862793</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6187210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5775909423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5228805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0160675048828</t>
+    <t xml:space="preserve">66.6187286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5775833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8470230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5228652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0160751342773</t>
   </si>
   <si>
     <t xml:space="preserve">64.4270172119141</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">64.2900314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7923049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.162109375</t>
+    <t xml:space="preserve">64.7922897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1621170043945</t>
   </si>
   <si>
     <t xml:space="preserve">64.944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2089309692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6771926879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3025894165039</t>
+    <t xml:space="preserve">66.2089385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6771850585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.302604675293</t>
   </si>
   <si>
     <t xml:space="preserve">70.0016708374023</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">69.4866027832031</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2056655883789</t>
+    <t xml:space="preserve">69.2056732177734</t>
   </si>
   <si>
     <t xml:space="preserve">69.627082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7508697509766</t>
+    <t xml:space="preserve">70.750862121582</t>
   </si>
   <si>
     <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8913192749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5769958496094</t>
+    <t xml:space="preserve">69.7675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8913269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5769882202148</t>
   </si>
   <si>
     <t xml:space="preserve">73.0452270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459487915039</t>
+    <t xml:space="preserve">75.2459411621094</t>
   </si>
   <si>
     <t xml:space="preserve">75.1054763793945</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9649963378906</t>
+    <t xml:space="preserve">74.9650039672852</t>
   </si>
   <si>
     <t xml:space="preserve">74.5904083251953</t>
@@ -1673,31 +1673,31 @@
     <t xml:space="preserve">75.0586547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2927780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6840515136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.556999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1355972290039</t>
+    <t xml:space="preserve">75.2927703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1355895996094</t>
   </si>
   <si>
     <t xml:space="preserve">74.8713531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8847808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9784240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7109146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6172561645508</t>
+    <t xml:space="preserve">76.8847732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9784164428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7109069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6172637939453</t>
   </si>
   <si>
     <t xml:space="preserve">79.694206237793</t>
@@ -1706,76 +1706,76 @@
     <t xml:space="preserve">79.2727966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">79.6005783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2259750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4132766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7878494262695</t>
+    <t xml:space="preserve">79.6005706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2259826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4132690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7878646850586</t>
   </si>
   <si>
     <t xml:space="preserve">80.0219802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0386734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8815155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6775283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3029403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7711639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0354080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7076416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3330459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.239387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2227020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.145751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9751510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.26953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5036544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0186996459961</t>
+    <t xml:space="preserve">79.0386810302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8815078735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6775054931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7711563110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.035400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.707649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3330535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2393951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2227096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9751586914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2695159912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5036468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0187149047852</t>
   </si>
   <si>
     <t xml:space="preserve">83.2528305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9250640869141</t>
+    <t xml:space="preserve">82.9250564575195</t>
   </si>
   <si>
     <t xml:space="preserve">83.6742477416992</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">82.9718856811523</t>
   </si>
   <si>
-    <t xml:space="preserve">84.048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0019989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7980194091797</t>
+    <t xml:space="preserve">84.0488357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0020065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7980117797852</t>
   </si>
   <si>
     <t xml:space="preserve">85.7813110351562</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">86.8582611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">86.1559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8281402587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6876754760742</t>
+    <t xml:space="preserve">86.1558990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8281478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6876678466797</t>
   </si>
   <si>
     <t xml:space="preserve">85.2194290161133</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">85.1257858276367</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6408386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822372436523</t>
+    <t xml:space="preserve">85.6408462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822296142578</t>
   </si>
   <si>
     <t xml:space="preserve">79.7410354614258</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">81.5671615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8481140136719</t>
+    <t xml:space="preserve">81.8481216430664</t>
   </si>
   <si>
     <t xml:space="preserve">83.8147125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">84.1893081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2829437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3130722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1693420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4803848266602</t>
+    <t xml:space="preserve">84.1893005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2829513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3130798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4804000854492</t>
   </si>
   <si>
     <t xml:space="preserve">91.2597045898438</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">91.2128829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6854858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.543701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8347930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.598503112793</t>
+    <t xml:space="preserve">91.6854934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1580963134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5984954833984</t>
   </si>
   <si>
     <t xml:space="preserve">89.1806793212891</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">86.5340957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0786285400391</t>
+    <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
     <t xml:space="preserve">91.3546676635742</t>
@@ -1895,34 +1895,34 @@
     <t xml:space="preserve">91.9690551757812</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1033096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5608520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4115447998047</t>
+    <t xml:space="preserve">93.1033020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5608596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4115600585938</t>
   </si>
   <si>
     <t xml:space="preserve">93.8122100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0731964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8293609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3416900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.326652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6800537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.247184753418</t>
+    <t xml:space="preserve">97.0731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3416976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.326637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2471694946289</t>
   </si>
   <si>
     <t xml:space="preserve">96.8841552734375</t>
@@ -1931,25 +1931,25 @@
     <t xml:space="preserve">97.6403198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9389343261719</t>
+    <t xml:space="preserve">95.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">96.3170318603516</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5060729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2622299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9786682128906</t>
+    <t xml:space="preserve">96.5060577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2622375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9786758422852</t>
   </si>
   <si>
     <t xml:space="preserve">99.5307464599609</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3019561767578</t>
+    <t xml:space="preserve">98.3019714355469</t>
   </si>
   <si>
     <t xml:space="preserve">97.3567657470703</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">98.2074508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">97.1677322387695</t>
+    <t xml:space="preserve">97.1677169799805</t>
   </si>
   <si>
     <t xml:space="preserve">97.5458068847656</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2225036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7499008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8444290161133</t>
+    <t xml:space="preserve">96.2225112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7499084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8444213867188</t>
   </si>
   <si>
     <t xml:space="preserve">95.4663391113281</t>
@@ -1979,82 +1979,82 @@
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1526565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.799240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.665008544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.097877502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9088287353516</t>
+    <t xml:space="preserve">102.082809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475967407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1526641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.664985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.097869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.908821105957</t>
   </si>
   <si>
     <t xml:space="preserve">98.3964920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">100.192390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.366386413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.177337646484</t>
+    <t xml:space="preserve">100.1923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.36637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.17733001709</t>
   </si>
   <si>
     <t xml:space="preserve">103.784194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">103.028030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.003341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.13761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.704727172852</t>
+    <t xml:space="preserve">103.028022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.003349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.137596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.704719543457</t>
   </si>
   <si>
     <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">103.500625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.933502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.381423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5855407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.112922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.948570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.286918640137</t>
+    <t xml:space="preserve">103.500633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.93350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.38143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5855331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6951065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1129302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0581436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.94856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.286911010742</t>
   </si>
   <si>
     <t xml:space="preserve">99.7197799682617</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">100.854034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">99.6252746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4266052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7101593017578</t>
+    <t xml:space="preserve">99.6252670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4265975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7101669311523</t>
   </si>
   <si>
     <t xml:space="preserve">93.8594741821289</t>
@@ -2078,25 +2078,25 @@
     <t xml:space="preserve">94.0957870483398</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2848205566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6156463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5211181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6382369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3471450805664</t>
+    <t xml:space="preserve">94.2848281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6156311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5211334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6382217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3471374511719</t>
   </si>
   <si>
     <t xml:space="preserve">91.3074111938477</t>
   </si>
   <si>
-    <t xml:space="preserve">92.2998733520508</t>
+    <t xml:space="preserve">92.2998809814453</t>
   </si>
   <si>
     <t xml:space="preserve">91.7327499389648</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">94.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">98.8690948486328</t>
+    <t xml:space="preserve">98.8690872192383</t>
   </si>
   <si>
     <t xml:space="preserve">97.9238815307617</t>
@@ -2123,43 +2123,43 @@
     <t xml:space="preserve">100.75951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">103.122535705566</t>
+    <t xml:space="preserve">103.122543334961</t>
   </si>
   <si>
     <t xml:space="preserve">104.634887695312</t>
   </si>
   <si>
-    <t xml:space="preserve">105.958183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.659561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.077377319336</t>
+    <t xml:space="preserve">105.95817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.226676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.659553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.07738494873</t>
   </si>
   <si>
     <t xml:space="preserve">112.574661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">113.803436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.65412902832</t>
+    <t xml:space="preserve">113.803428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.236305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.654121398926</t>
   </si>
   <si>
     <t xml:space="preserve">111.818481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">114.937683105469</t>
+    <t xml:space="preserve">114.937690734863</t>
   </si>
   <si>
     <t xml:space="preserve">115.977416992188</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">113.425346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">109.644500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.251365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.306137084961</t>
+    <t xml:space="preserve">109.644493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.251358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.589721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.306144714355</t>
   </si>
   <si>
     <t xml:space="preserve">111.156837463379</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">111.723968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.11710357666</t>
+    <t xml:space="preserve">111.062324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.117111206055</t>
   </si>
   <si>
     <t xml:space="preserve">109.833541870117</t>
@@ -2213,52 +2213,52 @@
     <t xml:space="preserve">111.913017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952751159668</t>
+    <t xml:space="preserve">112.29109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952743530273</t>
   </si>
   <si>
     <t xml:space="preserve">110.87328338623</t>
   </si>
   <si>
-    <t xml:space="preserve">109.455467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.470520019531</t>
+    <t xml:space="preserve">109.455474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.470512390137</t>
   </si>
   <si>
     <t xml:space="preserve">110.495193481445</t>
   </si>
   <si>
-    <t xml:space="preserve">108.037643432617</t>
+    <t xml:space="preserve">108.037658691406</t>
   </si>
   <si>
     <t xml:space="preserve">107.848602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">108.793815612793</t>
+    <t xml:space="preserve">108.793807983398</t>
   </si>
   <si>
     <t xml:space="preserve">106.430786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">109.171897888184</t>
+    <t xml:space="preserve">109.171890258789</t>
   </si>
   <si>
     <t xml:space="preserve">109.266426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">106.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.918449401855</t>
+    <t xml:space="preserve">106.997909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.918441772461</t>
   </si>
   <si>
     <t xml:space="preserve">105.769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">107.754089355469</t>
+    <t xml:space="preserve">107.75407409668</t>
   </si>
   <si>
     <t xml:space="preserve">108.415725708008</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">108.32120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">110.211631774902</t>
+    <t xml:space="preserve">110.211624145508</t>
   </si>
   <si>
     <t xml:space="preserve">114.276039123535</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">109.928070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">104.54035949707</t>
+    <t xml:space="preserve">104.540367126465</t>
   </si>
   <si>
     <t xml:space="preserve">98.7745742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">106.808868408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.595146179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.893768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8143081665039</t>
+    <t xml:space="preserve">106.808860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.595153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.893775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8143005371094</t>
   </si>
   <si>
     <t xml:space="preserve">108.132164001465</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">108.888336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.525291442871</t>
+    <t xml:space="preserve">106.52530670166</t>
   </si>
   <si>
     <t xml:space="preserve">104.445846557617</t>
@@ -2318,46 +2318,46 @@
     <t xml:space="preserve">102.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">114.086990356445</t>
+    <t xml:space="preserve">114.08699798584</t>
   </si>
   <si>
     <t xml:space="preserve">111.629440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">118.056884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.310333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.091178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.329574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876220703125</t>
+    <t xml:space="preserve">118.05689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.310317993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.091163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.32958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876235961914</t>
   </si>
   <si>
     <t xml:space="preserve">136.583038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">145.089920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.239227294922</t>
+    <t xml:space="preserve">145.089904785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.239242553711</t>
   </si>
   <si>
     <t xml:space="preserve">155.959854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">150.38313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.691360473633</t>
+    <t xml:space="preserve">150.383117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.691345214844</t>
   </si>
   <si>
     <t xml:space="preserve">157.755752563477</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">157.94482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">153.313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.885848999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.507751464844</t>
+    <t xml:space="preserve">153.313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.791305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.885818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.507736206055</t>
   </si>
   <si>
     <t xml:space="preserve">144.522796630859</t>
@@ -2387,13 +2387,13 @@
     <t xml:space="preserve">147.641983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">153.596832275391</t>
+    <t xml:space="preserve">153.596817016602</t>
   </si>
   <si>
     <t xml:space="preserve">151.706405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">163.048934936523</t>
+    <t xml:space="preserve">163.048919677734</t>
   </si>
   <si>
     <t xml:space="preserve">167.302383422852</t>
@@ -2402,58 +2402,58 @@
     <t xml:space="preserve">174.10791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">174.675048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.381866455078</t>
+    <t xml:space="preserve">174.675033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.381851196289</t>
   </si>
   <si>
     <t xml:space="preserve">178.833969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">180.440826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.688858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.927215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.206619262695</t>
+    <t xml:space="preserve">180.440811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.688842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.92724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.206604003906</t>
   </si>
   <si>
     <t xml:space="preserve">163.521545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839401245117</t>
+    <t xml:space="preserve">171.839416503906</t>
   </si>
   <si>
     <t xml:space="preserve">178.172302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">171.555847167969</t>
+    <t xml:space="preserve">171.55583190918</t>
   </si>
   <si>
     <t xml:space="preserve">169.098281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">163.994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.655776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.905059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.855712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.651596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.014663696289</t>
+    <t xml:space="preserve">163.994155883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.655792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.905075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.855728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.651626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.014633178711</t>
   </si>
   <si>
     <t xml:space="preserve">158.6064453125</t>
@@ -2462,16 +2462,16 @@
     <t xml:space="preserve">157.850280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">161.510162353516</t>
+    <t xml:space="preserve">161.510147094727</t>
   </si>
   <si>
     <t xml:space="preserve">162.365707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">161.890411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.129898071289</t>
+    <t xml:space="preserve">161.890396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.129913330078</t>
   </si>
   <si>
     <t xml:space="preserve">159.133605957031</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">162.270645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">167.11882019043</t>
+    <t xml:space="preserve">167.118804931641</t>
   </si>
   <si>
     <t xml:space="preserve">164.457061767578</t>
@@ -2492,40 +2492,40 @@
     <t xml:space="preserve">161.320037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">161.985458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.555847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.841018676758</t>
+    <t xml:space="preserve">161.985473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.55583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.841033935547</t>
   </si>
   <si>
     <t xml:space="preserve">162.650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">166.073135375977</t>
+    <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
     <t xml:space="preserve">169.685470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">170.350921630859</t>
+    <t xml:space="preserve">170.35090637207</t>
   </si>
   <si>
     <t xml:space="preserve">163.031143188477</t>
   </si>
   <si>
-    <t xml:space="preserve">164.362014770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.122512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.305221557617</t>
+    <t xml:space="preserve">164.361999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.122497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.305252075195</t>
   </si>
   <si>
     <t xml:space="preserve">169.400283813477</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">171.96696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">169.495361328125</t>
+    <t xml:space="preserve">169.495346069336</t>
   </si>
   <si>
     <t xml:space="preserve">166.358322143555</t>
   </si>
   <si>
-    <t xml:space="preserve">160.939804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.66569519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.17561340332</t>
+    <t xml:space="preserve">160.939788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.665710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.175598144531</t>
   </si>
   <si>
     <t xml:space="preserve">164.742263793945</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">159.22868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">157.802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.669403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.817565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.77555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.768157958984</t>
+    <t xml:space="preserve">157.802764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.669387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.81755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.775543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.768188476562</t>
   </si>
   <si>
     <t xml:space="preserve">145.254577636719</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">154.760772705078</t>
   </si>
   <si>
-    <t xml:space="preserve">151.243499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.190399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.855804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.950897216797</t>
+    <t xml:space="preserve">151.24348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.190368652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.855819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
     <t xml:space="preserve">155.426193237305</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">155.806442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">159.418792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.634841918945</t>
+    <t xml:space="preserve">159.418807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.634826660156</t>
   </si>
   <si>
     <t xml:space="preserve">138.600250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">144.018768310547</t>
+    <t xml:space="preserve">144.018783569336</t>
   </si>
   <si>
     <t xml:space="preserve">144.589126586914</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">143.543472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">135.55827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.797760009766</t>
+    <t xml:space="preserve">135.558258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.797775268555</t>
   </si>
   <si>
     <t xml:space="preserve">137.364440917969</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">144.779266357422</t>
   </si>
   <si>
-    <t xml:space="preserve">143.258285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.060760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.726196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.247161865234</t>
+    <t xml:space="preserve">143.258270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.060745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.726165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.247177124023</t>
   </si>
   <si>
     <t xml:space="preserve">152.954574584961</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">160.654602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">162.080505371094</t>
+    <t xml:space="preserve">162.080535888672</t>
   </si>
   <si>
     <t xml:space="preserve">161.795333862305</t>
@@ -2672,22 +2672,22 @@
     <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.670654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.487945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.716369628906</t>
+    <t xml:space="preserve">168.069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.91389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.29411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.670669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.48796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.716354370117</t>
   </si>
   <si>
     <t xml:space="preserve">180.712661743164</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">181.853393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">179.666976928711</t>
+    <t xml:space="preserve">179.6669921875</t>
   </si>
   <si>
     <t xml:space="preserve">184.990447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">184.039825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.663299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.275604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.089218139648</t>
+    <t xml:space="preserve">184.039840698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.663269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.275634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.08918762207</t>
   </si>
   <si>
     <t xml:space="preserve">181.568222045898</t>
@@ -2726,52 +2726,52 @@
     <t xml:space="preserve">178.050933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">179.191665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.529907226562</t>
+    <t xml:space="preserve">179.191650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.529922485352</t>
   </si>
   <si>
     <t xml:space="preserve">177.860809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">184.610198974609</t>
+    <t xml:space="preserve">184.61018371582</t>
   </si>
   <si>
     <t xml:space="preserve">189.838607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">191.264526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.703964233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.88671875</t>
+    <t xml:space="preserve">191.264541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.703979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.886688232422</t>
   </si>
   <si>
     <t xml:space="preserve">165.217559814453</t>
   </si>
   <si>
-    <t xml:space="preserve">164.932388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.8447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.266967773438</t>
+    <t xml:space="preserve">164.932373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.076812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.947204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.844741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.266952514648</t>
   </si>
   <si>
     <t xml:space="preserve">167.879302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">163.696594238281</t>
+    <t xml:space="preserve">163.696563720703</t>
   </si>
   <si>
     <t xml:space="preserve">161.605224609375</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">160.084228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745971679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.179306030273</t>
+    <t xml:space="preserve">162.745956420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.179290771484</t>
   </si>
   <si>
     <t xml:space="preserve">159.323745727539</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">158.468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">158.848449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.221252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.038543701172</t>
+    <t xml:space="preserve">158.848434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.221267700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
     <t xml:space="preserve">159.608917236328</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">153.810150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">152.859527587891</t>
+    <t xml:space="preserve">152.859512329102</t>
   </si>
   <si>
     <t xml:space="preserve">151.528656005859</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">155.616317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">154.4755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.570663452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.992874145508</t>
+    <t xml:space="preserve">154.475570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.57063293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.992858886719</t>
   </si>
   <si>
     <t xml:space="preserve">170.826217651367</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">179.001541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">168.924987792969</t>
+    <t xml:space="preserve">168.925003051758</t>
   </si>
   <si>
     <t xml:space="preserve">171.681793212891</t>
   </si>
   <si>
-    <t xml:space="preserve">171.111419677734</t>
+    <t xml:space="preserve">171.111404418945</t>
   </si>
   <si>
     <t xml:space="preserve">170.541030883789</t>
@@ -2861,19 +2861,19 @@
     <t xml:space="preserve">170.255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">173.868194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.202774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.389221191406</t>
+    <t xml:space="preserve">173.868209838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.202789306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.389190673828</t>
   </si>
   <si>
     <t xml:space="preserve">176.434875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">176.149703979492</t>
+    <t xml:space="preserve">176.149673461914</t>
   </si>
   <si>
     <t xml:space="preserve">177.195373535156</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">174.438583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">156.18669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.813858032227</t>
+    <t xml:space="preserve">156.186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.813842773438</t>
   </si>
   <si>
     <t xml:space="preserve">155.99658203125</t>
@@ -2894,64 +2894,64 @@
     <t xml:space="preserve">154.380508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">155.901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.137329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.000274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.197799682617</t>
+    <t xml:space="preserve">155.901504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.000259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.197784423828</t>
   </si>
   <si>
     <t xml:space="preserve">149.057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">147.155807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.706390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.082962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.695297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.987899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181716918945</t>
+    <t xml:space="preserve">147.155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.706420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.082946777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.6953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.987884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181732177734</t>
   </si>
   <si>
     <t xml:space="preserve">136.033569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">133.276763916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.037246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.086639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.273086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.136032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.519958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.90022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.044677734375</t>
+    <t xml:space="preserve">133.276779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.03727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.086669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.273071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.136016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.519973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.900207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.044662475586</t>
   </si>
   <si>
     <t xml:space="preserve">132.848999023438</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">145.492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">143.59098815918</t>
+    <t xml:space="preserve">143.591003417969</t>
   </si>
   <si>
     <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">148.201477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.058883666992</t>
+    <t xml:space="preserve">148.20149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.058898925781</t>
   </si>
   <si>
     <t xml:space="preserve">146.300247192383</t>
@@ -2984,25 +2984,25 @@
     <t xml:space="preserve">145.01692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">144.874328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.984176635742</t>
+    <t xml:space="preserve">144.874313354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.98420715332</t>
   </si>
   <si>
     <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">133.324295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.274917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.894683837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.227386474609</t>
+    <t xml:space="preserve">133.324310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.274932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.89469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.227401733398</t>
   </si>
   <si>
     <t xml:space="preserve">131.660720825195</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">131.470596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">131.185424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.655151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.031723022461</t>
+    <t xml:space="preserve">131.185409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.655181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.031707763672</t>
   </si>
   <si>
     <t xml:space="preserve">136.983856201172</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">136.744552612305</t>
   </si>
   <si>
-    <t xml:space="preserve">137.84538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.797515869141</t>
+    <t xml:space="preserve">137.845397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.797500610352</t>
   </si>
   <si>
     <t xml:space="preserve">138.084701538086</t>
@@ -3053,25 +3053,25 @@
     <t xml:space="preserve">138.46760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">135.978729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.059097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.963363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.356506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.218063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.659057617188</t>
+    <t xml:space="preserve">135.978744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.05908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.963348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.356521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.218048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.510360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.659072875977</t>
   </si>
   <si>
     <t xml:space="preserve">139.185546875</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">144.306884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">144.01969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.269271850586</t>
+    <t xml:space="preserve">144.019714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.269287109375</t>
   </si>
   <si>
     <t xml:space="preserve">145.790649414062</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">147.322250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">146.843612670898</t>
+    <t xml:space="preserve">146.843627929688</t>
   </si>
   <si>
     <t xml:space="preserve">147.226547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">143.397491455078</t>
+    <t xml:space="preserve">143.397506713867</t>
   </si>
   <si>
     <t xml:space="preserve">147.99235534668</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">149.428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">150.289749145508</t>
+    <t xml:space="preserve">150.289764404297</t>
   </si>
   <si>
     <t xml:space="preserve">153.065811157227</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">149.906860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">153.879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.320495605469</t>
+    <t xml:space="preserve">153.879486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.320510864258</t>
   </si>
   <si>
     <t xml:space="preserve">152.395721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">153.783737182617</t>
+    <t xml:space="preserve">153.783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">155.123931884766</t>
@@ -3149,31 +3149,31 @@
     <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">155.650436401367</t>
+    <t xml:space="preserve">155.650405883789</t>
   </si>
   <si>
     <t xml:space="preserve">156.081192016602</t>
   </si>
   <si>
-    <t xml:space="preserve">158.905090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.149536132812</t>
+    <t xml:space="preserve">158.90510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.149551391602</t>
   </si>
   <si>
     <t xml:space="preserve">162.207641601562</t>
   </si>
   <si>
-    <t xml:space="preserve">163.643508911133</t>
+    <t xml:space="preserve">163.643539428711</t>
   </si>
   <si>
     <t xml:space="preserve">164.983703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">161.729019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.91535949707</t>
+    <t xml:space="preserve">161.72900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.915344238281</t>
   </si>
   <si>
     <t xml:space="preserve">162.35124206543</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">165.07942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">163.834976196289</t>
+    <t xml:space="preserve">163.834991455078</t>
   </si>
   <si>
     <t xml:space="preserve">168.908462524414</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">168.860595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.036682128906</t>
+    <t xml:space="preserve">166.036666870117</t>
   </si>
   <si>
     <t xml:space="preserve">168.669143676758</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">171.158020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">170.248641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.349472045898</t>
+    <t xml:space="preserve">170.248626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.349487304688</t>
   </si>
   <si>
     <t xml:space="preserve">176.0400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">176.949447631836</t>
+    <t xml:space="preserve">176.949432373047</t>
   </si>
   <si>
     <t xml:space="preserve">177.140899658203</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">180.1083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">179.534057617188</t>
+    <t xml:space="preserve">179.534042358398</t>
   </si>
   <si>
     <t xml:space="preserve">178.05029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">177.475921630859</t>
+    <t xml:space="preserve">177.475936889648</t>
   </si>
   <si>
     <t xml:space="preserve">177.810989379883</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">184.990417480469</t>
   </si>
   <si>
-    <t xml:space="preserve">190.016036987305</t>
+    <t xml:space="preserve">190.016021728516</t>
   </si>
   <si>
     <t xml:space="preserve">192.409194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">193.270736694336</t>
+    <t xml:space="preserve">193.270706176758</t>
   </si>
   <si>
     <t xml:space="preserve">195.568130493164</t>
@@ -3266,16 +3266,16 @@
     <t xml:space="preserve">191.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">196.908309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.812606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.386947631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.29296875</t>
+    <t xml:space="preserve">196.908294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.386932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.292984008789</t>
   </si>
   <si>
     <t xml:space="preserve">193.175003051758</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">192.026290893555</t>
   </si>
   <si>
-    <t xml:space="preserve">193.940811157227</t>
+    <t xml:space="preserve">193.940826416016</t>
   </si>
   <si>
     <t xml:space="preserve">195.855331420898</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">194.515167236328</t>
   </si>
   <si>
-    <t xml:space="preserve">187.479309082031</t>
+    <t xml:space="preserve">187.47932434082</t>
   </si>
   <si>
     <t xml:space="preserve">180.539184570312</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">174.987060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">174.077682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.599044799805</t>
+    <t xml:space="preserve">174.077667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.599060058594</t>
   </si>
   <si>
     <t xml:space="preserve">167.664016723633</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">164.505065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">165.462356567383</t>
+    <t xml:space="preserve">165.462341308594</t>
   </si>
   <si>
     <t xml:space="preserve">162.781997680664</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">166.51530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">170.870834350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.25373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.402465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684509277344</t>
+    <t xml:space="preserve">170.870849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.253753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.402481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684524536133</t>
   </si>
   <si>
     <t xml:space="preserve">173.742630004883</t>
@@ -3353,88 +3353,88 @@
     <t xml:space="preserve">177.715240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">181.44856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.826354980469</t>
+    <t xml:space="preserve">181.448577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.826324462891</t>
   </si>
   <si>
     <t xml:space="preserve">182.884460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">182.83659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.34260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.096389770508</t>
+    <t xml:space="preserve">182.836608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.342620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.096405029297</t>
   </si>
   <si>
     <t xml:space="preserve">187.000686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">188.723724365234</t>
+    <t xml:space="preserve">188.723754882812</t>
   </si>
   <si>
     <t xml:space="preserve">189.202362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">186.426330566406</t>
+    <t xml:space="preserve">186.426315307617</t>
   </si>
   <si>
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.69987487793</t>
+    <t xml:space="preserve">174.699890136719</t>
   </si>
   <si>
     <t xml:space="preserve">176.231506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">175.561401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.964828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.874206542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.506683349609</t>
+    <t xml:space="preserve">175.561416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.093048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.964813232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.87419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.50666809082</t>
   </si>
   <si>
     <t xml:space="preserve">175.896469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">176.61442565918</t>
+    <t xml:space="preserve">176.614410400391</t>
   </si>
   <si>
     <t xml:space="preserve">175.800720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">171.636657714844</t>
+    <t xml:space="preserve">171.636672973633</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">179.294738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.188781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.682754516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.082778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.296478271484</t>
+    <t xml:space="preserve">179.294723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.188766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.682769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.082794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.296493530273</t>
   </si>
   <si>
     <t xml:space="preserve">169.147766113281</t>
@@ -3443,37 +3443,37 @@
     <t xml:space="preserve">164.935836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">167.472564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.392227172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.306747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.928955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.764877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.785369873047</t>
+    <t xml:space="preserve">167.472579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.392196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.306732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.928939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.764892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.785385131836</t>
   </si>
   <si>
     <t xml:space="preserve">170.53581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">152.060684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.688049316406</t>
+    <t xml:space="preserve">152.060699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.688034057617</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">154.932479858398</t>
+    <t xml:space="preserve">154.932495117188</t>
   </si>
   <si>
     <t xml:space="preserve">154.741012573242</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">156.22477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">152.156433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.640167236328</t>
+    <t xml:space="preserve">152.156402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.640182495117</t>
   </si>
   <si>
     <t xml:space="preserve">148.183792114258</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">141.770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">143.780395507812</t>
+    <t xml:space="preserve">143.780410766602</t>
   </si>
   <si>
     <t xml:space="preserve">147.609436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">141.387237548828</t>
+    <t xml:space="preserve">141.387252807617</t>
   </si>
   <si>
     <t xml:space="preserve">139.85563659668</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">137.223175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.946243286133</t>
+    <t xml:space="preserve">138.946228027344</t>
   </si>
   <si>
     <t xml:space="preserve">140.717178344727</t>
@@ -3530,31 +3530,31 @@
     <t xml:space="preserve">128.94287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">126.884773254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.325759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.144592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.006103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518981933594</t>
+    <t xml:space="preserve">126.884757995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.325790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.048843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.144577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.006088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518997192383</t>
   </si>
   <si>
     <t xml:space="preserve">119.41813659668</t>
@@ -3563,22 +3563,22 @@
     <t xml:space="preserve">122.289916992188</t>
   </si>
   <si>
-    <t xml:space="preserve">120.662582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.934387207031</t>
+    <t xml:space="preserve">120.662574768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.934379577637</t>
   </si>
   <si>
     <t xml:space="preserve">114.631843566895</t>
   </si>
   <si>
-    <t xml:space="preserve">117.072853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.546371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.589096069336</t>
+    <t xml:space="preserve">117.072860717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.546363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.58910369873</t>
   </si>
   <si>
     <t xml:space="preserve">112.286560058594</t>
@@ -3593,31 +3593,31 @@
     <t xml:space="preserve">120.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.103591918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.864273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.937728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.124084472656</t>
+    <t xml:space="preserve">123.10359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.864280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937759399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.124099731445</t>
   </si>
   <si>
     <t xml:space="preserve">123.77367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">123.15145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.088218688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.242050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.503616333008</t>
+    <t xml:space="preserve">123.151443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.08821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.242057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.503623962402</t>
   </si>
   <si>
     <t xml:space="preserve">120.806159973145</t>
@@ -3626,55 +3626,55 @@
     <t xml:space="preserve">115.541236877441</t>
   </si>
   <si>
-    <t xml:space="preserve">117.599349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.859153747559</t>
+    <t xml:space="preserve">117.59935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.859161376953</t>
   </si>
   <si>
     <t xml:space="preserve">131.718933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">132.293273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.693313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.597602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.448883056641</t>
+    <t xml:space="preserve">132.29328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.597564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.448890686035</t>
   </si>
   <si>
     <t xml:space="preserve">133.824905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">135.739410400391</t>
+    <t xml:space="preserve">135.73942565918</t>
   </si>
   <si>
     <t xml:space="preserve">135.83512878418</t>
   </si>
   <si>
-    <t xml:space="preserve">139.329147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.616333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.105194091797</t>
+    <t xml:space="preserve">139.329132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.105178833008</t>
   </si>
   <si>
     <t xml:space="preserve">139.041976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">136.170181274414</t>
+    <t xml:space="preserve">136.170196533203</t>
   </si>
   <si>
     <t xml:space="preserve">135.260787963867</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">128.416381835938</t>
   </si>
   <si>
-    <t xml:space="preserve">126.454010009766</t>
+    <t xml:space="preserve">126.454002380371</t>
   </si>
   <si>
     <t xml:space="preserve">124.539482116699</t>
   </si>
   <si>
-    <t xml:space="preserve">120.997627258301</t>
+    <t xml:space="preserve">120.997619628906</t>
   </si>
   <si>
     <t xml:space="preserve">118.7001953125</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">115.254058837891</t>
   </si>
   <si>
-    <t xml:space="preserve">118.652336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.70532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.173698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.64720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392532348633</t>
+    <t xml:space="preserve">118.652328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.70531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392524719238</t>
   </si>
   <si>
     <t xml:space="preserve">114.823295593262</t>
@@ -3731,28 +3731,28 @@
     <t xml:space="preserve">115.493385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">109.271186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.590858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.654090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.165222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.009628295898</t>
+    <t xml:space="preserve">109.271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.590866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.654098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.165214538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.009620666504</t>
   </si>
   <si>
     <t xml:space="preserve">114.871154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">113.435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.563491821289</t>
+    <t xml:space="preserve">113.435264587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.563484191895</t>
   </si>
   <si>
     <t xml:space="preserve">113.052360534668</t>
@@ -3773,22 +3773,22 @@
     <t xml:space="preserve">113.381454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">117.292816162109</t>
+    <t xml:space="preserve">117.292808532715</t>
   </si>
   <si>
     <t xml:space="preserve">118.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">118.306884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.761642456055</t>
+    <t xml:space="preserve">118.30687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.761650085449</t>
   </si>
   <si>
     <t xml:space="preserve">119.803825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">116.278755187988</t>
+    <t xml:space="preserve">116.278762817383</t>
   </si>
   <si>
     <t xml:space="preserve">118.258583068848</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">110.918731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">107.683410644531</t>
+    <t xml:space="preserve">107.683403015137</t>
   </si>
   <si>
     <t xml:space="preserve">112.657127380371</t>
   </si>
   <si>
-    <t xml:space="preserve">109.904670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.685234069824</t>
+    <t xml:space="preserve">109.904678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.685241699219</t>
   </si>
   <si>
     <t xml:space="preserve">112.801986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">113.912620544434</t>
+    <t xml:space="preserve">113.912612915039</t>
   </si>
   <si>
     <t xml:space="preserve">113.526321411133</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">120.190124511719</t>
   </si>
   <si>
-    <t xml:space="preserve">123.377166748047</t>
+    <t xml:space="preserve">123.377174377441</t>
   </si>
   <si>
     <t xml:space="preserve">122.797714233398</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">129.799530029297</t>
   </si>
   <si>
-    <t xml:space="preserve">130.668731689453</t>
+    <t xml:space="preserve">130.668746948242</t>
   </si>
   <si>
     <t xml:space="preserve">131.151641845703</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">131.537933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">125.598457336426</t>
+    <t xml:space="preserve">125.598449707031</t>
   </si>
   <si>
     <t xml:space="preserve">127.964584350586</t>
@@ -3893,19 +3893,19 @@
     <t xml:space="preserve">135.497589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">136.077056884766</t>
+    <t xml:space="preserve">136.077041625977</t>
   </si>
   <si>
     <t xml:space="preserve">132.841720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">128.785491943359</t>
+    <t xml:space="preserve">128.785507202148</t>
   </si>
   <si>
     <t xml:space="preserve">125.936454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">130.234146118164</t>
+    <t xml:space="preserve">130.234161376953</t>
   </si>
   <si>
     <t xml:space="preserve">130.958480834961</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">130.137573242188</t>
   </si>
   <si>
-    <t xml:space="preserve">135.787322998047</t>
+    <t xml:space="preserve">135.787338256836</t>
   </si>
   <si>
     <t xml:space="preserve">132.213958740234</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">131.924240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">135.111282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890014648438</t>
+    <t xml:space="preserve">135.111267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">131.779373168945</t>
@@ -3947,10 +3947,10 @@
     <t xml:space="preserve">132.020812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">131.489639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.310562133789</t>
+    <t xml:space="preserve">131.489624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.310546875</t>
   </si>
   <si>
     <t xml:space="preserve">126.515922546387</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">127.86799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">126.467636108398</t>
+    <t xml:space="preserve">126.467628479004</t>
   </si>
   <si>
     <t xml:space="preserve">125.888191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">129.171798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.061157226562</t>
+    <t xml:space="preserve">129.171783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.061172485352</t>
   </si>
   <si>
     <t xml:space="preserve">128.930358886719</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">126.226188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">129.123504638672</t>
+    <t xml:space="preserve">129.123489379883</t>
   </si>
   <si>
     <t xml:space="preserve">129.992706298828</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">111.449913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">112.463966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.64306640625</t>
+    <t xml:space="preserve">112.463958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">110.097831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">113.816047668457</t>
+    <t xml:space="preserve">113.816040039062</t>
   </si>
   <si>
     <t xml:space="preserve">111.305038452148</t>
@@ -4031,10 +4031,10 @@
     <t xml:space="preserve">108.504302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">109.132057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.974967956543</t>
+    <t xml:space="preserve">109.132064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.974975585938</t>
   </si>
   <si>
     <t xml:space="preserve">123.763473510742</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">121.687072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">124.584381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.64673614502</t>
+    <t xml:space="preserve">124.58438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.646743774414</t>
   </si>
   <si>
     <t xml:space="preserve">131.586227416992</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">126.660781860352</t>
   </si>
   <si>
-    <t xml:space="preserve">124.922416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.314819335938</t>
+    <t xml:space="preserve">124.922409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">124.777534484863</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">125.018974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">128.592330932617</t>
+    <t xml:space="preserve">128.592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">132.069107055664</t>
@@ -4091,16 +4091,16 @@
     <t xml:space="preserve">130.76530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">128.302612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.612503051758</t>
+    <t xml:space="preserve">128.302627563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.612518310547</t>
   </si>
   <si>
     <t xml:space="preserve">128.206024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">127.047096252441</t>
+    <t xml:space="preserve">127.04711151123</t>
   </si>
   <si>
     <t xml:space="preserve">124.487800598145</t>
@@ -4109,10 +4109,10 @@
     <t xml:space="preserve">127.240249633789</t>
   </si>
   <si>
-    <t xml:space="preserve">129.316665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.157745361328</t>
+    <t xml:space="preserve">129.316650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.157730102539</t>
   </si>
   <si>
     <t xml:space="preserve">125.26042175293</t>
@@ -4148,19 +4148,19 @@
     <t xml:space="preserve">123.039154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">122.652847290039</t>
+    <t xml:space="preserve">122.652839660645</t>
   </si>
   <si>
     <t xml:space="preserve">127.62654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">124.874114990234</t>
+    <t xml:space="preserve">124.874122619629</t>
   </si>
   <si>
     <t xml:space="preserve">125.405296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">122.846000671387</t>
+    <t xml:space="preserve">122.845993041992</t>
   </si>
   <si>
     <t xml:space="preserve">122.169960021973</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">121.880218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">122.218246459961</t>
+    <t xml:space="preserve">122.218254089355</t>
   </si>
   <si>
     <t xml:space="preserve">120.14183807373</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">117.196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">117.775703430176</t>
+    <t xml:space="preserve">117.775695800781</t>
   </si>
   <si>
     <t xml:space="preserve">116.906517028809</t>
   </si>
   <si>
-    <t xml:space="preserve">114.250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.415672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236587524414</t>
+    <t xml:space="preserve">114.250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.415679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.23657989502</t>
   </si>
   <si>
     <t xml:space="preserve">112.319107055664</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">112.077659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">109.42179107666</t>
+    <t xml:space="preserve">109.421798706055</t>
   </si>
   <si>
     <t xml:space="preserve">111.063598632812</t>
@@ -4256,13 +4256,13 @@
     <t xml:space="preserve">108.842315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">108.118003845215</t>
+    <t xml:space="preserve">108.11799621582</t>
   </si>
   <si>
     <t xml:space="preserve">107.73169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">105.993301391602</t>
+    <t xml:space="preserve">105.993309020996</t>
   </si>
   <si>
     <t xml:space="preserve">104.303199768066</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">104.013465881348</t>
   </si>
   <si>
-    <t xml:space="preserve">101.937065124512</t>
+    <t xml:space="preserve">101.937072753906</t>
   </si>
   <si>
     <t xml:space="preserve">103.675453186035</t>
@@ -4289,13 +4289,13 @@
     <t xml:space="preserve">97.5911026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1283874511719</t>
+    <t xml:space="preserve">95.1283798217773</t>
   </si>
   <si>
     <t xml:space="preserve">98.5568771362305</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6455078125</t>
+    <t xml:space="preserve">94.6455001831055</t>
   </si>
   <si>
     <t xml:space="preserve">96.5770416259766</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">93.6797332763672</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2100601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7851028442383</t>
+    <t xml:space="preserve">96.2100524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7851104736328</t>
   </si>
   <si>
     <t xml:space="preserve">95.7078475952148</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342666625977</t>
+    <t xml:space="preserve">93.8342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">95.5340118408203</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">95.9589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1819229125977</t>
+    <t xml:space="preserve">94.1819305419922</t>
   </si>
   <si>
     <t xml:space="preserve">93.1582183837891</t>
@@ -4352,25 +4352,25 @@
     <t xml:space="preserve">95.1090698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3750915527344</t>
+    <t xml:space="preserve">94.3750839233398</t>
   </si>
   <si>
     <t xml:space="preserve">94.6068725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3645706176758</t>
+    <t xml:space="preserve">96.3645782470703</t>
   </si>
   <si>
     <t xml:space="preserve">100.874717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">98.7017364501953</t>
+    <t xml:space="preserve">98.7017288208008</t>
   </si>
   <si>
     <t xml:space="preserve">101.164451599121</t>
   </si>
   <si>
-    <t xml:space="preserve">101.985359191895</t>
+    <t xml:space="preserve">101.9853515625</t>
   </si>
   <si>
     <t xml:space="preserve">101.45418548584</t>
@@ -5910,6 +5910,9 @@
   </si>
   <si>
     <t xml:space="preserve">78.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6999969482422</t>
   </si>
 </sst>
 </file>
@@ -12194,7 +12197,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G229" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -12246,7 +12249,7 @@
         <v>51.25</v>
       </c>
       <c r="G231" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12272,7 +12275,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G232" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12298,7 +12301,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G233" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12324,7 +12327,7 @@
         <v>52</v>
       </c>
       <c r="G234" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -12350,7 +12353,7 @@
         <v>51.5</v>
       </c>
       <c r="G235" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12376,7 +12379,7 @@
         <v>50.9000015258789</v>
       </c>
       <c r="G236" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12402,7 +12405,7 @@
         <v>51.25</v>
       </c>
       <c r="G237" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12428,7 +12431,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G238" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12454,7 +12457,7 @@
         <v>51.25</v>
       </c>
       <c r="G239" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12506,7 +12509,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G241" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12532,7 +12535,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G242" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12558,7 +12561,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G243" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12610,7 +12613,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G245" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12636,7 +12639,7 @@
         <v>51.8499984741211</v>
       </c>
       <c r="G246" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12662,7 +12665,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G247" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12688,7 +12691,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G248" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12740,7 +12743,7 @@
         <v>55.0999984741211</v>
       </c>
       <c r="G250" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12844,7 +12847,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G254" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -13052,7 +13055,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G262" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -13130,7 +13133,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G265" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -13416,7 +13419,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G276" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13442,7 +13445,7 @@
         <v>55.5499992370605</v>
       </c>
       <c r="G277" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13546,7 +13549,7 @@
         <v>58.4000015258789</v>
       </c>
       <c r="G281" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13676,7 +13679,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G286" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13832,7 +13835,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G292" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13884,7 +13887,7 @@
         <v>57.25</v>
       </c>
       <c r="G294" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13962,7 +13965,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G297" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13988,7 +13991,7 @@
         <v>58.75</v>
       </c>
       <c r="G298" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -14014,7 +14017,7 @@
         <v>59.75</v>
       </c>
       <c r="G299" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -14066,7 +14069,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G301" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -14092,7 +14095,7 @@
         <v>59.7999992370605</v>
       </c>
       <c r="G302" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -14118,7 +14121,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G303" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -14144,7 +14147,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G304" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -14196,7 +14199,7 @@
         <v>59.25</v>
       </c>
       <c r="G306" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14222,7 +14225,7 @@
         <v>59.6500015258789</v>
       </c>
       <c r="G307" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14274,7 +14277,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G309" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14300,7 +14303,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G310" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14326,7 +14329,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G311" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14352,7 +14355,7 @@
         <v>61.3499984741211</v>
       </c>
       <c r="G312" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14378,7 +14381,7 @@
         <v>62.25</v>
       </c>
       <c r="G313" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14404,7 +14407,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G314" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14430,7 +14433,7 @@
         <v>62.1500015258789</v>
       </c>
       <c r="G315" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14456,7 +14459,7 @@
         <v>63</v>
       </c>
       <c r="G316" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14482,7 +14485,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G317" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14508,7 +14511,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G318" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14534,7 +14537,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G319" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14560,7 +14563,7 @@
         <v>62.25</v>
       </c>
       <c r="G320" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14586,7 +14589,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G321" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14612,7 +14615,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14638,7 +14641,7 @@
         <v>63.7999992370605</v>
       </c>
       <c r="G323" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14664,7 +14667,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G324" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14690,7 +14693,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G325" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14716,7 +14719,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G326" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14742,7 +14745,7 @@
         <v>65</v>
       </c>
       <c r="G327" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14768,7 +14771,7 @@
         <v>65.9499969482422</v>
       </c>
       <c r="G328" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14794,7 +14797,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G329" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14820,7 +14823,7 @@
         <v>65.8000030517578</v>
       </c>
       <c r="G330" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14846,7 +14849,7 @@
         <v>65.0500030517578</v>
       </c>
       <c r="G331" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14872,7 +14875,7 @@
         <v>64</v>
       </c>
       <c r="G332" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14898,7 +14901,7 @@
         <v>64.25</v>
       </c>
       <c r="G333" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14924,7 +14927,7 @@
         <v>66.0999984741211</v>
       </c>
       <c r="G334" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14950,7 +14953,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G335" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14976,7 +14979,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G336" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -15002,7 +15005,7 @@
         <v>66</v>
       </c>
       <c r="G337" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -15028,7 +15031,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G338" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -15054,7 +15057,7 @@
         <v>67.5</v>
       </c>
       <c r="G339" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -15080,7 +15083,7 @@
         <v>68.8000030517578</v>
       </c>
       <c r="G340" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -15106,7 +15109,7 @@
         <v>71</v>
       </c>
       <c r="G341" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -15132,7 +15135,7 @@
         <v>69.5999984741211</v>
       </c>
       <c r="G342" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -15158,7 +15161,7 @@
         <v>69</v>
       </c>
       <c r="G343" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15184,7 +15187,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G344" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15210,7 +15213,7 @@
         <v>69.3000030517578</v>
       </c>
       <c r="G345" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15236,7 +15239,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G346" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15262,7 +15265,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G347" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15288,7 +15291,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G348" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15314,7 +15317,7 @@
         <v>70.25</v>
       </c>
       <c r="G349" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15340,7 +15343,7 @@
         <v>70</v>
       </c>
       <c r="G350" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15366,7 +15369,7 @@
         <v>70</v>
       </c>
       <c r="G351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15392,7 +15395,7 @@
         <v>68.1500015258789</v>
       </c>
       <c r="G352" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15418,7 +15421,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G353" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15444,7 +15447,7 @@
         <v>68.25</v>
       </c>
       <c r="G354" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15470,7 +15473,7 @@
         <v>68.25</v>
       </c>
       <c r="G355" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15496,7 +15499,7 @@
         <v>68.5500030517578</v>
       </c>
       <c r="G356" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15522,7 +15525,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G357" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15548,7 +15551,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G358" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15574,7 +15577,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G359" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15600,7 +15603,7 @@
         <v>68.0500030517578</v>
       </c>
       <c r="G360" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15626,7 +15629,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G361" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15652,7 +15655,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G362" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15678,7 +15681,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G363" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15704,7 +15707,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G364" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15730,7 +15733,7 @@
         <v>70.25</v>
       </c>
       <c r="G365" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15756,7 +15759,7 @@
         <v>71.4499969482422</v>
       </c>
       <c r="G366" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15782,7 +15785,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G367" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15808,7 +15811,7 @@
         <v>71.75</v>
       </c>
       <c r="G368" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15834,7 +15837,7 @@
         <v>72.5</v>
       </c>
       <c r="G369" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15860,7 +15863,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15886,7 +15889,7 @@
         <v>69.75</v>
       </c>
       <c r="G371" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15912,7 +15915,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G372" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15938,7 +15941,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G373" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15964,7 +15967,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G374" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15990,7 +15993,7 @@
         <v>71.1500015258789</v>
       </c>
       <c r="G375" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -16016,7 +16019,7 @@
         <v>71</v>
       </c>
       <c r="G376" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -16042,7 +16045,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G377" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -16068,7 +16071,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G378" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -16094,7 +16097,7 @@
         <v>72.6999969482422</v>
       </c>
       <c r="G379" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -16120,7 +16123,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G380" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -16146,7 +16149,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G381" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -16172,7 +16175,7 @@
         <v>67.5999984741211</v>
       </c>
       <c r="G382" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -16198,7 +16201,7 @@
         <v>66</v>
       </c>
       <c r="G383" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -16224,7 +16227,7 @@
         <v>67.25</v>
       </c>
       <c r="G384" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -16250,7 +16253,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G385" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -16276,7 +16279,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G386" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -16302,7 +16305,7 @@
         <v>67.25</v>
       </c>
       <c r="G387" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -16328,7 +16331,7 @@
         <v>66.5999984741211</v>
       </c>
       <c r="G388" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -16354,7 +16357,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G389" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -16380,7 +16383,7 @@
         <v>67</v>
       </c>
       <c r="G390" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -16406,7 +16409,7 @@
         <v>66.0500030517578</v>
       </c>
       <c r="G391" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -16432,7 +16435,7 @@
         <v>67</v>
       </c>
       <c r="G392" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -16458,7 +16461,7 @@
         <v>67.0999984741211</v>
       </c>
       <c r="G393" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -16484,7 +16487,7 @@
         <v>68</v>
       </c>
       <c r="G394" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -16510,7 +16513,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G395" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -16536,7 +16539,7 @@
         <v>69.75</v>
       </c>
       <c r="G396" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -16562,7 +16565,7 @@
         <v>69.9499969482422</v>
       </c>
       <c r="G397" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -16588,7 +16591,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G398" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -16614,7 +16617,7 @@
         <v>70.1500015258789</v>
       </c>
       <c r="G399" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -16640,7 +16643,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G400" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -16666,7 +16669,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G401" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -16692,7 +16695,7 @@
         <v>73.3000030517578</v>
       </c>
       <c r="G402" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -16718,7 +16721,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G403" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -16744,7 +16747,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G404" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -16770,7 +16773,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G405" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -16796,7 +16799,7 @@
         <v>73.4000015258789</v>
       </c>
       <c r="G406" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -16822,7 +16825,7 @@
         <v>73</v>
       </c>
       <c r="G407" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -16848,7 +16851,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G408" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -16874,7 +16877,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G409" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -16900,7 +16903,7 @@
         <v>72.5999984741211</v>
       </c>
       <c r="G410" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -16926,7 +16929,7 @@
         <v>71.9499969482422</v>
       </c>
       <c r="G411" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -16952,7 +16955,7 @@
         <v>72.1500015258789</v>
       </c>
       <c r="G412" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -16978,7 +16981,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G413" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -17004,7 +17007,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G414" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -17030,7 +17033,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G415" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -17056,7 +17059,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G416" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -17082,7 +17085,7 @@
         <v>71.6999969482422</v>
       </c>
       <c r="G417" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -17108,7 +17111,7 @@
         <v>71.5500030517578</v>
       </c>
       <c r="G418" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -17134,7 +17137,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G419" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -17160,7 +17163,7 @@
         <v>71.4000015258789</v>
       </c>
       <c r="G420" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -17186,7 +17189,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G421" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -17212,7 +17215,7 @@
         <v>70.8000030517578</v>
       </c>
       <c r="G422" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -17238,7 +17241,7 @@
         <v>70.5500030517578</v>
       </c>
       <c r="G423" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -17264,7 +17267,7 @@
         <v>70.0500030517578</v>
       </c>
       <c r="G424" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -17290,7 +17293,7 @@
         <v>69.9499969482422</v>
       </c>
       <c r="G425" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -17316,7 +17319,7 @@
         <v>71.3499984741211</v>
       </c>
       <c r="G426" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -17342,7 +17345,7 @@
         <v>72.4000015258789</v>
       </c>
       <c r="G427" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -17368,7 +17371,7 @@
         <v>72.4499969482422</v>
       </c>
       <c r="G428" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -17394,7 +17397,7 @@
         <v>72.5</v>
       </c>
       <c r="G429" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -17420,7 +17423,7 @@
         <v>73</v>
       </c>
       <c r="G430" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -17446,7 +17449,7 @@
         <v>73.3499984741211</v>
       </c>
       <c r="G431" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -17472,7 +17475,7 @@
         <v>73.6999969482422</v>
       </c>
       <c r="G432" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -17498,7 +17501,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G433" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -17524,7 +17527,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G434" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -17550,7 +17553,7 @@
         <v>73</v>
       </c>
       <c r="G435" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -17576,7 +17579,7 @@
         <v>74</v>
       </c>
       <c r="G436" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -17602,7 +17605,7 @@
         <v>74</v>
       </c>
       <c r="G437" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -17628,7 +17631,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G438" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -17654,7 +17657,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G439" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -17680,7 +17683,7 @@
         <v>74</v>
       </c>
       <c r="G440" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -17706,7 +17709,7 @@
         <v>74.25</v>
       </c>
       <c r="G441" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -17732,7 +17735,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G442" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -17758,7 +17761,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G443" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -17784,7 +17787,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G444" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -17810,7 +17813,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G445" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -17836,7 +17839,7 @@
         <v>75.0999984741211</v>
       </c>
       <c r="G446" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -17862,7 +17865,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G447" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -17888,7 +17891,7 @@
         <v>75.4499969482422</v>
       </c>
       <c r="G448" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -17914,7 +17917,7 @@
         <v>76.5</v>
       </c>
       <c r="G449" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -17940,7 +17943,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G450" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -17966,7 +17969,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G451" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -17992,7 +17995,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G452" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -18018,7 +18021,7 @@
         <v>79</v>
       </c>
       <c r="G453" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -18044,7 +18047,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G454" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -18070,7 +18073,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G455" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -18096,7 +18099,7 @@
         <v>78.75</v>
       </c>
       <c r="G456" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -18122,7 +18125,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G457" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -18148,7 +18151,7 @@
         <v>78.75</v>
       </c>
       <c r="G458" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -18174,7 +18177,7 @@
         <v>79</v>
       </c>
       <c r="G459" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -18200,7 +18203,7 @@
         <v>79</v>
       </c>
       <c r="G460" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18226,7 +18229,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G461" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18252,7 +18255,7 @@
         <v>77.75</v>
       </c>
       <c r="G462" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -18278,7 +18281,7 @@
         <v>77.8499984741211</v>
       </c>
       <c r="G463" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18304,7 +18307,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G464" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18330,7 +18333,7 @@
         <v>78.0500030517578</v>
       </c>
       <c r="G465" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18356,7 +18359,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G466" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -18382,7 +18385,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G467" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -18408,7 +18411,7 @@
         <v>78.3499984741211</v>
       </c>
       <c r="G468" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18434,7 +18437,7 @@
         <v>78</v>
       </c>
       <c r="G469" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18460,7 +18463,7 @@
         <v>78.0999984741211</v>
       </c>
       <c r="G470" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18486,7 +18489,7 @@
         <v>78.9499969482422</v>
       </c>
       <c r="G471" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -18512,7 +18515,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G472" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18538,7 +18541,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G473" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18564,7 +18567,7 @@
         <v>78.5500030517578</v>
       </c>
       <c r="G474" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18590,7 +18593,7 @@
         <v>78.25</v>
       </c>
       <c r="G475" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18616,7 +18619,7 @@
         <v>77.75</v>
       </c>
       <c r="G476" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18642,7 +18645,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G477" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18668,7 +18671,7 @@
         <v>72.5500030517578</v>
       </c>
       <c r="G478" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18694,7 +18697,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G479" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18720,7 +18723,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G480" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18746,7 +18749,7 @@
         <v>74</v>
       </c>
       <c r="G481" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18772,7 +18775,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G482" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18798,7 +18801,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G483" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18824,7 +18827,7 @@
         <v>76.6500015258789</v>
       </c>
       <c r="G484" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18850,7 +18853,7 @@
         <v>77.5</v>
       </c>
       <c r="G485" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18876,7 +18879,7 @@
         <v>77.1999969482422</v>
       </c>
       <c r="G486" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18902,7 +18905,7 @@
         <v>76.3499984741211</v>
       </c>
       <c r="G487" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18928,7 +18931,7 @@
         <v>74.5</v>
       </c>
       <c r="G488" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18954,7 +18957,7 @@
         <v>75.6500015258789</v>
       </c>
       <c r="G489" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18980,7 +18983,7 @@
         <v>76.4000015258789</v>
       </c>
       <c r="G490" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -19006,7 +19009,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G491" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -19032,7 +19035,7 @@
         <v>77.4000015258789</v>
       </c>
       <c r="G492" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -19058,7 +19061,7 @@
         <v>78.0500030517578</v>
       </c>
       <c r="G493" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -19084,7 +19087,7 @@
         <v>77.6500015258789</v>
       </c>
       <c r="G494" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -19110,7 +19113,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G495" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -19136,7 +19139,7 @@
         <v>78.4499969482422</v>
       </c>
       <c r="G496" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -19162,7 +19165,7 @@
         <v>79.5500030517578</v>
       </c>
       <c r="G497" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -19188,7 +19191,7 @@
         <v>80.5500030517578</v>
       </c>
       <c r="G498" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19214,7 +19217,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G499" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19240,7 +19243,7 @@
         <v>78.5500030517578</v>
       </c>
       <c r="G500" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19266,7 +19269,7 @@
         <v>77.3499984741211</v>
       </c>
       <c r="G501" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19292,7 +19295,7 @@
         <v>76.4000015258789</v>
       </c>
       <c r="G502" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19318,7 +19321,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G503" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19344,7 +19347,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G504" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19370,7 +19373,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G505" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19396,7 +19399,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G506" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19422,7 +19425,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G507" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19448,7 +19451,7 @@
         <v>74.4499969482422</v>
       </c>
       <c r="G508" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19474,7 +19477,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G509" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -19500,7 +19503,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G510" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19526,7 +19529,7 @@
         <v>74</v>
       </c>
       <c r="G511" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19552,7 +19555,7 @@
         <v>74.5</v>
       </c>
       <c r="G512" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19578,7 +19581,7 @@
         <v>74.8499984741211</v>
       </c>
       <c r="G513" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19604,7 +19607,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G514" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -19630,7 +19633,7 @@
         <v>76.8000030517578</v>
       </c>
       <c r="G515" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19656,7 +19659,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G516" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19682,7 +19685,7 @@
         <v>79.4499969482422</v>
       </c>
       <c r="G517" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19708,7 +19711,7 @@
         <v>79.25</v>
       </c>
       <c r="G518" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19734,7 +19737,7 @@
         <v>79.5999984741211</v>
       </c>
       <c r="G519" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19760,7 +19763,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G520" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19786,7 +19789,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G521" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19812,7 +19815,7 @@
         <v>79.3499984741211</v>
       </c>
       <c r="G522" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19838,7 +19841,7 @@
         <v>79.6500015258789</v>
       </c>
       <c r="G523" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -19864,7 +19867,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G524" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19890,7 +19893,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G525" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19916,7 +19919,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G526" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19942,7 +19945,7 @@
         <v>79.0500030517578</v>
       </c>
       <c r="G527" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -19968,7 +19971,7 @@
         <v>79</v>
       </c>
       <c r="G528" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19994,7 +19997,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G529" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -20020,7 +20023,7 @@
         <v>79.3000030517578</v>
       </c>
       <c r="G530" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20046,7 +20049,7 @@
         <v>78.8499984741211</v>
       </c>
       <c r="G531" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -20072,7 +20075,7 @@
         <v>77.25</v>
       </c>
       <c r="G532" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20098,7 +20101,7 @@
         <v>77.9499969482422</v>
       </c>
       <c r="G533" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20124,7 +20127,7 @@
         <v>79.4000015258789</v>
       </c>
       <c r="G534" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -20150,7 +20153,7 @@
         <v>76.5500030517578</v>
       </c>
       <c r="G535" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -20176,7 +20179,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G536" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20202,7 +20205,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G537" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -20228,7 +20231,7 @@
         <v>75.6999969482422</v>
       </c>
       <c r="G538" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20254,7 +20257,7 @@
         <v>74.0999984741211</v>
       </c>
       <c r="G539" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20280,7 +20283,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G540" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20306,7 +20309,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G541" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20332,7 +20335,7 @@
         <v>71</v>
       </c>
       <c r="G542" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20358,7 +20361,7 @@
         <v>70</v>
       </c>
       <c r="G543" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20384,7 +20387,7 @@
         <v>70.4000015258789</v>
       </c>
       <c r="G544" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20410,7 +20413,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G545" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20436,7 +20439,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G546" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20462,7 +20465,7 @@
         <v>69.5500030517578</v>
       </c>
       <c r="G547" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20488,7 +20491,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G548" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20514,7 +20517,7 @@
         <v>69.6500015258789</v>
       </c>
       <c r="G549" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20540,7 +20543,7 @@
         <v>69.75</v>
       </c>
       <c r="G550" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20566,7 +20569,7 @@
         <v>69.4499969482422</v>
       </c>
       <c r="G551" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20592,7 +20595,7 @@
         <v>68.5</v>
       </c>
       <c r="G552" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20618,7 +20621,7 @@
         <v>67.4499969482422</v>
       </c>
       <c r="G553" t="s">
-        <v>246</v>
+        <v>379</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20774,7 +20777,7 @@
         <v>73.5500030517578</v>
       </c>
       <c r="G559" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20852,7 +20855,7 @@
         <v>74</v>
       </c>
       <c r="G562" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -20878,7 +20881,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G563" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20904,7 +20907,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G564" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20982,7 +20985,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G567" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -21008,7 +21011,7 @@
         <v>72.5</v>
       </c>
       <c r="G568" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -21060,7 +21063,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G570" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -21086,7 +21089,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G571" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21138,7 +21141,7 @@
         <v>72.9000015258789</v>
       </c>
       <c r="G573" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -21164,7 +21167,7 @@
         <v>73.0999984741211</v>
       </c>
       <c r="G574" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -21190,7 +21193,7 @@
         <v>72.5</v>
       </c>
       <c r="G575" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21216,7 +21219,7 @@
         <v>71.75</v>
       </c>
       <c r="G576" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21294,7 +21297,7 @@
         <v>73.0500030517578</v>
       </c>
       <c r="G579" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21320,7 +21323,7 @@
         <v>73</v>
       </c>
       <c r="G580" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21346,7 +21349,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G581" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21424,7 +21427,7 @@
         <v>75.3499984741211</v>
       </c>
       <c r="G584" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21528,7 +21531,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G588" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21580,7 +21583,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G590" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21658,7 +21661,7 @@
         <v>78.4000015258789</v>
       </c>
       <c r="G593" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21684,7 +21687,7 @@
         <v>78.3499984741211</v>
       </c>
       <c r="G594" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21736,7 +21739,7 @@
         <v>78</v>
       </c>
       <c r="G596" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21788,7 +21791,7 @@
         <v>79.1500015258789</v>
       </c>
       <c r="G598" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21814,7 +21817,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G599" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -71144,7 +71147,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6496180556</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>145388</v>
@@ -71165,6 +71168,32 @@
         <v>1965</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6911111111</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>96967</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>78.6999969482422</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>77.9000015258789</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>78.3199996948242</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>77.6999969482422</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954566955566</t>
+    <t xml:space="preserve">42.4954605102539</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.298095703125</t>
+    <t xml:space="preserve">43.2980918884277</t>
   </si>
   <si>
     <t xml:space="preserve">43.042308807373</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9276428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8218040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1514739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4689979553223</t>
+    <t xml:space="preserve">42.9276390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8218002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1514701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.468994140625</t>
   </si>
   <si>
     <t xml:space="preserve">41.7281074523926</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2870979309082</t>
+    <t xml:space="preserve">41.2870941162109</t>
   </si>
   <si>
     <t xml:space="preserve">39.9993591308594</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">39.2761039733887</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0765609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443786621094</t>
+    <t xml:space="preserve">38.0765647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443748474121</t>
   </si>
   <si>
     <t xml:space="preserve">38.9585762023926</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">40.2551422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2606391906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3664817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.777702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.068775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9982070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2341766357422</t>
+    <t xml:space="preserve">41.2606353759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3664779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7776985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0687713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2341728210449</t>
   </si>
   <si>
     <t xml:space="preserve">39.4172248840332</t>
@@ -119,43 +119,43 @@
     <t xml:space="preserve">37.7590446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">38.014820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6057739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4029121398926</t>
+    <t xml:space="preserve">38.0148277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.605770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4029083251953</t>
   </si>
   <si>
     <t xml:space="preserve">40.1228408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3962593078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4932823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4017562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5483779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9397850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5924835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.209888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011840820312</t>
+    <t xml:space="preserve">40.3962669372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4932861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4017601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5483741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9397888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2098808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.901180267334</t>
   </si>
   <si>
     <t xml:space="preserve">43.2275238037109</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">42.5571975708008</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8074836730957</t>
+    <t xml:space="preserve">41.807487487793</t>
   </si>
   <si>
     <t xml:space="preserve">42.6453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7071342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.760066986084</t>
+    <t xml:space="preserve">42.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7600631713867</t>
   </si>
   <si>
     <t xml:space="preserve">40.757884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3521575927734</t>
+    <t xml:space="preserve">40.352165222168</t>
   </si>
   <si>
     <t xml:space="preserve">40.0081748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1636085510254</t>
+    <t xml:space="preserve">41.1636123657227</t>
   </si>
   <si>
     <t xml:space="preserve">40.5726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1581153869629</t>
+    <t xml:space="preserve">40.1581192016602</t>
   </si>
   <si>
     <t xml:space="preserve">39.6200866699219</t>
@@ -203,250 +203,250 @@
     <t xml:space="preserve">40.2904205322266</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8405952453613</t>
+    <t xml:space="preserve">39.8405914306641</t>
   </si>
   <si>
     <t xml:space="preserve">40.1316604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4668197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1007232666016</t>
+    <t xml:space="preserve">40.4668235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1007270812988</t>
   </si>
   <si>
     <t xml:space="preserve">44.7622337341309</t>
   </si>
   <si>
-    <t xml:space="preserve">45.291446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8647537231445</t>
+    <t xml:space="preserve">45.2914390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.86474609375</t>
   </si>
   <si>
     <t xml:space="preserve">45.3796463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6883506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8349609375</t>
+    <t xml:space="preserve">45.6883544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8349685668945</t>
   </si>
   <si>
     <t xml:space="preserve">45.9088478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4237403869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2032432556152</t>
+    <t xml:space="preserve">45.4237480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.203239440918</t>
   </si>
   <si>
     <t xml:space="preserve">44.8945388793945</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9386329650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3355445861816</t>
+    <t xml:space="preserve">44.9386405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3355484008789</t>
   </si>
   <si>
     <t xml:space="preserve">44.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">44.718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.982738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8504409790039</t>
+    <t xml:space="preserve">44.7181282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9827423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8504371643066</t>
   </si>
   <si>
     <t xml:space="preserve">45.776554107666</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6442451477051</t>
+    <t xml:space="preserve">45.6442489624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.8206481933594</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3057670593262</t>
+    <t xml:space="preserve">46.3057594299316</t>
   </si>
   <si>
     <t xml:space="preserve">46.1734580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.261661529541</t>
+    <t xml:space="preserve">46.2616577148438</t>
   </si>
   <si>
     <t xml:space="preserve">46.6144561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0852546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970550537109</t>
+    <t xml:space="preserve">46.085262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970626831055</t>
   </si>
   <si>
     <t xml:space="preserve">47.422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5119743347168</t>
+    <t xml:space="preserve">47.5119705200195</t>
   </si>
   <si>
     <t xml:space="preserve">47.1100883483887</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9138641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5836715698242</t>
+    <t xml:space="preserve">47.9138679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5836753845215</t>
   </si>
   <si>
     <t xml:space="preserve">49.5660667419434</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6553688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2358818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0748710632324</t>
+    <t xml:space="preserve">49.6553726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2358779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0748748779297</t>
   </si>
   <si>
     <t xml:space="preserve">49.9679489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1641807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7000274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9855575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7352485656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6188850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9314765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0924758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723556518555</t>
+    <t xml:space="preserve">49.1641731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000312805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9855613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566368103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7352447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6188926696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.931468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723480224609</t>
   </si>
   <si>
     <t xml:space="preserve">45.0113487243652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.038387298584</t>
+    <t xml:space="preserve">46.0383911132812</t>
   </si>
   <si>
     <t xml:space="preserve">48.8962478637695</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7446784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4144897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.137134552002</t>
+    <t xml:space="preserve">49.744686126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.414493560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1371307373047</t>
   </si>
   <si>
     <t xml:space="preserve">48.9409027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">49.833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0302124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931129455566</t>
+    <t xml:space="preserve">49.8339881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0302200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931091308594</t>
   </si>
   <si>
     <t xml:space="preserve">51.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2629165649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5755004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7987632751465</t>
+    <t xml:space="preserve">51.2629241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8610343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7987670898438</t>
   </si>
   <si>
     <t xml:space="preserve">50.9949951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7717208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2805290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0572509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1912231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6201553344727</t>
+    <t xml:space="preserve">50.7717247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2805328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.191219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6201515197754</t>
   </si>
   <si>
     <t xml:space="preserve">53.5849342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1654357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3711051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1207809448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0666961669922</t>
+    <t xml:space="preserve">53.0937347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1654396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3440551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3711013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1207885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0666885375977</t>
   </si>
   <si>
     <t xml:space="preserve">51.6648063659668</t>
@@ -455,64 +455,64 @@
     <t xml:space="preserve">50.6824150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3968811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6377601623535</t>
+    <t xml:space="preserve">51.3968772888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6377639770508</t>
   </si>
   <si>
     <t xml:space="preserve">52.2453079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7541122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.441535949707</t>
+    <t xml:space="preserve">51.7541198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4415397644043</t>
   </si>
   <si>
     <t xml:space="preserve">51.3522300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8880729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0843048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4591484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4767608642578</t>
+    <t xml:space="preserve">51.888069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0843124389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4591522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4767570495605</t>
   </si>
   <si>
     <t xml:space="preserve">49.2981414794922</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9773826599121</t>
+    <t xml:space="preserve">51.9773864746094</t>
   </si>
   <si>
     <t xml:space="preserve">52.5132331848145</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6918525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346176147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025428771973</t>
+    <t xml:space="preserve">52.6918487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025466918945</t>
   </si>
   <si>
     <t xml:space="preserve">52.2899627685547</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7094650268555</t>
+    <t xml:space="preserve">53.183048248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7094573974609</t>
   </si>
   <si>
     <t xml:space="preserve">51.1736106872559</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">50.7270698547363</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1465644836426</t>
+    <t xml:space="preserve">50.1465682983398</t>
   </si>
   <si>
     <t xml:space="preserve">50.905689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0126037597656</t>
+    <t xml:space="preserve">50.0126075744629</t>
   </si>
   <si>
     <t xml:space="preserve">48.7176361083984</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">45.3239212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7258148193359</t>
+    <t xml:space="preserve">45.7258110046387</t>
   </si>
   <si>
     <t xml:space="preserve">45.547191619873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3956184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6635437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7704658508301</t>
+    <t xml:space="preserve">46.395622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6635513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7704582214355</t>
   </si>
   <si>
     <t xml:space="preserve">46.1277008056641</t>
@@ -569,55 +569,55 @@
     <t xml:space="preserve">45.9937324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4578895568848</t>
+    <t xml:space="preserve">45.4578857421875</t>
   </si>
   <si>
     <t xml:space="preserve">45.6811561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3063125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2440605163574</t>
+    <t xml:space="preserve">46.5295829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3063087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2440490722656</t>
   </si>
   <si>
     <t xml:space="preserve">47.4673194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2088279724121</t>
+    <t xml:space="preserve">49.2088241577148</t>
   </si>
   <si>
     <t xml:space="preserve">50.3698387145996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1560020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5037994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8516006469727</t>
+    <t xml:space="preserve">52.1560096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5037956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8515930175781</t>
   </si>
   <si>
     <t xml:space="preserve">49.6107139587402</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8163795471191</t>
+    <t xml:space="preserve">50.8163757324219</t>
   </si>
   <si>
     <t xml:space="preserve">51.1289596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2006530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4685821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3616561889648</t>
+    <t xml:space="preserve">52.2006607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4685859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3616676330566</t>
   </si>
   <si>
     <t xml:space="preserve">53.4063186645508</t>
@@ -632,43 +632,43 @@
     <t xml:space="preserve">52.9151268005371</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2723503112793</t>
+    <t xml:space="preserve">53.2723579406738</t>
   </si>
   <si>
     <t xml:space="preserve">53.8528518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7905960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.505054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2641792297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1302185058594</t>
+    <t xml:space="preserve">54.7905921936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5943641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5050621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2641830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1302146911621</t>
   </si>
   <si>
     <t xml:space="preserve">55.6390266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8000259399414</t>
+    <t xml:space="preserve">56.8000335693359</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9786529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679512023926</t>
+    <t xml:space="preserve">56.9786415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">57.4251861572266</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">57.3358764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">58.050350189209</t>
+    <t xml:space="preserve">58.0503463745117</t>
   </si>
   <si>
     <t xml:space="preserve">58.8987693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0327377319336</t>
+    <t xml:space="preserve">59.0327415466309</t>
   </si>
   <si>
     <t xml:space="preserve">58.7648124694824</t>
@@ -692,49 +692,49 @@
     <t xml:space="preserve">58.0950012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1572608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3805313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5861892700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0151252746582</t>
+    <t xml:space="preserve">57.1572723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3805351257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5861854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0151176452637</t>
   </si>
   <si>
     <t xml:space="preserve">58.9434280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">59.3006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4088401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1585235595703</t>
+    <t xml:space="preserve">59.3006553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4088478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585273742676</t>
   </si>
   <si>
     <t xml:space="preserve">61.6226692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8906021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817863464355</t>
+    <t xml:space="preserve">61.8906059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817901611328</t>
   </si>
   <si>
     <t xml:space="preserve">62.7390251159668</t>
@@ -746,40 +746,40 @@
     <t xml:space="preserve">60.8635559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1937446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528617858887</t>
+    <t xml:space="preserve">60.1937408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528656005859</t>
   </si>
   <si>
     <t xml:space="preserve">61.6758041381836</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9468994140625</t>
+    <t xml:space="preserve">61.946907043457</t>
   </si>
   <si>
     <t xml:space="preserve">62.082447052002</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3083686828613</t>
+    <t xml:space="preserve">62.3083763122559</t>
   </si>
   <si>
     <t xml:space="preserve">62.5342903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4950714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4379539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7542572021484</t>
+    <t xml:space="preserve">61.4950790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.754264831543</t>
   </si>
   <si>
     <t xml:space="preserve">63.483154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5675582885742</t>
+    <t xml:space="preserve">64.5675659179688</t>
   </si>
   <si>
     <t xml:space="preserve">64.0705337524414</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">64.8386611938477</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5164260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0313186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5223922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8898086547852</t>
+    <t xml:space="preserve">65.5164108276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1668701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5223846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8897933959961</t>
   </si>
   <si>
     <t xml:space="preserve">64.432014465332</t>
@@ -809,115 +809,115 @@
     <t xml:space="preserve">64.2964553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">64.1609115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6971588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0884132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6425285339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8173065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5462112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6877250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365776062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4498748779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3987464904785</t>
+    <t xml:space="preserve">64.1609191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.697151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0884170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6425361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8173179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5462074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6877174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4498825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3987503051758</t>
   </si>
   <si>
     <t xml:space="preserve">63.2120513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5735168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927803039551</t>
+    <t xml:space="preserve">63.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927879333496</t>
   </si>
   <si>
     <t xml:space="preserve">63.1216812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2393646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7815475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0134506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5104522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3297271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9682540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6067810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.019401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2001342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7483139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7934646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6579360961914</t>
+    <t xml:space="preserve">66.2393569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7815628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0134353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5104675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.329719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.96826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6067886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0193786621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2001419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7482986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7934722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6579284667969</t>
   </si>
   <si>
     <t xml:space="preserve">64.4771881103516</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9801712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3024215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4260635375977</t>
+    <t xml:space="preserve">63.9801750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.302417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4260482788086</t>
   </si>
   <si>
     <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2845458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6008148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4652938842773</t>
+    <t xml:space="preserve">66.284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6008377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4652786254883</t>
   </si>
   <si>
     <t xml:space="preserve">66.871940612793</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">66.0586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3749008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978546142578</t>
+    <t xml:space="preserve">66.3749084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978469848633</t>
   </si>
   <si>
     <t xml:space="preserve">66.6912002563477</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">68.5437316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1370849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563369750977</t>
+    <t xml:space="preserve">68.1370697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563446044922</t>
   </si>
   <si>
     <t xml:space="preserve">68.182258605957</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">69.1311111450195</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3058853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962631225586</t>
+    <t xml:space="preserve">70.3058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962783813477</t>
   </si>
   <si>
     <t xml:space="preserve">71.9776840209961</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3903121948242</t>
+    <t xml:space="preserve">71.3903198242188</t>
   </si>
   <si>
     <t xml:space="preserve">71.5258560180664</t>
@@ -974,37 +974,37 @@
     <t xml:space="preserve">70.8481063842773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1643981933594</t>
+    <t xml:space="preserve">71.1643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">72.7910079956055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8932876586914</t>
+    <t xml:space="preserve">70.8932800292969</t>
   </si>
   <si>
     <t xml:space="preserve">70.2607116699219</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3510818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5318145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5769958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3451232910156</t>
+    <t xml:space="preserve">70.35107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5318069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5769882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3451156616211</t>
   </si>
   <si>
     <t xml:space="preserve">70.4414443969727</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">71.5710296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9836502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.712532043457</t>
+    <t xml:space="preserve">70.9836578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7125473022461</t>
   </si>
   <si>
     <t xml:space="preserve">65.1097717285156</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5616149902344</t>
+    <t xml:space="preserve">65.5616073608398</t>
   </si>
   <si>
     <t xml:space="preserve">67.4593200683594</t>
   </si>
   <si>
-    <t xml:space="preserve">67.82080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2666625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.034797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7636795043945</t>
+    <t xml:space="preserve">67.8207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2666702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0348052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.763671875</t>
   </si>
   <si>
     <t xml:space="preserve">68.9955596923828</t>
@@ -1046,58 +1046,58 @@
     <t xml:space="preserve">67.3237686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3629989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0407485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1763153076172</t>
+    <t xml:space="preserve">68.3629913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1763076782227</t>
   </si>
   <si>
     <t xml:space="preserve">69.9444274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1703414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8873291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6102600097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8992462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.49853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4081726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2785797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6400451660156</t>
+    <t xml:space="preserve">70.1703491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.887336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6102676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8992385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4081802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2785949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
     <t xml:space="preserve">69.4022216796875</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3391723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6162185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9325180053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0228729248047</t>
+    <t xml:space="preserve">72.3391647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6162261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9325103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0228805541992</t>
   </si>
   <si>
     <t xml:space="preserve">71.7065887451172</t>
@@ -1106,73 +1106,73 @@
     <t xml:space="preserve">71.4806747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4354858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6614074707031</t>
+    <t xml:space="preserve">71.4354934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614151000977</t>
   </si>
   <si>
     <t xml:space="preserve">71.2547454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8088760375977</t>
+    <t xml:space="preserve">69.8088684082031</t>
   </si>
   <si>
     <t xml:space="preserve">71.7517700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">68.0918884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9623031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8505783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6186981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0765037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9409523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9017219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7329025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.862491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113594055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7994422912598</t>
+    <t xml:space="preserve">68.0918960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572364807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6187133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0764999389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9409484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0039978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7329063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8113479614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.799430847168</t>
   </si>
   <si>
     <t xml:space="preserve">67.5496826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">66.7363891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453079223633</t>
+    <t xml:space="preserve">66.7363815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453231811523</t>
   </si>
   <si>
     <t xml:space="preserve">64.8838500976562</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">65.2904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4201049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2726364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1251602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8600158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540573120117</t>
+    <t xml:space="preserve">66.4200897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2726287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1251525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540649414062</t>
   </si>
   <si>
     <t xml:space="preserve">70.6221771240234</t>
@@ -1205,40 +1205,40 @@
     <t xml:space="preserve">71.1192016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0740280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6554489135742</t>
+    <t xml:space="preserve">71.0740203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6554412841797</t>
   </si>
   <si>
     <t xml:space="preserve">73.6946868896484</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4747085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4687652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1976547241211</t>
+    <t xml:space="preserve">72.4747161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.46875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1976470947266</t>
   </si>
   <si>
     <t xml:space="preserve">73.3783874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">74.688720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5591278076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1983642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6960983276367</t>
+    <t xml:space="preserve">74.6887130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5591201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6961135864258</t>
   </si>
   <si>
     <t xml:space="preserve">74.9289474487305</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">76.8466873168945</t>
   </si>
   <si>
-    <t xml:space="preserve">75.7964935302734</t>
+    <t xml:space="preserve">75.7964859008789</t>
   </si>
   <si>
     <t xml:space="preserve">74.1527099609375</t>
@@ -1256,31 +1256,31 @@
     <t xml:space="preserve">77.2576293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">75.4312057495117</t>
+    <t xml:space="preserve">75.4312133789062</t>
   </si>
   <si>
     <t xml:space="preserve">78.0795135498047</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9059448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5908508300781</t>
+    <t xml:space="preserve">79.9059371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5908432006836</t>
   </si>
   <si>
     <t xml:space="preserve">80.3625411987305</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7278289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2712326049805</t>
+    <t xml:space="preserve">80.7278213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2712173461914</t>
   </si>
   <si>
     <t xml:space="preserve">81.2300872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">83.102165222168</t>
+    <t xml:space="preserve">83.1021728515625</t>
   </si>
   <si>
     <t xml:space="preserve">84.3806762695312</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">85.2482223510742</t>
   </si>
   <si>
-    <t xml:space="preserve">84.928596496582</t>
+    <t xml:space="preserve">84.9286041259766</t>
   </si>
   <si>
     <t xml:space="preserve">84.2893524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">83.056510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127349853516</t>
+    <t xml:space="preserve">83.0565185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127502441406</t>
   </si>
   <si>
     <t xml:space="preserve">87.6682281494141</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8006896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3942642211914</t>
+    <t xml:space="preserve">86.8006820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3942565917969</t>
   </si>
   <si>
     <t xml:space="preserve">88.8554000854492</t>
@@ -1319,40 +1319,40 @@
     <t xml:space="preserve">87.9878540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2206954956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9421997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0380401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572860717773</t>
+    <t xml:space="preserve">89.2206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9422073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0380477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2573013305664</t>
   </si>
   <si>
     <t xml:space="preserve">87.4855880737305</t>
   </si>
   <si>
-    <t xml:space="preserve">87.576904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6772994995117</t>
+    <t xml:space="preserve">87.5769195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6772918701172</t>
   </si>
   <si>
     <t xml:space="preserve">89.1750259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4033279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1248397827148</t>
+    <t xml:space="preserve">89.4033355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1248321533203</t>
   </si>
   <si>
     <t xml:space="preserve">87.6225662231445</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">84.4719924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8327484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7689666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2255706787109</t>
+    <t xml:space="preserve">83.8327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.6685791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7689514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2255630493164</t>
   </si>
   <si>
     <t xml:space="preserve">80.4538726806641</t>
@@ -1397,76 +1397,76 @@
     <t xml:space="preserve">79.3580169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">80.4995269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6501007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2391586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7414093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.837272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6410293579102</t>
+    <t xml:space="preserve">80.4995193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6135101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6501083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2391662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8372802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3350143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6410446166992</t>
   </si>
   <si>
     <t xml:space="preserve">81.9150009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0017852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.275764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.53125</t>
+    <t xml:space="preserve">81.0017929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2757415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8282089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5312423706055</t>
   </si>
   <si>
     <t xml:space="preserve">88.7640762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2436981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199127197266</t>
+    <t xml:space="preserve">84.2436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199203491211</t>
   </si>
   <si>
     <t xml:space="preserve">84.8829345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">82.7368927001953</t>
+    <t xml:space="preserve">82.7368850708008</t>
   </si>
   <si>
     <t xml:space="preserve">83.3761367797852</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">81.4583969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2667007446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1572418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4266662597656</t>
+    <t xml:space="preserve">79.2666931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4266738891602</t>
   </si>
   <si>
     <t xml:space="preserve">73.3308258056641</t>
@@ -1493,28 +1493,28 @@
     <t xml:space="preserve">74.8376159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6002502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9198837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5179977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485580444336</t>
+    <t xml:space="preserve">72.6002578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5179901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485733032227</t>
   </si>
   <si>
     <t xml:space="preserve">76.4357376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8285675048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8330917358398</t>
+    <t xml:space="preserve">72.8285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8330841064453</t>
   </si>
   <si>
     <t xml:space="preserve">72.280632019043</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">75.06591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">76.5270538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9516143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.3398895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1161041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0568618774414</t>
+    <t xml:space="preserve">76.5270614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9516067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.3398818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1161193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0568542480469</t>
   </si>
   <si>
     <t xml:space="preserve">70.5455322265625</t>
@@ -1547,91 +1547,91 @@
     <t xml:space="preserve">70.6825103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0934600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9610137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1025161743164</t>
+    <t xml:space="preserve">71.0934524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9609985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1025238037109</t>
   </si>
   <si>
     <t xml:space="preserve">72.326286315918</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0477981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8651580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5821228027344</t>
+    <t xml:space="preserve">71.0477905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8651428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5821304321289</t>
   </si>
   <si>
     <t xml:space="preserve">68.4907913208008</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8561019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3217544555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8013534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3949508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.938362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187286376953</t>
+    <t xml:space="preserve">68.856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3217620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8013687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3949584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.938346862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187210083008</t>
   </si>
   <si>
     <t xml:space="preserve">67.5775985717773</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8470230102539</t>
+    <t xml:space="preserve">66.8470306396484</t>
   </si>
   <si>
     <t xml:space="preserve">65.5228652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0160675048828</t>
+    <t xml:space="preserve">64.0160522460938</t>
   </si>
   <si>
     <t xml:space="preserve">64.4270248413086</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7922897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.162109375</t>
+    <t xml:space="preserve">64.2900543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7923049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1621170043945</t>
   </si>
   <si>
     <t xml:space="preserve">64.944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2089462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6771697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3025894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0016784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4866027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2056579589844</t>
+    <t xml:space="preserve">66.2089309692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6771926879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3025970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0016555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4866104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2056732177734</t>
   </si>
   <si>
     <t xml:space="preserve">69.627082824707</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">70.7508544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1421432495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7675476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8913192749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5769882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0452270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2459411621094</t>
+    <t xml:space="preserve">70.1421508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7675628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8913269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0452194213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2459487915039</t>
   </si>
   <si>
     <t xml:space="preserve">75.10546875</t>
@@ -1664,49 +1664,49 @@
     <t xml:space="preserve">74.9650039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">74.5904083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0586471557617</t>
+    <t xml:space="preserve">74.5904159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0586547851562</t>
   </si>
   <si>
     <t xml:space="preserve">75.2927703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">74.6840667724609</t>
+    <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
     <t xml:space="preserve">76.557014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">76.1356048583984</t>
+    <t xml:space="preserve">76.1355895996094</t>
   </si>
   <si>
     <t xml:space="preserve">74.8713531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8847885131836</t>
+    <t xml:space="preserve">76.8847732543945</t>
   </si>
   <si>
     <t xml:space="preserve">76.9784317016602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.7109222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.6941986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2728042602539</t>
+    <t xml:space="preserve">78.7109146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6172637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6942138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2727966308594</t>
   </si>
   <si>
     <t xml:space="preserve">79.6005706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2259750366211</t>
+    <t xml:space="preserve">79.2259826660156</t>
   </si>
   <si>
     <t xml:space="preserve">79.4132766723633</t>
@@ -1715,196 +1715,196 @@
     <t xml:space="preserve">79.7878570556641</t>
   </si>
   <si>
-    <t xml:space="preserve">80.02197265625</t>
+    <t xml:space="preserve">80.0219802856445</t>
   </si>
   <si>
     <t xml:space="preserve">79.0386810302734</t>
   </si>
   <si>
-    <t xml:space="preserve">79.8815231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6775054931641</t>
+    <t xml:space="preserve">79.8815155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6775131225586</t>
   </si>
   <si>
     <t xml:space="preserve">80.3029174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">80.7711715698242</t>
+    <t xml:space="preserve">80.7711563110352</t>
   </si>
   <si>
     <t xml:space="preserve">82.0354080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7076263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798675537109</t>
+    <t xml:space="preserve">81.707649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798828125</t>
   </si>
   <si>
     <t xml:space="preserve">81.3330459594727</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2394027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2226943969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1457443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9751510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.26953125</t>
+    <t xml:space="preserve">81.2393951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2227096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.145751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9751663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2695236206055</t>
   </si>
   <si>
     <t xml:space="preserve">82.5036468505859</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0187072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2528305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6742401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9718856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.048828125</t>
+    <t xml:space="preserve">83.0187149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2528228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9250564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6742477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9718780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0488357543945</t>
   </si>
   <si>
     <t xml:space="preserve">84.0020065307617</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7980194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.7813034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8582534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8281478881836</t>
+    <t xml:space="preserve">84.7980117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7813186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.858268737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1558990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8281402587891</t>
   </si>
   <si>
     <t xml:space="preserve">85.6876602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2194213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1257705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7410354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2560958862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5671539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8481140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8147201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1893081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.282958984375</t>
+    <t xml:space="preserve">85.2194290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1257781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6408386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7410278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.256103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5671691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8147125244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1893005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2829437255859</t>
   </si>
   <si>
     <t xml:space="preserve">85.3130722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">88.169319152832</t>
+    <t xml:space="preserve">88.1693344116211</t>
   </si>
   <si>
     <t xml:space="preserve">89.4804153442383</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2596893310547</t>
+    <t xml:space="preserve">91.2596969604492</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.158088684082</t>
+    <t xml:space="preserve">91.6854858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1580963134766</t>
   </si>
   <si>
     <t xml:space="preserve">91.5437088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8347930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.598503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1806793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3299789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8025970458984</t>
+    <t xml:space="preserve">90.8348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5984954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1806716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3299865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8025894165039</t>
   </si>
   <si>
     <t xml:space="preserve">86.5340957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0786285400391</t>
+    <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
     <t xml:space="preserve">91.3546752929688</t>
   </si>
   <si>
-    <t xml:space="preserve">91.9690628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1033096313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5608520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8122177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0731964111328</t>
+    <t xml:space="preserve">91.9690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1033172607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5608444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4115371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8122100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">97.8293609619141</t>
@@ -1916,31 +1916,31 @@
     <t xml:space="preserve">101.326644897461</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6800537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.247184753418</t>
+    <t xml:space="preserve">98.680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2471771240234</t>
   </si>
   <si>
     <t xml:space="preserve">96.8841552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6403198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9389343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3170318603516</t>
+    <t xml:space="preserve">97.6403274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9389419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.317024230957</t>
   </si>
   <si>
     <t xml:space="preserve">96.5060653686523</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2622299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9786758422852</t>
+    <t xml:space="preserve">97.2622375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9786834716797</t>
   </si>
   <si>
     <t xml:space="preserve">99.5307540893555</t>
@@ -1949,70 +1949,70 @@
     <t xml:space="preserve">98.3019638061523</t>
   </si>
   <si>
-    <t xml:space="preserve">97.3567657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2074508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.167724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5458068847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2225036621094</t>
+    <t xml:space="preserve">97.3567581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2074432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1677169799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5457916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2225112915039</t>
   </si>
   <si>
     <t xml:space="preserve">95.7499008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8444290161133</t>
+    <t xml:space="preserve">95.8444137573242</t>
   </si>
   <si>
     <t xml:space="preserve">95.4663391113281</t>
   </si>
   <si>
-    <t xml:space="preserve">96.7896347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.082809448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1526565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.799240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.665000915527</t>
+    <t xml:space="preserve">96.7896270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.082801818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1526641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.664993286133</t>
   </si>
   <si>
     <t xml:space="preserve">100.097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9088287353516</t>
+    <t xml:space="preserve">99.908821105957</t>
   </si>
   <si>
     <t xml:space="preserve">98.396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">100.192390441895</t>
+    <t xml:space="preserve">100.192398071289</t>
   </si>
   <si>
     <t xml:space="preserve">102.36637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">102.17733001709</t>
+    <t xml:space="preserve">102.177337646484</t>
   </si>
   <si>
     <t xml:space="preserve">103.784194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">103.028030395508</t>
+    <t xml:space="preserve">103.028038024902</t>
   </si>
   <si>
     <t xml:space="preserve">100.003349304199</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">101.137603759766</t>
   </si>
   <si>
-    <t xml:space="preserve">101.704719543457</t>
+    <t xml:space="preserve">101.704727172852</t>
   </si>
   <si>
     <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">103.500633239746</t>
+    <t xml:space="preserve">103.500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">102.93350982666</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">96.6951065063477</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1129302978516</t>
+    <t xml:space="preserve">98.1129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">99.0581359863281</t>
@@ -2063,52 +2063,52 @@
     <t xml:space="preserve">99.6252670288086</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4266128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7101593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8594818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0957870483398</t>
+    <t xml:space="preserve">94.4265975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7101669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8594741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0957794189453</t>
   </si>
   <si>
     <t xml:space="preserve">94.2848281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6156387329102</t>
+    <t xml:space="preserve">94.6156463623047</t>
   </si>
   <si>
     <t xml:space="preserve">94.521125793457</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6382293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3471450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3074111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2998809814453</t>
+    <t xml:space="preserve">91.6382217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3471298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3074035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2998733520508</t>
   </si>
   <si>
     <t xml:space="preserve">91.7327575683594</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0163040161133</t>
+    <t xml:space="preserve">92.0163116455078</t>
   </si>
   <si>
     <t xml:space="preserve">93.1505661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3718109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8046951293945</t>
+    <t xml:space="preserve">95.3718185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8046875</t>
   </si>
   <si>
     <t xml:space="preserve">98.8691024780273</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">100.75951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">103.122543334961</t>
+    <t xml:space="preserve">103.122550964355</t>
   </si>
   <si>
     <t xml:space="preserve">104.634887695312</t>
@@ -2132,22 +2132,22 @@
     <t xml:space="preserve">108.226692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">107.659561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.574661254883</t>
+    <t xml:space="preserve">107.659553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.077377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.574653625488</t>
   </si>
   <si>
     <t xml:space="preserve">113.803428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">113.236312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519874572754</t>
+    <t xml:space="preserve">113.236305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519866943359</t>
   </si>
   <si>
     <t xml:space="preserve">114.654121398926</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977416992188</t>
+    <t xml:space="preserve">115.977424621582</t>
   </si>
   <si>
     <t xml:space="preserve">117.206192016602</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">115.315773010254</t>
   </si>
   <si>
-    <t xml:space="preserve">114.370559692383</t>
+    <t xml:space="preserve">114.370567321777</t>
   </si>
   <si>
     <t xml:space="preserve">113.425346374512</t>
   </si>
   <si>
-    <t xml:space="preserve">109.644500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.251365661621</t>
+    <t xml:space="preserve">109.644493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.251358032227</t>
   </si>
   <si>
     <t xml:space="preserve">110.589714050293</t>
@@ -2192,46 +2192,46 @@
     <t xml:space="preserve">111.156837463379</t>
   </si>
   <si>
-    <t xml:space="preserve">111.723960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.062316894531</t>
+    <t xml:space="preserve">111.723968505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.062324523926</t>
   </si>
   <si>
     <t xml:space="preserve">110.117111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">109.833534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.510261535645</t>
+    <t xml:space="preserve">109.833549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.51025390625</t>
   </si>
   <si>
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952751159668</t>
+    <t xml:space="preserve">112.29109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952743530273</t>
   </si>
   <si>
     <t xml:space="preserve">110.87328338623</t>
   </si>
   <si>
-    <t xml:space="preserve">109.455459594727</t>
+    <t xml:space="preserve">109.455474853516</t>
   </si>
   <si>
     <t xml:space="preserve">107.470512390137</t>
   </si>
   <si>
-    <t xml:space="preserve">110.495185852051</t>
+    <t xml:space="preserve">110.495193481445</t>
   </si>
   <si>
     <t xml:space="preserve">108.037651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">107.848602294922</t>
+    <t xml:space="preserve">107.848609924316</t>
   </si>
   <si>
     <t xml:space="preserve">108.793815612793</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">109.171905517578</t>
   </si>
   <si>
-    <t xml:space="preserve">109.266418457031</t>
+    <t xml:space="preserve">109.266426086426</t>
   </si>
   <si>
     <t xml:space="preserve">106.997909545898</t>
@@ -2255,28 +2255,28 @@
     <t xml:space="preserve">105.769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">107.754089355469</t>
+    <t xml:space="preserve">107.754081726074</t>
   </si>
   <si>
     <t xml:space="preserve">108.415725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">108.321212768555</t>
+    <t xml:space="preserve">108.32120513916</t>
   </si>
   <si>
     <t xml:space="preserve">110.211631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">114.276031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.465072631836</t>
+    <t xml:space="preserve">114.276039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
     <t xml:space="preserve">109.928070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">104.540367126465</t>
+    <t xml:space="preserve">104.54035949707</t>
   </si>
   <si>
     <t xml:space="preserve">98.7745742797852</t>
@@ -2291,22 +2291,22 @@
     <t xml:space="preserve">101.893768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8143005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.132171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.485572814941</t>
+    <t xml:space="preserve">99.8143081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.13215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.485565185547</t>
   </si>
   <si>
     <t xml:space="preserve">110.400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">108.888343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.525299072266</t>
+    <t xml:space="preserve">108.888328552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.52530670166</t>
   </si>
   <si>
     <t xml:space="preserve">104.445838928223</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">102.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">114.086990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.629455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.056884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.310325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.091178894043</t>
+    <t xml:space="preserve">114.087005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.629447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.05687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.310333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.091156005859</t>
   </si>
   <si>
     <t xml:space="preserve">132.329574584961</t>
@@ -2336,31 +2336,31 @@
     <t xml:space="preserve">141.592651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">141.876235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.583038330078</t>
+    <t xml:space="preserve">141.876205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.583023071289</t>
   </si>
   <si>
     <t xml:space="preserve">145.089920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">144.239242553711</t>
+    <t xml:space="preserve">144.239227294922</t>
   </si>
   <si>
     <t xml:space="preserve">155.959854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">150.38313293457</t>
+    <t xml:space="preserve">150.383102416992</t>
   </si>
   <si>
     <t xml:space="preserve">153.691345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">157.755752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.94482421875</t>
+    <t xml:space="preserve">157.755767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.944808959961</t>
   </si>
   <si>
     <t xml:space="preserve">153.313262939453</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">146.791320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">146.885848999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.507751464844</t>
+    <t xml:space="preserve">146.885818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.507736206055</t>
   </si>
   <si>
     <t xml:space="preserve">144.52278137207</t>
@@ -2381,61 +2381,61 @@
     <t xml:space="preserve">146.318695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">147.641998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.596817016602</t>
+    <t xml:space="preserve">147.641983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.59684753418</t>
   </si>
   <si>
     <t xml:space="preserve">151.706405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">163.048950195312</t>
+    <t xml:space="preserve">163.048934936523</t>
   </si>
   <si>
     <t xml:space="preserve">167.302398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">174.107894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.675048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.381866455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.440826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.688858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.927230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.206619262695</t>
+    <t xml:space="preserve">174.10791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.675018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.381851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.833969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.440841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.688827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.927215576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.206634521484</t>
   </si>
   <si>
     <t xml:space="preserve">163.521545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.172302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.555847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.098281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.994155883789</t>
+    <t xml:space="preserve">171.839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.172332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.55583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.09831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.994140625</t>
   </si>
   <si>
     <t xml:space="preserve">164.655792236328</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">150.855728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">152.651596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.014663696289</t>
+    <t xml:space="preserve">152.651611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.014633178711</t>
   </si>
   <si>
     <t xml:space="preserve">158.6064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">157.850280761719</t>
+    <t xml:space="preserve">157.85026550293</t>
   </si>
   <si>
     <t xml:space="preserve">161.510162353516</t>
   </si>
   <si>
-    <t xml:space="preserve">162.365707397461</t>
+    <t xml:space="preserve">162.36572265625</t>
   </si>
   <si>
     <t xml:space="preserve">161.890411376953</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">161.129898071289</t>
   </si>
   <si>
-    <t xml:space="preserve">159.133590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.270645141602</t>
+    <t xml:space="preserve">159.133605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.270660400391</t>
   </si>
   <si>
     <t xml:space="preserve">167.118835449219</t>
@@ -2483,25 +2483,25 @@
     <t xml:space="preserve">164.457061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">162.936096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.320022583008</t>
+    <t xml:space="preserve">162.936080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.320053100586</t>
   </si>
   <si>
     <t xml:space="preserve">161.985473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">162.55583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.841033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.650894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.073135375977</t>
+    <t xml:space="preserve">162.555816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.841018676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
     <t xml:space="preserve">169.685470581055</t>
@@ -2510,22 +2510,22 @@
     <t xml:space="preserve">170.350921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">163.031143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.362014770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.122512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647186279297</t>
+    <t xml:space="preserve">163.031127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.361999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.122497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647201538086</t>
   </si>
   <si>
     <t xml:space="preserve">169.305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">169.400283813477</t>
+    <t xml:space="preserve">169.400299072266</t>
   </si>
   <si>
     <t xml:space="preserve">171.96696472168</t>
@@ -2534,91 +2534,91 @@
     <t xml:space="preserve">169.495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.358322143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.939804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.665710449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.17561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.742248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.22868347168</t>
+    <t xml:space="preserve">166.358291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.939788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.66569519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.175598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.742263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.228668212891</t>
   </si>
   <si>
     <t xml:space="preserve">157.802749633789</t>
   </si>
   <si>
-    <t xml:space="preserve">152.669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.81755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.775573730469</t>
+    <t xml:space="preserve">152.669403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.817565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.77555847168</t>
   </si>
   <si>
     <t xml:space="preserve">150.768173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">145.25456237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.722503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.289138793945</t>
+    <t xml:space="preserve">145.254577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.72248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.289169311523</t>
   </si>
   <si>
     <t xml:space="preserve">151.623733520508</t>
   </si>
   <si>
-    <t xml:space="preserve">148.391616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.760772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.243499755859</t>
+    <t xml:space="preserve">148.391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.7607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.243469238281</t>
   </si>
   <si>
     <t xml:space="preserve">154.190399169922</t>
   </si>
   <si>
-    <t xml:space="preserve">154.855819702148</t>
+    <t xml:space="preserve">154.855834960938</t>
   </si>
   <si>
     <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">155.426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.806442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.418792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.634841918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.600250244141</t>
+    <t xml:space="preserve">155.426193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.806457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.418807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.634826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.600234985352</t>
   </si>
   <si>
     <t xml:space="preserve">144.018768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">144.589141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.543472290039</t>
+    <t xml:space="preserve">144.589157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.54345703125</t>
   </si>
   <si>
     <t xml:space="preserve">135.55827331543</t>
@@ -2627,22 +2627,22 @@
     <t xml:space="preserve">134.797760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">137.364440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.17431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.779266357422</t>
+    <t xml:space="preserve">137.36442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.779251098633</t>
   </si>
   <si>
     <t xml:space="preserve">143.258270263672</t>
   </si>
   <si>
-    <t xml:space="preserve">147.060760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.726196289062</t>
+    <t xml:space="preserve">147.060745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.726181030273</t>
   </si>
   <si>
     <t xml:space="preserve">149.247161865234</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">152.95458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">150.387908935547</t>
+    <t xml:space="preserve">150.387924194336</t>
   </si>
   <si>
     <t xml:space="preserve">161.03483581543</t>
@@ -2660,31 +2660,31 @@
     <t xml:space="preserve">160.654602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">162.080520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.795318603516</t>
+    <t xml:space="preserve">162.080535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.795333862305</t>
   </si>
   <si>
     <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913879394531</t>
+    <t xml:space="preserve">168.069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.91389465332</t>
   </si>
   <si>
     <t xml:space="preserve">175.294128417969</t>
   </si>
   <si>
-    <t xml:space="preserve">177.670654296875</t>
+    <t xml:space="preserve">177.670669555664</t>
   </si>
   <si>
     <t xml:space="preserve">173.487945556641</t>
   </si>
   <si>
-    <t xml:space="preserve">178.716369628906</t>
+    <t xml:space="preserve">178.716339111328</t>
   </si>
   <si>
     <t xml:space="preserve">180.712677001953</t>
@@ -2696,19 +2696,19 @@
     <t xml:space="preserve">181.853393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">179.666976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.039825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.663299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.275604248047</t>
+    <t xml:space="preserve">179.666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.039840698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.663284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.275634765625</t>
   </si>
   <si>
     <t xml:space="preserve">183.089218139648</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">181.568222045898</t>
   </si>
   <si>
-    <t xml:space="preserve">179.286758422852</t>
+    <t xml:space="preserve">179.286727905273</t>
   </si>
   <si>
     <t xml:space="preserve">178.050933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">179.191650390625</t>
+    <t xml:space="preserve">179.191665649414</t>
   </si>
   <si>
     <t xml:space="preserve">176.529922485352</t>
@@ -2735,22 +2735,22 @@
     <t xml:space="preserve">184.610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">189.838623046875</t>
+    <t xml:space="preserve">189.838592529297</t>
   </si>
   <si>
     <t xml:space="preserve">191.264526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">159.703964233398</t>
+    <t xml:space="preserve">159.703979492188</t>
   </si>
   <si>
     <t xml:space="preserve">163.88671875</t>
   </si>
   <si>
-    <t xml:space="preserve">165.217559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.932403564453</t>
+    <t xml:space="preserve">165.21760559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.932373046875</t>
   </si>
   <si>
     <t xml:space="preserve">164.076843261719</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">156.947189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">160.8447265625</t>
+    <t xml:space="preserve">160.844711303711</t>
   </si>
   <si>
     <t xml:space="preserve">164.266967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">167.879287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.696594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.605224609375</t>
+    <t xml:space="preserve">167.879318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.696578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.605209350586</t>
   </si>
   <si>
     <t xml:space="preserve">160.084228515625</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">162.745956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">160.179306030273</t>
+    <t xml:space="preserve">160.179290771484</t>
   </si>
   <si>
     <t xml:space="preserve">159.32373046875</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">158.468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">158.848449707031</t>
+    <t xml:space="preserve">158.848434448242</t>
   </si>
   <si>
     <t xml:space="preserve">163.221267700195</t>
@@ -2798,25 +2798,25 @@
     <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">159.608901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.700271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.224990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.859527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.52864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.616317749023</t>
+    <t xml:space="preserve">159.608917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.700302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.224975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.810134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.859497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.528656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.616333007812</t>
   </si>
   <si>
     <t xml:space="preserve">154.475570678711</t>
@@ -2825,28 +2825,28 @@
     <t xml:space="preserve">154.570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">157.992874145508</t>
+    <t xml:space="preserve">157.992858886719</t>
   </si>
   <si>
     <t xml:space="preserve">170.826202392578</t>
   </si>
   <si>
-    <t xml:space="preserve">169.970657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.001541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.92497253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.681793212891</t>
+    <t xml:space="preserve">169.970672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.001556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.924957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.68180847168</t>
   </si>
   <si>
     <t xml:space="preserve">171.111419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">170.541046142578</t>
+    <t xml:space="preserve">170.541030883789</t>
   </si>
   <si>
     <t xml:space="preserve">167.784255981445</t>
@@ -2855,49 +2855,49 @@
     <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255859375</t>
+    <t xml:space="preserve">170.255844116211</t>
   </si>
   <si>
     <t xml:space="preserve">173.868194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">173.202774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.389221191406</t>
+    <t xml:space="preserve">173.202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.389175415039</t>
   </si>
   <si>
     <t xml:space="preserve">176.434875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">176.149703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.195358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.438583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.186676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.813858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.99658203125</t>
+    <t xml:space="preserve">176.149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.195373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.438568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.18669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.813842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.996566772461</t>
   </si>
   <si>
     <t xml:space="preserve">154.380508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">155.901519775391</t>
+    <t xml:space="preserve">155.901504516602</t>
   </si>
   <si>
     <t xml:space="preserve">157.137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">154.000274658203</t>
+    <t xml:space="preserve">154.000259399414</t>
   </si>
   <si>
     <t xml:space="preserve">150.197784423828</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">132.706405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">135.082962036133</t>
+    <t xml:space="preserve">135.082977294922</t>
   </si>
   <si>
     <t xml:space="preserve">138.695297241211</t>
@@ -2921,28 +2921,28 @@
     <t xml:space="preserve">134.987884521484</t>
   </si>
   <si>
-    <t xml:space="preserve">133.181732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.033569335938</t>
+    <t xml:space="preserve">133.181716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.033584594727</t>
   </si>
   <si>
     <t xml:space="preserve">133.276763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">134.037246704102</t>
+    <t xml:space="preserve">134.037261962891</t>
   </si>
   <si>
     <t xml:space="preserve">133.086654663086</t>
   </si>
   <si>
-    <t xml:space="preserve">135.273101806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.136047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.519958496094</t>
+    <t xml:space="preserve">135.273071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.136032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.519973754883</t>
   </si>
   <si>
     <t xml:space="preserve">130.90022277832</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">130.044677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">132.848983764648</t>
+    <t xml:space="preserve">132.848999023438</t>
   </si>
   <si>
     <t xml:space="preserve">135.463195800781</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">133.229248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">145.492248535156</t>
+    <t xml:space="preserve">145.492218017578</t>
   </si>
   <si>
     <t xml:space="preserve">143.59098815918</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">148.201477050781</t>
+    <t xml:space="preserve">148.20149230957</t>
   </si>
   <si>
     <t xml:space="preserve">148.058883666992</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">146.300247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.016937255859</t>
+    <t xml:space="preserve">145.01692199707</t>
   </si>
   <si>
     <t xml:space="preserve">144.874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">136.984176635742</t>
+    <t xml:space="preserve">136.984191894531</t>
   </si>
   <si>
     <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">133.324295043945</t>
+    <t xml:space="preserve">133.324310302734</t>
   </si>
   <si>
     <t xml:space="preserve">134.274932861328</t>
@@ -3008,37 +3008,37 @@
     <t xml:space="preserve">133.847152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">135.605773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.423065185547</t>
+    <t xml:space="preserve">135.605804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.423080444336</t>
   </si>
   <si>
     <t xml:space="preserve">128.333557128906</t>
   </si>
   <si>
-    <t xml:space="preserve">131.470611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.185424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.655151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.031707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.983856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.744552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.84538269043</t>
+    <t xml:space="preserve">131.470581054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.185409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.655166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.983871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.744537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.845397949219</t>
   </si>
   <si>
     <t xml:space="preserve">137.797515869141</t>
@@ -3053,19 +3053,19 @@
     <t xml:space="preserve">135.978729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">133.059097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.963363647461</t>
+    <t xml:space="preserve">133.05908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.963348388672</t>
   </si>
   <si>
     <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">136.218063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.510330200195</t>
+    <t xml:space="preserve">136.218048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.510345458984</t>
   </si>
   <si>
     <t xml:space="preserve">138.659057617188</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">143.2060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.306884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.01969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.269271850586</t>
+    <t xml:space="preserve">144.306900024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.019714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.269287109375</t>
   </si>
   <si>
     <t xml:space="preserve">145.790649414062</t>
@@ -3092,22 +3092,22 @@
     <t xml:space="preserve">147.322250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">146.843612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.226547241211</t>
+    <t xml:space="preserve">146.843627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.226531982422</t>
   </si>
   <si>
     <t xml:space="preserve">143.397491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">147.99235534668</t>
+    <t xml:space="preserve">147.992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">149.428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">150.289749145508</t>
+    <t xml:space="preserve">150.289764404297</t>
   </si>
   <si>
     <t xml:space="preserve">153.065811157227</t>
@@ -3122,25 +3122,25 @@
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.879501342773</t>
+    <t xml:space="preserve">149.906875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.879470825195</t>
   </si>
   <si>
     <t xml:space="preserve">156.320495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">152.395721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.783737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.123931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.458953857422</t>
+    <t xml:space="preserve">152.395736694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.783752441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.123916625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.458969116211</t>
   </si>
   <si>
     <t xml:space="preserve">155.028198242188</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">162.207641601562</t>
   </si>
   <si>
-    <t xml:space="preserve">163.643508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.983703613281</t>
+    <t xml:space="preserve">163.643539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.983688354492</t>
   </si>
   <si>
     <t xml:space="preserve">161.729019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">160.91535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.35124206543</t>
+    <t xml:space="preserve">160.915344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.351226806641</t>
   </si>
   <si>
     <t xml:space="preserve">165.07942199707</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">164.600799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">168.142654418945</t>
+    <t xml:space="preserve">168.142639160156</t>
   </si>
   <si>
     <t xml:space="preserve">168.860595703125</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">168.669143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">168.334106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.052047729492</t>
+    <t xml:space="preserve">168.334121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">179.534057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">178.05029296875</t>
+    <t xml:space="preserve">178.050308227539</t>
   </si>
   <si>
     <t xml:space="preserve">177.475921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">177.810989379883</t>
+    <t xml:space="preserve">177.810974121094</t>
   </si>
   <si>
     <t xml:space="preserve">181.352844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">182.740859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990417480469</t>
+    <t xml:space="preserve">182.740875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">190.016036987305</t>
@@ -3254,34 +3254,34 @@
     <t xml:space="preserve">192.409194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">193.270736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.568130493164</t>
+    <t xml:space="preserve">193.270721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.568161010742</t>
   </si>
   <si>
     <t xml:space="preserve">191.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">196.908309936523</t>
+    <t xml:space="preserve">196.908325195312</t>
   </si>
   <si>
     <t xml:space="preserve">196.812606811523</t>
   </si>
   <si>
-    <t xml:space="preserve">197.386947631836</t>
+    <t xml:space="preserve">197.386932373047</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
   </si>
   <si>
-    <t xml:space="preserve">193.175003051758</t>
+    <t xml:space="preserve">193.175018310547</t>
   </si>
   <si>
     <t xml:space="preserve">190.351089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">192.026290893555</t>
+    <t xml:space="preserve">192.026306152344</t>
   </si>
   <si>
     <t xml:space="preserve">193.940811157227</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">195.855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">194.515167236328</t>
+    <t xml:space="preserve">194.515151977539</t>
   </si>
   <si>
     <t xml:space="preserve">187.479309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">180.539184570312</t>
+    <t xml:space="preserve">180.539169311523</t>
   </si>
   <si>
     <t xml:space="preserve">174.987060546875</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">167.664016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">164.505065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.462356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.781997680664</t>
+    <t xml:space="preserve">164.505081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.462341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.782012939453</t>
   </si>
   <si>
     <t xml:space="preserve">163.404220581055</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">162.111923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">166.51530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.870834350586</t>
+    <t xml:space="preserve">166.515319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.870849609375</t>
   </si>
   <si>
     <t xml:space="preserve">171.25373840332</t>
@@ -3341,22 +3341,22 @@
     <t xml:space="preserve">172.402465820312</t>
   </si>
   <si>
-    <t xml:space="preserve">171.684509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.742630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.715240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.44856262207</t>
+    <t xml:space="preserve">171.684539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.742614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.448577880859</t>
   </si>
   <si>
     <t xml:space="preserve">180.826354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">182.884460449219</t>
+    <t xml:space="preserve">182.88444519043</t>
   </si>
   <si>
     <t xml:space="preserve">182.83659362793</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096389770508</t>
+    <t xml:space="preserve">187.096420288086</t>
   </si>
   <si>
     <t xml:space="preserve">187.000686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">188.723724365234</t>
+    <t xml:space="preserve">188.723739624023</t>
   </si>
   <si>
     <t xml:space="preserve">189.202362060547</t>
@@ -3401,19 +3401,19 @@
     <t xml:space="preserve">180.874206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">183.506683349609</t>
+    <t xml:space="preserve">183.50666809082</t>
   </si>
   <si>
     <t xml:space="preserve">175.896469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">176.61442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.800720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.636657714844</t>
+    <t xml:space="preserve">176.614395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.800735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.636672973633</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">179.294738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">177.188781738281</t>
+    <t xml:space="preserve">177.188766479492</t>
   </si>
   <si>
     <t xml:space="preserve">180.682754516602</t>
@@ -3431,10 +3431,10 @@
     <t xml:space="preserve">175.082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">170.296478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.147766113281</t>
+    <t xml:space="preserve">170.296493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.14778137207</t>
   </si>
   <si>
     <t xml:space="preserve">164.935836791992</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">172.306747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">172.928955078125</t>
+    <t xml:space="preserve">172.928970336914</t>
   </si>
   <si>
     <t xml:space="preserve">168.764877319336</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">172.785369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">170.53581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.060684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.688049316406</t>
+    <t xml:space="preserve">170.535797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.060699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.688034057617</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">159.240158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">157.947830200195</t>
+    <t xml:space="preserve">157.947845458984</t>
   </si>
   <si>
     <t xml:space="preserve">160.293121337891</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">156.22477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">152.156433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.640167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.183792114258</t>
+    <t xml:space="preserve">152.15641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.640182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.183807373047</t>
   </si>
   <si>
     <t xml:space="preserve">141.770156860352</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">147.609436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">141.387237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.85563659668</t>
+    <t xml:space="preserve">141.387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.855651855469</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">137.223175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.946243286133</t>
+    <t xml:space="preserve">138.946228027344</t>
   </si>
   <si>
     <t xml:space="preserve">140.717178344727</t>
@@ -3527,34 +3527,34 @@
     <t xml:space="preserve">128.94287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">126.884773254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.325759887695</t>
+    <t xml:space="preserve">126.884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.325775146484</t>
   </si>
   <si>
     <t xml:space="preserve">131.048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">131.144592285156</t>
+    <t xml:space="preserve">131.144561767578</t>
   </si>
   <si>
     <t xml:space="preserve">132.006103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">127.698432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.41813659668</t>
+    <t xml:space="preserve">127.698440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.418144226074</t>
   </si>
   <si>
     <t xml:space="preserve">122.289916992188</t>
@@ -3572,10 +3572,10 @@
     <t xml:space="preserve">117.072853088379</t>
   </si>
   <si>
-    <t xml:space="preserve">116.546371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.589096069336</t>
+    <t xml:space="preserve">116.546363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.58910369873</t>
   </si>
   <si>
     <t xml:space="preserve">112.286560058594</t>
@@ -3584,109 +3584,109 @@
     <t xml:space="preserve">112.430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">116.211318969727</t>
+    <t xml:space="preserve">116.211326599121</t>
   </si>
   <si>
     <t xml:space="preserve">120.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.103591918945</t>
+    <t xml:space="preserve">123.10359954834</t>
   </si>
   <si>
     <t xml:space="preserve">122.864273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">127.937728881836</t>
+    <t xml:space="preserve">127.93775177002</t>
   </si>
   <si>
     <t xml:space="preserve">127.124084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">123.77367401123</t>
+    <t xml:space="preserve">123.773666381836</t>
   </si>
   <si>
     <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">120.088218688965</t>
+    <t xml:space="preserve">120.08821105957</t>
   </si>
   <si>
     <t xml:space="preserve">122.242050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">117.503616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.806159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541236877441</t>
+    <t xml:space="preserve">117.503623962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.806167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541229248047</t>
   </si>
   <si>
     <t xml:space="preserve">117.599349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">121.859153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.718933105469</t>
+    <t xml:space="preserve">121.859161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.71891784668</t>
   </si>
   <si>
     <t xml:space="preserve">132.293273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">126.693313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.597602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204452514648</t>
+    <t xml:space="preserve">126.693305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.59757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204444885254</t>
   </si>
   <si>
     <t xml:space="preserve">125.448883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.824905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.739410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.83512878418</t>
+    <t xml:space="preserve">133.824890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.73942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.835159301758</t>
   </si>
   <si>
     <t xml:space="preserve">139.329147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">139.616333007812</t>
+    <t xml:space="preserve">139.616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">142.105194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">139.041976928711</t>
+    <t xml:space="preserve">139.041946411133</t>
   </si>
   <si>
     <t xml:space="preserve">136.170181274414</t>
   </si>
   <si>
-    <t xml:space="preserve">135.260787963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.628326416016</t>
+    <t xml:space="preserve">135.260803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.628341674805</t>
   </si>
   <si>
     <t xml:space="preserve">129.038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">129.086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.559982299805</t>
+    <t xml:space="preserve">129.086486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.559967041016</t>
   </si>
   <si>
     <t xml:space="preserve">128.416381835938</t>
@@ -3695,37 +3695,37 @@
     <t xml:space="preserve">126.454010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">124.539482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.997627258301</t>
+    <t xml:space="preserve">124.539489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.997611999512</t>
   </si>
   <si>
     <t xml:space="preserve">118.7001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">115.254058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.652336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.70532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.173698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.64720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392532348633</t>
+    <t xml:space="preserve">115.254066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.652328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.705322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392524719238</t>
   </si>
   <si>
     <t xml:space="preserve">114.823295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">115.493385314941</t>
+    <t xml:space="preserve">115.493370056152</t>
   </si>
   <si>
     <t xml:space="preserve">109.271186828613</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">109.654090881348</t>
   </si>
   <si>
-    <t xml:space="preserve">107.165222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.009628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.871154785156</t>
+    <t xml:space="preserve">107.165214538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.009620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.871147155762</t>
   </si>
   <si>
     <t xml:space="preserve">113.435272216797</t>
@@ -3761,10 +3761,10 @@
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.932800292969</t>
+    <t xml:space="preserve">111.884498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.932792663574</t>
   </si>
   <si>
     <t xml:space="preserve">113.381454467773</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">119.803825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">116.278755187988</t>
+    <t xml:space="preserve">116.278762817383</t>
   </si>
   <si>
     <t xml:space="preserve">118.258583068848</t>
@@ -3794,31 +3794,31 @@
     <t xml:space="preserve">117.727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">118.74146270752</t>
+    <t xml:space="preserve">118.741470336914</t>
   </si>
   <si>
     <t xml:space="preserve">115.071548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">111.787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.918731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.683410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.657127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.904670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.685234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.801986694336</t>
+    <t xml:space="preserve">111.787933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.918724060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.683403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.657119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.904678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.685241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.80199432373</t>
   </si>
   <si>
     <t xml:space="preserve">113.912620544434</t>
@@ -3827,46 +3827,46 @@
     <t xml:space="preserve">113.526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">120.190124511719</t>
+    <t xml:space="preserve">120.190132141113</t>
   </si>
   <si>
     <t xml:space="preserve">123.377166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">122.797714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.866172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.914451599121</t>
+    <t xml:space="preserve">122.797706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.866180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.914459228516</t>
   </si>
   <si>
     <t xml:space="preserve">122.025093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">126.564224243164</t>
+    <t xml:space="preserve">126.56421661377</t>
   </si>
   <si>
     <t xml:space="preserve">127.578285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">129.799530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.668731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.151641845703</t>
+    <t xml:space="preserve">129.799545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.668746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.151626586914</t>
   </si>
   <si>
     <t xml:space="preserve">131.537933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">125.598457336426</t>
+    <t xml:space="preserve">125.598449707031</t>
   </si>
   <si>
     <t xml:space="preserve">127.964584350586</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">124.970687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">127.916290283203</t>
+    <t xml:space="preserve">127.916297912598</t>
   </si>
   <si>
     <t xml:space="preserve">127.674842834473</t>
@@ -3890,34 +3890,34 @@
     <t xml:space="preserve">135.497589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">136.077056884766</t>
+    <t xml:space="preserve">136.077041625977</t>
   </si>
   <si>
     <t xml:space="preserve">132.841720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">128.785491943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.936454772949</t>
+    <t xml:space="preserve">128.785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">130.234146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">130.958480834961</t>
+    <t xml:space="preserve">130.958465576172</t>
   </si>
   <si>
     <t xml:space="preserve">130.861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">128.640609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.137573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.787322998047</t>
+    <t xml:space="preserve">128.640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.137557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.787338256836</t>
   </si>
   <si>
     <t xml:space="preserve">132.213958740234</t>
@@ -3941,34 +3941,34 @@
     <t xml:space="preserve">130.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">132.020812988281</t>
+    <t xml:space="preserve">132.02082824707</t>
   </si>
   <si>
     <t xml:space="preserve">131.489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">132.310562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.515922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.86799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.467636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.888191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.171798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.061157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.930358886719</t>
+    <t xml:space="preserve">132.310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.515914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.868011474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.888168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.171783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.061172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.93034362793</t>
   </si>
   <si>
     <t xml:space="preserve">126.226188659668</t>
@@ -3983,16 +3983,16 @@
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.115562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473747253418</t>
+    <t xml:space="preserve">125.11555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473754882812</t>
   </si>
   <si>
     <t xml:space="preserve">121.397338867188</t>
   </si>
   <si>
-    <t xml:space="preserve">120.721305847168</t>
+    <t xml:space="preserve">120.721298217773</t>
   </si>
   <si>
     <t xml:space="preserve">123.135734558105</t>
@@ -4004,34 +4004,34 @@
     <t xml:space="preserve">112.463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">111.64306640625</t>
+    <t xml:space="preserve">111.643051147461</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.870452880859</t>
+    <t xml:space="preserve">107.779983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.870445251465</t>
   </si>
   <si>
     <t xml:space="preserve">110.097831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">113.816047668457</t>
+    <t xml:space="preserve">113.816040039062</t>
   </si>
   <si>
     <t xml:space="preserve">111.305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">108.504302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.132057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.974967956543</t>
+    <t xml:space="preserve">108.50431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.132064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.974975585938</t>
   </si>
   <si>
     <t xml:space="preserve">123.763473510742</t>
@@ -4040,34 +4040,34 @@
     <t xml:space="preserve">121.687072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">124.584381103516</t>
+    <t xml:space="preserve">124.58438873291</t>
   </si>
   <si>
     <t xml:space="preserve">125.64673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">131.586227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.344772338867</t>
+    <t xml:space="preserve">131.586212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.344787597656</t>
   </si>
   <si>
     <t xml:space="preserve">121.300765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">124.680961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.771430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.660781860352</t>
+    <t xml:space="preserve">124.680969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.771423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.660789489746</t>
   </si>
   <si>
     <t xml:space="preserve">124.922416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">122.314819335938</t>
+    <t xml:space="preserve">122.314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">124.777534484863</t>
@@ -4085,13 +4085,13 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.76530456543</t>
+    <t xml:space="preserve">130.765319824219</t>
   </si>
   <si>
     <t xml:space="preserve">128.302612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">126.612503051758</t>
+    <t xml:space="preserve">126.612518310547</t>
   </si>
   <si>
     <t xml:space="preserve">128.206024169922</t>
@@ -4100,31 +4100,31 @@
     <t xml:space="preserve">127.047096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">124.487800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.240249633789</t>
+    <t xml:space="preserve">124.487808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.240257263184</t>
   </si>
   <si>
     <t xml:space="preserve">129.316665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">128.157745361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.26042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.509826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.682815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.84782409668</t>
+    <t xml:space="preserve">128.157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.682800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.847839355469</t>
   </si>
   <si>
     <t xml:space="preserve">125.067268371582</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.783653259277</t>
+    <t xml:space="preserve">123.42546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.783645629883</t>
   </si>
   <si>
     <t xml:space="preserve">123.522041320801</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">122.652847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">127.62654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.874114990234</t>
+    <t xml:space="preserve">127.626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.874122619629</t>
   </si>
   <si>
     <t xml:space="preserve">125.405296325684</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">121.880218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.218246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.14183807373</t>
+    <t xml:space="preserve">121.880226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.218254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.141845703125</t>
   </si>
   <si>
     <t xml:space="preserve">125.550155639648</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">115.168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.188285827637</t>
+    <t xml:space="preserve">113.188293457031</t>
   </si>
   <si>
     <t xml:space="preserve">115.651008605957</t>
@@ -4208,37 +4208,37 @@
     <t xml:space="preserve">117.196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">117.775703430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.906517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.415672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236587524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.319107055664</t>
+    <t xml:space="preserve">117.775695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.415679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.23657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.31909942627</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.077659606934</t>
+    <t xml:space="preserve">112.077667236328</t>
   </si>
   <si>
     <t xml:space="preserve">109.42179107666</t>
   </si>
   <si>
-    <t xml:space="preserve">111.063598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.242691040039</t>
+    <t xml:space="preserve">111.063606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.242698669434</t>
   </si>
   <si>
     <t xml:space="preserve">107.20051574707</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">108.649169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">108.842315673828</t>
+    <t xml:space="preserve">108.842330932617</t>
   </si>
   <si>
     <t xml:space="preserve">108.118003845215</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">105.993301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">104.303199768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.013465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.937065124512</t>
+    <t xml:space="preserve">104.303207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.013473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.937072753906</t>
   </si>
   <si>
     <t xml:space="preserve">103.675453186035</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">97.7359619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9431762695312</t>
+    <t xml:space="preserve">98.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">97.5911026000977</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">98.5568771362305</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6455078125</t>
+    <t xml:space="preserve">94.6455001831055</t>
   </si>
   <si>
     <t xml:space="preserve">96.5770416259766</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">93.737678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6797332763672</t>
+    <t xml:space="preserve">93.6797256469727</t>
   </si>
   <si>
     <t xml:space="preserve">96.2100601196289</t>
@@ -4316,22 +4316,22 @@
     <t xml:space="preserve">95.7851028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7078475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9887771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5251998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9694671630859</t>
+    <t xml:space="preserve">95.7078552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9887847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5252075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9694595336914</t>
   </si>
   <si>
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342666625977</t>
+    <t xml:space="preserve">93.8342514038086</t>
   </si>
   <si>
     <t xml:space="preserve">95.5340118408203</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">93.1582183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1090698242188</t>
+    <t xml:space="preserve">95.1090774536133</t>
   </si>
   <si>
     <t xml:space="preserve">94.3750915527344</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">98.0739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1222763061523</t>
+    <t xml:space="preserve">98.1222686767578</t>
   </si>
   <si>
     <t xml:space="preserve">98.8948974609375</t>
@@ -4385,13 +4385,13 @@
     <t xml:space="preserve">100.408088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2853851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299743652344</t>
+    <t xml:space="preserve">99.2853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299819946289</t>
   </si>
   <si>
     <t xml:space="preserve">96.8642730712891</t>
@@ -4421,13 +4421,13 @@
     <t xml:space="preserve">95.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6384048461914</t>
+    <t xml:space="preserve">94.6384124755859</t>
   </si>
   <si>
     <t xml:space="preserve">94.4236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0679626464844</t>
+    <t xml:space="preserve">95.0679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">95.1265411376953</t>
@@ -4439,13 +4439,13 @@
     <t xml:space="preserve">95.4389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3579483032227</t>
+    <t xml:space="preserve">98.3579559326172</t>
   </si>
   <si>
     <t xml:space="preserve">96.6104431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4779891967773</t>
+    <t xml:space="preserve">95.4779968261719</t>
   </si>
   <si>
     <t xml:space="preserve">94.7946090698242</t>
@@ -4466,16 +4466,16 @@
     <t xml:space="preserve">90.8700561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4405059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.084831237793</t>
+    <t xml:space="preserve">90.4404983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0848388671875</t>
   </si>
   <si>
     <t xml:space="preserve">91.5534362792969</t>
@@ -4493,13 +4493,13 @@
     <t xml:space="preserve">90.1280975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7054138183594</t>
+    <t xml:space="preserve">92.7054214477539</t>
   </si>
   <si>
     <t xml:space="preserve">92.1196670532227</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5729675292969</t>
+    <t xml:space="preserve">91.5729598999023</t>
   </si>
   <si>
     <t xml:space="preserve">90.0109405517578</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">91.7877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2716445922852</t>
+    <t xml:space="preserve">93.2716522216797</t>
   </si>
   <si>
     <t xml:space="preserve">93.6816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3091354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6270904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3413162231445</t>
+    <t xml:space="preserve">98.3091278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.627082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413238525391</t>
   </si>
   <si>
     <t xml:space="preserve">92.9397201538086</t>
@@ -4544,13 +4544,13 @@
     <t xml:space="preserve">91.7682113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5492172241211</t>
+    <t xml:space="preserve">92.5492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">92.6273193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">89.11279296875</t>
+    <t xml:space="preserve">89.1127853393555</t>
   </si>
   <si>
     <t xml:space="preserve">88.1365280151367</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">87.1016998291016</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6679382324219</t>
+    <t xml:space="preserve">87.6679306030273</t>
   </si>
   <si>
     <t xml:space="preserve">87.3164825439453</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">90.9676818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8114700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906387329102</t>
+    <t xml:space="preserve">90.8114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906463623047</t>
   </si>
   <si>
     <t xml:space="preserve">92.8225708007812</t>
@@ -4586,10 +4586,10 @@
     <t xml:space="preserve">94.4626846313477</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0721740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444686889648</t>
+    <t xml:space="preserve">94.0721817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444763183594</t>
   </si>
   <si>
     <t xml:space="preserve">91.1238784790039</t>
@@ -4604,13 +4604,13 @@
     <t xml:space="preserve">90.6357498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5032958984375</t>
+    <t xml:space="preserve">89.503288269043</t>
   </si>
   <si>
     <t xml:space="preserve">90.303825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9328536987305</t>
+    <t xml:space="preserve">89.9328460693359</t>
   </si>
   <si>
     <t xml:space="preserve">88.8003921508789</t>
@@ -4622,22 +4622,22 @@
     <t xml:space="preserve">88.1755828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">85.207763671875</t>
+    <t xml:space="preserve">85.2077560424805</t>
   </si>
   <si>
     <t xml:space="preserve">84.4853286743164</t>
   </si>
   <si>
-    <t xml:space="preserve">83.9581451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132904052734</t>
+    <t xml:space="preserve">83.9581527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132827758789</t>
   </si>
   <si>
     <t xml:space="preserve">84.2314987182617</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">84.8563079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3053817749023</t>
+    <t xml:space="preserve">85.3053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">85.6373138427734</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">86.4378433227539</t>
   </si>
   <si>
-    <t xml:space="preserve">83.4700241088867</t>
+    <t xml:space="preserve">83.4700164794922</t>
   </si>
   <si>
     <t xml:space="preserve">81.5175094604492</t>
@@ -4688,16 +4688,16 @@
     <t xml:space="preserve">82.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8146057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531234741211</t>
+    <t xml:space="preserve">80.8145980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531158447266</t>
   </si>
   <si>
     <t xml:space="preserve">80.4436264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">80.131217956543</t>
+    <t xml:space="preserve">80.1312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">82.493766784668</t>
@@ -4718,10 +4718,10 @@
     <t xml:space="preserve">85.5006408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7892990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816390991211</t>
+    <t xml:space="preserve">86.789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816467285156</t>
   </si>
   <si>
     <t xml:space="preserve">83.1185684204102</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">88.8394393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2969512939453</t>
+    <t xml:space="preserve">87.2969436645508</t>
   </si>
   <si>
     <t xml:space="preserve">84.3096008300781</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">86.6916732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4183120727539</t>
+    <t xml:space="preserve">86.4183197021484</t>
   </si>
   <si>
     <t xml:space="preserve">85.98876953125</t>
@@ -4778,13 +4778,13 @@
     <t xml:space="preserve">89.6985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8589553833008</t>
+    <t xml:space="preserve">88.8589630126953</t>
   </si>
   <si>
     <t xml:space="preserve">87.6093521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9064483642578</t>
+    <t xml:space="preserve">86.9064407348633</t>
   </si>
   <si>
     <t xml:space="preserve">86.3402252197266</t>
@@ -4811,16 +4811,16 @@
     <t xml:space="preserve">90.9481582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9872055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0262603759766</t>
+    <t xml:space="preserve">90.9871978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">87.8436584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6135787963867</t>
+    <t xml:space="preserve">86.6135711669922</t>
   </si>
   <si>
     <t xml:space="preserve">87.2774276733398</t>
@@ -4829,13 +4829,13 @@
     <t xml:space="preserve">88.4294128417969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.7808685302734</t>
+    <t xml:space="preserve">88.7808609008789</t>
   </si>
   <si>
     <t xml:space="preserve">88.2341613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5117263793945</t>
+    <t xml:space="preserve">87.5117340087891</t>
   </si>
   <si>
     <t xml:space="preserve">87.121223449707</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">85.9106674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1296539306641</t>
+    <t xml:space="preserve">85.1296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">84.0167236328125</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">82.6304397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">84.3877105712891</t>
+    <t xml:space="preserve">84.3877029418945</t>
   </si>
   <si>
     <t xml:space="preserve">84.3486557006836</t>
@@ -4871,10 +4871,10 @@
     <t xml:space="preserve">83.8605270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4547119140625</t>
+    <t xml:space="preserve">83.0014114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.454719543457</t>
   </si>
   <si>
     <t xml:space="preserve">82.9428405761719</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">84.9344100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">84.055778503418</t>
+    <t xml:space="preserve">84.0557708740234</t>
   </si>
   <si>
     <t xml:space="preserve">84.8953552246094</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">85.6958923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7001113891602</t>
+    <t xml:space="preserve">84.7001037597656</t>
   </si>
   <si>
     <t xml:space="preserve">84.7196350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2578964233398</t>
+    <t xml:space="preserve">87.2579040527344</t>
   </si>
   <si>
     <t xml:space="preserve">88.1170120239258</t>
@@ -4925,19 +4925,19 @@
     <t xml:space="preserve">92.3149108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2843017578125</t>
+    <t xml:space="preserve">90.284309387207</t>
   </si>
   <si>
     <t xml:space="preserve">91.7096405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8310012817383</t>
+    <t xml:space="preserve">90.8310089111328</t>
   </si>
   <si>
     <t xml:space="preserve">91.4753341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4125518798828</t>
+    <t xml:space="preserve">92.4125442504883</t>
   </si>
   <si>
     <t xml:space="preserve">94.5017395019531</t>
@@ -4955,13 +4955,13 @@
     <t xml:space="preserve">91.2605667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4515838623047</t>
+    <t xml:space="preserve">92.4515914916992</t>
   </si>
   <si>
     <t xml:space="preserve">89.6399765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9259719848633</t>
+    <t xml:space="preserve">86.9259796142578</t>
   </si>
   <si>
     <t xml:space="preserve">86.0863952636719</t>
@@ -4976,7 +4976,7 @@
     <t xml:space="preserve">84.1338806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9275360107422</t>
+    <t xml:space="preserve">81.9275283813477</t>
   </si>
   <si>
     <t xml:space="preserve">81.3222579956055</t>
@@ -4985,22 +4985,22 @@
     <t xml:space="preserve">83.7238464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6721420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615936279297</t>
+    <t xml:space="preserve">86.6721496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615859985352</t>
   </si>
   <si>
     <t xml:space="preserve">85.2858581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4098815917969</t>
+    <t xml:space="preserve">88.4098892211914</t>
   </si>
   <si>
     <t xml:space="preserve">87.4531555175781</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">92.6858978271484</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5840530395508</t>
+    <t xml:space="preserve">93.5840454101562</t>
   </si>
   <si>
     <t xml:space="preserve">93.7402496337891</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">91.4362869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6468505859375</t>
+    <t xml:space="preserve">92.646842956543</t>
   </si>
   <si>
     <t xml:space="preserve">93.9550247192383</t>
@@ -5033,7 +5033,7 @@
     <t xml:space="preserve">90.7724304199219</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6510543823242</t>
+    <t xml:space="preserve">91.6510620117188</t>
   </si>
   <si>
     <t xml:space="preserve">91.1043548583984</t>
@@ -5468,9 +5468,6 @@
     <t xml:space="preserve">95.2035980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">99.627082824707</t>
-  </si>
-  <si>
     <t xml:space="preserve">97.6128234863281</t>
   </si>
   <si>
@@ -5922,6 +5919,9 @@
   </si>
   <si>
     <t xml:space="preserve">76.2799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.3600006103516</t>
   </si>
 </sst>
 </file>
@@ -67014,7 +67014,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1818</v>
+        <v>1505</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67066,7 +67066,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67092,7 +67092,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67118,7 +67118,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67144,7 +67144,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67170,7 +67170,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67196,7 +67196,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67222,7 +67222,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67248,7 +67248,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67274,7 +67274,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67300,7 +67300,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67326,7 +67326,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67352,7 +67352,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67378,7 +67378,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67404,7 +67404,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67430,7 +67430,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67456,7 +67456,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67482,7 +67482,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67534,7 +67534,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67560,7 +67560,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67586,7 +67586,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67612,7 +67612,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67638,7 +67638,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67664,7 +67664,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67716,7 +67716,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67742,7 +67742,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67768,7 +67768,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67794,7 +67794,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67846,7 +67846,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67898,7 +67898,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67950,7 +67950,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68002,7 +68002,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68028,7 +68028,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68080,7 +68080,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68106,7 +68106,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68132,7 +68132,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68158,7 +68158,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68184,7 +68184,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68210,7 +68210,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68236,7 +68236,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68262,7 +68262,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68288,7 +68288,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68314,7 +68314,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68340,7 +68340,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68366,7 +68366,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68392,7 +68392,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68418,7 +68418,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68444,7 +68444,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68470,7 +68470,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68496,7 +68496,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68522,7 +68522,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68548,7 +68548,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68574,7 +68574,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68600,7 +68600,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68626,7 +68626,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68652,7 +68652,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68678,7 +68678,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68704,7 +68704,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68730,7 +68730,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68756,7 +68756,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68782,7 +68782,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68808,7 +68808,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68834,7 +68834,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68860,7 +68860,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68886,7 +68886,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68912,7 +68912,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68938,7 +68938,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68964,7 +68964,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68990,7 +68990,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69016,7 +69016,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69042,7 +69042,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69068,7 +69068,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69094,7 +69094,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69120,7 +69120,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69146,7 +69146,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69172,7 +69172,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69198,7 +69198,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69224,7 +69224,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69250,7 +69250,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69276,7 +69276,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69302,7 +69302,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69328,7 +69328,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69354,7 +69354,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69380,7 +69380,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69406,7 +69406,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69432,7 +69432,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69458,7 +69458,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69484,7 +69484,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69510,7 +69510,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69536,7 +69536,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69562,7 +69562,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69588,7 +69588,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69614,7 +69614,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69640,7 +69640,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69666,7 +69666,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69692,7 +69692,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69718,7 +69718,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69744,7 +69744,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69770,7 +69770,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69796,7 +69796,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69822,7 +69822,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69848,7 +69848,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69874,7 +69874,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69900,7 +69900,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69926,7 +69926,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69952,7 +69952,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69978,7 +69978,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70004,7 +70004,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70030,7 +70030,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70056,7 +70056,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70082,7 +70082,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70108,7 +70108,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70134,7 +70134,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70160,7 +70160,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70186,7 +70186,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70212,7 +70212,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70238,7 +70238,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70264,7 +70264,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70290,7 +70290,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70316,7 +70316,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70342,7 +70342,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70368,7 +70368,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70394,7 +70394,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70420,7 +70420,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70446,7 +70446,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70472,7 +70472,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70498,7 +70498,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70524,7 +70524,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70550,7 +70550,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70576,7 +70576,7 @@
         <v>77.8600006103516</v>
       </c>
       <c r="G2474" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70602,7 +70602,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2475" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70628,7 +70628,7 @@
         <v>74.1800003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70654,7 +70654,7 @@
         <v>74.1399993896484</v>
       </c>
       <c r="G2477" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70680,7 +70680,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2478" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70706,7 +70706,7 @@
         <v>75.5199966430664</v>
       </c>
       <c r="G2479" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70732,7 +70732,7 @@
         <v>77.6600036621094</v>
       </c>
       <c r="G2480" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70758,7 +70758,7 @@
         <v>77.8399963378906</v>
       </c>
       <c r="G2481" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70784,7 +70784,7 @@
         <v>78.879997253418</v>
       </c>
       <c r="G2482" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70810,7 +70810,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2483" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70836,7 +70836,7 @@
         <v>79.0400009155273</v>
       </c>
       <c r="G2484" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70862,7 +70862,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G2485" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70888,7 +70888,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G2486" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70914,7 +70914,7 @@
         <v>75.6399993896484</v>
       </c>
       <c r="G2487" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70940,7 +70940,7 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2488" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70966,7 +70966,7 @@
         <v>74.1999969482422</v>
       </c>
       <c r="G2489" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70992,7 +70992,7 @@
         <v>74.2399978637695</v>
       </c>
       <c r="G2490" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -71018,7 +71018,7 @@
         <v>74.9400024414062</v>
       </c>
       <c r="G2491" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -71044,7 +71044,7 @@
         <v>75.2600021362305</v>
       </c>
       <c r="G2492" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71070,7 +71070,7 @@
         <v>75.9400024414062</v>
       </c>
       <c r="G2493" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71096,7 +71096,7 @@
         <v>75.9599990844727</v>
       </c>
       <c r="G2494" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71122,7 +71122,7 @@
         <v>77.9400024414062</v>
       </c>
       <c r="G2495" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71148,7 +71148,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2496" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71174,7 +71174,7 @@
         <v>78.5999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71200,7 +71200,7 @@
         <v>77.6999969482422</v>
       </c>
       <c r="G2498" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71226,7 +71226,7 @@
         <v>77.2399978637695</v>
       </c>
       <c r="G2499" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71252,7 +71252,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2500" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -71278,7 +71278,7 @@
         <v>76.3199996948242</v>
       </c>
       <c r="G2501" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -71304,7 +71304,7 @@
         <v>76.6999969482422</v>
       </c>
       <c r="G2502" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -71312,7 +71312,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911805556</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>127641</v>
@@ -71330,9 +71330,35 @@
         <v>76.2799987792969</v>
       </c>
       <c r="G2503" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6920833333</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>152275</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>76.3600006103516</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>75.2399978637695</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>75.620002746582</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>76.3600006103516</v>
+      </c>
+      <c r="G2504" t="s">
         <v>1969</v>
       </c>
-      <c r="H2503" t="s">
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1977">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980918884277</t>
+    <t xml:space="preserve">43.298095703125</t>
   </si>
   <si>
     <t xml:space="preserve">43.042308807373</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9276466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8218002319336</t>
+    <t xml:space="preserve">42.9276428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8218040466309</t>
   </si>
   <si>
     <t xml:space="preserve">42.1514701843262</t>
@@ -62,37 +62,37 @@
     <t xml:space="preserve">42.4689979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7281074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2870979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9993515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2761001586914</t>
+    <t xml:space="preserve">41.728099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2870941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9993591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2760963439941</t>
   </si>
   <si>
     <t xml:space="preserve">38.0765609741211</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8384170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9585800170898</t>
+    <t xml:space="preserve">37.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9585762023926</t>
   </si>
   <si>
     <t xml:space="preserve">40.2551383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2606315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544471740723</t>
+    <t xml:space="preserve">41.2606353759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544509887695</t>
   </si>
   <si>
     <t xml:space="preserve">41.3664779663086</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">42.7776985168457</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0687713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8780517578125</t>
+    <t xml:space="preserve">43.0687675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9981994628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780479431152</t>
   </si>
   <si>
     <t xml:space="preserve">41.2341804504395</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">39.4172248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7590370178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.014820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6057739257812</t>
+    <t xml:space="preserve">37.7590484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0148239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6057777404785</t>
   </si>
   <si>
     <t xml:space="preserve">38.4029121398926</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">40.1228370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3962593078613</t>
+    <t xml:space="preserve">40.3962631225586</t>
   </si>
   <si>
     <t xml:space="preserve">40.4932823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4017562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5483894348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9397850036621</t>
+    <t xml:space="preserve">41.4017601013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5483818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9397811889648</t>
   </si>
   <si>
     <t xml:space="preserve">42.5924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">43.209888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011840820312</t>
+    <t xml:space="preserve">43.2098922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.901180267334</t>
   </si>
   <si>
     <t xml:space="preserve">43.2275276184082</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">42.7071380615234</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7600631713867</t>
+    <t xml:space="preserve">42.760066986084</t>
   </si>
   <si>
     <t xml:space="preserve">40.7578887939453</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">40.0081787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1636161804199</t>
+    <t xml:space="preserve">41.1636123657227</t>
   </si>
   <si>
     <t xml:space="preserve">40.5726661682129</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">40.1581153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6200866699219</t>
+    <t xml:space="preserve">39.6200942993164</t>
   </si>
   <si>
     <t xml:space="preserve">40.1140174865723</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">40.2904167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8405876159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1316566467285</t>
+    <t xml:space="preserve">39.8405914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1316604614258</t>
   </si>
   <si>
     <t xml:space="preserve">40.4668273925781</t>
@@ -215,49 +215,49 @@
     <t xml:space="preserve">44.1007232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2914352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8647537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3796463012695</t>
+    <t xml:space="preserve">44.7622299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2914428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.86474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3796424865723</t>
   </si>
   <si>
     <t xml:space="preserve">45.688346862793</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8349723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9088554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4237480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2032470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8945388793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9386405944824</t>
+    <t xml:space="preserve">46.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9088516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4237442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8945350646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9386367797852</t>
   </si>
   <si>
     <t xml:space="preserve">45.3355445861816</t>
   </si>
   <si>
-    <t xml:space="preserve">44.806339263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7181396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473449707031</t>
+    <t xml:space="preserve">44.8063278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7181358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473373413086</t>
   </si>
   <si>
     <t xml:space="preserve">44.982738494873</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">44.8504333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">45.776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442527770996</t>
+    <t xml:space="preserve">45.7765464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442489624023</t>
   </si>
   <si>
     <t xml:space="preserve">45.8206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3057632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1734504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.261661529541</t>
+    <t xml:space="preserve">46.3057594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1734580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2616577148438</t>
   </si>
   <si>
     <t xml:space="preserve">46.6144599914551</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">46.0852546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9970512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4226684570312</t>
+    <t xml:space="preserve">45.9970550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4226608276367</t>
   </si>
   <si>
     <t xml:space="preserve">47.5119781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1100845336914</t>
+    <t xml:space="preserve">47.1100883483887</t>
   </si>
   <si>
     <t xml:space="preserve">47.9138641357422</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">48.1817893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1195220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.583667755127</t>
+    <t xml:space="preserve">49.1195297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5836753845215</t>
   </si>
   <si>
     <t xml:space="preserve">49.5660667419434</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6553688049316</t>
+    <t xml:space="preserve">49.6553764343262</t>
   </si>
   <si>
     <t xml:space="preserve">50.2358779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0748672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9679489135742</t>
+    <t xml:space="preserve">49.0748710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">49.164176940918</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">48.9855613708496</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5566368103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7352485656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6188926696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0924835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723556518555</t>
+    <t xml:space="preserve">47.5566329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7352523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6189002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9314727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723594665527</t>
   </si>
   <si>
     <t xml:space="preserve">45.0113487243652</t>
@@ -365,103 +365,103 @@
     <t xml:space="preserve">46.0383834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8962516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.744686126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.414493560791</t>
+    <t xml:space="preserve">48.8962554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7446823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4144897460938</t>
   </si>
   <si>
     <t xml:space="preserve">48.1371307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9409027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8339881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.030216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.21826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2629165649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610305786133</t>
+    <t xml:space="preserve">48.9409065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0302124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2182693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2629241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8610343933105</t>
   </si>
   <si>
     <t xml:space="preserve">51.575496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">51.798770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9949913024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.771728515625</t>
+    <t xml:space="preserve">51.7987670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9949951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">50.2805328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0572624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.191219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6201515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5849342346191</t>
+    <t xml:space="preserve">50.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1912231445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6201553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5849380493164</t>
   </si>
   <si>
     <t xml:space="preserve">53.0937423706055</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1654357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3440551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.37109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.120777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0666923522949</t>
+    <t xml:space="preserve">54.1654434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3440437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3711013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1207809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0666961669922</t>
   </si>
   <si>
     <t xml:space="preserve">51.6648063659668</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6824111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968772888184</t>
+    <t xml:space="preserve">50.6824150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968734741211</t>
   </si>
   <si>
     <t xml:space="preserve">50.637767791748</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2453155517578</t>
+    <t xml:space="preserve">52.2453193664551</t>
   </si>
   <si>
     <t xml:space="preserve">51.7541160583496</t>
@@ -473,37 +473,37 @@
     <t xml:space="preserve">51.3522300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8880767822266</t>
+    <t xml:space="preserve">51.8880805969238</t>
   </si>
   <si>
     <t xml:space="preserve">51.0843048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4591522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4767532348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2981376647949</t>
+    <t xml:space="preserve">50.4591484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4767646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2981452941895</t>
   </si>
   <si>
     <t xml:space="preserve">51.9773826599121</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5132293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6918487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308494567871</t>
+    <t xml:space="preserve">52.5132331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6918525695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308456420898</t>
   </si>
   <si>
     <t xml:space="preserve">52.3346138000488</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6025428771973</t>
+    <t xml:space="preserve">52.6025505065918</t>
   </si>
   <si>
     <t xml:space="preserve">52.2899627685547</t>
@@ -512,43 +512,43 @@
     <t xml:space="preserve">53.183048248291</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7094650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270698547363</t>
+    <t xml:space="preserve">51.7094688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270736694336</t>
   </si>
   <si>
     <t xml:space="preserve">50.1465721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">50.905689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0126075744629</t>
+    <t xml:space="preserve">50.9056854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0125999450684</t>
   </si>
   <si>
     <t xml:space="preserve">48.7176361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6459274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8245468139648</t>
+    <t xml:space="preserve">47.645938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8245506286621</t>
   </si>
   <si>
     <t xml:space="preserve">45.3239250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7258110046387</t>
+    <t xml:space="preserve">45.7258186340332</t>
   </si>
   <si>
     <t xml:space="preserve">45.547191619873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3956184387207</t>
+    <t xml:space="preserve">46.395622253418</t>
   </si>
   <si>
     <t xml:space="preserve">46.6635513305664</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">45.7704658508301</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1277008056641</t>
+    <t xml:space="preserve">46.1277046203613</t>
   </si>
   <si>
     <t xml:space="preserve">46.5742378234863</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4402809143066</t>
+    <t xml:space="preserve">46.4402770996094</t>
   </si>
   <si>
     <t xml:space="preserve">45.9937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4578895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.68115234375</t>
+    <t xml:space="preserve">45.4578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811561584473</t>
   </si>
   <si>
     <t xml:space="preserve">46.5295867919922</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3063087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2440528869629</t>
+    <t xml:space="preserve">46.3063163757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2440490722656</t>
   </si>
   <si>
     <t xml:space="preserve">47.4673194885254</t>
@@ -593,94 +593,94 @@
     <t xml:space="preserve">50.3698348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1560020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5037956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8516006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6107139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8163833618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.128963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2006607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3616638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4063110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4509696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.674243927002</t>
+    <t xml:space="preserve">52.156005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5038032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8515892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8163795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1289596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2006568908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.406322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4509735107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6742401123047</t>
   </si>
   <si>
     <t xml:space="preserve">52.9151229858398</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2723579406738</t>
+    <t xml:space="preserve">53.2723617553711</t>
   </si>
   <si>
     <t xml:space="preserve">53.8528594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">54.790584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.505054473877</t>
+    <t xml:space="preserve">54.7905921936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5943756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5050621032715</t>
   </si>
   <si>
     <t xml:space="preserve">56.2641792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1302146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.639030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8000259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5321044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.978645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3358726501465</t>
+    <t xml:space="preserve">56.1302185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6390228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8000221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5321083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9786491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.335880279541</t>
   </si>
   <si>
     <t xml:space="preserve">58.0503425598145</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8987731933594</t>
+    <t xml:space="preserve">58.8987808227539</t>
   </si>
   <si>
     <t xml:space="preserve">59.0327301025391</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">58.0949974060059</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1572647094727</t>
+    <t xml:space="preserve">57.1572608947754</t>
   </si>
   <si>
     <t xml:space="preserve">57.3805313110352</t>
@@ -701,100 +701,100 @@
     <t xml:space="preserve">58.5861968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0151214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.943431854248</t>
+    <t xml:space="preserve">60.0151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9434204101562</t>
   </si>
   <si>
     <t xml:space="preserve">59.3006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2830505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4088325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1585311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.622673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8905944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283271789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943740844727</t>
+    <t xml:space="preserve">60.2830543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440689086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4088363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6226806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8906097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943778991699</t>
   </si>
   <si>
     <t xml:space="preserve">62.3817977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">62.7390327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8635635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9469032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5342826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950675964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4379539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7542495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4831466674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5675506591797</t>
+    <t xml:space="preserve">62.7390289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5157623291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8635597229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6758079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9469108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.082447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.534294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4950752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4379730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7542572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.483154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5675582885742</t>
   </si>
   <si>
     <t xml:space="preserve">64.0705413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5164184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.031322479248</t>
+    <t xml:space="preserve">64.8386611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5164260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.166862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0313148498535</t>
   </si>
   <si>
     <t xml:space="preserve">64.5223846435547</t>
@@ -803,61 +803,61 @@
     <t xml:space="preserve">63.8898086547852</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4320220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2964630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1609115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6971435546875</t>
+    <t xml:space="preserve">64.4320068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2964553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1609191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.697151184082</t>
   </si>
   <si>
     <t xml:space="preserve">61.0884132385254</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6425361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1847305297852</t>
+    <t xml:space="preserve">59.6425323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.184741973877</t>
   </si>
   <si>
     <t xml:space="preserve">60.8173141479492</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5462112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6877174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4498863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3987426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2120513916016</t>
+    <t xml:space="preserve">60.5462188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6877136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365776062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4498901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3987503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.212043762207</t>
   </si>
   <si>
     <t xml:space="preserve">63.5735130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3927917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216773986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2393493652344</t>
+    <t xml:space="preserve">63.3927955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2393646240234</t>
   </si>
   <si>
     <t xml:space="preserve">66.7815704345703</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">66.0134353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5104598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3297271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.96826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778839111328</t>
+    <t xml:space="preserve">66.5104675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3297348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9682540893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778991699219</t>
   </si>
   <si>
     <t xml:space="preserve">65.6067886352539</t>
   </si>
   <si>
-    <t xml:space="preserve">65.0193862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2001342773438</t>
+    <t xml:space="preserve">65.0193939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2001419067383</t>
   </si>
   <si>
     <t xml:space="preserve">64.7483062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7934875488281</t>
+    <t xml:space="preserve">64.7934722900391</t>
   </si>
   <si>
     <t xml:space="preserve">64.6579284667969</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">64.4771957397461</t>
   </si>
   <si>
-    <t xml:space="preserve">63.980167388916</t>
+    <t xml:space="preserve">63.9801712036133</t>
   </si>
   <si>
     <t xml:space="preserve">63.302417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4260559082031</t>
+    <t xml:space="preserve">65.4260482788086</t>
   </si>
   <si>
     <t xml:space="preserve">65.4712448120117</t>
   </si>
   <si>
-    <t xml:space="preserve">66.284538269043</t>
+    <t xml:space="preserve">66.2845458984375</t>
   </si>
   <si>
     <t xml:space="preserve">66.600830078125</t>
@@ -920,94 +920,94 @@
     <t xml:space="preserve">66.4652786254883</t>
   </si>
   <si>
-    <t xml:space="preserve">66.871940612793</t>
+    <t xml:space="preserve">66.8719177246094</t>
   </si>
   <si>
     <t xml:space="preserve">66.0586318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3749084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6912002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5437240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1370849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563217163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1822509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1311187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3059005737305</t>
+    <t xml:space="preserve">66.3749008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6911926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141464233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5437393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.137077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.182258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1311264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3058929443359</t>
   </si>
   <si>
     <t xml:space="preserve">70.3962631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9776992797852</t>
+    <t xml:space="preserve">71.9776916503906</t>
   </si>
   <si>
     <t xml:space="preserve">71.3903045654297</t>
   </si>
   <si>
-    <t xml:space="preserve">71.5258560180664</t>
+    <t xml:space="preserve">71.5258636474609</t>
   </si>
   <si>
     <t xml:space="preserve">70.8481063842773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1643905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7910003662109</t>
+    <t xml:space="preserve">71.1643981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7910079956055</t>
   </si>
   <si>
     <t xml:space="preserve">70.8932723999023</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2607192993164</t>
+    <t xml:space="preserve">70.2607116699219</t>
   </si>
   <si>
     <t xml:space="preserve">70.3510818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5318145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029174804688</t>
+    <t xml:space="preserve">70.5318222045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029098510742</t>
   </si>
   <si>
     <t xml:space="preserve">70.4866333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5770034790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3451309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4414367675781</t>
+    <t xml:space="preserve">70.5769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3451232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4414520263672</t>
   </si>
   <si>
     <t xml:space="preserve">71.5710372924805</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">70.7125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">65.1097793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5615921020508</t>
+    <t xml:space="preserve">65.1097717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5616073608398</t>
   </si>
   <si>
     <t xml:space="preserve">67.4593276977539</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">67.8207931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2666702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.034797668457</t>
+    <t xml:space="preserve">69.2666625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.034782409668</t>
   </si>
   <si>
     <t xml:space="preserve">69.7636871337891</t>
@@ -1043,79 +1043,79 @@
     <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3237533569336</t>
+    <t xml:space="preserve">67.3237686157227</t>
   </si>
   <si>
     <t xml:space="preserve">68.3629989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0407638549805</t>
+    <t xml:space="preserve">69.0407485961914</t>
   </si>
   <si>
     <t xml:space="preserve">69.1763000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9444351196289</t>
+    <t xml:space="preserve">69.9444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">70.1703414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">71.887336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6102600097656</t>
+    <t xml:space="preserve">71.8873291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6102676391602</t>
   </si>
   <si>
     <t xml:space="preserve">69.8992385864258</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4985504150391</t>
+    <t xml:space="preserve">68.4985580444336</t>
   </si>
   <si>
     <t xml:space="preserve">68.4081802368164</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2785797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6400375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.402214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6162261962891</t>
+    <t xml:space="preserve">67.2785873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6400604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4022369384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6162185668945</t>
   </si>
   <si>
     <t xml:space="preserve">71.9325103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0228805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7065887451172</t>
+    <t xml:space="preserve">72.0228729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7065811157227</t>
   </si>
   <si>
     <t xml:space="preserve">71.4806747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4354782104492</t>
+    <t xml:space="preserve">71.4354934692383</t>
   </si>
   <si>
     <t xml:space="preserve">71.6614151000977</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2547607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8088760375977</t>
+    <t xml:space="preserve">71.2547378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8088684082031</t>
   </si>
   <si>
     <t xml:space="preserve">71.7517700195312</t>
@@ -1124,70 +1124,70 @@
     <t xml:space="preserve">68.0918960571289</t>
   </si>
   <si>
-    <t xml:space="preserve">66.962287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416366577148</t>
+    <t xml:space="preserve">66.9623031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8505706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416442871094</t>
   </si>
   <si>
     <t xml:space="preserve">63.2572364807129</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6187133789062</t>
+    <t xml:space="preserve">63.6187057495117</t>
   </si>
   <si>
     <t xml:space="preserve">63.0764999389648</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9409523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7601928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.901725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7328987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.799430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5496978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7363815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2905044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4200897216797</t>
+    <t xml:space="preserve">62.9409446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0040054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7328948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.811351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7994270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.549690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7363739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6519622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4200973510742</t>
   </si>
   <si>
     <t xml:space="preserve">68.2726287841797</t>
@@ -1196,55 +1196,55 @@
     <t xml:space="preserve">70.1251602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8600082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540573120117</t>
+    <t xml:space="preserve">68.8600158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540649414062</t>
   </si>
   <si>
     <t xml:space="preserve">70.622184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1191940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0740127563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6554565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6946792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4747085571289</t>
+    <t xml:space="preserve">71.1192016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0740203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6554489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6946716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4747161865234</t>
   </si>
   <si>
     <t xml:space="preserve">73.4687652587891</t>
   </si>
   <si>
-    <t xml:space="preserve">73.1976470947266</t>
+    <t xml:space="preserve">73.1976547241211</t>
   </si>
   <si>
     <t xml:space="preserve">73.3783874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">74.688720703125</t>
+    <t xml:space="preserve">74.6887130737305</t>
   </si>
   <si>
     <t xml:space="preserve">73.5591278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1983642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6960983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9289474487305</t>
+    <t xml:space="preserve">74.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6961059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9289398193359</t>
   </si>
   <si>
     <t xml:space="preserve">76.8466796875</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">75.7964935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">74.152717590332</t>
+    <t xml:space="preserve">74.1527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">77.2576293945312</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">80.5908508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3625411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7278289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2712249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2301025390625</t>
+    <t xml:space="preserve">80.3625564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7278213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2712326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2300872802734</t>
   </si>
   <si>
     <t xml:space="preserve">83.1021728515625</t>
@@ -1289,64 +1289,64 @@
     <t xml:space="preserve">84.3806762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2482147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9286117553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893600463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0565185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8006896972656</t>
+    <t xml:space="preserve">85.2482299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.928596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.056510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8006820678711</t>
   </si>
   <si>
     <t xml:space="preserve">87.3942642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8554077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9878463745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2206954956055</t>
+    <t xml:space="preserve">88.8554153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9878540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2206802368164</t>
   </si>
   <si>
     <t xml:space="preserve">87.9421920776367</t>
   </si>
   <si>
-    <t xml:space="preserve">89.0380554199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335159301758</t>
+    <t xml:space="preserve">89.0380477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335235595703</t>
   </si>
   <si>
     <t xml:space="preserve">87.2572937011719</t>
   </si>
   <si>
-    <t xml:space="preserve">87.485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5769195556641</t>
+    <t xml:space="preserve">87.4855880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5769119262695</t>
   </si>
   <si>
     <t xml:space="preserve">87.8052139282227</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6772994995117</t>
+    <t xml:space="preserve">89.6772842407227</t>
   </si>
   <si>
     <t xml:space="preserve">89.1750259399414</t>
@@ -1358,28 +1358,28 @@
     <t xml:space="preserve">88.1248474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">87.62255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3531341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8418045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4719848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8327484130859</t>
+    <t xml:space="preserve">87.6225738525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.353141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2984085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4719924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">77.6685791015625</t>
@@ -1388,70 +1388,70 @@
     <t xml:space="preserve">79.7689590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0474548339844</t>
+    <t xml:space="preserve">81.0474472045898</t>
   </si>
   <si>
     <t xml:space="preserve">80.2255554199219</t>
   </si>
   <si>
-    <t xml:space="preserve">80.453857421875</t>
+    <t xml:space="preserve">80.4538650512695</t>
   </si>
   <si>
     <t xml:space="preserve">79.3580169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">80.4995269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6501159667969</t>
+    <t xml:space="preserve">80.4995346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6135025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6500930786133</t>
   </si>
   <si>
     <t xml:space="preserve">83.2391510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">83.7414245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3350143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6410446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9149932861328</t>
+    <t xml:space="preserve">83.7414093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8372802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3350067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6410369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9150009155273</t>
   </si>
   <si>
     <t xml:space="preserve">81.0017929077148</t>
   </si>
   <si>
-    <t xml:space="preserve">81.275749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8282089233398</t>
+    <t xml:space="preserve">81.2757568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8282165527344</t>
   </si>
   <si>
     <t xml:space="preserve">87.5312423706055</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">84.2436904907227</t>
   </si>
   <si>
-    <t xml:space="preserve">85.0199203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.882926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7368927001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3761367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4583892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2666931152344</t>
+    <t xml:space="preserve">85.0199127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8829498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3761520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4584045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2666854858398</t>
   </si>
   <si>
     <t xml:space="preserve">75.1572418212891</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">74.4266738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3308258056641</t>
+    <t xml:space="preserve">73.3308181762695</t>
   </si>
   <si>
     <t xml:space="preserve">72.7828903198242</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">74.8376159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6002578735352</t>
+    <t xml:space="preserve">72.6002502441406</t>
   </si>
   <si>
     <t xml:space="preserve">72.9198760986328</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">74.5179901123047</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8832702636719</t>
+    <t xml:space="preserve">74.8832855224609</t>
   </si>
   <si>
     <t xml:space="preserve">75.2485656738281</t>
   </si>
   <si>
-    <t xml:space="preserve">76.4357223510742</t>
+    <t xml:space="preserve">76.4357376098633</t>
   </si>
   <si>
     <t xml:space="preserve">72.8285522460938</t>
@@ -1520,22 +1520,22 @@
     <t xml:space="preserve">73.8330917358398</t>
   </si>
   <si>
-    <t xml:space="preserve">72.2806396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9700775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0659103393555</t>
+    <t xml:space="preserve">72.2806243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9700698852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.06591796875</t>
   </si>
   <si>
     <t xml:space="preserve">76.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9516067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.3398895263672</t>
+    <t xml:space="preserve">79.9515991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.3398818969727</t>
   </si>
   <si>
     <t xml:space="preserve">76.1161193847656</t>
@@ -1544,31 +1544,31 @@
     <t xml:space="preserve">73.0568618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5455322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6825180053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0934524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9610061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1025238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.326286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0478057861328</t>
+    <t xml:space="preserve">70.545539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.682502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0934600830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9609985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1025161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3262939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477981567383</t>
   </si>
   <si>
     <t xml:space="preserve">70.8651504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">68.5821304321289</t>
+    <t xml:space="preserve">68.5821151733398</t>
   </si>
   <si>
     <t xml:space="preserve">68.4908065795898</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">68.8560943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3217697143555</t>
+    <t xml:space="preserve">71.3217544555664</t>
   </si>
   <si>
     <t xml:space="preserve">66.8013610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3949508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.938346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5775985717773</t>
+    <t xml:space="preserve">67.3949432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9383544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187210083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5775909423828</t>
   </si>
   <si>
     <t xml:space="preserve">66.8470230102539</t>
@@ -1601,46 +1601,46 @@
     <t xml:space="preserve">65.5228729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0160751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4270095825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2900314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7923049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1621170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.944694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2089385986328</t>
+    <t xml:space="preserve">64.0160675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4270248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2900238037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.9446868896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2089309692383</t>
   </si>
   <si>
     <t xml:space="preserve">66.6771697998047</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3025894165039</t>
+    <t xml:space="preserve">66.3025970458984</t>
   </si>
   <si>
     <t xml:space="preserve">70.0016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4866180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2056732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6270904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7508544921875</t>
+    <t xml:space="preserve">69.4866027832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2056655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.627082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.750862121582</t>
   </si>
   <si>
     <t xml:space="preserve">70.1421432495117</t>
@@ -1649,25 +1649,25 @@
     <t xml:space="preserve">69.7675552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8913345336914</t>
+    <t xml:space="preserve">70.8913192749023</t>
   </si>
   <si>
     <t xml:space="preserve">72.5769882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0452194213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2459411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.10546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9649963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5904159545898</t>
+    <t xml:space="preserve">73.0452346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2459487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.1054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9650039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5904235839844</t>
   </si>
   <si>
     <t xml:space="preserve">75.0586547851562</t>
@@ -1679,40 +1679,40 @@
     <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">76.557014465332</t>
+    <t xml:space="preserve">76.5570068359375</t>
   </si>
   <si>
     <t xml:space="preserve">76.1355972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8713531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8847732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9784240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7109146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.694206237793</t>
+    <t xml:space="preserve">74.8713607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8847808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7109069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6172485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6942138671875</t>
   </si>
   <si>
     <t xml:space="preserve">79.2728042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">79.6005630493164</t>
+    <t xml:space="preserve">79.6005706787109</t>
   </si>
   <si>
     <t xml:space="preserve">79.2259826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4132614135742</t>
+    <t xml:space="preserve">79.4132690429688</t>
   </si>
   <si>
     <t xml:space="preserve">79.7878570556641</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">80.02197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0386734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8815155029297</t>
+    <t xml:space="preserve">79.0386810302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8815078735352</t>
   </si>
   <si>
     <t xml:space="preserve">80.6775131225586</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">80.7711639404297</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0354080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7076416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3330459594727</t>
+    <t xml:space="preserve">82.035400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.707633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3330383300781</t>
   </si>
   <si>
     <t xml:space="preserve">81.2393951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2227020263672</t>
+    <t xml:space="preserve">82.2227096557617</t>
   </si>
   <si>
     <t xml:space="preserve">81.145751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3497543334961</t>
+    <t xml:space="preserve">80.3497467041016</t>
   </si>
   <si>
     <t xml:space="preserve">79.9751586914062</t>
@@ -1766,82 +1766,82 @@
     <t xml:space="preserve">82.26953125</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5036392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0187149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2528305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6742477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9718780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.048828125</t>
+    <t xml:space="preserve">82.5036468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0187072753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2528228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6742401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9718856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0488357543945</t>
   </si>
   <si>
     <t xml:space="preserve">84.0020065307617</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7980041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.7813186645508</t>
+    <t xml:space="preserve">84.7980194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7813034057617</t>
   </si>
   <si>
     <t xml:space="preserve">86.8582611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">86.1558990478516</t>
+    <t xml:space="preserve">86.1559066772461</t>
   </si>
   <si>
     <t xml:space="preserve">85.8281402587891</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6876602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2194366455078</t>
+    <t xml:space="preserve">85.6876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2194290161133</t>
   </si>
   <si>
     <t xml:space="preserve">85.1257781982422</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6408462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7410278320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2561111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5671615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8481063842773</t>
+    <t xml:space="preserve">85.6408386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822219848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7410507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2560882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5671691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8481140136719</t>
   </si>
   <si>
     <t xml:space="preserve">83.8147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">84.1892929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.282958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3130798339844</t>
+    <t xml:space="preserve">84.1893081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2829513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3130645751953</t>
   </si>
   <si>
     <t xml:space="preserve">88.1693344116211</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">89.4804000854492</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2596969604492</t>
+    <t xml:space="preserve">91.2597045898438</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6854858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1581039428711</t>
+    <t xml:space="preserve">91.6854782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1580963134766</t>
   </si>
   <si>
     <t xml:space="preserve">91.5437088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8348083496094</t>
+    <t xml:space="preserve">90.8348007202148</t>
   </si>
   <si>
     <t xml:space="preserve">90.5984954833984</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">88.8025894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">86.5340881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0786285400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3546676635742</t>
+    <t xml:space="preserve">86.5341033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0786361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3546600341797</t>
   </si>
   <si>
     <t xml:space="preserve">91.9690551757812</t>
@@ -1898,31 +1898,31 @@
     <t xml:space="preserve">93.1033096313477</t>
   </si>
   <si>
-    <t xml:space="preserve">95.5608520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4115371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8122100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0731811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8293609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3416976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.326652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6800537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2471771240234</t>
+    <t xml:space="preserve">95.5608444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4115524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8122024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3417053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.326644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.247184753418</t>
   </si>
   <si>
     <t xml:space="preserve">96.8841552734375</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">95.9389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">96.317024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.5060729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2622451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9786834716797</t>
+    <t xml:space="preserve">96.3170318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5060653686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2622375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9786758422852</t>
   </si>
   <si>
     <t xml:space="preserve">99.5307464599609</t>
@@ -1952,46 +1952,46 @@
     <t xml:space="preserve">98.3019638061523</t>
   </si>
   <si>
-    <t xml:space="preserve">97.3567581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2074432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1677169799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5457916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2225189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7499008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8444137573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4663314819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7896194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.082809448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475952148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1526641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.665000915527</t>
+    <t xml:space="preserve">97.3567504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2074508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.167724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5457992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2225112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7499084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4663391113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7896347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.082817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1526565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.799247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.665008544922</t>
   </si>
   <si>
     <t xml:space="preserve">100.097877502441</t>
@@ -2009,46 +2009,46 @@
     <t xml:space="preserve">102.36637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">102.17733001709</t>
+    <t xml:space="preserve">102.177337646484</t>
   </si>
   <si>
     <t xml:space="preserve">103.784194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">103.028038024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.003349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.137603759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.704727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.689674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.500625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.93350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.38143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5855331420898</t>
+    <t xml:space="preserve">103.028022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.003356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.137596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.704734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.689666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.500633239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.933494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.381423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5855407714844</t>
   </si>
   <si>
     <t xml:space="preserve">96.6951065063477</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1129379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0581359863281</t>
+    <t xml:space="preserve">98.112922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0581436157227</t>
   </si>
   <si>
     <t xml:space="preserve">100.948554992676</t>
@@ -2057,46 +2057,46 @@
     <t xml:space="preserve">100.286911010742</t>
   </si>
   <si>
-    <t xml:space="preserve">99.7197875976562</t>
+    <t xml:space="preserve">99.7197799682617</t>
   </si>
   <si>
     <t xml:space="preserve">100.854034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">99.6252670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4265975952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7101669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8594741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0957794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2848281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6156463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6382217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3471374511719</t>
+    <t xml:space="preserve">99.6252746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4266128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7101593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8594818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0957870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2848205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6156539916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5211181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6382293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3471298217773</t>
   </si>
   <si>
     <t xml:space="preserve">91.3074035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">92.2998733520508</t>
+    <t xml:space="preserve">92.2998809814453</t>
   </si>
   <si>
     <t xml:space="preserve">91.7327575683594</t>
@@ -2108,34 +2108,34 @@
     <t xml:space="preserve">93.1505661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3718185424805</t>
+    <t xml:space="preserve">95.3718109130859</t>
   </si>
   <si>
     <t xml:space="preserve">94.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">98.8691024780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9238891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.759521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.122550964355</t>
+    <t xml:space="preserve">98.8690948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9238739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.75951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.122535705566</t>
   </si>
   <si>
     <t xml:space="preserve">104.634887695312</t>
   </si>
   <si>
-    <t xml:space="preserve">105.95817565918</t>
+    <t xml:space="preserve">105.958168029785</t>
   </si>
   <si>
     <t xml:space="preserve">108.226692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">107.659553527832</t>
+    <t xml:space="preserve">107.659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">109.077377319336</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">112.574661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">113.803428649902</t>
+    <t xml:space="preserve">113.803443908691</t>
   </si>
   <si>
     <t xml:space="preserve">113.236312866211</t>
@@ -2153,46 +2153,46 @@
     <t xml:space="preserve">113.519866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">114.654121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.818489074707</t>
+    <t xml:space="preserve">114.65412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.818481445312</t>
   </si>
   <si>
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.206192016602</t>
+    <t xml:space="preserve">115.977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.206184387207</t>
   </si>
   <si>
     <t xml:space="preserve">117.017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">115.315773010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.370567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.425338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.644500732422</t>
+    <t xml:space="preserve">115.315780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.370544433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.425346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.644508361816</t>
   </si>
   <si>
     <t xml:space="preserve">111.251358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">110.589714050293</t>
+    <t xml:space="preserve">110.589706420898</t>
   </si>
   <si>
     <t xml:space="preserve">110.30615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">111.156845092773</t>
+    <t xml:space="preserve">111.156829833984</t>
   </si>
   <si>
     <t xml:space="preserve">111.723968505859</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">111.062324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">110.11710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.833549499512</t>
+    <t xml:space="preserve">110.117118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.833541870117</t>
   </si>
   <si>
     <t xml:space="preserve">108.51025390625</t>
@@ -2213,37 +2213,37 @@
     <t xml:space="preserve">111.913017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">112.29109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952743530273</t>
+    <t xml:space="preserve">112.291091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952751159668</t>
   </si>
   <si>
     <t xml:space="preserve">110.87328338623</t>
   </si>
   <si>
-    <t xml:space="preserve">109.455474853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.470520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.49520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.037651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.848609924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.793823242188</t>
+    <t xml:space="preserve">109.455467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.470512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.495193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.037643432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.848602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.793807983398</t>
   </si>
   <si>
     <t xml:space="preserve">106.430786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">109.171905517578</t>
+    <t xml:space="preserve">109.171890258789</t>
   </si>
   <si>
     <t xml:space="preserve">109.266418457031</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">105.769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">107.754081726074</t>
+    <t xml:space="preserve">107.754089355469</t>
   </si>
   <si>
     <t xml:space="preserve">108.415725708008</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">108.32120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">110.211631774902</t>
+    <t xml:space="preserve">110.211624145508</t>
   </si>
   <si>
     <t xml:space="preserve">114.276039123535</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
-    <t xml:space="preserve">109.928070068359</t>
+    <t xml:space="preserve">109.928077697754</t>
   </si>
   <si>
     <t xml:space="preserve">104.54035949707</t>
@@ -2285,19 +2285,19 @@
     <t xml:space="preserve">98.7745742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">106.808876037598</t>
+    <t xml:space="preserve">106.808868408203</t>
   </si>
   <si>
     <t xml:space="preserve">103.595146179199</t>
   </si>
   <si>
-    <t xml:space="preserve">101.893768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8143081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.132164001465</t>
+    <t xml:space="preserve">101.893775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8143005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.132171630859</t>
   </si>
   <si>
     <t xml:space="preserve">105.485572814941</t>
@@ -2306,52 +2306,52 @@
     <t xml:space="preserve">110.400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">108.888328552246</t>
+    <t xml:space="preserve">108.888336181641</t>
   </si>
   <si>
     <t xml:space="preserve">106.52530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">104.445838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.55541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.08699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.629447937012</t>
+    <t xml:space="preserve">104.445846557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.55542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.086990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.629440307617</t>
   </si>
   <si>
     <t xml:space="preserve">118.056884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">122.310325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.091171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.329574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.583023071289</t>
+    <t xml:space="preserve">122.310340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.32958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.5830078125</t>
   </si>
   <si>
     <t xml:space="preserve">145.089920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">144.239242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.959854125977</t>
+    <t xml:space="preserve">144.239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.959869384766</t>
   </si>
   <si>
     <t xml:space="preserve">150.383117675781</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">153.691345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">157.755752563477</t>
+    <t xml:space="preserve">157.755737304688</t>
   </si>
   <si>
     <t xml:space="preserve">157.944808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">153.313278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791305541992</t>
+    <t xml:space="preserve">153.313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.791320800781</t>
   </si>
   <si>
     <t xml:space="preserve">146.885818481445</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">146.507736206055</t>
   </si>
   <si>
-    <t xml:space="preserve">144.52278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.318710327148</t>
+    <t xml:space="preserve">144.522827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.318695068359</t>
   </si>
   <si>
     <t xml:space="preserve">147.641998291016</t>
   </si>
   <si>
-    <t xml:space="preserve">153.596832275391</t>
+    <t xml:space="preserve">153.596817016602</t>
   </si>
   <si>
     <t xml:space="preserve">151.706420898438</t>
   </si>
   <si>
-    <t xml:space="preserve">163.048934936523</t>
+    <t xml:space="preserve">163.048965454102</t>
   </si>
   <si>
     <t xml:space="preserve">167.302383422852</t>
@@ -2402,28 +2402,28 @@
     <t xml:space="preserve">174.10791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">174.675018310547</t>
+    <t xml:space="preserve">174.675033569336</t>
   </si>
   <si>
     <t xml:space="preserve">169.381866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">178.833953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.440841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.688827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.927215576172</t>
+    <t xml:space="preserve">178.833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.440811157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.688842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.927230834961</t>
   </si>
   <si>
     <t xml:space="preserve">186.206619262695</t>
   </si>
   <si>
-    <t xml:space="preserve">163.521545410156</t>
+    <t xml:space="preserve">163.521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">171.839401245117</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">171.55583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">169.098297119141</t>
+    <t xml:space="preserve">169.098281860352</t>
   </si>
   <si>
     <t xml:space="preserve">163.994140625</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">156.905059814453</t>
   </si>
   <si>
-    <t xml:space="preserve">150.855728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.651611328125</t>
+    <t xml:space="preserve">150.855697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.651596069336</t>
   </si>
   <si>
     <t xml:space="preserve">155.014633178711</t>
   </si>
   <si>
-    <t xml:space="preserve">158.6064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.850280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.510162353516</t>
+    <t xml:space="preserve">158.606460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.85026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.510147094727</t>
   </si>
   <si>
     <t xml:space="preserve">162.36572265625</t>
@@ -2471,61 +2471,61 @@
     <t xml:space="preserve">161.890411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">161.129898071289</t>
+    <t xml:space="preserve">161.129913330078</t>
   </si>
   <si>
     <t xml:space="preserve">159.133605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">162.270660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.118835449219</t>
+    <t xml:space="preserve">162.270629882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.118804931641</t>
   </si>
   <si>
     <t xml:space="preserve">164.457061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">162.936080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.320053100586</t>
+    <t xml:space="preserve">162.936065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.320037841797</t>
   </si>
   <si>
     <t xml:space="preserve">161.985473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">162.555816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.841018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.650909423828</t>
+    <t xml:space="preserve">162.555847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.841033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.350921630859</t>
+    <t xml:space="preserve">169.685501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.35090637207</t>
   </si>
   <si>
     <t xml:space="preserve">163.031127929688</t>
   </si>
   <si>
-    <t xml:space="preserve">164.361999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.122497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.305236816406</t>
+    <t xml:space="preserve">164.362014770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.122512817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.305252075195</t>
   </si>
   <si>
     <t xml:space="preserve">169.400299072266</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">169.495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.358291625977</t>
+    <t xml:space="preserve">166.358306884766</t>
   </si>
   <si>
     <t xml:space="preserve">160.939788818359</t>
   </si>
   <si>
-    <t xml:space="preserve">154.66569519043</t>
+    <t xml:space="preserve">154.665710449219</t>
   </si>
   <si>
     <t xml:space="preserve">162.175598144531</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">159.228668212891</t>
   </si>
   <si>
-    <t xml:space="preserve">157.802749633789</t>
+    <t xml:space="preserve">157.802734375</t>
   </si>
   <si>
     <t xml:space="preserve">152.669403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">149.817565917969</t>
+    <t xml:space="preserve">149.81755065918</t>
   </si>
   <si>
     <t xml:space="preserve">146.77555847168</t>
@@ -2573,85 +2573,85 @@
     <t xml:space="preserve">145.254577636719</t>
   </si>
   <si>
-    <t xml:space="preserve">149.72248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.289169311523</t>
+    <t xml:space="preserve">149.722473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.289138793945</t>
   </si>
   <si>
     <t xml:space="preserve">151.623733520508</t>
   </si>
   <si>
-    <t xml:space="preserve">148.391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.7607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.243469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.190399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.855834960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.950881958008</t>
+    <t xml:space="preserve">148.3916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.760772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.243499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.190383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.855819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.950897216797</t>
   </si>
   <si>
     <t xml:space="preserve">155.426193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">155.806457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.418807983398</t>
+    <t xml:space="preserve">155.806442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.418792724609</t>
   </si>
   <si>
     <t xml:space="preserve">145.634826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">138.600234985352</t>
+    <t xml:space="preserve">138.600250244141</t>
   </si>
   <si>
     <t xml:space="preserve">144.018768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">144.589157104492</t>
+    <t xml:space="preserve">144.589126586914</t>
   </si>
   <si>
     <t xml:space="preserve">143.54345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">135.55827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.797760009766</t>
+    <t xml:space="preserve">135.558288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.797775268555</t>
   </si>
   <si>
     <t xml:space="preserve">137.36442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">137.174301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.779251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.258270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.060745239258</t>
+    <t xml:space="preserve">137.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.779266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.258285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.060760498047</t>
   </si>
   <si>
     <t xml:space="preserve">147.726181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.247161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.95458984375</t>
+    <t xml:space="preserve">149.247177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.954574584961</t>
   </si>
   <si>
     <t xml:space="preserve">150.387924194336</t>
@@ -2660,70 +2660,70 @@
     <t xml:space="preserve">161.03483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">160.654602050781</t>
+    <t xml:space="preserve">160.654586791992</t>
   </si>
   <si>
     <t xml:space="preserve">162.080535888672</t>
   </si>
   <si>
-    <t xml:space="preserve">161.795333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.411392211914</t>
+    <t xml:space="preserve">161.795349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.411376953125</t>
   </si>
   <si>
     <t xml:space="preserve">168.069427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">174.91389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.670669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.487945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.716339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.712677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.24104309082</t>
+    <t xml:space="preserve">174.913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.29411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.670654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.487976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.716354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.712646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.241058349609</t>
   </si>
   <si>
     <t xml:space="preserve">181.853393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">179.666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.039840698242</t>
+    <t xml:space="preserve">179.666976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.039825439453</t>
   </si>
   <si>
     <t xml:space="preserve">181.663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">185.275634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.089218139648</t>
+    <t xml:space="preserve">185.275619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.08918762207</t>
   </si>
   <si>
     <t xml:space="preserve">181.568222045898</t>
   </si>
   <si>
-    <t xml:space="preserve">179.286727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.050933837891</t>
+    <t xml:space="preserve">179.286743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.050918579102</t>
   </si>
   <si>
     <t xml:space="preserve">179.191665649414</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">177.860809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">184.610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.838592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.264526367188</t>
+    <t xml:space="preserve">184.61018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.838607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.264541625977</t>
   </si>
   <si>
     <t xml:space="preserve">159.703979492188</t>
@@ -2750,19 +2750,19 @@
     <t xml:space="preserve">163.88671875</t>
   </si>
   <si>
-    <t xml:space="preserve">165.21760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.932373046875</t>
+    <t xml:space="preserve">165.217559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.932388305664</t>
   </si>
   <si>
     <t xml:space="preserve">164.076843261719</t>
   </si>
   <si>
-    <t xml:space="preserve">156.947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.844711303711</t>
+    <t xml:space="preserve">156.947204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.8447265625</t>
   </si>
   <si>
     <t xml:space="preserve">164.266967773438</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">160.084228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745956420898</t>
+    <t xml:space="preserve">162.745971679688</t>
   </si>
   <si>
     <t xml:space="preserve">160.179290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">159.32373046875</t>
+    <t xml:space="preserve">159.323745727539</t>
   </si>
   <si>
     <t xml:space="preserve">158.468170166016</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">163.221267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">159.038558959961</t>
+    <t xml:space="preserve">159.038543701172</t>
   </si>
   <si>
     <t xml:space="preserve">159.608917236328</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">153.810134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">152.859497070312</t>
+    <t xml:space="preserve">152.859527587891</t>
   </si>
   <si>
     <t xml:space="preserve">151.528656005859</t>
   </si>
   <si>
-    <t xml:space="preserve">155.616333007812</t>
+    <t xml:space="preserve">155.616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">154.475570678711</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">154.570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">157.992858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.826202392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.970672607422</t>
+    <t xml:space="preserve">157.992874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.826217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">179.001556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">168.924957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.68180847168</t>
+    <t xml:space="preserve">168.924987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.681793212891</t>
   </si>
   <si>
     <t xml:space="preserve">171.111419677734</t>
@@ -2852,37 +2852,37 @@
     <t xml:space="preserve">170.541030883789</t>
   </si>
   <si>
-    <t xml:space="preserve">167.784255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.499053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.255844116211</t>
+    <t xml:space="preserve">167.784240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.499069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.255859375</t>
   </si>
   <si>
     <t xml:space="preserve">173.868194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">173.202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.389175415039</t>
+    <t xml:space="preserve">173.202774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.389190673828</t>
   </si>
   <si>
     <t xml:space="preserve">176.434875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">176.149688720703</t>
+    <t xml:space="preserve">176.149673461914</t>
   </si>
   <si>
     <t xml:space="preserve">177.195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">174.438568115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.18669128418</t>
+    <t xml:space="preserve">174.438583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.186706542969</t>
   </si>
   <si>
     <t xml:space="preserve">151.813842773438</t>
@@ -2894,52 +2894,52 @@
     <t xml:space="preserve">154.380508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">155.901504516602</t>
+    <t xml:space="preserve">155.901489257812</t>
   </si>
   <si>
     <t xml:space="preserve">157.137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">154.000259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.197784423828</t>
+    <t xml:space="preserve">154.000274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.197799682617</t>
   </si>
   <si>
     <t xml:space="preserve">149.057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">147.155807495117</t>
+    <t xml:space="preserve">147.155822753906</t>
   </si>
   <si>
     <t xml:space="preserve">132.706405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">135.082977294922</t>
+    <t xml:space="preserve">135.082946777344</t>
   </si>
   <si>
     <t xml:space="preserve">138.695297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">134.987884521484</t>
+    <t xml:space="preserve">134.987899780273</t>
   </si>
   <si>
     <t xml:space="preserve">133.181716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">136.033584594727</t>
+    <t xml:space="preserve">136.033569335938</t>
   </si>
   <si>
     <t xml:space="preserve">133.276763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">134.037261962891</t>
+    <t xml:space="preserve">134.03727722168</t>
   </si>
   <si>
     <t xml:space="preserve">133.086654663086</t>
   </si>
   <si>
-    <t xml:space="preserve">135.273071289062</t>
+    <t xml:space="preserve">135.273056030273</t>
   </si>
   <si>
     <t xml:space="preserve">132.136032104492</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">130.90022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">130.044677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.848999023438</t>
+    <t xml:space="preserve">130.044692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.848983764648</t>
   </si>
   <si>
     <t xml:space="preserve">135.463195800781</t>
   </si>
   <si>
-    <t xml:space="preserve">133.229248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.492218017578</t>
+    <t xml:space="preserve">133.229232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.492233276367</t>
   </si>
   <si>
     <t xml:space="preserve">143.59098815918</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">148.20149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.058883666992</t>
+    <t xml:space="preserve">148.201477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.05891418457</t>
   </si>
   <si>
     <t xml:space="preserve">146.300247192383</t>
   </si>
   <si>
-    <t xml:space="preserve">145.01692199707</t>
+    <t xml:space="preserve">145.016937255859</t>
   </si>
   <si>
     <t xml:space="preserve">144.874328613281</t>
@@ -2993,28 +2993,28 @@
     <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">133.324310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.274932861328</t>
+    <t xml:space="preserve">133.324295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.274917602539</t>
   </si>
   <si>
     <t xml:space="preserve">133.894683837891</t>
   </si>
   <si>
-    <t xml:space="preserve">134.227386474609</t>
+    <t xml:space="preserve">134.227401733398</t>
   </si>
   <si>
     <t xml:space="preserve">131.660720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">133.847152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.605804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.423080444336</t>
+    <t xml:space="preserve">133.84716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.60578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.423065185547</t>
   </si>
   <si>
     <t xml:space="preserve">128.333557128906</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">136.889129638672</t>
   </si>
   <si>
-    <t xml:space="preserve">137.031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.983871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.744537353516</t>
+    <t xml:space="preserve">137.031707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.983856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.744552612305</t>
   </si>
   <si>
     <t xml:space="preserve">137.845397949219</t>
@@ -3056,28 +3056,28 @@
     <t xml:space="preserve">135.978729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">133.05908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.963348388672</t>
+    <t xml:space="preserve">133.059097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.963363647461</t>
   </si>
   <si>
     <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">136.218048095703</t>
+    <t xml:space="preserve">136.218032836914</t>
   </si>
   <si>
     <t xml:space="preserve">137.510345458984</t>
   </si>
   <si>
-    <t xml:space="preserve">138.659057617188</t>
+    <t xml:space="preserve">138.659072875977</t>
   </si>
   <si>
     <t xml:space="preserve">139.185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">143.2060546875</t>
+    <t xml:space="preserve">143.206039428711</t>
   </si>
   <si>
     <t xml:space="preserve">144.306900024414</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">144.019714355469</t>
   </si>
   <si>
-    <t xml:space="preserve">146.269287109375</t>
+    <t xml:space="preserve">146.269271850586</t>
   </si>
   <si>
     <t xml:space="preserve">145.790649414062</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">143.397491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">147.992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.428237915039</t>
+    <t xml:space="preserve">147.99235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.42822265625</t>
   </si>
   <si>
     <t xml:space="preserve">150.289764404297</t>
@@ -3119,40 +3119,40 @@
     <t xml:space="preserve">152.682922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768402099609</t>
+    <t xml:space="preserve">150.76838684082</t>
   </si>
   <si>
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.879470825195</t>
+    <t xml:space="preserve">149.906890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.879486083984</t>
   </si>
   <si>
     <t xml:space="preserve">156.320495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">152.395736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.783752441406</t>
+    <t xml:space="preserve">152.395721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">155.123916625977</t>
   </si>
   <si>
-    <t xml:space="preserve">155.458969116211</t>
+    <t xml:space="preserve">155.458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">155.650436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.081192016602</t>
+    <t xml:space="preserve">155.650421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.081207275391</t>
   </si>
   <si>
     <t xml:space="preserve">158.905090332031</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">163.643539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">164.983688354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.729019165039</t>
+    <t xml:space="preserve">164.983703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.72900390625</t>
   </si>
   <si>
     <t xml:space="preserve">160.915344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">162.351226806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.07942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.834976196289</t>
+    <t xml:space="preserve">162.35124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.079437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.834991455078</t>
   </si>
   <si>
     <t xml:space="preserve">168.908462524414</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">164.600799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">168.142639160156</t>
+    <t xml:space="preserve">168.142654418945</t>
   </si>
   <si>
     <t xml:space="preserve">168.860595703125</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">166.036682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">168.669143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.334121704102</t>
+    <t xml:space="preserve">168.669158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.334106445312</t>
   </si>
   <si>
     <t xml:space="preserve">169.052062988281</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">171.158020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">170.248641967773</t>
+    <t xml:space="preserve">170.248626708984</t>
   </si>
   <si>
     <t xml:space="preserve">171.349472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">176.0400390625</t>
+    <t xml:space="preserve">176.040054321289</t>
   </si>
   <si>
     <t xml:space="preserve">176.949447631836</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">179.534057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">178.050308227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.475921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.810974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.352844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.740875244141</t>
+    <t xml:space="preserve">178.05029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.475936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.810989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.352828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.740844726562</t>
   </si>
   <si>
     <t xml:space="preserve">184.990432739258</t>
@@ -3254,37 +3254,37 @@
     <t xml:space="preserve">190.016036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">192.409194946289</t>
+    <t xml:space="preserve">192.4091796875</t>
   </si>
   <si>
     <t xml:space="preserve">193.270721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">195.568161010742</t>
+    <t xml:space="preserve">195.568145751953</t>
   </si>
   <si>
     <t xml:space="preserve">191.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">196.908325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.812606811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.386932373047</t>
+    <t xml:space="preserve">196.908309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.386947631836</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
   </si>
   <si>
-    <t xml:space="preserve">193.175018310547</t>
+    <t xml:space="preserve">193.175003051758</t>
   </si>
   <si>
     <t xml:space="preserve">190.351089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">192.026306152344</t>
+    <t xml:space="preserve">192.026290893555</t>
   </si>
   <si>
     <t xml:space="preserve">193.940811157227</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">187.479309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">180.539169311523</t>
+    <t xml:space="preserve">180.539184570312</t>
   </si>
   <si>
     <t xml:space="preserve">174.987060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">174.077682495117</t>
+    <t xml:space="preserve">174.077667236328</t>
   </si>
   <si>
     <t xml:space="preserve">173.599044799805</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">167.664016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">164.505081176758</t>
+    <t xml:space="preserve">164.505065917969</t>
   </si>
   <si>
     <t xml:space="preserve">165.462341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">162.782012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.404220581055</t>
+    <t xml:space="preserve">162.781997680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.404205322266</t>
   </si>
   <si>
     <t xml:space="preserve">164.744400024414</t>
@@ -3332,34 +3332,34 @@
     <t xml:space="preserve">162.111923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">166.515319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.870849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.25373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.402465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684539794922</t>
+    <t xml:space="preserve">166.515289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.253753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.402481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684524536133</t>
   </si>
   <si>
     <t xml:space="preserve">173.742614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">177.715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.448577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.826354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.88444519043</t>
+    <t xml:space="preserve">177.715240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.44856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.82633972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.884460449219</t>
   </si>
   <si>
     <t xml:space="preserve">182.83659362793</t>
@@ -3368,10 +3368,10 @@
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.000686645508</t>
+    <t xml:space="preserve">187.096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.000671386719</t>
   </si>
   <si>
     <t xml:space="preserve">188.723739624023</t>
@@ -3386,43 +3386,43 @@
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.69987487793</t>
+    <t xml:space="preserve">174.699905395508</t>
   </si>
   <si>
     <t xml:space="preserve">176.231506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">175.561401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.964828491211</t>
+    <t xml:space="preserve">175.561416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.093048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.964813232422</t>
   </si>
   <si>
     <t xml:space="preserve">180.874206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">183.50666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.896469116211</t>
+    <t xml:space="preserve">183.506652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.896453857422</t>
   </si>
   <si>
     <t xml:space="preserve">176.614395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">175.800735473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.636672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.865707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.294738769531</t>
+    <t xml:space="preserve">175.800704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.636657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.86572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.294723510742</t>
   </si>
   <si>
     <t xml:space="preserve">177.188766479492</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">175.082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">170.296493530273</t>
+    <t xml:space="preserve">170.296463012695</t>
   </si>
   <si>
     <t xml:space="preserve">169.14778137207</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">164.935836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">167.472564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.392227172852</t>
+    <t xml:space="preserve">167.472579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">172.306747436523</t>
   </si>
   <si>
-    <t xml:space="preserve">172.928970336914</t>
+    <t xml:space="preserve">172.928955078125</t>
   </si>
   <si>
     <t xml:space="preserve">168.764877319336</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">172.785369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">170.535797119141</t>
+    <t xml:space="preserve">170.53581237793</t>
   </si>
   <si>
     <t xml:space="preserve">152.060699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">153.688034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.400863647461</t>
+    <t xml:space="preserve">153.688049316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.400848388672</t>
   </si>
   <si>
     <t xml:space="preserve">154.932479858398</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">159.240158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">157.947845458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.293121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.22477722168</t>
+    <t xml:space="preserve">157.947830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.293106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.224761962891</t>
   </si>
   <si>
     <t xml:space="preserve">152.15641784668</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">141.770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">143.780395507812</t>
+    <t xml:space="preserve">143.780380249023</t>
   </si>
   <si>
     <t xml:space="preserve">147.609436035156</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">141.387252807617</t>
   </si>
   <si>
-    <t xml:space="preserve">139.855651855469</t>
+    <t xml:space="preserve">139.85563659668</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
@@ -3524,49 +3524,49 @@
     <t xml:space="preserve">138.946228027344</t>
   </si>
   <si>
-    <t xml:space="preserve">140.717178344727</t>
+    <t xml:space="preserve">140.717163085938</t>
   </si>
   <si>
     <t xml:space="preserve">128.94287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">126.884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.325775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.144561767578</t>
+    <t xml:space="preserve">126.884750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.325790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.048843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.144577026367</t>
   </si>
   <si>
     <t xml:space="preserve">132.006103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">127.698440551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.418144226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.289916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.662582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.934387207031</t>
+    <t xml:space="preserve">127.698425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.41813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.289924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.662574768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.934379577637</t>
   </si>
   <si>
     <t xml:space="preserve">114.631843566895</t>
@@ -3584,73 +3584,73 @@
     <t xml:space="preserve">112.286560058594</t>
   </si>
   <si>
-    <t xml:space="preserve">112.430145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.211326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.136085510254</t>
+    <t xml:space="preserve">112.430137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.211318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.136093139648</t>
   </si>
   <si>
     <t xml:space="preserve">123.10359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">122.864273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.93775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.124084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.773666381836</t>
+    <t xml:space="preserve">122.864288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.124099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.77367401123</t>
   </si>
   <si>
     <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">120.08821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.242050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.503623962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.806167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541229248047</t>
+    <t xml:space="preserve">120.088218688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.242057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.503616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.806159973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541236877441</t>
   </si>
   <si>
     <t xml:space="preserve">117.599349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">121.859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.71891784668</t>
+    <t xml:space="preserve">121.859153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.718933105469</t>
   </si>
   <si>
     <t xml:space="preserve">132.293273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">126.693305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.59757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.448883056641</t>
+    <t xml:space="preserve">126.693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.448890686035</t>
   </si>
   <si>
     <t xml:space="preserve">133.824890136719</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">135.73942565918</t>
   </si>
   <si>
-    <t xml:space="preserve">135.835159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.329147338867</t>
+    <t xml:space="preserve">135.83512878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.329132080078</t>
   </si>
   <si>
     <t xml:space="preserve">139.616317749023</t>
@@ -3671,43 +3671,43 @@
     <t xml:space="preserve">142.105194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">139.041946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.170181274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.260803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.628341674805</t>
+    <t xml:space="preserve">139.041976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.170166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.260787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.628326416016</t>
   </si>
   <si>
     <t xml:space="preserve">129.038604736328</t>
   </si>
   <si>
-    <t xml:space="preserve">129.086486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.559967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.416381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.454010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.539489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.997611999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.7001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.254066467285</t>
+    <t xml:space="preserve">129.086471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.559982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.453994750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.539482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.997619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.700187683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.254051208496</t>
   </si>
   <si>
     <t xml:space="preserve">118.652328491211</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">119.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">118.173706054688</t>
+    <t xml:space="preserve">118.173713684082</t>
   </si>
   <si>
     <t xml:space="preserve">117.647216796875</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">114.392524719238</t>
   </si>
   <si>
-    <t xml:space="preserve">114.823295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.493370056152</t>
+    <t xml:space="preserve">114.823287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.493385314941</t>
   </si>
   <si>
     <t xml:space="preserve">109.271186828613</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">106.590858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">109.654090881348</t>
+    <t xml:space="preserve">109.654098510742</t>
   </si>
   <si>
     <t xml:space="preserve">107.165214538574</t>
@@ -3746,40 +3746,40 @@
     <t xml:space="preserve">114.009620666504</t>
   </si>
   <si>
-    <t xml:space="preserve">114.871147155762</t>
+    <t xml:space="preserve">114.871154785156</t>
   </si>
   <si>
     <t xml:space="preserve">113.435272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">110.563491821289</t>
+    <t xml:space="preserve">110.563484191895</t>
   </si>
   <si>
     <t xml:space="preserve">113.052360534668</t>
   </si>
   <si>
-    <t xml:space="preserve">114.057487487793</t>
+    <t xml:space="preserve">114.057479858398</t>
   </si>
   <si>
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884498596191</t>
+    <t xml:space="preserve">111.884506225586</t>
   </si>
   <si>
     <t xml:space="preserve">111.932792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">113.381454467773</t>
+    <t xml:space="preserve">113.381446838379</t>
   </si>
   <si>
     <t xml:space="preserve">117.292816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">118.403450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.306884765625</t>
+    <t xml:space="preserve">118.403457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.30687713623</t>
   </si>
   <si>
     <t xml:space="preserve">116.761642456055</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">115.071548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">111.787933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.918724060059</t>
+    <t xml:space="preserve">111.787925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.918731689453</t>
   </si>
   <si>
     <t xml:space="preserve">107.683403015137</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">109.904678344727</t>
   </si>
   <si>
-    <t xml:space="preserve">114.685241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.80199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.912620544434</t>
+    <t xml:space="preserve">114.685234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.801986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.912612915039</t>
   </si>
   <si>
     <t xml:space="preserve">113.526321411133</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">120.190132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">123.377166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.797706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.866180419922</t>
+    <t xml:space="preserve">123.377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.797714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.866172790527</t>
   </si>
   <si>
     <t xml:space="preserve">120.914459228516</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">122.025093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">126.56421661377</t>
+    <t xml:space="preserve">126.564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">127.578285217285</t>
@@ -3860,10 +3860,10 @@
     <t xml:space="preserve">129.799545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">130.668746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.151626586914</t>
+    <t xml:space="preserve">130.668731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.151641845703</t>
   </si>
   <si>
     <t xml:space="preserve">131.537933349609</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">125.598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">127.964584350586</t>
+    <t xml:space="preserve">127.964576721191</t>
   </si>
   <si>
     <t xml:space="preserve">124.970687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">127.916297912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.433410644531</t>
+    <t xml:space="preserve">127.916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.674850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.433403015137</t>
   </si>
   <si>
     <t xml:space="preserve">129.413238525391</t>
@@ -3893,25 +3893,25 @@
     <t xml:space="preserve">135.497589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">136.077041625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.841720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.785507202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.936462402344</t>
+    <t xml:space="preserve">136.077056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.841735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.785491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.936454772949</t>
   </si>
   <si>
     <t xml:space="preserve">130.234146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">130.958465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.861892700195</t>
+    <t xml:space="preserve">130.958480834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.861907958984</t>
   </si>
   <si>
     <t xml:space="preserve">128.640625</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">135.787338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">132.213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.910186767578</t>
+    <t xml:space="preserve">132.213973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.910171508789</t>
   </si>
   <si>
     <t xml:space="preserve">131.924240112305</t>
@@ -3944,31 +3944,31 @@
     <t xml:space="preserve">130.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">132.02082824707</t>
+    <t xml:space="preserve">132.020812988281</t>
   </si>
   <si>
     <t xml:space="preserve">131.489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">132.310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.868011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.888168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.171783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.061172485352</t>
+    <t xml:space="preserve">132.310562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.515922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.868003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.467643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.888191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.171813964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.061157226562</t>
   </si>
   <si>
     <t xml:space="preserve">128.93034362793</t>
@@ -3986,19 +3986,19 @@
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.11555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.397338867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.721298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.135734558105</t>
+    <t xml:space="preserve">125.115562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.397331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.721305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.135726928711</t>
   </si>
   <si>
     <t xml:space="preserve">111.449913024902</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">112.463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">111.643051147461</t>
+    <t xml:space="preserve">111.643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779983520508</t>
+    <t xml:space="preserve">107.779975891113</t>
   </si>
   <si>
     <t xml:space="preserve">110.870445251465</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">110.097831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">113.816040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.305038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.50431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.132064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.974975585938</t>
+    <t xml:space="preserve">113.816047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.305046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.504302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.132057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.974967956543</t>
   </si>
   <si>
     <t xml:space="preserve">123.763473510742</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">121.687072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">124.58438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.64673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.586212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.344787597656</t>
+    <t xml:space="preserve">124.584381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.646728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.586227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.344772338867</t>
   </si>
   <si>
     <t xml:space="preserve">121.300765991211</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">126.660789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">124.922416687012</t>
+    <t xml:space="preserve">124.922409057617</t>
   </si>
   <si>
     <t xml:space="preserve">122.314826965332</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.765319824219</t>
+    <t xml:space="preserve">130.76530456543</t>
   </si>
   <si>
     <t xml:space="preserve">128.302612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">126.612518310547</t>
+    <t xml:space="preserve">126.612503051758</t>
   </si>
   <si>
     <t xml:space="preserve">128.206024169922</t>
@@ -4106,55 +4106,55 @@
     <t xml:space="preserve">124.487808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">127.240257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.316665649414</t>
+    <t xml:space="preserve">127.240249633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">128.157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">125.260429382324</t>
+    <t xml:space="preserve">125.26042175293</t>
   </si>
   <si>
     <t xml:space="preserve">129.509811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">131.682800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.847839355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.067268371582</t>
+    <t xml:space="preserve">131.682815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.84782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.067276000977</t>
   </si>
   <si>
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.42546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.783645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.522041320801</t>
+    <t xml:space="preserve">123.425468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.783653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.522033691406</t>
   </si>
   <si>
     <t xml:space="preserve">123.039154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">122.652847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.874122619629</t>
+    <t xml:space="preserve">122.652854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.62654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.874114990234</t>
   </si>
   <si>
     <t xml:space="preserve">125.405296325684</t>
@@ -4169,13 +4169,13 @@
     <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">121.880226135254</t>
+    <t xml:space="preserve">121.880218505859</t>
   </si>
   <si>
     <t xml:space="preserve">122.218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">120.141845703125</t>
+    <t xml:space="preserve">120.14183807373</t>
   </si>
   <si>
     <t xml:space="preserve">125.550155639648</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">115.168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.188293457031</t>
+    <t xml:space="preserve">113.188285827637</t>
   </si>
   <si>
     <t xml:space="preserve">115.651008605957</t>
@@ -4211,34 +4211,34 @@
     <t xml:space="preserve">117.196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">117.775695800781</t>
+    <t xml:space="preserve">117.775703430176</t>
   </si>
   <si>
     <t xml:space="preserve">116.906509399414</t>
   </si>
   <si>
-    <t xml:space="preserve">114.250648498535</t>
+    <t xml:space="preserve">114.250640869141</t>
   </si>
   <si>
     <t xml:space="preserve">112.415679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">113.23657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.31909942627</t>
+    <t xml:space="preserve">113.236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.319107055664</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.077667236328</t>
+    <t xml:space="preserve">112.077659606934</t>
   </si>
   <si>
     <t xml:space="preserve">109.42179107666</t>
   </si>
   <si>
-    <t xml:space="preserve">111.063606262207</t>
+    <t xml:space="preserve">111.063598632812</t>
   </si>
   <si>
     <t xml:space="preserve">110.242698669434</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">106.186454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">108.649169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.842330932617</t>
+    <t xml:space="preserve">108.64917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.842323303223</t>
   </si>
   <si>
     <t xml:space="preserve">108.118003845215</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">105.993301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">104.303207397461</t>
+    <t xml:space="preserve">104.303199768066</t>
   </si>
   <si>
     <t xml:space="preserve">104.013473510742</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">97.7359619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9431838989258</t>
+    <t xml:space="preserve">98.9431762695312</t>
   </si>
   <si>
     <t xml:space="preserve">97.5911026000977</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">98.5568771362305</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6455001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.5770416259766</t>
+    <t xml:space="preserve">94.6455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5770492553711</t>
   </si>
   <si>
     <t xml:space="preserve">94.6648178100586</t>
@@ -4307,22 +4307,22 @@
     <t xml:space="preserve">95.070442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">93.737678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6797256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2100601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7851028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7078552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9887847900391</t>
+    <t xml:space="preserve">93.7376708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6797332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2100524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7078475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9887771606445</t>
   </si>
   <si>
     <t xml:space="preserve">93.5252075195312</t>
@@ -4334,22 +4334,22 @@
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5340118408203</t>
+    <t xml:space="preserve">93.8342666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5340042114258</t>
   </si>
   <si>
     <t xml:space="preserve">95.9589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1819229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1582183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1090774536133</t>
+    <t xml:space="preserve">94.1819305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1582107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1090698242188</t>
   </si>
   <si>
     <t xml:space="preserve">94.3750915527344</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">98.0739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1222686767578</t>
+    <t xml:space="preserve">98.1222763061523</t>
   </si>
   <si>
     <t xml:space="preserve">98.8948974609375</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">100.408088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2853927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299819946289</t>
+    <t xml:space="preserve">99.2853851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299743652344</t>
   </si>
   <si>
     <t xml:space="preserve">96.8642730712891</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">95.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6384124755859</t>
+    <t xml:space="preserve">94.6384048461914</t>
   </si>
   <si>
     <t xml:space="preserve">94.4236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0679550170898</t>
+    <t xml:space="preserve">95.0679626464844</t>
   </si>
   <si>
     <t xml:space="preserve">95.1265411376953</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">95.4389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3579559326172</t>
+    <t xml:space="preserve">98.3579483032227</t>
   </si>
   <si>
     <t xml:space="preserve">96.6104431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4779968261719</t>
+    <t xml:space="preserve">95.4779891967773</t>
   </si>
   <si>
     <t xml:space="preserve">94.7946090698242</t>
@@ -4469,16 +4469,16 @@
     <t xml:space="preserve">90.8700561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4404983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0848388671875</t>
+    <t xml:space="preserve">90.4405059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.084831237793</t>
   </si>
   <si>
     <t xml:space="preserve">91.5534362792969</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">90.1280975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7054214477539</t>
+    <t xml:space="preserve">92.7054138183594</t>
   </si>
   <si>
     <t xml:space="preserve">92.1196670532227</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5729598999023</t>
+    <t xml:space="preserve">91.5729675292969</t>
   </si>
   <si>
     <t xml:space="preserve">90.0109405517578</t>
@@ -4523,954 +4523,957 @@
     <t xml:space="preserve">91.7877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2716522216797</t>
+    <t xml:space="preserve">93.2716445922852</t>
   </si>
   <si>
     <t xml:space="preserve">93.6816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3091278076172</t>
+    <t xml:space="preserve">98.3091354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6270904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9397201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8030395507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7682113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5492172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6273193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.11279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1365280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1016998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6679382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3164825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7375946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9676818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8114700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8225708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4626846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0721740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1238784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2800827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6790161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6357498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5032958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.303825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9328536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8003921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3681793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1755828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4853286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.9581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2314987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5090713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8563079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3053817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6373138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7824249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4378433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5175094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3961410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2008895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.673713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2678985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6193466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6932373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2985153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8146057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4436264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.131217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8800506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3206939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0974807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5006408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7892990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1185684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8394393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2969512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3096008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6526184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3792724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8520889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4183120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.98876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5201644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1380996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1143569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8758392333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.5243835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2942962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2663345336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8589553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6093521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9064483642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3402252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9703369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7180709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.980339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1518402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4600296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2996063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9481582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9872055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0262603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8436584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6135787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2774276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4294128417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7808685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2341613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.121223449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9106674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1296539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9037933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3138198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4742431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.6304397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3877105712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3486557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8605270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4547119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9428405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1966705322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.9344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.055778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6958923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7001113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7196350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2578964233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1170120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2647705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7138519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9286270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3302230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.388801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3149108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2843017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8310012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4753341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4125518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5017395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5645217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.369270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5423431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4515838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6399765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9259719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0863952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3750534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1338806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9275360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3222579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7238464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6721420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2858581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4098815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.4531555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0151672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6858978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5840530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7402496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4362869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6468505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9550247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8352203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7724304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6510543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1043548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2004241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9437026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.749778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7484588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1389617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6002044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1460113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0993728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0598907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5733261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.375846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4789733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.380241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6918106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.244743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2321319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4296035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.268890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9287796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1827545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7439270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9342727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1388702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5788116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0922470092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3868179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7494049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.675895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0834655761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3006973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1032104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2628479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0796356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1657562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8624038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6523132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0275192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3308639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8739318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.219512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.466361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.515731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.342391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.046173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.490501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.082931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1191253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7258224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6764526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9359130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8865432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2249984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3632354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8371734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5607070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1855087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.120780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.700592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.910682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.305633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.971580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.317161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.687973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8245620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.94743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.651222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.762580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.293022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.10816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.194282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.404373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.008323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.576622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.786712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.625984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.93482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.749961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.589241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.996810913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.095542907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.24365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.428512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.503120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.713203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.23104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7384414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4027328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2815017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.170143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.748863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.575523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.118591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.105972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.526161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.699501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.033561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.094451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.045082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.403282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.218421936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.465270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.527252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.836082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.391754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.638603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.565093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.367622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9726715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9852828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1262588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.663833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.144912719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.267791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.05770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.477882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.860214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.441131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.280403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.55248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.861312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0840225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.632568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3237380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7186965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6594467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.009422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0346527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.4745864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1964721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2035980224609</t>
   </si>
   <si>
     <t xml:space="preserve">99.627082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9397201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8030395507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7682113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5492248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6273193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1127853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1365280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1016998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6679306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3164825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7375946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9676818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8225708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4626846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0721817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1238784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2800827026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6790161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6357498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.503288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.303825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9328460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8003921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3681793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1755828857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2077560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4853286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.9581527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2314987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5090713500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8563079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3053894042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6373138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7824249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4378433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4700164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5175094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3961410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.673713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2678985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6193466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6932373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2985153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8145980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4436264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.1312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8800506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3206939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0974807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7391586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5006408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.789306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1185684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8394393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2969436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3096008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6526184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3792724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8520889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6916732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4183197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.98876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5201644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1380996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1143569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8758392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.5243835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2942962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2663345336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6985397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8589630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6093521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9064407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3402252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9703369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7180709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.980339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1518402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4600296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2996063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9481582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9871978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8436584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6135711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2774276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7808609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2341613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5117340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.121223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9106674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9037933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3138198852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4742431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6304397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3877029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3486557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8605270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0014114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.454719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9428405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1966705322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9344100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0557708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8953552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6958923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7001037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7196350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2579040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1170120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2647705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7138519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9286270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3302230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.388801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3149108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.284309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7096405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8310089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4753341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4125442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5017395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5645217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.369270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5423431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2605667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6399765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9259796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0863952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6177825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3750534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1338806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9275283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3222579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7238464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6721496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2858581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4098892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4531555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0151672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6858978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5840454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7402496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4362869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.646842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9550247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8352203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7724304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6510620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1043548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2004241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9437026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.749778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7484588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1389617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6002044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1460113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0598907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5733261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.375846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4789733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.380241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6918106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.244743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2321319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4296035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.268890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9287796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1827545166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7439270019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9342727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1388702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5788116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0922470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3868179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7494049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.675895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0834655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3006973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1032104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2628479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0796356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1657562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.8624038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6523132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0275192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3308639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8739318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0077743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.219512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.466361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.515731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.342391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.046173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.490501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.082931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1191253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7258224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9359130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8865432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2249984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3632354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8371734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5607070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1855087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.120780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.700592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.910682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.971580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.317161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.687973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8245620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.94743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.651222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.762580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.293022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.10816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.194282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.404373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.008323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.576622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.786712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.625984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.93482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.749961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.095542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.24365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.428512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.503120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.23104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4027328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2815017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.170143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.748863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.575523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.118591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.105972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.526161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.699501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.033561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.094451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.045082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.403282165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.218421936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.465270996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.527252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.836082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.391754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.638603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.565093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.367622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9726715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9852828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1262588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.663833618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.144912719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.267791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.05770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.477882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.860214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.441131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.280403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.55248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.861312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0840225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.632568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3237380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7186965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6594467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.009422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0346527099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5283508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.4745864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1964721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2035980224609</t>
-  </si>
-  <si>
     <t xml:space="preserve">97.6128234863281</t>
   </si>
   <si>
@@ -5937,6 +5940,9 @@
   </si>
   <si>
     <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1599998474121</t>
   </si>
 </sst>
 </file>
@@ -67029,7 +67035,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1506</v>
+        <v>1819</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67081,7 +67087,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67107,7 +67113,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67133,7 +67139,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67159,7 +67165,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67185,7 +67191,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67211,7 +67217,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67237,7 +67243,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67263,7 +67269,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67289,7 +67295,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67315,7 +67321,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67341,7 +67347,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67367,7 +67373,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67393,7 +67399,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67419,7 +67425,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67445,7 +67451,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67471,7 +67477,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67497,7 +67503,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67549,7 +67555,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67575,7 +67581,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67601,7 +67607,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67627,7 +67633,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67653,7 +67659,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67679,7 +67685,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67731,7 +67737,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67757,7 +67763,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67783,7 +67789,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67809,7 +67815,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67861,7 +67867,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67913,7 +67919,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67965,7 +67971,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68017,7 +68023,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68043,7 +68049,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68095,7 +68101,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68121,7 +68127,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68147,7 +68153,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68173,7 +68179,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68199,7 +68205,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68225,7 +68231,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68251,7 +68257,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68277,7 +68283,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68303,7 +68309,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68329,7 +68335,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68355,7 +68361,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68381,7 +68387,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68407,7 +68413,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68433,7 +68439,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68459,7 +68465,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68485,7 +68491,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68511,7 +68517,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68537,7 +68543,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68563,7 +68569,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68589,7 +68595,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68615,7 +68621,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68641,7 +68647,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68667,7 +68673,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68693,7 +68699,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68719,7 +68725,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68745,7 +68751,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68771,7 +68777,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68797,7 +68803,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68823,7 +68829,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68849,7 +68855,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68875,7 +68881,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68901,7 +68907,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68927,7 +68933,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68953,7 +68959,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68979,7 +68985,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -69005,7 +69011,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69031,7 +69037,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69057,7 +69063,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69083,7 +69089,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69109,7 +69115,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69135,7 +69141,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69161,7 +69167,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69187,7 +69193,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69213,7 +69219,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69239,7 +69245,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69265,7 +69271,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69291,7 +69297,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69317,7 +69323,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69343,7 +69349,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69369,7 +69375,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69395,7 +69401,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69421,7 +69427,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69447,7 +69453,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69473,7 +69479,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69499,7 +69505,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69525,7 +69531,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69551,7 +69557,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69577,7 +69583,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69603,7 +69609,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69629,7 +69635,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69655,7 +69661,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69681,7 +69687,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69707,7 +69713,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69733,7 +69739,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69759,7 +69765,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69785,7 +69791,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69811,7 +69817,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69837,7 +69843,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69863,7 +69869,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69889,7 +69895,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69915,7 +69921,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69941,7 +69947,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69967,7 +69973,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69993,7 +69999,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70019,7 +70025,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70045,7 +70051,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70071,7 +70077,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70097,7 +70103,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70123,7 +70129,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70149,7 +70155,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70175,7 +70181,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70201,7 +70207,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70227,7 +70233,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70253,7 +70259,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70279,7 +70285,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70305,7 +70311,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70331,7 +70337,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70357,7 +70363,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70383,7 +70389,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70409,7 +70415,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70435,7 +70441,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70461,7 +70467,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70487,7 +70493,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70513,7 +70519,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70539,7 +70545,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70565,7 +70571,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70591,7 +70597,7 @@
         <v>77.8600006103516</v>
       </c>
       <c r="G2474" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70617,7 +70623,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2475" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70643,7 +70649,7 @@
         <v>74.1800003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70669,7 +70675,7 @@
         <v>74.1399993896484</v>
       </c>
       <c r="G2477" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70695,7 +70701,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2478" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70721,7 +70727,7 @@
         <v>75.5199966430664</v>
       </c>
       <c r="G2479" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70747,7 +70753,7 @@
         <v>77.6600036621094</v>
       </c>
       <c r="G2480" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70773,7 +70779,7 @@
         <v>77.8399963378906</v>
       </c>
       <c r="G2481" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70799,7 +70805,7 @@
         <v>78.879997253418</v>
       </c>
       <c r="G2482" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70825,7 +70831,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2483" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70851,7 +70857,7 @@
         <v>79.0400009155273</v>
       </c>
       <c r="G2484" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70877,7 +70883,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G2485" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70903,7 +70909,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G2486" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70929,7 +70935,7 @@
         <v>75.6399993896484</v>
       </c>
       <c r="G2487" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70955,7 +70961,7 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2488" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70981,7 +70987,7 @@
         <v>74.1999969482422</v>
       </c>
       <c r="G2489" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -71007,7 +71013,7 @@
         <v>74.2399978637695</v>
       </c>
       <c r="G2490" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -71033,7 +71039,7 @@
         <v>74.9400024414062</v>
       </c>
       <c r="G2491" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -71059,7 +71065,7 @@
         <v>75.2600021362305</v>
       </c>
       <c r="G2492" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71085,7 +71091,7 @@
         <v>75.9400024414062</v>
       </c>
       <c r="G2493" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71111,7 +71117,7 @@
         <v>75.9599990844727</v>
       </c>
       <c r="G2494" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71137,7 +71143,7 @@
         <v>77.9400024414062</v>
       </c>
       <c r="G2495" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71163,7 +71169,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2496" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71189,7 +71195,7 @@
         <v>78.5999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71215,7 +71221,7 @@
         <v>77.6999969482422</v>
       </c>
       <c r="G2498" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71241,7 +71247,7 @@
         <v>77.2399978637695</v>
       </c>
       <c r="G2499" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71267,7 +71273,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2500" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -71293,7 +71299,7 @@
         <v>76.3199996948242</v>
       </c>
       <c r="G2501" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -71319,7 +71325,7 @@
         <v>76.6999969482422</v>
       </c>
       <c r="G2502" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -71345,7 +71351,7 @@
         <v>76.2799987792969</v>
       </c>
       <c r="G2503" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -71371,7 +71377,7 @@
         <v>76.3600006103516</v>
       </c>
       <c r="G2504" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -71397,7 +71403,7 @@
         <v>74.2600021362305</v>
       </c>
       <c r="G2505" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -71423,7 +71429,7 @@
         <v>60.3199996948242</v>
       </c>
       <c r="G2506" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -71449,7 +71455,7 @@
         <v>59.2200012207031</v>
       </c>
       <c r="G2507" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71457,7 +71463,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6911689815</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>373361</v>
@@ -71475,9 +71481,35 @@
         <v>59</v>
       </c>
       <c r="G2508" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6909722222</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>436223</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>60.8600006103516</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>59.1399993896484</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>59.1399993896484</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>60.1599998474121</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="1982">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954566955566</t>
+    <t xml:space="preserve">42.4954643249512</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0423049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9276390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8217964172363</t>
+    <t xml:space="preserve">43.2980918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.042308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9276428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8218002319336</t>
   </si>
   <si>
     <t xml:space="preserve">42.1514701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4689979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7281036376953</t>
+    <t xml:space="preserve">42.468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7281112670898</t>
   </si>
   <si>
     <t xml:space="preserve">41.2871017456055</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9993553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2761001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0765609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443786621094</t>
+    <t xml:space="preserve">39.9993476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2761039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0765647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384284973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443748474121</t>
   </si>
   <si>
     <t xml:space="preserve">38.9585723876953</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">40.2551422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2606391906738</t>
+    <t xml:space="preserve">41.2606430053711</t>
   </si>
   <si>
     <t xml:space="preserve">42.0544509887695</t>
@@ -98,76 +98,76 @@
     <t xml:space="preserve">41.3664817810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.777702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.068775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9981994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8780517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2341766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4172248840332</t>
+    <t xml:space="preserve">42.7776985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0687713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780479431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2341728210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4172286987305</t>
   </si>
   <si>
     <t xml:space="preserve">37.7590408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0148315429688</t>
+    <t xml:space="preserve">38.014820098877</t>
   </si>
   <si>
     <t xml:space="preserve">38.5881385803223</t>
   </si>
   <si>
-    <t xml:space="preserve">38.605770111084</t>
+    <t xml:space="preserve">38.6057739257812</t>
   </si>
   <si>
     <t xml:space="preserve">38.4029159545898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1228370666504</t>
+    <t xml:space="preserve">40.1228408813477</t>
   </si>
   <si>
     <t xml:space="preserve">40.3962593078613</t>
   </si>
   <si>
-    <t xml:space="preserve">40.493293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4017601013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5483779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9397888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5924797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2098846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011878967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2275276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.557201385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8074913024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6454048156738</t>
+    <t xml:space="preserve">40.4932899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4017562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5483741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9397850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5924758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.209888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.901180267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2275314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5571975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.807487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6453971862793</t>
   </si>
   <si>
     <t xml:space="preserve">42.7071418762207</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">42.7600631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7578887939453</t>
+    <t xml:space="preserve">40.7578926086426</t>
   </si>
   <si>
     <t xml:space="preserve">40.3521614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0081787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1636161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5726623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1581115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6200942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1140174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2904243469238</t>
+    <t xml:space="preserve">40.0081748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1636085510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5726661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6200828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.114013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2904205322266</t>
   </si>
   <si>
     <t xml:space="preserve">39.8405952453613</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">40.1316604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4668235778809</t>
+    <t xml:space="preserve">40.4668197631836</t>
   </si>
   <si>
     <t xml:space="preserve">44.1007194519043</t>
@@ -218,34 +218,34 @@
     <t xml:space="preserve">44.7622337341309</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2914428710938</t>
+    <t xml:space="preserve">45.2914390563965</t>
   </si>
   <si>
     <t xml:space="preserve">45.8647537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">45.379638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6883430480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8349685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9088478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4237518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2032470703125</t>
+    <t xml:space="preserve">45.3796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6883544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9088516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4237442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.203239440918</t>
   </si>
   <si>
     <t xml:space="preserve">44.8945426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9386444091797</t>
+    <t xml:space="preserve">44.9386405944824</t>
   </si>
   <si>
     <t xml:space="preserve">45.3355407714844</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">44.8063316345215</t>
   </si>
   <si>
-    <t xml:space="preserve">44.718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9827423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8504257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.776554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442489624023</t>
+    <t xml:space="preserve">44.7181282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.982738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8504295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7765502929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442451477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.8206520080566</t>
@@ -278,46 +278,46 @@
     <t xml:space="preserve">46.3057594299316</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1734580993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.261661529541</t>
+    <t xml:space="preserve">46.173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2616539001465</t>
   </si>
   <si>
     <t xml:space="preserve">46.6144638061523</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0852584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970550537109</t>
+    <t xml:space="preserve">46.0852546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">47.422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5119743347168</t>
+    <t xml:space="preserve">47.5119781494141</t>
   </si>
   <si>
     <t xml:space="preserve">47.1100883483887</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9138603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195220947266</t>
+    <t xml:space="preserve">47.9138679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195259094238</t>
   </si>
   <si>
     <t xml:space="preserve">48.5836753845215</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5660629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553726196289</t>
+    <t xml:space="preserve">49.5660667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553649902344</t>
   </si>
   <si>
     <t xml:space="preserve">50.2358741760254</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">49.0748710632324</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9679527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1641731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7000274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9855651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7352485656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6188888549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.931468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0924835205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0113525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0383834838867</t>
+    <t xml:space="preserve">49.9679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1641693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000312805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9855537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7352447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.618896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9314727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723556518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.011344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.038387298584</t>
   </si>
   <si>
     <t xml:space="preserve">48.8962516784668</t>
@@ -377,91 +377,91 @@
     <t xml:space="preserve">48.1371383666992</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9409065246582</t>
+    <t xml:space="preserve">48.9409027099609</t>
   </si>
   <si>
     <t xml:space="preserve">49.8339881896973</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0302085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2182693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2629241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7987670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9949989318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7717247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2805252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1912231445312</t>
+    <t xml:space="preserve">49.030216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8610343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5755043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.798770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.994987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7717208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2805213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1912269592285</t>
   </si>
   <si>
     <t xml:space="preserve">51.6201515197754</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5849266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0937461853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1654434204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3440551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.37109375</t>
+    <t xml:space="preserve">53.5849342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0937423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1654396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3710975646973</t>
   </si>
   <si>
     <t xml:space="preserve">54.120777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0666923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6648101806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6824188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968811035156</t>
+    <t xml:space="preserve">52.0666885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6647987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6824150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968772888184</t>
   </si>
   <si>
     <t xml:space="preserve">50.6377601623535</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2453079223633</t>
+    <t xml:space="preserve">52.2453117370605</t>
   </si>
   <si>
     <t xml:space="preserve">51.7541160583496</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">51.441535949707</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3522262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8880767822266</t>
+    <t xml:space="preserve">51.3522300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">51.0843048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4591484069824</t>
+    <t xml:space="preserve">50.4591445922852</t>
   </si>
   <si>
     <t xml:space="preserve">49.4767570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2981338500977</t>
+    <t xml:space="preserve">49.2981414794922</t>
   </si>
   <si>
     <t xml:space="preserve">51.9773864746094</t>
@@ -494,46 +494,46 @@
     <t xml:space="preserve">52.5132331848145</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6918487548828</t>
+    <t xml:space="preserve">52.6918563842773</t>
   </si>
   <si>
     <t xml:space="preserve">51.5308456420898</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3346214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2899551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.183048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7094612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736145019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270698547363</t>
+    <t xml:space="preserve">52.3346176147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2899627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1830406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7094650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270622253418</t>
   </si>
   <si>
     <t xml:space="preserve">50.1465682983398</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9056854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0126037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6459350585938</t>
+    <t xml:space="preserve">50.9056816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0126075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6459312438965</t>
   </si>
   <si>
     <t xml:space="preserve">47.8245468139648</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">45.3239250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7258110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5471954345703</t>
+    <t xml:space="preserve">45.7258071899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5471992492676</t>
   </si>
   <si>
     <t xml:space="preserve">46.395622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6635513305664</t>
+    <t xml:space="preserve">46.6635551452637</t>
   </si>
   <si>
     <t xml:space="preserve">45.7704696655273</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">45.9937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">45.457893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6811599731445</t>
+    <t xml:space="preserve">45.4578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811561584473</t>
   </si>
   <si>
     <t xml:space="preserve">46.5295829772949</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3063049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2440528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4673233032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2088317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3698348999023</t>
+    <t xml:space="preserve">46.3063087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2440490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4673194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2088241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3698463439941</t>
   </si>
   <si>
     <t xml:space="preserve">52.156005859375</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">48.8516006469727</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6107139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8163795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.128963470459</t>
+    <t xml:space="preserve">49.6107177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8163871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1289596557617</t>
   </si>
   <si>
     <t xml:space="preserve">52.2006568908691</t>
@@ -617,34 +617,34 @@
     <t xml:space="preserve">52.4685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4063186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4509735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.674243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9151191711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2723541259766</t>
+    <t xml:space="preserve">53.3616638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.406307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4509696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6742401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9151229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2723617553711</t>
   </si>
   <si>
     <t xml:space="preserve">53.852855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264427185059</t>
+    <t xml:space="preserve">54.7905960083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5943717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264389038086</t>
   </si>
   <si>
     <t xml:space="preserve">55.5050621032715</t>
@@ -653,100 +653,100 @@
     <t xml:space="preserve">56.2641792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1302223205566</t>
+    <t xml:space="preserve">56.1302185058594</t>
   </si>
   <si>
     <t xml:space="preserve">55.6390190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8000259399414</t>
+    <t xml:space="preserve">56.8000221252441</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9786415100098</t>
+    <t xml:space="preserve">56.978645324707</t>
   </si>
   <si>
     <t xml:space="preserve">57.0679550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4251937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.335880279541</t>
+    <t xml:space="preserve">57.4251899719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3358764648438</t>
   </si>
   <si>
     <t xml:space="preserve">58.0503425598145</t>
   </si>
   <si>
-    <t xml:space="preserve">58.8987731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0327377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.764820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0950012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1572608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3805313110352</t>
+    <t xml:space="preserve">58.8987693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0327339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7648239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0950088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3805351257324</t>
   </si>
   <si>
     <t xml:space="preserve">58.5861930847168</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0151252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.943431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440574645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4088439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1585273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6226768493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8906021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283271789551</t>
+    <t xml:space="preserve">60.0151214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9434280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3006629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4088478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6226654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8906097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283348083496</t>
   </si>
   <si>
     <t xml:space="preserve">62.6943740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3817977905273</t>
+    <t xml:space="preserve">62.3817825317383</t>
   </si>
   <si>
     <t xml:space="preserve">62.7390289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">62.515754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937446594238</t>
+    <t xml:space="preserve">62.5157508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8635635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937408447266</t>
   </si>
   <si>
     <t xml:space="preserve">60.9528656005859</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">61.6758079528809</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9469032287598</t>
+    <t xml:space="preserve">61.9468994140625</t>
   </si>
   <si>
     <t xml:space="preserve">62.0824508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3083686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5342903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7542572021484</t>
+    <t xml:space="preserve">62.3083648681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5342826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4950675964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.754264831543</t>
   </si>
   <si>
     <t xml:space="preserve">63.483154296875</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">64.5675582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0705413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8386611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5164184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.031322479248</t>
+    <t xml:space="preserve">64.0705337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8386688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5164108276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.166862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0313186645508</t>
   </si>
   <si>
     <t xml:space="preserve">64.5223770141602</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">63.8898010253906</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4320220947266</t>
+    <t xml:space="preserve">64.432014465332</t>
   </si>
   <si>
     <t xml:space="preserve">64.2964553833008</t>
@@ -812,31 +812,31 @@
     <t xml:space="preserve">64.1609115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">65.697151184082</t>
+    <t xml:space="preserve">65.6971588134766</t>
   </si>
   <si>
     <t xml:space="preserve">61.0884132385254</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6425361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.184741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.817310333252</t>
+    <t xml:space="preserve">59.6425323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1847381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8173179626465</t>
   </si>
   <si>
     <t xml:space="preserve">60.5462036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6877212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365699768066</t>
+    <t xml:space="preserve">59.6877174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365776062012</t>
   </si>
   <si>
     <t xml:space="preserve">61.4498863220215</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">62.3987426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2120399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927841186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216850280762</t>
+    <t xml:space="preserve">63.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216773986816</t>
   </si>
   <si>
     <t xml:space="preserve">66.2393569946289</t>
@@ -863,43 +863,43 @@
     <t xml:space="preserve">66.7815704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0134506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5104598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3297271728516</t>
+    <t xml:space="preserve">66.0134429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5104675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3297348022461</t>
   </si>
   <si>
     <t xml:space="preserve">65.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8778839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6067810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.019401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2001342773438</t>
+    <t xml:space="preserve">65.8778915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6067886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.0193939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2001419067383</t>
   </si>
   <si>
     <t xml:space="preserve">64.748291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7934722900391</t>
+    <t xml:space="preserve">64.7934646606445</t>
   </si>
   <si>
     <t xml:space="preserve">64.6579284667969</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4772033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9801750183105</t>
+    <t xml:space="preserve">64.4771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9801826477051</t>
   </si>
   <si>
     <t xml:space="preserve">63.302417755127</t>
@@ -911,76 +911,76 @@
     <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">66.284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6008224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4652862548828</t>
+    <t xml:space="preserve">66.2845458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6008148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4652786254883</t>
   </si>
   <si>
     <t xml:space="preserve">66.8719329833984</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0586242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3749237060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6911926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5437316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1370697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.182258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1311264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3058929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962707519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3903121948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5258636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8480987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1643829345703</t>
+    <t xml:space="preserve">66.0586318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3749084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6912002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1370849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563217163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1311187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3059005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776840209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3903045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5258560180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8481063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1643905639648</t>
   </si>
   <si>
     <t xml:space="preserve">72.7910079956055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8932800292969</t>
+    <t xml:space="preserve">70.8932723999023</t>
   </si>
   <si>
     <t xml:space="preserve">70.2607116699219</t>
@@ -989,58 +989,58 @@
     <t xml:space="preserve">70.35107421875</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5318069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5769958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3451156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4414520263672</t>
+    <t xml:space="preserve">70.5318145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5770034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3451309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4414443969727</t>
   </si>
   <si>
     <t xml:space="preserve">71.5710372924805</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9836578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7125473022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1097640991211</t>
+    <t xml:space="preserve">70.9836654663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1097717285156</t>
   </si>
   <si>
     <t xml:space="preserve">65.5616073608398</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4593200683594</t>
+    <t xml:space="preserve">67.4593124389648</t>
   </si>
   <si>
     <t xml:space="preserve">67.8207931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2666625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.034797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7636795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9955673217773</t>
+    <t xml:space="preserve">69.2666702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0347900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
     <t xml:space="preserve">67.3237686157227</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">68.3629989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0407562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1763000488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9444274902344</t>
+    <t xml:space="preserve">69.0407638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1763076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9444351196289</t>
   </si>
   <si>
     <t xml:space="preserve">70.1703338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">71.8873291015625</t>
+    <t xml:space="preserve">71.887336730957</t>
   </si>
   <si>
     <t xml:space="preserve">72.6102676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8992462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4985504150391</t>
+    <t xml:space="preserve">69.8992385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4985580444336</t>
   </si>
   <si>
     <t xml:space="preserve">68.4081802368164</t>
@@ -1082,91 +1082,91 @@
     <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.402214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969665527344</t>
+    <t xml:space="preserve">69.4022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969589233398</t>
   </si>
   <si>
     <t xml:space="preserve">71.6162185668945</t>
   </si>
   <si>
-    <t xml:space="preserve">71.932502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0228805541992</t>
+    <t xml:space="preserve">71.9325180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0228729248047</t>
   </si>
   <si>
     <t xml:space="preserve">71.7065887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4806823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4354858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6613998413086</t>
+    <t xml:space="preserve">71.4806671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4354934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614074707031</t>
   </si>
   <si>
     <t xml:space="preserve">71.2547454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8088760375977</t>
+    <t xml:space="preserve">69.8088836669922</t>
   </si>
   <si>
     <t xml:space="preserve">71.7517776489258</t>
   </si>
   <si>
-    <t xml:space="preserve">68.0918884277344</t>
+    <t xml:space="preserve">68.0918807983398</t>
   </si>
   <si>
     <t xml:space="preserve">66.9623031616211</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8505821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.618709564209</t>
+    <t xml:space="preserve">62.8505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572250366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6187057495117</t>
   </si>
   <si>
     <t xml:space="preserve">63.0765075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9409484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602043151855</t>
+    <t xml:space="preserve">62.9409523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602119445801</t>
   </si>
   <si>
     <t xml:space="preserve">61.9017181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9528617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0040016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7329025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.811351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.799446105957</t>
+    <t xml:space="preserve">60.9528579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0040092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7328987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8113555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7994384765625</t>
   </si>
   <si>
     <t xml:space="preserve">67.549690246582</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">66.7363815307617</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2453079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838577270508</t>
+    <t xml:space="preserve">65.2453002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838500976562</t>
   </si>
   <si>
     <t xml:space="preserve">65.651969909668</t>
@@ -1193,43 +1193,43 @@
     <t xml:space="preserve">68.2726364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1251525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8600158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540649414062</t>
+    <t xml:space="preserve">70.1251602172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540725708008</t>
   </si>
   <si>
     <t xml:space="preserve">70.622184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1192016601562</t>
+    <t xml:space="preserve">71.1191940307617</t>
   </si>
   <si>
     <t xml:space="preserve">71.0740127563477</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6554489135742</t>
+    <t xml:space="preserve">72.6554565429688</t>
   </si>
   <si>
     <t xml:space="preserve">73.6946868896484</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4747085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4687576293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1976623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3783874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6887054443359</t>
+    <t xml:space="preserve">72.4747009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4687652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1976470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3783798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.688720703125</t>
   </si>
   <si>
     <t xml:space="preserve">73.5591278076172</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">75.7964935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">74.152702331543</t>
+    <t xml:space="preserve">74.1527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">77.2576293945312</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">78.0795135498047</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9059295654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5908432006836</t>
+    <t xml:space="preserve">79.9059371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5908508300781</t>
   </si>
   <si>
     <t xml:space="preserve">80.3625411987305</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">80.2712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2300796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1021728515625</t>
+    <t xml:space="preserve">81.2300872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.102180480957</t>
   </si>
   <si>
     <t xml:space="preserve">84.3806762695312</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">84.9285888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2893600463867</t>
+    <t xml:space="preserve">84.2893524169922</t>
   </si>
   <si>
     <t xml:space="preserve">83.056510925293</t>
@@ -1304,76 +1304,76 @@
     <t xml:space="preserve">81.7323532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4127426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682357788086</t>
+    <t xml:space="preserve">81.4127349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682281494141</t>
   </si>
   <si>
     <t xml:space="preserve">86.8006973266602</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3942642211914</t>
+    <t xml:space="preserve">87.3942718505859</t>
   </si>
   <si>
     <t xml:space="preserve">88.8554077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9878463745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2206726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9421997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0380401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572937011719</t>
+    <t xml:space="preserve">87.9878387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2206802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9422073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0380477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2572860717773</t>
   </si>
   <si>
     <t xml:space="preserve">87.485595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5769119262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6772918701172</t>
+    <t xml:space="preserve">87.5769271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052215576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6772842407227</t>
   </si>
   <si>
     <t xml:space="preserve">89.1750335693359</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4033279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1248397827148</t>
+    <t xml:space="preserve">89.4033355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1248474121094</t>
   </si>
   <si>
     <t xml:space="preserve">87.62255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.353141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2984085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8418045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263153076172</t>
+    <t xml:space="preserve">88.3531265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2984161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263305664062</t>
   </si>
   <si>
     <t xml:space="preserve">84.4719924926758</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">81.0474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">80.2255554199219</t>
+    <t xml:space="preserve">80.2255630493164</t>
   </si>
   <si>
     <t xml:space="preserve">80.4538650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">79.358024597168</t>
+    <t xml:space="preserve">79.3580169677734</t>
   </si>
   <si>
     <t xml:space="preserve">80.4995269775391</t>
@@ -1406,28 +1406,28 @@
     <t xml:space="preserve">79.0383834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">79.3123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587768554688</t>
+    <t xml:space="preserve">79.3123474121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6135101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587844848633</t>
   </si>
   <si>
     <t xml:space="preserve">83.8784103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6501007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2391662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7414245605469</t>
+    <t xml:space="preserve">83.6500930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7414169311523</t>
   </si>
   <si>
     <t xml:space="preserve">84.8372802734375</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">84.3350143432617</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6410446166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9149932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0017852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.275749206543</t>
+    <t xml:space="preserve">81.6410369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9149856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0017776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.275764465332</t>
   </si>
   <si>
     <t xml:space="preserve">82.8282165527344</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5312423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2436752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199203491211</t>
+    <t xml:space="preserve">87.53125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2436904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199127197266</t>
   </si>
   <si>
     <t xml:space="preserve">84.882926940918</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">83.3761444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4583969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2667007446289</t>
+    <t xml:space="preserve">81.4583892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2666931152344</t>
   </si>
   <si>
     <t xml:space="preserve">75.1572418212891</t>
@@ -1487,49 +1487,49 @@
     <t xml:space="preserve">74.4266738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">73.330810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7829055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8376235961914</t>
+    <t xml:space="preserve">73.3308258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8376159667969</t>
   </si>
   <si>
     <t xml:space="preserve">72.6002578735352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.9198684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5179901123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485580444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4357376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8285522460938</t>
+    <t xml:space="preserve">72.9198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5179824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4357299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">73.8330841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">72.2806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9700698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0659255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5270538330078</t>
+    <t xml:space="preserve">72.280632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9700775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.06591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.5270690917969</t>
   </si>
   <si>
     <t xml:space="preserve">79.9516067504883</t>
@@ -1541,55 +1541,55 @@
     <t xml:space="preserve">76.1161193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0568695068359</t>
+    <t xml:space="preserve">73.0568618774414</t>
   </si>
   <si>
     <t xml:space="preserve">70.545524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6825103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0934600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9610137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1025238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3262939453125</t>
+    <t xml:space="preserve">70.6825180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0934524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9610214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1025314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.326286315918</t>
   </si>
   <si>
     <t xml:space="preserve">71.0477905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8651351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5821228027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4907989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3217620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3949661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.938362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187210083008</t>
+    <t xml:space="preserve">70.8651580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5821151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4908065795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8560943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3217544555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8013687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3949737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9383544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187286376953</t>
   </si>
   <si>
     <t xml:space="preserve">67.5775909423828</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">66.8470230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5228652954102</t>
+    <t xml:space="preserve">65.5228729248047</t>
   </si>
   <si>
     <t xml:space="preserve">64.0160675048828</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">66.162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">64.9446868896484</t>
+    <t xml:space="preserve">64.944694519043</t>
   </si>
   <si>
     <t xml:space="preserve">66.2089385986328</t>
@@ -1625,25 +1625,25 @@
     <t xml:space="preserve">66.6771774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3025970458984</t>
+    <t xml:space="preserve">66.302604675293</t>
   </si>
   <si>
     <t xml:space="preserve">70.0016784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4866027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2056579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.6270751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7508544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1421432495117</t>
+    <t xml:space="preserve">69.4865951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2056732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.627082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.750862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1421508789062</t>
   </si>
   <si>
     <t xml:space="preserve">69.7675552368164</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">73.0452270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459411621094</t>
+    <t xml:space="preserve">75.2459335327148</t>
   </si>
   <si>
     <t xml:space="preserve">75.1054763793945</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9650039672852</t>
+    <t xml:space="preserve">74.9650115966797</t>
   </si>
   <si>
     <t xml:space="preserve">74.5904083251953</t>
@@ -1673,46 +1673,46 @@
     <t xml:space="preserve">75.0586547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2927627563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6840591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1355972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8713531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8847732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9784240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7109146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6172714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.6942138671875</t>
+    <t xml:space="preserve">75.2927703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.5570068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1356048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.871337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8847808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9784164428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7109222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6172485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.694206237793</t>
   </si>
   <si>
     <t xml:space="preserve">79.2728118896484</t>
   </si>
   <si>
-    <t xml:space="preserve">79.6005630493164</t>
+    <t xml:space="preserve">79.6005706787109</t>
   </si>
   <si>
     <t xml:space="preserve">79.2259750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4132690429688</t>
+    <t xml:space="preserve">79.4132766723633</t>
   </si>
   <si>
     <t xml:space="preserve">79.7878570556641</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">80.0219802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0386810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8815078735352</t>
+    <t xml:space="preserve">79.0386734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">80.6775131225586</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3029098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7711563110352</t>
+    <t xml:space="preserve">80.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7711639404297</t>
   </si>
   <si>
     <t xml:space="preserve">82.035400390625</t>
@@ -1742,34 +1742,34 @@
     <t xml:space="preserve">81.707633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">81.3798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3330535888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2393951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2227096557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1457595825195</t>
+    <t xml:space="preserve">81.3798751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3330459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2394104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2227020263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.145751953125</t>
   </si>
   <si>
     <t xml:space="preserve">80.3497543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9751663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2695159912109</t>
+    <t xml:space="preserve">79.9751510620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2695236206055</t>
   </si>
   <si>
     <t xml:space="preserve">82.5036468505859</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0187225341797</t>
+    <t xml:space="preserve">83.0187149047852</t>
   </si>
   <si>
     <t xml:space="preserve">83.2528305053711</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">83.6742324829102</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9718780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0488204956055</t>
+    <t xml:space="preserve">82.9718856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0488357543945</t>
   </si>
   <si>
     <t xml:space="preserve">84.0019989013672</t>
@@ -1796,64 +1796,64 @@
     <t xml:space="preserve">85.7813110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8582534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.155891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8281478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6876602172852</t>
+    <t xml:space="preserve">86.8582611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1558990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8281402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6876678466797</t>
   </si>
   <si>
     <t xml:space="preserve">85.2194213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1257934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6408462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822448730469</t>
+    <t xml:space="preserve">85.1257858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6408386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822372436523</t>
   </si>
   <si>
     <t xml:space="preserve">79.7410430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">80.2560958862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5671615600586</t>
+    <t xml:space="preserve">80.256103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5671691894531</t>
   </si>
   <si>
     <t xml:space="preserve">81.8481063842773</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8147125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1893157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2829513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3130722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1693420410156</t>
+    <t xml:space="preserve">83.8147201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1893005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.282958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3130798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1693267822266</t>
   </si>
   <si>
     <t xml:space="preserve">89.4804077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2597045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128753662109</t>
+    <t xml:space="preserve">91.2596969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128829956055</t>
   </si>
   <si>
     <t xml:space="preserve">91.6855010986328</t>
@@ -1880,22 +1880,22 @@
     <t xml:space="preserve">88.3299789428711</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8025894165039</t>
+    <t xml:space="preserve">88.8025817871094</t>
   </si>
   <si>
     <t xml:space="preserve">86.5340957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0786437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3546676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9690628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1033020019531</t>
+    <t xml:space="preserve">90.0786361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3546752929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1032943725586</t>
   </si>
   <si>
     <t xml:space="preserve">95.5608520507812</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">93.8122177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0731887817383</t>
+    <t xml:space="preserve">97.0731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">97.8293685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3416900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.326644897461</t>
+    <t xml:space="preserve">99.3416976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.326637268066</t>
   </si>
   <si>
     <t xml:space="preserve">98.6800537109375</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">99.2471771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">96.8841552734375</t>
+    <t xml:space="preserve">96.884147644043</t>
   </si>
   <si>
     <t xml:space="preserve">97.6403274536133</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">95.9389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">96.317024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.5060577392578</t>
+    <t xml:space="preserve">96.3170318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5060729980469</t>
   </si>
   <si>
     <t xml:space="preserve">97.2622375488281</t>
@@ -1949,46 +1949,46 @@
     <t xml:space="preserve">99.5307540893555</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3019790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.3567657470703</t>
+    <t xml:space="preserve">98.3019638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3567581176758</t>
   </si>
   <si>
     <t xml:space="preserve">98.2074508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">97.167724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5457992553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2225112915039</t>
+    <t xml:space="preserve">97.1677322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5457916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2224960327148</t>
   </si>
   <si>
     <t xml:space="preserve">95.7499008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8444213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4663314819336</t>
+    <t xml:space="preserve">95.8444290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4663391113281</t>
   </si>
   <si>
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475967407227</t>
+    <t xml:space="preserve">102.082809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475959777832</t>
   </si>
   <si>
     <t xml:space="preserve">99.1526565551758</t>
   </si>
   <si>
-    <t xml:space="preserve">101.799240112305</t>
+    <t xml:space="preserve">101.79923248291</t>
   </si>
   <si>
     <t xml:space="preserve">100.665000915527</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">100.097869873047</t>
   </si>
   <si>
-    <t xml:space="preserve">99.908821105957</t>
+    <t xml:space="preserve">99.9088287353516</t>
   </si>
   <si>
     <t xml:space="preserve">98.396484375</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">100.192390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">102.366371154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.177337646484</t>
+    <t xml:space="preserve">102.366386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.17733001709</t>
   </si>
   <si>
     <t xml:space="preserve">103.784194946289</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">100.003349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">101.13761138916</t>
+    <t xml:space="preserve">101.137603759766</t>
   </si>
   <si>
     <t xml:space="preserve">101.704719543457</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">103.500640869141</t>
+    <t xml:space="preserve">103.500633239746</t>
   </si>
   <si>
     <t xml:space="preserve">102.93350982666</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">100.38143157959</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5855331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6951141357422</t>
+    <t xml:space="preserve">98.5855407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6951065063477</t>
   </si>
   <si>
     <t xml:space="preserve">98.1129379272461</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0581359863281</t>
+    <t xml:space="preserve">99.0581436157227</t>
   </si>
   <si>
     <t xml:space="preserve">100.94856262207</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">99.7197875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">100.854034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6252670288086</t>
+    <t xml:space="preserve">100.854026794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6252746582031</t>
   </si>
   <si>
     <t xml:space="preserve">94.4266052246094</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">94.7101593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8594741821289</t>
+    <t xml:space="preserve">93.8594818115234</t>
   </si>
   <si>
     <t xml:space="preserve">94.0957870483398</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">94.6156387329102</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5211334228516</t>
+    <t xml:space="preserve">94.5211181640625</t>
   </si>
   <si>
     <t xml:space="preserve">91.6382217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3471221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3074035644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2998809814453</t>
+    <t xml:space="preserve">92.3471298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3074111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2998886108398</t>
   </si>
   <si>
     <t xml:space="preserve">91.7327499389648</t>
@@ -2105,28 +2105,28 @@
     <t xml:space="preserve">92.0163192749023</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1505813598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3718109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8046951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8690872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9238891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.759506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.122550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.634887695312</t>
+    <t xml:space="preserve">93.1505737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3718185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8047027587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8691024780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9238815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.75951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.122535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.634880065918</t>
   </si>
   <si>
     <t xml:space="preserve">105.95817565918</t>
@@ -2150,34 +2150,34 @@
     <t xml:space="preserve">113.236312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">113.519866943359</t>
+    <t xml:space="preserve">113.519859313965</t>
   </si>
   <si>
     <t xml:space="preserve">114.654121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">111.818481445312</t>
+    <t xml:space="preserve">111.818496704102</t>
   </si>
   <si>
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.206192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.017150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.315765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.425338745117</t>
+    <t xml:space="preserve">115.977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.206184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.017158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.315773010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.370559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.425346374512</t>
   </si>
   <si>
     <t xml:space="preserve">109.644500732422</t>
@@ -2189,37 +2189,37 @@
     <t xml:space="preserve">110.589721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">110.306144714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.156845092773</t>
+    <t xml:space="preserve">110.306137084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.156837463379</t>
   </si>
   <si>
     <t xml:space="preserve">111.723960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.11710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.833549499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.510246276855</t>
+    <t xml:space="preserve">111.062309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.117111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.833541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.51025390625</t>
   </si>
   <si>
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.29109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.873275756836</t>
+    <t xml:space="preserve">112.291107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.873291015625</t>
   </si>
   <si>
     <t xml:space="preserve">109.455459594727</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">110.49520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">108.037643432617</t>
+    <t xml:space="preserve">108.037651062012</t>
   </si>
   <si>
     <t xml:space="preserve">107.848602294922</t>
@@ -2240,28 +2240,28 @@
     <t xml:space="preserve">108.793807983398</t>
   </si>
   <si>
-    <t xml:space="preserve">106.430786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.171890258789</t>
+    <t xml:space="preserve">106.430778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.171905517578</t>
   </si>
   <si>
     <t xml:space="preserve">109.266418457031</t>
   </si>
   <si>
-    <t xml:space="preserve">106.997909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.918449401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.769142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.754089355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.415718078613</t>
+    <t xml:space="preserve">106.997901916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.918441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.769149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.754081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.415725708008</t>
   </si>
   <si>
     <t xml:space="preserve">108.32120513916</t>
@@ -2270,19 +2270,19 @@
     <t xml:space="preserve">110.211631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">114.276039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.465087890625</t>
+    <t xml:space="preserve">114.27604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
     <t xml:space="preserve">109.928070068359</t>
   </si>
   <si>
-    <t xml:space="preserve">104.540367126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7745819091797</t>
+    <t xml:space="preserve">104.54035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7745742797852</t>
   </si>
   <si>
     <t xml:space="preserve">106.808876037598</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">103.595153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">101.893775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8142929077148</t>
+    <t xml:space="preserve">101.893783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8143005371094</t>
   </si>
   <si>
     <t xml:space="preserve">108.132171630859</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">108.888328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">106.525299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.445854187012</t>
+    <t xml:space="preserve">106.525291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.445846557617</t>
   </si>
   <si>
     <t xml:space="preserve">102.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">114.08699798584</t>
+    <t xml:space="preserve">114.086990356445</t>
   </si>
   <si>
     <t xml:space="preserve">111.629447937012</t>
@@ -2327,49 +2327,49 @@
     <t xml:space="preserve">118.056884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">122.310317993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.091148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.329574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876251220703</t>
+    <t xml:space="preserve">122.310325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.091171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.32958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876235961914</t>
   </si>
   <si>
     <t xml:space="preserve">136.583023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">145.089935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.2392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.959838867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.383117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.691345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.755752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.944808959961</t>
+    <t xml:space="preserve">145.089920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.239242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.959854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.38313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.691360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.755737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.94482421875</t>
   </si>
   <si>
     <t xml:space="preserve">153.313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">146.791305541992</t>
+    <t xml:space="preserve">146.791320800781</t>
   </si>
   <si>
     <t xml:space="preserve">146.885818481445</t>
@@ -2384,19 +2384,19 @@
     <t xml:space="preserve">146.318695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">147.641998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.596832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.706405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.048919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.302368164062</t>
+    <t xml:space="preserve">147.642013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.596817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.706420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.048934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.302383422852</t>
   </si>
   <si>
     <t xml:space="preserve">174.10791015625</t>
@@ -2408,88 +2408,88 @@
     <t xml:space="preserve">169.381851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">178.833969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.440811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.688842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.927215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.206604003906</t>
+    <t xml:space="preserve">178.833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.440826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.688858032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.927230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.206588745117</t>
   </si>
   <si>
     <t xml:space="preserve">163.521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.172302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.55583190918</t>
+    <t xml:space="preserve">171.839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.172317504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.555847167969</t>
   </si>
   <si>
     <t xml:space="preserve">169.098281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">163.994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.655792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.905059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.855728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.651626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.014633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.6064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.85026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.510162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.365737915039</t>
+    <t xml:space="preserve">163.994171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.655807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.905075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.855743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.651611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.0146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.606460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.850280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.510147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.365707397461</t>
   </si>
   <si>
     <t xml:space="preserve">161.890411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">161.129898071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.133605957031</t>
+    <t xml:space="preserve">161.129913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.133590698242</t>
   </si>
   <si>
     <t xml:space="preserve">162.270645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">167.11882019043</t>
+    <t xml:space="preserve">167.118835449219</t>
   </si>
   <si>
     <t xml:space="preserve">164.457061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">162.936080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.320037841797</t>
+    <t xml:space="preserve">162.936096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.320022583008</t>
   </si>
   <si>
     <t xml:space="preserve">161.985473632812</t>
@@ -2501,34 +2501,34 @@
     <t xml:space="preserve">162.841033935547</t>
   </si>
   <si>
-    <t xml:space="preserve">162.650894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.685470581055</t>
+    <t xml:space="preserve">162.650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.073135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.685485839844</t>
   </si>
   <si>
     <t xml:space="preserve">170.35090637207</t>
   </si>
   <si>
-    <t xml:space="preserve">163.031127929688</t>
+    <t xml:space="preserve">163.031143188477</t>
   </si>
   <si>
     <t xml:space="preserve">164.362014770508</t>
   </si>
   <si>
-    <t xml:space="preserve">165.122512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.400299072266</t>
+    <t xml:space="preserve">165.122497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.305252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.400283813477</t>
   </si>
   <si>
     <t xml:space="preserve">171.96696472168</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">169.495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.358291625977</t>
+    <t xml:space="preserve">166.358322143555</t>
   </si>
   <si>
     <t xml:space="preserve">160.939804077148</t>
@@ -2546,79 +2546,79 @@
     <t xml:space="preserve">154.665710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">162.175598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.742279052734</t>
+    <t xml:space="preserve">162.17561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">159.228668212891</t>
   </si>
   <si>
-    <t xml:space="preserve">157.802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.669387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.81755065918</t>
+    <t xml:space="preserve">157.802749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.669418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.817565917969</t>
   </si>
   <si>
     <t xml:space="preserve">146.77555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.254577636719</t>
+    <t xml:space="preserve">150.768188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.25456237793</t>
   </si>
   <si>
     <t xml:space="preserve">149.72248840332</t>
   </si>
   <si>
-    <t xml:space="preserve">152.289154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.623718261719</t>
+    <t xml:space="preserve">152.289138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.623733520508</t>
   </si>
   <si>
     <t xml:space="preserve">148.391616821289</t>
   </si>
   <si>
-    <t xml:space="preserve">154.760757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.24348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.190368652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.855834960938</t>
+    <t xml:space="preserve">154.760772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.243499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.190383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.855819702148</t>
   </si>
   <si>
     <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">155.426208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.806457519531</t>
+    <t xml:space="preserve">155.426177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.806442260742</t>
   </si>
   <si>
     <t xml:space="preserve">159.418792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">145.634811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.600234985352</t>
+    <t xml:space="preserve">145.634826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.600250244141</t>
   </si>
   <si>
     <t xml:space="preserve">144.018768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">144.589141845703</t>
+    <t xml:space="preserve">144.589157104492</t>
   </si>
   <si>
     <t xml:space="preserve">143.543472290039</t>
@@ -2633,85 +2633,85 @@
     <t xml:space="preserve">137.364440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">137.174301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.779251098633</t>
+    <t xml:space="preserve">137.174331665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.779266357422</t>
   </si>
   <si>
     <t xml:space="preserve">143.258255004883</t>
   </si>
   <si>
-    <t xml:space="preserve">147.060745239258</t>
+    <t xml:space="preserve">147.060760498047</t>
   </si>
   <si>
     <t xml:space="preserve">147.726181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.247177124023</t>
+    <t xml:space="preserve">149.247161865234</t>
   </si>
   <si>
     <t xml:space="preserve">152.95458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">150.387924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.03483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.654586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.080520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.795333862305</t>
+    <t xml:space="preserve">150.387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.034820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.654602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.080535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.795318603516</t>
   </si>
   <si>
     <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.29411315918</t>
+    <t xml:space="preserve">168.069442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.294128417969</t>
   </si>
   <si>
     <t xml:space="preserve">177.670654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">173.48796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.716339111328</t>
+    <t xml:space="preserve">173.487945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.716369628906</t>
   </si>
   <si>
     <t xml:space="preserve">180.712677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">178.24104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.853393554688</t>
+    <t xml:space="preserve">178.241058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.853408813477</t>
   </si>
   <si>
     <t xml:space="preserve">179.666976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">184.990463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.039840698242</t>
+    <t xml:space="preserve">184.990447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.039825439453</t>
   </si>
   <si>
     <t xml:space="preserve">181.663299560547</t>
   </si>
   <si>
-    <t xml:space="preserve">185.275619506836</t>
+    <t xml:space="preserve">185.275604248047</t>
   </si>
   <si>
     <t xml:space="preserve">183.089218139648</t>
@@ -2720,40 +2720,40 @@
     <t xml:space="preserve">181.568222045898</t>
   </si>
   <si>
-    <t xml:space="preserve">179.286743164062</t>
+    <t xml:space="preserve">179.286758422852</t>
   </si>
   <si>
     <t xml:space="preserve">178.050933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">179.191650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.529922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.860809326172</t>
+    <t xml:space="preserve">179.191665649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.529937744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.860824584961</t>
   </si>
   <si>
     <t xml:space="preserve">184.610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">189.838592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.264541625977</t>
+    <t xml:space="preserve">189.838607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.264526367188</t>
   </si>
   <si>
     <t xml:space="preserve">159.703964233398</t>
   </si>
   <si>
-    <t xml:space="preserve">163.88671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.217590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.932373046875</t>
+    <t xml:space="preserve">163.886703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.217575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.932403564453</t>
   </si>
   <si>
     <t xml:space="preserve">164.076843261719</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">160.8447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">164.266983032227</t>
+    <t xml:space="preserve">164.266967773438</t>
   </si>
   <si>
     <t xml:space="preserve">167.879302978516</t>
@@ -2774,25 +2774,25 @@
     <t xml:space="preserve">163.696578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">161.605209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.084228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.745956420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.179275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.32373046875</t>
+    <t xml:space="preserve">161.605224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.084213256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.745941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.179306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.323745727539</t>
   </si>
   <si>
     <t xml:space="preserve">158.468170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">158.848434448242</t>
+    <t xml:space="preserve">158.848449707031</t>
   </si>
   <si>
     <t xml:space="preserve">163.221267700195</t>
@@ -2801,43 +2801,43 @@
     <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">159.608932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.700302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.224975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.810134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.859512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.528671264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.4755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.57063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.992858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.826217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.970672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.001571655273</t>
+    <t xml:space="preserve">159.60888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.700286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.224990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.810150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.859527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.52864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.616302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.475570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.570648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.992874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.826202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.970657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.001541137695</t>
   </si>
   <si>
     <t xml:space="preserve">168.92497253418</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">171.681793212891</t>
   </si>
   <si>
-    <t xml:space="preserve">171.111404418945</t>
+    <t xml:space="preserve">171.111419677734</t>
   </si>
   <si>
     <t xml:space="preserve">170.541030883789</t>
@@ -2858,43 +2858,43 @@
     <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.868209838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.389175415039</t>
+    <t xml:space="preserve">170.255874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.868194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.202774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.389205932617</t>
   </si>
   <si>
     <t xml:space="preserve">176.43489074707</t>
   </si>
   <si>
-    <t xml:space="preserve">176.149688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.195358276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.438568115234</t>
+    <t xml:space="preserve">176.149703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.195343017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.438583374023</t>
   </si>
   <si>
     <t xml:space="preserve">156.18669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">151.813827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.996566772461</t>
+    <t xml:space="preserve">151.813842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.99658203125</t>
   </si>
   <si>
     <t xml:space="preserve">154.380508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">155.901489257812</t>
+    <t xml:space="preserve">155.901504516602</t>
   </si>
   <si>
     <t xml:space="preserve">157.137313842773</t>
@@ -2903,31 +2903,31 @@
     <t xml:space="preserve">154.000274658203</t>
   </si>
   <si>
-    <t xml:space="preserve">150.197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.057037353516</t>
+    <t xml:space="preserve">150.197784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.057067871094</t>
   </si>
   <si>
     <t xml:space="preserve">147.155807495117</t>
   </si>
   <si>
-    <t xml:space="preserve">132.706420898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.082977294922</t>
+    <t xml:space="preserve">132.706405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.082962036133</t>
   </si>
   <si>
     <t xml:space="preserve">138.695297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">134.987899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.033584594727</t>
+    <t xml:space="preserve">134.987884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.033569335938</t>
   </si>
   <si>
     <t xml:space="preserve">133.276763916016</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">134.037261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">133.086654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.273071289062</t>
+    <t xml:space="preserve">133.086669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.273086547852</t>
   </si>
   <si>
     <t xml:space="preserve">132.136032104492</t>
@@ -2951,43 +2951,43 @@
     <t xml:space="preserve">130.90022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">130.044662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.46321105957</t>
+    <t xml:space="preserve">130.044677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.848983764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.463195800781</t>
   </si>
   <si>
     <t xml:space="preserve">133.229248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">145.492218017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.59098815918</t>
+    <t xml:space="preserve">145.492248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.591003417969</t>
   </si>
   <si>
     <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">148.20149230957</t>
+    <t xml:space="preserve">148.201477050781</t>
   </si>
   <si>
     <t xml:space="preserve">148.058898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">146.300262451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.01692199707</t>
+    <t xml:space="preserve">146.300247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.016937255859</t>
   </si>
   <si>
     <t xml:space="preserve">144.874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">136.98420715332</t>
+    <t xml:space="preserve">136.984191894531</t>
   </si>
   <si>
     <t xml:space="preserve">136.794052124023</t>
@@ -3008,52 +3008,52 @@
     <t xml:space="preserve">131.660720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">133.847137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.60578918457</t>
+    <t xml:space="preserve">133.847152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.605773925781</t>
   </si>
   <si>
     <t xml:space="preserve">131.423065185547</t>
   </si>
   <si>
-    <t xml:space="preserve">128.333541870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.470581054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.185424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.655181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889129638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.983871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.744552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.845397949219</t>
+    <t xml:space="preserve">128.333557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.470611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.185409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.655151367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.031692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.983856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.744567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.84538269043</t>
   </si>
   <si>
     <t xml:space="preserve">137.797515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">138.084701538086</t>
+    <t xml:space="preserve">138.084716796875</t>
   </si>
   <si>
     <t xml:space="preserve">138.467590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">135.978729248047</t>
+    <t xml:space="preserve">135.978744506836</t>
   </si>
   <si>
     <t xml:space="preserve">133.05908203125</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">136.218048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">137.510345458984</t>
+    <t xml:space="preserve">137.510330200195</t>
   </si>
   <si>
     <t xml:space="preserve">138.659072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">139.185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.2060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.306900024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.01969909668</t>
+    <t xml:space="preserve">139.185531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.206069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.306884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.019714355469</t>
   </si>
   <si>
     <t xml:space="preserve">146.269271850586</t>
@@ -3095,61 +3095,61 @@
     <t xml:space="preserve">147.322250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">146.843627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.226531982422</t>
+    <t xml:space="preserve">146.843612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.226547241211</t>
   </si>
   <si>
     <t xml:space="preserve">143.397491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">147.992340087891</t>
+    <t xml:space="preserve">147.99235534668</t>
   </si>
   <si>
     <t xml:space="preserve">149.428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">150.289779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.065826416016</t>
+    <t xml:space="preserve">150.289749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.065795898438</t>
   </si>
   <si>
     <t xml:space="preserve">152.682922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768402099609</t>
+    <t xml:space="preserve">150.76838684082</t>
   </si>
   <si>
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906875610352</t>
+    <t xml:space="preserve">149.906860351562</t>
   </si>
   <si>
     <t xml:space="preserve">153.879486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">156.320495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.395736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.783767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.123916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.458969116211</t>
+    <t xml:space="preserve">156.320510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.395721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.783737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.458953857422</t>
   </si>
   <si>
     <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">155.650421142578</t>
+    <t xml:space="preserve">155.650436401367</t>
   </si>
   <si>
     <t xml:space="preserve">156.081192016602</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">162.207641601562</t>
   </si>
   <si>
-    <t xml:space="preserve">163.643539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.983688354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.729019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.915344238281</t>
+    <t xml:space="preserve">163.643524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.98371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.72900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.91535949707</t>
   </si>
   <si>
     <t xml:space="preserve">162.35124206543</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">165.07942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">163.834991455078</t>
+    <t xml:space="preserve">163.834976196289</t>
   </si>
   <si>
     <t xml:space="preserve">168.908462524414</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">168.669143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">168.334106445312</t>
+    <t xml:space="preserve">168.334121704102</t>
   </si>
   <si>
     <t xml:space="preserve">169.052062988281</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">171.158020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">170.248626708984</t>
+    <t xml:space="preserve">170.248641967773</t>
   </si>
   <si>
     <t xml:space="preserve">171.349472045898</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">176.040023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">176.949447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.140914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.108383178711</t>
+    <t xml:space="preserve">176.949462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.140899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.1083984375</t>
   </si>
   <si>
     <t xml:space="preserve">179.534057617188</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">197.386932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">188.292984008789</t>
+    <t xml:space="preserve">188.29296875</t>
   </si>
   <si>
     <t xml:space="preserve">193.175003051758</t>
@@ -3293,34 +3293,34 @@
     <t xml:space="preserve">195.855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">194.515151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.47932434082</t>
+    <t xml:space="preserve">194.515167236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.479309082031</t>
   </si>
   <si>
     <t xml:space="preserve">180.539184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">174.987060546875</t>
+    <t xml:space="preserve">174.987075805664</t>
   </si>
   <si>
     <t xml:space="preserve">174.077682495117</t>
   </si>
   <si>
-    <t xml:space="preserve">173.599044799805</t>
+    <t xml:space="preserve">173.599060058594</t>
   </si>
   <si>
     <t xml:space="preserve">167.664016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">164.505065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.462341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.782012939453</t>
+    <t xml:space="preserve">164.505081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.462356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">163.404220581055</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">170.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">171.25373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.402465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684539794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.742614746094</t>
+    <t xml:space="preserve">171.253723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.402481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.742630004883</t>
   </si>
   <si>
     <t xml:space="preserve">177.715240478516</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">180.82633972168</t>
   </si>
   <si>
-    <t xml:space="preserve">182.88444519043</t>
+    <t xml:space="preserve">182.884460449219</t>
   </si>
   <si>
     <t xml:space="preserve">182.83659362793</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096420288086</t>
+    <t xml:space="preserve">187.096389770508</t>
   </si>
   <si>
     <t xml:space="preserve">187.000686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">188.723739624023</t>
+    <t xml:space="preserve">188.723724365234</t>
   </si>
   <si>
     <t xml:space="preserve">189.202362060547</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.699890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.231491088867</t>
+    <t xml:space="preserve">174.69987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.231506347656</t>
   </si>
   <si>
     <t xml:space="preserve">175.561401367188</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">177.093032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">179.964813232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.874206542969</t>
+    <t xml:space="preserve">179.964828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.874221801758</t>
   </si>
   <si>
     <t xml:space="preserve">183.50666809082</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">175.896469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">176.614395141602</t>
+    <t xml:space="preserve">176.614410400391</t>
   </si>
   <si>
     <t xml:space="preserve">175.800720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">171.636672973633</t>
+    <t xml:space="preserve">171.636657714844</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">170.296478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">169.14778137207</t>
+    <t xml:space="preserve">169.147766113281</t>
   </si>
   <si>
     <t xml:space="preserve">164.935836791992</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">167.472564697266</t>
   </si>
   <si>
-    <t xml:space="preserve">170.392211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.306732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.928955078125</t>
+    <t xml:space="preserve">170.392227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.306747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.928939819336</t>
   </si>
   <si>
     <t xml:space="preserve">168.764877319336</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">170.535797119141</t>
   </si>
   <si>
-    <t xml:space="preserve">152.060684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.688034057617</t>
+    <t xml:space="preserve">152.060699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.688049316406</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
   </si>
   <si>
-    <t xml:space="preserve">154.932479858398</t>
+    <t xml:space="preserve">154.932495117188</t>
   </si>
   <si>
     <t xml:space="preserve">154.741012573242</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">160.293121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">156.22477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.156402587891</t>
+    <t xml:space="preserve">156.224761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.15641784668</t>
   </si>
   <si>
     <t xml:space="preserve">153.640182495117</t>
@@ -3506,61 +3506,61 @@
     <t xml:space="preserve">143.780395507812</t>
   </si>
   <si>
-    <t xml:space="preserve">147.609436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.387252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.855651855469</t>
+    <t xml:space="preserve">147.609420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.387237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.85563659668</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">137.223175048828</t>
+    <t xml:space="preserve">137.223190307617</t>
   </si>
   <si>
     <t xml:space="preserve">138.946228027344</t>
   </si>
   <si>
-    <t xml:space="preserve">140.717178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.884750366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.990753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.325790405273</t>
+    <t xml:space="preserve">140.717163085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.884773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.325775146484</t>
   </si>
   <si>
     <t xml:space="preserve">131.048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">131.144561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.006088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518997192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.418144226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.289916992188</t>
+    <t xml:space="preserve">131.144577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.006103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.41813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.289924621582</t>
   </si>
   <si>
     <t xml:space="preserve">120.662582397461</t>
@@ -3569,52 +3569,52 @@
     <t xml:space="preserve">117.934379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">114.6318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.072853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.546356201172</t>
+    <t xml:space="preserve">114.631843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.072860717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.546363830566</t>
   </si>
   <si>
     <t xml:space="preserve">115.589096069336</t>
   </si>
   <si>
-    <t xml:space="preserve">112.286560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.430145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.211318969727</t>
+    <t xml:space="preserve">112.286567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.430137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.211326599121</t>
   </si>
   <si>
     <t xml:space="preserve">120.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.10359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.864280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.93775177002</t>
+    <t xml:space="preserve">123.103591918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.864273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937728881836</t>
   </si>
   <si>
     <t xml:space="preserve">127.124084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">123.773666381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.151443481445</t>
+    <t xml:space="preserve">123.773681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
     <t xml:space="preserve">120.08821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">122.242050170898</t>
+    <t xml:space="preserve">122.242042541504</t>
   </si>
   <si>
     <t xml:space="preserve">117.503623962402</t>
@@ -3632,67 +3632,67 @@
     <t xml:space="preserve">121.859161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">131.718933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.293258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.693321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.59757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204429626465</t>
+    <t xml:space="preserve">131.718948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.293273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.693313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.597587585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204444885254</t>
   </si>
   <si>
     <t xml:space="preserve">125.448883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.824890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.73942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.835144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.329132080078</t>
+    <t xml:space="preserve">133.824905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.739410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.83512878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.329147338867</t>
   </si>
   <si>
     <t xml:space="preserve">139.616333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">142.105194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.041961669922</t>
+    <t xml:space="preserve">142.105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.041976928711</t>
   </si>
   <si>
     <t xml:space="preserve">136.170181274414</t>
   </si>
   <si>
-    <t xml:space="preserve">135.260803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.038604736328</t>
+    <t xml:space="preserve">135.260787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.628341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.038619995117</t>
   </si>
   <si>
     <t xml:space="preserve">129.086486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">128.559967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.416381835938</t>
+    <t xml:space="preserve">128.559982299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.416366577148</t>
   </si>
   <si>
     <t xml:space="preserve">126.454010009766</t>
@@ -3701,43 +3701,43 @@
     <t xml:space="preserve">124.539489746094</t>
   </si>
   <si>
-    <t xml:space="preserve">120.997619628906</t>
+    <t xml:space="preserve">120.997627258301</t>
   </si>
   <si>
     <t xml:space="preserve">118.7001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">115.254058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.652328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.705322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.173706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.647216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392524719238</t>
+    <t xml:space="preserve">115.254066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.652336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.70532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.173698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.64720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392532348633</t>
   </si>
   <si>
     <t xml:space="preserve">114.823295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">115.493377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.271194458008</t>
+    <t xml:space="preserve">115.493385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.271186828613</t>
   </si>
   <si>
     <t xml:space="preserve">106.590858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">109.654090881348</t>
+    <t xml:space="preserve">109.654098510742</t>
   </si>
   <si>
     <t xml:space="preserve">107.165214538574</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">114.009620666504</t>
   </si>
   <si>
-    <t xml:space="preserve">114.871147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.435264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.563484191895</t>
+    <t xml:space="preserve">114.871154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.435272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.563491821289</t>
   </si>
   <si>
     <t xml:space="preserve">113.052360534668</t>
@@ -3764,25 +3764,25 @@
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884498596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.932792663574</t>
+    <t xml:space="preserve">111.884506225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.932800292969</t>
   </si>
   <si>
     <t xml:space="preserve">113.381454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">117.292816162109</t>
+    <t xml:space="preserve">117.292808532715</t>
   </si>
   <si>
     <t xml:space="preserve">118.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">118.306884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.761642456055</t>
+    <t xml:space="preserve">118.30687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.761650085449</t>
   </si>
   <si>
     <t xml:space="preserve">119.803825378418</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">117.727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">118.741470336914</t>
+    <t xml:space="preserve">118.74146270752</t>
   </si>
   <si>
     <t xml:space="preserve">115.071548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">111.787933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.918724060059</t>
+    <t xml:space="preserve">111.787925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.918731689453</t>
   </si>
   <si>
     <t xml:space="preserve">107.683403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">112.657119750977</t>
+    <t xml:space="preserve">112.657127380371</t>
   </si>
   <si>
     <t xml:space="preserve">109.904678344727</t>
@@ -3821,49 +3821,49 @@
     <t xml:space="preserve">114.685241699219</t>
   </si>
   <si>
-    <t xml:space="preserve">112.80199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.912620544434</t>
+    <t xml:space="preserve">112.801986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.912612915039</t>
   </si>
   <si>
     <t xml:space="preserve">113.526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">120.190132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.377166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.797706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.866180419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.914459228516</t>
+    <t xml:space="preserve">120.190124511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.377174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.797714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.866172790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.914451599121</t>
   </si>
   <si>
     <t xml:space="preserve">122.025093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">126.56421661377</t>
+    <t xml:space="preserve">126.564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">127.578285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">129.799545288086</t>
+    <t xml:space="preserve">129.799530029297</t>
   </si>
   <si>
     <t xml:space="preserve">130.668746948242</t>
   </si>
   <si>
-    <t xml:space="preserve">131.151626586914</t>
+    <t xml:space="preserve">131.151641845703</t>
   </si>
   <si>
     <t xml:space="preserve">131.537933349609</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">124.970687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">127.916297912598</t>
+    <t xml:space="preserve">127.916290283203</t>
   </si>
   <si>
     <t xml:space="preserve">127.674842834473</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">128.785507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">125.936462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.234146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.958465576172</t>
+    <t xml:space="preserve">125.936454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.234161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.958480834961</t>
   </si>
   <si>
     <t xml:space="preserve">130.861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">128.640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.137557983398</t>
+    <t xml:space="preserve">128.640609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.137573242188</t>
   </si>
   <si>
     <t xml:space="preserve">135.787338256836</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">131.924240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">135.111282348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.890014648438</t>
+    <t xml:space="preserve">135.111267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.890029907227</t>
   </si>
   <si>
     <t xml:space="preserve">131.779373168945</t>
@@ -3944,25 +3944,25 @@
     <t xml:space="preserve">130.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">132.02082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.489639282227</t>
+    <t xml:space="preserve">132.020812988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.489624023438</t>
   </si>
   <si>
     <t xml:space="preserve">132.310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">126.515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.868011474609</t>
+    <t xml:space="preserve">126.515922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.86799621582</t>
   </si>
   <si>
     <t xml:space="preserve">126.467628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">125.888168334961</t>
+    <t xml:space="preserve">125.888191223145</t>
   </si>
   <si>
     <t xml:space="preserve">129.171783447266</t>
@@ -3971,13 +3971,13 @@
     <t xml:space="preserve">128.061172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">128.93034362793</t>
+    <t xml:space="preserve">128.930358886719</t>
   </si>
   <si>
     <t xml:space="preserve">126.226188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">129.123504638672</t>
+    <t xml:space="preserve">129.123489379883</t>
   </si>
   <si>
     <t xml:space="preserve">129.992706298828</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.11555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473754882812</t>
+    <t xml:space="preserve">125.115562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473747253418</t>
   </si>
   <si>
     <t xml:space="preserve">121.397338867188</t>
   </si>
   <si>
-    <t xml:space="preserve">120.721298217773</t>
+    <t xml:space="preserve">120.721305847168</t>
   </si>
   <si>
     <t xml:space="preserve">123.135734558105</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">111.449913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">112.463966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.643051147461</t>
+    <t xml:space="preserve">112.463958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.870445251465</t>
+    <t xml:space="preserve">107.779975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.870452880859</t>
   </si>
   <si>
     <t xml:space="preserve">110.097831726074</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">111.305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">108.50431060791</t>
+    <t xml:space="preserve">108.504302978516</t>
   </si>
   <si>
     <t xml:space="preserve">109.132064819336</t>
@@ -4046,28 +4046,28 @@
     <t xml:space="preserve">124.58438873291</t>
   </si>
   <si>
-    <t xml:space="preserve">125.64673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.586212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.344787597656</t>
+    <t xml:space="preserve">125.646743774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.586227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.344772338867</t>
   </si>
   <si>
     <t xml:space="preserve">121.300765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">124.680969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.771423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.660789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.922416687012</t>
+    <t xml:space="preserve">124.680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.771430969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.660781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.922409057617</t>
   </si>
   <si>
     <t xml:space="preserve">122.314826965332</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">125.018974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">128.592330932617</t>
+    <t xml:space="preserve">128.592315673828</t>
   </si>
   <si>
     <t xml:space="preserve">132.069107055664</t>
@@ -4088,10 +4088,10 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.765319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.302612304688</t>
+    <t xml:space="preserve">130.76530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.302627563477</t>
   </si>
   <si>
     <t xml:space="preserve">126.612518310547</t>
@@ -4100,34 +4100,34 @@
     <t xml:space="preserve">128.206024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">127.047096252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.487808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.240257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.316665649414</t>
+    <t xml:space="preserve">127.04711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.487800598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.240249633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.316650390625</t>
   </si>
   <si>
     <t xml:space="preserve">128.157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">125.260429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.682800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.847839355469</t>
+    <t xml:space="preserve">125.26042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.509826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.682815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.84782409668</t>
   </si>
   <si>
     <t xml:space="preserve">125.067268371582</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.42546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.783645629883</t>
+    <t xml:space="preserve">123.425468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.783653259277</t>
   </si>
   <si>
     <t xml:space="preserve">123.522041320801</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">123.039154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">122.652847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.626556396484</t>
+    <t xml:space="preserve">122.652839660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.62654876709</t>
   </si>
   <si>
     <t xml:space="preserve">124.874122619629</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">125.405296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">122.846000671387</t>
+    <t xml:space="preserve">122.845993041992</t>
   </si>
   <si>
     <t xml:space="preserve">122.169960021973</t>
@@ -4169,13 +4169,13 @@
     <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">121.880226135254</t>
+    <t xml:space="preserve">121.880218505859</t>
   </si>
   <si>
     <t xml:space="preserve">122.218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">120.141845703125</t>
+    <t xml:space="preserve">120.14183807373</t>
   </si>
   <si>
     <t xml:space="preserve">125.550155639648</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">115.168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.188293457031</t>
+    <t xml:space="preserve">113.188285827637</t>
   </si>
   <si>
     <t xml:space="preserve">115.651008605957</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">117.775695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">116.906509399414</t>
+    <t xml:space="preserve">116.906517028809</t>
   </si>
   <si>
     <t xml:space="preserve">114.250648498535</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">113.23657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">112.31909942627</t>
+    <t xml:space="preserve">112.319107055664</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.077667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.42179107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.063606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.242698669434</t>
+    <t xml:space="preserve">112.077659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.421798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.063598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.242691040039</t>
   </si>
   <si>
     <t xml:space="preserve">107.20051574707</t>
@@ -4253,22 +4253,22 @@
     <t xml:space="preserve">108.649169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">108.842330932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.118003845215</t>
+    <t xml:space="preserve">108.842315673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.11799621582</t>
   </si>
   <si>
     <t xml:space="preserve">107.73169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">105.993301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.303207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.013473510742</t>
+    <t xml:space="preserve">105.993309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.303199768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.013465881348</t>
   </si>
   <si>
     <t xml:space="preserve">101.937072753906</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">97.7359619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9431838989258</t>
+    <t xml:space="preserve">98.9431762695312</t>
   </si>
   <si>
     <t xml:space="preserve">97.5911026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1283874511719</t>
+    <t xml:space="preserve">95.1283798217773</t>
   </si>
   <si>
     <t xml:space="preserve">98.5568771362305</t>
@@ -4310,31 +4310,31 @@
     <t xml:space="preserve">93.737678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6797256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2100601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7851028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7078552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9887847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5252075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9694595336914</t>
+    <t xml:space="preserve">93.6797332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2100524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7078475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9887771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5251998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9694671630859</t>
   </si>
   <si>
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342514038086</t>
+    <t xml:space="preserve">93.8342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">95.5340118408203</t>
@@ -4343,34 +4343,34 @@
     <t xml:space="preserve">95.9589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1819229125977</t>
+    <t xml:space="preserve">94.1819305419922</t>
   </si>
   <si>
     <t xml:space="preserve">93.1582183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1090774536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3750915527344</t>
+    <t xml:space="preserve">95.1090698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3750839233398</t>
   </si>
   <si>
     <t xml:space="preserve">94.6068725585938</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3645706176758</t>
+    <t xml:space="preserve">96.3645782470703</t>
   </si>
   <si>
     <t xml:space="preserve">100.874717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">98.7017364501953</t>
+    <t xml:space="preserve">98.7017288208008</t>
   </si>
   <si>
     <t xml:space="preserve">101.164451599121</t>
   </si>
   <si>
-    <t xml:space="preserve">101.985359191895</t>
+    <t xml:space="preserve">101.9853515625</t>
   </si>
   <si>
     <t xml:space="preserve">101.45418548584</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">98.0739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1222686767578</t>
+    <t xml:space="preserve">98.1222763061523</t>
   </si>
   <si>
     <t xml:space="preserve">98.8948974609375</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">100.408088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2853927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299819946289</t>
+    <t xml:space="preserve">99.2853851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885528564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299743652344</t>
   </si>
   <si>
     <t xml:space="preserve">96.8642730712891</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">95.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6384124755859</t>
+    <t xml:space="preserve">94.6384048461914</t>
   </si>
   <si>
     <t xml:space="preserve">94.4236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0679550170898</t>
+    <t xml:space="preserve">95.0679626464844</t>
   </si>
   <si>
     <t xml:space="preserve">95.1265411376953</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">95.4389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3579559326172</t>
+    <t xml:space="preserve">98.3579483032227</t>
   </si>
   <si>
     <t xml:space="preserve">96.6104431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4779968261719</t>
+    <t xml:space="preserve">95.4779891967773</t>
   </si>
   <si>
     <t xml:space="preserve">94.7946090698242</t>
@@ -4469,16 +4469,16 @@
     <t xml:space="preserve">90.8700561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4404983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0848388671875</t>
+    <t xml:space="preserve">90.4405059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.084831237793</t>
   </si>
   <si>
     <t xml:space="preserve">91.5534362792969</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">90.1280975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7054214477539</t>
+    <t xml:space="preserve">92.7054138183594</t>
   </si>
   <si>
     <t xml:space="preserve">92.1196670532227</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5729598999023</t>
+    <t xml:space="preserve">91.5729675292969</t>
   </si>
   <si>
     <t xml:space="preserve">90.0109405517578</t>
@@ -4523,952 +4523,955 @@
     <t xml:space="preserve">91.7877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2716522216797</t>
+    <t xml:space="preserve">93.2716445922852</t>
   </si>
   <si>
     <t xml:space="preserve">93.6816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3091278076172</t>
+    <t xml:space="preserve">98.3091354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6270904541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9397201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8030395507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7682113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5492172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6273193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.11279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1365280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1016998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6679382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3164825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7375946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9676818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8114700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8225708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4626846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0721740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1238784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2800827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6790161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6357498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5032958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.303825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9328536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8003921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3681793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1755828857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4853286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.9581451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2314987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5090713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8563079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3053817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6373138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7824249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4378433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4700241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5175094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.3961410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2008895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.673713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2678985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6193466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6932373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2985153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8146057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4436264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.131217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8800506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3206939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0974807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5006408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7892990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1185684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8394393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2969512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3096008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6526184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3792724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8520889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4183120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.98876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.5201644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1380996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1143569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8758392333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.5243835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2942962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2663345336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6985397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8589553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6093521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9064483642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.3402252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9703369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7180709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.980339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1518402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4600296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2996063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9481582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9872055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0262603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8436584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6135787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2774276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4294128417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7808685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2341613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5117263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.121223449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.9106674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1296539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9037933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3138198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4742431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.6304397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3877105712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3486557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8605270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4547119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9428405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1966705322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.9344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.055778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6958923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7001113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7196350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2578964233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1170120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2647705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7138519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.9286270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3302230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.388801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3149108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2843017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8310012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4753341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4125518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5017395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5645217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.369270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5423431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4515838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6399765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9259719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0863952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3750534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1338806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9275360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3222579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7238464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6721420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2858581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4098815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.4531555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0151672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6858978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5840530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7402496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4362869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6468505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9550247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8352203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7724304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6510543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1043548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2004241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9437026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.749778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7484588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1389617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6002044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1460113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0993728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0598907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5733261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.375846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4789733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.380241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6918106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.244743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2321319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4296035766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.268890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9287796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1827545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7439270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9342727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1388702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5788116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0922470092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3868179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7494049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.675895690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0834655761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3006973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1032104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2628479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0796356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1657562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8624038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6523132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0275192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3308639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8739318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.219512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.466361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.515731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.342391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.046173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.490501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.082931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1191253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7258224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6764526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9359130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8865432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2249984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3632354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8371734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5607070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1855087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.120780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.700592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.910682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.305633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.971580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.317161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.687973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8245620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.94743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.651222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.762580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.293022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.10816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.194282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.404373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.008323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.576622009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.786712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.625984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.93482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.749961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.589241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.996810913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.095542907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.24365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.428512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.503120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.713203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.23104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7384414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4027328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2815017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.170143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.748863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.575523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.118591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.105972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.526161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.699501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.033561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.094451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.045082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.403282165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.218421936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.465270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.527252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.836082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.391754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.638603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.565093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.367622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9726715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9852828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1262588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.663833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.144912719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.267791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.05770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.477882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.860214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.441131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.280403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.55248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.861312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0840225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.632568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3237380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7186965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6594467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.009422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0346527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.4745864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1964721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2035980224609</t>
   </si>
   <si>
     <t xml:space="preserve">99.627082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9397201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8030395507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7682113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5492248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6273193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1127853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1365280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1016998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6679306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3164825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7375946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9676818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8114776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8225708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4626846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0721817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1238784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2800827026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6790161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6357498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.503288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.303825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9328460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8003921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3681793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1755828857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2077560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4853286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.9581527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2314987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5090713500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8563079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3053894042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6373138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7824249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4378433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4700164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5175094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.3961410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2008895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.673713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2678985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6193466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6932373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2985153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8145980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4436264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.1312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8800506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3206939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0974807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7391586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5006408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.789306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1185684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8394393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2969436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3096008300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6526184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3792724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8520889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6916732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4183197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.98876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5201644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1380996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1143569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8758392333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.5243835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2942962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2663345336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6985397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8589630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6093521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9064407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.3402252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9703369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7180709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.980339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1518402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4600296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2996063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9481582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9871978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8436584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6135711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2774276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7808609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2341613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5117340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.121223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.9106674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9037933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3138198852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4742431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6304397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3877029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3486557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8605270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0014114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.454719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9428405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1966705322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9344100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0557708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8953552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6958923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7001037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7196350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2579040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1170120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2647705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7138519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.9286270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3302230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.388801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3149108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.284309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7096405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8310089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4753341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4125442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5017395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5645217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.369270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5423431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2605667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4515914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6399765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9259796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0863952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6177825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3750534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1338806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9275283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3222579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7238464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6721496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2858581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4098892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4531555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0151672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6858978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5840454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7402496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4362869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.646842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9550247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8352203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7724304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6510620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1043548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.2004241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9437026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.749778747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7484588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1389617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6002044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1460113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0598907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5733261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.375846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4789733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.380241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6918106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.244743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2321319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4296035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.268890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9287796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1827545166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7439270019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9342727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1388702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5788116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0922470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3868179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7494049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.675895690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0834655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3006973266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1032104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2628479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0796356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1657562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.8624038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6523132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0275192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3308639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8739318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0077743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.219512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.466361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.515731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.342391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.046173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.490501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.082931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1191253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7258224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9359130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8865432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2249984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3632354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8371734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5607070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1855087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.120780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.700592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.910682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.305633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.971580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.317161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.687973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8245620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.94743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.651222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.762580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.293022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.885452270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.10816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.194282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.404373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.008323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.576622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.786712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.625984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.93482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.749961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.095542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.24365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.428512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.503120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.23104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4027328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2815017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.170143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.748863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.575523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.118591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.105972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.526161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.699501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.033561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.094451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.045082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.403282165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.218421936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.465270996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.527252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.836082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.391754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.638603210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.565093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.367622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9726715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9852828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1262588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.663833618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.144912719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.267791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.05770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.477882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.860214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.441131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.280403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.55248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.861312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0840225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.632568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3237380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7186965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6594467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.009422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0346527099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5283508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.4745864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1964721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2035980224609</t>
   </si>
   <si>
     <t xml:space="preserve">97.6128234863281</t>
@@ -67047,7 +67050,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1506</v>
+        <v>1819</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67099,7 +67102,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67125,7 +67128,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67151,7 +67154,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67177,7 +67180,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67203,7 +67206,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67229,7 +67232,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67255,7 +67258,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67281,7 +67284,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67307,7 +67310,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67333,7 +67336,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67359,7 +67362,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67385,7 +67388,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67411,7 +67414,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67437,7 +67440,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67463,7 +67466,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67489,7 +67492,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67515,7 +67518,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67567,7 +67570,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67593,7 +67596,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67619,7 +67622,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67645,7 +67648,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67671,7 +67674,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67697,7 +67700,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67749,7 +67752,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67775,7 +67778,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67801,7 +67804,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67827,7 +67830,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67879,7 +67882,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67931,7 +67934,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67983,7 +67986,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68035,7 +68038,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68061,7 +68064,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68113,7 +68116,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68139,7 +68142,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68165,7 +68168,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68191,7 +68194,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68217,7 +68220,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68243,7 +68246,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68269,7 +68272,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68295,7 +68298,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68321,7 +68324,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68347,7 +68350,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68373,7 +68376,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68399,7 +68402,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68425,7 +68428,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68451,7 +68454,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68477,7 +68480,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68503,7 +68506,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68529,7 +68532,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68555,7 +68558,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68581,7 +68584,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68607,7 +68610,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68633,7 +68636,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68659,7 +68662,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68685,7 +68688,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68711,7 +68714,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68737,7 +68740,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68763,7 +68766,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68789,7 +68792,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68815,7 +68818,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68841,7 +68844,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68867,7 +68870,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68893,7 +68896,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68919,7 +68922,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68945,7 +68948,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68971,7 +68974,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68997,7 +69000,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -69023,7 +69026,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69049,7 +69052,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69075,7 +69078,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69101,7 +69104,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69127,7 +69130,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69153,7 +69156,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69179,7 +69182,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69205,7 +69208,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69231,7 +69234,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69257,7 +69260,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69283,7 +69286,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69309,7 +69312,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69335,7 +69338,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69361,7 +69364,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69387,7 +69390,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69413,7 +69416,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69439,7 +69442,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69465,7 +69468,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69491,7 +69494,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69517,7 +69520,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69543,7 +69546,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69569,7 +69572,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69595,7 +69598,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69621,7 +69624,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69647,7 +69650,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69673,7 +69676,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69699,7 +69702,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69725,7 +69728,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69751,7 +69754,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69777,7 +69780,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69803,7 +69806,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69829,7 +69832,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69855,7 +69858,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69881,7 +69884,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69907,7 +69910,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69933,7 +69936,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69959,7 +69962,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69985,7 +69988,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -70011,7 +70014,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70037,7 +70040,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70063,7 +70066,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70089,7 +70092,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70115,7 +70118,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70141,7 +70144,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70167,7 +70170,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70193,7 +70196,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70219,7 +70222,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70245,7 +70248,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70271,7 +70274,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70297,7 +70300,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70323,7 +70326,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70349,7 +70352,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70375,7 +70378,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70401,7 +70404,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70427,7 +70430,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70453,7 +70456,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70479,7 +70482,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70505,7 +70508,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70531,7 +70534,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70557,7 +70560,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70583,7 +70586,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70609,7 +70612,7 @@
         <v>77.8600006103516</v>
       </c>
       <c r="G2474" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70635,7 +70638,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2475" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70661,7 +70664,7 @@
         <v>74.1800003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70687,7 +70690,7 @@
         <v>74.1399993896484</v>
       </c>
       <c r="G2477" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70713,7 +70716,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2478" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70739,7 +70742,7 @@
         <v>75.5199966430664</v>
       </c>
       <c r="G2479" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70765,7 +70768,7 @@
         <v>77.6600036621094</v>
       </c>
       <c r="G2480" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70791,7 +70794,7 @@
         <v>77.8399963378906</v>
       </c>
       <c r="G2481" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70817,7 +70820,7 @@
         <v>78.879997253418</v>
       </c>
       <c r="G2482" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70843,7 +70846,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2483" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70869,7 +70872,7 @@
         <v>79.0400009155273</v>
       </c>
       <c r="G2484" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70895,7 +70898,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G2485" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70921,7 +70924,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G2486" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70947,7 +70950,7 @@
         <v>75.6399993896484</v>
       </c>
       <c r="G2487" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70973,7 +70976,7 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2488" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70999,7 +71002,7 @@
         <v>74.1999969482422</v>
       </c>
       <c r="G2489" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -71025,7 +71028,7 @@
         <v>74.2399978637695</v>
       </c>
       <c r="G2490" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -71051,7 +71054,7 @@
         <v>74.9400024414062</v>
       </c>
       <c r="G2491" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -71077,7 +71080,7 @@
         <v>75.2600021362305</v>
       </c>
       <c r="G2492" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71103,7 +71106,7 @@
         <v>75.9400024414062</v>
       </c>
       <c r="G2493" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71129,7 +71132,7 @@
         <v>75.9599990844727</v>
       </c>
       <c r="G2494" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71155,7 +71158,7 @@
         <v>77.9400024414062</v>
       </c>
       <c r="G2495" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71181,7 +71184,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2496" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71207,7 +71210,7 @@
         <v>78.5999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71233,7 +71236,7 @@
         <v>77.6999969482422</v>
       </c>
       <c r="G2498" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71259,7 +71262,7 @@
         <v>77.2399978637695</v>
       </c>
       <c r="G2499" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71285,7 +71288,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2500" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -71311,7 +71314,7 @@
         <v>76.3199996948242</v>
       </c>
       <c r="G2501" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -71337,7 +71340,7 @@
         <v>76.6999969482422</v>
       </c>
       <c r="G2502" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -71363,7 +71366,7 @@
         <v>76.2799987792969</v>
       </c>
       <c r="G2503" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -71389,7 +71392,7 @@
         <v>76.3600006103516</v>
       </c>
       <c r="G2504" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -71415,7 +71418,7 @@
         <v>74.2600021362305</v>
       </c>
       <c r="G2505" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -71441,7 +71444,7 @@
         <v>60.3199996948242</v>
       </c>
       <c r="G2506" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -71467,7 +71470,7 @@
         <v>59.2200012207031</v>
       </c>
       <c r="G2507" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71493,7 +71496,7 @@
         <v>59</v>
       </c>
       <c r="G2508" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71519,7 +71522,7 @@
         <v>60.1599998474121</v>
       </c>
       <c r="G2509" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71545,7 +71548,7 @@
         <v>60.5</v>
       </c>
       <c r="G2510" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71571,7 +71574,7 @@
         <v>60.1800003051758</v>
       </c>
       <c r="G2511" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71597,7 +71600,7 @@
         <v>58.9199981689453</v>
       </c>
       <c r="G2512" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71623,7 +71626,7 @@
         <v>58.8600006103516</v>
       </c>
       <c r="G2513" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71631,7 +71634,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6910763889</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>250882</v>
@@ -71649,9 +71652,35 @@
         <v>58.3600006103516</v>
       </c>
       <c r="G2514" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6910648148</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>224540</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>59.7999992370605</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>58.1800003051758</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>58.6599998474121</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>59</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1975</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">43.298095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0423126220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9276466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8218078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1514739990234</t>
+    <t xml:space="preserve">43.042308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9276428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8218002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1514778137207</t>
   </si>
   <si>
     <t xml:space="preserve">42.4690017700195</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">41.7281074523926</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2871017456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9993553161621</t>
+    <t xml:space="preserve">41.2870979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9993591308594</t>
   </si>
   <si>
     <t xml:space="preserve">39.2761001586914</t>
@@ -77,34 +77,34 @@
     <t xml:space="preserve">38.0765609741211</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8384170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9585838317871</t>
+    <t xml:space="preserve">37.8384208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443748474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9585800170898</t>
   </si>
   <si>
     <t xml:space="preserve">40.2551422119141</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2606353759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3664779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.777702331543</t>
+    <t xml:space="preserve">41.2606315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3664855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7777061462402</t>
   </si>
   <si>
     <t xml:space="preserve">43.0687637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9982147216797</t>
+    <t xml:space="preserve">42.9981994628906</t>
   </si>
   <si>
     <t xml:space="preserve">41.878044128418</t>
@@ -113,28 +113,28 @@
     <t xml:space="preserve">41.2341804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4172286987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.759033203125</t>
+    <t xml:space="preserve">39.4172325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7590408325195</t>
   </si>
   <si>
     <t xml:space="preserve">38.0148239135742</t>
   </si>
   <si>
-    <t xml:space="preserve">38.588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6057777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.402904510498</t>
+    <t xml:space="preserve">38.5881271362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.605770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4029121398926</t>
   </si>
   <si>
     <t xml:space="preserve">40.1228408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3962593078613</t>
+    <t xml:space="preserve">40.3962631225586</t>
   </si>
   <si>
     <t xml:space="preserve">40.4932861328125</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">41.4017562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5483779907227</t>
+    <t xml:space="preserve">42.5483818054199</t>
   </si>
   <si>
     <t xml:space="preserve">41.9397888183594</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">42.5924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2098922729492</t>
+    <t xml:space="preserve">43.209888458252</t>
   </si>
   <si>
     <t xml:space="preserve">42.9011840820312</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">43.2275238037109</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5571975708008</t>
+    <t xml:space="preserve">42.5571937561035</t>
   </si>
   <si>
     <t xml:space="preserve">41.8074913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6454010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7071380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.760066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7578887939453</t>
+    <t xml:space="preserve">42.6454086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7600593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7578811645508</t>
   </si>
   <si>
     <t xml:space="preserve">40.3521614074707</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">40.0081787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1636123657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5726623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1581153869629</t>
+    <t xml:space="preserve">41.1636161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5726661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1581192016602</t>
   </si>
   <si>
     <t xml:space="preserve">39.6200904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1140251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2904205322266</t>
+    <t xml:space="preserve">40.1140213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2904243469238</t>
   </si>
   <si>
     <t xml:space="preserve">39.8405914306641</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">40.1316566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4668235778809</t>
+    <t xml:space="preserve">40.4668273925781</t>
   </si>
   <si>
     <t xml:space="preserve">44.1007232666016</t>
@@ -218,133 +218,133 @@
     <t xml:space="preserve">44.7622375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">45.291446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8647575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3796463012695</t>
+    <t xml:space="preserve">45.2914390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.86474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3796424865723</t>
   </si>
   <si>
     <t xml:space="preserve">45.6883506774902</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9088478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4237442016602</t>
+    <t xml:space="preserve">46.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9088554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4237518310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.203239440918</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8945350646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9386405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3355484008789</t>
+    <t xml:space="preserve">44.89453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9386367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3355445861816</t>
   </si>
   <si>
     <t xml:space="preserve">44.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">44.718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473373413086</t>
+    <t xml:space="preserve">44.7181396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473411560059</t>
   </si>
   <si>
     <t xml:space="preserve">44.9827346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8504295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7765502929688</t>
+    <t xml:space="preserve">44.8504371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">45.6442489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8206520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3057594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1734580993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2616577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6144599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0852508544922</t>
+    <t xml:space="preserve">45.8206558227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3057556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1734619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.261661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6144676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0852546691895</t>
   </si>
   <si>
     <t xml:space="preserve">45.9970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4226684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5119781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1100807189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817817687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1195297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5836753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553649902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2358818054199</t>
+    <t xml:space="preserve">47.4226722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5119743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1100883483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1195182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.583667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5660591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2358741760254</t>
   </si>
   <si>
     <t xml:space="preserve">49.0748710632324</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9679527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.164176940918</t>
+    <t xml:space="preserve">49.9679489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1641807556152</t>
   </si>
   <si>
     <t xml:space="preserve">49.7000274658203</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9855575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7352447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6188888549805</t>
+    <t xml:space="preserve">48.9855651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7352523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6188926696777</t>
   </si>
   <si>
     <t xml:space="preserve">46.9314727783203</t>
@@ -353,88 +353,88 @@
     <t xml:space="preserve">48.0924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0113487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.038387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8962554931641</t>
+    <t xml:space="preserve">49.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.011344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0383834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8962478637695</t>
   </si>
   <si>
     <t xml:space="preserve">49.7446823120117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.414493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1371383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9409065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8339881896973</t>
+    <t xml:space="preserve">50.4144897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1371307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9409103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8339958190918</t>
   </si>
   <si>
     <t xml:space="preserve">49.0302124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5931129455566</t>
+    <t xml:space="preserve">50.5931167602539</t>
   </si>
   <si>
     <t xml:space="preserve">51.2182579040527</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2629203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5755043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7987632751465</t>
+    <t xml:space="preserve">51.2629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.861026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7987747192383</t>
   </si>
   <si>
     <t xml:space="preserve">50.9949913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7717170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2805252075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.191219329834</t>
+    <t xml:space="preserve">50.7717208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2805366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0572624206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1912231445312</t>
   </si>
   <si>
     <t xml:space="preserve">51.6201515197754</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5849380493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0937347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1654357910156</t>
+    <t xml:space="preserve">53.5849266052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0937423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1654396057129</t>
   </si>
   <si>
     <t xml:space="preserve">54.344051361084</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">54.1207809448242</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0666885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6648101806641</t>
+    <t xml:space="preserve">52.0666923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">50.6824150085449</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">51.3968811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6377601623535</t>
+    <t xml:space="preserve">50.6377639770508</t>
   </si>
   <si>
     <t xml:space="preserve">52.2453117370605</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">51.4415321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">51.352222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8880767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0843048095703</t>
+    <t xml:space="preserve">51.3522300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.888069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0843086242676</t>
   </si>
   <si>
     <t xml:space="preserve">50.4591484069824</t>
@@ -488,79 +488,79 @@
     <t xml:space="preserve">49.2981376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">51.9773826599121</t>
+    <t xml:space="preserve">51.9773864746094</t>
   </si>
   <si>
     <t xml:space="preserve">52.5132331848145</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6918487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.289966583252</t>
+    <t xml:space="preserve">52.6918563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2899703979492</t>
   </si>
   <si>
     <t xml:space="preserve">53.1830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7094612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736145019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270698547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1465721130371</t>
+    <t xml:space="preserve">51.7094650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270736694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1465682983398</t>
   </si>
   <si>
     <t xml:space="preserve">50.9056854248047</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0126037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6459350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8245544433594</t>
+    <t xml:space="preserve">50.0126075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.645938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8245506286621</t>
   </si>
   <si>
     <t xml:space="preserve">45.3239250183105</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7258148193359</t>
+    <t xml:space="preserve">45.7258071899414</t>
   </si>
   <si>
     <t xml:space="preserve">45.547191619873</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3956184387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6635437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7704544067383</t>
+    <t xml:space="preserve">46.395622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6635475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7704620361328</t>
   </si>
   <si>
     <t xml:space="preserve">46.1276969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5742416381836</t>
+    <t xml:space="preserve">46.5742378234863</t>
   </si>
   <si>
     <t xml:space="preserve">46.4402732849121</t>
@@ -569,34 +569,34 @@
     <t xml:space="preserve">45.9937324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4578857421875</t>
+    <t xml:space="preserve">45.4578895568848</t>
   </si>
   <si>
     <t xml:space="preserve">45.6811561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3063163757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2440528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4673271179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2088279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3698348999023</t>
+    <t xml:space="preserve">46.5295867919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3063087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2440490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4673194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2088317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3698387145996</t>
   </si>
   <si>
     <t xml:space="preserve">52.156005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5037994384766</t>
+    <t xml:space="preserve">50.5038032531738</t>
   </si>
   <si>
     <t xml:space="preserve">48.8515968322754</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">50.8163833618164</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1289596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2006568908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3616676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4063148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4509735107422</t>
+    <t xml:space="preserve">51.1289558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2006530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3616638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4063186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4509620666504</t>
   </si>
   <si>
     <t xml:space="preserve">53.6742401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9151268005371</t>
+    <t xml:space="preserve">52.9151191711426</t>
   </si>
   <si>
     <t xml:space="preserve">53.2723579406738</t>
@@ -638,40 +638,40 @@
     <t xml:space="preserve">53.852855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5943603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264503479004</t>
+    <t xml:space="preserve">54.7905883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.594367980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264465332031</t>
   </si>
   <si>
     <t xml:space="preserve">55.5050582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2641792297363</t>
+    <t xml:space="preserve">56.2641830444336</t>
   </si>
   <si>
     <t xml:space="preserve">56.1302146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6390190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8000297546387</t>
+    <t xml:space="preserve">55.6390266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8000259399414</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.978645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
+    <t xml:space="preserve">56.9786529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251976013184</t>
   </si>
   <si>
     <t xml:space="preserve">57.3358764648438</t>
@@ -683,91 +683,91 @@
     <t xml:space="preserve">58.8987693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0327301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7648162841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0950050354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1572685241699</t>
+    <t xml:space="preserve">59.0327377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7648086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0950012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1572608947754</t>
   </si>
   <si>
     <t xml:space="preserve">57.3805313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5861930847168</t>
+    <t xml:space="preserve">58.5861968994141</t>
   </si>
   <si>
     <t xml:space="preserve">60.0151252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9434204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3006553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440612792969</t>
+    <t xml:space="preserve">58.943431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3006629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440574645996</t>
   </si>
   <si>
     <t xml:space="preserve">63.4088363647461</t>
   </si>
   <si>
-    <t xml:space="preserve">62.158519744873</t>
+    <t xml:space="preserve">62.1585235595703</t>
   </si>
   <si>
     <t xml:space="preserve">61.622673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8906021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7390365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.515754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8635597229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6758003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9469032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950714111328</t>
+    <t xml:space="preserve">61.8906135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7390174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5157508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8635559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6758079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.946907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.082447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5342750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4950637817383</t>
   </si>
   <si>
     <t xml:space="preserve">63.4379615783691</t>
@@ -776,61 +776,61 @@
     <t xml:space="preserve">63.754264831543</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4831619262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5675506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0705413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8386611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5164260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1668663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0313186645508</t>
+    <t xml:space="preserve">63.4831390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5675582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8386688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5164108276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1668701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0313110351562</t>
   </si>
   <si>
     <t xml:space="preserve">64.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8898010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.431999206543</t>
+    <t xml:space="preserve">63.8897972106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.432014465332</t>
   </si>
   <si>
     <t xml:space="preserve">64.2964630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">64.1609039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6971588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0884017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6425247192383</t>
+    <t xml:space="preserve">64.1608963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.697151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0884170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6425399780273</t>
   </si>
   <si>
     <t xml:space="preserve">60.7721252441406</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1847305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5462074279785</t>
+    <t xml:space="preserve">60.184741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.817310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5462112426758</t>
   </si>
   <si>
     <t xml:space="preserve">59.6877174377441</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">60.6365776062012</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4498710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3987464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2120513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735168457031</t>
+    <t xml:space="preserve">61.4498863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3987503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.212043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735206604004</t>
   </si>
   <si>
     <t xml:space="preserve">63.3927803039551</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">63.1216735839844</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2393646240234</t>
+    <t xml:space="preserve">66.2393493652344</t>
   </si>
   <si>
     <t xml:space="preserve">66.7815628051758</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">66.5104598999023</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3297271728516</t>
+    <t xml:space="preserve">66.3297348022461</t>
   </si>
   <si>
     <t xml:space="preserve">65.9682540893555</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8778915405273</t>
+    <t xml:space="preserve">65.8778991699219</t>
   </si>
   <si>
     <t xml:space="preserve">65.6067810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">65.0194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2001342773438</t>
+    <t xml:space="preserve">65.0193939208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2001266479492</t>
   </si>
   <si>
     <t xml:space="preserve">64.7482986450195</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">64.4771881103516</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9801712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3024063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4260559082031</t>
+    <t xml:space="preserve">63.9801750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4260635375977</t>
   </si>
   <si>
     <t xml:space="preserve">65.4712295532227</t>
@@ -917,118 +917,118 @@
     <t xml:space="preserve">66.600830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4652938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8719329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0586242675781</t>
+    <t xml:space="preserve">66.4652862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0586166381836</t>
   </si>
   <si>
     <t xml:space="preserve">66.3749084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">67.0978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6912078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5437316894531</t>
+    <t xml:space="preserve">67.0978393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6912002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5437240600586</t>
   </si>
   <si>
     <t xml:space="preserve">68.137077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8659820556641</t>
+    <t xml:space="preserve">67.8659744262695</t>
   </si>
   <si>
     <t xml:space="preserve">67.9563369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">68.182258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1311187744141</t>
+    <t xml:space="preserve">68.1822662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1311111450195</t>
   </si>
   <si>
     <t xml:space="preserve">70.3059005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3962783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3903045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5258560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8480987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1643981933594</t>
+    <t xml:space="preserve">70.3962707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3902969360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5258636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1643905639648</t>
   </si>
   <si>
     <t xml:space="preserve">72.7909927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8932952880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2607040405273</t>
+    <t xml:space="preserve">70.8932876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2607192993164</t>
   </si>
   <si>
     <t xml:space="preserve">70.35107421875</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5318145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5769958496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3451232910156</t>
+    <t xml:space="preserve">70.5318069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5770034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3451156616211</t>
   </si>
   <si>
     <t xml:space="preserve">70.4414443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">71.571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.983642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7125396728516</t>
+    <t xml:space="preserve">71.5710372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.9836502075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">65.1097717285156</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5616149902344</t>
+    <t xml:space="preserve">65.5616073608398</t>
   </si>
   <si>
     <t xml:space="preserve">67.4593200683594</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8207931518555</t>
+    <t xml:space="preserve">67.8207778930664</t>
   </si>
   <si>
     <t xml:space="preserve">69.2666625976562</t>
@@ -1037,61 +1037,61 @@
     <t xml:space="preserve">70.0347900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7636795043945</t>
+    <t xml:space="preserve">69.7636871337891</t>
   </si>
   <si>
     <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3237609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3629913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0407562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1763000488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9444274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1703491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.887321472168</t>
+    <t xml:space="preserve">67.3237762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3629989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0407638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1762924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9444351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1703414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8873291015625</t>
   </si>
   <si>
     <t xml:space="preserve">72.6102676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8992385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.49853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4081802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2785873413086</t>
+    <t xml:space="preserve">69.8992233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4081726074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2785797119141</t>
   </si>
   <si>
     <t xml:space="preserve">67.6400604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">69.402229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391723632812</t>
+    <t xml:space="preserve">69.4022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391494750977</t>
   </si>
   <si>
     <t xml:space="preserve">71.7969589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6162185668945</t>
+    <t xml:space="preserve">71.6162261962891</t>
   </si>
   <si>
     <t xml:space="preserve">71.9325103759766</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">71.4354858398438</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6614303588867</t>
+    <t xml:space="preserve">71.6614151000977</t>
   </si>
   <si>
     <t xml:space="preserve">71.254753112793</t>
@@ -1118,76 +1118,76 @@
     <t xml:space="preserve">69.8088760375977</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7517776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0918884277344</t>
+    <t xml:space="preserve">71.7517700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918960571289</t>
   </si>
   <si>
     <t xml:space="preserve">66.9623031616211</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8505821228027</t>
+    <t xml:space="preserve">62.8505859375</t>
   </si>
   <si>
     <t xml:space="preserve">64.3416366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2572326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6186981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0765113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9409523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9017219543457</t>
+    <t xml:space="preserve">63.2572288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6187057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0765037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9409561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017181396484</t>
   </si>
   <si>
     <t xml:space="preserve">60.9528579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0040016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7328948974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113594055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7994422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5496826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7363739013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.651969909668</t>
+    <t xml:space="preserve">60.0040054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7329025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.862491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.811351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7994384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.549690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7363815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6519775390625</t>
   </si>
   <si>
     <t xml:space="preserve">65.2904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4200897216797</t>
+    <t xml:space="preserve">66.4200973510742</t>
   </si>
   <si>
     <t xml:space="preserve">68.2726287841797</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">70.1251602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8600082397461</t>
+    <t xml:space="preserve">68.8600006103516</t>
   </si>
   <si>
     <t xml:space="preserve">69.8540649414062</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">71.1192016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0740280151367</t>
+    <t xml:space="preserve">71.0740203857422</t>
   </si>
   <si>
     <t xml:space="preserve">72.6554412841797</t>
@@ -1217,61 +1217,61 @@
     <t xml:space="preserve">73.6946716308594</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4747085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4687576293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1976470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3783874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6887359619141</t>
+    <t xml:space="preserve">72.4747161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4687652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1976699829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3783798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.688720703125</t>
   </si>
   <si>
     <t xml:space="preserve">73.5591201782227</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1983795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9289474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8466873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.7964859008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1527099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.2576217651367</t>
+    <t xml:space="preserve">74.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6960983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9289321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8466949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.152702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.2576293945312</t>
   </si>
   <si>
     <t xml:space="preserve">75.4312057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">78.0795211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9059371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5908508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3625564575195</t>
+    <t xml:space="preserve">78.0795135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9059448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5908432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.362548828125</t>
   </si>
   <si>
     <t xml:space="preserve">80.7278213500977</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">80.2712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.230094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.102165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3806686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2482147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9286041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893600463867</t>
+    <t xml:space="preserve">81.2300872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1021881103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3806762695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2482223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.928596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893524169922</t>
   </si>
   <si>
     <t xml:space="preserve">83.056510925293</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">81.4127349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8006820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3942794799805</t>
+    <t xml:space="preserve">87.6682357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8006973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3942642211914</t>
   </si>
   <si>
     <t xml:space="preserve">88.8554077148438</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">87.9878616333008</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2206726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9421997070312</t>
+    <t xml:space="preserve">89.2206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9422073364258</t>
   </si>
   <si>
     <t xml:space="preserve">89.0380477905273</t>
   </si>
   <si>
-    <t xml:space="preserve">88.0335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572784423828</t>
+    <t xml:space="preserve">88.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2572937011719</t>
   </si>
   <si>
     <t xml:space="preserve">87.485595703125</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">87.5769195556641</t>
   </si>
   <si>
-    <t xml:space="preserve">87.8052139282227</t>
+    <t xml:space="preserve">87.8052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">89.6772842407227</t>
@@ -1352,31 +1352,31 @@
     <t xml:space="preserve">89.1750259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4033279418945</t>
+    <t xml:space="preserve">89.4033355712891</t>
   </si>
   <si>
     <t xml:space="preserve">88.1248321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6225662231445</t>
+    <t xml:space="preserve">87.6225738525391</t>
   </si>
   <si>
     <t xml:space="preserve">88.3531341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2984161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8418045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1614303588867</t>
+    <t xml:space="preserve">86.2984085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1614379882812</t>
   </si>
   <si>
     <t xml:space="preserve">84.4263229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">84.4719848632812</t>
+    <t xml:space="preserve">84.4719924926758</t>
   </si>
   <si>
     <t xml:space="preserve">83.8327484130859</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">77.668571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7689514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474548339844</t>
+    <t xml:space="preserve">79.7689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474472045898</t>
   </si>
   <si>
     <t xml:space="preserve">80.2255630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">80.4538726806641</t>
+    <t xml:space="preserve">80.4538650512695</t>
   </si>
   <si>
     <t xml:space="preserve">79.3580169677734</t>
@@ -1409,31 +1409,31 @@
     <t xml:space="preserve">79.3123474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587692260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784103393555</t>
+    <t xml:space="preserve">85.1112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6135025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784027099609</t>
   </si>
   <si>
     <t xml:space="preserve">83.6501083374023</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2391586303711</t>
+    <t xml:space="preserve">83.2391510009766</t>
   </si>
   <si>
     <t xml:space="preserve">83.7414245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">84.8372650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591796875</t>
+    <t xml:space="preserve">84.8372802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591644287109</t>
   </si>
   <si>
     <t xml:space="preserve">84.3350143432617</t>
@@ -1445,52 +1445,52 @@
     <t xml:space="preserve">81.9150009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0017852783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2757720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8282165527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5312423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640914916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2436904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199279785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8829345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7368927001953</t>
+    <t xml:space="preserve">81.0017929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.275764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8282089233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.53125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.882926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7368850708008</t>
   </si>
   <si>
     <t xml:space="preserve">83.3761444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4583969116211</t>
+    <t xml:space="preserve">81.458381652832</t>
   </si>
   <si>
     <t xml:space="preserve">79.2666931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">75.1572570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4266662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828979492188</t>
+    <t xml:space="preserve">75.1572494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4266815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3308334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828826904297</t>
   </si>
   <si>
     <t xml:space="preserve">74.8376159667969</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">72.6002578735352</t>
   </si>
   <si>
-    <t xml:space="preserve">72.9198760986328</t>
+    <t xml:space="preserve">72.9198837280273</t>
   </si>
   <si>
     <t xml:space="preserve">74.5179901123047</t>
@@ -1508,61 +1508,61 @@
     <t xml:space="preserve">74.8832778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2485656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4357452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8285675048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.2806243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9700622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0659255981445</t>
+    <t xml:space="preserve">75.2485580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4357376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.8330841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.2806396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9700775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.06591796875</t>
   </si>
   <si>
     <t xml:space="preserve">76.5270690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9516143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.3398895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1161041259766</t>
+    <t xml:space="preserve">79.9516067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.3398971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1161193847656</t>
   </si>
   <si>
     <t xml:space="preserve">73.0568542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5455322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.682502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0934524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9610137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.1025161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3262939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0478057861328</t>
+    <t xml:space="preserve">70.545524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6825180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0934448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9610214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1025085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.326286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477981567383</t>
   </si>
   <si>
     <t xml:space="preserve">70.8651428222656</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">68.5821304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4907913208008</t>
+    <t xml:space="preserve">68.4908065795898</t>
   </si>
   <si>
     <t xml:space="preserve">68.8560943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3217544555664</t>
+    <t xml:space="preserve">71.3217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">66.8013687133789</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">67.3949508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">66.938346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187210083008</t>
+    <t xml:space="preserve">66.9383392333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187133789062</t>
   </si>
   <si>
     <t xml:space="preserve">67.5776062011719</t>
@@ -1604,31 +1604,31 @@
     <t xml:space="preserve">64.0160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4270248413086</t>
+    <t xml:space="preserve">64.4270324707031</t>
   </si>
   <si>
     <t xml:space="preserve">64.2900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7922973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.9447021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2089462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6771774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0016632080078</t>
+    <t xml:space="preserve">64.7923049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1621170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.944694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2089385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6771697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3025894165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0016708374023</t>
   </si>
   <si>
     <t xml:space="preserve">69.4866027832031</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">69.2056655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">69.627082824707</t>
+    <t xml:space="preserve">69.6270904541016</t>
   </si>
   <si>
     <t xml:space="preserve">70.7508544921875</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8913192749023</t>
+    <t xml:space="preserve">69.7675628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8913269042969</t>
   </si>
   <si>
     <t xml:space="preserve">72.5769882202148</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">73.0452270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459487915039</t>
+    <t xml:space="preserve">75.2459411621094</t>
   </si>
   <si>
     <t xml:space="preserve">75.10546875</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9650039672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5904083251953</t>
+    <t xml:space="preserve">74.9649963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5904006958008</t>
   </si>
   <si>
     <t xml:space="preserve">75.0586547851562</t>
@@ -1676,19 +1676,19 @@
     <t xml:space="preserve">75.2927627563477</t>
   </si>
   <si>
-    <t xml:space="preserve">74.6840591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5570297241211</t>
+    <t xml:space="preserve">74.6840744018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.557014465332</t>
   </si>
   <si>
     <t xml:space="preserve">76.135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">74.8713531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8847885131836</t>
+    <t xml:space="preserve">74.8713455200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8847732543945</t>
   </si>
   <si>
     <t xml:space="preserve">76.9784317016602</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">78.6172561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">79.6942138671875</t>
+    <t xml:space="preserve">79.6941986083984</t>
   </si>
   <si>
     <t xml:space="preserve">79.2728042602539</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">79.6005630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2259674072266</t>
+    <t xml:space="preserve">79.2259750366211</t>
   </si>
   <si>
     <t xml:space="preserve">79.4132690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7878494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0219879150391</t>
+    <t xml:space="preserve">79.7878646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.02197265625</t>
   </si>
   <si>
     <t xml:space="preserve">79.0386734008789</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">79.8815155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6775054931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3029174804688</t>
+    <t xml:space="preserve">80.6775131225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3029327392578</t>
   </si>
   <si>
     <t xml:space="preserve">80.7711639404297</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0354080200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.707633972168</t>
+    <t xml:space="preserve">82.0354156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7076416015625</t>
   </si>
   <si>
     <t xml:space="preserve">81.3798751831055</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">81.3330459594727</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2393951416016</t>
+    <t xml:space="preserve">81.2394027709961</t>
   </si>
   <si>
     <t xml:space="preserve">82.2227020263672</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1457443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.349739074707</t>
+    <t xml:space="preserve">81.145751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497543334961</t>
   </si>
   <si>
     <t xml:space="preserve">79.9751510620117</t>
@@ -1766,85 +1766,85 @@
     <t xml:space="preserve">82.2695236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5036392211914</t>
+    <t xml:space="preserve">82.5036468505859</t>
   </si>
   <si>
     <t xml:space="preserve">83.0187072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2528305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9250564575195</t>
+    <t xml:space="preserve">83.2528228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9250717163086</t>
   </si>
   <si>
     <t xml:space="preserve">83.6742401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9718780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0488357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0019989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7980117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.7813110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8582611083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8281478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6876525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2194290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1257781982422</t>
+    <t xml:space="preserve">82.9718933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0020065307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7980194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7813186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.858268737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1559143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8281402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2194366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1257705688477</t>
   </si>
   <si>
     <t xml:space="preserve">85.6408309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0822296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7410354614258</t>
+    <t xml:space="preserve">82.0822372436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7410278320312</t>
   </si>
   <si>
     <t xml:space="preserve">80.2560882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5671615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8481216430664</t>
+    <t xml:space="preserve">81.5671691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8480987548828</t>
   </si>
   <si>
     <t xml:space="preserve">83.8147125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">84.1893081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2829437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3130645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1693267822266</t>
+    <t xml:space="preserve">84.1892929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2829513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3130798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1693420410156</t>
   </si>
   <si>
     <t xml:space="preserve">89.4804077148438</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">91.2597045898438</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2128829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6854858398438</t>
+    <t xml:space="preserve">91.2128982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6854934692383</t>
   </si>
   <si>
     <t xml:space="preserve">91.1656265258789</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1580963134766</t>
+    <t xml:space="preserve">92.1581039428711</t>
   </si>
   <si>
     <t xml:space="preserve">91.5437088012695</t>
@@ -1871,49 +1871,49 @@
     <t xml:space="preserve">90.8348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5984954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1806716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3299789428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8025970458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5340957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0786285400391</t>
+    <t xml:space="preserve">90.598503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1806869506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3299865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8025894165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5340881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
     <t xml:space="preserve">91.3546676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">91.9690628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1033172607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5608444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4115447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8122177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0731964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8293533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3416976928711</t>
+    <t xml:space="preserve">91.9690551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1033020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5608520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4115371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8122100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3417053222656</t>
   </si>
   <si>
     <t xml:space="preserve">101.326644897461</t>
@@ -1922,61 +1922,61 @@
     <t xml:space="preserve">98.6800537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2471771240234</t>
+    <t xml:space="preserve">99.247184753418</t>
   </si>
   <si>
     <t xml:space="preserve">96.884147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6403274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9389419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3170318603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.5060577392578</t>
+    <t xml:space="preserve">97.6403350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9389343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.317024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5060729980469</t>
   </si>
   <si>
     <t xml:space="preserve">97.2622375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">96.9786758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5307540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3019714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.3567581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2074508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1677169799805</t>
+    <t xml:space="preserve">96.9786682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3019638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3567504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2074432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">97.5457992553711</t>
   </si>
   <si>
-    <t xml:space="preserve">96.2225036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7499084472656</t>
+    <t xml:space="preserve">96.2225189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7499008178711</t>
   </si>
   <si>
     <t xml:space="preserve">95.8444213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4663314819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7896347045898</t>
+    <t xml:space="preserve">95.4663238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7896194458008</t>
   </si>
   <si>
     <t xml:space="preserve">102.082809448242</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">100.475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">99.1526565551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.665000915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.097869873047</t>
+    <t xml:space="preserve">99.1526641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.799247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.665008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.097877502441</t>
   </si>
   <si>
     <t xml:space="preserve">99.9088287353516</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">100.192390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">102.366386413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.177337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.784194946289</t>
+    <t xml:space="preserve">102.366371154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.17733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.784187316895</t>
   </si>
   <si>
     <t xml:space="preserve">103.028022766113</t>
@@ -2021,52 +2021,52 @@
     <t xml:space="preserve">100.003349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">101.137596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.704719543457</t>
+    <t xml:space="preserve">101.137603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.704734802246</t>
   </si>
   <si>
     <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">103.500640869141</t>
+    <t xml:space="preserve">103.500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">102.93350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">100.381423950195</t>
+    <t xml:space="preserve">100.381439208984</t>
   </si>
   <si>
     <t xml:space="preserve">98.5855407714844</t>
   </si>
   <si>
-    <t xml:space="preserve">96.6951065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1129302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0581436157227</t>
+    <t xml:space="preserve">96.6951217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0581512451172</t>
   </si>
   <si>
     <t xml:space="preserve">100.948554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">100.286911010742</t>
+    <t xml:space="preserve">100.286918640137</t>
   </si>
   <si>
     <t xml:space="preserve">99.7197875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">100.854049682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6252670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4266128540039</t>
+    <t xml:space="preserve">100.854042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6252593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4266052246094</t>
   </si>
   <si>
     <t xml:space="preserve">94.7101593017578</t>
@@ -2075,16 +2075,16 @@
     <t xml:space="preserve">93.8594818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0957870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2848281860352</t>
+    <t xml:space="preserve">94.0957717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2848205566406</t>
   </si>
   <si>
     <t xml:space="preserve">94.6156463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">94.521125793457</t>
+    <t xml:space="preserve">94.521110534668</t>
   </si>
   <si>
     <t xml:space="preserve">91.6382293701172</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">92.3471374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3074111938477</t>
+    <t xml:space="preserve">91.3074035644531</t>
   </si>
   <si>
     <t xml:space="preserve">92.2998809814453</t>
@@ -2102,25 +2102,25 @@
     <t xml:space="preserve">91.7327575683594</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0163040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1505737304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3718109130859</t>
+    <t xml:space="preserve">92.0163116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1505661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3718185424805</t>
   </si>
   <si>
     <t xml:space="preserve">94.8046951293945</t>
   </si>
   <si>
-    <t xml:space="preserve">98.8690948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9238815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.75951385498</t>
+    <t xml:space="preserve">98.8691024780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9238891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.759521484375</t>
   </si>
   <si>
     <t xml:space="preserve">103.122550964355</t>
@@ -2132,28 +2132,28 @@
     <t xml:space="preserve">105.95817565918</t>
   </si>
   <si>
-    <t xml:space="preserve">108.226684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.659568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.574661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.803428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236305236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.654121398926</t>
+    <t xml:space="preserve">108.226692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.659561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.07738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.574653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.803443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.65412902832</t>
   </si>
   <si>
     <t xml:space="preserve">111.818489074707</t>
@@ -2162,49 +2162,49 @@
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977409362793</t>
+    <t xml:space="preserve">115.977416992188</t>
   </si>
   <si>
     <t xml:space="preserve">117.206199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">117.017158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.315780639648</t>
+    <t xml:space="preserve">117.017166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.315765380859</t>
   </si>
   <si>
     <t xml:space="preserve">114.370559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.425354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.644500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.251365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.589706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.30615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.156829833984</t>
+    <t xml:space="preserve">113.425346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.644508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.251358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.589721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.306144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.156837463379</t>
   </si>
   <si>
     <t xml:space="preserve">111.723960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062316894531</t>
+    <t xml:space="preserve">111.062324523926</t>
   </si>
   <si>
     <t xml:space="preserve">110.117111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">109.833534240723</t>
+    <t xml:space="preserve">109.833541870117</t>
   </si>
   <si>
     <t xml:space="preserve">108.510261535645</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.87328338623</t>
+    <t xml:space="preserve">112.29109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.873275756836</t>
   </si>
   <si>
     <t xml:space="preserve">109.455459594727</t>
   </si>
   <si>
-    <t xml:space="preserve">107.470520019531</t>
+    <t xml:space="preserve">107.470512390137</t>
   </si>
   <si>
     <t xml:space="preserve">110.495185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">108.037643432617</t>
+    <t xml:space="preserve">108.037651062012</t>
   </si>
   <si>
     <t xml:space="preserve">107.848602294922</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">106.430786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">109.171897888184</t>
+    <t xml:space="preserve">109.171905517578</t>
   </si>
   <si>
     <t xml:space="preserve">109.266410827637</t>
@@ -2258,28 +2258,28 @@
     <t xml:space="preserve">105.769142150879</t>
   </si>
   <si>
-    <t xml:space="preserve">107.754081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.415725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.32120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.211631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.276031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.465072631836</t>
+    <t xml:space="preserve">107.754089355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.415733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.321212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.211616516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.276039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
     <t xml:space="preserve">109.928062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">104.54035949707</t>
+    <t xml:space="preserve">104.540374755859</t>
   </si>
   <si>
     <t xml:space="preserve">98.7745742797852</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">101.893768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8143005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.132171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.485565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.400680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.888336181641</t>
+    <t xml:space="preserve">99.8143081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.132179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.485580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.400672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.888328552246</t>
   </si>
   <si>
     <t xml:space="preserve">106.52530670166</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">104.445838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">102.55542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.08699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.629447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.05689239502</t>
+    <t xml:space="preserve">102.55541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.086990356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.629440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.05687713623</t>
   </si>
   <si>
     <t xml:space="preserve">122.310325622559</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">126.091171264648</t>
   </si>
   <si>
-    <t xml:space="preserve">132.329574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592651367188</t>
+    <t xml:space="preserve">132.32958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592636108398</t>
   </si>
   <si>
     <t xml:space="preserve">141.876220703125</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">136.583023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">145.089920043945</t>
+    <t xml:space="preserve">145.089935302734</t>
   </si>
   <si>
     <t xml:space="preserve">144.239242553711</t>
@@ -2354,34 +2354,34 @@
     <t xml:space="preserve">155.959854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">150.383102416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.691360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.755752563477</t>
+    <t xml:space="preserve">150.383117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.691345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.755737304688</t>
   </si>
   <si>
     <t xml:space="preserve">157.944793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">153.313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791320800781</t>
+    <t xml:space="preserve">153.313278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.791305541992</t>
   </si>
   <si>
     <t xml:space="preserve">146.885818481445</t>
   </si>
   <si>
-    <t xml:space="preserve">146.507751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.522796630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.318695068359</t>
+    <t xml:space="preserve">146.507736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.522811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.318710327148</t>
   </si>
   <si>
     <t xml:space="preserve">147.641998291016</t>
@@ -2390,28 +2390,28 @@
     <t xml:space="preserve">153.596832275391</t>
   </si>
   <si>
-    <t xml:space="preserve">151.706405639648</t>
+    <t xml:space="preserve">151.706420898438</t>
   </si>
   <si>
     <t xml:space="preserve">163.048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">167.302398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.107894897461</t>
+    <t xml:space="preserve">167.302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.10791015625</t>
   </si>
   <si>
     <t xml:space="preserve">174.675033569336</t>
   </si>
   <si>
-    <t xml:space="preserve">169.381851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.440811157227</t>
+    <t xml:space="preserve">169.381866455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.440826416016</t>
   </si>
   <si>
     <t xml:space="preserve">191.688842773438</t>
@@ -2420,43 +2420,43 @@
     <t xml:space="preserve">197.927230834961</t>
   </si>
   <si>
-    <t xml:space="preserve">186.206634521484</t>
+    <t xml:space="preserve">186.206604003906</t>
   </si>
   <si>
     <t xml:space="preserve">163.521545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839401245117</t>
+    <t xml:space="preserve">171.839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">178.172317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">171.55583190918</t>
+    <t xml:space="preserve">171.555816650391</t>
   </si>
   <si>
     <t xml:space="preserve">169.098281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">163.994140625</t>
+    <t xml:space="preserve">163.994125366211</t>
   </si>
   <si>
     <t xml:space="preserve">164.655792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">156.905059814453</t>
+    <t xml:space="preserve">156.905044555664</t>
   </si>
   <si>
     <t xml:space="preserve">150.855728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">152.651611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.0146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.6064453125</t>
+    <t xml:space="preserve">152.651626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.014633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.606460571289</t>
   </si>
   <si>
     <t xml:space="preserve">157.850280761719</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">161.510147094727</t>
   </si>
   <si>
-    <t xml:space="preserve">162.36572265625</t>
+    <t xml:space="preserve">162.365707397461</t>
   </si>
   <si>
     <t xml:space="preserve">161.890411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">161.129898071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.13362121582</t>
+    <t xml:space="preserve">161.129913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.133605957031</t>
   </si>
   <si>
     <t xml:space="preserve">162.270645141602</t>
@@ -2486,16 +2486,16 @@
     <t xml:space="preserve">164.457061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">162.936080932617</t>
+    <t xml:space="preserve">162.936065673828</t>
   </si>
   <si>
     <t xml:space="preserve">161.320022583008</t>
   </si>
   <si>
-    <t xml:space="preserve">161.985458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.555847167969</t>
+    <t xml:space="preserve">161.985473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.55583190918</t>
   </si>
   <si>
     <t xml:space="preserve">162.841033935547</t>
@@ -2510,49 +2510,49 @@
     <t xml:space="preserve">169.685485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">170.35090637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.031143188477</t>
+    <t xml:space="preserve">170.350921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.031158447266</t>
   </si>
   <si>
     <t xml:space="preserve">164.362014770508</t>
   </si>
   <si>
-    <t xml:space="preserve">165.122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647216796875</t>
+    <t xml:space="preserve">165.122497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647201538086</t>
   </si>
   <si>
     <t xml:space="preserve">169.305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">169.400283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.966979980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.495346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.358322143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.939804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.66569519043</t>
+    <t xml:space="preserve">169.400299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.96696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.358306884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.939788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.665710449219</t>
   </si>
   <si>
     <t xml:space="preserve">162.175598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">164.742248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.228652954102</t>
+    <t xml:space="preserve">164.742279052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.22868347168</t>
   </si>
   <si>
     <t xml:space="preserve">157.802734375</t>
@@ -2561,40 +2561,40 @@
     <t xml:space="preserve">152.669418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">149.817535400391</t>
+    <t xml:space="preserve">149.81755065918</t>
   </si>
   <si>
     <t xml:space="preserve">146.77555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.254577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.72248840332</t>
+    <t xml:space="preserve">150.768173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.254592895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.722503662109</t>
   </si>
   <si>
     <t xml:space="preserve">152.289154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">151.62370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.391616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.760757446289</t>
+    <t xml:space="preserve">151.623733520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.3916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.7607421875</t>
   </si>
   <si>
     <t xml:space="preserve">151.243469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">154.190399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.855819702148</t>
+    <t xml:space="preserve">154.190383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.855834960938</t>
   </si>
   <si>
     <t xml:space="preserve">154.950881958008</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">155.806427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">159.41877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.634826660156</t>
+    <t xml:space="preserve">159.418792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.634811401367</t>
   </si>
   <si>
     <t xml:space="preserve">138.600234985352</t>
@@ -2642,94 +2642,94 @@
     <t xml:space="preserve">143.258270263672</t>
   </si>
   <si>
-    <t xml:space="preserve">147.060760498047</t>
+    <t xml:space="preserve">147.060745239258</t>
   </si>
   <si>
     <t xml:space="preserve">147.726165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">149.247177124023</t>
+    <t xml:space="preserve">149.247161865234</t>
   </si>
   <si>
     <t xml:space="preserve">152.95458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">150.387908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.034851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.654602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.080520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.795349121094</t>
+    <t xml:space="preserve">150.387924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.03483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.65461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.080535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.795333862305</t>
   </si>
   <si>
     <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
-    <t xml:space="preserve">168.069442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.91389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.670654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.48796081543</t>
+    <t xml:space="preserve">168.069412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.29411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.670684814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.487945556641</t>
   </si>
   <si>
     <t xml:space="preserve">178.716354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">180.712661743164</t>
+    <t xml:space="preserve">180.712692260742</t>
   </si>
   <si>
     <t xml:space="preserve">178.241058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">181.853408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.666976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.039825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.663284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.275619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.089202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.568206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.286758422852</t>
+    <t xml:space="preserve">181.853393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.6669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.039840698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.663269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.275650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.089218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.568237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.286743164062</t>
   </si>
   <si>
     <t xml:space="preserve">178.050933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">179.191665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.529937744141</t>
+    <t xml:space="preserve">179.191650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.529922485352</t>
   </si>
   <si>
     <t xml:space="preserve">177.860809326172</t>
@@ -2738,40 +2738,40 @@
     <t xml:space="preserve">184.610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">189.838607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.264511108398</t>
+    <t xml:space="preserve">189.838592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.264526367188</t>
   </si>
   <si>
     <t xml:space="preserve">159.703979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">163.886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.217559814453</t>
+    <t xml:space="preserve">163.88671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.217575073242</t>
   </si>
   <si>
     <t xml:space="preserve">164.932388305664</t>
   </si>
   <si>
-    <t xml:space="preserve">164.07682800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.947174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.844711303711</t>
+    <t xml:space="preserve">164.076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.947189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.844741821289</t>
   </si>
   <si>
     <t xml:space="preserve">164.266952514648</t>
   </si>
   <si>
-    <t xml:space="preserve">167.879287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.696594238281</t>
+    <t xml:space="preserve">167.879302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.696578979492</t>
   </si>
   <si>
     <t xml:space="preserve">161.605224609375</t>
@@ -2789,25 +2789,25 @@
     <t xml:space="preserve">159.32373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468170166016</t>
+    <t xml:space="preserve">158.468154907227</t>
   </si>
   <si>
     <t xml:space="preserve">158.848419189453</t>
   </si>
   <si>
-    <t xml:space="preserve">163.221282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.038558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.608901977539</t>
+    <t xml:space="preserve">163.221267700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.038543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.608917236328</t>
   </si>
   <si>
     <t xml:space="preserve">161.700286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">161.224990844727</t>
+    <t xml:space="preserve">161.224960327148</t>
   </si>
   <si>
     <t xml:space="preserve">153.810150146484</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">152.859512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">151.528656005859</t>
+    <t xml:space="preserve">151.52864074707</t>
   </si>
   <si>
     <t xml:space="preserve">155.616317749023</t>
@@ -2825,67 +2825,67 @@
     <t xml:space="preserve">154.4755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">154.570663452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.992874145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.826232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.970672607422</t>
+    <t xml:space="preserve">154.570648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.992858886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.826202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">179.001556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">168.924987792969</t>
+    <t xml:space="preserve">168.924957275391</t>
   </si>
   <si>
     <t xml:space="preserve">171.681793212891</t>
   </si>
   <si>
-    <t xml:space="preserve">171.111389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.784255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.499038696289</t>
+    <t xml:space="preserve">171.111419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.784240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
     <t xml:space="preserve">170.255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">173.868194580078</t>
+    <t xml:space="preserve">173.868209838867</t>
   </si>
   <si>
     <t xml:space="preserve">173.202758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">175.389221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.434875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.149703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.195373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.438583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.18669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.813858032227</t>
+    <t xml:space="preserve">175.389190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.43489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.195358276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.438568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.813842773438</t>
   </si>
   <si>
     <t xml:space="preserve">155.996566772461</t>
@@ -2900,70 +2900,70 @@
     <t xml:space="preserve">157.137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">154.000259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.197784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.057067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.155807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.706420898438</t>
+    <t xml:space="preserve">154.000274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.197799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.057052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.155822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.706405639648</t>
   </si>
   <si>
     <t xml:space="preserve">135.082962036133</t>
   </si>
   <si>
-    <t xml:space="preserve">138.6953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.987899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181716918945</t>
+    <t xml:space="preserve">138.695297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.987915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181732177734</t>
   </si>
   <si>
     <t xml:space="preserve">136.033569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">133.276763916016</t>
+    <t xml:space="preserve">133.276779174805</t>
   </si>
   <si>
     <t xml:space="preserve">134.037261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">133.086654663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.273086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.136016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.519973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.900238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.044677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.848983764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.463195800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.229248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.492248535156</t>
+    <t xml:space="preserve">133.086669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.273071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.136032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.520004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.90022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.044662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.463180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.229232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.492233276367</t>
   </si>
   <si>
     <t xml:space="preserve">143.59098815918</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">141.784820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">148.20149230957</t>
+    <t xml:space="preserve">148.201477050781</t>
   </si>
   <si>
     <t xml:space="preserve">148.058898925781</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">146.300262451172</t>
   </si>
   <si>
-    <t xml:space="preserve">145.01692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.874313354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.984191894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.794067382812</t>
+    <t xml:space="preserve">145.016906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.874328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.98420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">133.324295043945</t>
@@ -2999,22 +2999,22 @@
     <t xml:space="preserve">134.274932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">133.894668579102</t>
+    <t xml:space="preserve">133.894683837891</t>
   </si>
   <si>
     <t xml:space="preserve">134.227386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">131.660736083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.847152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.605773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.423065185547</t>
+    <t xml:space="preserve">131.660720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.847137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.605804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.423049926758</t>
   </si>
   <si>
     <t xml:space="preserve">128.333541870117</t>
@@ -3026,25 +3026,25 @@
     <t xml:space="preserve">131.185424804688</t>
   </si>
   <si>
-    <t xml:space="preserve">134.655151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.031707763672</t>
+    <t xml:space="preserve">134.655166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.031723022461</t>
   </si>
   <si>
     <t xml:space="preserve">136.983856201172</t>
   </si>
   <si>
-    <t xml:space="preserve">136.744552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.84538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.797515869141</t>
+    <t xml:space="preserve">136.744537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.845397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.79753112793</t>
   </si>
   <si>
     <t xml:space="preserve">138.084701538086</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">133.05908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">132.963363647461</t>
+    <t xml:space="preserve">132.963348388672</t>
   </si>
   <si>
     <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">136.218048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.510314941406</t>
+    <t xml:space="preserve">136.218032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.510345458984</t>
   </si>
   <si>
     <t xml:space="preserve">138.659057617188</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">143.2060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.306884765625</t>
+    <t xml:space="preserve">144.306900024414</t>
   </si>
   <si>
     <t xml:space="preserve">144.019714355469</t>
   </si>
   <si>
-    <t xml:space="preserve">146.269271850586</t>
+    <t xml:space="preserve">146.269287109375</t>
   </si>
   <si>
     <t xml:space="preserve">145.790649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">147.322250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.843612670898</t>
+    <t xml:space="preserve">147.322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.843643188477</t>
   </si>
   <si>
     <t xml:space="preserve">147.226547241211</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">143.397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">147.99235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.428237915039</t>
+    <t xml:space="preserve">147.992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.42822265625</t>
   </si>
   <si>
     <t xml:space="preserve">150.289764404297</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.879501342773</t>
+    <t xml:space="preserve">149.906875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.879470825195</t>
   </si>
   <si>
     <t xml:space="preserve">156.320495605469</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">155.458953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">155.028182983398</t>
+    <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
     <t xml:space="preserve">155.650421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">156.081192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.90510559082</t>
+    <t xml:space="preserve">156.081207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.905090332031</t>
   </si>
   <si>
     <t xml:space="preserve">160.149536132812</t>
@@ -3164,49 +3164,49 @@
     <t xml:space="preserve">162.207641601562</t>
   </si>
   <si>
-    <t xml:space="preserve">163.643524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.983703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.729019165039</t>
+    <t xml:space="preserve">163.643539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.983688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.72900390625</t>
   </si>
   <si>
     <t xml:space="preserve">160.915344238281</t>
   </si>
   <si>
-    <t xml:space="preserve">162.35124206543</t>
+    <t xml:space="preserve">162.351226806641</t>
   </si>
   <si>
     <t xml:space="preserve">165.07942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">163.834976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.908477783203</t>
+    <t xml:space="preserve">163.834991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.908462524414</t>
   </si>
   <si>
     <t xml:space="preserve">164.600799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">168.142654418945</t>
+    <t xml:space="preserve">168.142639160156</t>
   </si>
   <si>
     <t xml:space="preserve">168.860595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.036666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.669143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.334106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.052047729492</t>
+    <t xml:space="preserve">166.036682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.669158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.334121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">171.349472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">176.0400390625</t>
+    <t xml:space="preserve">176.040054321289</t>
   </si>
   <si>
     <t xml:space="preserve">176.949447631836</t>
@@ -3239,40 +3239,40 @@
     <t xml:space="preserve">177.475921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">177.810989379883</t>
+    <t xml:space="preserve">177.810974121094</t>
   </si>
   <si>
     <t xml:space="preserve">181.352844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">182.740844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.990417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.016052246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.409194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.270721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.568145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.643371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.908294677734</t>
+    <t xml:space="preserve">182.740859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.016036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.4091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.270706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.568161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.64338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.908309936523</t>
   </si>
   <si>
     <t xml:space="preserve">196.812591552734</t>
   </si>
   <si>
-    <t xml:space="preserve">197.386947631836</t>
+    <t xml:space="preserve">197.386932373047</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">193.175003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">190.35107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.026290893555</t>
+    <t xml:space="preserve">190.351089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.026306152344</t>
   </si>
   <si>
     <t xml:space="preserve">193.940811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">195.855316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.515167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.479309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.539184570312</t>
+    <t xml:space="preserve">195.855331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.515151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.479293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.539169311523</t>
   </si>
   <si>
     <t xml:space="preserve">174.987060546875</t>
@@ -3311,16 +3311,16 @@
     <t xml:space="preserve">173.599044799805</t>
   </si>
   <si>
-    <t xml:space="preserve">167.664016723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.505065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.462356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.781997680664</t>
+    <t xml:space="preserve">167.664031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.505081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.462341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.782012939453</t>
   </si>
   <si>
     <t xml:space="preserve">163.404205322266</t>
@@ -3338,22 +3338,22 @@
     <t xml:space="preserve">170.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">171.253753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.402465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.742630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.715240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.44856262207</t>
+    <t xml:space="preserve">171.25373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.402481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684524536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.742614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.448577880859</t>
   </si>
   <si>
     <t xml:space="preserve">180.826354980469</t>
@@ -3365,43 +3365,43 @@
     <t xml:space="preserve">182.83659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">179.342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.096389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.000686645508</t>
+    <t xml:space="preserve">179.34260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.000671386719</t>
   </si>
   <si>
     <t xml:space="preserve">188.723739624023</t>
   </si>
   <si>
-    <t xml:space="preserve">189.202346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.426315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.79899597168</t>
+    <t xml:space="preserve">189.202362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
     <t xml:space="preserve">174.69987487793</t>
   </si>
   <si>
-    <t xml:space="preserve">176.231506347656</t>
+    <t xml:space="preserve">176.231521606445</t>
   </si>
   <si>
     <t xml:space="preserve">175.561416625977</t>
   </si>
   <si>
-    <t xml:space="preserve">177.093032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.964813232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.87419128418</t>
+    <t xml:space="preserve">177.093048095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.964828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.874206542969</t>
   </si>
   <si>
     <t xml:space="preserve">183.50666809082</t>
@@ -3410,16 +3410,16 @@
     <t xml:space="preserve">175.896453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">176.614410400391</t>
+    <t xml:space="preserve">176.614395141602</t>
   </si>
   <si>
     <t xml:space="preserve">175.800720214844</t>
   </si>
   <si>
-    <t xml:space="preserve">171.636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.865707397461</t>
+    <t xml:space="preserve">171.636672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.86572265625</t>
   </si>
   <si>
     <t xml:space="preserve">179.294738769531</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">170.296478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">169.147766113281</t>
+    <t xml:space="preserve">169.14778137207</t>
   </si>
   <si>
     <t xml:space="preserve">164.935836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">167.472549438477</t>
+    <t xml:space="preserve">167.472579956055</t>
   </si>
   <si>
     <t xml:space="preserve">170.392211914062</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">172.785369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">170.53581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.060699462891</t>
+    <t xml:space="preserve">170.535797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.06071472168</t>
   </si>
   <si>
     <t xml:space="preserve">153.688034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">153.40087890625</t>
+    <t xml:space="preserve">153.400863647461</t>
   </si>
   <si>
     <t xml:space="preserve">154.932479858398</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">154.741012573242</t>
   </si>
   <si>
-    <t xml:space="preserve">159.240142822266</t>
+    <t xml:space="preserve">159.240158081055</t>
   </si>
   <si>
     <t xml:space="preserve">157.947845458984</t>
@@ -3494,46 +3494,46 @@
     <t xml:space="preserve">152.156433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">153.640167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.183792114258</t>
+    <t xml:space="preserve">153.640182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.183807373047</t>
   </si>
   <si>
     <t xml:space="preserve">141.770156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">143.780395507812</t>
+    <t xml:space="preserve">143.780380249023</t>
   </si>
   <si>
     <t xml:space="preserve">147.609436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">141.387237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.855651855469</t>
+    <t xml:space="preserve">141.387252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.85563659668</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">137.223175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.946243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.717178344727</t>
+    <t xml:space="preserve">137.223190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.946228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.717163085938</t>
   </si>
   <si>
     <t xml:space="preserve">128.94287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">126.884773254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.99072265625</t>
+    <t xml:space="preserve">126.884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.990737915039</t>
   </si>
   <si>
     <t xml:space="preserve">129.325775146484</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">131.048843383789</t>
   </si>
   <si>
-    <t xml:space="preserve">131.144592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.006088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.698432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.975372314453</t>
+    <t xml:space="preserve">131.144577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.006118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.698440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.975364685059</t>
   </si>
   <si>
     <t xml:space="preserve">120.518989562988</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">119.41813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">122.289924621582</t>
+    <t xml:space="preserve">122.289916992188</t>
   </si>
   <si>
     <t xml:space="preserve">120.662574768066</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">117.934387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">114.631843566895</t>
+    <t xml:space="preserve">114.631851196289</t>
   </si>
   <si>
     <t xml:space="preserve">117.072853088379</t>
   </si>
   <si>
-    <t xml:space="preserve">116.546363830566</t>
+    <t xml:space="preserve">116.546371459961</t>
   </si>
   <si>
     <t xml:space="preserve">115.58910369873</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">112.430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">116.211318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.136085510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.103591918945</t>
+    <t xml:space="preserve">116.211334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.136093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.10359954834</t>
   </si>
   <si>
     <t xml:space="preserve">122.864280700684</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">123.77367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">123.151443481445</t>
+    <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
     <t xml:space="preserve">120.088218688965</t>
@@ -3620,28 +3620,28 @@
     <t xml:space="preserve">117.503616333008</t>
   </si>
   <si>
-    <t xml:space="preserve">120.806159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541236877441</t>
+    <t xml:space="preserve">120.806167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541229248047</t>
   </si>
   <si>
     <t xml:space="preserve">117.599349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">121.859153747559</t>
+    <t xml:space="preserve">121.859161376953</t>
   </si>
   <si>
     <t xml:space="preserve">131.718933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">132.293273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.693328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.597587585449</t>
+    <t xml:space="preserve">132.29328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.597579956055</t>
   </si>
   <si>
     <t xml:space="preserve">125.257431030273</t>
@@ -3653,25 +3653,25 @@
     <t xml:space="preserve">125.448883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">133.824920654297</t>
+    <t xml:space="preserve">133.824890136719</t>
   </si>
   <si>
     <t xml:space="preserve">135.73942565918</t>
   </si>
   <si>
-    <t xml:space="preserve">135.83512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.329162597656</t>
+    <t xml:space="preserve">135.835159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.329147338867</t>
   </si>
   <si>
     <t xml:space="preserve">139.616317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">142.105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.041976928711</t>
+    <t xml:space="preserve">142.105194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.041961669922</t>
   </si>
   <si>
     <t xml:space="preserve">136.170181274414</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">135.260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">132.628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.038604736328</t>
+    <t xml:space="preserve">132.628341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.038589477539</t>
   </si>
   <si>
     <t xml:space="preserve">129.086471557617</t>
@@ -3692,37 +3692,37 @@
     <t xml:space="preserve">128.559982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">128.416381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.454010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.539474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.997627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.7001953125</t>
+    <t xml:space="preserve">128.416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.454002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.539482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.997611999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.700187683105</t>
   </si>
   <si>
     <t xml:space="preserve">115.254066467285</t>
   </si>
   <si>
-    <t xml:space="preserve">118.652336120605</t>
+    <t xml:space="preserve">118.652320861816</t>
   </si>
   <si>
     <t xml:space="preserve">119.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">118.173698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.64720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392532348633</t>
+    <t xml:space="preserve">118.173706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392524719238</t>
   </si>
   <si>
     <t xml:space="preserve">114.823287963867</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">115.493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">109.271194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.590866088867</t>
+    <t xml:space="preserve">109.271186828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.590858459473</t>
   </si>
   <si>
     <t xml:space="preserve">109.654098510742</t>
@@ -3743,19 +3743,19 @@
     <t xml:space="preserve">107.165222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">114.009628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.871154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.435264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.563484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.052352905273</t>
+    <t xml:space="preserve">114.009620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.871147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.435272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.563491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.052360534668</t>
   </si>
   <si>
     <t xml:space="preserve">114.057487487793</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884506225586</t>
+    <t xml:space="preserve">111.884498596191</t>
   </si>
   <si>
     <t xml:space="preserve">111.932792663574</t>
@@ -3788,10 +3788,10 @@
     <t xml:space="preserve">119.803825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">116.278762817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.258583068848</t>
+    <t xml:space="preserve">116.278770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.258590698242</t>
   </si>
   <si>
     <t xml:space="preserve">117.727416992188</t>
@@ -3809,16 +3809,16 @@
     <t xml:space="preserve">110.918731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">107.683403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.657119750977</t>
+    <t xml:space="preserve">107.683395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.657112121582</t>
   </si>
   <si>
     <t xml:space="preserve">109.904678344727</t>
   </si>
   <si>
-    <t xml:space="preserve">114.685234069824</t>
+    <t xml:space="preserve">114.685241699219</t>
   </si>
   <si>
     <t xml:space="preserve">112.801986694336</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">113.912612915039</t>
   </si>
   <si>
-    <t xml:space="preserve">113.526321411133</t>
+    <t xml:space="preserve">113.526313781738</t>
   </si>
   <si>
     <t xml:space="preserve">120.190132141113</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">123.377174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">122.797714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604545593262</t>
+    <t xml:space="preserve">122.797706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604553222656</t>
   </si>
   <si>
     <t xml:space="preserve">120.866172790527</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">126.564224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">127.578285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.799545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.668731689453</t>
+    <t xml:space="preserve">127.578269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.799530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.668746948242</t>
   </si>
   <si>
     <t xml:space="preserve">131.151641845703</t>
@@ -3896,22 +3896,22 @@
     <t xml:space="preserve">136.077056884766</t>
   </si>
   <si>
-    <t xml:space="preserve">132.841735839844</t>
+    <t xml:space="preserve">132.841720581055</t>
   </si>
   <si>
     <t xml:space="preserve">128.785491943359</t>
   </si>
   <si>
-    <t xml:space="preserve">125.936454772949</t>
+    <t xml:space="preserve">125.936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">130.234146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">130.958480834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.861907958984</t>
+    <t xml:space="preserve">130.958465576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.861892700195</t>
   </si>
   <si>
     <t xml:space="preserve">128.640625</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">130.910171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">131.924240112305</t>
+    <t xml:space="preserve">131.924255371094</t>
   </si>
   <si>
     <t xml:space="preserve">135.111282348633</t>
@@ -3950,31 +3950,31 @@
     <t xml:space="preserve">131.489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">132.310562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.515922546387</t>
+    <t xml:space="preserve">132.310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.515914916992</t>
   </si>
   <si>
     <t xml:space="preserve">127.868003845215</t>
   </si>
   <si>
-    <t xml:space="preserve">126.467643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.888191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.171813964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.061157226562</t>
+    <t xml:space="preserve">126.467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.888175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.171798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.061172485352</t>
   </si>
   <si>
     <t xml:space="preserve">128.93034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">126.226188659668</t>
+    <t xml:space="preserve">126.226196289062</t>
   </si>
   <si>
     <t xml:space="preserve">129.123504638672</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.115562438965</t>
+    <t xml:space="preserve">125.11555480957</t>
   </si>
   <si>
     <t xml:space="preserve">123.473747253418</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">120.721305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">123.135726928711</t>
+    <t xml:space="preserve">123.135734558105</t>
   </si>
   <si>
     <t xml:space="preserve">111.449913024902</t>
   </si>
   <si>
-    <t xml:space="preserve">112.463966369629</t>
+    <t xml:space="preserve">112.463958740234</t>
   </si>
   <si>
     <t xml:space="preserve">111.643058776855</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779975891113</t>
+    <t xml:space="preserve">107.779983520508</t>
   </si>
   <si>
     <t xml:space="preserve">110.870445251465</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">113.816047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">111.305046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.504302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.132057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.974967956543</t>
+    <t xml:space="preserve">111.305038452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.50431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.132064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.974975585938</t>
   </si>
   <si>
     <t xml:space="preserve">123.763473510742</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">124.584381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">125.646728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.586227416992</t>
+    <t xml:space="preserve">125.64673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.586212158203</t>
   </si>
   <si>
     <t xml:space="preserve">131.344772338867</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">124.777534484863</t>
   </si>
   <si>
-    <t xml:space="preserve">125.018974304199</t>
+    <t xml:space="preserve">125.018981933594</t>
   </si>
   <si>
     <t xml:space="preserve">128.592330932617</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.76530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.302612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.612503051758</t>
+    <t xml:space="preserve">130.765319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.302597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.612518310547</t>
   </si>
   <si>
     <t xml:space="preserve">128.206024169922</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">124.487808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">127.240249633789</t>
+    <t xml:space="preserve">127.240264892578</t>
   </si>
   <si>
     <t xml:space="preserve">129.316650390625</t>
@@ -4115,61 +4115,61 @@
     <t xml:space="preserve">128.157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">125.26042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.682815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435241699219</t>
+    <t xml:space="preserve">125.260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.509826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.682800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435256958008</t>
   </si>
   <si>
     <t xml:space="preserve">129.84782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">125.067276000977</t>
+    <t xml:space="preserve">125.067268371582</t>
   </si>
   <si>
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.783653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.522033691406</t>
+    <t xml:space="preserve">123.42546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.783645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.522041320801</t>
   </si>
   <si>
     <t xml:space="preserve">123.039154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">122.652854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.62654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.874114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.405296325684</t>
+    <t xml:space="preserve">122.652847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.874122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.405303955078</t>
   </si>
   <si>
     <t xml:space="preserve">122.846000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">122.169960021973</t>
+    <t xml:space="preserve">122.169967651367</t>
   </si>
   <si>
     <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">121.880218505859</t>
+    <t xml:space="preserve">121.880226135254</t>
   </si>
   <si>
     <t xml:space="preserve">122.218254089355</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">122.990859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">121.011039733887</t>
+    <t xml:space="preserve">121.011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">120.479858398438</t>
@@ -4208,10 +4208,10 @@
     <t xml:space="preserve">115.651008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.196243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.775703430176</t>
+    <t xml:space="preserve">117.196235656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.775695800781</t>
   </si>
   <si>
     <t xml:space="preserve">116.906509399414</t>
@@ -4226,10 +4226,7 @@
     <t xml:space="preserve">113.236587524414</t>
   </si>
   <si>
-    <t xml:space="preserve">114.057479858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.319107055664</t>
+    <t xml:space="preserve">112.31909942627</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
@@ -4247,13 +4244,13 @@
     <t xml:space="preserve">110.242698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">107.20051574707</t>
+    <t xml:space="preserve">107.200523376465</t>
   </si>
   <si>
     <t xml:space="preserve">106.186454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">108.64917755127</t>
+    <t xml:space="preserve">108.649169921875</t>
   </si>
   <si>
     <t xml:space="preserve">108.842323303223</t>
@@ -4268,7 +4265,7 @@
     <t xml:space="preserve">105.993301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">104.303199768066</t>
+    <t xml:space="preserve">104.303207397461</t>
   </si>
   <si>
     <t xml:space="preserve">104.013473510742</t>
@@ -4295,13 +4292,13 @@
     <t xml:space="preserve">95.1283874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5568771362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.5770492553711</t>
+    <t xml:space="preserve">98.5568695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6455001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5770416259766</t>
   </si>
   <si>
     <t xml:space="preserve">94.6648178100586</t>
@@ -4310,7 +4307,7 @@
     <t xml:space="preserve">95.070442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7376708984375</t>
+    <t xml:space="preserve">93.737678527832</t>
   </si>
   <si>
     <t xml:space="preserve">93.6797332763672</t>
@@ -4325,7 +4322,7 @@
     <t xml:space="preserve">95.7078475952148</t>
   </si>
   <si>
-    <t xml:space="preserve">93.9887771606445</t>
+    <t xml:space="preserve">93.9887847900391</t>
   </si>
   <si>
     <t xml:space="preserve">93.5252075195312</t>
@@ -4334,13 +4331,13 @@
     <t xml:space="preserve">93.9694595336914</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0467224121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8342666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5340042114258</t>
+    <t xml:space="preserve">94.0467147827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5340118408203</t>
   </si>
   <si>
     <t xml:space="preserve">95.9589538574219</t>
@@ -4349,7 +4346,7 @@
     <t xml:space="preserve">94.1819305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1582107543945</t>
+    <t xml:space="preserve">93.1582183837891</t>
   </si>
   <si>
     <t xml:space="preserve">95.1090698242188</t>
@@ -4358,7 +4355,7 @@
     <t xml:space="preserve">94.3750915527344</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6068725585938</t>
+    <t xml:space="preserve">94.6068649291992</t>
   </si>
   <si>
     <t xml:space="preserve">96.3645706176758</t>
@@ -4373,7 +4370,7 @@
     <t xml:space="preserve">101.164451599121</t>
   </si>
   <si>
-    <t xml:space="preserve">101.985359191895</t>
+    <t xml:space="preserve">101.9853515625</t>
   </si>
   <si>
     <t xml:space="preserve">101.45418548584</t>
@@ -4385,160 +4382,163 @@
     <t xml:space="preserve">98.1222763061523</t>
   </si>
   <si>
+    <t xml:space="preserve">98.894889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.408088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299819946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8642730712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4347229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9159774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.790397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.493293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6969833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9270706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2046356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6384124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4236297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0679550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5365676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4389419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3579559326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6104431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4779968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7946090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7750854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8183517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9982986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9565887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8700561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4404983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0848388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5534362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.741813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3275680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3861465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1280975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7054214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1196670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5729598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0109405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8072662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6901092529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1824569702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1629257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7877349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2716522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6816787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3091278076172</t>
+  </si>
+  <si>
     <t xml:space="preserve">98.8948974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">100.408088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2853851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.8642730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4347229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2436828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9159774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.790397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.493293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6969833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9270706176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2046356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6384048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4236297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0679626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1265411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5365676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4389419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3579483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6104431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4779891967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7946090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7750854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8183517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9982986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9565887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8700561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4405059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.084831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.5534362792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.741813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3275680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3861465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1280975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7054138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1196670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.5729675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0109405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8072662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6901092529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1824569702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1629257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7877349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2716445922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6816787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3091354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6270904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3413162231445</t>
+    <t xml:space="preserve">99.627082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413238525391</t>
   </si>
   <si>
     <t xml:space="preserve">92.9397201538086</t>
@@ -4550,13 +4550,13 @@
     <t xml:space="preserve">91.7682113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5492172241211</t>
+    <t xml:space="preserve">92.5492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">92.6273193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">89.11279296875</t>
+    <t xml:space="preserve">89.1127853393555</t>
   </si>
   <si>
     <t xml:space="preserve">88.1365280151367</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">87.1016998291016</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6679382324219</t>
+    <t xml:space="preserve">87.6679306030273</t>
   </si>
   <si>
     <t xml:space="preserve">87.3164825439453</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">90.9676818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8114700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906387329102</t>
+    <t xml:space="preserve">90.8114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906463623047</t>
   </si>
   <si>
     <t xml:space="preserve">92.8225708007812</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">94.4626846313477</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0721740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444686889648</t>
+    <t xml:space="preserve">94.0721817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444763183594</t>
   </si>
   <si>
     <t xml:space="preserve">91.1238784790039</t>
@@ -4610,13 +4610,13 @@
     <t xml:space="preserve">90.6357498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5032958984375</t>
+    <t xml:space="preserve">89.503288269043</t>
   </si>
   <si>
     <t xml:space="preserve">90.303825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9328536987305</t>
+    <t xml:space="preserve">89.9328460693359</t>
   </si>
   <si>
     <t xml:space="preserve">88.8003921508789</t>
@@ -4628,22 +4628,22 @@
     <t xml:space="preserve">88.1755828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">85.207763671875</t>
+    <t xml:space="preserve">85.2077560424805</t>
   </si>
   <si>
     <t xml:space="preserve">84.4853286743164</t>
   </si>
   <si>
-    <t xml:space="preserve">83.9581451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132904052734</t>
+    <t xml:space="preserve">83.9581527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132827758789</t>
   </si>
   <si>
     <t xml:space="preserve">84.2314987182617</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">84.8563079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3053817749023</t>
+    <t xml:space="preserve">85.3053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">85.6373138427734</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">86.4378433227539</t>
   </si>
   <si>
-    <t xml:space="preserve">83.4700241088867</t>
+    <t xml:space="preserve">83.4700164794922</t>
   </si>
   <si>
     <t xml:space="preserve">81.5175094604492</t>
@@ -4694,16 +4694,16 @@
     <t xml:space="preserve">82.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8146057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531234741211</t>
+    <t xml:space="preserve">80.8145980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531158447266</t>
   </si>
   <si>
     <t xml:space="preserve">80.4436264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">80.131217956543</t>
+    <t xml:space="preserve">80.1312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">82.493766784668</t>
@@ -4724,10 +4724,10 @@
     <t xml:space="preserve">85.5006408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7892990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816390991211</t>
+    <t xml:space="preserve">86.789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816467285156</t>
   </si>
   <si>
     <t xml:space="preserve">83.1185684204102</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">88.8394393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2969512939453</t>
+    <t xml:space="preserve">87.2969436645508</t>
   </si>
   <si>
     <t xml:space="preserve">84.3096008300781</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">86.6916732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4183120727539</t>
+    <t xml:space="preserve">86.4183197021484</t>
   </si>
   <si>
     <t xml:space="preserve">85.98876953125</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">89.6985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8589553833008</t>
+    <t xml:space="preserve">88.8589630126953</t>
   </si>
   <si>
     <t xml:space="preserve">87.6093521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9064483642578</t>
+    <t xml:space="preserve">86.9064407348633</t>
   </si>
   <si>
     <t xml:space="preserve">86.3402252197266</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">90.9481582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9872055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0262603759766</t>
+    <t xml:space="preserve">90.9871978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">87.8436584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6135787963867</t>
+    <t xml:space="preserve">86.6135711669922</t>
   </si>
   <si>
     <t xml:space="preserve">87.2774276733398</t>
@@ -4835,13 +4835,13 @@
     <t xml:space="preserve">88.4294128417969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.7808685302734</t>
+    <t xml:space="preserve">88.7808609008789</t>
   </si>
   <si>
     <t xml:space="preserve">88.2341613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5117263793945</t>
+    <t xml:space="preserve">87.5117340087891</t>
   </si>
   <si>
     <t xml:space="preserve">87.121223449707</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">85.9106674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1296539306641</t>
+    <t xml:space="preserve">85.1296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">84.0167236328125</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">82.6304397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">84.3877105712891</t>
+    <t xml:space="preserve">84.3877029418945</t>
   </si>
   <si>
     <t xml:space="preserve">84.3486557006836</t>
@@ -4877,10 +4877,10 @@
     <t xml:space="preserve">83.8605270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4547119140625</t>
+    <t xml:space="preserve">83.0014114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.454719543457</t>
   </si>
   <si>
     <t xml:space="preserve">82.9428405761719</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">84.9344100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">84.055778503418</t>
+    <t xml:space="preserve">84.0557708740234</t>
   </si>
   <si>
     <t xml:space="preserve">84.8953552246094</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">85.6958923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7001113891602</t>
+    <t xml:space="preserve">84.7001037597656</t>
   </si>
   <si>
     <t xml:space="preserve">84.7196350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2578964233398</t>
+    <t xml:space="preserve">87.2579040527344</t>
   </si>
   <si>
     <t xml:space="preserve">88.1170120239258</t>
@@ -4931,19 +4931,19 @@
     <t xml:space="preserve">92.3149108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2843017578125</t>
+    <t xml:space="preserve">90.284309387207</t>
   </si>
   <si>
     <t xml:space="preserve">91.7096405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8310012817383</t>
+    <t xml:space="preserve">90.8310089111328</t>
   </si>
   <si>
     <t xml:space="preserve">91.4753341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4125518798828</t>
+    <t xml:space="preserve">92.4125442504883</t>
   </si>
   <si>
     <t xml:space="preserve">94.5017395019531</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">91.2605667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4515838623047</t>
+    <t xml:space="preserve">92.4515914916992</t>
   </si>
   <si>
     <t xml:space="preserve">89.6399765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9259719848633</t>
+    <t xml:space="preserve">86.9259796142578</t>
   </si>
   <si>
     <t xml:space="preserve">86.0863952636719</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">84.1338806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9275360107422</t>
+    <t xml:space="preserve">81.9275283813477</t>
   </si>
   <si>
     <t xml:space="preserve">81.3222579956055</t>
@@ -4991,22 +4991,22 @@
     <t xml:space="preserve">83.7238464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6721420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615936279297</t>
+    <t xml:space="preserve">86.6721496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615859985352</t>
   </si>
   <si>
     <t xml:space="preserve">85.2858581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4098815917969</t>
+    <t xml:space="preserve">88.4098892211914</t>
   </si>
   <si>
     <t xml:space="preserve">87.4531555175781</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">92.6858978271484</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5840530395508</t>
+    <t xml:space="preserve">93.5840454101562</t>
   </si>
   <si>
     <t xml:space="preserve">93.7402496337891</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">91.4362869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6468505859375</t>
+    <t xml:space="preserve">92.646842956543</t>
   </si>
   <si>
     <t xml:space="preserve">93.9550247192383</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">90.7724304199219</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6510543823242</t>
+    <t xml:space="preserve">91.6510620117188</t>
   </si>
   <si>
     <t xml:space="preserve">91.1043548583984</t>
@@ -5474,9 +5474,6 @@
     <t xml:space="preserve">95.2035980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">99.627082824707</t>
-  </si>
-  <si>
     <t xml:space="preserve">97.6128234863281</t>
   </si>
   <si>
@@ -5976,6 +5973,9 @@
   </si>
   <si>
     <t xml:space="preserve">60.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4199981689453</t>
   </si>
 </sst>
 </file>
@@ -53470,7 +53470,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G1814" t="s">
-        <v>1404</v>
+        <v>1248</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -53548,7 +53548,7 @@
         <v>116.300003051758</v>
       </c>
       <c r="G1817" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -53574,7 +53574,7 @@
         <v>116.550003051758</v>
       </c>
       <c r="G1818" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -53652,7 +53652,7 @@
         <v>116.050003051758</v>
       </c>
       <c r="G1821" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -53678,7 +53678,7 @@
         <v>113.300003051758</v>
       </c>
       <c r="G1822" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -53704,7 +53704,7 @@
         <v>115</v>
       </c>
       <c r="G1823" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -53730,7 +53730,7 @@
         <v>114.150001525879</v>
       </c>
       <c r="G1824" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -53756,7 +53756,7 @@
         <v>111</v>
       </c>
       <c r="G1825" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -53782,7 +53782,7 @@
         <v>109.949996948242</v>
       </c>
       <c r="G1826" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -53808,7 +53808,7 @@
         <v>112.5</v>
       </c>
       <c r="G1827" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -53834,7 +53834,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1828" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -53860,7 +53860,7 @@
         <v>111.949996948242</v>
       </c>
       <c r="G1829" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -53912,7 +53912,7 @@
         <v>111.550003051758</v>
       </c>
       <c r="G1831" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -53938,7 +53938,7 @@
         <v>109.75</v>
       </c>
       <c r="G1832" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -53964,7 +53964,7 @@
         <v>108</v>
       </c>
       <c r="G1833" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -53990,7 +53990,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G1834" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -54016,7 +54016,7 @@
         <v>105.550003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -54042,7 +54042,7 @@
         <v>107.349998474121</v>
       </c>
       <c r="G1836" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -54068,7 +54068,7 @@
         <v>105.699996948242</v>
       </c>
       <c r="G1837" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -54094,7 +54094,7 @@
         <v>101.199996948242</v>
       </c>
       <c r="G1838" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -54120,7 +54120,7 @@
         <v>102.449996948242</v>
       </c>
       <c r="G1839" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -54146,7 +54146,7 @@
         <v>101.050003051758</v>
       </c>
       <c r="G1840" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -54172,7 +54172,7 @@
         <v>98.5</v>
       </c>
       <c r="G1841" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -54198,7 +54198,7 @@
         <v>102.050003051758</v>
       </c>
       <c r="G1842" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -54224,7 +54224,7 @@
         <v>98</v>
       </c>
       <c r="G1843" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -54250,7 +54250,7 @@
         <v>100</v>
       </c>
       <c r="G1844" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -54276,7 +54276,7 @@
         <v>98.0199966430664</v>
       </c>
       <c r="G1845" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -54302,7 +54302,7 @@
         <v>98.4400024414062</v>
       </c>
       <c r="G1846" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -54328,7 +54328,7 @@
         <v>97.0599975585938</v>
       </c>
       <c r="G1847" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -54354,7 +54354,7 @@
         <v>97</v>
       </c>
       <c r="G1848" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -54380,7 +54380,7 @@
         <v>97.0599975585938</v>
       </c>
       <c r="G1849" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -54406,7 +54406,7 @@
         <v>98</v>
       </c>
       <c r="G1850" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -54432,7 +54432,7 @@
         <v>97.0599975585938</v>
       </c>
       <c r="G1851" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -54458,7 +54458,7 @@
         <v>99.620002746582</v>
       </c>
       <c r="G1852" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -54484,7 +54484,7 @@
         <v>99.1800003051758</v>
       </c>
       <c r="G1853" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -54510,7 +54510,7 @@
         <v>99.0999984741211</v>
       </c>
       <c r="G1854" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -54536,7 +54536,7 @@
         <v>97.3199996948242</v>
       </c>
       <c r="G1855" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -54562,7 +54562,7 @@
         <v>96.8399963378906</v>
       </c>
       <c r="G1856" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -54588,7 +54588,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G1857" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -54614,7 +54614,7 @@
         <v>97.379997253418</v>
       </c>
       <c r="G1858" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -54640,7 +54640,7 @@
         <v>97.1600036621094</v>
       </c>
       <c r="G1859" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -54666,7 +54666,7 @@
         <v>98.9199981689453</v>
       </c>
       <c r="G1860" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54692,7 +54692,7 @@
         <v>99.3600006103516</v>
       </c>
       <c r="G1861" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -54718,7 +54718,7 @@
         <v>97.5199966430664</v>
       </c>
       <c r="G1862" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -54744,7 +54744,7 @@
         <v>96.4599990844727</v>
       </c>
       <c r="G1863" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -54770,7 +54770,7 @@
         <v>97.3199996948242</v>
       </c>
       <c r="G1864" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -54796,7 +54796,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G1865" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -54822,7 +54822,7 @@
         <v>97.7200012207031</v>
       </c>
       <c r="G1866" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54848,7 +54848,7 @@
         <v>97.9599990844727</v>
       </c>
       <c r="G1867" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -54874,7 +54874,7 @@
         <v>99.7799987792969</v>
       </c>
       <c r="G1868" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -54900,7 +54900,7 @@
         <v>104.449996948242</v>
       </c>
       <c r="G1869" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -54926,7 +54926,7 @@
         <v>102.050003051758</v>
       </c>
       <c r="G1870" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -54952,7 +54952,7 @@
         <v>102.199996948242</v>
       </c>
       <c r="G1871" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -54978,7 +54978,7 @@
         <v>105.550003051758</v>
       </c>
       <c r="G1872" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -55004,7 +55004,7 @@
         <v>104.75</v>
       </c>
       <c r="G1873" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -55030,7 +55030,7 @@
         <v>105.599998474121</v>
       </c>
       <c r="G1874" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -55056,7 +55056,7 @@
         <v>105.050003051758</v>
       </c>
       <c r="G1875" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -55082,7 +55082,7 @@
         <v>105.550003051758</v>
       </c>
       <c r="G1876" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -55108,7 +55108,7 @@
         <v>101.550003051758</v>
       </c>
       <c r="G1877" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -55134,7 +55134,7 @@
         <v>101.599998474121</v>
       </c>
       <c r="G1878" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -55160,7 +55160,7 @@
         <v>102.400001525879</v>
       </c>
       <c r="G1879" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -55186,7 +55186,7 @@
         <v>102.849998474121</v>
       </c>
       <c r="G1880" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -55212,7 +55212,7 @@
         <v>101.699996948242</v>
       </c>
       <c r="G1881" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -55238,7 +55238,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G1882" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -55264,7 +55264,7 @@
         <v>98.9800033569336</v>
       </c>
       <c r="G1883" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -55290,7 +55290,7 @@
         <v>99.2200012207031</v>
       </c>
       <c r="G1884" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -55316,7 +55316,7 @@
         <v>98.7799987792969</v>
       </c>
       <c r="G1885" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -55342,7 +55342,7 @@
         <v>97.5599975585938</v>
       </c>
       <c r="G1886" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -55368,7 +55368,7 @@
         <v>96.1999969482422</v>
       </c>
       <c r="G1887" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -55394,7 +55394,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G1888" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -55420,7 +55420,7 @@
         <v>98.8399963378906</v>
       </c>
       <c r="G1889" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -55446,7 +55446,7 @@
         <v>97</v>
       </c>
       <c r="G1890" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -55472,7 +55472,7 @@
         <v>98.2600021362305</v>
       </c>
       <c r="G1891" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -55498,7 +55498,7 @@
         <v>97.5199966430664</v>
       </c>
       <c r="G1892" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -55524,7 +55524,7 @@
         <v>96.9400024414062</v>
       </c>
       <c r="G1893" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -55550,7 +55550,7 @@
         <v>96.7200012207031</v>
       </c>
       <c r="G1894" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -55576,7 +55576,7 @@
         <v>97.379997253418</v>
       </c>
       <c r="G1895" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -55602,7 +55602,7 @@
         <v>97.4400024414062</v>
       </c>
       <c r="G1896" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -55628,7 +55628,7 @@
         <v>97.8600006103516</v>
       </c>
       <c r="G1897" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -55654,7 +55654,7 @@
         <v>97.7600021362305</v>
       </c>
       <c r="G1898" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -55680,7 +55680,7 @@
         <v>100.75</v>
       </c>
       <c r="G1899" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -55706,7 +55706,7 @@
         <v>98.9599990844727</v>
       </c>
       <c r="G1900" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -55732,7 +55732,7 @@
         <v>97.8000030517578</v>
       </c>
       <c r="G1901" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -55758,7 +55758,7 @@
         <v>97.0999984741211</v>
       </c>
       <c r="G1902" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -55784,7 +55784,7 @@
         <v>97.0800018310547</v>
       </c>
       <c r="G1903" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -55810,7 +55810,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G1904" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -55836,7 +55836,7 @@
         <v>95.2600021362305</v>
       </c>
       <c r="G1905" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -55862,7 +55862,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G1906" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -55888,7 +55888,7 @@
         <v>93.0800018310547</v>
       </c>
       <c r="G1907" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -55914,7 +55914,7 @@
         <v>92.6399993896484</v>
       </c>
       <c r="G1908" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -55940,7 +55940,7 @@
         <v>95.4000015258789</v>
       </c>
       <c r="G1909" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -55966,7 +55966,7 @@
         <v>93.5999984741211</v>
       </c>
       <c r="G1910" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -55992,7 +55992,7 @@
         <v>93.3000030517578</v>
       </c>
       <c r="G1911" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -56018,7 +56018,7 @@
         <v>93.7799987792969</v>
       </c>
       <c r="G1912" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -56044,7 +56044,7 @@
         <v>90.9000015258789</v>
       </c>
       <c r="G1913" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -56070,7 +56070,7 @@
         <v>91.5</v>
       </c>
       <c r="G1914" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -56096,7 +56096,7 @@
         <v>91.5599975585938</v>
       </c>
       <c r="G1915" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -56122,7 +56122,7 @@
         <v>92.3199996948242</v>
       </c>
       <c r="G1916" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -56148,7 +56148,7 @@
         <v>94.9599990844727</v>
       </c>
       <c r="G1917" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -56174,7 +56174,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G1918" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -56200,7 +56200,7 @@
         <v>93.8000030517578</v>
       </c>
       <c r="G1919" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -56226,7 +56226,7 @@
         <v>92.1999969482422</v>
       </c>
       <c r="G1920" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -56252,7 +56252,7 @@
         <v>94.0400009155273</v>
       </c>
       <c r="G1921" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -56278,7 +56278,7 @@
         <v>93.9199981689453</v>
       </c>
       <c r="G1922" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -56304,7 +56304,7 @@
         <v>93.4000015258789</v>
       </c>
       <c r="G1923" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -56330,7 +56330,7 @@
         <v>93.379997253418</v>
       </c>
       <c r="G1924" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -56356,7 +56356,7 @@
         <v>94.0199966430664</v>
       </c>
       <c r="G1925" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -56382,7 +56382,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G1926" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -56408,7 +56408,7 @@
         <v>95.9599990844727</v>
       </c>
       <c r="G1927" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -56434,7 +56434,7 @@
         <v>100.699996948242</v>
       </c>
       <c r="G1928" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -56460,7 +56460,7 @@
         <v>101.300003051758</v>
       </c>
       <c r="G1929" t="s">
-        <v>1457</v>
+        <v>1506</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -56512,7 +56512,7 @@
         <v>98.7799987792969</v>
       </c>
       <c r="G1931" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -56564,7 +56564,7 @@
         <v>97.8000030517578</v>
       </c>
       <c r="G1933" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -56720,7 +56720,7 @@
         <v>91.5</v>
       </c>
       <c r="G1939" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -57032,7 +57032,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G1951" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -57058,7 +57058,7 @@
         <v>97.5599975585938</v>
       </c>
       <c r="G1952" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -57266,7 +57266,7 @@
         <v>91.5599975585938</v>
       </c>
       <c r="G1960" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -59112,7 +59112,7 @@
         <v>91.5</v>
       </c>
       <c r="G2031" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -60256,7 +60256,7 @@
         <v>92.6399993896484</v>
       </c>
       <c r="G2075" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -60360,7 +60360,7 @@
         <v>93.379997253418</v>
       </c>
       <c r="G2079" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -60490,7 +60490,7 @@
         <v>95.2600021362305</v>
       </c>
       <c r="G2084" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60516,7 +60516,7 @@
         <v>97</v>
       </c>
       <c r="G2085" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -61556,7 +61556,7 @@
         <v>92.1999969482422</v>
       </c>
       <c r="G2125" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -67068,7 +67068,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1820</v>
+        <v>1507</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67120,7 +67120,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67146,7 +67146,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67172,7 +67172,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67198,7 +67198,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67224,7 +67224,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67250,7 +67250,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67276,7 +67276,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67302,7 +67302,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67328,7 +67328,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67354,7 +67354,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67380,7 +67380,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67406,7 +67406,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67432,7 +67432,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67458,7 +67458,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67484,7 +67484,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67510,7 +67510,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67536,7 +67536,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67588,7 +67588,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67614,7 +67614,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67640,7 +67640,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67666,7 +67666,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67692,7 +67692,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67718,7 +67718,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67770,7 +67770,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67796,7 +67796,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67822,7 +67822,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67848,7 +67848,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67900,7 +67900,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67952,7 +67952,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -68004,7 +68004,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68056,7 +68056,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68082,7 +68082,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68134,7 +68134,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68160,7 +68160,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68186,7 +68186,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68212,7 +68212,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68238,7 +68238,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68264,7 +68264,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68290,7 +68290,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68316,7 +68316,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68342,7 +68342,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68368,7 +68368,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68394,7 +68394,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68420,7 +68420,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68446,7 +68446,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68472,7 +68472,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68498,7 +68498,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68524,7 +68524,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68550,7 +68550,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68576,7 +68576,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68602,7 +68602,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68628,7 +68628,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68654,7 +68654,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68680,7 +68680,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68706,7 +68706,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68732,7 +68732,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68758,7 +68758,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68784,7 +68784,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68810,7 +68810,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68836,7 +68836,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68862,7 +68862,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68888,7 +68888,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68914,7 +68914,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68940,7 +68940,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68966,7 +68966,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68992,7 +68992,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -69018,7 +69018,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -69044,7 +69044,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69070,7 +69070,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69096,7 +69096,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69122,7 +69122,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69148,7 +69148,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69174,7 +69174,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69200,7 +69200,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69226,7 +69226,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69252,7 +69252,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69278,7 +69278,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69304,7 +69304,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69330,7 +69330,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69356,7 +69356,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69382,7 +69382,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69408,7 +69408,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69434,7 +69434,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69460,7 +69460,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69486,7 +69486,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69512,7 +69512,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69538,7 +69538,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69564,7 +69564,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69590,7 +69590,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69616,7 +69616,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69642,7 +69642,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69668,7 +69668,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69694,7 +69694,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69720,7 +69720,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69746,7 +69746,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69772,7 +69772,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69798,7 +69798,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69824,7 +69824,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69850,7 +69850,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69876,7 +69876,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69902,7 +69902,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69928,7 +69928,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69954,7 +69954,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69980,7 +69980,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -70006,7 +70006,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -70032,7 +70032,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70058,7 +70058,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70084,7 +70084,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70110,7 +70110,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70136,7 +70136,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70162,7 +70162,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70188,7 +70188,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70214,7 +70214,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70240,7 +70240,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70266,7 +70266,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70292,7 +70292,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70318,7 +70318,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70344,7 +70344,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70370,7 +70370,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70396,7 +70396,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70422,7 +70422,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70448,7 +70448,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70474,7 +70474,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70500,7 +70500,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70526,7 +70526,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70552,7 +70552,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70578,7 +70578,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70604,7 +70604,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70630,7 +70630,7 @@
         <v>77.8600006103516</v>
       </c>
       <c r="G2474" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70656,7 +70656,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2475" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70682,7 +70682,7 @@
         <v>74.1800003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70708,7 +70708,7 @@
         <v>74.1399993896484</v>
       </c>
       <c r="G2477" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70734,7 +70734,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2478" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70760,7 +70760,7 @@
         <v>75.5199966430664</v>
       </c>
       <c r="G2479" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70786,7 +70786,7 @@
         <v>77.6600036621094</v>
       </c>
       <c r="G2480" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70812,7 +70812,7 @@
         <v>77.8399963378906</v>
       </c>
       <c r="G2481" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70838,7 +70838,7 @@
         <v>78.879997253418</v>
       </c>
       <c r="G2482" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70864,7 +70864,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2483" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70890,7 +70890,7 @@
         <v>79.0400009155273</v>
       </c>
       <c r="G2484" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70916,7 +70916,7 @@
         <v>79.0999984741211</v>
       </c>
       <c r="G2485" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70942,7 +70942,7 @@
         <v>77.9000015258789</v>
       </c>
       <c r="G2486" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70968,7 +70968,7 @@
         <v>75.6399993896484</v>
       </c>
       <c r="G2487" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70994,7 +70994,7 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2488" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -71020,7 +71020,7 @@
         <v>74.1999969482422</v>
       </c>
       <c r="G2489" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -71046,7 +71046,7 @@
         <v>74.2399978637695</v>
       </c>
       <c r="G2490" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -71072,7 +71072,7 @@
         <v>74.9400024414062</v>
       </c>
       <c r="G2491" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -71098,7 +71098,7 @@
         <v>75.2600021362305</v>
       </c>
       <c r="G2492" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71124,7 +71124,7 @@
         <v>75.9400024414062</v>
       </c>
       <c r="G2493" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71150,7 +71150,7 @@
         <v>75.9599990844727</v>
       </c>
       <c r="G2494" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71176,7 +71176,7 @@
         <v>77.9400024414062</v>
       </c>
       <c r="G2495" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71202,7 +71202,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2496" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71228,7 +71228,7 @@
         <v>78.5999984741211</v>
       </c>
       <c r="G2497" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71254,7 +71254,7 @@
         <v>77.6999969482422</v>
       </c>
       <c r="G2498" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71280,7 +71280,7 @@
         <v>77.2399978637695</v>
       </c>
       <c r="G2499" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71306,7 +71306,7 @@
         <v>76.4400024414062</v>
       </c>
       <c r="G2500" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -71332,7 +71332,7 @@
         <v>76.3199996948242</v>
       </c>
       <c r="G2501" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -71358,7 +71358,7 @@
         <v>76.6999969482422</v>
       </c>
       <c r="G2502" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -71384,7 +71384,7 @@
         <v>76.2799987792969</v>
       </c>
       <c r="G2503" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -71410,7 +71410,7 @@
         <v>76.3600006103516</v>
       </c>
       <c r="G2504" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -71436,7 +71436,7 @@
         <v>74.2600021362305</v>
       </c>
       <c r="G2505" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -71462,7 +71462,7 @@
         <v>60.3199996948242</v>
       </c>
       <c r="G2506" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -71488,7 +71488,7 @@
         <v>59.2200012207031</v>
       </c>
       <c r="G2507" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71514,7 +71514,7 @@
         <v>59</v>
       </c>
       <c r="G2508" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -71540,7 +71540,7 @@
         <v>60.1599998474121</v>
       </c>
       <c r="G2509" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71566,7 +71566,7 @@
         <v>60.5</v>
       </c>
       <c r="G2510" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71592,7 +71592,7 @@
         <v>60.1800003051758</v>
       </c>
       <c r="G2511" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71618,7 +71618,7 @@
         <v>58.9199981689453</v>
       </c>
       <c r="G2512" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71644,7 +71644,7 @@
         <v>58.8600006103516</v>
       </c>
       <c r="G2513" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71670,7 +71670,7 @@
         <v>58.3600006103516</v>
       </c>
       <c r="G2514" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71696,7 +71696,7 @@
         <v>59</v>
       </c>
       <c r="G2515" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71722,7 +71722,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G2516" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71748,7 +71748,7 @@
         <v>59.5400009155273</v>
       </c>
       <c r="G2517" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71774,7 +71774,7 @@
         <v>60.6599998474121</v>
       </c>
       <c r="G2518" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71800,7 +71800,7 @@
         <v>60.4799995422363</v>
       </c>
       <c r="G2519" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71808,7 +71808,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.69125</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>243587</v>
@@ -71826,9 +71826,35 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G2520" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6923726852</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>248413</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>61.8199996948242</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>60.7999992370605</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>61.3600006103516</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>61.4199981689453</v>
+      </c>
+      <c r="G2521" t="s">
         <v>1987</v>
       </c>
-      <c r="H2520" t="s">
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="1998">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980880737305</t>
+    <t xml:space="preserve">43.2980918884277</t>
   </si>
   <si>
     <t xml:space="preserve">43.0423049926758</t>
@@ -56,40 +56,40 @@
     <t xml:space="preserve">42.8218040466309</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1514701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4690017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7281074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2870941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9993553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2761039733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0765571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9585800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2551460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606353759766</t>
+    <t xml:space="preserve">42.1514739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4689979553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7281112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2871017456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9993515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2761077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0765686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443786621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2551422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2606315612793</t>
   </si>
   <si>
     <t xml:space="preserve">42.0544509887695</t>
@@ -101,19 +101,19 @@
     <t xml:space="preserve">42.7776985168457</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0687637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9981994628906</t>
+    <t xml:space="preserve">43.0687713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9982070922852</t>
   </si>
   <si>
     <t xml:space="preserve">41.8780517578125</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2341728210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4172210693359</t>
+    <t xml:space="preserve">41.2341766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4172248840332</t>
   </si>
   <si>
     <t xml:space="preserve">37.7590408325195</t>
@@ -122,25 +122,25 @@
     <t xml:space="preserve">38.0148239135742</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5881309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.605785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4029121398926</t>
+    <t xml:space="preserve">38.588134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6057777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4029159545898</t>
   </si>
   <si>
     <t xml:space="preserve">40.1228408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3962631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4932823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4017562866211</t>
+    <t xml:space="preserve">40.3962554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.493278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4017601013184</t>
   </si>
   <si>
     <t xml:space="preserve">42.5483818054199</t>
@@ -152,43 +152,43 @@
     <t xml:space="preserve">42.5924835205078</t>
   </si>
   <si>
-    <t xml:space="preserve">43.209888458252</t>
+    <t xml:space="preserve">43.2098846435547</t>
   </si>
   <si>
     <t xml:space="preserve">42.9011878967285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2275352478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5571937561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8074836730957</t>
+    <t xml:space="preserve">43.2275276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5571975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.807487487793</t>
   </si>
   <si>
     <t xml:space="preserve">42.6453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7071380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7600593566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7578887939453</t>
+    <t xml:space="preserve">42.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7600555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7578926086426</t>
   </si>
   <si>
     <t xml:space="preserve">40.3521614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0081825256348</t>
+    <t xml:space="preserve">40.0081787109375</t>
   </si>
   <si>
     <t xml:space="preserve">41.1636123657227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5726661682129</t>
+    <t xml:space="preserve">40.5726623535156</t>
   </si>
   <si>
     <t xml:space="preserve">40.1581192016602</t>
@@ -197,61 +197,61 @@
     <t xml:space="preserve">39.6200904846191</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1140174865723</t>
+    <t xml:space="preserve">40.114013671875</t>
   </si>
   <si>
     <t xml:space="preserve">40.2904205322266</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8405990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1316566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4668235778809</t>
+    <t xml:space="preserve">39.8405914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1316528320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4668273925781</t>
   </si>
   <si>
     <t xml:space="preserve">44.1007194519043</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7622299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.291446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8647575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3796463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6883506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9088478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4237442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2032432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8945350646973</t>
+    <t xml:space="preserve">44.7622337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2914428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8647537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6883430480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9088516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4237480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2032470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8945388793945</t>
   </si>
   <si>
     <t xml:space="preserve">44.9386367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3355369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8063316345215</t>
+    <t xml:space="preserve">45.3355407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">44.7181358337402</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">45.2473373413086</t>
   </si>
   <si>
-    <t xml:space="preserve">44.982738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8504295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7765502929688</t>
+    <t xml:space="preserve">44.9827423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8504371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7765464782715</t>
   </si>
   <si>
     <t xml:space="preserve">45.6442527770996</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8206481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3057556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1734657287598</t>
+    <t xml:space="preserve">45.8206520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3057594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1734580993652</t>
   </si>
   <si>
     <t xml:space="preserve">46.261661529541</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">46.6144714355469</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0852584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970512390137</t>
+    <t xml:space="preserve">46.0852546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970550537109</t>
   </si>
   <si>
     <t xml:space="preserve">47.4226684570312</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">47.5119705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1100883483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817855834961</t>
+    <t xml:space="preserve">47.1100921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817893981934</t>
   </si>
   <si>
     <t xml:space="preserve">49.1195182800293</t>
@@ -314,49 +314,49 @@
     <t xml:space="preserve">48.5836791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5660591125488</t>
+    <t xml:space="preserve">49.5660629272461</t>
   </si>
   <si>
     <t xml:space="preserve">49.6553688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2358741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0748672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9679527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1641731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7000350952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9855613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5566291809082</t>
+    <t xml:space="preserve">50.2358779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0748710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1641807556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000312805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9855575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">47.7352447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6188926696777</t>
+    <t xml:space="preserve">46.6188888549805</t>
   </si>
   <si>
     <t xml:space="preserve">46.9314727783203</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0924835205078</t>
+    <t xml:space="preserve">48.0924797058105</t>
   </si>
   <si>
     <t xml:space="preserve">49.3427925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1723480224609</t>
+    <t xml:space="preserve">46.1723518371582</t>
   </si>
   <si>
     <t xml:space="preserve">45.0113487243652</t>
@@ -365,40 +365,40 @@
     <t xml:space="preserve">46.038387298584</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8962516784668</t>
+    <t xml:space="preserve">48.8962440490723</t>
   </si>
   <si>
     <t xml:space="preserve">49.744686126709</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4144973754883</t>
+    <t xml:space="preserve">50.4144897460938</t>
   </si>
   <si>
     <t xml:space="preserve">48.137134552002</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9409065246582</t>
+    <t xml:space="preserve">48.9409027099609</t>
   </si>
   <si>
     <t xml:space="preserve">49.833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0302124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2182655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2629280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9503364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8610343933105</t>
+    <t xml:space="preserve">49.030216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.21826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2629203796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9503402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.861026763916</t>
   </si>
   <si>
     <t xml:space="preserve">51.5754928588867</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">50.9949951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7717208862305</t>
+    <t xml:space="preserve">50.771728515625</t>
   </si>
   <si>
     <t xml:space="preserve">50.2805328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0572547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8786430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1912231445312</t>
+    <t xml:space="preserve">50.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8786392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1912269592285</t>
   </si>
   <si>
     <t xml:space="preserve">51.6201515197754</t>
@@ -440,22 +440,22 @@
     <t xml:space="preserve">54.3440551757812</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3710975646973</t>
+    <t xml:space="preserve">55.3711013793945</t>
   </si>
   <si>
     <t xml:space="preserve">54.1207847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0666961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6648025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6824150085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968811035156</t>
+    <t xml:space="preserve">52.0666885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6648063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6824111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968849182129</t>
   </si>
   <si>
     <t xml:space="preserve">50.6377639770508</t>
@@ -470,91 +470,91 @@
     <t xml:space="preserve">51.4415397644043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3522262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.888069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0843048095703</t>
+    <t xml:space="preserve">51.3522300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8880729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0843086242676</t>
   </si>
   <si>
     <t xml:space="preserve">50.4591445922852</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4767608642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2981414794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9773864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5132293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6918525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346138000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.289966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.183048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7094688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1736106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1465644836426</t>
+    <t xml:space="preserve">49.4767570495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2981376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9773902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5132331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6918487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346176147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2899703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1830406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7094612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1736068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270698547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1465682983398</t>
   </si>
   <si>
     <t xml:space="preserve">50.9056816101074</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0126075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.645938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8245468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3239288330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7258110046387</t>
+    <t xml:space="preserve">50.0126113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6459350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8245506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3239250183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7258186340332</t>
   </si>
   <si>
     <t xml:space="preserve">45.5471954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3956260681152</t>
+    <t xml:space="preserve">46.395622253418</t>
   </si>
   <si>
     <t xml:space="preserve">46.6635475158691</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2616577148438</t>
+    <t xml:space="preserve">46.2616539001465</t>
   </si>
   <si>
     <t xml:space="preserve">45.7704620361328</t>
@@ -566,37 +566,37 @@
     <t xml:space="preserve">46.5742416381836</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4402732849121</t>
+    <t xml:space="preserve">46.4402694702148</t>
   </si>
   <si>
     <t xml:space="preserve">45.9937362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4578857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6811561584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5295829772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3063087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2440528869629</t>
+    <t xml:space="preserve">45.4578819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5295791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3063125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2440490722656</t>
   </si>
   <si>
     <t xml:space="preserve">47.4673156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2088241577148</t>
+    <t xml:space="preserve">49.2088279724121</t>
   </si>
   <si>
     <t xml:space="preserve">50.3698387145996</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1560020446777</t>
+    <t xml:space="preserve">52.1559982299805</t>
   </si>
   <si>
     <t xml:space="preserve">50.5037994384766</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">48.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6107139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8163795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1289520263672</t>
+    <t xml:space="preserve">49.6107215881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8163757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1289558410645</t>
   </si>
   <si>
     <t xml:space="preserve">52.2006568908691</t>
@@ -623,16 +623,16 @@
     <t xml:space="preserve">53.3616638183594</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4063148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4509696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6742401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9151191711426</t>
+    <t xml:space="preserve">53.4063186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4509773254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6742362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9151153564453</t>
   </si>
   <si>
     <t xml:space="preserve">53.2723541259766</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">53.8528594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7905960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5943717956543</t>
+    <t xml:space="preserve">54.790599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.594367980957</t>
   </si>
   <si>
     <t xml:space="preserve">55.3264465332031</t>
@@ -653,118 +653,118 @@
     <t xml:space="preserve">55.5050582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2641792297363</t>
+    <t xml:space="preserve">56.2641830444336</t>
   </si>
   <si>
     <t xml:space="preserve">56.1302223205566</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6390190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8000259399414</t>
+    <t xml:space="preserve">55.6390228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8000335693359</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">56.978645324707</t>
+    <t xml:space="preserve">56.9786415100098</t>
   </si>
   <si>
     <t xml:space="preserve">57.0679550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4251976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.335880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0503425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8987731933594</t>
+    <t xml:space="preserve">57.4251937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3358688354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0503463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8987693786621</t>
   </si>
   <si>
     <t xml:space="preserve">59.0327339172363</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7648086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0950050354004</t>
+    <t xml:space="preserve">58.764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0949974060059</t>
   </si>
   <si>
     <t xml:space="preserve">57.1572647094727</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3805313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5861968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0151290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9434204101562</t>
+    <t xml:space="preserve">57.3805351257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5861892700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0151252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9434280395508</t>
   </si>
   <si>
     <t xml:space="preserve">59.3006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2830581665039</t>
+    <t xml:space="preserve">60.2830505371094</t>
   </si>
   <si>
     <t xml:space="preserve">61.4440650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4088325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1585273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6226654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8906021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817901611328</t>
+    <t xml:space="preserve">63.408821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6226806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8905944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817977905273</t>
   </si>
   <si>
     <t xml:space="preserve">62.7390289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">62.5157585144043</t>
+    <t xml:space="preserve">62.5157508850098</t>
   </si>
   <si>
     <t xml:space="preserve">60.8635482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1937484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6758079528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9469108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083686828613</t>
+    <t xml:space="preserve">60.1937522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6757965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.946907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.0824546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083610534668</t>
   </si>
   <si>
     <t xml:space="preserve">62.534294128418</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">61.4950675964355</t>
   </si>
   <si>
-    <t xml:space="preserve">63.4379653930664</t>
+    <t xml:space="preserve">63.4379577636719</t>
   </si>
   <si>
     <t xml:space="preserve">63.7542610168457</t>
@@ -782,88 +782,88 @@
     <t xml:space="preserve">63.483154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5675582885742</t>
+    <t xml:space="preserve">64.5675659179688</t>
   </si>
   <si>
     <t xml:space="preserve">64.0705413818359</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8386611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5164184570312</t>
+    <t xml:space="preserve">64.8386688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5164260864258</t>
   </si>
   <si>
     <t xml:space="preserve">63.1668586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">63.031307220459</t>
+    <t xml:space="preserve">63.0313148498535</t>
   </si>
   <si>
     <t xml:space="preserve">64.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8898010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4320220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.2964553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1609039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.697151184082</t>
+    <t xml:space="preserve">63.8898086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4320068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.2964630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.160888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6971588134766</t>
   </si>
   <si>
     <t xml:space="preserve">61.0884094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6425285339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.7721328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8173179626465</t>
+    <t xml:space="preserve">59.6425361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.7721214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.184741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8173065185547</t>
   </si>
   <si>
     <t xml:space="preserve">60.5462074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6877174377441</t>
+    <t xml:space="preserve">59.6877250671387</t>
   </si>
   <si>
     <t xml:space="preserve">60.6365737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">61.449878692627</t>
+    <t xml:space="preserve">61.449893951416</t>
   </si>
   <si>
     <t xml:space="preserve">62.3987464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2120399475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2393646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7815628051758</t>
+    <t xml:space="preserve">63.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.239372253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7815704345703</t>
   </si>
   <si>
     <t xml:space="preserve">66.0134429931641</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">65.96826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8778839111328</t>
+    <t xml:space="preserve">65.8778762817383</t>
   </si>
   <si>
     <t xml:space="preserve">65.6067810058594</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">65.0193939208984</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2001266479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7482986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7934722900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6579360961914</t>
+    <t xml:space="preserve">65.2001419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.748291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7934799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6579437255859</t>
   </si>
   <si>
     <t xml:space="preserve">64.4771957397461</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">63.9801826477051</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3024253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4260559082031</t>
+    <t xml:space="preserve">63.3024215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.4260482788086</t>
   </si>
   <si>
     <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">66.284538269043</t>
+    <t xml:space="preserve">66.2845458984375</t>
   </si>
   <si>
     <t xml:space="preserve">66.600830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4652786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8719329833984</t>
+    <t xml:space="preserve">66.4652633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.871940612793</t>
   </si>
   <si>
     <t xml:space="preserve">66.0586242675781</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">66.3749084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">67.0978622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6911849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4141387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5437316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1370697021484</t>
+    <t xml:space="preserve">67.0978393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6912002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4141311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5437469482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.137077331543</t>
   </si>
   <si>
     <t xml:space="preserve">67.865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">67.9563446044922</t>
+    <t xml:space="preserve">67.9563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">68.1822662353516</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">69.1311187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">70.305908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962707519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3903045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5258407592773</t>
+    <t xml:space="preserve">70.3059005737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3903121948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5258636474609</t>
   </si>
   <si>
     <t xml:space="preserve">70.8481063842773</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1643905639648</t>
+    <t xml:space="preserve">71.1643829345703</t>
   </si>
   <si>
     <t xml:space="preserve">72.791015625</t>
@@ -986,43 +986,43 @@
     <t xml:space="preserve">70.8932800292969</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2607116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3510818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5318145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4866256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5769882202148</t>
+    <t xml:space="preserve">70.2607040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3510665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5318069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4866409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5769958496094</t>
   </si>
   <si>
     <t xml:space="preserve">71.3451232910156</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4414367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5710296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.9836578369141</t>
+    <t xml:space="preserve">70.4414443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.983642578125</t>
   </si>
   <si>
     <t xml:space="preserve">70.7125396728516</t>
   </si>
   <si>
-    <t xml:space="preserve">65.1097640991211</t>
+    <t xml:space="preserve">65.1097717285156</t>
   </si>
   <si>
     <t xml:space="preserve">65.5615997314453</t>
@@ -1031,34 +1031,34 @@
     <t xml:space="preserve">67.4593200683594</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8207855224609</t>
+    <t xml:space="preserve">67.82080078125</t>
   </si>
   <si>
     <t xml:space="preserve">69.2666778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">70.034797668457</t>
+    <t xml:space="preserve">70.0347900390625</t>
   </si>
   <si>
     <t xml:space="preserve">69.7636795043945</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9955673217773</t>
+    <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
     <t xml:space="preserve">67.3237686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3629913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0407562255859</t>
+    <t xml:space="preserve">68.3630065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0407485961914</t>
   </si>
   <si>
     <t xml:space="preserve">69.1763000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9444274902344</t>
+    <t xml:space="preserve">69.9444198608398</t>
   </si>
   <si>
     <t xml:space="preserve">70.1703491210938</t>
@@ -1076,85 +1076,85 @@
     <t xml:space="preserve">68.4985504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4081802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2785873413086</t>
+    <t xml:space="preserve">68.4081649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2785797119141</t>
   </si>
   <si>
     <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.402229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6162185668945</t>
+    <t xml:space="preserve">69.402214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6162338256836</t>
   </si>
   <si>
     <t xml:space="preserve">71.9325103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">72.0228729248047</t>
+    <t xml:space="preserve">72.0228652954102</t>
   </si>
   <si>
     <t xml:space="preserve">71.7065887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4806671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4355010986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6614074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2547607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8088607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7517776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0918884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6187057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0765037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9409370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602081298828</t>
+    <t xml:space="preserve">71.4806747436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4354934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2547378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8088760375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7517700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9623031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572250366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6186904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0764961242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9409484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602119445801</t>
   </si>
   <si>
     <t xml:space="preserve">61.9017181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9528579711914</t>
+    <t xml:space="preserve">60.9528617858887</t>
   </si>
   <si>
     <t xml:space="preserve">60.0040054321289</t>
@@ -1163,46 +1163,46 @@
     <t xml:space="preserve">59.7329025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8624992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7994270324707</t>
+    <t xml:space="preserve">60.862491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8113594055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7994346618652</t>
   </si>
   <si>
     <t xml:space="preserve">67.5496978759766</t>
   </si>
   <si>
-    <t xml:space="preserve">66.7363739013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838577270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2905120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4200973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2726364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1251525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8600158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540649414062</t>
+    <t xml:space="preserve">66.7363815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6519622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4200897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2726211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1251602172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540725708008</t>
   </si>
   <si>
     <t xml:space="preserve">70.622184753418</t>
@@ -1220,355 +1220,355 @@
     <t xml:space="preserve">73.6946792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4747161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.46875</t>
+    <t xml:space="preserve">72.4747085571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4687576293945</t>
   </si>
   <si>
     <t xml:space="preserve">73.1976623535156</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3783798217773</t>
+    <t xml:space="preserve">73.3783950805664</t>
   </si>
   <si>
     <t xml:space="preserve">74.688720703125</t>
   </si>
   <si>
+    <t xml:space="preserve">73.5591201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6960983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9289398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.7964859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1527099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.2576217651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.4312210083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0795211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9059371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5908508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3625411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7278289794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2712326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2300796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.102165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3806686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2482223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.928596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.056510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8006896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3942642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8554153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9878463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9421920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0380554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2572937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5769119262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6772918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1750259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4033279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1248397827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6225662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3531341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2984161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8418045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1614303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4720001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8327484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.668571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2255554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4538650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3580169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.49951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6135177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784027099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6500930786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7414245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8372802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3350067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6410369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9149856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0017852783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2757568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8282012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.53125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.0199279785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8829345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7368850708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3761444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4583969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2667083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.1572494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4266738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3308181762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8376159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6002426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9198684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5179977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4357376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8285598754883</t>
+  </si>
+  <si>
     <t xml:space="preserve">73.5591354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">74.198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9289398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.796501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.152702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.2576293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.4312057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0795211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9059371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5908432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.362548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7278137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2712326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2300872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.102180480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3806762695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2482223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9286041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893600463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.056510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8006896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3942642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8554077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9878540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2206802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9421920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0380401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4855880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5769119262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6772918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1750335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4033279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1248245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6225662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.353141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2984008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8418197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4719848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8327484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77.668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7689514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2255630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4538726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3580169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4995269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123474121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6500930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2391586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7414245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.837272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6591644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3350067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6410369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9149932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0017776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2757568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8282089233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.53125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2436981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0199203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.882926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7368774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3761367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4583969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2666931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.1572418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4266738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8376312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6002502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9198760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5179977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4357376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8285522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5591430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.8330917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.2806167602539</t>
+    <t xml:space="preserve">73.8330841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.2806396484375</t>
   </si>
   <si>
     <t xml:space="preserve">73.9700698852539</t>
   </si>
   <si>
-    <t xml:space="preserve">75.06591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.5270538330078</t>
+    <t xml:space="preserve">75.0659255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.5270614624023</t>
   </si>
   <si>
     <t xml:space="preserve">79.9515991210938</t>
   </si>
   <si>
-    <t xml:space="preserve">75.3398895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1161041259766</t>
+    <t xml:space="preserve">75.3398818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.1161117553711</t>
   </si>
   <si>
     <t xml:space="preserve">73.0568618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5455169677734</t>
+    <t xml:space="preserve">70.5455322265625</t>
   </si>
   <si>
     <t xml:space="preserve">70.6825103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0934600830078</t>
+    <t xml:space="preserve">71.0934448242188</t>
   </si>
   <si>
     <t xml:space="preserve">71.9610061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">73.1025238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3262786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0478057861328</t>
+    <t xml:space="preserve">73.1025314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3262939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477981567383</t>
   </si>
   <si>
     <t xml:space="preserve">70.8651580810547</t>
@@ -1577,43 +1577,43 @@
     <t xml:space="preserve">68.5821228027344</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4908065795898</t>
+    <t xml:space="preserve">68.4908142089844</t>
   </si>
   <si>
     <t xml:space="preserve">68.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3217544555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8013687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3949432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.938346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5775985717773</t>
+    <t xml:space="preserve">71.3217620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8013763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3949584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9383544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5776062011719</t>
   </si>
   <si>
     <t xml:space="preserve">66.8470230102539</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5228652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0160675048828</t>
+    <t xml:space="preserve">65.5228729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0160598754883</t>
   </si>
   <si>
     <t xml:space="preserve">64.4270248413086</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2900466918945</t>
+    <t xml:space="preserve">64.2900314331055</t>
   </si>
   <si>
     <t xml:space="preserve">64.7922973632812</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">66.1621170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">64.944694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2089385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6771774291992</t>
+    <t xml:space="preserve">64.9446868896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2089309692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6771697998047</t>
   </si>
   <si>
     <t xml:space="preserve">66.3025894165039</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">70.750862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1421508789062</t>
+    <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
     <t xml:space="preserve">69.7675628662109</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">73.0452194213867</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459487915039</t>
+    <t xml:space="preserve">75.2459411621094</t>
   </si>
   <si>
     <t xml:space="preserve">75.10546875</t>
@@ -1673,70 +1673,70 @@
     <t xml:space="preserve">74.9650039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">74.5904159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.0586547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2927703857422</t>
+    <t xml:space="preserve">74.5904235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.0586624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2927627563477</t>
   </si>
   <si>
     <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">76.557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.1355972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8713607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8847732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9784240722656</t>
+    <t xml:space="preserve">76.5570068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8713531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9784317016602</t>
   </si>
   <si>
     <t xml:space="preserve">78.7109222412109</t>
   </si>
   <si>
-    <t xml:space="preserve">78.6172637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.6942138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2728042602539</t>
+    <t xml:space="preserve">78.6172485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.694206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2727966308594</t>
   </si>
   <si>
     <t xml:space="preserve">79.6005630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2259750366211</t>
+    <t xml:space="preserve">79.2259674072266</t>
   </si>
   <si>
     <t xml:space="preserve">79.4132766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7878494262695</t>
+    <t xml:space="preserve">79.7878570556641</t>
   </si>
   <si>
     <t xml:space="preserve">80.0219802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0386810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8815078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6775131225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3029174804688</t>
+    <t xml:space="preserve">79.0386734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8815155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6775207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3029251098633</t>
   </si>
   <si>
     <t xml:space="preserve">80.7711563110352</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">82.0354080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">81.707633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798675537109</t>
+    <t xml:space="preserve">81.7076416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">81.3330459594727</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">81.2394027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2227020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.145751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497543334961</t>
+    <t xml:space="preserve">82.2226943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497619628906</t>
   </si>
   <si>
     <t xml:space="preserve">79.9751510620117</t>
@@ -1772,76 +1772,76 @@
     <t xml:space="preserve">82.26953125</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5036544799805</t>
+    <t xml:space="preserve">82.5036468505859</t>
   </si>
   <si>
     <t xml:space="preserve">83.0187072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2528228759766</t>
+    <t xml:space="preserve">83.2528305053711</t>
   </si>
   <si>
     <t xml:space="preserve">82.9250640869141</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6742401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9718856811523</t>
+    <t xml:space="preserve">83.6742477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9718780517578</t>
   </si>
   <si>
     <t xml:space="preserve">84.0488357543945</t>
   </si>
   <si>
-    <t xml:space="preserve">84.0020065307617</t>
+    <t xml:space="preserve">84.0019989013672</t>
   </si>
   <si>
     <t xml:space="preserve">84.7980194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">85.7813110351562</t>
+    <t xml:space="preserve">85.7813186645508</t>
   </si>
   <si>
     <t xml:space="preserve">86.8582611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">86.1559143066406</t>
+    <t xml:space="preserve">86.1558990478516</t>
   </si>
   <si>
     <t xml:space="preserve">85.8281402587891</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6876678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2194366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1257705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6408386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7410354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.256103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5671691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8481063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8147125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1893005371094</t>
+    <t xml:space="preserve">85.6876602172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2194213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1257858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6408462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7410430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2560958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.5671615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8147201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1893081665039</t>
   </si>
   <si>
     <t xml:space="preserve">84.2829513549805</t>
@@ -1850,43 +1850,43 @@
     <t xml:space="preserve">85.3130722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1693420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4804000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2597045898438</t>
+    <t xml:space="preserve">88.1693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4804077148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2596969604492</t>
   </si>
   <si>
     <t xml:space="preserve">91.212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6854858398438</t>
+    <t xml:space="preserve">91.6854934692383</t>
   </si>
   <si>
     <t xml:space="preserve">91.1656112670898</t>
   </si>
   <si>
-    <t xml:space="preserve">92.158088684082</t>
+    <t xml:space="preserve">92.1580963134766</t>
   </si>
   <si>
     <t xml:space="preserve">91.5437088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8348083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.598503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1806869506836</t>
+    <t xml:space="preserve">90.8348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5984878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1806793212891</t>
   </si>
   <si>
     <t xml:space="preserve">88.3299789428711</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8025894165039</t>
+    <t xml:space="preserve">88.8025817871094</t>
   </si>
   <si>
     <t xml:space="preserve">86.5340957641602</t>
@@ -1895,25 +1895,25 @@
     <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3546676635742</t>
+    <t xml:space="preserve">91.3546752929688</t>
   </si>
   <si>
     <t xml:space="preserve">91.9690551757812</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1033096313477</t>
+    <t xml:space="preserve">93.1033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">95.5608520507812</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8122177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0731887817383</t>
+    <t xml:space="preserve">96.4115447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8122253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">97.8293762207031</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">99.3416976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">101.326644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2471694946289</t>
+    <t xml:space="preserve">101.326637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6800537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2471771240234</t>
   </si>
   <si>
     <t xml:space="preserve">96.8841552734375</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">97.6403274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9389495849609</t>
+    <t xml:space="preserve">95.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">96.3170318603516</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5060501098633</t>
+    <t xml:space="preserve">96.5060653686523</t>
   </si>
   <si>
     <t xml:space="preserve">97.2622375488281</t>
@@ -1955,64 +1955,64 @@
     <t xml:space="preserve">99.5307540893555</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3019714355469</t>
+    <t xml:space="preserve">98.3019790649414</t>
   </si>
   <si>
     <t xml:space="preserve">97.3567581176758</t>
   </si>
   <si>
-    <t xml:space="preserve">98.2074508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1677169799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.5457992553711</t>
+    <t xml:space="preserve">98.2074432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1677322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.5457916259766</t>
   </si>
   <si>
     <t xml:space="preserve">96.2225112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7499084472656</t>
+    <t xml:space="preserve">95.7499008178711</t>
   </si>
   <si>
     <t xml:space="preserve">95.8444213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4663391113281</t>
+    <t xml:space="preserve">95.4663314819336</t>
   </si>
   <si>
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082801818848</t>
+    <t xml:space="preserve">102.082809448242</t>
   </si>
   <si>
     <t xml:space="preserve">100.475959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">99.1526641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.799255371094</t>
+    <t xml:space="preserve">99.1526565551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.799247741699</t>
   </si>
   <si>
     <t xml:space="preserve">100.664993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">100.097869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9088363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3964767456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.1923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.366386413574</t>
+    <t xml:space="preserve">100.097877502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.908821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3964920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.192390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.366394042969</t>
   </si>
   <si>
     <t xml:space="preserve">102.17733001709</t>
@@ -2027,10 +2027,10 @@
     <t xml:space="preserve">100.003356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">101.137596130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.704734802246</t>
+    <t xml:space="preserve">101.137603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.704727172852</t>
   </si>
   <si>
     <t xml:space="preserve">103.689666748047</t>
@@ -2039,67 +2039,67 @@
     <t xml:space="preserve">103.500633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">102.933502197266</t>
+    <t xml:space="preserve">102.93350982666</t>
   </si>
   <si>
     <t xml:space="preserve">100.381423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5855331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6951065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1129302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0581359863281</t>
+    <t xml:space="preserve">98.5855407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6951141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0581512451172</t>
   </si>
   <si>
     <t xml:space="preserve">100.94856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">100.286903381348</t>
+    <t xml:space="preserve">100.286895751953</t>
   </si>
   <si>
     <t xml:space="preserve">99.7197799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">100.854042053223</t>
+    <t xml:space="preserve">100.854034423828</t>
   </si>
   <si>
     <t xml:space="preserve">99.6252746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4266052246094</t>
+    <t xml:space="preserve">94.4266128540039</t>
   </si>
   <si>
     <t xml:space="preserve">94.7101593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8594818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0957794189453</t>
+    <t xml:space="preserve">93.859489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0957870483398</t>
   </si>
   <si>
     <t xml:space="preserve">94.2848281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6156463623047</t>
+    <t xml:space="preserve">94.6156387329102</t>
   </si>
   <si>
     <t xml:space="preserve">94.521125793457</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6382141113281</t>
+    <t xml:space="preserve">91.6382217407227</t>
   </si>
   <si>
     <t xml:space="preserve">92.3471298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3074035644531</t>
+    <t xml:space="preserve">91.3074111938477</t>
   </si>
   <si>
     <t xml:space="preserve">92.2998809814453</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">92.0163192749023</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1505584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3718109130859</t>
+    <t xml:space="preserve">93.1505737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3718185424805</t>
   </si>
   <si>
     <t xml:space="preserve">94.8046951293945</t>
   </si>
   <si>
-    <t xml:space="preserve">98.8690872192383</t>
+    <t xml:space="preserve">98.8690948486328</t>
   </si>
   <si>
     <t xml:space="preserve">97.9238815307617</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">100.75951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">103.122543334961</t>
+    <t xml:space="preserve">103.122535705566</t>
   </si>
   <si>
     <t xml:space="preserve">104.634880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">105.958168029785</t>
+    <t xml:space="preserve">105.95817565918</t>
   </si>
   <si>
     <t xml:space="preserve">108.226684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">107.659561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.077377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.574668884277</t>
+    <t xml:space="preserve">107.659553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.07738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.574653625488</t>
   </si>
   <si>
     <t xml:space="preserve">113.803436279297</t>
@@ -2162,28 +2162,28 @@
     <t xml:space="preserve">114.654121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">111.818481445312</t>
+    <t xml:space="preserve">111.818496704102</t>
   </si>
   <si>
     <t xml:space="preserve">114.937683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.206192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.017150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.315780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.370567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.425354003906</t>
+    <t xml:space="preserve">115.977409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.206199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.017158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.370552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.425346374512</t>
   </si>
   <si>
     <t xml:space="preserve">109.644500732422</t>
@@ -2192,28 +2192,28 @@
     <t xml:space="preserve">111.251358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">110.589721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.306144714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.156837463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.723960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.117111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.833534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.510261535645</t>
+    <t xml:space="preserve">110.589714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.30615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.156845092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.723968505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.062309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.11710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.833541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.51025390625</t>
   </si>
   <si>
     <t xml:space="preserve">111.913009643555</t>
@@ -2225,37 +2225,37 @@
     <t xml:space="preserve">112.952743530273</t>
   </si>
   <si>
-    <t xml:space="preserve">110.873268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.455474853516</t>
+    <t xml:space="preserve">110.87328338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.455467224121</t>
   </si>
   <si>
     <t xml:space="preserve">107.470512390137</t>
   </si>
   <si>
-    <t xml:space="preserve">110.49520111084</t>
+    <t xml:space="preserve">110.495193481445</t>
   </si>
   <si>
     <t xml:space="preserve">108.037651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">107.848594665527</t>
+    <t xml:space="preserve">107.848602294922</t>
   </si>
   <si>
     <t xml:space="preserve">108.793807983398</t>
   </si>
   <si>
-    <t xml:space="preserve">106.430786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.171890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.266418457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.997909545898</t>
+    <t xml:space="preserve">106.430778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.171897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.266410827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.997901916504</t>
   </si>
   <si>
     <t xml:space="preserve">104.918441772461</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">105.769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">107.75407409668</t>
+    <t xml:space="preserve">107.754089355469</t>
   </si>
   <si>
     <t xml:space="preserve">108.415733337402</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">114.27604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">114.46508026123</t>
+    <t xml:space="preserve">114.465087890625</t>
   </si>
   <si>
     <t xml:space="preserve">109.928070068359</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">98.7745742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">106.808868408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.595153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.893775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8143081665039</t>
+    <t xml:space="preserve">106.808876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.595146179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.893783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8143005371094</t>
   </si>
   <si>
     <t xml:space="preserve">108.132164001465</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">105.485565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">110.400672912598</t>
+    <t xml:space="preserve">110.400665283203</t>
   </si>
   <si>
     <t xml:space="preserve">108.888336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">106.52530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.445838928223</t>
+    <t xml:space="preserve">106.525299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.445846557617</t>
   </si>
   <si>
     <t xml:space="preserve">102.555419921875</t>
@@ -2327,52 +2327,52 @@
     <t xml:space="preserve">114.08699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">111.629455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.05687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.310333251953</t>
+    <t xml:space="preserve">111.629447937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.05689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.310325622559</t>
   </si>
   <si>
     <t xml:space="preserve">126.091171264648</t>
   </si>
   <si>
-    <t xml:space="preserve">132.329574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876205444336</t>
+    <t xml:space="preserve">132.32958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876220703125</t>
   </si>
   <si>
     <t xml:space="preserve">136.583038330078</t>
   </si>
   <si>
-    <t xml:space="preserve">145.089920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.239242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.959869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.383117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.691345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.755752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.944808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.313232421875</t>
+    <t xml:space="preserve">145.089935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.2392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.959854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.38313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.691375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.755737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.94482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.313247680664</t>
   </si>
   <si>
     <t xml:space="preserve">146.791320800781</t>
@@ -2390,67 +2390,67 @@
     <t xml:space="preserve">146.318710327148</t>
   </si>
   <si>
-    <t xml:space="preserve">147.641983032227</t>
+    <t xml:space="preserve">147.641998291016</t>
   </si>
   <si>
     <t xml:space="preserve">153.596817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">151.706390380859</t>
+    <t xml:space="preserve">151.706405639648</t>
   </si>
   <si>
     <t xml:space="preserve">163.048934936523</t>
   </si>
   <si>
-    <t xml:space="preserve">167.302398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.107925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.675033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.381866455078</t>
+    <t xml:space="preserve">167.302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.10791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.675048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.381851196289</t>
   </si>
   <si>
     <t xml:space="preserve">178.833969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">180.440811157227</t>
+    <t xml:space="preserve">180.440826416016</t>
   </si>
   <si>
     <t xml:space="preserve">191.688842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">197.92724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.206619262695</t>
+    <t xml:space="preserve">197.927230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.206604003906</t>
   </si>
   <si>
     <t xml:space="preserve">163.521545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">171.839385986328</t>
+    <t xml:space="preserve">171.839416503906</t>
   </si>
   <si>
     <t xml:space="preserve">178.172332763672</t>
   </si>
   <si>
-    <t xml:space="preserve">171.55583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.098297119141</t>
+    <t xml:space="preserve">171.555847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.098266601562</t>
   </si>
   <si>
     <t xml:space="preserve">163.994155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">164.655807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.905075073242</t>
+    <t xml:space="preserve">164.655792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.905059814453</t>
   </si>
   <si>
     <t xml:space="preserve">150.855728149414</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">152.651611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">155.0146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.606460571289</t>
+    <t xml:space="preserve">155.014633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.606430053711</t>
   </si>
   <si>
     <t xml:space="preserve">157.850280761719</t>
@@ -2474,31 +2474,31 @@
     <t xml:space="preserve">162.365707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">161.890411376953</t>
+    <t xml:space="preserve">161.890396118164</t>
   </si>
   <si>
     <t xml:space="preserve">161.129928588867</t>
   </si>
   <si>
-    <t xml:space="preserve">159.133605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.270660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.118804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.936065673828</t>
+    <t xml:space="preserve">159.133590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.270645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.11882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.457061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.936080932617</t>
   </si>
   <si>
     <t xml:space="preserve">161.320037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">161.985443115234</t>
+    <t xml:space="preserve">161.985458374023</t>
   </si>
   <si>
     <t xml:space="preserve">162.55583190918</t>
@@ -2507,70 +2507,70 @@
     <t xml:space="preserve">162.841018676758</t>
   </si>
   <si>
-    <t xml:space="preserve">162.650894165039</t>
+    <t xml:space="preserve">162.650909423828</t>
   </si>
   <si>
     <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.350891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.031127929688</t>
+    <t xml:space="preserve">169.685485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.35090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.031143188477</t>
   </si>
   <si>
     <t xml:space="preserve">164.361999511719</t>
   </si>
   <si>
-    <t xml:space="preserve">165.122512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.647201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.400299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.966949462891</t>
+    <t xml:space="preserve">165.122482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.647186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.305252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.400283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.96696472168</t>
   </si>
   <si>
     <t xml:space="preserve">169.495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.358322143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.939804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.665710449219</t>
+    <t xml:space="preserve">166.358306884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.939788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.665679931641</t>
   </si>
   <si>
     <t xml:space="preserve">162.175598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">164.742248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.22868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.669403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.817535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.77555847168</t>
+    <t xml:space="preserve">164.742263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.228668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.802749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.669418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.81755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.775543212891</t>
   </si>
   <si>
     <t xml:space="preserve">150.768173217773</t>
@@ -2594,28 +2594,28 @@
     <t xml:space="preserve">154.760772705078</t>
   </si>
   <si>
-    <t xml:space="preserve">151.243469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.190399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.855834960938</t>
+    <t xml:space="preserve">151.24348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.190383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.855819702148</t>
   </si>
   <si>
     <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">155.426208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.806442260742</t>
+    <t xml:space="preserve">155.426193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.806427001953</t>
   </si>
   <si>
     <t xml:space="preserve">159.418792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">145.634811401367</t>
+    <t xml:space="preserve">145.634796142578</t>
   </si>
   <si>
     <t xml:space="preserve">138.600250244141</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">144.018783569336</t>
   </si>
   <si>
-    <t xml:space="preserve">144.589141845703</t>
+    <t xml:space="preserve">144.589157104492</t>
   </si>
   <si>
     <t xml:space="preserve">143.543472290039</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">144.779266357422</t>
   </si>
   <si>
-    <t xml:space="preserve">143.258285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.060760498047</t>
+    <t xml:space="preserve">143.258270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.060745239258</t>
   </si>
   <si>
     <t xml:space="preserve">147.726165771484</t>
@@ -2657,25 +2657,25 @@
     <t xml:space="preserve">149.247177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">152.954574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.387893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.034851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.654602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.080520629883</t>
+    <t xml:space="preserve">152.95458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.387908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.03483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.65461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.080535888672</t>
   </si>
   <si>
     <t xml:space="preserve">161.795333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">163.411376953125</t>
+    <t xml:space="preserve">163.411392211914</t>
   </si>
   <si>
     <t xml:space="preserve">168.069442749023</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">177.670669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">173.487976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.716339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.712661743164</t>
+    <t xml:space="preserve">173.48796081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.716354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.712677001953</t>
   </si>
   <si>
     <t xml:space="preserve">178.241058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">181.853408813477</t>
+    <t xml:space="preserve">181.853424072266</t>
   </si>
   <si>
     <t xml:space="preserve">179.666976928711</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">184.990447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">184.039840698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.663269042969</t>
+    <t xml:space="preserve">184.039825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.663284301758</t>
   </si>
   <si>
     <t xml:space="preserve">185.275619506836</t>
   </si>
   <si>
-    <t xml:space="preserve">183.089218139648</t>
+    <t xml:space="preserve">183.089202880859</t>
   </si>
   <si>
     <t xml:space="preserve">181.568222045898</t>
@@ -2735,37 +2735,37 @@
     <t xml:space="preserve">179.191665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">176.529937744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.860809326172</t>
+    <t xml:space="preserve">176.52995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.860824584961</t>
   </si>
   <si>
     <t xml:space="preserve">184.610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">189.838607788086</t>
+    <t xml:space="preserve">189.838592529297</t>
   </si>
   <si>
     <t xml:space="preserve">191.264526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">159.703994750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.217559814453</t>
+    <t xml:space="preserve">159.703979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.886688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.217575073242</t>
   </si>
   <si>
     <t xml:space="preserve">164.932373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">164.076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.947189331055</t>
+    <t xml:space="preserve">164.07682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.947204589844</t>
   </si>
   <si>
     <t xml:space="preserve">160.8447265625</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">164.266952514648</t>
   </si>
   <si>
-    <t xml:space="preserve">167.879318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.696578979492</t>
+    <t xml:space="preserve">167.879333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.696563720703</t>
   </si>
   <si>
     <t xml:space="preserve">161.605224609375</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">159.323745727539</t>
   </si>
   <si>
-    <t xml:space="preserve">158.468170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.848434448242</t>
+    <t xml:space="preserve">158.468185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.848449707031</t>
   </si>
   <si>
     <t xml:space="preserve">163.221267700195</t>
@@ -2807,37 +2807,37 @@
     <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">159.608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.700271606445</t>
+    <t xml:space="preserve">159.608901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.700286865234</t>
   </si>
   <si>
     <t xml:space="preserve">161.224975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">153.810165405273</t>
+    <t xml:space="preserve">153.810150146484</t>
   </si>
   <si>
     <t xml:space="preserve">152.859527587891</t>
   </si>
   <si>
-    <t xml:space="preserve">151.528656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.4755859375</t>
+    <t xml:space="preserve">151.52864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.616302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.475570678711</t>
   </si>
   <si>
     <t xml:space="preserve">154.570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">157.992858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.826232910156</t>
+    <t xml:space="preserve">157.992874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.826217651367</t>
   </si>
   <si>
     <t xml:space="preserve">169.970672607422</t>
@@ -2846,16 +2846,16 @@
     <t xml:space="preserve">179.001541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">168.924987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.681777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.111404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.541030883789</t>
+    <t xml:space="preserve">168.92497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.681793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.111419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.541015625</t>
   </si>
   <si>
     <t xml:space="preserve">167.784240722656</t>
@@ -2864,19 +2864,19 @@
     <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255874633789</t>
+    <t xml:space="preserve">170.255859375</t>
   </si>
   <si>
     <t xml:space="preserve">173.868194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">173.202774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.389221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.434875488281</t>
+    <t xml:space="preserve">173.202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.389190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.434906005859</t>
   </si>
   <si>
     <t xml:space="preserve">176.149703979492</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">174.438583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">156.18669128418</t>
+    <t xml:space="preserve">156.186706542969</t>
   </si>
   <si>
     <t xml:space="preserve">151.813842773438</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">155.901504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">157.137313842773</t>
+    <t xml:space="preserve">157.137329101562</t>
   </si>
   <si>
     <t xml:space="preserve">154.000274658203</t>
@@ -2915,46 +2915,46 @@
     <t xml:space="preserve">149.057052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">147.155807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.706405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.082946777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.6953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.987884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181701660156</t>
+    <t xml:space="preserve">147.155822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.706420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.082962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.695297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.987899780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181732177734</t>
   </si>
   <si>
     <t xml:space="preserve">136.033569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">133.276779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.037261962891</t>
+    <t xml:space="preserve">133.276763916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.03727722168</t>
   </si>
   <si>
     <t xml:space="preserve">133.086654663086</t>
   </si>
   <si>
-    <t xml:space="preserve">135.273056030273</t>
+    <t xml:space="preserve">135.273086547852</t>
   </si>
   <si>
     <t xml:space="preserve">132.136016845703</t>
   </si>
   <si>
-    <t xml:space="preserve">130.519973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.900238037109</t>
+    <t xml:space="preserve">130.519989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.90022277832</t>
   </si>
   <si>
     <t xml:space="preserve">130.044677734375</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">132.848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">135.463195800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.229248046875</t>
+    <t xml:space="preserve">135.46321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.229232788086</t>
   </si>
   <si>
     <t xml:space="preserve">145.492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">143.59098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.784820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.201461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.058898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.300247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.01692199707</t>
+    <t xml:space="preserve">143.591003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.784805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.201477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.05891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.300231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.016937255859</t>
   </si>
   <si>
     <t xml:space="preserve">144.874313354492</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">136.984191894531</t>
   </si>
   <si>
-    <t xml:space="preserve">136.794067382812</t>
+    <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
     <t xml:space="preserve">133.324310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">134.274948120117</t>
+    <t xml:space="preserve">134.274932861328</t>
   </si>
   <si>
     <t xml:space="preserve">133.894683837891</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">134.227386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">131.660736083984</t>
+    <t xml:space="preserve">131.660705566406</t>
   </si>
   <si>
     <t xml:space="preserve">133.847152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">135.605804443359</t>
+    <t xml:space="preserve">135.60578918457</t>
   </si>
   <si>
     <t xml:space="preserve">131.423065185547</t>
@@ -3026,19 +3026,19 @@
     <t xml:space="preserve">128.333541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">131.470611572266</t>
+    <t xml:space="preserve">131.470596313477</t>
   </si>
   <si>
     <t xml:space="preserve">131.185409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">134.655181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.031707763672</t>
+    <t xml:space="preserve">134.655166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.031692504883</t>
   </si>
   <si>
     <t xml:space="preserve">136.983856201172</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">137.845397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">137.797500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.084701538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.46760559082</t>
+    <t xml:space="preserve">137.797515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.084716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.467590332031</t>
   </si>
   <si>
     <t xml:space="preserve">135.978744506836</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">132.963348388672</t>
   </si>
   <si>
-    <t xml:space="preserve">135.356521606445</t>
+    <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
     <t xml:space="preserve">136.218048095703</t>
   </si>
   <si>
-    <t xml:space="preserve">137.510360717773</t>
+    <t xml:space="preserve">137.510330200195</t>
   </si>
   <si>
     <t xml:space="preserve">138.659072875977</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">139.185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">143.2060546875</t>
+    <t xml:space="preserve">143.206069946289</t>
   </si>
   <si>
     <t xml:space="preserve">144.306884765625</t>
@@ -3110,22 +3110,22 @@
     <t xml:space="preserve">143.397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">147.99235534668</t>
+    <t xml:space="preserve">147.992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">149.428237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">150.289764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.065811157227</t>
+    <t xml:space="preserve">150.289749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.065795898438</t>
   </si>
   <si>
     <t xml:space="preserve">152.682922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768402099609</t>
+    <t xml:space="preserve">150.76838684082</t>
   </si>
   <si>
     <t xml:space="preserve">151.534210205078</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">152.395721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">153.783767700195</t>
+    <t xml:space="preserve">153.783752441406</t>
   </si>
   <si>
     <t xml:space="preserve">155.123931884766</t>
@@ -3155,31 +3155,31 @@
     <t xml:space="preserve">155.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">155.650405883789</t>
+    <t xml:space="preserve">155.650421142578</t>
   </si>
   <si>
     <t xml:space="preserve">156.081192016602</t>
   </si>
   <si>
-    <t xml:space="preserve">158.90510559082</t>
+    <t xml:space="preserve">158.905090332031</t>
   </si>
   <si>
     <t xml:space="preserve">160.149551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">162.207641601562</t>
+    <t xml:space="preserve">162.207656860352</t>
   </si>
   <si>
     <t xml:space="preserve">163.643539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">164.983703613281</t>
+    <t xml:space="preserve">164.98371887207</t>
   </si>
   <si>
     <t xml:space="preserve">161.72900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">160.915344238281</t>
+    <t xml:space="preserve">160.91535949707</t>
   </si>
   <si>
     <t xml:space="preserve">162.35124206543</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">165.07942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">163.834991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.908462524414</t>
+    <t xml:space="preserve">163.834976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.908447265625</t>
   </si>
   <si>
     <t xml:space="preserve">164.600799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">168.142654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.860595703125</t>
+    <t xml:space="preserve">168.142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.860580444336</t>
   </si>
   <si>
     <t xml:space="preserve">166.036666870117</t>
@@ -3209,10 +3209,10 @@
     <t xml:space="preserve">168.669143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">168.334106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.052047729492</t>
+    <t xml:space="preserve">168.334121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">176.0400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">176.949432373047</t>
+    <t xml:space="preserve">176.949447631836</t>
   </si>
   <si>
     <t xml:space="preserve">177.140899658203</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">180.1083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">179.534042358398</t>
+    <t xml:space="preserve">179.534057617188</t>
   </si>
   <si>
     <t xml:space="preserve">178.05029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">177.475936889648</t>
+    <t xml:space="preserve">177.475921630859</t>
   </si>
   <si>
     <t xml:space="preserve">177.810989379883</t>
@@ -3254,10 +3254,10 @@
     <t xml:space="preserve">182.740859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">184.990417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.016021728516</t>
+    <t xml:space="preserve">184.990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.016036987305</t>
   </si>
   <si>
     <t xml:space="preserve">192.409194946289</t>
@@ -3266,34 +3266,34 @@
     <t xml:space="preserve">193.270706176758</t>
   </si>
   <si>
-    <t xml:space="preserve">195.568130493164</t>
+    <t xml:space="preserve">195.568145751953</t>
   </si>
   <si>
     <t xml:space="preserve">191.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">196.908294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.812591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.386932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.175003051758</t>
+    <t xml:space="preserve">196.908309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.812606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.386947631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.29296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.175018310547</t>
   </si>
   <si>
     <t xml:space="preserve">190.351089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">192.026290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.940826416016</t>
+    <t xml:space="preserve">192.026306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.940811157227</t>
   </si>
   <si>
     <t xml:space="preserve">195.855331420898</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">194.515167236328</t>
   </si>
   <si>
-    <t xml:space="preserve">187.47932434082</t>
+    <t xml:space="preserve">187.479309082031</t>
   </si>
   <si>
     <t xml:space="preserve">180.539184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">174.987060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.077667236328</t>
+    <t xml:space="preserve">174.987075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.077682495117</t>
   </si>
   <si>
     <t xml:space="preserve">173.599060058594</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">167.664016723633</t>
   </si>
   <si>
-    <t xml:space="preserve">164.505065917969</t>
+    <t xml:space="preserve">164.505081176758</t>
   </si>
   <si>
     <t xml:space="preserve">165.462341308594</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">166.51530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">170.870849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.253753662109</t>
+    <t xml:space="preserve">170.870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.25373840332</t>
   </si>
   <si>
     <t xml:space="preserve">172.402481079102</t>
@@ -3368,25 +3368,25 @@
     <t xml:space="preserve">182.884460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">182.836608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.342620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.096405029297</t>
+    <t xml:space="preserve">182.83659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.34260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.096389770508</t>
   </si>
   <si>
     <t xml:space="preserve">187.000686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">188.723754882812</t>
+    <t xml:space="preserve">188.723739624023</t>
   </si>
   <si>
     <t xml:space="preserve">189.202362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">186.426315307617</t>
+    <t xml:space="preserve">186.426330566406</t>
   </si>
   <si>
     <t xml:space="preserve">184.798980712891</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">174.699890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">176.231506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.561416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.093048095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.964813232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.87419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.50666809082</t>
+    <t xml:space="preserve">176.231521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.561401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.093032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.964828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.874221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.506652832031</t>
   </si>
   <si>
     <t xml:space="preserve">175.896469116211</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">176.614410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">175.800720214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.636672973633</t>
+    <t xml:space="preserve">175.800704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.636657714844</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
@@ -3434,25 +3434,25 @@
     <t xml:space="preserve">177.188766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">180.682769775391</t>
+    <t xml:space="preserve">180.682754516602</t>
   </si>
   <si>
     <t xml:space="preserve">175.082794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">170.296493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.147766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.935836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.472579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.392196655273</t>
+    <t xml:space="preserve">170.296478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.14778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.935852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.472564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.392227172852</t>
   </si>
   <si>
     <t xml:space="preserve">172.306732177734</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">168.764892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">172.785385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.53581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.060699462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.688034057617</t>
+    <t xml:space="preserve">172.785369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.535797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.06071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.688049316406</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">160.293121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">156.22477722168</t>
+    <t xml:space="preserve">156.224761962891</t>
   </si>
   <si>
     <t xml:space="preserve">152.156402587891</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">148.183792114258</t>
   </si>
   <si>
-    <t xml:space="preserve">141.770156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.780410766602</t>
+    <t xml:space="preserve">141.770172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.780395507812</t>
   </si>
   <si>
     <t xml:space="preserve">147.609436035156</t>
@@ -3527,25 +3527,25 @@
     <t xml:space="preserve">137.223175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.946228027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.717178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.94287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.884757995605</t>
+    <t xml:space="preserve">138.946212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.717163085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.884773254395</t>
   </si>
   <si>
     <t xml:space="preserve">128.990753173828</t>
   </si>
   <si>
-    <t xml:space="preserve">129.325790405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.048843383789</t>
+    <t xml:space="preserve">129.325775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.048828125</t>
   </si>
   <si>
     <t xml:space="preserve">131.144577026367</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">127.698425292969</t>
   </si>
   <si>
-    <t xml:space="preserve">125.975379943848</t>
+    <t xml:space="preserve">125.975387573242</t>
   </si>
   <si>
     <t xml:space="preserve">120.518997192383</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">115.58910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">112.286560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.430145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.211318969727</t>
+    <t xml:space="preserve">112.286567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.430137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.211326599121</t>
   </si>
   <si>
     <t xml:space="preserve">120.136085510254</t>
   </si>
   <si>
-    <t xml:space="preserve">123.10359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.864280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.937759399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.124099731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.77367401123</t>
+    <t xml:space="preserve">123.103591918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.864273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.124084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.773681640625</t>
   </si>
   <si>
     <t xml:space="preserve">123.151443481445</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">120.08821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">122.242057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.503623962402</t>
+    <t xml:space="preserve">122.242050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.503631591797</t>
   </si>
   <si>
     <t xml:space="preserve">120.806159973145</t>
@@ -3632,13 +3632,13 @@
     <t xml:space="preserve">115.541236877441</t>
   </si>
   <si>
-    <t xml:space="preserve">117.59935760498</t>
+    <t xml:space="preserve">117.599349975586</t>
   </si>
   <si>
     <t xml:space="preserve">121.859161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">131.718933105469</t>
+    <t xml:space="preserve">131.718948364258</t>
   </si>
   <si>
     <t xml:space="preserve">132.29328918457</t>
@@ -3647,16 +3647,16 @@
     <t xml:space="preserve">126.693321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">126.597564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.448890686035</t>
+    <t xml:space="preserve">126.597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.448883056641</t>
   </si>
   <si>
     <t xml:space="preserve">133.824905395508</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">139.329132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">139.616317749023</t>
+    <t xml:space="preserve">139.616333007812</t>
   </si>
   <si>
     <t xml:space="preserve">142.105178833008</t>
@@ -3680,16 +3680,16 @@
     <t xml:space="preserve">139.041976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">136.170196533203</t>
+    <t xml:space="preserve">136.170181274414</t>
   </si>
   <si>
     <t xml:space="preserve">135.260787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">132.628326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.038604736328</t>
+    <t xml:space="preserve">132.628341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.038619995117</t>
   </si>
   <si>
     <t xml:space="preserve">129.086471557617</t>
@@ -3698,34 +3698,34 @@
     <t xml:space="preserve">128.559982299805</t>
   </si>
   <si>
-    <t xml:space="preserve">128.416381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.454002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.539482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.997619628906</t>
+    <t xml:space="preserve">128.416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.45401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.539489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.997627258301</t>
   </si>
   <si>
     <t xml:space="preserve">118.7001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">115.254058837891</t>
+    <t xml:space="preserve">115.254066467285</t>
   </si>
   <si>
     <t xml:space="preserve">118.652328491211</t>
   </si>
   <si>
-    <t xml:space="preserve">119.70531463623</t>
+    <t xml:space="preserve">119.705322265625</t>
   </si>
   <si>
     <t xml:space="preserve">118.173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">117.647216796875</t>
+    <t xml:space="preserve">117.64720916748</t>
   </si>
   <si>
     <t xml:space="preserve">114.392524719238</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">115.493385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">109.271194458008</t>
+    <t xml:space="preserve">109.271186828613</t>
   </si>
   <si>
     <t xml:space="preserve">106.590866088867</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">114.871154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">113.435264587402</t>
+    <t xml:space="preserve">113.435272216797</t>
   </si>
   <si>
     <t xml:space="preserve">110.563484191895</t>
@@ -6003,6 +6003,9 @@
   </si>
   <si>
     <t xml:space="preserve">61.6800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0400009155273</t>
   </si>
 </sst>
 </file>
@@ -72043,7 +72046,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6909722222</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>245002</v>
@@ -72064,6 +72067,32 @@
         <v>1996</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6911458333</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>171125</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>61.7200012207031</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>60.9199981689453</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>61.6800003051758</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>61.0400009155273</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="2003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="2004">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,106 +38,106 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954566955566</t>
+    <t xml:space="preserve">42.4954643249512</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.042308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9276466369629</t>
+    <t xml:space="preserve">43.298095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0423049926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9276351928711</t>
   </si>
   <si>
     <t xml:space="preserve">42.8218040466309</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1514739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4689979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.728099822998</t>
+    <t xml:space="preserve">42.1514663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7281074523926</t>
   </si>
   <si>
     <t xml:space="preserve">41.2870979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9993591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2761001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0765609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443786621094</t>
+    <t xml:space="preserve">39.9993553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2761039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0765647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443824768066</t>
   </si>
   <si>
     <t xml:space="preserve">38.9585800170898</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544548034668</t>
+    <t xml:space="preserve">40.2551460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2606391906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544509887695</t>
   </si>
   <si>
     <t xml:space="preserve">41.3664817810059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.777702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0687637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9981994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.878044128418</t>
+    <t xml:space="preserve">42.7776985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0687713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8780479431152</t>
   </si>
   <si>
     <t xml:space="preserve">41.2341766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4172248840332</t>
+    <t xml:space="preserve">39.4172325134277</t>
   </si>
   <si>
     <t xml:space="preserve">37.7590446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">38.014820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881271362305</t>
+    <t xml:space="preserve">38.0148239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881309509277</t>
   </si>
   <si>
     <t xml:space="preserve">38.605770111084</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4029083251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1228408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3962593078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4932861328125</t>
+    <t xml:space="preserve">38.4029121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1228332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3962631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4932823181152</t>
   </si>
   <si>
     <t xml:space="preserve">41.4017562866211</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">42.5483818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9397888183594</t>
+    <t xml:space="preserve">41.9397926330566</t>
   </si>
   <si>
     <t xml:space="preserve">42.5924797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">43.209888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9011840820312</t>
+    <t xml:space="preserve">43.2098922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.901180267334</t>
   </si>
   <si>
     <t xml:space="preserve">43.2275276184082</t>
@@ -173,28 +173,28 @@
     <t xml:space="preserve">42.7071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7600517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.757884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3521537780762</t>
+    <t xml:space="preserve">42.7600631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7578887939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3521614074707</t>
   </si>
   <si>
     <t xml:space="preserve">40.0081748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1636199951172</t>
+    <t xml:space="preserve">41.1636085510254</t>
   </si>
   <si>
     <t xml:space="preserve">40.5726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1581153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6200866699219</t>
+    <t xml:space="preserve">40.1581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6200904846191</t>
   </si>
   <si>
     <t xml:space="preserve">40.1140174865723</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">40.2904243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8405914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1316680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4668273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1007270812988</t>
+    <t xml:space="preserve">39.8405952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1316604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4668235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1007232666016</t>
   </si>
   <si>
     <t xml:space="preserve">44.7622375488281</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">45.8647537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3796501159668</t>
+    <t xml:space="preserve">45.3796463012695</t>
   </si>
   <si>
     <t xml:space="preserve">45.6883506774902</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8349685668945</t>
+    <t xml:space="preserve">46.8349647521973</t>
   </si>
   <si>
     <t xml:space="preserve">45.9088478088379</t>
@@ -242,34 +242,34 @@
     <t xml:space="preserve">45.2032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8945426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9386329650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3355407714844</t>
+    <t xml:space="preserve">44.8945465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3355484008789</t>
   </si>
   <si>
     <t xml:space="preserve">44.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">44.718132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9827346801758</t>
+    <t xml:space="preserve">44.7181396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.982738494873</t>
   </si>
   <si>
     <t xml:space="preserve">44.8504371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7765464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442489624023</t>
+    <t xml:space="preserve">45.776554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442451477051</t>
   </si>
   <si>
     <t xml:space="preserve">45.8206520080566</t>
@@ -287,52 +287,52 @@
     <t xml:space="preserve">46.6144599914551</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0852546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970588684082</t>
+    <t xml:space="preserve">46.085262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970550537109</t>
   </si>
   <si>
     <t xml:space="preserve">47.422664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5119743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1100845336914</t>
+    <t xml:space="preserve">47.5119705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1100921630859</t>
   </si>
   <si>
     <t xml:space="preserve">47.9138679504395</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1817855834961</t>
+    <t xml:space="preserve">48.1817893981934</t>
   </si>
   <si>
     <t xml:space="preserve">49.1195259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5836715698242</t>
+    <t xml:space="preserve">48.5836753845215</t>
   </si>
   <si>
     <t xml:space="preserve">49.5660591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6553726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2358703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0748634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9679527282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1641807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.700023651123</t>
+    <t xml:space="preserve">49.6553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2358741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0748672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1641731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000274658203</t>
   </si>
   <si>
     <t xml:space="preserve">48.9855613708496</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">47.5566253662109</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7352409362793</t>
+    <t xml:space="preserve">47.7352447509766</t>
   </si>
   <si>
     <t xml:space="preserve">46.6188926696777</t>
@@ -350,25 +350,25 @@
     <t xml:space="preserve">46.9314727783203</t>
   </si>
   <si>
-    <t xml:space="preserve">48.092472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723480224609</t>
+    <t xml:space="preserve">48.0924797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723556518555</t>
   </si>
   <si>
     <t xml:space="preserve">45.011344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.038387298584</t>
+    <t xml:space="preserve">46.0383911132812</t>
   </si>
   <si>
     <t xml:space="preserve">48.8962554931641</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7446784973145</t>
+    <t xml:space="preserve">49.744686126709</t>
   </si>
   <si>
     <t xml:space="preserve">50.414493560791</t>
@@ -380,16 +380,16 @@
     <t xml:space="preserve">48.9409065246582</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8339881896973</t>
+    <t xml:space="preserve">49.8339920043945</t>
   </si>
   <si>
     <t xml:space="preserve">49.030216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5931053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2182655334473</t>
+    <t xml:space="preserve">50.5931129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.21826171875</t>
   </si>
   <si>
     <t xml:space="preserve">51.2629241943359</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">50.9503364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8610343933105</t>
+    <t xml:space="preserve">50.8610305786133</t>
   </si>
   <si>
     <t xml:space="preserve">51.575496673584</t>
@@ -407,67 +407,67 @@
     <t xml:space="preserve">51.798770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9949913024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7717247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2805328369141</t>
+    <t xml:space="preserve">50.994987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7717208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2805290222168</t>
   </si>
   <si>
     <t xml:space="preserve">50.057258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8786430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.191219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6201515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5849304199219</t>
+    <t xml:space="preserve">49.8786392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1912269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6201477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5849342346191</t>
   </si>
   <si>
     <t xml:space="preserve">53.0937385559082</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1654396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3440551757812</t>
+    <t xml:space="preserve">54.1654434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3440589904785</t>
   </si>
   <si>
     <t xml:space="preserve">55.37109375</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1207847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0666923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6648063659668</t>
+    <t xml:space="preserve">54.1207809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0666961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">50.6824150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3968849182129</t>
+    <t xml:space="preserve">51.3968772888184</t>
   </si>
   <si>
     <t xml:space="preserve">50.6377639770508</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2453079223633</t>
+    <t xml:space="preserve">52.2453117370605</t>
   </si>
   <si>
     <t xml:space="preserve">51.7541160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4415321350098</t>
+    <t xml:space="preserve">51.441535949707</t>
   </si>
   <si>
     <t xml:space="preserve">51.3522300720215</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">51.8880805969238</t>
   </si>
   <si>
-    <t xml:space="preserve">51.084300994873</t>
+    <t xml:space="preserve">51.0843048095703</t>
   </si>
   <si>
     <t xml:space="preserve">50.4591484069824</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4767570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2981452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9773864746094</t>
+    <t xml:space="preserve">49.476749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2981414794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9773902893066</t>
   </si>
   <si>
     <t xml:space="preserve">52.5132369995117</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">52.6918487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5308456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3346176147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6025428771973</t>
+    <t xml:space="preserve">51.5308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3346252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6025466918945</t>
   </si>
   <si>
     <t xml:space="preserve">52.2899627685547</t>
   </si>
   <si>
-    <t xml:space="preserve">53.183048248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7094573974609</t>
+    <t xml:space="preserve">53.1830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7094650268555</t>
   </si>
   <si>
     <t xml:space="preserve">51.1736068725586</t>
@@ -521,64 +521,64 @@
     <t xml:space="preserve">50.7270736694336</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1465759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9056930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0126037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7176284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6459350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8245582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3239250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7258071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.547191619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.395622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6635437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7704658508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1277008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5742416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4402770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9937362670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4578895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6811599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5295867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3063125610352</t>
+    <t xml:space="preserve">50.1465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.905689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0126075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7176361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6459274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8245544433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.323917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7258110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3956184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6635475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7704582214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1276969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5742378234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4402694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9937400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4578857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6811561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5295829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3063163757324</t>
   </si>
   <si>
     <t xml:space="preserve">47.2440452575684</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">47.4673233032227</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2088241577148</t>
+    <t xml:space="preserve">49.2088317871094</t>
   </si>
   <si>
     <t xml:space="preserve">50.3698425292969</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1560020446777</t>
+    <t xml:space="preserve">52.156005859375</t>
   </si>
   <si>
     <t xml:space="preserve">50.5037994384766</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">49.6107177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8163795471191</t>
+    <t xml:space="preserve">50.8163871765137</t>
   </si>
   <si>
     <t xml:space="preserve">51.1289596557617</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">52.2006568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">52.468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3616676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4063148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4509658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6742401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9151153564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2723541259766</t>
+    <t xml:space="preserve">52.4685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4063186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4509735107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6742362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9151191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2723579406738</t>
   </si>
   <si>
     <t xml:space="preserve">53.8528594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7905960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264541625977</t>
+    <t xml:space="preserve">54.790599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5943717956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264465332031</t>
   </si>
   <si>
     <t xml:space="preserve">55.5050621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2641830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1302108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6390190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8000297546387</t>
+    <t xml:space="preserve">56.2641792297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1302185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6390228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8000221252441</t>
   </si>
   <si>
     <t xml:space="preserve">56.5321044921875</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">56.9786415100098</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0679550170898</t>
+    <t xml:space="preserve">57.0679512023926</t>
   </si>
   <si>
     <t xml:space="preserve">57.4251899719238</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">57.3358764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">58.050350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8987655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0327377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7648124694824</t>
+    <t xml:space="preserve">58.0503463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8987693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0327262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7648086547852</t>
   </si>
   <si>
     <t xml:space="preserve">58.0949974060059</t>
@@ -695,49 +695,49 @@
     <t xml:space="preserve">57.1572647094727</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3805274963379</t>
+    <t xml:space="preserve">57.3805313110352</t>
   </si>
   <si>
     <t xml:space="preserve">58.5861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0151214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9434204101562</t>
+    <t xml:space="preserve">60.0151176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.943431854248</t>
   </si>
   <si>
     <t xml:space="preserve">59.300666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2830543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4088401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.158519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6226806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8906097412109</t>
+    <t xml:space="preserve">60.2830467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4088478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1585311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6226692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8905982971191</t>
   </si>
   <si>
     <t xml:space="preserve">62.8283386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">62.6943626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7390289306641</t>
+    <t xml:space="preserve">62.6943740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7390365600586</t>
   </si>
   <si>
     <t xml:space="preserve">62.5157585144043</t>
@@ -746,58 +746,58 @@
     <t xml:space="preserve">60.8635559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">60.1937484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6757926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.946907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.0824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3083648681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5342864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4379653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7542533874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4831504821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5675659179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0705337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8386611938477</t>
+    <t xml:space="preserve">60.1937446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9528541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6757888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.082447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3083686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5342788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.495059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4379577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7542457580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4831428527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5675582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8386688232422</t>
   </si>
   <si>
     <t xml:space="preserve">65.5164184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1668586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0313148498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5223846435547</t>
+    <t xml:space="preserve">63.1668663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0313110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5223770141602</t>
   </si>
   <si>
     <t xml:space="preserve">63.8898010253906</t>
@@ -806,88 +806,88 @@
     <t xml:space="preserve">64.432014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">64.2964630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1609039306641</t>
+    <t xml:space="preserve">64.2964553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1609115600586</t>
   </si>
   <si>
     <t xml:space="preserve">65.697151184082</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0884056091309</t>
+    <t xml:space="preserve">61.0884208679199</t>
   </si>
   <si>
     <t xml:space="preserve">59.6425323486328</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7721176147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1847343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8173217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5462074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6877174377441</t>
+    <t xml:space="preserve">60.7721214294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1847305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.817310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5462036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">60.6365699768066</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4498825073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3987464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927803039551</t>
+    <t xml:space="preserve">61.4498863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3987426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2120361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927726745605</t>
   </si>
   <si>
     <t xml:space="preserve">63.1216812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2393569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7815628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0134506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5104598999023</t>
+    <t xml:space="preserve">66.2393646240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7815551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0134429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5104522705078</t>
   </si>
   <si>
     <t xml:space="preserve">66.3297271728516</t>
   </si>
   <si>
-    <t xml:space="preserve">65.96826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6067810058594</t>
+    <t xml:space="preserve">65.9682464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6067733764648</t>
   </si>
   <si>
     <t xml:space="preserve">65.0193939208984</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2001342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7483062744141</t>
+    <t xml:space="preserve">65.2001266479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7482986450195</t>
   </si>
   <si>
     <t xml:space="preserve">64.7934799194336</t>
@@ -899,40 +899,40 @@
     <t xml:space="preserve">64.4771957397461</t>
   </si>
   <si>
-    <t xml:space="preserve">63.9801712036133</t>
+    <t xml:space="preserve">63.9801788330078</t>
   </si>
   <si>
     <t xml:space="preserve">63.302417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">65.4260635375977</t>
+    <t xml:space="preserve">65.4260406494141</t>
   </si>
   <si>
     <t xml:space="preserve">65.4712371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2845458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4652862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8719329833984</t>
+    <t xml:space="preserve">66.284553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6008148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4652786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8719253540039</t>
   </si>
   <si>
     <t xml:space="preserve">66.0586166381836</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3749008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6912002563477</t>
+    <t xml:space="preserve">66.3749160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6911926269531</t>
   </si>
   <si>
     <t xml:space="preserve">67.4141387939453</t>
@@ -944,100 +944,100 @@
     <t xml:space="preserve">68.137077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1822662353516</t>
+    <t xml:space="preserve">67.865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.182258605957</t>
   </si>
   <si>
     <t xml:space="preserve">69.1311264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3058853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3962478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9776992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3902969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5258712768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8480911254883</t>
+    <t xml:space="preserve">70.3058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3962707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9776840209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3903045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5258636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8480987548828</t>
   </si>
   <si>
     <t xml:space="preserve">71.1643905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7910003662109</t>
+    <t xml:space="preserve">72.7910079956055</t>
   </si>
   <si>
     <t xml:space="preserve">70.8932800292969</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2607192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3510894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5318222045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7577285766602</t>
+    <t xml:space="preserve">70.2607116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3510818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5318145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7577438354492</t>
   </si>
   <si>
     <t xml:space="preserve">70.8029174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4866256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5769882202148</t>
+    <t xml:space="preserve">70.4866333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5769958496094</t>
   </si>
   <si>
     <t xml:space="preserve">71.3451156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4414443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.5710220336914</t>
+    <t xml:space="preserve">70.4414520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5710372924805</t>
   </si>
   <si>
     <t xml:space="preserve">70.9836578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1097564697266</t>
+    <t xml:space="preserve">70.7125473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1097640991211</t>
   </si>
   <si>
     <t xml:space="preserve">65.5616073608398</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4593200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8208084106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2666625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.034797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7636871337891</t>
+    <t xml:space="preserve">67.4593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.82080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2666702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0347900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7636795043945</t>
   </si>
   <si>
     <t xml:space="preserve">68.9955673217773</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">67.3237686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3629989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0407409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1763000488281</t>
+    <t xml:space="preserve">68.3630065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1763153076172</t>
   </si>
   <si>
     <t xml:space="preserve">69.9444198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1703491210938</t>
+    <t xml:space="preserve">70.1703414916992</t>
   </si>
   <si>
     <t xml:space="preserve">71.887336730957</t>
@@ -1070,97 +1070,97 @@
     <t xml:space="preserve">69.8992462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4985427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4081649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2785797119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6400604248047</t>
+    <t xml:space="preserve">68.4985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4081802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2785873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
     <t xml:space="preserve">69.402214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3391723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969512939453</t>
+    <t xml:space="preserve">72.3391571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969589233398</t>
   </si>
   <si>
     <t xml:space="preserve">71.6162261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9324951171875</t>
+    <t xml:space="preserve">71.932502746582</t>
   </si>
   <si>
     <t xml:space="preserve">72.0228729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7065887451172</t>
+    <t xml:space="preserve">71.7065963745117</t>
   </si>
   <si>
     <t xml:space="preserve">71.4806671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4354934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6614074707031</t>
+    <t xml:space="preserve">71.4354782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6614227294922</t>
   </si>
   <si>
     <t xml:space="preserve">71.2547454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8088836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7517776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9623107910156</t>
+    <t xml:space="preserve">69.8088760375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7517852783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9623031616211</t>
   </si>
   <si>
     <t xml:space="preserve">62.8505821228027</t>
   </si>
   <si>
-    <t xml:space="preserve">64.3416442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572326660156</t>
+    <t xml:space="preserve">64.3416366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572288513184</t>
   </si>
   <si>
     <t xml:space="preserve">63.6187057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0764999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9409332275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.7602081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9017219543457</t>
+    <t xml:space="preserve">63.076488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9409523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.7602195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017143249512</t>
   </si>
   <si>
     <t xml:space="preserve">60.0040016174316</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7329063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8624877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8113555908203</t>
+    <t xml:space="preserve">59.7328948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8625030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8113632202148</t>
   </si>
   <si>
     <t xml:space="preserve">63.7994384765625</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">67.5496826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">66.7363815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8838424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6519775390625</t>
+    <t xml:space="preserve">66.7363739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8838500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.651985168457</t>
   </si>
   <si>
     <t xml:space="preserve">65.2905044555664</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">70.1251449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8600158691406</t>
+    <t xml:space="preserve">68.8600082397461</t>
   </si>
   <si>
     <t xml:space="preserve">69.8540573120117</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">70.622184753418</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1191940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0740203857422</t>
+    <t xml:space="preserve">71.1192016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0740127563477</t>
   </si>
   <si>
     <t xml:space="preserve">72.6554489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">73.694694519043</t>
+    <t xml:space="preserve">73.6946792602539</t>
   </si>
   <si>
     <t xml:space="preserve">72.4747161865234</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">73.4687576293945</t>
   </si>
   <si>
-    <t xml:space="preserve">73.1976547241211</t>
+    <t xml:space="preserve">73.1976470947266</t>
   </si>
   <si>
     <t xml:space="preserve">73.3783874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">74.688720703125</t>
+    <t xml:space="preserve">74.6887130737305</t>
   </si>
   <si>
     <t xml:space="preserve">73.5591278076172</t>
@@ -1238,73 +1238,73 @@
     <t xml:space="preserve">74.7919616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6961059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.928955078125</t>
+    <t xml:space="preserve">73.6960983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9289398193359</t>
   </si>
   <si>
     <t xml:space="preserve">76.8466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">75.796501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.152702331543</t>
+    <t xml:space="preserve">75.7964859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">77.2576293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">75.4312133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9059371948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5908432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3625411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7278366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2712249755859</t>
+    <t xml:space="preserve">75.4312057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0795211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9059448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5908584594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3625335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7278213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2712173461914</t>
   </si>
   <si>
     <t xml:space="preserve">81.2300872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1021881103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3806686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2482223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.928596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2893524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0564956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4127349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6682281494141</t>
+    <t xml:space="preserve">83.1021728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3806762695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2482070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.9286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2893676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.056510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7323608398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4127426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6682357788086</t>
   </si>
   <si>
     <t xml:space="preserve">86.8006820678711</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">88.8554077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9878540039062</t>
+    <t xml:space="preserve">87.9878616333008</t>
   </si>
   <si>
     <t xml:space="preserve">89.2206802368164</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9421997070312</t>
+    <t xml:space="preserve">87.9421920776367</t>
   </si>
   <si>
     <t xml:space="preserve">89.0380477905273</t>
@@ -1334,58 +1334,58 @@
     <t xml:space="preserve">87.2572860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">87.4855728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.576904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6772918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1750335693359</t>
+    <t xml:space="preserve">87.485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5769195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6772994995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1750411987305</t>
   </si>
   <si>
     <t xml:space="preserve">89.4033279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1248397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.62255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3531341552734</t>
+    <t xml:space="preserve">88.1248321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6225662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.353141784668</t>
   </si>
   <si>
     <t xml:space="preserve">86.2984161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">85.8418045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1614303588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4263381958008</t>
+    <t xml:space="preserve">85.8418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1614379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4263229370117</t>
   </si>
   <si>
     <t xml:space="preserve">84.4719924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">83.8327560424805</t>
+    <t xml:space="preserve">83.8327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">77.668571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7689666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474472045898</t>
+    <t xml:space="preserve">79.7689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474395751953</t>
   </si>
   <si>
     <t xml:space="preserve">80.2255706787109</t>
@@ -1394,40 +1394,40 @@
     <t xml:space="preserve">80.4538650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">79.358024597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4995269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.0383911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3123397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1112442016602</t>
+    <t xml:space="preserve">79.3580093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4995193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0383834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.3123550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1112365722656</t>
   </si>
   <si>
     <t xml:space="preserve">85.6135025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">83.5587921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6501007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2391586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7414169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.837272644043</t>
+    <t xml:space="preserve">83.5587768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6501083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2391662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7414093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8372802734375</t>
   </si>
   <si>
     <t xml:space="preserve">85.6591644287109</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">81.6410369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9149932861328</t>
+    <t xml:space="preserve">81.9150009155273</t>
   </si>
   <si>
     <t xml:space="preserve">81.0017929077148</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">82.8282089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5312576293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.7640762329102</t>
+    <t xml:space="preserve">87.5312423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.7640838623047</t>
   </si>
   <si>
     <t xml:space="preserve">84.2436904907227</t>
   </si>
   <si>
-    <t xml:space="preserve">85.019905090332</t>
+    <t xml:space="preserve">85.0199203491211</t>
   </si>
   <si>
     <t xml:space="preserve">84.8829345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">82.7369003295898</t>
+    <t xml:space="preserve">82.7368927001953</t>
   </si>
   <si>
     <t xml:space="preserve">83.3761444091797</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">81.4583969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.2666931152344</t>
+    <t xml:space="preserve">79.2667007446289</t>
   </si>
   <si>
     <t xml:space="preserve">75.1572494506836</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">74.4266662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8376159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6002502441406</t>
+    <t xml:space="preserve">73.3308181762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8376007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6002578735352</t>
   </si>
   <si>
     <t xml:space="preserve">72.9198684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">74.5179977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.8832702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.2485656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.4357223510742</t>
+    <t xml:space="preserve">74.5180053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.8832778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.2485733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.4357299804688</t>
   </si>
   <si>
     <t xml:space="preserve">72.8285598754883</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">73.9700622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">75.06591796875</t>
+    <t xml:space="preserve">75.0659255981445</t>
   </si>
   <si>
     <t xml:space="preserve">76.5270614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9515991210938</t>
+    <t xml:space="preserve">79.9516067504883</t>
   </si>
   <si>
     <t xml:space="preserve">75.3398895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">76.1161193847656</t>
+    <t xml:space="preserve">76.1161270141602</t>
   </si>
   <si>
     <t xml:space="preserve">73.0568618774414</t>
@@ -1547,49 +1547,49 @@
     <t xml:space="preserve">70.6825103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0934600830078</t>
+    <t xml:space="preserve">71.0934524536133</t>
   </si>
   <si>
     <t xml:space="preserve">71.9610137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">73.1025238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3262786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0477828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8651504516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5821304321289</t>
+    <t xml:space="preserve">73.1025161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3262939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8651428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5821151733398</t>
   </si>
   <si>
     <t xml:space="preserve">68.4908065795898</t>
   </si>
   <si>
-    <t xml:space="preserve">68.856086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3217544555664</t>
+    <t xml:space="preserve">68.8560943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">66.8013687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3949584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.938346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6187210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5775985717773</t>
+    <t xml:space="preserve">67.3949508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9383544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6187286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5775909423828</t>
   </si>
   <si>
     <t xml:space="preserve">66.8470153808594</t>
@@ -1598,37 +1598,37 @@
     <t xml:space="preserve">65.5228729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0160751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4270248413086</t>
+    <t xml:space="preserve">64.0160675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4270172119141</t>
   </si>
   <si>
     <t xml:space="preserve">64.2900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7923049926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1621170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.944694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2089462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.6771774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3025894165039</t>
+    <t xml:space="preserve">64.7922897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1621246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.9446868896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2089385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.6771697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3025970458984</t>
   </si>
   <si>
     <t xml:space="preserve">70.0016708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4866104125977</t>
+    <t xml:space="preserve">69.4866027832031</t>
   </si>
   <si>
     <t xml:space="preserve">69.2056655883789</t>
@@ -1637,34 +1637,34 @@
     <t xml:space="preserve">69.6270751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">70.750862121582</t>
+    <t xml:space="preserve">70.7508544921875</t>
   </si>
   <si>
     <t xml:space="preserve">70.1421508789062</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675552368164</t>
+    <t xml:space="preserve">69.7675628662109</t>
   </si>
   <si>
     <t xml:space="preserve">70.8913192749023</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5769882202148</t>
+    <t xml:space="preserve">72.5769958496094</t>
   </si>
   <si>
     <t xml:space="preserve">73.0452194213867</t>
   </si>
   <si>
-    <t xml:space="preserve">75.2459411621094</t>
+    <t xml:space="preserve">75.2459487915039</t>
   </si>
   <si>
     <t xml:space="preserve">75.1054763793945</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9650039672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.5904159545898</t>
+    <t xml:space="preserve">74.9649963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.5904083251953</t>
   </si>
   <si>
     <t xml:space="preserve">75.0586547851562</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">74.6840591430664</t>
   </si>
   <si>
-    <t xml:space="preserve">76.557014465332</t>
+    <t xml:space="preserve">76.5570068359375</t>
   </si>
   <si>
     <t xml:space="preserve">76.1355972290039</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">74.8713531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8847808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9784240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7109069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.6172561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.694206237793</t>
+    <t xml:space="preserve">76.8847885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7109146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6172714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.6942138671875</t>
   </si>
   <si>
     <t xml:space="preserve">79.2727966308594</t>
@@ -1709,64 +1709,64 @@
     <t xml:space="preserve">79.2259750366211</t>
   </si>
   <si>
-    <t xml:space="preserve">79.4132843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7878570556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0219802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.038688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8815078735352</t>
+    <t xml:space="preserve">79.4132766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7878646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.02197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0386810302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">80.6775131225586</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3029251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7711563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0354156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.707633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3330383300781</t>
+    <t xml:space="preserve">80.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7711639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0354080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7076416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3798675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3330459594727</t>
   </si>
   <si>
     <t xml:space="preserve">81.2393951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2227020263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.145751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9751510620117</t>
+    <t xml:space="preserve">82.2227096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1457595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9751663208008</t>
   </si>
   <si>
     <t xml:space="preserve">82.2695236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5036468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0186996459961</t>
+    <t xml:space="preserve">82.5036392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0187149047852</t>
   </si>
   <si>
     <t xml:space="preserve">83.2528305053711</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">82.9250564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6742477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9718933105469</t>
+    <t xml:space="preserve">83.6742401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9718780517578</t>
   </si>
   <si>
     <t xml:space="preserve">84.048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">84.0019989013672</t>
+    <t xml:space="preserve">84.0020065307617</t>
   </si>
   <si>
     <t xml:space="preserve">84.7980194091797</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">86.1559066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">85.8281402587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6876754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2194366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1257858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6408309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.0822296142578</t>
+    <t xml:space="preserve">85.8281326293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2194290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1257781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6408462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0822372436523</t>
   </si>
   <si>
     <t xml:space="preserve">79.7410354614258</t>
@@ -1826,49 +1826,49 @@
     <t xml:space="preserve">81.5671615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">81.8481140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8147125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1893005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2829437255859</t>
+    <t xml:space="preserve">81.8481216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8147201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1893081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2829513549805</t>
   </si>
   <si>
     <t xml:space="preserve">85.3130722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1693344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4804000854492</t>
+    <t xml:space="preserve">88.1693267822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4804077148438</t>
   </si>
   <si>
     <t xml:space="preserve">91.2597045898438</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2128829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6854858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1580963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.5437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8347930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5984954833984</t>
+    <t xml:space="preserve">91.212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6855010986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5437088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5984878540039</t>
   </si>
   <si>
     <t xml:space="preserve">89.1806793212891</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">88.3299789428711</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8025817871094</t>
+    <t xml:space="preserve">88.8025970458984</t>
   </si>
   <si>
     <t xml:space="preserve">86.5340881347656</t>
@@ -1886,43 +1886,43 @@
     <t xml:space="preserve">90.0786361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3546676635742</t>
+    <t xml:space="preserve">91.3546600341797</t>
   </si>
   <si>
     <t xml:space="preserve">91.9690551757812</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1033096313477</t>
+    <t xml:space="preserve">93.1033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">95.5608520507812</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4115524291992</t>
+    <t xml:space="preserve">96.4115600585938</t>
   </si>
   <si>
     <t xml:space="preserve">93.8122177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0731964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8293609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3416976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.326644897461</t>
+    <t xml:space="preserve">97.0731811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3417053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.326637268066</t>
   </si>
   <si>
     <t xml:space="preserve">98.6800537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">99.247184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.8841552734375</t>
+    <t xml:space="preserve">99.2471771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.884147644043</t>
   </si>
   <si>
     <t xml:space="preserve">97.6403274536133</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">96.5060577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2622375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.9786605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5307540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3019714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.3567657470703</t>
+    <t xml:space="preserve">97.2622451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9786682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3019790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3567733764648</t>
   </si>
   <si>
     <t xml:space="preserve">98.2074508666992</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">97.167724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">97.5457916259766</t>
+    <t xml:space="preserve">97.5458068847656</t>
   </si>
   <si>
     <t xml:space="preserve">96.2225112915039</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">95.7499008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8444290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4663314819336</t>
+    <t xml:space="preserve">95.8444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4663391113281</t>
   </si>
   <si>
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082801818848</t>
+    <t xml:space="preserve">102.082817077637</t>
   </si>
   <si>
     <t xml:space="preserve">100.475959777832</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">99.1526718139648</t>
   </si>
   <si>
-    <t xml:space="preserve">101.799247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.664993286133</t>
+    <t xml:space="preserve">101.799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.665000915527</t>
   </si>
   <si>
     <t xml:space="preserve">100.097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9088134765625</t>
+    <t xml:space="preserve">99.9088287353516</t>
   </si>
   <si>
     <t xml:space="preserve">98.396484375</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">100.003349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">101.137603759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.704727172852</t>
+    <t xml:space="preserve">101.137596130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.704719543457</t>
   </si>
   <si>
     <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">103.500633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.933502197266</t>
+    <t xml:space="preserve">103.500625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.93350982666</t>
   </si>
   <si>
     <t xml:space="preserve">100.381423950195</t>
@@ -2039,28 +2039,28 @@
     <t xml:space="preserve">98.5855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">96.6951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.112922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0581359863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.948570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.286903381348</t>
+    <t xml:space="preserve">96.6951065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1129379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0581436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.94856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.286911010742</t>
   </si>
   <si>
     <t xml:space="preserve">99.7197799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">100.854034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6252746582031</t>
+    <t xml:space="preserve">100.854042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6252593994141</t>
   </si>
   <si>
     <t xml:space="preserve">94.4266128540039</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">94.7101669311523</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8594741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0957870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2848281860352</t>
+    <t xml:space="preserve">93.8594818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0957794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2848205566406</t>
   </si>
   <si>
     <t xml:space="preserve">94.6156463623047</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">91.6382293701172</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3471374511719</t>
+    <t xml:space="preserve">92.3471221923828</t>
   </si>
   <si>
     <t xml:space="preserve">91.3074111938477</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">91.7327499389648</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0163116455078</t>
+    <t xml:space="preserve">92.0163192749023</t>
   </si>
   <si>
     <t xml:space="preserve">93.1505737304688</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3718109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8690948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9238891601562</t>
+    <t xml:space="preserve">95.3718185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8046951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8690872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.9238815307617</t>
   </si>
   <si>
     <t xml:space="preserve">100.75951385498</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">103.122543334961</t>
   </si>
   <si>
-    <t xml:space="preserve">104.634880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.958183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.659553527832</t>
+    <t xml:space="preserve">104.634887695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.95817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.226676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.659561157227</t>
   </si>
   <si>
     <t xml:space="preserve">109.077377319336</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">112.574661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">113.803436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236305236816</t>
+    <t xml:space="preserve">113.803428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.236312866211</t>
   </si>
   <si>
     <t xml:space="preserve">113.519866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">114.65412902832</t>
+    <t xml:space="preserve">114.654121398926</t>
   </si>
   <si>
     <t xml:space="preserve">111.818489074707</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">115.977416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">117.206192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.017158508301</t>
+    <t xml:space="preserve">117.206184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.017150878906</t>
   </si>
   <si>
     <t xml:space="preserve">115.315773010254</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">114.370559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">113.425354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.644500732422</t>
+    <t xml:space="preserve">113.425346374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.644508361816</t>
   </si>
   <si>
     <t xml:space="preserve">111.251365661621</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">110.30615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">111.156837463379</t>
+    <t xml:space="preserve">111.156845092773</t>
   </si>
   <si>
     <t xml:space="preserve">111.723968505859</t>
   </si>
   <si>
-    <t xml:space="preserve">111.062316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.117111206055</t>
+    <t xml:space="preserve">111.06233215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.11710357666</t>
   </si>
   <si>
     <t xml:space="preserve">109.833541870117</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">110.873275756836</t>
   </si>
   <si>
-    <t xml:space="preserve">109.455459594727</t>
+    <t xml:space="preserve">109.455474853516</t>
   </si>
   <si>
     <t xml:space="preserve">107.470520019531</t>
@@ -2231,31 +2231,31 @@
     <t xml:space="preserve">108.037651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">107.848594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.793823242188</t>
+    <t xml:space="preserve">107.848602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.793807983398</t>
   </si>
   <si>
     <t xml:space="preserve">106.430786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">109.171897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.266410827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.997917175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.918441772461</t>
+    <t xml:space="preserve">109.171890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.266426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.997901916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.918449401855</t>
   </si>
   <si>
     <t xml:space="preserve">105.769142150879</t>
   </si>
   <si>
-    <t xml:space="preserve">107.754081726074</t>
+    <t xml:space="preserve">107.754089355469</t>
   </si>
   <si>
     <t xml:space="preserve">108.415725708008</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">110.211631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">114.276039123535</t>
+    <t xml:space="preserve">114.276031494141</t>
   </si>
   <si>
     <t xml:space="preserve">114.46508026123</t>
   </si>
   <si>
-    <t xml:space="preserve">109.928070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.540351867676</t>
+    <t xml:space="preserve">109.928062438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.54035949707</t>
   </si>
   <si>
     <t xml:space="preserve">98.7745742797852</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">101.893783569336</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8143005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.13215637207</t>
+    <t xml:space="preserve">99.8142929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.132171630859</t>
   </si>
   <si>
     <t xml:space="preserve">105.485572814941</t>
   </si>
   <si>
-    <t xml:space="preserve">110.400680541992</t>
+    <t xml:space="preserve">110.400672912598</t>
   </si>
   <si>
     <t xml:space="preserve">108.888336181641</t>
@@ -2309,34 +2309,34 @@
     <t xml:space="preserve">106.52530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">104.445831298828</t>
+    <t xml:space="preserve">104.445838928223</t>
   </si>
   <si>
     <t xml:space="preserve">102.55541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">114.086990356445</t>
+    <t xml:space="preserve">114.08699798584</t>
   </si>
   <si>
     <t xml:space="preserve">111.629447937012</t>
   </si>
   <si>
-    <t xml:space="preserve">118.05687713623</t>
+    <t xml:space="preserve">118.05689239502</t>
   </si>
   <si>
     <t xml:space="preserve">122.310325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">126.091171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.32958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.592666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.876205444336</t>
+    <t xml:space="preserve">126.091163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.329574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.592651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.876220703125</t>
   </si>
   <si>
     <t xml:space="preserve">136.583038330078</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">155.959854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">150.383117675781</t>
+    <t xml:space="preserve">150.38313293457</t>
   </si>
   <si>
     <t xml:space="preserve">153.691360473633</t>
   </si>
   <si>
-    <t xml:space="preserve">157.755767822266</t>
+    <t xml:space="preserve">157.755752563477</t>
   </si>
   <si>
     <t xml:space="preserve">157.94482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">153.313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791320800781</t>
+    <t xml:space="preserve">153.313232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.791305541992</t>
   </si>
   <si>
     <t xml:space="preserve">146.885833740234</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">144.522796630859</t>
   </si>
   <si>
-    <t xml:space="preserve">146.318710327148</t>
+    <t xml:space="preserve">146.318695068359</t>
   </si>
   <si>
     <t xml:space="preserve">147.641998291016</t>
@@ -2387,67 +2387,67 @@
     <t xml:space="preserve">153.596832275391</t>
   </si>
   <si>
-    <t xml:space="preserve">151.706390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.048934936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.302368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.10791015625</t>
+    <t xml:space="preserve">151.706405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.048950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.302398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.107925415039</t>
   </si>
   <si>
     <t xml:space="preserve">174.675048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">169.381866455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.833984375</t>
+    <t xml:space="preserve">169.3818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.833953857422</t>
   </si>
   <si>
     <t xml:space="preserve">180.440811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">191.688858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.927230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.206619262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.521545410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.839416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.172302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.55583190918</t>
+    <t xml:space="preserve">191.688842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.927215576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.206604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.521530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.172317504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.555847167969</t>
   </si>
   <si>
     <t xml:space="preserve">169.098297119141</t>
   </si>
   <si>
-    <t xml:space="preserve">163.994155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.655776977539</t>
+    <t xml:space="preserve">163.994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.655792236328</t>
   </si>
   <si>
     <t xml:space="preserve">156.905059814453</t>
   </si>
   <si>
-    <t xml:space="preserve">150.855712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.651596069336</t>
+    <t xml:space="preserve">150.855728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.651611328125</t>
   </si>
   <si>
     <t xml:space="preserve">155.014633178711</t>
@@ -2456,31 +2456,31 @@
     <t xml:space="preserve">158.606430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">157.850280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.510162353516</t>
+    <t xml:space="preserve">157.85026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.510147094727</t>
   </si>
   <si>
     <t xml:space="preserve">162.365707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">161.890411376953</t>
+    <t xml:space="preserve">161.890396118164</t>
   </si>
   <si>
     <t xml:space="preserve">161.129913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">159.133590698242</t>
+    <t xml:space="preserve">159.133605957031</t>
   </si>
   <si>
     <t xml:space="preserve">162.270645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">167.11882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.457077026367</t>
+    <t xml:space="preserve">167.118804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.457061767578</t>
   </si>
   <si>
     <t xml:space="preserve">162.936065673828</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">161.320037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">161.985443115234</t>
+    <t xml:space="preserve">161.985458374023</t>
   </si>
   <si>
     <t xml:space="preserve">162.55583190918</t>
@@ -2504,28 +2504,28 @@
     <t xml:space="preserve">166.073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">169.685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.350921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.031143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.361999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.122512817383</t>
+    <t xml:space="preserve">169.685485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.35090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.031127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.362014770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.122497558594</t>
   </si>
   <si>
     <t xml:space="preserve">164.647186279297</t>
   </si>
   <si>
-    <t xml:space="preserve">169.305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.400283813477</t>
+    <t xml:space="preserve">169.305252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.400299072266</t>
   </si>
   <si>
     <t xml:space="preserve">171.96696472168</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">169.495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">166.358306884766</t>
+    <t xml:space="preserve">166.358322143555</t>
   </si>
   <si>
     <t xml:space="preserve">160.939804077148</t>
   </si>
   <si>
-    <t xml:space="preserve">154.66569519043</t>
+    <t xml:space="preserve">154.665710449219</t>
   </si>
   <si>
     <t xml:space="preserve">162.175582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">164.742248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.228668212891</t>
+    <t xml:space="preserve">164.742263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.22868347168</t>
   </si>
   <si>
     <t xml:space="preserve">157.802749633789</t>
@@ -2558,28 +2558,28 @@
     <t xml:space="preserve">152.669403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">149.817535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.77555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.768157958984</t>
+    <t xml:space="preserve">149.81755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.775543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.768188476562</t>
   </si>
   <si>
     <t xml:space="preserve">145.25456237793</t>
   </si>
   <si>
-    <t xml:space="preserve">149.72248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.289154052734</t>
+    <t xml:space="preserve">149.722473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.289138793945</t>
   </si>
   <si>
     <t xml:space="preserve">151.623718261719</t>
   </si>
   <si>
-    <t xml:space="preserve">148.391632080078</t>
+    <t xml:space="preserve">148.3916015625</t>
   </si>
   <si>
     <t xml:space="preserve">154.760772705078</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">151.24348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">154.190399169922</t>
+    <t xml:space="preserve">154.190383911133</t>
   </si>
   <si>
     <t xml:space="preserve">154.855819702148</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">155.426208496094</t>
+    <t xml:space="preserve">155.426193237305</t>
   </si>
   <si>
     <t xml:space="preserve">155.806427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">159.41877746582</t>
+    <t xml:space="preserve">159.418792724609</t>
   </si>
   <si>
     <t xml:space="preserve">145.634811401367</t>
@@ -2612,28 +2612,28 @@
     <t xml:space="preserve">138.600250244141</t>
   </si>
   <si>
-    <t xml:space="preserve">144.018768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.589141845703</t>
+    <t xml:space="preserve">144.018783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.589126586914</t>
   </si>
   <si>
     <t xml:space="preserve">143.543472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">135.558288574219</t>
+    <t xml:space="preserve">135.55827331543</t>
   </si>
   <si>
     <t xml:space="preserve">134.797775268555</t>
   </si>
   <si>
-    <t xml:space="preserve">137.364440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.17431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.779266357422</t>
+    <t xml:space="preserve">137.36442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.779251098633</t>
   </si>
   <si>
     <t xml:space="preserve">143.258285522461</t>
@@ -2645,40 +2645,40 @@
     <t xml:space="preserve">147.726181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.247177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.95458984375</t>
+    <t xml:space="preserve">149.247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.954574584961</t>
   </si>
   <si>
     <t xml:space="preserve">150.387908935547</t>
   </si>
   <si>
-    <t xml:space="preserve">161.034851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.65461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.080505371094</t>
+    <t xml:space="preserve">161.03483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.654602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.080535888672</t>
   </si>
   <si>
     <t xml:space="preserve">161.795333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">163.411392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.069442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.913879394531</t>
+    <t xml:space="preserve">163.411376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.91389465332</t>
   </si>
   <si>
     <t xml:space="preserve">175.294128417969</t>
   </si>
   <si>
-    <t xml:space="preserve">177.670669555664</t>
+    <t xml:space="preserve">177.670684814453</t>
   </si>
   <si>
     <t xml:space="preserve">173.48796081543</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">178.716354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">180.712677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.24104309082</t>
+    <t xml:space="preserve">180.712661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.241058349609</t>
   </si>
   <si>
     <t xml:space="preserve">181.853393554688</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">184.990447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">184.039840698242</t>
+    <t xml:space="preserve">184.039825439453</t>
   </si>
   <si>
     <t xml:space="preserve">181.663284301758</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">183.089218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">181.568222045898</t>
+    <t xml:space="preserve">181.568206787109</t>
   </si>
   <si>
     <t xml:space="preserve">179.286727905273</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">178.050933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">179.191650390625</t>
+    <t xml:space="preserve">179.191665649414</t>
   </si>
   <si>
     <t xml:space="preserve">176.529937744141</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">177.860824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">184.61018371582</t>
+    <t xml:space="preserve">184.610198974609</t>
   </si>
   <si>
     <t xml:space="preserve">189.838607788086</t>
@@ -2744,19 +2744,19 @@
     <t xml:space="preserve">159.703979492188</t>
   </si>
   <si>
-    <t xml:space="preserve">163.886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.217559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.932388305664</t>
+    <t xml:space="preserve">163.886703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.217575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.932373046875</t>
   </si>
   <si>
     <t xml:space="preserve">164.07682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">156.947189331055</t>
+    <t xml:space="preserve">156.947204589844</t>
   </si>
   <si>
     <t xml:space="preserve">160.8447265625</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">163.696563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">161.605224609375</t>
+    <t xml:space="preserve">161.605209350586</t>
   </si>
   <si>
     <t xml:space="preserve">160.084228515625</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">162.745956420898</t>
   </si>
   <si>
-    <t xml:space="preserve">160.179290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.32373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.468185424805</t>
+    <t xml:space="preserve">160.179306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.323745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.468200683594</t>
   </si>
   <si>
     <t xml:space="preserve">158.848449707031</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">163.221267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">159.038543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.608901977539</t>
+    <t xml:space="preserve">159.038558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.608932495117</t>
   </si>
   <si>
     <t xml:space="preserve">161.700286865234</t>
@@ -2807,40 +2807,40 @@
     <t xml:space="preserve">161.224975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">153.810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.859527587891</t>
+    <t xml:space="preserve">153.810134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.85954284668</t>
   </si>
   <si>
     <t xml:space="preserve">151.528656005859</t>
   </si>
   <si>
-    <t xml:space="preserve">155.616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.4755859375</t>
+    <t xml:space="preserve">155.616302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.475570678711</t>
   </si>
   <si>
     <t xml:space="preserve">154.570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">157.992889404297</t>
+    <t xml:space="preserve">157.992874145508</t>
   </si>
   <si>
     <t xml:space="preserve">170.826217651367</t>
   </si>
   <si>
-    <t xml:space="preserve">169.970657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.001541137695</t>
+    <t xml:space="preserve">169.970672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.001556396484</t>
   </si>
   <si>
     <t xml:space="preserve">168.92497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">171.681777954102</t>
+    <t xml:space="preserve">171.681793212891</t>
   </si>
   <si>
     <t xml:space="preserve">171.111419677734</t>
@@ -2849,46 +2849,46 @@
     <t xml:space="preserve">170.541030883789</t>
   </si>
   <si>
-    <t xml:space="preserve">167.784255981445</t>
+    <t xml:space="preserve">167.784240722656</t>
   </si>
   <si>
     <t xml:space="preserve">167.499069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.868194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.202758789062</t>
+    <t xml:space="preserve">170.255844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.868209838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.202774047852</t>
   </si>
   <si>
     <t xml:space="preserve">175.389205932617</t>
   </si>
   <si>
-    <t xml:space="preserve">176.43489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.149703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.195388793945</t>
+    <t xml:space="preserve">176.434875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.195373535156</t>
   </si>
   <si>
     <t xml:space="preserve">174.438583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">156.18669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.813842773438</t>
+    <t xml:space="preserve">156.186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.813827514648</t>
   </si>
   <si>
     <t xml:space="preserve">155.996566772461</t>
   </si>
   <si>
-    <t xml:space="preserve">154.380508422852</t>
+    <t xml:space="preserve">154.380523681641</t>
   </si>
   <si>
     <t xml:space="preserve">155.901504516602</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">157.137329101562</t>
   </si>
   <si>
-    <t xml:space="preserve">154.000274658203</t>
+    <t xml:space="preserve">154.000259399414</t>
   </si>
   <si>
     <t xml:space="preserve">150.197784423828</t>
@@ -2909,19 +2909,19 @@
     <t xml:space="preserve">147.155807495117</t>
   </si>
   <si>
-    <t xml:space="preserve">132.706405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.082962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.695297241211</t>
+    <t xml:space="preserve">132.706420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.082946777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.695281982422</t>
   </si>
   <si>
     <t xml:space="preserve">134.987899780273</t>
   </si>
   <si>
-    <t xml:space="preserve">133.181701660156</t>
+    <t xml:space="preserve">133.181716918945</t>
   </si>
   <si>
     <t xml:space="preserve">136.033569335938</t>
@@ -2930,31 +2930,31 @@
     <t xml:space="preserve">133.276763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">134.037261962891</t>
+    <t xml:space="preserve">134.03727722168</t>
   </si>
   <si>
     <t xml:space="preserve">133.086654663086</t>
   </si>
   <si>
-    <t xml:space="preserve">135.273086547852</t>
+    <t xml:space="preserve">135.273056030273</t>
   </si>
   <si>
     <t xml:space="preserve">132.136032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">130.519973754883</t>
+    <t xml:space="preserve">130.519989013672</t>
   </si>
   <si>
     <t xml:space="preserve">130.90022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">130.044662475586</t>
+    <t xml:space="preserve">130.044677734375</t>
   </si>
   <si>
     <t xml:space="preserve">132.848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">135.46321105957</t>
+    <t xml:space="preserve">135.463195800781</t>
   </si>
   <si>
     <t xml:space="preserve">133.229248046875</t>
@@ -2963,52 +2963,52 @@
     <t xml:space="preserve">145.492233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">143.59098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.784790039062</t>
+    <t xml:space="preserve">143.591003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.784805297852</t>
   </si>
   <si>
     <t xml:space="preserve">148.201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">148.058898925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.300231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.01692199707</t>
+    <t xml:space="preserve">148.05891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.300247192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.016937255859</t>
   </si>
   <si>
     <t xml:space="preserve">144.874313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">136.984176635742</t>
+    <t xml:space="preserve">136.984191894531</t>
   </si>
   <si>
     <t xml:space="preserve">136.794052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">133.324310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.274948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.894683837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.227386474609</t>
+    <t xml:space="preserve">133.324295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.274932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.89469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.227401733398</t>
   </si>
   <si>
     <t xml:space="preserve">131.660705566406</t>
   </si>
   <si>
-    <t xml:space="preserve">133.847152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.60578918457</t>
+    <t xml:space="preserve">133.84716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.605804443359</t>
   </si>
   <si>
     <t xml:space="preserve">131.423065185547</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">128.333541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">131.470596313477</t>
+    <t xml:space="preserve">131.470581054688</t>
   </si>
   <si>
     <t xml:space="preserve">131.185424804688</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">134.655181884766</t>
   </si>
   <si>
-    <t xml:space="preserve">136.889114379883</t>
+    <t xml:space="preserve">136.889129638672</t>
   </si>
   <si>
     <t xml:space="preserve">137.031707763672</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">137.845397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">137.797515869141</t>
+    <t xml:space="preserve">137.797500610352</t>
   </si>
   <si>
     <t xml:space="preserve">138.084701538086</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">138.46760559082</t>
   </si>
   <si>
-    <t xml:space="preserve">135.978729248047</t>
+    <t xml:space="preserve">135.978744506836</t>
   </si>
   <si>
     <t xml:space="preserve">133.059097290039</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">136.218063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.659057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.185562133789</t>
+    <t xml:space="preserve">136.218032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.510345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.659072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.185546875</t>
   </si>
   <si>
     <t xml:space="preserve">143.2060546875</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">144.306884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">144.01969909668</t>
+    <t xml:space="preserve">144.019714355469</t>
   </si>
   <si>
     <t xml:space="preserve">146.269287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">145.790649414062</t>
+    <t xml:space="preserve">145.790634155273</t>
   </si>
   <si>
     <t xml:space="preserve">147.322250366211</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">143.397506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">147.992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.428237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.289749145508</t>
+    <t xml:space="preserve">147.99235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.42822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.289764404297</t>
   </si>
   <si>
     <t xml:space="preserve">153.065811157227</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">151.534210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">149.906860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.879501342773</t>
+    <t xml:space="preserve">149.906875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.879486083984</t>
   </si>
   <si>
     <t xml:space="preserve">156.320495605469</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">152.395721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">153.783752441406</t>
+    <t xml:space="preserve">153.783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">155.123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">155.458953857422</t>
+    <t xml:space="preserve">155.458969116211</t>
   </si>
   <si>
     <t xml:space="preserve">155.028198242188</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">155.650421142578</t>
   </si>
   <si>
-    <t xml:space="preserve">156.081192016602</t>
+    <t xml:space="preserve">156.081207275391</t>
   </si>
   <si>
     <t xml:space="preserve">158.905090332031</t>
   </si>
   <si>
-    <t xml:space="preserve">160.149551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.207656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.643524169922</t>
+    <t xml:space="preserve">160.149536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.207641601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.643539428711</t>
   </si>
   <si>
     <t xml:space="preserve">164.983703613281</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">161.729019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">160.91535949707</t>
+    <t xml:space="preserve">160.915344238281</t>
   </si>
   <si>
     <t xml:space="preserve">162.35124206543</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">165.07942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">163.834976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.908447265625</t>
+    <t xml:space="preserve">163.834991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.908462524414</t>
   </si>
   <si>
     <t xml:space="preserve">164.600799560547</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">168.142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">168.860580444336</t>
+    <t xml:space="preserve">168.860595703125</t>
   </si>
   <si>
     <t xml:space="preserve">166.036666870117</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">168.334106445312</t>
   </si>
   <si>
-    <t xml:space="preserve">169.052047729492</t>
+    <t xml:space="preserve">169.052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">170.248626708984</t>
   </si>
   <si>
-    <t xml:space="preserve">171.349487304688</t>
+    <t xml:space="preserve">171.349472045898</t>
   </si>
   <si>
     <t xml:space="preserve">176.040054321289</t>
   </si>
   <si>
-    <t xml:space="preserve">176.949432373047</t>
+    <t xml:space="preserve">176.949447631836</t>
   </si>
   <si>
     <t xml:space="preserve">177.140899658203</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">180.1083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">179.534057617188</t>
+    <t xml:space="preserve">179.534042358398</t>
   </si>
   <si>
     <t xml:space="preserve">178.05029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">177.475921630859</t>
+    <t xml:space="preserve">177.475936889648</t>
   </si>
   <si>
     <t xml:space="preserve">177.810989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">181.352844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.740859985352</t>
+    <t xml:space="preserve">181.352828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.740844726562</t>
   </si>
   <si>
     <t xml:space="preserve">184.990417480469</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">190.016036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">192.409194946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.270721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.568130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.643371582031</t>
+    <t xml:space="preserve">192.4091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.270706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.568145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.64338684082</t>
   </si>
   <si>
     <t xml:space="preserve">196.908309936523</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">196.812606811523</t>
   </si>
   <si>
-    <t xml:space="preserve">197.386962890625</t>
+    <t xml:space="preserve">197.386947631836</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">194.515167236328</t>
   </si>
   <si>
-    <t xml:space="preserve">187.479309082031</t>
+    <t xml:space="preserve">187.47932434082</t>
   </si>
   <si>
     <t xml:space="preserve">180.539184570312</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">174.987060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">174.077682495117</t>
+    <t xml:space="preserve">174.077667236328</t>
   </si>
   <si>
     <t xml:space="preserve">173.599044799805</t>
@@ -3332,28 +3332,28 @@
     <t xml:space="preserve">166.51530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">170.870849609375</t>
+    <t xml:space="preserve">170.870864868164</t>
   </si>
   <si>
     <t xml:space="preserve">171.253753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">172.402465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.684509277344</t>
+    <t xml:space="preserve">172.402481079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.684524536133</t>
   </si>
   <si>
     <t xml:space="preserve">173.742630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">177.715240478516</t>
+    <t xml:space="preserve">177.715225219727</t>
   </si>
   <si>
     <t xml:space="preserve">181.44856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">180.82633972168</t>
+    <t xml:space="preserve">180.826324462891</t>
   </si>
   <si>
     <t xml:space="preserve">182.884460449219</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">187.096389770508</t>
   </si>
   <si>
-    <t xml:space="preserve">187.000686645508</t>
+    <t xml:space="preserve">187.000671386719</t>
   </si>
   <si>
     <t xml:space="preserve">188.723739624023</t>
   </si>
   <si>
-    <t xml:space="preserve">189.202362060547</t>
+    <t xml:space="preserve">189.202377319336</t>
   </si>
   <si>
     <t xml:space="preserve">186.426330566406</t>
@@ -3383,37 +3383,37 @@
     <t xml:space="preserve">184.798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">174.699890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.231521606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.561401367188</t>
+    <t xml:space="preserve">174.699905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.231506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.561416625977</t>
   </si>
   <si>
     <t xml:space="preserve">177.093032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">179.964828491211</t>
+    <t xml:space="preserve">179.964813232422</t>
   </si>
   <si>
     <t xml:space="preserve">180.874206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">183.50666809082</t>
+    <t xml:space="preserve">183.506652832031</t>
   </si>
   <si>
     <t xml:space="preserve">175.896469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">176.61442565918</t>
+    <t xml:space="preserve">176.614410400391</t>
   </si>
   <si>
     <t xml:space="preserve">175.800704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">171.636657714844</t>
+    <t xml:space="preserve">171.636672973633</t>
   </si>
   <si>
     <t xml:space="preserve">169.865707397461</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">177.188766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">180.682754516602</t>
+    <t xml:space="preserve">180.682769775391</t>
   </si>
   <si>
     <t xml:space="preserve">175.082794189453</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">169.14778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">164.935836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.472564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.392227172852</t>
+    <t xml:space="preserve">164.935852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.472579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">172.306732177734</t>
   </si>
   <si>
-    <t xml:space="preserve">172.928955078125</t>
+    <t xml:space="preserve">172.928939819336</t>
   </si>
   <si>
     <t xml:space="preserve">168.764892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">172.785369873047</t>
+    <t xml:space="preserve">172.785385131836</t>
   </si>
   <si>
     <t xml:space="preserve">170.53581237793</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">152.060699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">153.688049316406</t>
+    <t xml:space="preserve">153.688034057617</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">160.293121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">156.22477722168</t>
+    <t xml:space="preserve">156.224761962891</t>
   </si>
   <si>
     <t xml:space="preserve">152.15641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">153.640167236328</t>
+    <t xml:space="preserve">153.640182495117</t>
   </si>
   <si>
     <t xml:space="preserve">148.183792114258</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">141.91374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">137.223159790039</t>
+    <t xml:space="preserve">137.223175048828</t>
   </si>
   <si>
     <t xml:space="preserve">138.946228027344</t>
@@ -3524,22 +3524,22 @@
     <t xml:space="preserve">140.717178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">128.94287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.884773254395</t>
+    <t xml:space="preserve">128.942886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.884757995605</t>
   </si>
   <si>
     <t xml:space="preserve">128.990753173828</t>
   </si>
   <si>
-    <t xml:space="preserve">129.325759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.144592285156</t>
+    <t xml:space="preserve">129.325790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.048843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.144577026367</t>
   </si>
   <si>
     <t xml:space="preserve">132.006088256836</t>
@@ -3548,22 +3548,22 @@
     <t xml:space="preserve">127.698425292969</t>
   </si>
   <si>
-    <t xml:space="preserve">125.975372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518989562988</t>
+    <t xml:space="preserve">125.975379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518997192383</t>
   </si>
   <si>
     <t xml:space="preserve">119.41813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">122.289909362793</t>
+    <t xml:space="preserve">122.289916992188</t>
   </si>
   <si>
     <t xml:space="preserve">120.662574768066</t>
   </si>
   <si>
-    <t xml:space="preserve">117.934387207031</t>
+    <t xml:space="preserve">117.934379577637</t>
   </si>
   <si>
     <t xml:space="preserve">114.631843566895</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">117.072853088379</t>
   </si>
   <si>
-    <t xml:space="preserve">116.546371459961</t>
+    <t xml:space="preserve">116.546363830566</t>
   </si>
   <si>
     <t xml:space="preserve">115.58910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">112.286560058594</t>
+    <t xml:space="preserve">112.286552429199</t>
   </si>
   <si>
     <t xml:space="preserve">112.430145263672</t>
@@ -3587,19 +3587,19 @@
     <t xml:space="preserve">116.211318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">120.136085510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.103591918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.864273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.937728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.124084472656</t>
+    <t xml:space="preserve">120.136093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.10359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.864288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.124099731445</t>
   </si>
   <si>
     <t xml:space="preserve">123.77367401123</t>
@@ -3629,25 +3629,25 @@
     <t xml:space="preserve">121.859153747559</t>
   </si>
   <si>
-    <t xml:space="preserve">131.718933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.29328918457</t>
+    <t xml:space="preserve">131.718948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.293273925781</t>
   </si>
   <si>
     <t xml:space="preserve">126.693321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">126.597595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.204444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.448883056641</t>
+    <t xml:space="preserve">126.597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.257438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.448890686035</t>
   </si>
   <si>
     <t xml:space="preserve">133.824905395508</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">139.329132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">139.616333007812</t>
+    <t xml:space="preserve">139.616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">142.105194091797</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">132.628326416016</t>
   </si>
   <si>
-    <t xml:space="preserve">129.038604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.086456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.559982299805</t>
+    <t xml:space="preserve">129.038619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.086471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.559967041016</t>
   </si>
   <si>
     <t xml:space="preserve">128.416381835938</t>
   </si>
   <si>
-    <t xml:space="preserve">126.45401763916</t>
+    <t xml:space="preserve">126.454002380371</t>
   </si>
   <si>
     <t xml:space="preserve">124.539482116699</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">118.652328491211</t>
   </si>
   <si>
-    <t xml:space="preserve">119.705322265625</t>
+    <t xml:space="preserve">119.70531463623</t>
   </si>
   <si>
     <t xml:space="preserve">118.173706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">117.64720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.392524719238</t>
+    <t xml:space="preserve">117.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.392532348633</t>
   </si>
   <si>
     <t xml:space="preserve">114.823295593262</t>
@@ -3728,19 +3728,19 @@
     <t xml:space="preserve">115.493385314941</t>
   </si>
   <si>
-    <t xml:space="preserve">109.271186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.590866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.654090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.165222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.009628295898</t>
+    <t xml:space="preserve">109.271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.590858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.654106140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.165214538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.009620666504</t>
   </si>
   <si>
     <t xml:space="preserve">114.871154785156</t>
@@ -6021,6 +6021,9 @@
   </si>
   <si>
     <t xml:space="preserve">64.3199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3199996948242</t>
   </si>
 </sst>
 </file>
@@ -72295,7 +72298,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6912384259</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>687923</v>
@@ -72316,6 +72319,32 @@
         <v>2002</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6939930556</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>637339</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>67.879997253418</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>63.6399993896484</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>64.379997253418</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>67.3199996948242</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>2003</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DIA.MI.xlsx
+++ b/data/DIA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="2006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="2005">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4954528808594</t>
+    <t xml:space="preserve">42.4954605102539</t>
   </si>
   <si>
     <t xml:space="preserve">DIA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2980880737305</t>
+    <t xml:space="preserve">43.2980918884277</t>
   </si>
   <si>
     <t xml:space="preserve">43.042308807373</t>
@@ -56,73 +56,73 @@
     <t xml:space="preserve">42.8218002319336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1514701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4689979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7281112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2871017456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9993515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2761039733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0765647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8384208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6443786621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9585800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2551422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2606353759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0544471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3664741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7777061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0687675476074</t>
+    <t xml:space="preserve">42.1514739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4690017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7281036376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2870979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9993476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2761001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0765609741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8384170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6443748474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2551345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2606430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0544509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3664817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.777702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0687713623047</t>
   </si>
   <si>
     <t xml:space="preserve">42.9982070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">41.878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2341728210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4172286987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7590370178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.014820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881309509277</t>
+    <t xml:space="preserve">41.8780479431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2341766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4172248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7590408325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0148162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.588134765625</t>
   </si>
   <si>
     <t xml:space="preserve">38.6057777404785</t>
@@ -131,31 +131,31 @@
     <t xml:space="preserve">38.4029121398926</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1228446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3962631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4932861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4017524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5483741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9397811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5924873352051</t>
+    <t xml:space="preserve">40.1228408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3962593078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4932823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4017639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5483856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9397888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5924797058105</t>
   </si>
   <si>
     <t xml:space="preserve">43.209888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9011840820312</t>
+    <t xml:space="preserve">42.9011878967285</t>
   </si>
   <si>
     <t xml:space="preserve">43.2275276184082</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">42.5571937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8074798583984</t>
+    <t xml:space="preserve">41.8074836730957</t>
   </si>
   <si>
     <t xml:space="preserve">42.6454010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7071418762207</t>
+    <t xml:space="preserve">42.7071342468262</t>
   </si>
   <si>
     <t xml:space="preserve">42.7600631713867</t>
@@ -191,37 +191,37 @@
     <t xml:space="preserve">40.5726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1581153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6200904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1140174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2904167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8405952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1316604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4668273925781</t>
+    <t xml:space="preserve">40.1581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6200866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1140213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.290412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8405914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1316566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4668312072754</t>
   </si>
   <si>
     <t xml:space="preserve">44.1007194519043</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7622375488281</t>
+    <t xml:space="preserve">44.7622337341309</t>
   </si>
   <si>
     <t xml:space="preserve">45.2914390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8647575378418</t>
+    <t xml:space="preserve">45.8647537231445</t>
   </si>
   <si>
     <t xml:space="preserve">45.3796424865723</t>
@@ -230,52 +230,52 @@
     <t xml:space="preserve">45.6883506774902</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8349685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9088516235352</t>
+    <t xml:space="preserve">46.8349723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9088554382324</t>
   </si>
   <si>
     <t xml:space="preserve">45.4237480163574</t>
   </si>
   <si>
-    <t xml:space="preserve">45.203239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8945388793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9386367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3355484008789</t>
+    <t xml:space="preserve">45.2032356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8945350646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9386405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3355445861816</t>
   </si>
   <si>
     <t xml:space="preserve">44.8063354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7181358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2473449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9827423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8504409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7765502929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6442451477051</t>
+    <t xml:space="preserve">44.7181396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2473487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.982738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8504371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7765579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6442527770996</t>
   </si>
   <si>
     <t xml:space="preserve">45.8206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3057632446289</t>
+    <t xml:space="preserve">46.3057556152344</t>
   </si>
   <si>
     <t xml:space="preserve">46.1734580993652</t>
@@ -284,97 +284,97 @@
     <t xml:space="preserve">46.2616577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6144599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0852584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9970512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4226722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5119781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1100807189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9138641357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1817855834961</t>
+    <t xml:space="preserve">46.6144638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0852546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4226684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5119743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1100921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9138603210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1817932128906</t>
   </si>
   <si>
     <t xml:space="preserve">49.1195220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5836715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6553726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2358779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0748634338379</t>
+    <t xml:space="preserve">48.5836753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5660591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6553649902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2358741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0748710632324</t>
   </si>
   <si>
     <t xml:space="preserve">49.9679527282715</t>
   </si>
   <si>
-    <t xml:space="preserve">49.164176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7000274658203</t>
+    <t xml:space="preserve">49.1641731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7000350952148</t>
   </si>
   <si>
     <t xml:space="preserve">48.9855575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5566253662109</t>
+    <t xml:space="preserve">47.5566291809082</t>
   </si>
   <si>
     <t xml:space="preserve">47.7352447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6188888549805</t>
+    <t xml:space="preserve">46.6188926696777</t>
   </si>
   <si>
     <t xml:space="preserve">46.9314727783203</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0924797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3427925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1723594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0113487243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.038387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8962516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7446823120117</t>
+    <t xml:space="preserve">48.0924758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3427963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1723518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0113410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0383911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8962478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.744686126709</t>
   </si>
   <si>
     <t xml:space="preserve">50.4144897460938</t>
   </si>
   <si>
-    <t xml:space="preserve">48.137134552002</t>
+    <t xml:space="preserve">48.1371307373047</t>
   </si>
   <si>
     <t xml:space="preserve">48.9409065246582</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">49.833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">49.030216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.5931053161621</t>
+    <t xml:space="preserve">49.0302200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5931129455566</t>
   </si>
   <si>
     <t xml:space="preserve">51.2182655334473</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">50.8610305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">51.575496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7987632751465</t>
+    <t xml:space="preserve">51.5755004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.798770904541</t>
   </si>
   <si>
     <t xml:space="preserve">50.9949951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7717247009277</t>
+    <t xml:space="preserve">50.771728515625</t>
   </si>
   <si>
     <t xml:space="preserve">50.2805290222168</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">49.8786468505859</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1912269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6201515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5849304199219</t>
+    <t xml:space="preserve">50.191219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6201553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5849342346191</t>
   </si>
   <si>
     <t xml:space="preserve">53.0937385559082</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1654357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3710975646973</t>
+    <t xml:space="preserve">54.1654396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3440551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.37109375</t>
   </si>
   <si>
     <t xml:space="preserve">54.1207809448242</t>
@@ -449,34 +449,34 @@
     <t xml:space="preserve">52.0666923522949</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6648025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6824188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3968811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6377601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2453079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7541198730469</t>
+    <t xml:space="preserve">51.6648063659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6824150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3968772888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6377639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2453117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7541160583496</t>
   </si>
   <si>
     <t xml:space="preserve">51.4415397644043</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3522262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8880767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.084300994873</t>
+    <t xml:space="preserve">51.3522300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8880805969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0843048095703</t>
   </si>
   <si>
     <t xml:space="preserve">50.4591445922852</t>
@@ -485,28 +485,28 @@
     <t xml:space="preserve">49.4767570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2981414794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9773902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5132293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6918525695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5308494567871</t>
+    <t xml:space="preserve">49.2981376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.9773826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5132331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6918449401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5308456420898</t>
   </si>
   <si>
     <t xml:space="preserve">52.3346176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2899627685547</t>
+    <t xml:space="preserve">52.6025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.289966583252</t>
   </si>
   <si>
     <t xml:space="preserve">53.183048248291</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">51.7094612121582</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1736106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7270660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1465682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.905689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0125999450684</t>
+    <t xml:space="preserve">51.1736068725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7270736694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1465721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9056854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0126037597656</t>
   </si>
   <si>
     <t xml:space="preserve">48.7176361083984</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">47.6459350585938</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8245544433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3239250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7258148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5471992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.395622253418</t>
+    <t xml:space="preserve">47.8245506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3239212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7258110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3956184387207</t>
   </si>
   <si>
     <t xml:space="preserve">46.6635437011719</t>
@@ -560,64 +560,64 @@
     <t xml:space="preserve">46.1276969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5742340087891</t>
+    <t xml:space="preserve">46.5742454528809</t>
   </si>
   <si>
     <t xml:space="preserve">46.4402770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9937324523926</t>
+    <t xml:space="preserve">45.9937362670898</t>
   </si>
   <si>
     <t xml:space="preserve">45.4578857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6811561584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5295829772949</t>
+    <t xml:space="preserve">45.6811599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">46.3063125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2440490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4673271179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2088241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3698425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1560096740723</t>
+    <t xml:space="preserve">47.2440567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4673194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2088279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3698348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1559982299805</t>
   </si>
   <si>
     <t xml:space="preserve">50.5038032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8515968322754</t>
+    <t xml:space="preserve">48.8516082763672</t>
   </si>
   <si>
     <t xml:space="preserve">49.6107215881348</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8163833618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.128963470459</t>
+    <t xml:space="preserve">50.8163871765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1289558410645</t>
   </si>
   <si>
     <t xml:space="preserve">52.2006607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4685821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3616638183594</t>
+    <t xml:space="preserve">52.4685859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">53.4063186645508</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">53.4509696960449</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6742401123047</t>
+    <t xml:space="preserve">53.6742362976074</t>
   </si>
   <si>
     <t xml:space="preserve">52.9151229858398</t>
@@ -635,85 +635,85 @@
     <t xml:space="preserve">53.2723541259766</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8528594970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.594367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3264427185059</t>
+    <t xml:space="preserve">53.852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7905883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5943641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3264389038086</t>
   </si>
   <si>
     <t xml:space="preserve">55.5050621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2641754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1302146911621</t>
+    <t xml:space="preserve">56.2641792297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1302185058594</t>
   </si>
   <si>
     <t xml:space="preserve">55.6390190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8000297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5321083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9786491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0679626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4251899719238</t>
+    <t xml:space="preserve">56.8000259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5321006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.978645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0679588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4251937866211</t>
   </si>
   <si>
     <t xml:space="preserve">57.3358726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0503425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.8987731933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0327377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7648086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0949935913086</t>
+    <t xml:space="preserve">58.0503387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.8987617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0327339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7648162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0950012207031</t>
   </si>
   <si>
     <t xml:space="preserve">57.1572647094727</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3805389404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5861892700195</t>
+    <t xml:space="preserve">57.3805313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5861930847168</t>
   </si>
   <si>
     <t xml:space="preserve">60.0151252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">58.9434356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2830467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4440650939941</t>
+    <t xml:space="preserve">58.9434280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3006629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2830505371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4440612792969</t>
   </si>
   <si>
     <t xml:space="preserve">63.4088287353516</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">61.6226692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8905868530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8283348083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6943740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3817939758301</t>
+    <t xml:space="preserve">61.8905944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8283309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6943664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.3817863464355</t>
   </si>
   <si>
     <t xml:space="preserve">62.7390289306641</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">62.5157585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8635444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1937484741211</t>
+    <t xml:space="preserve">60.8635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1937522888184</t>
   </si>
   <si>
     <t xml:space="preserve">60.9528694152832</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">62.0824508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3083763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.534294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4950752258301</t>
+    <t xml:space="preserve">62.3083686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5343017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4950714111328</t>
   </si>
   <si>
     <t xml:space="preserve">63.4379615783691</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7542572021484</t>
+    <t xml:space="preserve">63.7542495727539</t>
   </si>
   <si>
     <t xml:space="preserve">63.483154296875</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">64.5675582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0705490112305</t>
+    <t xml:space="preserve">64.0705413818359</t>
   </si>
   <si>
     <t xml:space="preserve">64.8386611938477</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">65.5164184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1668586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0313148498535</t>
+    <t xml:space="preserve">63.166862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.031322479248</t>
   </si>
   <si>
     <t xml:space="preserve">64.5223770141602</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8897933959961</t>
+    <t xml:space="preserve">63.8898086547852</t>
   </si>
   <si>
     <t xml:space="preserve">64.4320068359375</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">64.1608963012695</t>
   </si>
   <si>
-    <t xml:space="preserve">65.6971435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0884094238281</t>
+    <t xml:space="preserve">65.697151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0884056091309</t>
   </si>
   <si>
     <t xml:space="preserve">59.6425361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">60.7721252441406</t>
+    <t xml:space="preserve">60.7721405029297</t>
   </si>
   <si>
     <t xml:space="preserve">60.184741973877</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">60.5462036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6877174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.449893951416</t>
+    <t xml:space="preserve">59.6877250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6365852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4498901367188</t>
   </si>
   <si>
     <t xml:space="preserve">62.398738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2120552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5735092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3927917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1216812133789</t>
+    <t xml:space="preserve">63.2120513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5735168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3927803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1216735839844</t>
   </si>
   <si>
     <t xml:space="preserve">66.2393646240234</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">66.7815704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0134353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5104598999023</t>
+    <t xml:space="preserve">66.0134429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5104675292969</t>
   </si>
   <si>
     <t xml:space="preserve">66.3297271728516</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9682540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8778915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6067886352539</t>
+    <t xml:space="preserve">65.9682464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8778839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6067810058594</t>
   </si>
   <si>
     <t xml:space="preserve">65.019401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2001190185547</t>
+    <t xml:space="preserve">65.2001342773438</t>
   </si>
   <si>
     <t xml:space="preserve">64.7483062744141</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">64.6579284667969</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9801864624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3024101257324</t>
+    <t xml:space="preserve">64.4771881103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9801712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3024139404297</t>
   </si>
   <si>
     <t xml:space="preserve">65.4260559082031</t>
@@ -914,40 +914,40 @@
     <t xml:space="preserve">66.2845458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">66.600830078125</t>
+    <t xml:space="preserve">66.6008224487305</t>
   </si>
   <si>
     <t xml:space="preserve">66.4652862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8719329833984</t>
+    <t xml:space="preserve">66.8719253540039</t>
   </si>
   <si>
     <t xml:space="preserve">66.0586318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0978546142578</t>
+    <t xml:space="preserve">66.3749008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0978469848633</t>
   </si>
   <si>
     <t xml:space="preserve">66.6911926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">67.4141387939453</t>
+    <t xml:space="preserve">67.4141311645508</t>
   </si>
   <si>
     <t xml:space="preserve">68.5437316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1370849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9563369750977</t>
+    <t xml:space="preserve">68.137077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8659896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9563293457031</t>
   </si>
   <si>
     <t xml:space="preserve">68.182258605957</t>
@@ -956,76 +956,76 @@
     <t xml:space="preserve">69.1311187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3059005737305</t>
+    <t xml:space="preserve">70.305908203125</t>
   </si>
   <si>
     <t xml:space="preserve">70.3962631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9777069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3903198242188</t>
+    <t xml:space="preserve">71.9776916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3903121948242</t>
   </si>
   <si>
     <t xml:space="preserve">71.5258636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">70.8480987548828</t>
+    <t xml:space="preserve">70.8481063842773</t>
   </si>
   <si>
     <t xml:space="preserve">71.1643905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7910003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8932952880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2607040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3510894775391</t>
+    <t xml:space="preserve">72.7909851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8932800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2607116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3510818481445</t>
   </si>
   <si>
     <t xml:space="preserve">70.5318222045898</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7577362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8029174804688</t>
+    <t xml:space="preserve">70.7577285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8029251098633</t>
   </si>
   <si>
     <t xml:space="preserve">70.4866409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5769958496094</t>
+    <t xml:space="preserve">70.5769882202148</t>
   </si>
   <si>
     <t xml:space="preserve">71.3451232910156</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4414291381836</t>
+    <t xml:space="preserve">70.4414443969727</t>
   </si>
   <si>
     <t xml:space="preserve">71.571044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">70.9836502075195</t>
+    <t xml:space="preserve">70.983642578125</t>
   </si>
   <si>
     <t xml:space="preserve">70.7125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">65.1097793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5616073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.4593200683594</t>
+    <t xml:space="preserve">65.1097717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.4593124389648</t>
   </si>
   <si>
     <t xml:space="preserve">67.8207931518555</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">69.2666625976562</t>
   </si>
   <si>
-    <t xml:space="preserve">70.034782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.7636795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9955673217773</t>
+    <t xml:space="preserve">70.034797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.7636871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9955596923828</t>
   </si>
   <si>
     <t xml:space="preserve">67.3237686157227</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">68.3629913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">69.040771484375</t>
+    <t xml:space="preserve">69.0407562255859</t>
   </si>
   <si>
     <t xml:space="preserve">69.1763076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9444198608398</t>
+    <t xml:space="preserve">69.9444351196289</t>
   </si>
   <si>
     <t xml:space="preserve">70.1703414916992</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">71.8873291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6102752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8992462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4985427856445</t>
+    <t xml:space="preserve">72.6102676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8992309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.49853515625</t>
   </si>
   <si>
     <t xml:space="preserve">68.4081802368164</t>
@@ -1082,28 +1082,28 @@
     <t xml:space="preserve">67.6400527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">69.402214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3391647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7969512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6162185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9325103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.0228652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7065811157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4806671142578</t>
+    <t xml:space="preserve">69.4022216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3391723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7969589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6162261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.0228729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7065887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4806747436523</t>
   </si>
   <si>
     <t xml:space="preserve">71.4354858398438</t>
@@ -1112,70 +1112,70 @@
     <t xml:space="preserve">71.6614151000977</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2547607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8088684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7517776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0918884277344</t>
+    <t xml:space="preserve">71.2547454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8088760375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7517700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0918960571289</t>
   </si>
   <si>
     <t xml:space="preserve">66.9623031616211</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3416366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2572326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6187057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.076488494873</t>
+    <t xml:space="preserve">62.8505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3416519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2572364807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6186981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0764999389648</t>
   </si>
   <si>
     <t xml:space="preserve">62.9409523010254</t>
   </si>
   <si>
-    <t xml:space="preserve">62.7602081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9017219543457</t>
+    <t xml:space="preserve">62.7602119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9017143249512</t>
   </si>
   <si>
     <t xml:space="preserve">60.9528617858887</t>
   </si>
   <si>
-    <t xml:space="preserve">60.0040092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7329025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.862491607666</t>
+    <t xml:space="preserve">60.0040054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7328987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8624954223633</t>
   </si>
   <si>
     <t xml:space="preserve">61.8113555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7994346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5496978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7363891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2453231811523</t>
+    <t xml:space="preserve">63.7994270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5496826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7363815307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2453308105469</t>
   </si>
   <si>
     <t xml:space="preserve">64.8838500976562</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">65.651969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">65.2905044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4200897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2726364135742</t>
+    <t xml:space="preserve">65.2904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4200973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2726440429688</t>
   </si>
   <si>
     <t xml:space="preserve">70.1251602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">68.8600234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.8540725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6221771240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1192016601562</t>
+    <t xml:space="preserve">68.8600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.8540649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1192092895508</t>
   </si>
   <si>
     <t xml:space="preserve">71.0740203857422</t>
@@ -1214,79 +1214,79 @@
     <t xml:space="preserve">72.6554489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6946716308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4747161865234</t>
+    <t xml:space="preserve">73.6946792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4747009277344</t>
   </si>
   <si>
     <t xml:space="preserve">73.4687652587891</t>
   </si>
   <si>
-    <t xml:space="preserve">73.1976547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3783798217773</t>
+    <t xml:space="preserve">73.1976470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3784027099609</t>
   </si>
   <si>
     <t xml:space="preserve">74.688720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5591201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1983795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6960983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.928955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.7964935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1526947021484</t>
+    <t xml:space="preserve">73.5591278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6961059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9289398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8466873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.7964859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.152702331543</t>
   </si>
   <si>
     <t xml:space="preserve">77.2576293945312</t>
   </si>
   <si>
-    <t xml:space="preserve">75.4312133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.0795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9059448242188</t>
+    <t xml:space="preserve">75.4312057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.0795211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9059371948242</t>
   </si>
   <si>
     <t xml:space="preserve">80.5908508300781</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3625411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.7278137207031</t>
+    <t xml:space="preserve">80.362548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.7278213500977</t>
   </si>
   <si>
     <t xml:space="preserve">80.2712249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.230094909668</t>
+    <t xml:space="preserve">81.2300872802734</t>
   </si>
   <si>
     <t xml:space="preserve">83.1021728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">84.3806762695312</t>
+    <t xml:space="preserve">84.3806838989258</t>
   </si>
   <si>
     <t xml:space="preserve">85.2482299804688</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">84.928596496582</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2893600463867</t>
+    <t xml:space="preserve">84.2893447875977</t>
   </si>
   <si>
     <t xml:space="preserve">83.0565185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7323608398438</t>
+    <t xml:space="preserve">81.7323532104492</t>
   </si>
   <si>
     <t xml:space="preserve">81.4127349853516</t>
@@ -1310,40 +1310,40 @@
     <t xml:space="preserve">87.6682205200195</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8006744384766</t>
+    <t xml:space="preserve">86.8006820678711</t>
   </si>
   <si>
     <t xml:space="preserve">87.3942642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8554000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9878463745117</t>
+    <t xml:space="preserve">88.8554153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9878540039062</t>
   </si>
   <si>
     <t xml:space="preserve">89.2206802368164</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9421844482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0380554199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0335311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2572860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4855880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5769195556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8052139282227</t>
+    <t xml:space="preserve">87.9421920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0380477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0335159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2572937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5769119262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8052215576172</t>
   </si>
   <si>
     <t xml:space="preserve">89.6772918701172</t>
@@ -1355,49 +1355,49 @@
     <t xml:space="preserve">89.4033279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1248245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6225662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3531341552734</t>
+    <t xml:space="preserve">88.1248397827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.62255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3531265258789</t>
   </si>
   <si>
     <t xml:space="preserve">86.2984161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">85.8418121337891</t>
+    <t xml:space="preserve">85.8418045043945</t>
   </si>
   <si>
     <t xml:space="preserve">86.1614303588867</t>
   </si>
   <si>
-    <t xml:space="preserve">84.4263381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.4719924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8327484130859</t>
+    <t xml:space="preserve">84.4263305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.4720001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">77.668571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">79.7689743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0474472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2255554199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4538650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.3580169677734</t>
+    <t xml:space="preserve">79.7689514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2255630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.453857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.358024597168</t>
   </si>
   <si>
     <t xml:space="preserve">80.4995269775391</t>
@@ -1409,40 +1409,40 @@
     <t xml:space="preserve">79.3123550415039</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1112365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.6135025024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5587921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8784027099609</t>
+    <t xml:space="preserve">85.1112289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.6134948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5587768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8784103393555</t>
   </si>
   <si>
     <t xml:space="preserve">83.6501083374023</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2391662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7414169311523</t>
+    <t xml:space="preserve">83.2391586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7414321899414</t>
   </si>
   <si>
     <t xml:space="preserve">84.837272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">85.6591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.3349990844727</t>
+    <t xml:space="preserve">85.6591720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.3350067138672</t>
   </si>
   <si>
     <t xml:space="preserve">81.6410446166992</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9150009155273</t>
+    <t xml:space="preserve">81.9150085449219</t>
   </si>
   <si>
     <t xml:space="preserve">81.0017929077148</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">82.8282089233398</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5312423706055</t>
+    <t xml:space="preserve">87.53125</t>
   </si>
   <si>
     <t xml:space="preserve">88.7640838623047</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">84.2436904907227</t>
   </si>
   <si>
-    <t xml:space="preserve">85.0199279785156</t>
+    <t xml:space="preserve">85.0199203491211</t>
   </si>
   <si>
     <t xml:space="preserve">84.882926940918</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">82.7368927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">83.3761520385742</t>
+    <t xml:space="preserve">83.3761444091797</t>
   </si>
   <si>
     <t xml:space="preserve">81.4583969116211</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">75.1572418212891</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4266815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7828903198242</t>
+    <t xml:space="preserve">74.4266738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.330810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7828979492188</t>
   </si>
   <si>
     <t xml:space="preserve">74.8376159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6002578735352</t>
+    <t xml:space="preserve">72.6002655029297</t>
   </si>
   <si>
     <t xml:space="preserve">72.9198837280273</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">76.4357299804688</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8285522460938</t>
+    <t xml:space="preserve">72.8285446166992</t>
   </si>
   <si>
     <t xml:space="preserve">73.8330841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">72.280632019043</t>
+    <t xml:space="preserve">72.2806396484375</t>
   </si>
   <si>
     <t xml:space="preserve">73.9700698852539</t>
   </si>
   <si>
-    <t xml:space="preserve">75.06591796875</t>
+    <t xml:space="preserve">75.0659255981445</t>
   </si>
   <si>
     <t xml:space="preserve">76.5270690917969</t>
   </si>
   <si>
-    <t xml:space="preserve">79.9516067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.3398742675781</t>
+    <t xml:space="preserve">79.9515914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.3398971557617</t>
   </si>
   <si>
     <t xml:space="preserve">76.1161117553711</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">73.0568618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">70.545524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.682502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0934600830078</t>
+    <t xml:space="preserve">70.5455322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6825103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0934524536133</t>
   </si>
   <si>
     <t xml:space="preserve">71.9610137939453</t>
@@ -1559,43 +1559,43 @@
     <t xml:space="preserve">73.1025161743164</t>
   </si>
   <si>
-    <t xml:space="preserve">72.326301574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.0478057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8651580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5821151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4908065795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.8560943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3217620849609</t>
+    <t xml:space="preserve">72.326286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0477981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8651657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5821228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4908142089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3217544555664</t>
   </si>
   <si>
     <t xml:space="preserve">66.8013687133789</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3949508666992</t>
+    <t xml:space="preserve">67.3949584960938</t>
   </si>
   <si>
     <t xml:space="preserve">66.9383544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">66.6187210083008</t>
+    <t xml:space="preserve">66.6187286376953</t>
   </si>
   <si>
     <t xml:space="preserve">67.5775909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8470153808594</t>
+    <t xml:space="preserve">66.8470230102539</t>
   </si>
   <si>
     <t xml:space="preserve">65.5228652954102</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">64.0160751342773</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4270172119141</t>
+    <t xml:space="preserve">64.4270324707031</t>
   </si>
   <si>
     <t xml:space="preserve">64.2900390625</t>
@@ -1613,28 +1613,28 @@
     <t xml:space="preserve">64.7922897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1621170043945</t>
+    <t xml:space="preserve">66.1621246337891</t>
   </si>
   <si>
     <t xml:space="preserve">64.944694519043</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2089385986328</t>
+    <t xml:space="preserve">66.2089309692383</t>
   </si>
   <si>
     <t xml:space="preserve">66.6771774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.0016784667969</t>
+    <t xml:space="preserve">66.3025894165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.0016708374023</t>
   </si>
   <si>
     <t xml:space="preserve">69.4866104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2056579589844</t>
+    <t xml:space="preserve">69.2056655883789</t>
   </si>
   <si>
     <t xml:space="preserve">69.6270751953125</t>
@@ -1646,97 +1646,97 @@
     <t xml:space="preserve">70.1421432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">69.7675476074219</t>
+    <t xml:space="preserve">69.7675552368164</t>
   </si>
   <si>
     <t xml:space="preserve">70.8913192749023</t>
   </si>
   <si>
-    <t xml:space="preserve">72.5769882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0452270507812</t>
+    <t xml:space="preserve">72.5769958496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">75.2459411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">75.10546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9650115966797</t>
+    <t xml:space="preserve">75.1054763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9650039672852</t>
   </si>
   <si>
     <t xml:space="preserve">74.5904083251953</t>
   </si>
   <si>
-    <t xml:space="preserve">75.0586547851562</t>
+    <t xml:space="preserve">75.0586471557617</t>
   </si>
   <si>
     <t xml:space="preserve">75.2927703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">74.6840591430664</t>
+    <t xml:space="preserve">74.6840515136719</t>
   </si>
   <si>
     <t xml:space="preserve">76.557014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">76.135612487793</t>
+    <t xml:space="preserve">76.1355972290039</t>
   </si>
   <si>
     <t xml:space="preserve">74.8713531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8847808837891</t>
+    <t xml:space="preserve">76.8847732543945</t>
   </si>
   <si>
     <t xml:space="preserve">76.9784317016602</t>
   </si>
   <si>
-    <t xml:space="preserve">78.7109146118164</t>
+    <t xml:space="preserve">78.7109222412109</t>
   </si>
   <si>
     <t xml:space="preserve">78.6172637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">79.6942138671875</t>
+    <t xml:space="preserve">79.694206237793</t>
   </si>
   <si>
     <t xml:space="preserve">79.2727966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">79.6005706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.2259674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.4132690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7878570556641</t>
+    <t xml:space="preserve">79.6005783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.2259750366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.4132766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7878646850586</t>
   </si>
   <si>
     <t xml:space="preserve">80.0219802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">79.0386810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8815231323242</t>
+    <t xml:space="preserve">79.038688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">80.6775131225586</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3029174804688</t>
+    <t xml:space="preserve">80.3029098510742</t>
   </si>
   <si>
     <t xml:space="preserve">80.7711639404297</t>
   </si>
   <si>
-    <t xml:space="preserve">82.035400390625</t>
+    <t xml:space="preserve">82.0354080200195</t>
   </si>
   <si>
     <t xml:space="preserve">81.707633972168</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">81.3798675537109</t>
   </si>
   <si>
-    <t xml:space="preserve">81.3330535888672</t>
+    <t xml:space="preserve">81.3330459594727</t>
   </si>
   <si>
     <t xml:space="preserve">81.2393951416016</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">82.2227020263672</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1457443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3497467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.9751434326172</t>
+    <t xml:space="preserve">81.145751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3497543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.9751510620117</t>
   </si>
   <si>
     <t xml:space="preserve">82.26953125</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5036468505859</t>
+    <t xml:space="preserve">82.5036392211914</t>
   </si>
   <si>
     <t xml:space="preserve">83.0187072753906</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">83.6742401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9718780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0488204956055</t>
+    <t xml:space="preserve">82.9718704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.0488357543945</t>
   </si>
   <si>
     <t xml:space="preserve">84.0020065307617</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7980194091797</t>
+    <t xml:space="preserve">84.7980117797852</t>
   </si>
   <si>
     <t xml:space="preserve">85.7813110351562</t>
@@ -1802,46 +1802,46 @@
     <t xml:space="preserve">86.1559066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">85.8281478881836</t>
+    <t xml:space="preserve">85.8281326293945</t>
   </si>
   <si>
     <t xml:space="preserve">85.6876678466797</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2194290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1257781982422</t>
+    <t xml:space="preserve">85.2194213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1257858276367</t>
   </si>
   <si>
     <t xml:space="preserve">85.6408386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">82.0822372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.7410278320312</t>
+    <t xml:space="preserve">82.0822296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7410354614258</t>
   </si>
   <si>
     <t xml:space="preserve">80.2560958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5671539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8481063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8147125244141</t>
+    <t xml:space="preserve">81.5671691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8147201538086</t>
   </si>
   <si>
     <t xml:space="preserve">84.1893157958984</t>
   </si>
   <si>
-    <t xml:space="preserve">84.2829513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3130722045898</t>
+    <t xml:space="preserve">84.2829360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3130798339844</t>
   </si>
   <si>
     <t xml:space="preserve">88.1693267822266</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">89.4804000854492</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2596969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6854934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1656341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1580963134766</t>
+    <t xml:space="preserve">91.2597045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6854858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1656188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.158088684082</t>
   </si>
   <si>
     <t xml:space="preserve">91.5437088012695</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">89.1806716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3299789428711</t>
+    <t xml:space="preserve">88.3299865722656</t>
   </si>
   <si>
     <t xml:space="preserve">88.8025970458984</t>
   </si>
   <si>
-    <t xml:space="preserve">86.5340881347656</t>
+    <t xml:space="preserve">86.5340957641602</t>
   </si>
   <si>
     <t xml:space="preserve">90.0786285400391</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">91.3546752929688</t>
   </si>
   <si>
-    <t xml:space="preserve">91.9690628051758</t>
+    <t xml:space="preserve">91.9690551757812</t>
   </si>
   <si>
     <t xml:space="preserve">93.1033096313477</t>
@@ -1901,46 +1901,46 @@
     <t xml:space="preserve">95.5608520507812</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4115524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8122177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0731964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8293609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3416976928711</t>
+    <t xml:space="preserve">96.4115447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8122100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0731887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8293685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3417053222656</t>
   </si>
   <si>
     <t xml:space="preserve">101.326644897461</t>
   </si>
   <si>
-    <t xml:space="preserve">98.6800537109375</t>
+    <t xml:space="preserve">98.680061340332</t>
   </si>
   <si>
     <t xml:space="preserve">99.2471771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">96.884162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6403198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9389343261719</t>
+    <t xml:space="preserve">96.8841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6403274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9389419555664</t>
   </si>
   <si>
     <t xml:space="preserve">96.3170394897461</t>
   </si>
   <si>
-    <t xml:space="preserve">96.5060653686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2622451782227</t>
+    <t xml:space="preserve">96.5060577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2622299194336</t>
   </si>
   <si>
     <t xml:space="preserve">96.9786758422852</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">99.5307540893555</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3019714355469</t>
+    <t xml:space="preserve">98.3019790649414</t>
   </si>
   <si>
     <t xml:space="preserve">97.3567581176758</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">97.1677169799805</t>
   </si>
   <si>
-    <t xml:space="preserve">97.5458068847656</t>
+    <t xml:space="preserve">97.5457992553711</t>
   </si>
   <si>
     <t xml:space="preserve">96.2225112915039</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">95.7499084472656</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8444213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4663391113281</t>
+    <t xml:space="preserve">95.8444137573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4663314819336</t>
   </si>
   <si>
     <t xml:space="preserve">96.7896347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">102.082817077637</t>
+    <t xml:space="preserve">102.082809448242</t>
   </si>
   <si>
     <t xml:space="preserve">100.475959777832</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">100.097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">99.908821105957</t>
+    <t xml:space="preserve">99.9088287353516</t>
   </si>
   <si>
     <t xml:space="preserve">98.396484375</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">100.192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">102.366371154785</t>
+    <t xml:space="preserve">102.366386413574</t>
   </si>
   <si>
     <t xml:space="preserve">102.17733001709</t>
@@ -2018,34 +2018,34 @@
     <t xml:space="preserve">103.028030395508</t>
   </si>
   <si>
-    <t xml:space="preserve">100.003356933594</t>
+    <t xml:space="preserve">100.003349304199</t>
   </si>
   <si>
     <t xml:space="preserve">101.137603759766</t>
   </si>
   <si>
-    <t xml:space="preserve">101.704719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.689666748047</t>
+    <t xml:space="preserve">101.704734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.689674377441</t>
   </si>
   <si>
     <t xml:space="preserve">103.500633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">102.933502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.38143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5855331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6951141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1129302978516</t>
+    <t xml:space="preserve">102.93350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.381423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5855255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6951065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1129379272461</t>
   </si>
   <si>
     <t xml:space="preserve">99.0581283569336</t>
@@ -2057,49 +2057,49 @@
     <t xml:space="preserve">100.286903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">99.7197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.854049682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6252593994141</t>
+    <t xml:space="preserve">99.7197723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.854042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6252670288086</t>
   </si>
   <si>
     <t xml:space="preserve">94.4266052246094</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7101593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8594741821289</t>
+    <t xml:space="preserve">94.7101669311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.859489440918</t>
   </si>
   <si>
     <t xml:space="preserve">94.0957794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2848205566406</t>
+    <t xml:space="preserve">94.2848281860352</t>
   </si>
   <si>
     <t xml:space="preserve">94.6156387329102</t>
   </si>
   <si>
-    <t xml:space="preserve">94.521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6382293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3471374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3074111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2998733520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7327575683594</t>
+    <t xml:space="preserve">94.5211334228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6382217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3471298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3074035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2998809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7327499389648</t>
   </si>
   <si>
     <t xml:space="preserve">92.0163040161133</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">93.1505737304688</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3718109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8046875</t>
+    <t xml:space="preserve">95.3718185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8046951293945</t>
   </si>
   <si>
     <t xml:space="preserve">98.8690948486328</t>
   </si>
   <si>
-    <t xml:space="preserve">97.9238815307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.759521484375</t>
+    <t xml:space="preserve">97.9238739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.75951385498</t>
   </si>
   <si>
     <t xml:space="preserve">103.122543334961</t>
@@ -2132,31 +2132,31 @@
     <t xml:space="preserve">105.958183288574</t>
   </si>
   <si>
-    <t xml:space="preserve">108.226692199707</t>
+    <t xml:space="preserve">108.226684570312</t>
   </si>
   <si>
     <t xml:space="preserve">107.659561157227</t>
   </si>
   <si>
-    <t xml:space="preserve">109.077392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.574661254883</t>
+    <t xml:space="preserve">109.07738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.574645996094</t>
   </si>
   <si>
     <t xml:space="preserve">113.803436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">113.236312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.519874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.65412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.818489074707</t>
+    <t xml:space="preserve">113.236305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.519866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.654121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.818481445312</t>
   </si>
   <si>
     <t xml:space="preserve">114.937683105469</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">115.977416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">117.206192016602</t>
+    <t xml:space="preserve">117.206184387207</t>
   </si>
   <si>
     <t xml:space="preserve">117.017158508301</t>
@@ -2174,37 +2174,37 @@
     <t xml:space="preserve">115.315773010254</t>
   </si>
   <si>
-    <t xml:space="preserve">114.370559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.425346374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.644508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.251358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.30615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.156845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.723968505859</t>
+    <t xml:space="preserve">114.370552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.425354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.644500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.251365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.589721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.306144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.156829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.723960876465</t>
   </si>
   <si>
     <t xml:space="preserve">111.062316894531</t>
   </si>
   <si>
-    <t xml:space="preserve">110.117111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.833534240723</t>
+    <t xml:space="preserve">110.117118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.833541870117</t>
   </si>
   <si>
     <t xml:space="preserve">108.51025390625</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">111.913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">112.291107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.952751159668</t>
+    <t xml:space="preserve">112.29109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.952743530273</t>
   </si>
   <si>
     <t xml:space="preserve">110.87328338623</t>
@@ -2228,19 +2228,19 @@
     <t xml:space="preserve">107.470504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">110.495185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.037658691406</t>
+    <t xml:space="preserve">110.495178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.037643432617</t>
   </si>
   <si>
     <t xml:space="preserve">107.848602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">108.793815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.430778503418</t>
+    <t xml:space="preserve">108.793807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.430786132812</t>
   </si>
   <si>
     <t xml:space="preserve">109.171905517578</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">109.266418457031</t>
   </si>
   <si>
-    <t xml:space="preserve">106.997917175293</t>
+    <t xml:space="preserve">106.997909545898</t>
   </si>
   <si>
     <t xml:space="preserve">104.918441772461</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">108.415725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">108.321212768555</t>
+    <t xml:space="preserve">108.32120513916</t>
   </si>
   <si>
     <t xml:space="preserve">110.211631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">114.276031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.465072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.928062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.540374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7745742797852</t>
+    <t xml:space="preserve">114.27604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.46508026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.928070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.540367126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7745819091797</t>
   </si>
   <si>
     <t xml:space="preserve">106.808868408203</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">101.893775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">99.8143157958984</t>
+    <t xml:space="preserve">99.8143081665039</t>
   </si>
   <si>
     <t xml:space="preserve">108.132164001465</t>
@@ -2303,34 +2303,34 @@
     <t xml:space="preserve">105.485572814941</t>
   </si>
   <si>
-    <t xml:space="preserve">110.400672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.888343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.52530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.445846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.55541229248</t>
+    <t xml:space="preserve">110.400680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.888336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.525314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.445838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.55542755127</t>
   </si>
   <si>
     <t xml:space="preserve">114.086990356445</t>
   </si>
   <si>
-    <t xml:space="preserve">111.629447937012</t>
+    <t xml:space="preserve">111.629455566406</t>
   </si>
   <si>
     <t xml:space="preserve">118.056884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">122.310317993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.091171264648</t>
+    <t xml:space="preserve">122.310333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.091163635254</t>
   </si>
   <si>
     <t xml:space="preserve">132.329574584961</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">141.592651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">141.876235961914</t>
+    <t xml:space="preserve">141.876220703125</t>
   </si>
   <si>
     <t xml:space="preserve">136.583038330078</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">145.089935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">144.2392578125</t>
+    <t xml:space="preserve">144.239227294922</t>
   </si>
   <si>
     <t xml:space="preserve">155.959854125977</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">150.383117675781</t>
   </si>
   <si>
-    <t xml:space="preserve">153.691360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.755752563477</t>
+    <t xml:space="preserve">153.691345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.755737304688</t>
   </si>
   <si>
     <t xml:space="preserve">157.944808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">153.313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.791320800781</t>
+    <t xml:space="preserve">153.313247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.79133605957</t>
   </si>
   <si>
     <t xml:space="preserve">146.885833740234</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">146.318710327148</t>
   </si>
   <si>
-    <t xml:space="preserve">147.641983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.596817016602</t>
+    <t xml:space="preserve">147.641998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.596832275391</t>
   </si>
   <si>
     <t xml:space="preserve">151.706390380859</t>
@@ -2396,25 +2396,25 @@
     <t xml:space="preserve">163.048934936523</t>
   </si>
   <si>
-    <t xml:space="preserve">167.302383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.10791015625</t>
+    <t xml:space="preserve">167.302398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.107925415039</t>
   </si>
   <si>
     <t xml:space="preserve">174.675048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">169.381866455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.833984375</t>
+    <t xml:space="preserve">169.3818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.833969116211</t>
   </si>
   <si>
     <t xml:space="preserve">180.440811157227</t>
   </si>
   <si>
-    <t xml:space="preserve">191.688842773438</t>
+    <t xml:space="preserve">191.688827514648</t>
   </si>
   <si>
     <t xml:space="preserve">197.92724609375</t>
@@ -2423,10 +2423,10 @@
     <t xml:space="preserve">186.206619262695</t>
   </si>
   <si>
-    <t xml:space="preserve">163.521545410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.839401245117</t>
+    <t xml:space="preserve">163.521530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">178.172317504883</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">163.994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">164.655776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.905059814453</t>
+    <t xml:space="preserve">164.655792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.905075073242</t>
   </si>
   <si>
     <t xml:space="preserve">150.855728149414</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">152.651611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">155.014663696289</t>
+    <t xml:space="preserve">155.014617919922</t>
   </si>
   <si>
     <t xml:space="preserve">158.6064453125</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">157.850280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">161.510162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.365707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.890396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.129898071289</t>
+    <t xml:space="preserve">161.510147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.36572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.890411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.129913330078</t>
   </si>
   <si>
     <t xml:space="preserve">159.133590698242</t>
   </si>
   <si>
-    <t xml:space="preserve">162.270645141602</t>
+    <t xml:space="preserve">162.270629882812</t>
   </si>
   <si>
     <t xml:space="preserve">167.11882019043</t>
@@ -2498,28 +2498,28 @@
     <t xml:space="preserve">162.55583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">162.841018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.650894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.685470581055</t>
+    <t xml:space="preserve">162.841033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.073135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.685485839844</t>
   </si>
   <si>
     <t xml:space="preserve">170.350921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">163.031143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.362014770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.122512817383</t>
+    <t xml:space="preserve">163.031158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.361999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.122497558594</t>
   </si>
   <si>
     <t xml:space="preserve">164.647201538086</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">166.358306884766</t>
   </si>
   <si>
-    <t xml:space="preserve">160.939788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.66569519043</t>
+    <t xml:space="preserve">160.939804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.665710449219</t>
   </si>
   <si>
     <t xml:space="preserve">162.175598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">164.742248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.22868347168</t>
+    <t xml:space="preserve">164.742263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.228668212891</t>
   </si>
   <si>
     <t xml:space="preserve">157.802749633789</t>
@@ -2561,10 +2561,10 @@
     <t xml:space="preserve">152.669418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">149.817535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.775573730469</t>
+    <t xml:space="preserve">149.81755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.77555847168</t>
   </si>
   <si>
     <t xml:space="preserve">150.768173217773</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">145.254577636719</t>
   </si>
   <si>
-    <t xml:space="preserve">149.722503662109</t>
+    <t xml:space="preserve">149.72248840332</t>
   </si>
   <si>
     <t xml:space="preserve">152.289154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">151.623718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.391616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.760772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.243499755859</t>
+    <t xml:space="preserve">151.623733520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.3916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.760757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.24348449707</t>
   </si>
   <si>
     <t xml:space="preserve">154.190399169922</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">154.950881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">155.426193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.806427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.418792724609</t>
+    <t xml:space="preserve">155.426177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.806442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.418807983398</t>
   </si>
   <si>
     <t xml:space="preserve">145.634826660156</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">144.018768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">144.589141845703</t>
+    <t xml:space="preserve">144.589157104492</t>
   </si>
   <si>
     <t xml:space="preserve">143.54345703125</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">135.55827331543</t>
   </si>
   <si>
-    <t xml:space="preserve">134.797775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.364440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.174301147461</t>
+    <t xml:space="preserve">134.797760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.36442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.174331665039</t>
   </si>
   <si>
     <t xml:space="preserve">144.779266357422</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">143.258270263672</t>
   </si>
   <si>
-    <t xml:space="preserve">147.060760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.726181030273</t>
+    <t xml:space="preserve">147.060729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.726165771484</t>
   </si>
   <si>
     <t xml:space="preserve">149.247177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">152.95458984375</t>
+    <t xml:space="preserve">152.954605102539</t>
   </si>
   <si>
     <t xml:space="preserve">150.387908935547</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">161.03483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">160.65461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.080520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.795333862305</t>
+    <t xml:space="preserve">160.654602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.080535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.795318603516</t>
   </si>
   <si>
     <t xml:space="preserve">163.411392211914</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">168.069442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">174.913879394531</t>
+    <t xml:space="preserve">174.91389465332</t>
   </si>
   <si>
     <t xml:space="preserve">175.294128417969</t>
@@ -2684,25 +2684,25 @@
     <t xml:space="preserve">177.670669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">173.48796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.716369628906</t>
+    <t xml:space="preserve">173.487945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.716354370117</t>
   </si>
   <si>
     <t xml:space="preserve">180.712677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">178.24104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.853408813477</t>
+    <t xml:space="preserve">178.241058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181.853393554688</t>
   </si>
   <si>
     <t xml:space="preserve">179.666976928711</t>
   </si>
   <si>
-    <t xml:space="preserve">184.990447998047</t>
+    <t xml:space="preserve">184.990432739258</t>
   </si>
   <si>
     <t xml:space="preserve">184.039825439453</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">183.089202880859</t>
   </si>
   <si>
-    <t xml:space="preserve">181.568222045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.286758422852</t>
+    <t xml:space="preserve">181.568206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.286743164062</t>
   </si>
   <si>
     <t xml:space="preserve">178.050933837891</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">177.860809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">184.610198974609</t>
+    <t xml:space="preserve">184.610214233398</t>
   </si>
   <si>
     <t xml:space="preserve">189.838607788086</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">163.88671875</t>
   </si>
   <si>
-    <t xml:space="preserve">165.217559814453</t>
+    <t xml:space="preserve">165.217590332031</t>
   </si>
   <si>
     <t xml:space="preserve">164.932388305664</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">156.947189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">160.844711303711</t>
+    <t xml:space="preserve">160.8447265625</t>
   </si>
   <si>
     <t xml:space="preserve">164.266952514648</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">167.879302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">163.696594238281</t>
+    <t xml:space="preserve">163.696563720703</t>
   </si>
   <si>
     <t xml:space="preserve">161.605224609375</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">160.084213256836</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745971679688</t>
+    <t xml:space="preserve">162.745941162109</t>
   </si>
   <si>
     <t xml:space="preserve">160.179306030273</t>
   </si>
   <si>
-    <t xml:space="preserve">159.32373046875</t>
+    <t xml:space="preserve">159.323715209961</t>
   </si>
   <si>
     <t xml:space="preserve">158.468170166016</t>
@@ -2795,28 +2795,28 @@
     <t xml:space="preserve">158.848434448242</t>
   </si>
   <si>
-    <t xml:space="preserve">163.221267700195</t>
+    <t xml:space="preserve">163.221282958984</t>
   </si>
   <si>
     <t xml:space="preserve">159.038558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">159.608917236328</t>
+    <t xml:space="preserve">159.608901977539</t>
   </si>
   <si>
     <t xml:space="preserve">161.700286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">161.224990844727</t>
+    <t xml:space="preserve">161.224975585938</t>
   </si>
   <si>
     <t xml:space="preserve">153.810150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">152.859527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.528656005859</t>
+    <t xml:space="preserve">152.859512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.52864074707</t>
   </si>
   <si>
     <t xml:space="preserve">155.616317749023</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">154.570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">157.992858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.826217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.970672607422</t>
+    <t xml:space="preserve">157.992874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.826202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.970657348633</t>
   </si>
   <si>
     <t xml:space="preserve">179.001556396484</t>
@@ -2849,22 +2849,22 @@
     <t xml:space="preserve">171.111419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">170.541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.784255981445</t>
+    <t xml:space="preserve">170.541046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.784240722656</t>
   </si>
   <si>
     <t xml:space="preserve">167.499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">170.255844116211</t>
+    <t xml:space="preserve">170.255859375</t>
   </si>
   <si>
     <t xml:space="preserve">173.868194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">173.202774047852</t>
+    <t xml:space="preserve">173.202789306641</t>
   </si>
   <si>
     <t xml:space="preserve">175.389205932617</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">176.149703979492</t>
   </si>
   <si>
-    <t xml:space="preserve">177.195373535156</t>
+    <t xml:space="preserve">177.195343017578</t>
   </si>
   <si>
     <t xml:space="preserve">174.438583374023</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">156.18669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">151.813858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.99658203125</t>
+    <t xml:space="preserve">151.813842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.996566772461</t>
   </si>
   <si>
     <t xml:space="preserve">154.380523681641</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">155.901504516602</t>
   </si>
   <si>
-    <t xml:space="preserve">157.137313842773</t>
+    <t xml:space="preserve">157.137298583984</t>
   </si>
   <si>
     <t xml:space="preserve">154.000259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">150.197799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.057037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.155822753906</t>
+    <t xml:space="preserve">150.197784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.057067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.155807495117</t>
   </si>
   <si>
     <t xml:space="preserve">132.706405639648</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">133.181732177734</t>
   </si>
   <si>
-    <t xml:space="preserve">136.033584594727</t>
+    <t xml:space="preserve">136.033569335938</t>
   </si>
   <si>
     <t xml:space="preserve">133.276763916016</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">134.037261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">133.086639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.273101806641</t>
+    <t xml:space="preserve">133.086669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.273086547852</t>
   </si>
   <si>
     <t xml:space="preserve">132.136047363281</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">135.463195800781</t>
   </si>
   <si>
-    <t xml:space="preserve">133.229232788086</t>
+    <t xml:space="preserve">133.229248046875</t>
   </si>
   <si>
     <t xml:space="preserve">145.492248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">143.590972900391</t>
+    <t xml:space="preserve">143.59098815918</t>
   </si>
   <si>
     <t xml:space="preserve">141.784820556641</t>
@@ -2978,40 +2978,40 @@
     <t xml:space="preserve">148.058898925781</t>
   </si>
   <si>
-    <t xml:space="preserve">146.300247192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.016937255859</t>
+    <t xml:space="preserve">146.300231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.01692199707</t>
   </si>
   <si>
     <t xml:space="preserve">144.874313354492</t>
   </si>
   <si>
-    <t xml:space="preserve">136.984176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.794067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.324295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.274932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.894668579102</t>
+    <t xml:space="preserve">136.984191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.794052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.324310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.274948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.894683837891</t>
   </si>
   <si>
     <t xml:space="preserve">134.227386474609</t>
   </si>
   <si>
-    <t xml:space="preserve">131.660720825195</t>
+    <t xml:space="preserve">131.660736083984</t>
   </si>
   <si>
     <t xml:space="preserve">133.847152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">135.605773925781</t>
+    <t xml:space="preserve">135.60578918457</t>
   </si>
   <si>
     <t xml:space="preserve">131.423065185547</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">131.185424804688</t>
   </si>
   <si>
-    <t xml:space="preserve">134.655151367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.889129638672</t>
+    <t xml:space="preserve">134.655166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.889114379883</t>
   </si>
   <si>
     <t xml:space="preserve">137.031707763672</t>
@@ -3044,34 +3044,34 @@
     <t xml:space="preserve">137.84538269043</t>
   </si>
   <si>
-    <t xml:space="preserve">137.797515869141</t>
+    <t xml:space="preserve">137.79753112793</t>
   </si>
   <si>
     <t xml:space="preserve">138.084701538086</t>
   </si>
   <si>
-    <t xml:space="preserve">138.46760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.978729248047</t>
+    <t xml:space="preserve">138.467620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.978744506836</t>
   </si>
   <si>
     <t xml:space="preserve">133.059097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">132.963363647461</t>
+    <t xml:space="preserve">132.963348388672</t>
   </si>
   <si>
     <t xml:space="preserve">135.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">136.218063354492</t>
+    <t xml:space="preserve">136.218048095703</t>
   </si>
   <si>
     <t xml:space="preserve">137.510330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">138.659057617188</t>
+    <t xml:space="preserve">138.659072875977</t>
   </si>
   <si>
     <t xml:space="preserve">139.185546875</t>
@@ -3080,37 +3080,37 @@
     <t xml:space="preserve">143.2060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">144.306884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.01969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.269271850586</t>
+    <t xml:space="preserve">144.306900024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.019714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.269287109375</t>
   </si>
   <si>
     <t xml:space="preserve">145.790649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">147.322250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.843612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.226547241211</t>
+    <t xml:space="preserve">147.322235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.843627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.226531982422</t>
   </si>
   <si>
     <t xml:space="preserve">143.397491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">147.99235534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.428237915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.289749145508</t>
+    <t xml:space="preserve">147.992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.42822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.289764404297</t>
   </si>
   <si>
     <t xml:space="preserve">153.065811157227</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">152.682922363281</t>
   </si>
   <si>
-    <t xml:space="preserve">150.768402099609</t>
+    <t xml:space="preserve">150.76838684082</t>
   </si>
   <si>
     <t xml:space="preserve">151.534210205078</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">149.906860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">153.879501342773</t>
+    <t xml:space="preserve">153.879486083984</t>
   </si>
   <si>
     <t xml:space="preserve">156.320495605469</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">152.395721435547</t>
   </si>
   <si>
-    <t xml:space="preserve">153.783737182617</t>
+    <t xml:space="preserve">153.783752441406</t>
   </si>
   <si>
     <t xml:space="preserve">155.123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">155.458953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.028198242188</t>
+    <t xml:space="preserve">155.458969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.028182983398</t>
   </si>
   <si>
     <t xml:space="preserve">155.650436401367</t>
@@ -3173,19 +3173,19 @@
     <t xml:space="preserve">161.729019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">160.91535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.35124206543</t>
+    <t xml:space="preserve">160.915344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.351226806641</t>
   </si>
   <si>
     <t xml:space="preserve">165.07942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">163.834976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.908462524414</t>
+    <t xml:space="preserve">163.834991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.908477783203</t>
   </si>
   <si>
     <t xml:space="preserve">164.600799560547</t>
@@ -3203,10 +3203,10 @@
     <t xml:space="preserve">168.669143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">168.334106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.052047729492</t>
+    <t xml:space="preserve">168.334121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.052062988281</t>
   </si>
   <si>
     <t xml:space="preserve">171.158020019531</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">176.0400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">176.949447631836</t>
+    <t xml:space="preserve">176.949462890625</t>
   </si>
   <si>
     <t xml:space="preserve">177.140899658203</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">179.534057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">178.05029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.475921630859</t>
+    <t xml:space="preserve">178.050308227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.475936889648</t>
   </si>
   <si>
     <t xml:space="preserve">177.810989379883</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">192.409194946289</t>
   </si>
   <si>
-    <t xml:space="preserve">193.270736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.568130493164</t>
+    <t xml:space="preserve">193.270721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.568161010742</t>
   </si>
   <si>
     <t xml:space="preserve">191.643371582031</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">196.812606811523</t>
   </si>
   <si>
-    <t xml:space="preserve">197.386947631836</t>
+    <t xml:space="preserve">197.386917114258</t>
   </si>
   <si>
     <t xml:space="preserve">188.29296875</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">195.855331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">194.515167236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.479309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180.539184570312</t>
+    <t xml:space="preserve">194.515151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.479293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180.539169311523</t>
   </si>
   <si>
     <t xml:space="preserve">174.987060546875</t>
@@ -3311,22 +3311,22 @@
     <t xml:space="preserve">173.599044799805</t>
   </si>
   <si>
-    <t xml:space="preserve">167.664016723633</t>
+    <t xml:space="preserve">167.664031982422</t>
   </si>
   <si>
     <t xml:space="preserve">164.505065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">165.462356567383</t>
+    <t xml:space="preserve">165.462341308594</t>
   </si>
   <si>
     <t xml:space="preserve">162.781997680664</t>
   </si>
   <si>
-    <t xml:space="preserve">163.404220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.744400024414</t>
+    <t xml:space="preserve">163.404205322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.744384765625</t>
   </si>
   <si>
     <t xml:space="preserve">162.111923217773</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">166.51530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">170.870834350586</t>
+    <t xml:space="preserve">170.870849609375</t>
   </si>
   <si>
     <t xml:space="preserve">171.25373840332</t>
@@ -3353,25 +3353,25 @@
     <t xml:space="preserve">177.715240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">181.44856262207</t>
+    <t xml:space="preserve">181.448577880859</t>
   </si>
   <si>
     <t xml:space="preserve">180.826354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">182.884460449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.83659362793</t>
+    <t xml:space="preserve">182.88444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.836578369141</t>
   </si>
   <si>
     <t xml:space="preserve">179.34260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">187.096389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.000686645508</t>
+    <t xml:space="preserve">187.096405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.000671386719</t>
   </si>
   <si>
     <t xml:space="preserve">188.723724365234</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">177.093032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">179.964828491211</t>
+    <t xml:space="preserve">179.964813232422</t>
   </si>
   <si>
     <t xml:space="preserve">180.874206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">183.506683349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.896469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.61442565918</t>
+    <t xml:space="preserve">183.50666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.896453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.614410400391</t>
   </si>
   <si>
     <t xml:space="preserve">175.800720214844</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">171.636657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">169.865707397461</t>
+    <t xml:space="preserve">169.86572265625</t>
   </si>
   <si>
     <t xml:space="preserve">179.294738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">177.188781738281</t>
+    <t xml:space="preserve">177.188751220703</t>
   </si>
   <si>
     <t xml:space="preserve">180.682754516602</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">175.082778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">170.296478271484</t>
+    <t xml:space="preserve">170.296493530273</t>
   </si>
   <si>
     <t xml:space="preserve">169.147766113281</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">167.472564697266</t>
   </si>
   <si>
-    <t xml:space="preserve">170.392227172852</t>
+    <t xml:space="preserve">170.392211914062</t>
   </si>
   <si>
     <t xml:space="preserve">172.306747436523</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">172.928955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">168.764877319336</t>
+    <t xml:space="preserve">168.764862060547</t>
   </si>
   <si>
     <t xml:space="preserve">172.785369873047</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">170.53581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">152.060684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.688049316406</t>
+    <t xml:space="preserve">152.060699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.688034057617</t>
   </si>
   <si>
     <t xml:space="preserve">153.400863647461</t>
@@ -3476,22 +3476,22 @@
     <t xml:space="preserve">154.932479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">154.741012573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.240158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.947830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.293121337891</t>
+    <t xml:space="preserve">154.741027832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.240142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.947845458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.29313659668</t>
   </si>
   <si>
     <t xml:space="preserve">156.22477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">152.156433105469</t>
+    <t xml:space="preserve">152.15641784668</t>
   </si>
   <si>
     <t xml:space="preserve">153.640167236328</t>
@@ -3500,31 +3500,31 @@
     <t xml:space="preserve">148.183792114258</t>
   </si>
   <si>
-    <t xml:space="preserve">141.770156860352</t>
+    <t xml:space="preserve">141.770172119141</t>
   </si>
   <si>
     <t xml:space="preserve">143.780395507812</t>
   </si>
   <si>
-    <t xml:space="preserve">147.609436035156</t>
+    <t xml:space="preserve">147.609451293945</t>
   </si>
   <si>
     <t xml:space="preserve">141.387237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">139.85563659668</t>
+    <t xml:space="preserve">139.855651855469</t>
   </si>
   <si>
     <t xml:space="preserve">141.91374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">137.223175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.946243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.717178344727</t>
+    <t xml:space="preserve">137.223190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.946228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.717163085938</t>
   </si>
   <si>
     <t xml:space="preserve">128.94287109375</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">126.884773254395</t>
   </si>
   <si>
-    <t xml:space="preserve">128.990737915039</t>
+    <t xml:space="preserve">128.99072265625</t>
   </si>
   <si>
     <t xml:space="preserve">129.325759887695</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">131.048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">131.144592285156</t>
+    <t xml:space="preserve">131.144577026367</t>
   </si>
   <si>
     <t xml:space="preserve">132.006103515625</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">127.698432922363</t>
   </si>
   <si>
-    <t xml:space="preserve">125.975372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.518981933594</t>
+    <t xml:space="preserve">125.975379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.518989562988</t>
   </si>
   <si>
     <t xml:space="preserve">119.41813659668</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">120.662582397461</t>
   </si>
   <si>
-    <t xml:space="preserve">117.934387207031</t>
+    <t xml:space="preserve">117.934379577637</t>
   </si>
   <si>
     <t xml:space="preserve">114.631843566895</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">116.546371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">115.589096069336</t>
+    <t xml:space="preserve">115.58910369873</t>
   </si>
   <si>
     <t xml:space="preserve">112.286560058594</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">112.430145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">116.211318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.136085510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.103591918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.864273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.937728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.124084472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.77367401123</t>
+    <t xml:space="preserve">116.211326599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.136093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.10359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.864280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.937744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.124069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.773681640625</t>
   </si>
   <si>
     <t xml:space="preserve">123.15145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">120.088218688965</t>
+    <t xml:space="preserve">120.08821105957</t>
   </si>
   <si>
     <t xml:space="preserve">122.242050170898</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">117.503616333008</t>
   </si>
   <si>
-    <t xml:space="preserve">120.806159973145</t>
+    <t xml:space="preserve">120.806167602539</t>
   </si>
   <si>
     <t xml:space="preserve">115.541236877441</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">131.718933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">132.293273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.693313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.597602844238</t>
+    <t xml:space="preserve">132.29328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.693321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.597579956055</t>
   </si>
   <si>
     <t xml:space="preserve">125.257431030273</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">124.204452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">125.448883056641</t>
+    <t xml:space="preserve">125.448875427246</t>
   </si>
   <si>
     <t xml:space="preserve">133.824905395508</t>
@@ -3665,22 +3665,22 @@
     <t xml:space="preserve">139.329147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">139.616333007812</t>
+    <t xml:space="preserve">139.616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">142.105194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">139.041976928711</t>
+    <t xml:space="preserve">139.041946411133</t>
   </si>
   <si>
     <t xml:space="preserve">136.170181274414</t>
   </si>
   <si>
-    <t xml:space="preserve">135.260787963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.628326416016</t>
+    <t xml:space="preserve">135.260803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.628341674805</t>
   </si>
   <si>
     <t xml:space="preserve">129.038604736328</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">129.086471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">128.559982299805</t>
+    <t xml:space="preserve">128.559951782227</t>
   </si>
   <si>
     <t xml:space="preserve">128.416381835938</t>
@@ -3701,25 +3701,25 @@
     <t xml:space="preserve">124.539482116699</t>
   </si>
   <si>
-    <t xml:space="preserve">120.997627258301</t>
+    <t xml:space="preserve">120.997619628906</t>
   </si>
   <si>
     <t xml:space="preserve">118.7001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">115.254058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.652336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.70532989502</t>
+    <t xml:space="preserve">115.254066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.652328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.705322265625</t>
   </si>
   <si>
     <t xml:space="preserve">118.173698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">117.64720916748</t>
+    <t xml:space="preserve">117.647216796875</t>
   </si>
   <si>
     <t xml:space="preserve">114.392532348633</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">114.823295593262</t>
   </si>
   <si>
-    <t xml:space="preserve">115.493385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.271186828613</t>
+    <t xml:space="preserve">115.493377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.271194458008</t>
   </si>
   <si>
     <t xml:space="preserve">106.590858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">109.654090881348</t>
+    <t xml:space="preserve">109.654098510742</t>
   </si>
   <si>
     <t xml:space="preserve">107.165222167969</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">114.871154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">113.435272216797</t>
+    <t xml:space="preserve">113.435264587402</t>
   </si>
   <si>
     <t xml:space="preserve">110.563491821289</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">112.995140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">111.884506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.932800292969</t>
+    <t xml:space="preserve">111.884498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.932792663574</t>
   </si>
   <si>
     <t xml:space="preserve">113.381454467773</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">119.803825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">116.278755187988</t>
+    <t xml:space="preserve">116.278762817383</t>
   </si>
   <si>
     <t xml:space="preserve">118.258583068848</t>
@@ -3797,31 +3797,31 @@
     <t xml:space="preserve">117.727416992188</t>
   </si>
   <si>
-    <t xml:space="preserve">118.74146270752</t>
+    <t xml:space="preserve">118.741470336914</t>
   </si>
   <si>
     <t xml:space="preserve">115.071548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">111.787925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.918731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.683410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.657127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.904670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.685234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.801986694336</t>
+    <t xml:space="preserve">111.787933349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.918724060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.683403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.657119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.904678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.685241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.80199432373</t>
   </si>
   <si>
     <t xml:space="preserve">113.912620544434</t>
@@ -3830,46 +3830,46 @@
     <t xml:space="preserve">113.526321411133</t>
   </si>
   <si>
-    <t xml:space="preserve">120.190124511719</t>
+    <t xml:space="preserve">120.190132141113</t>
   </si>
   <si>
     <t xml:space="preserve">123.377166748047</t>
   </si>
   <si>
-    <t xml:space="preserve">122.797714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.604545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.866172790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.914451599121</t>
+    <t xml:space="preserve">122.797706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.604553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.866180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.914459228516</t>
   </si>
   <si>
     <t xml:space="preserve">122.025093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">126.564224243164</t>
+    <t xml:space="preserve">126.56421661377</t>
   </si>
   <si>
     <t xml:space="preserve">127.578285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">129.799530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.668731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.151641845703</t>
+    <t xml:space="preserve">129.799545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.668746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.151626586914</t>
   </si>
   <si>
     <t xml:space="preserve">131.537933349609</t>
   </si>
   <si>
-    <t xml:space="preserve">125.598457336426</t>
+    <t xml:space="preserve">125.598449707031</t>
   </si>
   <si>
     <t xml:space="preserve">127.964584350586</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">124.970687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">127.916290283203</t>
+    <t xml:space="preserve">127.916297912598</t>
   </si>
   <si>
     <t xml:space="preserve">127.674842834473</t>
@@ -3893,34 +3893,34 @@
     <t xml:space="preserve">135.497589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">136.077056884766</t>
+    <t xml:space="preserve">136.077041625977</t>
   </si>
   <si>
     <t xml:space="preserve">132.841720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">128.785491943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.936454772949</t>
+    <t xml:space="preserve">128.785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.936462402344</t>
   </si>
   <si>
     <t xml:space="preserve">130.234146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">130.958480834961</t>
+    <t xml:space="preserve">130.958465576172</t>
   </si>
   <si>
     <t xml:space="preserve">130.861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">128.640609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.137573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.787322998047</t>
+    <t xml:space="preserve">128.640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.137557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.787338256836</t>
   </si>
   <si>
     <t xml:space="preserve">132.213958740234</t>
@@ -3944,34 +3944,34 @@
     <t xml:space="preserve">130.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">132.020812988281</t>
+    <t xml:space="preserve">132.02082824707</t>
   </si>
   <si>
     <t xml:space="preserve">131.489639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">132.310562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.515922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.86799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.467636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.888191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.171798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.061157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.930358886719</t>
+    <t xml:space="preserve">132.310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.515914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.868011474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.888168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.171783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.061172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.93034362793</t>
   </si>
   <si>
     <t xml:space="preserve">126.226188659668</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">131.972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">125.115562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473747253418</t>
+    <t xml:space="preserve">125.11555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473754882812</t>
   </si>
   <si>
     <t xml:space="preserve">121.397338867188</t>
   </si>
   <si>
-    <t xml:space="preserve">120.721305847168</t>
+    <t xml:space="preserve">120.721298217773</t>
   </si>
   <si>
     <t xml:space="preserve">123.135734558105</t>
@@ -4007,34 +4007,34 @@
     <t xml:space="preserve">112.463966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">111.64306640625</t>
+    <t xml:space="preserve">111.643051147461</t>
   </si>
   <si>
     <t xml:space="preserve">110.822158813477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.779975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.870452880859</t>
+    <t xml:space="preserve">107.779983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.870445251465</t>
   </si>
   <si>
     <t xml:space="preserve">110.097831726074</t>
   </si>
   <si>
-    <t xml:space="preserve">113.816047668457</t>
+    <t xml:space="preserve">113.816040039062</t>
   </si>
   <si>
     <t xml:space="preserve">111.305038452148</t>
   </si>
   <si>
-    <t xml:space="preserve">108.504302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.132057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.974967956543</t>
+    <t xml:space="preserve">108.50431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.132064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.974975585938</t>
   </si>
   <si>
     <t xml:space="preserve">123.763473510742</t>
@@ -4043,34 +4043,34 @@
     <t xml:space="preserve">121.687072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">124.584381103516</t>
+    <t xml:space="preserve">124.58438873291</t>
   </si>
   <si>
     <t xml:space="preserve">125.64673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">131.586227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.344772338867</t>
+    <t xml:space="preserve">131.586212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.344787597656</t>
   </si>
   <si>
     <t xml:space="preserve">121.300765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">124.680961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.771430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.660781860352</t>
+    <t xml:space="preserve">124.680969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.771423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.660789489746</t>
   </si>
   <si>
     <t xml:space="preserve">124.922416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">122.314819335938</t>
+    <t xml:space="preserve">122.314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">124.777534484863</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">133.517761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">130.76530456543</t>
+    <t xml:space="preserve">130.765319824219</t>
   </si>
   <si>
     <t xml:space="preserve">128.302612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">126.612503051758</t>
+    <t xml:space="preserve">126.612518310547</t>
   </si>
   <si>
     <t xml:space="preserve">128.206024169922</t>
@@ -4103,31 +4103,31 @@
     <t xml:space="preserve">127.047096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">124.487800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.240249633789</t>
+    <t xml:space="preserve">124.487808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.240257263184</t>
   </si>
   <si>
     <t xml:space="preserve">129.316665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">128.157745361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.26042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.509826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.682815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.435241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.84782409668</t>
+    <t xml:space="preserve">128.157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.260429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.682800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.435256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.847839355469</t>
   </si>
   <si>
     <t xml:space="preserve">125.067268371582</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">120.286712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.783653259277</t>
+    <t xml:space="preserve">123.42546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.783645629883</t>
   </si>
   <si>
     <t xml:space="preserve">123.522041320801</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">122.652847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">127.62654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.874114990234</t>
+    <t xml:space="preserve">127.626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.874122619629</t>
   </si>
   <si>
     <t xml:space="preserve">125.405296325684</t>
@@ -4169,13 +4169,13 @@
     <t xml:space="preserve">123.232307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">121.880218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.218246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.14183807373</t>
+    <t xml:space="preserve">121.880226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.218254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.141845703125</t>
   </si>
   <si>
     <t xml:space="preserve">125.550155639648</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">115.168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.188285827637</t>
+    <t xml:space="preserve">113.188293457031</t>
   </si>
   <si>
     <t xml:space="preserve">115.651008605957</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">117.196243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">117.775703430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.906517028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.250640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.415672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.236587524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.319107055664</t>
+    <t xml:space="preserve">117.775695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.415679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.23657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.31909942627</t>
   </si>
   <si>
     <t xml:space="preserve">112.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.077659606934</t>
+    <t xml:space="preserve">112.077667236328</t>
   </si>
   <si>
     <t xml:space="preserve">109.42179107666</t>
   </si>
   <si>
-    <t xml:space="preserve">111.063598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.242691040039</t>
+    <t xml:space="preserve">111.063606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.242698669434</t>
   </si>
   <si>
     <t xml:space="preserve">107.20051574707</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">108.649169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">108.842315673828</t>
+    <t xml:space="preserve">108.842330932617</t>
   </si>
   <si>
     <t xml:space="preserve">108.118003845215</t>
@@ -4265,13 +4265,13 @@
     <t xml:space="preserve">105.993301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">104.303199768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.013465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.937065124512</t>
+    <t xml:space="preserve">104.303207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.013473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.937072753906</t>
   </si>
   <si>
     <t xml:space="preserve">103.675453186035</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">97.7359619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9431762695312</t>
+    <t xml:space="preserve">98.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">97.5911026000977</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">98.5568771362305</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6455078125</t>
+    <t xml:space="preserve">94.6455001831055</t>
   </si>
   <si>
     <t xml:space="preserve">96.5770416259766</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">93.737678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6797332763672</t>
+    <t xml:space="preserve">93.6797256469727</t>
   </si>
   <si>
     <t xml:space="preserve">96.2100601196289</t>
@@ -4319,22 +4319,22 @@
     <t xml:space="preserve">95.7851028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7078475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9887771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5251998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9694671630859</t>
+    <t xml:space="preserve">95.7078552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9887847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5252075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9694595336914</t>
   </si>
   <si>
     <t xml:space="preserve">94.0467224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8342666625977</t>
+    <t xml:space="preserve">93.8342514038086</t>
   </si>
   <si>
     <t xml:space="preserve">95.5340118408203</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">93.1582183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1090698242188</t>
+    <t xml:space="preserve">95.1090774536133</t>
   </si>
   <si>
     <t xml:space="preserve">94.3750915527344</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">98.0739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1222763061523</t>
+    <t xml:space="preserve">98.1222686767578</t>
   </si>
   <si>
     <t xml:space="preserve">98.8948974609375</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">100.408088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2853851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6885528564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6299743652344</t>
+    <t xml:space="preserve">99.2853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6885452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.6299819946289</t>
   </si>
   <si>
     <t xml:space="preserve">96.8642730712891</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">95.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6384048461914</t>
+    <t xml:space="preserve">94.6384124755859</t>
   </si>
   <si>
     <t xml:space="preserve">94.4236297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0679626464844</t>
+    <t xml:space="preserve">95.0679550170898</t>
   </si>
   <si>
     <t xml:space="preserve">95.1265411376953</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">95.4389419555664</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3579483032227</t>
+    <t xml:space="preserve">98.3579559326172</t>
   </si>
   <si>
     <t xml:space="preserve">96.6104431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4779891967773</t>
+    <t xml:space="preserve">95.4779968261719</t>
   </si>
   <si>
     <t xml:space="preserve">94.7946090698242</t>
@@ -4469,16 +4469,16 @@
     <t xml:space="preserve">90.8700561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4405059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1349716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3777084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.084831237793</t>
+    <t xml:space="preserve">90.4404983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1349792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3777008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0848388671875</t>
   </si>
   <si>
     <t xml:space="preserve">91.5534362792969</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">90.1280975341797</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7054138183594</t>
+    <t xml:space="preserve">92.7054214477539</t>
   </si>
   <si>
     <t xml:space="preserve">92.1196670532227</t>
   </si>
   <si>
-    <t xml:space="preserve">91.5729675292969</t>
+    <t xml:space="preserve">91.5729598999023</t>
   </si>
   <si>
     <t xml:space="preserve">90.0109405517578</t>
@@ -4523,19 +4523,19 @@
     <t xml:space="preserve">91.7877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2716445922852</t>
+    <t xml:space="preserve">93.2716522216797</t>
   </si>
   <si>
     <t xml:space="preserve">93.6816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3091354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6270904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3413162231445</t>
+    <t xml:space="preserve">98.3091278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.627082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3413238525391</t>
   </si>
   <si>
     <t xml:space="preserve">92.9397201538086</t>
@@ -4547,13 +4547,13 @@
     <t xml:space="preserve">91.7682113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5492172241211</t>
+    <t xml:space="preserve">92.5492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">92.6273193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">89.11279296875</t>
+    <t xml:space="preserve">89.1127853393555</t>
   </si>
   <si>
     <t xml:space="preserve">88.1365280151367</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">87.1016998291016</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6679382324219</t>
+    <t xml:space="preserve">87.6679306030273</t>
   </si>
   <si>
     <t xml:space="preserve">87.3164825439453</t>
@@ -4577,10 +4577,10 @@
     <t xml:space="preserve">90.9676818847656</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8114700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4906387329102</t>
+    <t xml:space="preserve">90.8114776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4906463623047</t>
   </si>
   <si>
     <t xml:space="preserve">92.8225708007812</t>
@@ -4589,10 +4589,10 @@
     <t xml:space="preserve">94.4626846313477</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0721740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7444686889648</t>
+    <t xml:space="preserve">94.0721817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7444763183594</t>
   </si>
   <si>
     <t xml:space="preserve">91.1238784790039</t>
@@ -4607,13 +4607,13 @@
     <t xml:space="preserve">90.6357498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5032958984375</t>
+    <t xml:space="preserve">89.503288269043</t>
   </si>
   <si>
     <t xml:space="preserve">90.303825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9328536987305</t>
+    <t xml:space="preserve">89.9328460693359</t>
   </si>
   <si>
     <t xml:space="preserve">88.8003921508789</t>
@@ -4625,22 +4625,22 @@
     <t xml:space="preserve">88.1755828857422</t>
   </si>
   <si>
-    <t xml:space="preserve">85.207763671875</t>
+    <t xml:space="preserve">85.2077560424805</t>
   </si>
   <si>
     <t xml:space="preserve">84.4853286743164</t>
   </si>
   <si>
-    <t xml:space="preserve">83.9581451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.8061599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7866516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5132904052734</t>
+    <t xml:space="preserve">83.9581527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7866439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5132827758789</t>
   </si>
   <si>
     <t xml:space="preserve">84.2314987182617</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">84.8563079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3053817749023</t>
+    <t xml:space="preserve">85.3053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">85.6373138427734</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">86.4378433227539</t>
   </si>
   <si>
-    <t xml:space="preserve">83.4700241088867</t>
+    <t xml:space="preserve">83.4700164794922</t>
   </si>
   <si>
     <t xml:space="preserve">81.5175094604492</t>
@@ -4691,16 +4691,16 @@
     <t xml:space="preserve">82.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8146057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0531234741211</t>
+    <t xml:space="preserve">80.8145980834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.0531158447266</t>
   </si>
   <si>
     <t xml:space="preserve">80.4436264038086</t>
   </si>
   <si>
-    <t xml:space="preserve">80.131217956543</t>
+    <t xml:space="preserve">80.1312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">82.493766784668</t>
@@ -4721,10 +4721,10 @@
     <t xml:space="preserve">85.5006408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7892990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2816390991211</t>
+    <t xml:space="preserve">86.789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2816467285156</t>
   </si>
   <si>
     <t xml:space="preserve">83.1185684204102</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">88.8394393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2969512939453</t>
+    <t xml:space="preserve">87.2969436645508</t>
   </si>
   <si>
     <t xml:space="preserve">84.3096008300781</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">86.6916732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4183120727539</t>
+    <t xml:space="preserve">86.4183197021484</t>
   </si>
   <si>
     <t xml:space="preserve">85.98876953125</t>
@@ -4781,13 +4781,13 @@
     <t xml:space="preserve">89.6985397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8589553833008</t>
+    <t xml:space="preserve">88.8589630126953</t>
   </si>
   <si>
     <t xml:space="preserve">87.6093521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9064483642578</t>
+    <t xml:space="preserve">86.9064407348633</t>
   </si>
   <si>
     <t xml:space="preserve">86.3402252197266</t>
@@ -4814,16 +4814,16 @@
     <t xml:space="preserve">90.9481582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9872055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0262603759766</t>
+    <t xml:space="preserve">90.9871978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.026252746582</t>
   </si>
   <si>
     <t xml:space="preserve">87.8436584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6135787963867</t>
+    <t xml:space="preserve">86.6135711669922</t>
   </si>
   <si>
     <t xml:space="preserve">87.2774276733398</t>
@@ -4832,13 +4832,13 @@
     <t xml:space="preserve">88.4294128417969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.7808685302734</t>
+    <t xml:space="preserve">88.7808609008789</t>
   </si>
   <si>
     <t xml:space="preserve">88.2341613769531</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5117263793945</t>
+    <t xml:space="preserve">87.5117340087891</t>
   </si>
   <si>
     <t xml:space="preserve">87.121223449707</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">85.9106674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1296539306641</t>
+    <t xml:space="preserve">85.1296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">84.0167236328125</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">82.6304397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">84.3877105712891</t>
+    <t xml:space="preserve">84.3877029418945</t>
   </si>
   <si>
     <t xml:space="preserve">84.3486557006836</t>
@@ -4874,10 +4874,10 @@
     <t xml:space="preserve">83.8605270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4547119140625</t>
+    <t xml:space="preserve">83.0014114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.454719543457</t>
   </si>
   <si>
     <t xml:space="preserve">82.9428405761719</t>
@@ -4889,7 +4889,7 @@
     <t xml:space="preserve">84.9344100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">84.055778503418</t>
+    <t xml:space="preserve">84.0557708740234</t>
   </si>
   <si>
     <t xml:space="preserve">84.8953552246094</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">85.6958923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7001113891602</t>
+    <t xml:space="preserve">84.7001037597656</t>
   </si>
   <si>
     <t xml:space="preserve">84.7196350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2578964233398</t>
+    <t xml:space="preserve">87.2579040527344</t>
   </si>
   <si>
     <t xml:space="preserve">88.1170120239258</t>
@@ -4928,19 +4928,19 @@
     <t xml:space="preserve">92.3149108886719</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2843017578125</t>
+    <t xml:space="preserve">90.284309387207</t>
   </si>
   <si>
     <t xml:space="preserve">91.7096405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8310012817383</t>
+    <t xml:space="preserve">90.8310089111328</t>
   </si>
   <si>
     <t xml:space="preserve">91.4753341674805</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4125518798828</t>
+    <t xml:space="preserve">92.4125442504883</t>
   </si>
   <si>
     <t xml:space="preserve">94.5017395019531</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">91.2605667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4515838623047</t>
+    <t xml:space="preserve">92.4515914916992</t>
   </si>
   <si>
     <t xml:space="preserve">89.6399765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9259719848633</t>
+    <t xml:space="preserve">86.9259796142578</t>
   </si>
   <si>
     <t xml:space="preserve">86.0863952636719</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">84.1338806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9275360107422</t>
+    <t xml:space="preserve">81.9275283813477</t>
   </si>
   <si>
     <t xml:space="preserve">81.3222579956055</t>
@@ -4988,22 +4988,22 @@
     <t xml:space="preserve">83.7238464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6721420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4225387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4615936279297</t>
+    <t xml:space="preserve">86.6721496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4225311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4615859985352</t>
   </si>
   <si>
     <t xml:space="preserve">85.2858581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4098815917969</t>
+    <t xml:space="preserve">88.4098892211914</t>
   </si>
   <si>
     <t xml:space="preserve">87.4531555175781</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">92.6858978271484</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5840530395508</t>
+    <t xml:space="preserve">93.5840454101562</t>
   </si>
   <si>
     <t xml:space="preserve">93.7402496337891</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">91.4362869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6468505859375</t>
+    <t xml:space="preserve">92.646842956543</t>
   </si>
   <si>
     <t xml:space="preserve">93.9550247192383</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">90.7724304199219</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6510543823242</t>
+    <t xml:space="preserve">91.6510620117188</t>
   </si>
   <si>
     <t xml:space="preserve">91.1043548583984</t>
@@ -5469,9 +5469,6 @@
   </si>
   <si>
     <t xml:space="preserve">95.2035980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.627082824707</t>
   </si>
   <si>
     <t xml:space="preserve">97.6128234863281</t>
@@ -67122,7 +67119,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G2337" t="s">
-        <v>1819</v>
+        <v>1506</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67174,7 +67171,7 @@
         <v>98.8600006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67200,7 +67197,7 @@
         <v>98.0599975585938</v>
       </c>
       <c r="G2340" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67226,7 +67223,7 @@
         <v>95.4400024414062</v>
       </c>
       <c r="G2341" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67252,7 +67249,7 @@
         <v>95.1600036621094</v>
       </c>
       <c r="G2342" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67278,7 +67275,7 @@
         <v>95.9400024414062</v>
       </c>
       <c r="G2343" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67304,7 +67301,7 @@
         <v>95.5400009155273</v>
       </c>
       <c r="G2344" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67330,7 +67327,7 @@
         <v>94.0999984741211</v>
       </c>
       <c r="G2345" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67356,7 +67353,7 @@
         <v>94.9800033569336</v>
       </c>
       <c r="G2346" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67382,7 +67379,7 @@
         <v>95.5800018310547</v>
       </c>
       <c r="G2347" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67408,7 +67405,7 @@
         <v>94.9400024414062</v>
       </c>
       <c r="G2348" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67434,7 +67431,7 @@
         <v>94.5199966430664</v>
       </c>
       <c r="G2349" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67460,7 +67457,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2350" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67486,7 +67483,7 @@
         <v>93.6800003051758</v>
       </c>
       <c r="G2351" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67512,7 +67509,7 @@
         <v>91.5</v>
       </c>
       <c r="G2352" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67538,7 +67535,7 @@
         <v>92.0800018310547</v>
       </c>
       <c r="G2353" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67564,7 +67561,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2354" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67590,7 +67587,7 @@
         <v>91.7399978637695</v>
       </c>
       <c r="G2355" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67642,7 +67639,7 @@
         <v>90.7600021362305</v>
       </c>
       <c r="G2357" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -67668,7 +67665,7 @@
         <v>93.7200012207031</v>
       </c>
       <c r="G2358" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67694,7 +67691,7 @@
         <v>90.7200012207031</v>
       </c>
       <c r="G2359" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67720,7 +67717,7 @@
         <v>91.5400009155273</v>
       </c>
       <c r="G2360" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67746,7 +67743,7 @@
         <v>94.5</v>
       </c>
       <c r="G2361" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67772,7 +67769,7 @@
         <v>96.0800018310547</v>
       </c>
       <c r="G2362" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67824,7 +67821,7 @@
         <v>98.120002746582</v>
       </c>
       <c r="G2364" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67850,7 +67847,7 @@
         <v>97.9199981689453</v>
       </c>
       <c r="G2365" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67876,7 +67873,7 @@
         <v>97.879997253418</v>
       </c>
       <c r="G2366" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67902,7 +67899,7 @@
         <v>98.4800033569336</v>
       </c>
       <c r="G2367" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67954,7 +67951,7 @@
         <v>99.0400009155273</v>
       </c>
       <c r="G2369" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -68006,7 +68003,7 @@
         <v>99.3399963378906</v>
       </c>
       <c r="G2371" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -68058,7 +68055,7 @@
         <v>99</v>
       </c>
       <c r="G2373" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68110,7 +68107,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G2375" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68136,7 +68133,7 @@
         <v>95.6999969482422</v>
       </c>
       <c r="G2376" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68188,7 +68185,7 @@
         <v>95.379997253418</v>
       </c>
       <c r="G2378" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68214,7 +68211,7 @@
         <v>96.6999969482422</v>
       </c>
       <c r="G2379" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68240,7 +68237,7 @@
         <v>96.620002746582</v>
       </c>
       <c r="G2380" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68266,7 +68263,7 @@
         <v>94.6999969482422</v>
       </c>
       <c r="G2381" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68292,7 +68289,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2382" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68318,7 +68315,7 @@
         <v>95.120002746582</v>
       </c>
       <c r="G2383" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68344,7 +68341,7 @@
         <v>93.9599990844727</v>
       </c>
       <c r="G2384" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68370,7 +68367,7 @@
         <v>93.620002746582</v>
       </c>
       <c r="G2385" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68396,7 +68393,7 @@
         <v>92.9800033569336</v>
       </c>
       <c r="G2386" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68422,7 +68419,7 @@
         <v>91.7200012207031</v>
       </c>
       <c r="G2387" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68448,7 +68445,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2388" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68474,7 +68471,7 @@
         <v>91.2200012207031</v>
       </c>
       <c r="G2389" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68500,7 +68497,7 @@
         <v>91.5999984741211</v>
       </c>
       <c r="G2390" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68526,7 +68523,7 @@
         <v>91.0400009155273</v>
       </c>
       <c r="G2391" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68552,7 +68549,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2392" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68578,7 +68575,7 @@
         <v>91.3600006103516</v>
       </c>
       <c r="G2393" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68604,7 +68601,7 @@
         <v>90.4000015258789</v>
       </c>
       <c r="G2394" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68630,7 +68627,7 @@
         <v>90.3000030517578</v>
       </c>
       <c r="G2395" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68656,7 +68653,7 @@
         <v>90.9400024414062</v>
       </c>
       <c r="G2396" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68682,7 +68679,7 @@
         <v>91.0599975585938</v>
       </c>
       <c r="G2397" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68708,7 +68705,7 @@
         <v>92.120002746582</v>
       </c>
       <c r="G2398" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68734,7 +68731,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G2399" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68760,7 +68757,7 @@
         <v>95.0999984741211</v>
       </c>
       <c r="G2400" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68786,7 +68783,7 @@
         <v>94.5800018310547</v>
       </c>
       <c r="G2401" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68812,7 +68809,7 @@
         <v>94.379997253418</v>
       </c>
       <c r="G2402" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68838,7 +68835,7 @@
         <v>93.3199996948242</v>
       </c>
       <c r="G2403" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68864,7 +68861,7 @@
         <v>93.9800033569336</v>
       </c>
       <c r="G2404" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68890,7 +68887,7 @@
         <v>93.4400024414062</v>
       </c>
       <c r="G2405" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68916,7 +68913,7 @@
         <v>93.5800018310547</v>
       </c>
       <c r="G2406" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68942,7 +68939,7 @@
         <v>93.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68968,7 +68965,7 @@
         <v>94.3600006103516</v>
       </c>
       <c r="G2408" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68994,7 +68991,7 @@
         <v>94</v>
       </c>
       <c r="G2409" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -69020,7 +69017,7 @@
         <v>94.6800003051758</v>
       </c>
       <c r="G2410" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -69046,7 +69043,7 @@
         <v>93.6600036621094</v>
       </c>
       <c r="G2411" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -69072,7 +69069,7 @@
         <v>94</v>
       </c>
       <c r="G2412" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -69098,7 +69095,7 @@
         <v>92.0400009155273</v>
       </c>
       <c r="G2413" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69124,7 +69121,7 @@
         <v>90.8600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69150,7 +69147,7 @@
         <v>91.6600036621094</v>
       </c>
       <c r="G2415" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69176,7 +69173,7 @@
         <v>91.3000030517578</v>
       </c>
       <c r="G2416" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69202,7 +69199,7 @@
         <v>90.3399963378906</v>
       </c>
       <c r="G2417" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69228,7 +69225,7 @@
         <v>90.2799987792969</v>
       </c>
       <c r="G2418" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69254,7 +69251,7 @@
         <v>89.2799987792969</v>
       </c>
       <c r="G2419" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69280,7 +69277,7 @@
         <v>89.1800003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69306,7 +69303,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2421" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69332,7 +69329,7 @@
         <v>91.0800018310547</v>
       </c>
       <c r="G2422" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69358,7 +69355,7 @@
         <v>90.6399993896484</v>
       </c>
       <c r="G2423" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69384,7 +69381,7 @@
         <v>90.5199966430664</v>
       </c>
       <c r="G2424" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69410,7 +69407,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2425" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69436,7 +69433,7 @@
         <v>88.6800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69462,7 +69459,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G2427" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69488,7 +69485,7 @@
         <v>90.5</v>
       </c>
       <c r="G2428" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69514,7 +69511,7 @@
         <v>89</v>
       </c>
       <c r="G2429" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69540,7 +69537,7 @@
         <v>89.4800033569336</v>
       </c>
       <c r="G2430" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69566,7 +69563,7 @@
         <v>91.120002746582</v>
       </c>
       <c r="G2431" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69592,7 +69589,7 @@
         <v>90.9199981689453</v>
       </c>
       <c r="G2432" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69618,7 +69615,7 @@
         <v>90.5</v>
       </c>
       <c r="G2433" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69644,7 +69641,7 @@
         <v>90.2200012207031</v>
       </c>
       <c r="G2434" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69670,7 +69667,7 @@
         <v>89.8600006103516</v>
       </c>
       <c r="G2435" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69696,7 +69693,7 @@
         <v>88.1399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69722,7 +69719,7 @@
         <v>85.6999969482422</v>
       </c>
       <c r="G2437" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69748,7 +69745,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G2438" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69774,7 +69771,7 @@
         <v>85</v>
       </c>
       <c r="G2439" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69800,7 +69797,7 @@
         <v>85.2799987792969</v>
       </c>
       <c r="G2440" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69826,7 +69823,7 @@
         <v>83.4000015258789</v>
       </c>
       <c r="G2441" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69852,7 +69849,7 @@
         <v>83.5400009155273</v>
       </c>
       <c r="G2442" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69878,7 +69875,7 @@
         <v>82.9000015258789</v>
       </c>
       <c r="G2443" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69904,7 +69901,7 @@
         <v>82.4800033569336</v>
       </c>
       <c r="G2444" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69930,7 +69927,7 @@
         <v>82.3000030517578</v>
       </c>
       <c r="G2445" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69956,7 +69953,7 @@
         <v>83.2399978637695</v>
       </c>
       <c r="G2446" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69982,7 +69979,7 @@
         <v>84.0400009155273</v>
       </c>
       <c r="G2447" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -70008,7 +70005,7 @@
         <v>84.7399978637695</v>
       </c>
       <c r="G2448" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -70034,7 +70031,7 @@
         <v>85.9000015258789</v>
       </c>
       <c r="G2449" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -70060,7 +70057,7 @@
         <v>86.7399978637695</v>
       </c>
       <c r="G2450" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -70086,7 +70083,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G2451" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70112,7 +70109,7 @@
         <v>86.9400024414062</v>
       </c>
       <c r="G2452" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70138,7 +70135,7 @@
         <v>86.379997253418</v>
       </c>
       <c r="G2453" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70164,7 +70161,7 @@
         <v>90.4599990844727</v>
       </c>
       <c r="G2454" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70190,7 +70187,7 @@
         <v>85.1800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70216,7 +70213,7 @@
         <v>86</v>
       </c>
       <c r="G2456" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70242,7 +70239,7 @@
         <v>86.1800003051758</v>
       </c>
       <c r="G2457" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70268,7 +70265,7 @@
         <v>85.379997253418</v>
       </c>
       <c r="G2458" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70294,7 +70291,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2459" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70320,7 +70317,7 @@
         <v>85.2600021362305</v>
       </c>
       <c r="G2460" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70346,7 +70343,7 @@
         <v>82.5599975585938</v>
       </c>
       <c r="G2461" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70372,7 +70369,7 @@
         <v>82.3399963378906</v>
       </c>
       <c r="G2462" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70398,7 +70395,7 @@
         <v>82</v>
       </c>
       <c r="G2463" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70424,7 +70421,7 @@
         <v>82.0400009155273</v>
       </c>
       <c r="G2464" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70450,7 +70447,7 @@
         <v>81.5599975585938</v>
       </c>
       <c r="G2465" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70476,7 +70473,7 @@
         <v>80.0999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70502,7 +70499,7 @@
         <v>79.1399993896484</v>
       </c>
       <c r="G2467" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70528,7 +70525,7 @@
         <v>78.3000030517578</v>
       </c>
       <c r="G2468" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70554,7 +70551,7 @@
         <v>78</v>
       </c>
       <c r="G2469" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70580,7 +70577,7 @@
         <v>78.7200012207031</v>
       </c>
       <c r="G2470" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70606,7 +70603,7 @@
         <v>79</v>
       </c>
       <c r="G2471" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70632,7 +70629,7 @@
         <v>78.6600036621094</v>
       </c>
       <c r="G2472" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70658,7 +70655,7 @@
         <v>78.1800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1943</v>
+        <